--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FF51FC-7431-4262-8C45-7FA56BE9F970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D1F369-41F0-4695-94AC-40570846D454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="PL_F1a" sheetId="3" r:id="rId2"/>
-    <sheet name="PL_F1b" sheetId="4" r:id="rId3"/>
+    <sheet name="IT_F1a" sheetId="3" r:id="rId2"/>
+    <sheet name="IT_F1b" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>Description:</t>
   </si>
@@ -132,49 +132,36 @@
     <t>Y2020</t>
   </si>
   <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
-  </si>
-  <si>
-    <t>PL10</t>
+    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
+  </si>
+  <si>
+    <t>ITF</t>
+  </si>
+  <si>
+    <t>ITG</t>
+  </si>
+  <si>
+    <t>ITH</t>
+  </si>
+  <si>
+    <t>ITI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -187,28 +174,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -227,12 +193,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +532,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -579,7 +543,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -603,11 +567,11 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -617,14 +581,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>9</v>
       </c>
       <c r="C1" t="s">
@@ -637,126 +601,92 @@
         <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
-        <v>-0.33877183111340164</v>
+      <c r="B2">
+        <v>-1.9658875381585693E-3</v>
       </c>
       <c r="C2">
-        <v>5.9273678788696743E-3</v>
+        <v>1.6312345539927151E-2</v>
       </c>
       <c r="D2">
-        <v>-8.0783036998965723E-4</v>
+        <v>-1.1828889899364998E-2</v>
       </c>
       <c r="E2">
-        <v>1.7426093405267219E-2</v>
+        <v>4.7442327799468692E-2</v>
       </c>
       <c r="F2">
-        <v>7.3003900325142018E-3</v>
-      </c>
-      <c r="G2">
-        <v>-0.13268969440411649</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+        <v>-0.35302933071638515</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
-        <v>0.32659602149356004</v>
+      <c r="B3">
+        <v>0.14643989603547861</v>
       </c>
       <c r="C3">
-        <v>-8.0783036998965723E-4</v>
+        <v>-1.1828889899364998E-2</v>
       </c>
       <c r="D3">
-        <v>2.2626024511415942E-2</v>
+        <v>0.18750309379931057</v>
       </c>
       <c r="E3">
-        <v>5.10778215858438E-3</v>
+        <v>-0.15455786365213553</v>
       </c>
       <c r="F3">
-        <v>1.2537029016663603E-3</v>
-      </c>
-      <c r="G3">
-        <v>-8.0755321463503574E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+        <v>-0.42919776248276365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
-        <v>-0.96853811409855861</v>
+      <c r="B4">
+        <v>-0.48186314363830368</v>
       </c>
       <c r="C4">
-        <v>1.7426093405267219E-2</v>
+        <v>4.7442327799468692E-2</v>
       </c>
       <c r="D4">
-        <v>5.10778215858438E-3</v>
+        <v>-0.15455786365213553</v>
       </c>
       <c r="E4">
-        <v>0.14779296919533721</v>
+        <v>0.50907778618380339</v>
       </c>
       <c r="F4">
-        <v>9.0841112336903243E-2</v>
-      </c>
-      <c r="G4">
-        <v>-0.49105472984089227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4">
-        <v>-0.60092237408894833</v>
+        <v>-0.73373494833229547</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>-0.59270779555611164</v>
       </c>
       <c r="C5">
-        <v>7.3003900325142018E-3</v>
+        <v>-0.35302933071638515</v>
       </c>
       <c r="D5">
-        <v>1.2537029016663603E-3</v>
+        <v>-0.42919776248276365</v>
       </c>
       <c r="E5">
-        <v>9.0841112336903243E-2</v>
+        <v>-0.73373494833229547</v>
       </c>
       <c r="F5">
-        <v>0.34097859502626987</v>
-      </c>
-      <c r="G5">
-        <v>-0.24174421005554725</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4">
-        <v>6.4673633509546748</v>
-      </c>
-      <c r="C6">
-        <v>-0.13268969440411649</v>
-      </c>
-      <c r="D6">
-        <v>-8.0755321463503574E-2</v>
-      </c>
-      <c r="E6">
-        <v>-0.49105472984089227</v>
-      </c>
-      <c r="F6">
-        <v>-0.24174421005554725</v>
-      </c>
-      <c r="G6">
-        <v>3.4723866729624069</v>
-      </c>
+        <v>10.430772870143954</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -772,10 +702,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>9</v>
       </c>
       <c r="C1" t="s">
@@ -842,13 +772,13 @@
         <v>33</v>
       </c>
       <c r="X1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Z1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA1" t="s">
         <v>40</v>
@@ -867,2758 +797,2758 @@
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
-        <v>0.21222166754916791</v>
+      <c r="B2">
+        <v>0.25685035252636784</v>
       </c>
       <c r="C2">
-        <v>8.2670710700671977E-4</v>
+        <v>1.3521539366952381E-3</v>
       </c>
       <c r="D2">
-        <v>-1.1889967441694152E-5</v>
+        <v>-1.8754822350946112E-5</v>
       </c>
       <c r="E2">
-        <v>1.3954253592297309E-4</v>
+        <v>8.9056117468504226E-5</v>
       </c>
       <c r="F2">
-        <v>-1.5599553235947998E-4</v>
+        <v>6.7063061460856388E-5</v>
       </c>
       <c r="G2">
-        <v>-2.6702735423156908E-4</v>
+        <v>-9.5887305326766703E-5</v>
       </c>
       <c r="H2">
-        <v>-2.6739376720805869E-4</v>
+        <v>9.1379723694169634E-5</v>
       </c>
       <c r="I2">
-        <v>-3.3654092924715977E-4</v>
+        <v>-3.0072084295433218E-4</v>
       </c>
       <c r="J2">
-        <v>9.8342213252174994E-5</v>
+        <v>-9.0818006520796378E-5</v>
       </c>
       <c r="K2">
-        <v>-1.8877589968322069E-4</v>
+        <v>1.0206408574724157E-4</v>
       </c>
       <c r="L2">
-        <v>-1.0975709844830445E-4</v>
+        <v>1.1566475225018719E-4</v>
       </c>
       <c r="M2">
-        <v>-8.5185570430833853E-5</v>
+        <v>-4.0148122286011445E-5</v>
       </c>
       <c r="N2">
-        <v>-1.3499536097145645E-4</v>
+        <v>-8.9329145078764077E-5</v>
       </c>
       <c r="O2">
-        <v>7.6912382475424756E-5</v>
+        <v>-3.0777543329596566E-4</v>
       </c>
       <c r="P2">
-        <v>-1.1692880680639565E-4</v>
+        <v>1.7080749835791595E-5</v>
       </c>
       <c r="Q2">
-        <v>-7.3303706793806898E-5</v>
+        <v>1.520296086144089E-4</v>
       </c>
       <c r="R2">
-        <v>-2.5130572391913238E-4</v>
+        <v>-4.5032176654757634E-5</v>
       </c>
       <c r="S2">
-        <v>1.9243435626443449E-4</v>
+        <v>3.540702064387842E-5</v>
       </c>
       <c r="T2">
-        <v>4.4902128542772526E-4</v>
+        <v>1.5759634054272626E-4</v>
       </c>
       <c r="U2">
-        <v>2.3257402569426891E-4</v>
+        <v>6.7481258606760797E-4</v>
       </c>
       <c r="V2">
-        <v>1.036745703606724E-3</v>
+        <v>5.4872781593778841E-4</v>
       </c>
       <c r="W2">
-        <v>8.256034511573869E-5</v>
+        <v>1.3867767885126017E-4</v>
       </c>
       <c r="X2">
-        <v>4.255967225028686E-7</v>
+        <v>2.5913086894540846E-5</v>
       </c>
       <c r="Y2">
-        <v>-3.4369943042798063E-5</v>
+        <v>9.3965165858727467E-5</v>
       </c>
       <c r="Z2">
-        <v>5.7247109565838894E-6</v>
+        <v>-1.6917361960915034E-4</v>
       </c>
       <c r="AA2">
-        <v>-1.5838513064547559E-5</v>
+        <v>-3.875855575427925E-5</v>
       </c>
       <c r="AB2">
-        <v>5.9137605493958998E-6</v>
+        <v>2.7676159033733147E-5</v>
       </c>
       <c r="AC2">
-        <v>5.159375546955015E-5</v>
+        <v>-2.8837001124054889E-4</v>
       </c>
       <c r="AD2">
-        <v>2.5710270849494711E-5</v>
+        <v>-8.8906726277164852E-5</v>
       </c>
       <c r="AE2">
-        <v>-1.3815079267640334E-2</v>
+        <v>-2.4829431322037993E-2</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4">
-        <v>-4.4664697275741058E-3</v>
+      <c r="B3">
+        <v>-4.8096184442453487E-3</v>
       </c>
       <c r="C3">
-        <v>-1.1889967441694152E-5</v>
+        <v>-1.8754822350946112E-5</v>
       </c>
       <c r="D3">
-        <v>1.7303393143819542E-7</v>
+        <v>2.6308282537022193E-7</v>
       </c>
       <c r="E3">
-        <v>-2.1698517924429514E-6</v>
+        <v>-5.3490168679679387E-7</v>
       </c>
       <c r="F3">
-        <v>2.0828800479358259E-6</v>
+        <v>-1.2432081387031601E-7</v>
       </c>
       <c r="G3">
-        <v>3.6712026487779582E-6</v>
+        <v>1.4494476693503668E-6</v>
       </c>
       <c r="H3">
-        <v>3.4809970050741673E-6</v>
+        <v>-1.7199274866531414E-6</v>
       </c>
       <c r="I3">
-        <v>4.9164130985844696E-6</v>
+        <v>4.0778520476240335E-6</v>
       </c>
       <c r="J3">
-        <v>-8.4759990998648817E-7</v>
+        <v>2.1578858707211663E-6</v>
       </c>
       <c r="K3">
-        <v>3.0324858947823705E-6</v>
+        <v>-1.4554829651541759E-6</v>
       </c>
       <c r="L3">
-        <v>2.2771119802513846E-6</v>
+        <v>-1.5482169949105717E-6</v>
       </c>
       <c r="M3">
-        <v>2.0995616541072575E-6</v>
+        <v>9.6509726436080608E-7</v>
       </c>
       <c r="N3">
-        <v>3.0967256168015677E-6</v>
+        <v>1.4300579061547161E-6</v>
       </c>
       <c r="O3">
-        <v>-1.2798079003760058E-6</v>
+        <v>3.7347654422265314E-6</v>
       </c>
       <c r="P3">
-        <v>2.0231536991994901E-6</v>
+        <v>-4.9467523507792E-7</v>
       </c>
       <c r="Q3">
-        <v>1.7874509792603665E-6</v>
+        <v>-1.6566145337345119E-6</v>
       </c>
       <c r="R3">
-        <v>3.9857705274844041E-6</v>
+        <v>6.1326581762181589E-7</v>
       </c>
       <c r="S3">
-        <v>-2.8319923634328983E-6</v>
+        <v>-9.1955951857247437E-9</v>
       </c>
       <c r="T3">
-        <v>-6.4012366243920116E-6</v>
+        <v>-1.9322631231452825E-6</v>
       </c>
       <c r="U3">
-        <v>-2.9933107869743519E-6</v>
+        <v>-1.4569497607665009E-6</v>
       </c>
       <c r="V3">
-        <v>-1.417677093281909E-5</v>
+        <v>-7.0509937480622278E-6</v>
       </c>
       <c r="W3">
-        <v>-9.7725192968876098E-7</v>
+        <v>-2.2688969186693666E-6</v>
       </c>
       <c r="X3">
-        <v>-9.8252358527322638E-9</v>
+        <v>-7.9257668560221402E-7</v>
       </c>
       <c r="Y3">
-        <v>4.5168458805109964E-7</v>
+        <v>-1.4457021524091158E-6</v>
       </c>
       <c r="Z3">
-        <v>1.5333999195543346E-8</v>
+        <v>2.4065892310144482E-6</v>
       </c>
       <c r="AA3">
-        <v>2.6570736051742815E-7</v>
+        <v>3.0475044868048156E-7</v>
       </c>
       <c r="AB3">
-        <v>-1.1857098752095007E-7</v>
+        <v>-2.0298817239389688E-7</v>
       </c>
       <c r="AC3">
-        <v>-8.1506749543800876E-7</v>
+        <v>3.7089664899785427E-6</v>
       </c>
       <c r="AD3">
-        <v>-4.0582316391967095E-7</v>
+        <v>1.0264545465087224E-6</v>
       </c>
       <c r="AE3">
-        <v>1.9533488433813129E-4</v>
+        <v>3.2634569391603403E-4</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4">
-        <v>0.31855061702804771</v>
+      <c r="B4">
+        <v>-0.29118186561899223</v>
       </c>
       <c r="C4">
-        <v>1.3954253592297309E-4</v>
+        <v>8.9056117468504226E-5</v>
       </c>
       <c r="D4">
-        <v>-2.1698517924429514E-6</v>
+        <v>-5.3490168679679387E-7</v>
       </c>
       <c r="E4">
-        <v>1.8517432113345257E-2</v>
+        <v>2.4237931065596883E-2</v>
       </c>
       <c r="F4">
-        <v>1.1320569731069548E-2</v>
+        <v>1.5644749416402162E-2</v>
       </c>
       <c r="G4">
-        <v>1.1280306269238073E-2</v>
+        <v>1.5527379691744369E-2</v>
       </c>
       <c r="H4">
-        <v>1.1290573524496765E-2</v>
+        <v>1.5418119334999938E-2</v>
       </c>
       <c r="I4">
-        <v>6.7062584488728307E-5</v>
+        <v>-1.0753962923125821E-3</v>
       </c>
       <c r="J4">
-        <v>1.9036617985941987E-5</v>
+        <v>1.0366554294107006E-3</v>
       </c>
       <c r="K4">
-        <v>2.8581898359109591E-4</v>
+        <v>-7.7187129409041037E-5</v>
       </c>
       <c r="L4">
-        <v>1.9187935253608566E-4</v>
+        <v>1.100302661056701E-3</v>
       </c>
       <c r="M4">
-        <v>2.6102082543709784E-5</v>
+        <v>-8.7757110840701574E-5</v>
       </c>
       <c r="N4">
-        <v>1.4441779640450439E-4</v>
+        <v>-1.4947585475790814E-3</v>
       </c>
       <c r="O4">
-        <v>-1.7894663167861979E-3</v>
+        <v>1.2088369009304446E-5</v>
       </c>
       <c r="P4">
-        <v>-1.2299244315679115E-3</v>
+        <v>-3.7145430702920255E-3</v>
       </c>
       <c r="Q4">
-        <v>8.4570820704380021E-4</v>
+        <v>9.8258554659475298E-4</v>
       </c>
       <c r="R4">
-        <v>7.0392566944827827E-4</v>
+        <v>3.3292275234410606E-3</v>
       </c>
       <c r="S4">
-        <v>9.9688721730346614E-5</v>
+        <v>1.3206990312926962E-4</v>
       </c>
       <c r="T4">
-        <v>-5.009227910631991E-4</v>
+        <v>-3.7923012566569328E-4</v>
       </c>
       <c r="U4">
-        <v>-1.1482362773312244E-3</v>
+        <v>-2.9596719659817005E-3</v>
       </c>
       <c r="V4">
-        <v>1.1254545305906362E-3</v>
+        <v>1.2881052067806157E-3</v>
       </c>
       <c r="W4">
-        <v>-3.3471972248961439E-5</v>
+        <v>5.6124109139208593E-4</v>
       </c>
       <c r="X4">
-        <v>2.2856607472792245E-4</v>
+        <v>-5.6944476809105203E-4</v>
       </c>
       <c r="Y4">
-        <v>3.1057699376862123E-4</v>
+        <v>8.8462643243483719E-4</v>
       </c>
       <c r="Z4">
-        <v>1.7767527515970575E-4</v>
+        <v>-3.6064803144921593E-5</v>
       </c>
       <c r="AA4">
-        <v>2.8429778853909923E-4</v>
+        <v>1.555712424833489E-4</v>
       </c>
       <c r="AB4">
-        <v>-1.5808479232049642E-5</v>
+        <v>-4.1240557598391076E-5</v>
       </c>
       <c r="AC4">
-        <v>2.3912491505732447E-4</v>
+        <v>-3.3106782533749848E-4</v>
       </c>
       <c r="AD4">
-        <v>3.1818351229789257E-4</v>
+        <v>1.9770032406867682E-4</v>
       </c>
       <c r="AE4">
-        <v>-1.2059508707464417E-2</v>
+        <v>-1.2387257461297358E-2</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
-        <v>0.1844490687169042</v>
+      <c r="B5">
+        <v>-0.25374958465246789</v>
       </c>
       <c r="C5">
-        <v>-1.5599553235947998E-4</v>
+        <v>6.7063061460856388E-5</v>
       </c>
       <c r="D5">
-        <v>2.0828800479358259E-6</v>
+        <v>-1.2432081387031601E-7</v>
       </c>
       <c r="E5">
-        <v>1.1320569731069548E-2</v>
+        <v>1.5644749416402162E-2</v>
       </c>
       <c r="F5">
-        <v>1.2872111649297965E-2</v>
+        <v>1.7279542876207886E-2</v>
       </c>
       <c r="G5">
-        <v>1.2292005584855248E-2</v>
+        <v>1.6081353893827761E-2</v>
       </c>
       <c r="H5">
-        <v>1.2426352354062968E-2</v>
+        <v>1.6062702318711868E-2</v>
       </c>
       <c r="I5">
-        <v>7.9250022030465344E-5</v>
+        <v>-8.7380584592961679E-4</v>
       </c>
       <c r="J5">
-        <v>-3.7778947827987134E-5</v>
+        <v>1.042648556051197E-3</v>
       </c>
       <c r="K5">
-        <v>-3.2499269089043652E-5</v>
+        <v>-3.4233027565256941E-4</v>
       </c>
       <c r="L5">
-        <v>2.6041787162320654E-5</v>
+        <v>-1.5159552284008809E-4</v>
       </c>
       <c r="M5">
-        <v>-7.0223993073513079E-5</v>
+        <v>-4.144254055447839E-4</v>
       </c>
       <c r="N5">
-        <v>2.5516700505571251E-5</v>
+        <v>-1.7746651959421539E-3</v>
       </c>
       <c r="O5">
-        <v>-3.0266143440537893E-4</v>
+        <v>-7.1864096380589489E-4</v>
       </c>
       <c r="P5">
-        <v>-1.8572697416285927E-3</v>
+        <v>-3.5958768533381784E-3</v>
       </c>
       <c r="Q5">
-        <v>1.3745203024877932E-3</v>
+        <v>2.1904230782756311E-3</v>
       </c>
       <c r="R5">
-        <v>1.9093028696430976E-3</v>
+        <v>3.931381177573569E-3</v>
       </c>
       <c r="S5">
-        <v>-5.1143586603134314E-5</v>
+        <v>2.8870103684609013E-4</v>
       </c>
       <c r="T5">
-        <v>-3.9607453399681308E-4</v>
+        <v>-3.5511976392773979E-4</v>
       </c>
       <c r="U5">
-        <v>-7.9171013475877808E-4</v>
+        <v>3.2629992669071795E-3</v>
       </c>
       <c r="V5">
-        <v>1.7154813598231292E-3</v>
+        <v>1.8284194929131326E-3</v>
       </c>
       <c r="W5">
-        <v>4.3733593379901355E-4</v>
+        <v>6.4064025476095999E-4</v>
       </c>
       <c r="X5">
-        <v>2.2090543634875268E-4</v>
+        <v>-4.6659838500573642E-4</v>
       </c>
       <c r="Y5">
-        <v>2.9942339633353343E-4</v>
+        <v>1.1539576645116312E-3</v>
       </c>
       <c r="Z5">
-        <v>1.9853308174726752E-4</v>
+        <v>-2.7223485210811898E-4</v>
       </c>
       <c r="AA5">
-        <v>2.7598110523056212E-4</v>
+        <v>-1.6058912491110668E-4</v>
       </c>
       <c r="AB5">
-        <v>-1.4929545295904917E-5</v>
+        <v>7.8199851678291627E-5</v>
       </c>
       <c r="AC5">
-        <v>-3.279483099759891E-5</v>
+        <v>-3.8058554416651037E-4</v>
       </c>
       <c r="AD5">
-        <v>2.3388041275380824E-4</v>
+        <v>3.3909788902428654E-4</v>
       </c>
       <c r="AE5">
-        <v>-8.55532189017464E-3</v>
+        <v>-2.2905120743896279E-2</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4">
-        <v>0.27446037376774834</v>
+      <c r="B6">
+        <v>-0.21214793782289593</v>
       </c>
       <c r="C6">
-        <v>-2.6702735423156908E-4</v>
+        <v>-9.5887305326766703E-5</v>
       </c>
       <c r="D6">
-        <v>3.6712026487779582E-6</v>
+        <v>1.4494476693503668E-6</v>
       </c>
       <c r="E6">
-        <v>1.1280306269238073E-2</v>
+        <v>1.5527379691744369E-2</v>
       </c>
       <c r="F6">
-        <v>1.2292005584855248E-2</v>
+        <v>1.6081353893827761E-2</v>
       </c>
       <c r="G6">
-        <v>1.332486449366245E-2</v>
+        <v>1.7977515760037768E-2</v>
       </c>
       <c r="H6">
-        <v>1.2924970267410255E-2</v>
+        <v>1.7405567007719766E-2</v>
       </c>
       <c r="I6">
-        <v>1.9133704315979017E-4</v>
+        <v>-9.3296917241863478E-4</v>
       </c>
       <c r="J6">
-        <v>-9.2012767221337499E-5</v>
+        <v>8.3763844462088669E-4</v>
       </c>
       <c r="K6">
-        <v>7.6892589997919723E-4</v>
+        <v>-6.0811684368765242E-4</v>
       </c>
       <c r="L6">
-        <v>1.7683144426818096E-4</v>
+        <v>-2.4672873281724426E-4</v>
       </c>
       <c r="M6">
-        <v>3.0609222464490424E-5</v>
+        <v>-9.1678912365764087E-4</v>
       </c>
       <c r="N6">
-        <v>1.8268207282184663E-4</v>
+        <v>-2.0758450549380461E-3</v>
       </c>
       <c r="O6">
-        <v>-3.2937110831517818E-5</v>
+        <v>-1.8702395239357105E-4</v>
       </c>
       <c r="P6">
-        <v>-2.0252793650416588E-3</v>
+        <v>-3.1549629000851712E-3</v>
       </c>
       <c r="Q6">
-        <v>1.4044007377681978E-3</v>
+        <v>2.213426846800716E-3</v>
       </c>
       <c r="R6">
-        <v>2.2619350017223068E-3</v>
+        <v>4.2960331845344601E-3</v>
       </c>
       <c r="S6">
-        <v>7.4599790917970381E-5</v>
+        <v>4.6045447648880621E-5</v>
       </c>
       <c r="T6">
-        <v>-1.931234465921913E-4</v>
+        <v>-9.5926360009204389E-6</v>
       </c>
       <c r="U6">
-        <v>-8.0763066515607794E-4</v>
+        <v>-9.347311100260304E-3</v>
       </c>
       <c r="V6">
-        <v>1.8108383199628032E-3</v>
+        <v>2.8534725468392086E-3</v>
       </c>
       <c r="W6">
-        <v>7.7486338378691662E-4</v>
+        <v>1.7134888506063516E-3</v>
       </c>
       <c r="X6">
-        <v>1.4899534601413875E-4</v>
+        <v>5.7599084600067161E-4</v>
       </c>
       <c r="Y6">
-        <v>3.6094664196645993E-4</v>
+        <v>2.0178087705291104E-3</v>
       </c>
       <c r="Z6">
-        <v>2.2530322637951653E-4</v>
+        <v>3.111905074119673E-4</v>
       </c>
       <c r="AA6">
-        <v>3.9546046006957644E-4</v>
+        <v>5.2490679053886951E-4</v>
       </c>
       <c r="AB6">
-        <v>-2.6689480399168821E-6</v>
+        <v>-1.9824853210931477E-4</v>
       </c>
       <c r="AC6">
-        <v>1.3158211822331036E-5</v>
+        <v>-1.1234744616190403E-4</v>
       </c>
       <c r="AD6">
-        <v>1.7514425447485776E-4</v>
+        <v>-3.9797461241870326E-4</v>
       </c>
       <c r="AE6">
-        <v>-7.707975565897307E-3</v>
+        <v>9.8791132255200004E-4</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4">
-        <v>0.37612250848583589</v>
+      <c r="B7">
+        <v>-3.794438309381995E-2</v>
       </c>
       <c r="C7">
-        <v>-2.6739376720805869E-4</v>
+        <v>9.1379723694169634E-5</v>
       </c>
       <c r="D7">
-        <v>3.4809970050741673E-6</v>
+        <v>-1.7199274866531414E-6</v>
       </c>
       <c r="E7">
-        <v>1.1290573524496765E-2</v>
+        <v>1.5418119334999938E-2</v>
       </c>
       <c r="F7">
-        <v>1.2426352354062968E-2</v>
+        <v>1.6062702318711868E-2</v>
       </c>
       <c r="G7">
-        <v>1.2924970267410255E-2</v>
+        <v>1.7405567007719766E-2</v>
       </c>
       <c r="H7">
-        <v>1.3839772299190145E-2</v>
+        <v>1.8747611972098236E-2</v>
       </c>
       <c r="I7">
-        <v>2.6026229509901243E-4</v>
+        <v>-8.3642587193154391E-4</v>
       </c>
       <c r="J7">
-        <v>-2.7422635542860996E-5</v>
+        <v>6.9468304637078327E-4</v>
       </c>
       <c r="K7">
-        <v>5.5371939317197961E-4</v>
+        <v>-6.4440130927274821E-4</v>
       </c>
       <c r="L7">
-        <v>2.0751314813649601E-4</v>
+        <v>-3.7285510514678197E-4</v>
       </c>
       <c r="M7">
-        <v>4.9513434686500497E-5</v>
+        <v>-1.1755351696067029E-3</v>
       </c>
       <c r="N7">
-        <v>1.4798977583223988E-4</v>
+        <v>-2.1963310811363417E-3</v>
       </c>
       <c r="O7">
-        <v>-2.0728071272302102E-4</v>
+        <v>2.6773540035407786E-5</v>
       </c>
       <c r="P7">
-        <v>-1.9193945033023304E-3</v>
+        <v>-2.8924257736682841E-3</v>
       </c>
       <c r="Q7">
-        <v>1.6537914542798754E-3</v>
+        <v>2.5474791375352645E-3</v>
       </c>
       <c r="R7">
-        <v>2.4738952248091104E-3</v>
+        <v>4.4855638125146794E-3</v>
       </c>
       <c r="S7">
-        <v>3.2980722929104134E-4</v>
+        <v>1.64285748659745E-4</v>
       </c>
       <c r="T7">
-        <v>4.4393048925213049E-5</v>
+        <v>3.5676189873261462E-4</v>
       </c>
       <c r="U7">
-        <v>-1.1885843689452662E-3</v>
+        <v>-1.0010428841263685E-2</v>
       </c>
       <c r="V7">
-        <v>1.7954571935368513E-3</v>
+        <v>3.0473936062167788E-3</v>
       </c>
       <c r="W7">
-        <v>8.621738419492082E-4</v>
+        <v>2.0052115667627927E-3</v>
       </c>
       <c r="X7">
-        <v>1.3861162955907996E-4</v>
+        <v>6.9347205352700454E-4</v>
       </c>
       <c r="Y7">
-        <v>2.8059981020544682E-4</v>
+        <v>2.275508788050011E-3</v>
       </c>
       <c r="Z7">
-        <v>2.605508110060199E-4</v>
+        <v>3.1228006393693979E-4</v>
       </c>
       <c r="AA7">
-        <v>4.0835041409025886E-4</v>
+        <v>7.0290194679995498E-4</v>
       </c>
       <c r="AB7">
-        <v>6.4342486495588409E-6</v>
+        <v>-2.275053647680643E-4</v>
       </c>
       <c r="AC7">
-        <v>5.1524792219336413E-5</v>
+        <v>-1.7836881509195371E-4</v>
       </c>
       <c r="AD7">
-        <v>1.6785572366683236E-4</v>
+        <v>-3.5256610842830015E-4</v>
       </c>
       <c r="AE7">
-        <v>-7.6562263933973307E-3</v>
+        <v>-7.1839709934884421E-4</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4">
-        <v>-0.41306030413085165</v>
+      <c r="B8">
+        <v>-0.36878326658701727</v>
       </c>
       <c r="C8">
-        <v>-3.3654092924715977E-4</v>
+        <v>-3.0072084295433218E-4</v>
       </c>
       <c r="D8">
-        <v>4.9164130985844696E-6</v>
+        <v>4.0778520476240335E-6</v>
       </c>
       <c r="E8">
-        <v>6.7062584488728307E-5</v>
+        <v>-1.0753962923125821E-3</v>
       </c>
       <c r="F8">
-        <v>7.9250022030465344E-5</v>
+        <v>-8.7380584592961679E-4</v>
       </c>
       <c r="G8">
-        <v>1.9133704315979017E-4</v>
+        <v>-9.3296917241863478E-4</v>
       </c>
       <c r="H8">
-        <v>2.6026229509901243E-4</v>
+        <v>-8.3642587193154391E-4</v>
       </c>
       <c r="I8">
-        <v>7.0922058417701871E-4</v>
+        <v>1.1663985903579467E-3</v>
       </c>
       <c r="J8">
-        <v>-2.0170762753444441E-4</v>
+        <v>-3.1923651000350804E-4</v>
       </c>
       <c r="K8">
-        <v>7.2478399788315729E-4</v>
+        <v>1.3990869178578773E-4</v>
       </c>
       <c r="L8">
-        <v>4.4363445549170971E-5</v>
+        <v>1.6090711830415863E-4</v>
       </c>
       <c r="M8">
-        <v>1.4275141007548311E-6</v>
+        <v>1.0199937074932813E-4</v>
       </c>
       <c r="N8">
-        <v>1.522459078858048E-6</v>
+        <v>3.1896410036064138E-4</v>
       </c>
       <c r="O8">
-        <v>-3.7220929695892715E-4</v>
+        <v>-1.7523152869481523E-4</v>
       </c>
       <c r="P8">
-        <v>-2.2424052881128437E-4</v>
+        <v>-2.4439620415757412E-4</v>
       </c>
       <c r="Q8">
-        <v>5.0848613629210786E-4</v>
+        <v>4.7308982556767574E-4</v>
       </c>
       <c r="R8">
-        <v>4.071472439698908E-4</v>
+        <v>2.3158615364190312E-4</v>
       </c>
       <c r="S8">
-        <v>3.9436415991214404E-6</v>
+        <v>1.3562733082982104E-4</v>
       </c>
       <c r="T8">
-        <v>-1.2530241957560461E-4</v>
+        <v>5.6902944001849785E-5</v>
       </c>
       <c r="U8">
-        <v>-4.0315965918530892E-5</v>
+        <v>3.4933142166057168E-3</v>
       </c>
       <c r="V8">
-        <v>-2.3002156782194079E-4</v>
+        <v>-3.6181095557555679E-4</v>
       </c>
       <c r="W8">
-        <v>-5.3974580672169834E-5</v>
+        <v>-2.767875043506819E-4</v>
       </c>
       <c r="X8">
-        <v>1.596535067560154E-5</v>
+        <v>-7.7850032275234428E-5</v>
       </c>
       <c r="Y8">
-        <v>1.0238385191772319E-4</v>
+        <v>-2.9617804134391724E-4</v>
       </c>
       <c r="Z8">
-        <v>3.4609419491087924E-5</v>
+        <v>-2.7750551696720379E-4</v>
       </c>
       <c r="AA8">
-        <v>3.9438556723504873E-5</v>
+        <v>-2.165427260908937E-4</v>
       </c>
       <c r="AB8">
-        <v>-2.7214548413133252E-6</v>
+        <v>7.9762339600379759E-5</v>
       </c>
       <c r="AC8">
-        <v>-2.5578364481533339E-5</v>
+        <v>-4.8693203654902339E-5</v>
       </c>
       <c r="AD8">
-        <v>-5.9407444466610905E-5</v>
+        <v>-2.8823954779161811E-5</v>
       </c>
       <c r="AE8">
-        <v>4.6719183804137653E-3</v>
+        <v>-9.458810079688261E-4</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4">
-        <v>0.56093378671650429</v>
+      <c r="B9">
+        <v>0.67214032524460321</v>
       </c>
       <c r="C9">
-        <v>9.8342213252174994E-5</v>
+        <v>-9.0818006520796378E-5</v>
       </c>
       <c r="D9">
-        <v>-8.4759990998648817E-7</v>
+        <v>2.1578858707211663E-6</v>
       </c>
       <c r="E9">
-        <v>1.9036617985941987E-5</v>
+        <v>1.0366554294107006E-3</v>
       </c>
       <c r="F9">
-        <v>-3.7778947827987134E-5</v>
+        <v>1.042648556051197E-3</v>
       </c>
       <c r="G9">
-        <v>-9.2012767221337499E-5</v>
+        <v>8.3763844462088669E-4</v>
       </c>
       <c r="H9">
-        <v>-2.7422635542860996E-5</v>
+        <v>6.9468304637078327E-4</v>
       </c>
       <c r="I9">
-        <v>-2.0170762753444441E-4</v>
+        <v>-3.1923651000350804E-4</v>
       </c>
       <c r="J9">
-        <v>1.0699542184820158E-3</v>
+        <v>1.5034699600935263E-3</v>
       </c>
       <c r="K9">
-        <v>-3.9693372344789049E-4</v>
+        <v>1.2342586240111832E-5</v>
       </c>
       <c r="L9">
-        <v>7.9312139127565699E-5</v>
+        <v>-3.9642029046557149E-5</v>
       </c>
       <c r="M9">
-        <v>2.0941614992615442E-5</v>
+        <v>-1.4671884627497078E-5</v>
       </c>
       <c r="N9">
-        <v>4.2723370883815132E-5</v>
+        <v>-2.323026270710485E-4</v>
       </c>
       <c r="O9">
-        <v>-3.1072209107085641E-5</v>
+        <v>-1.591639233410909E-4</v>
       </c>
       <c r="P9">
-        <v>2.099508191540614E-4</v>
+        <v>-2.2770236902859282E-5</v>
       </c>
       <c r="Q9">
-        <v>2.0846562536907653E-4</v>
+        <v>1.8110745063063219E-4</v>
       </c>
       <c r="R9">
-        <v>1.2881571186473638E-4</v>
+        <v>1.9570457331374391E-4</v>
       </c>
       <c r="S9">
-        <v>1.4029386085416724E-4</v>
+        <v>2.6685097109928075E-4</v>
       </c>
       <c r="T9">
-        <v>2.2074305865028154E-4</v>
+        <v>4.0082971452603519E-4</v>
       </c>
       <c r="U9">
-        <v>3.2994248329018538E-5</v>
+        <v>-3.1950436091474632E-3</v>
       </c>
       <c r="V9">
-        <v>-3.1131398564071446E-5</v>
+        <v>4.4284971095989549E-5</v>
       </c>
       <c r="W9">
-        <v>-1.514370799753645E-4</v>
+        <v>-1.1080150184194208E-4</v>
       </c>
       <c r="X9">
-        <v>-1.51395986420455E-5</v>
+        <v>-2.9735276442375153E-4</v>
       </c>
       <c r="Y9">
-        <v>-7.9660085159065244E-5</v>
+        <v>3.1027127734345765E-5</v>
       </c>
       <c r="Z9">
-        <v>5.1172868672602211E-5</v>
+        <v>-6.2188839705147776E-5</v>
       </c>
       <c r="AA9">
-        <v>-1.7265724705360424E-5</v>
+        <v>-1.6239261766208763E-4</v>
       </c>
       <c r="AB9">
-        <v>-2.7829571149668148E-6</v>
+        <v>-2.1941907255594692E-5</v>
       </c>
       <c r="AC9">
-        <v>-3.9288890784926135E-5</v>
+        <v>-2.9354741869922976E-4</v>
       </c>
       <c r="AD9">
-        <v>-3.1125863325718868E-5</v>
+        <v>-2.8384302803011391E-4</v>
       </c>
       <c r="AE9">
-        <v>-2.4581550854899849E-3</v>
+        <v>4.0779576794641205E-3</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4">
-        <v>-0.64712382259869561</v>
+      <c r="B10">
+        <v>7.7875191533664359E-2</v>
       </c>
       <c r="C10">
-        <v>-1.8877589968322069E-4</v>
+        <v>1.0206408574724157E-4</v>
       </c>
       <c r="D10">
-        <v>3.0324858947823705E-6</v>
+        <v>-1.4554829651541759E-6</v>
       </c>
       <c r="E10">
-        <v>2.8581898359109591E-4</v>
+        <v>-7.7187129409041037E-5</v>
       </c>
       <c r="F10">
-        <v>-3.2499269089043652E-5</v>
+        <v>-3.4233027565256941E-4</v>
       </c>
       <c r="G10">
-        <v>7.6892589997919723E-4</v>
+        <v>-6.0811684368765242E-4</v>
       </c>
       <c r="H10">
-        <v>5.5371939317197961E-4</v>
+        <v>-6.4440130927274821E-4</v>
       </c>
       <c r="I10">
-        <v>7.2478399788315729E-4</v>
+        <v>1.3990869178578773E-4</v>
       </c>
       <c r="J10">
-        <v>-3.9693372344789049E-4</v>
+        <v>1.2342586240111832E-5</v>
       </c>
       <c r="K10">
-        <v>0.11059377411863093</v>
+        <v>0.10246192973057192</v>
       </c>
       <c r="L10">
-        <v>8.3630292960545305E-2</v>
+        <v>7.9886352808894612E-2</v>
       </c>
       <c r="M10">
-        <v>8.3623036902625292E-2</v>
+        <v>7.9842090227712076E-2</v>
       </c>
       <c r="N10">
-        <v>8.3746692955021212E-2</v>
+        <v>7.9894971220947242E-2</v>
       </c>
       <c r="O10">
-        <v>-1.8266617968796389E-4</v>
+        <v>-3.7678059934378311E-4</v>
       </c>
       <c r="P10">
-        <v>-2.5036297542995606E-4</v>
+        <v>4.6101678998815288E-4</v>
       </c>
       <c r="Q10">
-        <v>1.9792630229049923E-4</v>
+        <v>2.9224530749283936E-4</v>
       </c>
       <c r="R10">
-        <v>4.0043684536892818E-4</v>
+        <v>-1.1255759961693763E-3</v>
       </c>
       <c r="S10">
-        <v>4.6918374592145543E-4</v>
+        <v>-1.1910415951903869E-4</v>
       </c>
       <c r="T10">
-        <v>5.5604009335982404E-5</v>
+        <v>2.4255833903196258E-4</v>
       </c>
       <c r="U10">
-        <v>5.5119593287239477E-4</v>
+        <v>-7.2647788215747244E-3</v>
       </c>
       <c r="V10">
-        <v>-1.0509328676614957E-4</v>
+        <v>-5.9380501088227011E-4</v>
       </c>
       <c r="W10">
-        <v>-1.7030843422933747E-4</v>
+        <v>-1.7200455675944748E-4</v>
       </c>
       <c r="X10">
-        <v>-3.8045096765947257E-4</v>
+        <v>1.6603513771593775E-4</v>
       </c>
       <c r="Y10">
-        <v>-2.4582271198870403E-4</v>
+        <v>-4.778326837388408E-4</v>
       </c>
       <c r="Z10">
-        <v>-1.284220570935005E-4</v>
+        <v>-3.8246733922961407E-4</v>
       </c>
       <c r="AA10">
-        <v>4.6902342506572204E-4</v>
+        <v>2.5723409530692409E-5</v>
       </c>
       <c r="AB10">
-        <v>-2.8285873803390448E-5</v>
+        <v>-1.2153932766847259E-4</v>
       </c>
       <c r="AC10">
-        <v>1.2965498805307535E-3</v>
+        <v>6.4573110388512628E-4</v>
       </c>
       <c r="AD10">
-        <v>1.7246407844620504E-4</v>
+        <v>-7.1332150796014036E-5</v>
       </c>
       <c r="AE10">
-        <v>-8.2742245904287581E-2</v>
+        <v>-6.9344512243916911E-2</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4">
-        <v>-0.55221004929509876</v>
+      <c r="B11">
+        <v>0.14500304335468325</v>
       </c>
       <c r="C11">
-        <v>-1.0975709844830445E-4</v>
+        <v>1.1566475225018719E-4</v>
       </c>
       <c r="D11">
-        <v>2.2771119802513846E-6</v>
+        <v>-1.5482169949105717E-6</v>
       </c>
       <c r="E11">
-        <v>1.9187935253608566E-4</v>
+        <v>1.100302661056701E-3</v>
       </c>
       <c r="F11">
-        <v>2.6041787162320654E-5</v>
+        <v>-1.5159552284008809E-4</v>
       </c>
       <c r="G11">
-        <v>1.7683144426818096E-4</v>
+        <v>-2.4672873281724426E-4</v>
       </c>
       <c r="H11">
-        <v>2.0751314813649601E-4</v>
+        <v>-3.7285510514678197E-4</v>
       </c>
       <c r="I11">
-        <v>4.4363445549170971E-5</v>
+        <v>1.6090711830415863E-4</v>
       </c>
       <c r="J11">
-        <v>7.9312139127565699E-5</v>
+        <v>-3.9642029046557149E-5</v>
       </c>
       <c r="K11">
-        <v>8.3630292960545305E-2</v>
+        <v>7.9886352808894612E-2</v>
       </c>
       <c r="L11">
-        <v>8.617942676225436E-2</v>
+        <v>8.4401554231552184E-2</v>
       </c>
       <c r="M11">
-        <v>8.4019119390448399E-2</v>
+        <v>7.9900025866150332E-2</v>
       </c>
       <c r="N11">
-        <v>8.4076260911171707E-2</v>
+        <v>7.9858906155957976E-2</v>
       </c>
       <c r="O11">
-        <v>9.5346709301363797E-6</v>
+        <v>-8.6859376383478099E-4</v>
       </c>
       <c r="P11">
-        <v>3.7303760612540648E-5</v>
+        <v>6.8685794684207602E-4</v>
       </c>
       <c r="Q11">
-        <v>-4.4398154379718391E-5</v>
+        <v>7.1041138971651707E-4</v>
       </c>
       <c r="R11">
-        <v>1.6280482176972422E-4</v>
+        <v>-8.6346397203709152E-4</v>
       </c>
       <c r="S11">
-        <v>4.2441989283114841E-5</v>
+        <v>-2.2862063244203507E-4</v>
       </c>
       <c r="T11">
-        <v>2.5658339404524035E-4</v>
+        <v>1.7847483114818985E-4</v>
       </c>
       <c r="U11">
-        <v>-1.6059617628885747E-4</v>
+        <v>-3.649038641633684E-3</v>
       </c>
       <c r="V11">
-        <v>3.7888829995916251E-4</v>
+        <v>-3.1392029688528944E-4</v>
       </c>
       <c r="W11">
-        <v>4.0183811021562987E-4</v>
+        <v>6.3305338590252669E-5</v>
       </c>
       <c r="X11">
-        <v>-3.7671397780852066E-4</v>
+        <v>7.2134580263658044E-5</v>
       </c>
       <c r="Y11">
-        <v>-3.4137581956191192E-4</v>
+        <v>-4.3427722434931371E-4</v>
       </c>
       <c r="Z11">
-        <v>-1.2230621992551528E-4</v>
+        <v>-3.3983709615911795E-4</v>
       </c>
       <c r="AA11">
-        <v>-1.0161682224577289E-4</v>
+        <v>-1.5114739733154692E-4</v>
       </c>
       <c r="AB11">
-        <v>-1.3468760293948025E-5</v>
+        <v>-6.3188053292702329E-5</v>
       </c>
       <c r="AC11">
-        <v>-6.8579148196939999E-5</v>
+        <v>1.084405486169622E-3</v>
       </c>
       <c r="AD11">
-        <v>-2.1924498427777772E-5</v>
+        <v>8.4224755973066195E-5</v>
       </c>
       <c r="AE11">
-        <v>-8.2753910604096759E-2</v>
+        <v>-7.592401252361336E-2</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="4">
-        <v>-0.41366978380732133</v>
+      <c r="B12">
+        <v>0.24475747577542964</v>
       </c>
       <c r="C12">
-        <v>-8.5185570430833853E-5</v>
+        <v>-4.0148122286011445E-5</v>
       </c>
       <c r="D12">
-        <v>2.0995616541072575E-6</v>
+        <v>9.6509726436080608E-7</v>
       </c>
       <c r="E12">
-        <v>2.6102082543709784E-5</v>
+        <v>-8.7757110840701574E-5</v>
       </c>
       <c r="F12">
-        <v>-7.0223993073513079E-5</v>
+        <v>-4.144254055447839E-4</v>
       </c>
       <c r="G12">
-        <v>3.0609222464490424E-5</v>
+        <v>-9.1678912365764087E-4</v>
       </c>
       <c r="H12">
-        <v>4.9513434686500497E-5</v>
+        <v>-1.1755351696067029E-3</v>
       </c>
       <c r="I12">
-        <v>1.4275141007548311E-6</v>
+        <v>1.0199937074932813E-4</v>
       </c>
       <c r="J12">
-        <v>2.0941614992615442E-5</v>
+        <v>-1.4671884627497078E-5</v>
       </c>
       <c r="K12">
-        <v>8.3623036902625292E-2</v>
+        <v>7.9842090227712076E-2</v>
       </c>
       <c r="L12">
-        <v>8.4019119390448399E-2</v>
+        <v>7.9900025866150332E-2</v>
       </c>
       <c r="M12">
-        <v>8.4511826872225915E-2</v>
+        <v>8.0462487804507321E-2</v>
       </c>
       <c r="N12">
-        <v>8.4288846745117718E-2</v>
+        <v>8.0004105150030841E-2</v>
       </c>
       <c r="O12">
-        <v>1.1969336146926135E-4</v>
+        <v>-9.1941523039774237E-4</v>
       </c>
       <c r="P12">
-        <v>5.0855648844080198E-4</v>
+        <v>3.6727462076713291E-4</v>
       </c>
       <c r="Q12">
-        <v>-8.549177615355813E-5</v>
+        <v>6.1208162672234633E-4</v>
       </c>
       <c r="R12">
-        <v>-7.739434985204463E-5</v>
+        <v>-8.728663974081341E-4</v>
       </c>
       <c r="S12">
-        <v>1.113668778462131E-4</v>
+        <v>4.2384003691629812E-5</v>
       </c>
       <c r="T12">
-        <v>5.1059293718817671E-4</v>
+        <v>3.7725084422883873E-4</v>
       </c>
       <c r="U12">
-        <v>7.3705097809739772E-4</v>
+        <v>-2.9094610916571284E-3</v>
       </c>
       <c r="V12">
-        <v>2.5820894272164316E-4</v>
+        <v>-6.1070456127521044E-4</v>
       </c>
       <c r="W12">
-        <v>4.4745943156195706E-4</v>
+        <v>-1.5116710570581976E-4</v>
       </c>
       <c r="X12">
-        <v>-4.6427709508903119E-4</v>
+        <v>-3.8423601706332605E-4</v>
       </c>
       <c r="Y12">
-        <v>-1.9277684255405948E-4</v>
+        <v>-6.121932368545191E-4</v>
       </c>
       <c r="Z12">
-        <v>-1.3906646043800389E-4</v>
+        <v>-5.6821633514136938E-4</v>
       </c>
       <c r="AA12">
-        <v>-4.9608189989342431E-5</v>
+        <v>-3.9098676380741604E-4</v>
       </c>
       <c r="AB12">
-        <v>-3.8728019827620447E-5</v>
+        <v>-3.1311804414090039E-5</v>
       </c>
       <c r="AC12">
-        <v>-5.9849585982117703E-5</v>
+        <v>7.1781241283169067E-4</v>
       </c>
       <c r="AD12">
-        <v>1.2623628609969434E-4</v>
+        <v>1.2550409944924509E-4</v>
       </c>
       <c r="AE12">
-        <v>-8.4244609024092143E-2</v>
+        <v>-7.4408123300112816E-2</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="4">
-        <v>-0.44881433206752941</v>
+      <c r="B13">
+        <v>0.22931572616828355</v>
       </c>
       <c r="C13">
-        <v>-1.3499536097145645E-4</v>
+        <v>-8.9329145078764077E-5</v>
       </c>
       <c r="D13">
-        <v>3.0967256168015677E-6</v>
+        <v>1.4300579061547161E-6</v>
       </c>
       <c r="E13">
-        <v>1.4441779640450439E-4</v>
+        <v>-1.4947585475790814E-3</v>
       </c>
       <c r="F13">
-        <v>2.5516700505571251E-5</v>
+        <v>-1.7746651959421539E-3</v>
       </c>
       <c r="G13">
-        <v>1.8268207282184663E-4</v>
+        <v>-2.0758450549380461E-3</v>
       </c>
       <c r="H13">
-        <v>1.4798977583223988E-4</v>
+        <v>-2.1963310811363417E-3</v>
       </c>
       <c r="I13">
-        <v>1.522459078858048E-6</v>
+        <v>3.1896410036064138E-4</v>
       </c>
       <c r="J13">
-        <v>4.2723370883815132E-5</v>
+        <v>-2.323026270710485E-4</v>
       </c>
       <c r="K13">
-        <v>8.3746692955021212E-2</v>
+        <v>7.9894971220947242E-2</v>
       </c>
       <c r="L13">
-        <v>8.4076260911171707E-2</v>
+        <v>7.9858906155957976E-2</v>
       </c>
       <c r="M13">
-        <v>8.4288846745117718E-2</v>
+        <v>8.0004105150030841E-2</v>
       </c>
       <c r="N13">
-        <v>8.5234064808457105E-2</v>
+        <v>8.1641485599922209E-2</v>
       </c>
       <c r="O13">
-        <v>4.7484290588423184E-4</v>
+        <v>-8.1412246595042453E-4</v>
       </c>
       <c r="P13">
-        <v>5.9352234694221712E-4</v>
+        <v>4.0464487793898107E-4</v>
       </c>
       <c r="Q13">
-        <v>-3.7995597374610585E-4</v>
+        <v>6.6901163816584109E-4</v>
       </c>
       <c r="R13">
-        <v>5.2295763002838808E-5</v>
+        <v>-8.4072254684584499E-4</v>
       </c>
       <c r="S13">
-        <v>1.1437322066732022E-4</v>
+        <v>-2.5038062205174488E-4</v>
       </c>
       <c r="T13">
-        <v>5.7813511922817987E-4</v>
+        <v>3.0245107304069374E-4</v>
       </c>
       <c r="U13">
-        <v>5.5518875917112687E-4</v>
+        <v>-4.2623579171752191E-3</v>
       </c>
       <c r="V13">
-        <v>2.4249225575666625E-4</v>
+        <v>-7.1168020374343111E-4</v>
       </c>
       <c r="W13">
-        <v>4.9592163070215529E-4</v>
+        <v>-6.0703632047888478E-5</v>
       </c>
       <c r="X13">
-        <v>-3.9430563060456614E-4</v>
+        <v>-7.0866272852798673E-5</v>
       </c>
       <c r="Y13">
-        <v>-1.7100302444384395E-4</v>
+        <v>-6.9105148763527746E-4</v>
       </c>
       <c r="Z13">
-        <v>-1.4266392760561245E-4</v>
+        <v>-3.3076199473364154E-4</v>
       </c>
       <c r="AA13">
-        <v>3.8489258457458618E-5</v>
+        <v>-1.8219403422939373E-4</v>
       </c>
       <c r="AB13">
-        <v>-3.7190050698999972E-5</v>
+        <v>-7.879956687860401E-5</v>
       </c>
       <c r="AC13">
-        <v>-1.1601445814387462E-4</v>
+        <v>9.289849170115716E-4</v>
       </c>
       <c r="AD13">
-        <v>1.4057615879197946E-4</v>
+        <v>-1.0482830196222558E-5</v>
       </c>
       <c r="AE13">
-        <v>-8.3793811011936059E-2</v>
+        <v>-6.980181834357313E-2</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
-        <v>-1.356913036515945</v>
+      <c r="B14">
+        <v>-0.88495250152528759</v>
       </c>
       <c r="C14">
-        <v>7.6912382475424756E-5</v>
+        <v>-3.0777543329596566E-4</v>
       </c>
       <c r="D14">
-        <v>-1.2798079003760058E-6</v>
+        <v>3.7347654422265314E-6</v>
       </c>
       <c r="E14">
-        <v>-1.7894663167861979E-3</v>
+        <v>1.2088369009304446E-5</v>
       </c>
       <c r="F14">
-        <v>-3.0266143440537893E-4</v>
+        <v>-7.1864096380589489E-4</v>
       </c>
       <c r="G14">
-        <v>-3.2937110831517818E-5</v>
+        <v>-1.8702395239357105E-4</v>
       </c>
       <c r="H14">
-        <v>-2.0728071272302102E-4</v>
+        <v>2.6773540035407786E-5</v>
       </c>
       <c r="I14">
-        <v>-3.7220929695892715E-4</v>
+        <v>-1.7523152869481523E-4</v>
       </c>
       <c r="J14">
-        <v>-3.1072209107085641E-5</v>
+        <v>-1.591639233410909E-4</v>
       </c>
       <c r="K14">
-        <v>-1.8266617968796389E-4</v>
+        <v>-3.7678059934378311E-4</v>
       </c>
       <c r="L14">
-        <v>9.5346709301363797E-6</v>
+        <v>-8.6859376383478099E-4</v>
       </c>
       <c r="M14">
-        <v>1.1969336146926135E-4</v>
+        <v>-9.1941523039774237E-4</v>
       </c>
       <c r="N14">
-        <v>4.7484290588423184E-4</v>
+        <v>-8.1412246595042453E-4</v>
       </c>
       <c r="O14">
-        <v>3.1729585625160643E-2</v>
+        <v>2.8576406519526577E-2</v>
       </c>
       <c r="P14">
-        <v>6.6023205155492934E-3</v>
+        <v>2.7762420239396601E-3</v>
       </c>
       <c r="Q14">
-        <v>-2.7469863201270164E-2</v>
+        <v>-2.319284804840073E-2</v>
       </c>
       <c r="R14">
-        <v>-4.7857464266051588E-3</v>
+        <v>-2.2648935501520585E-3</v>
       </c>
       <c r="S14">
-        <v>-2.1134127580801423E-6</v>
+        <v>-5.434939854039476E-4</v>
       </c>
       <c r="T14">
-        <v>4.811464463765682E-4</v>
+        <v>-1.4841064432457267E-4</v>
       </c>
       <c r="U14">
-        <v>-5.0795982176589762E-4</v>
+        <v>-1.0375994015841185E-2</v>
       </c>
       <c r="V14">
-        <v>6.9032131691097189E-4</v>
+        <v>6.2335694107264845E-4</v>
       </c>
       <c r="W14">
-        <v>1.4831380963284302E-4</v>
+        <v>4.7680745231862341E-4</v>
       </c>
       <c r="X14">
-        <v>7.6876093061210106E-5</v>
+        <v>-6.0251583119956499E-5</v>
       </c>
       <c r="Y14">
-        <v>1.0344903868390441E-4</v>
+        <v>2.975705552297446E-4</v>
       </c>
       <c r="Z14">
-        <v>8.3212268812885487E-5</v>
+        <v>2.5410061215240445E-4</v>
       </c>
       <c r="AA14">
-        <v>4.962905437433277E-5</v>
+        <v>2.6284742542824436E-4</v>
       </c>
       <c r="AB14">
-        <v>4.1569522667938513E-5</v>
+        <v>-2.2960068732225786E-4</v>
       </c>
       <c r="AC14">
-        <v>-5.2681368138991151E-4</v>
+        <v>-2.0857481001030124E-5</v>
       </c>
       <c r="AD14">
-        <v>-1.1693663405852828E-4</v>
+        <v>-3.2755124765183712E-4</v>
       </c>
       <c r="AE14">
-        <v>-6.2254617512547822E-4</v>
+        <v>2.5008630614879075E-2</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4">
-        <v>-0.91765994945200646</v>
+      <c r="B15">
+        <v>-0.60103951249965404</v>
       </c>
       <c r="C15">
-        <v>-1.1692880680639565E-4</v>
+        <v>1.7080749835791595E-5</v>
       </c>
       <c r="D15">
-        <v>2.0231536991994901E-6</v>
+        <v>-4.9467523507792E-7</v>
       </c>
       <c r="E15">
-        <v>-1.2299244315679115E-3</v>
+        <v>-3.7145430702920255E-3</v>
       </c>
       <c r="F15">
-        <v>-1.8572697416285927E-3</v>
+        <v>-3.5958768533381784E-3</v>
       </c>
       <c r="G15">
-        <v>-2.0252793650416588E-3</v>
+        <v>-3.1549629000851712E-3</v>
       </c>
       <c r="H15">
-        <v>-1.9193945033023304E-3</v>
+        <v>-2.8924257736682841E-3</v>
       </c>
       <c r="I15">
-        <v>-2.2424052881128437E-4</v>
+        <v>-2.4439620415757412E-4</v>
       </c>
       <c r="J15">
-        <v>2.099508191540614E-4</v>
+        <v>-2.2770236902859282E-5</v>
       </c>
       <c r="K15">
-        <v>-2.5036297542995606E-4</v>
+        <v>4.6101678998815288E-4</v>
       </c>
       <c r="L15">
-        <v>3.7303760612540648E-5</v>
+        <v>6.8685794684207602E-4</v>
       </c>
       <c r="M15">
-        <v>5.0855648844080198E-4</v>
+        <v>3.6727462076713291E-4</v>
       </c>
       <c r="N15">
-        <v>5.9352234694221712E-4</v>
+        <v>4.0464487793898107E-4</v>
       </c>
       <c r="O15">
-        <v>6.6023205155492934E-3</v>
+        <v>2.7762420239396601E-3</v>
       </c>
       <c r="P15">
-        <v>2.205402467012002E-2</v>
+        <v>2.6367085456375762E-2</v>
       </c>
       <c r="Q15">
-        <v>-7.0301688258032312E-3</v>
+        <v>-2.6094053066738425E-3</v>
       </c>
       <c r="R15">
-        <v>-1.7580472239878811E-2</v>
+        <v>-2.2258292865243431E-2</v>
       </c>
       <c r="S15">
-        <v>-1.32841498703681E-4</v>
+        <v>-4.0603738631635514E-4</v>
       </c>
       <c r="T15">
-        <v>4.8786060506086958E-4</v>
+        <v>-2.0658737129131653E-4</v>
       </c>
       <c r="U15">
-        <v>2.1220970524371673E-3</v>
+        <v>-7.998476587633821E-3</v>
       </c>
       <c r="V15">
-        <v>4.3644292906844982E-5</v>
+        <v>-5.9864412779825436E-4</v>
       </c>
       <c r="W15">
-        <v>2.7818894293340899E-4</v>
+        <v>5.812671467913188E-4</v>
       </c>
       <c r="X15">
-        <v>-9.6934724572757524E-5</v>
+        <v>2.2828525415892866E-4</v>
       </c>
       <c r="Y15">
-        <v>4.9287291610111998E-4</v>
+        <v>5.1378747704251739E-5</v>
       </c>
       <c r="Z15">
-        <v>2.1397395422366526E-4</v>
+        <v>3.4452728579310258E-4</v>
       </c>
       <c r="AA15">
-        <v>-4.8228911015247774E-6</v>
+        <v>1.6895230994670891E-4</v>
       </c>
       <c r="AB15">
-        <v>-3.8323392250187401E-5</v>
+        <v>-1.8890471060084807E-4</v>
       </c>
       <c r="AC15">
-        <v>1.7784775603164904E-4</v>
+        <v>5.5571748364532448E-4</v>
       </c>
       <c r="AD15">
-        <v>1.2564404886540901E-4</v>
+        <v>-3.36103046794762E-4</v>
       </c>
       <c r="AE15">
-        <v>8.6616340823723252E-4</v>
+        <v>1.6504489093138681E-2</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A16" s="4" t="s">
+      <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="4">
-        <v>1.2195717217396631</v>
+      <c r="B16">
+        <v>0.80427320195749852</v>
       </c>
       <c r="C16">
-        <v>-7.3303706793806898E-5</v>
+        <v>1.520296086144089E-4</v>
       </c>
       <c r="D16">
-        <v>1.7874509792603665E-6</v>
+        <v>-1.6566145337345119E-6</v>
       </c>
       <c r="E16">
-        <v>8.4570820704380021E-4</v>
+        <v>9.8258554659475298E-4</v>
       </c>
       <c r="F16">
-        <v>1.3745203024877932E-3</v>
+        <v>2.1904230782756311E-3</v>
       </c>
       <c r="G16">
-        <v>1.4044007377681978E-3</v>
+        <v>2.213426846800716E-3</v>
       </c>
       <c r="H16">
-        <v>1.6537914542798754E-3</v>
+        <v>2.5474791375352645E-3</v>
       </c>
       <c r="I16">
-        <v>5.0848613629210786E-4</v>
+        <v>4.7308982556767574E-4</v>
       </c>
       <c r="J16">
-        <v>2.0846562536907653E-4</v>
+        <v>1.8110745063063219E-4</v>
       </c>
       <c r="K16">
-        <v>1.9792630229049923E-4</v>
+        <v>2.9224530749283936E-4</v>
       </c>
       <c r="L16">
-        <v>-4.4398154379718391E-5</v>
+        <v>7.1041138971651707E-4</v>
       </c>
       <c r="M16">
-        <v>-8.549177615355813E-5</v>
+        <v>6.1208162672234633E-4</v>
       </c>
       <c r="N16">
-        <v>-3.7995597374610585E-4</v>
+        <v>6.6901163816584109E-4</v>
       </c>
       <c r="O16">
-        <v>-2.7469863201270164E-2</v>
+        <v>-2.319284804840073E-2</v>
       </c>
       <c r="P16">
-        <v>-7.0301688258032312E-3</v>
+        <v>-2.6094053066738425E-3</v>
       </c>
       <c r="Q16">
-        <v>2.8221062299334711E-2</v>
+        <v>2.4385032493327359E-2</v>
       </c>
       <c r="R16">
-        <v>5.8929398015794702E-3</v>
+        <v>3.1561818223486142E-3</v>
       </c>
       <c r="S16">
-        <v>-4.0754449678660542E-5</v>
+        <v>3.0415089520170356E-4</v>
       </c>
       <c r="T16">
-        <v>-7.2425620442973676E-4</v>
+        <v>3.0109542111242957E-4</v>
       </c>
       <c r="U16">
-        <v>-2.9147874716058033E-4</v>
+        <v>8.82665705467163E-3</v>
       </c>
       <c r="V16">
-        <v>-1.4736186988996832E-3</v>
+        <v>-6.9298365517534745E-4</v>
       </c>
       <c r="W16">
-        <v>1.6550412430280532E-4</v>
+        <v>3.7250565870342815E-4</v>
       </c>
       <c r="X16">
-        <v>-2.661655520219098E-4</v>
+        <v>8.0731490063672487E-5</v>
       </c>
       <c r="Y16">
-        <v>-1.5986730426279362E-4</v>
+        <v>-6.399401024035755E-5</v>
       </c>
       <c r="Z16">
-        <v>-8.3156147322452931E-5</v>
+        <v>-2.9044001037349838E-4</v>
       </c>
       <c r="AA16">
-        <v>-5.6907486115411382E-5</v>
+        <v>-2.877600456760495E-4</v>
       </c>
       <c r="AB16">
-        <v>-3.8230551777755741E-5</v>
+        <v>1.6316875023124995E-4</v>
       </c>
       <c r="AC16">
-        <v>4.545165394622421E-4</v>
+        <v>3.222092623969895E-4</v>
       </c>
       <c r="AD16">
-        <v>-8.3217073198970336E-6</v>
+        <v>1.978664787983278E-4</v>
       </c>
       <c r="AE16">
-        <v>-8.4558287762910578E-4</v>
+        <v>-2.1883668073604076E-2</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="4">
-        <v>0.61948063204069437</v>
+      <c r="B17">
+        <v>0.27142996688325505</v>
       </c>
       <c r="C17">
-        <v>-2.5130572391913238E-4</v>
+        <v>-4.5032176654757634E-5</v>
       </c>
       <c r="D17">
-        <v>3.9857705274844041E-6</v>
+        <v>6.1326581762181589E-7</v>
       </c>
       <c r="E17">
-        <v>7.0392566944827827E-4</v>
+        <v>3.3292275234410606E-3</v>
       </c>
       <c r="F17">
-        <v>1.9093028696430976E-3</v>
+        <v>3.931381177573569E-3</v>
       </c>
       <c r="G17">
-        <v>2.2619350017223068E-3</v>
+        <v>4.2960331845344601E-3</v>
       </c>
       <c r="H17">
-        <v>2.4738952248091104E-3</v>
+        <v>4.4855638125146794E-3</v>
       </c>
       <c r="I17">
-        <v>4.071472439698908E-4</v>
+        <v>2.3158615364190312E-4</v>
       </c>
       <c r="J17">
-        <v>1.2881571186473638E-4</v>
+        <v>1.9570457331374391E-4</v>
       </c>
       <c r="K17">
-        <v>4.0043684536892818E-4</v>
+        <v>-1.1255759961693763E-3</v>
       </c>
       <c r="L17">
-        <v>1.6280482176972422E-4</v>
+        <v>-8.6346397203709152E-4</v>
       </c>
       <c r="M17">
-        <v>-7.739434985204463E-5</v>
+        <v>-8.728663974081341E-4</v>
       </c>
       <c r="N17">
-        <v>5.2295763002838808E-5</v>
+        <v>-8.4072254684584499E-4</v>
       </c>
       <c r="O17">
-        <v>-4.7857464266051588E-3</v>
+        <v>-2.2648935501520585E-3</v>
       </c>
       <c r="P17">
-        <v>-1.7580472239878811E-2</v>
+        <v>-2.2258292865243431E-2</v>
       </c>
       <c r="Q17">
-        <v>5.8929398015794702E-3</v>
+        <v>3.1561818223486142E-3</v>
       </c>
       <c r="R17">
-        <v>1.8414443920753601E-2</v>
+        <v>2.4500604760612905E-2</v>
       </c>
       <c r="S17">
-        <v>6.9101004117114772E-5</v>
+        <v>2.3453967674091697E-4</v>
       </c>
       <c r="T17">
-        <v>-3.7907013253733887E-4</v>
+        <v>2.3332758907138713E-4</v>
       </c>
       <c r="U17">
-        <v>-2.5543451940962122E-3</v>
+        <v>4.0235680416472949E-3</v>
       </c>
       <c r="V17">
-        <v>-1.8369318955659765E-4</v>
+        <v>1.3423975894431648E-3</v>
       </c>
       <c r="W17">
-        <v>-6.4661622260776255E-6</v>
+        <v>4.2163652572025463E-4</v>
       </c>
       <c r="X17">
-        <v>1.7546977267600099E-4</v>
+        <v>-1.1991082457825809E-4</v>
       </c>
       <c r="Y17">
-        <v>-2.2846398251503505E-4</v>
+        <v>4.3593541650084958E-4</v>
       </c>
       <c r="Z17">
-        <v>-8.2324881837983325E-5</v>
+        <v>4.08985385420748E-5</v>
       </c>
       <c r="AA17">
-        <v>1.7121583925899119E-4</v>
+        <v>2.5207197076730983E-5</v>
       </c>
       <c r="AB17">
-        <v>3.086857548289209E-5</v>
+        <v>7.5724639217917417E-5</v>
       </c>
       <c r="AC17">
-        <v>-3.1174316931970438E-4</v>
+        <v>-4.4206742426121902E-4</v>
       </c>
       <c r="AD17">
-        <v>-2.4049389922529464E-4</v>
+        <v>7.7905155236683771E-5</v>
       </c>
       <c r="AE17">
-        <v>3.7602632527530353E-3</v>
+        <v>-1.0053438042088594E-2</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="4">
-        <v>-0.1205474725943646</v>
+      <c r="B18">
+        <v>-0.28530008667805085</v>
       </c>
       <c r="C18">
-        <v>1.9243435626443449E-4</v>
+        <v>3.540702064387842E-5</v>
       </c>
       <c r="D18">
-        <v>-2.8319923634328983E-6</v>
+        <v>-9.1955951857247437E-9</v>
       </c>
       <c r="E18">
-        <v>9.9688721730346614E-5</v>
+        <v>1.3206990312926962E-4</v>
       </c>
       <c r="F18">
-        <v>-5.1143586603134314E-5</v>
+        <v>2.8870103684609013E-4</v>
       </c>
       <c r="G18">
-        <v>7.4599790917970381E-5</v>
+        <v>4.6045447648880621E-5</v>
       </c>
       <c r="H18">
-        <v>3.2980722929104134E-4</v>
+        <v>1.64285748659745E-4</v>
       </c>
       <c r="I18">
-        <v>3.9436415991214404E-6</v>
+        <v>1.3562733082982104E-4</v>
       </c>
       <c r="J18">
-        <v>1.4029386085416724E-4</v>
+        <v>2.6685097109928075E-4</v>
       </c>
       <c r="K18">
-        <v>4.6918374592145543E-4</v>
+        <v>-1.1910415951903869E-4</v>
       </c>
       <c r="L18">
-        <v>4.2441989283114841E-5</v>
+        <v>-2.2862063244203507E-4</v>
       </c>
       <c r="M18">
-        <v>1.113668778462131E-4</v>
+        <v>4.2384003691629812E-5</v>
       </c>
       <c r="N18">
-        <v>1.1437322066732022E-4</v>
+        <v>-2.5038062205174488E-4</v>
       </c>
       <c r="O18">
-        <v>-2.1134127580801423E-6</v>
+        <v>-5.434939854039476E-4</v>
       </c>
       <c r="P18">
-        <v>-1.32841498703681E-4</v>
+        <v>-4.0603738631635514E-4</v>
       </c>
       <c r="Q18">
-        <v>-4.0754449678660542E-5</v>
+        <v>3.0415089520170356E-4</v>
       </c>
       <c r="R18">
-        <v>6.9101004117114772E-5</v>
+        <v>2.3453967674091697E-4</v>
       </c>
       <c r="S18">
-        <v>1.0828448908609188E-3</v>
+        <v>1.9210799163307988E-3</v>
       </c>
       <c r="T18">
-        <v>8.152753097305799E-4</v>
+        <v>1.2483683570379677E-3</v>
       </c>
       <c r="U18">
-        <v>-5.0083306979949518E-6</v>
+        <v>7.9949883265242883E-3</v>
       </c>
       <c r="V18">
-        <v>1.9592037078065437E-4</v>
+        <v>6.1913401883952578E-5</v>
       </c>
       <c r="W18">
-        <v>-1.3280603289883791E-4</v>
+        <v>-3.6821600525828208E-4</v>
       </c>
       <c r="X18">
-        <v>-1.0403971901812124E-4</v>
+        <v>-4.6164450322705355E-4</v>
       </c>
       <c r="Y18">
-        <v>-5.4826601102152367E-5</v>
+        <v>-2.4991452807371318E-4</v>
       </c>
       <c r="Z18">
-        <v>-2.3388965619314977E-5</v>
+        <v>-3.1266888160362202E-4</v>
       </c>
       <c r="AA18">
-        <v>4.2485836602178115E-5</v>
+        <v>-3.3986133414734814E-4</v>
       </c>
       <c r="AB18">
-        <v>1.5451025931629641E-5</v>
+        <v>1.9454093844275947E-4</v>
       </c>
       <c r="AC18">
-        <v>1.1634006715949784E-4</v>
+        <v>-1.3531950853782064E-4</v>
       </c>
       <c r="AD18">
-        <v>1.2973870902276401E-6</v>
+        <v>4.2491279157220584E-5</v>
       </c>
       <c r="AE18">
-        <v>-4.2793830195181314E-3</v>
+        <v>-1.6196901215115495E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="4">
-        <v>5.9088557073164148E-2</v>
+      <c r="B19">
+        <v>-0.41909387824518635</v>
       </c>
       <c r="C19">
-        <v>4.4902128542772526E-4</v>
+        <v>1.5759634054272626E-4</v>
       </c>
       <c r="D19">
-        <v>-6.4012366243920116E-6</v>
+        <v>-1.9322631231452825E-6</v>
       </c>
       <c r="E19">
-        <v>-5.009227910631991E-4</v>
+        <v>-3.7923012566569328E-4</v>
       </c>
       <c r="F19">
-        <v>-3.9607453399681308E-4</v>
+        <v>-3.5511976392773979E-4</v>
       </c>
       <c r="G19">
-        <v>-1.931234465921913E-4</v>
+        <v>-9.5926360009204389E-6</v>
       </c>
       <c r="H19">
-        <v>4.4393048925213049E-5</v>
+        <v>3.5676189873261462E-4</v>
       </c>
       <c r="I19">
-        <v>-1.2530241957560461E-4</v>
+        <v>5.6902944001849785E-5</v>
       </c>
       <c r="J19">
-        <v>2.2074305865028154E-4</v>
+        <v>4.0082971452603519E-4</v>
       </c>
       <c r="K19">
-        <v>5.5604009335982404E-5</v>
+        <v>2.4255833903196258E-4</v>
       </c>
       <c r="L19">
-        <v>2.5658339404524035E-4</v>
+        <v>1.7847483114818985E-4</v>
       </c>
       <c r="M19">
-        <v>5.1059293718817671E-4</v>
+        <v>3.7725084422883873E-4</v>
       </c>
       <c r="N19">
-        <v>5.7813511922817987E-4</v>
+        <v>3.0245107304069374E-4</v>
       </c>
       <c r="O19">
-        <v>4.811464463765682E-4</v>
+        <v>-1.4841064432457267E-4</v>
       </c>
       <c r="P19">
-        <v>4.8786060506086958E-4</v>
+        <v>-2.0658737129131653E-4</v>
       </c>
       <c r="Q19">
-        <v>-7.2425620442973676E-4</v>
+        <v>3.0109542111242957E-4</v>
       </c>
       <c r="R19">
-        <v>-3.7907013253733887E-4</v>
+        <v>2.3332758907138713E-4</v>
       </c>
       <c r="S19">
-        <v>8.152753097305799E-4</v>
+        <v>1.2483683570379677E-3</v>
       </c>
       <c r="T19">
-        <v>4.9797153633169495E-3</v>
+        <v>2.8909668466432564E-3</v>
       </c>
       <c r="U19">
-        <v>6.1396227502930056E-4</v>
+        <v>2.0135672055145715E-3</v>
       </c>
       <c r="V19">
-        <v>1.9810284272930552E-4</v>
+        <v>2.1280406399256865E-4</v>
       </c>
       <c r="W19">
-        <v>-1.8447870122822346E-4</v>
+        <v>-3.1412239510812678E-4</v>
       </c>
       <c r="X19">
-        <v>-2.4145573694213059E-4</v>
+        <v>-1.2656278945907731E-4</v>
       </c>
       <c r="Y19">
-        <v>8.0057584316888057E-5</v>
+        <v>6.1825727696772359E-5</v>
       </c>
       <c r="Z19">
-        <v>-2.6731577784837058E-4</v>
+        <v>6.9160869954369361E-5</v>
       </c>
       <c r="AA19">
-        <v>7.9096730570043443E-6</v>
+        <v>4.7610974969589451E-5</v>
       </c>
       <c r="AB19">
-        <v>2.7116128091147975E-5</v>
+        <v>7.3684689751557161E-5</v>
       </c>
       <c r="AC19">
-        <v>4.5098671527915232E-5</v>
+        <v>-1.333637379017402E-4</v>
       </c>
       <c r="AD19">
-        <v>3.9161793982513213E-6</v>
+        <v>-3.0856963767368921E-4</v>
       </c>
       <c r="AE19">
-        <v>-9.7520024108732409E-3</v>
+        <v>-8.7064736070815163E-3</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="4">
-        <v>0.138613214277678</v>
+      <c r="B20">
+        <v>0.69637983266555192</v>
       </c>
       <c r="C20">
-        <v>2.3257402569426891E-4</v>
+        <v>6.7481258606760797E-4</v>
       </c>
       <c r="D20">
-        <v>-2.9933107869743519E-6</v>
+        <v>-1.4569497607665009E-6</v>
       </c>
       <c r="E20">
-        <v>-1.1482362773312244E-3</v>
+        <v>-2.9596719659817005E-3</v>
       </c>
       <c r="F20">
-        <v>-7.9171013475877808E-4</v>
+        <v>3.2629992669071795E-3</v>
       </c>
       <c r="G20">
-        <v>-8.0763066515607794E-4</v>
+        <v>-9.347311100260304E-3</v>
       </c>
       <c r="H20">
-        <v>-1.1885843689452662E-3</v>
+        <v>-1.0010428841263685E-2</v>
       </c>
       <c r="I20">
-        <v>-4.0315965918530892E-5</v>
+        <v>3.4933142166057168E-3</v>
       </c>
       <c r="J20">
-        <v>3.2994248329018538E-5</v>
+        <v>-3.1950436091474632E-3</v>
       </c>
       <c r="K20">
-        <v>5.5119593287239477E-4</v>
+        <v>-7.2647788215747244E-3</v>
       </c>
       <c r="L20">
-        <v>-1.6059617628885747E-4</v>
+        <v>-3.649038641633684E-3</v>
       </c>
       <c r="M20">
-        <v>7.3705097809739772E-4</v>
+        <v>-2.9094610916571284E-3</v>
       </c>
       <c r="N20">
-        <v>5.5518875917112687E-4</v>
+        <v>-4.2623579171752191E-3</v>
       </c>
       <c r="O20">
-        <v>-5.0795982176589762E-4</v>
+        <v>-1.0375994015841185E-2</v>
       </c>
       <c r="P20">
-        <v>2.1220970524371673E-3</v>
+        <v>-7.998476587633821E-3</v>
       </c>
       <c r="Q20">
-        <v>-2.9147874716058033E-4</v>
+        <v>8.82665705467163E-3</v>
       </c>
       <c r="R20">
-        <v>-2.5543451940962122E-3</v>
+        <v>4.0235680416472949E-3</v>
       </c>
       <c r="S20">
-        <v>-5.0083306979949518E-6</v>
+        <v>7.9949883265242883E-3</v>
       </c>
       <c r="T20">
-        <v>6.1396227502930056E-4</v>
+        <v>2.0135672055145715E-3</v>
       </c>
       <c r="U20">
-        <v>6.2611610896891795E-2</v>
+        <v>3.4231343797052176</v>
       </c>
       <c r="V20">
-        <v>-8.4543211326497392E-5</v>
+        <v>-5.7065136194633936E-4</v>
       </c>
       <c r="W20">
-        <v>-1.2299409285449533E-4</v>
+        <v>-9.5619191450737606E-3</v>
       </c>
       <c r="X20">
-        <v>-1.1906319902616792E-4</v>
+        <v>-6.3245886603848778E-3</v>
       </c>
       <c r="Y20">
-        <v>4.5266018432429337E-4</v>
+        <v>-9.7551093127856703E-3</v>
       </c>
       <c r="Z20">
-        <v>3.8195269640143442E-4</v>
+        <v>-5.8251029763756179E-3</v>
       </c>
       <c r="AA20">
-        <v>5.0330488759703189E-4</v>
+        <v>-5.0273970842322768E-3</v>
       </c>
       <c r="AB20">
-        <v>-3.9745613158252062E-4</v>
+        <v>6.3095874666153851E-2</v>
       </c>
       <c r="AC20">
-        <v>-6.5513384018372339E-4</v>
+        <v>8.2458579527455056E-2</v>
       </c>
       <c r="AD20">
-        <v>3.5986587515630906E-3</v>
+        <v>-8.782333296422945E-3</v>
       </c>
       <c r="AE20">
-        <v>-8.2991507920076202E-2</v>
+        <v>-5.6162355854335502</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A21" s="4" t="s">
+      <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="4">
-        <v>7.6400911560965096E-2</v>
+      <c r="B21">
+        <v>-0.35436230584910272</v>
       </c>
       <c r="C21">
-        <v>1.036745703606724E-3</v>
+        <v>5.4872781593778841E-4</v>
       </c>
       <c r="D21">
-        <v>-1.417677093281909E-5</v>
+        <v>-7.0509937480622278E-6</v>
       </c>
       <c r="E21">
-        <v>1.1254545305906362E-3</v>
+        <v>1.2881052067806157E-3</v>
       </c>
       <c r="F21">
-        <v>1.7154813598231292E-3</v>
+        <v>1.8284194929131326E-3</v>
       </c>
       <c r="G21">
-        <v>1.8108383199628032E-3</v>
+        <v>2.8534725468392086E-3</v>
       </c>
       <c r="H21">
-        <v>1.7954571935368513E-3</v>
+        <v>3.0473936062167788E-3</v>
       </c>
       <c r="I21">
-        <v>-2.3002156782194079E-4</v>
+        <v>-3.6181095557555679E-4</v>
       </c>
       <c r="J21">
-        <v>-3.1131398564071446E-5</v>
+        <v>4.4284971095989549E-5</v>
       </c>
       <c r="K21">
-        <v>-1.0509328676614957E-4</v>
+        <v>-5.9380501088227011E-4</v>
       </c>
       <c r="L21">
-        <v>3.7888829995916251E-4</v>
+        <v>-3.1392029688528944E-4</v>
       </c>
       <c r="M21">
-        <v>2.5820894272164316E-4</v>
+        <v>-6.1070456127521044E-4</v>
       </c>
       <c r="N21">
-        <v>2.4249225575666625E-4</v>
+        <v>-7.1168020374343111E-4</v>
       </c>
       <c r="O21">
-        <v>6.9032131691097189E-4</v>
+        <v>6.2335694107264845E-4</v>
       </c>
       <c r="P21">
-        <v>4.3644292906844982E-5</v>
+        <v>-5.9864412779825436E-4</v>
       </c>
       <c r="Q21">
-        <v>-1.4736186988996832E-3</v>
+        <v>-6.9298365517534745E-4</v>
       </c>
       <c r="R21">
-        <v>-1.8369318955659765E-4</v>
+        <v>1.3423975894431648E-3</v>
       </c>
       <c r="S21">
-        <v>1.9592037078065437E-4</v>
+        <v>6.1913401883952578E-5</v>
       </c>
       <c r="T21">
-        <v>1.9810284272930552E-4</v>
+        <v>2.1280406399256865E-4</v>
       </c>
       <c r="U21">
-        <v>-8.4543211326497392E-5</v>
+        <v>-5.7065136194633936E-4</v>
       </c>
       <c r="V21">
-        <v>2.5186470893142965E-2</v>
+        <v>4.7047047387407601E-2</v>
       </c>
       <c r="W21">
-        <v>8.6605452987036698E-4</v>
+        <v>1.3382703100489396E-3</v>
       </c>
       <c r="X21">
-        <v>6.4511188072241326E-5</v>
+        <v>1.9969843380792177E-5</v>
       </c>
       <c r="Y21">
-        <v>-2.1972528175086799E-4</v>
+        <v>8.1693866547207297E-4</v>
       </c>
       <c r="Z21">
-        <v>9.1546500222922404E-5</v>
+        <v>3.631621331590465E-4</v>
       </c>
       <c r="AA21">
-        <v>6.6245223789805196E-5</v>
+        <v>4.5075525691440875E-4</v>
       </c>
       <c r="AB21">
-        <v>2.3522284162458171E-5</v>
+        <v>-4.7756520244131122E-5</v>
       </c>
       <c r="AC21">
-        <v>-3.6485347385505074E-7</v>
+        <v>-2.0169701332905989E-4</v>
       </c>
       <c r="AD21">
-        <v>4.2352086338522978E-5</v>
+        <v>-8.3207123552580891E-5</v>
       </c>
       <c r="AE21">
-        <v>-2.0888084053528877E-2</v>
+        <v>-1.1559934617145107E-2</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="4">
-        <v>-0.10837932836804987</v>
+      <c r="B22">
+        <v>-4.5493998582054371E-2</v>
       </c>
       <c r="C22">
-        <v>8.256034511573869E-5</v>
+        <v>1.3867767885126017E-4</v>
       </c>
       <c r="D22">
-        <v>-9.7725192968876098E-7</v>
+        <v>-2.2688969186693666E-6</v>
       </c>
       <c r="E22">
-        <v>-3.3471972248961439E-5</v>
+        <v>5.6124109139208593E-4</v>
       </c>
       <c r="F22">
-        <v>4.3733593379901355E-4</v>
+        <v>6.4064025476095999E-4</v>
       </c>
       <c r="G22">
-        <v>7.7486338378691662E-4</v>
+        <v>1.7134888506063516E-3</v>
       </c>
       <c r="H22">
-        <v>8.621738419492082E-4</v>
+        <v>2.0052115667627927E-3</v>
       </c>
       <c r="I22">
-        <v>-5.3974580672169834E-5</v>
+        <v>-2.767875043506819E-4</v>
       </c>
       <c r="J22">
-        <v>-1.514370799753645E-4</v>
+        <v>-1.1080150184194208E-4</v>
       </c>
       <c r="K22">
-        <v>-1.7030843422933747E-4</v>
+        <v>-1.7200455675944748E-4</v>
       </c>
       <c r="L22">
-        <v>4.0183811021562987E-4</v>
+        <v>6.3305338590252669E-5</v>
       </c>
       <c r="M22">
-        <v>4.4745943156195706E-4</v>
+        <v>-1.5116710570581976E-4</v>
       </c>
       <c r="N22">
-        <v>4.9592163070215529E-4</v>
+        <v>-6.0703632047888478E-5</v>
       </c>
       <c r="O22">
-        <v>1.4831380963284302E-4</v>
+        <v>4.7680745231862341E-4</v>
       </c>
       <c r="P22">
-        <v>2.7818894293340899E-4</v>
+        <v>5.812671467913188E-4</v>
       </c>
       <c r="Q22">
-        <v>1.6550412430280532E-4</v>
+        <v>3.7250565870342815E-4</v>
       </c>
       <c r="R22">
-        <v>-6.4661622260776255E-6</v>
+        <v>4.2163652572025463E-4</v>
       </c>
       <c r="S22">
-        <v>-1.3280603289883791E-4</v>
+        <v>-3.6821600525828208E-4</v>
       </c>
       <c r="T22">
-        <v>-1.8447870122822346E-4</v>
+        <v>-3.1412239510812678E-4</v>
       </c>
       <c r="U22">
-        <v>-1.2299409285449533E-4</v>
+        <v>-9.5619191450737606E-3</v>
       </c>
       <c r="V22">
-        <v>8.6605452987036698E-4</v>
+        <v>1.3382703100489396E-3</v>
       </c>
       <c r="W22">
-        <v>1.3926431850952248E-3</v>
+        <v>2.2041120805777453E-3</v>
       </c>
       <c r="X22">
-        <v>4.5726485996641208E-5</v>
+        <v>1.1632564856991036E-4</v>
       </c>
       <c r="Y22">
-        <v>1.2236270062001225E-4</v>
+        <v>2.3687198443829265E-4</v>
       </c>
       <c r="Z22">
-        <v>9.0385805348541825E-5</v>
+        <v>3.4509632723331188E-4</v>
       </c>
       <c r="AA22">
-        <v>6.3410483441622473E-5</v>
+        <v>3.1547674107313545E-4</v>
       </c>
       <c r="AB22">
-        <v>5.4576414940648319E-6</v>
+        <v>-2.0618813307545799E-4</v>
       </c>
       <c r="AC22">
-        <v>-8.1539065810655041E-5</v>
+        <v>3.6880647758329762E-5</v>
       </c>
       <c r="AD22">
-        <v>5.568759610072283E-6</v>
+        <v>-3.5070026313477196E-4</v>
       </c>
       <c r="AE22">
-        <v>-2.9693769645715174E-3</v>
+        <v>1.2265932677672115E-2</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="4">
-        <v>-9.3015094325197584E-2</v>
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23">
+        <v>-6.848468770174311E-2</v>
       </c>
       <c r="C23">
-        <v>4.255967225028686E-7</v>
+        <v>2.5913086894540846E-5</v>
       </c>
       <c r="D23">
-        <v>-9.8252358527322638E-9</v>
+        <v>-7.9257668560221402E-7</v>
       </c>
       <c r="E23">
-        <v>2.2856607472792245E-4</v>
+        <v>-5.6944476809105203E-4</v>
       </c>
       <c r="F23">
-        <v>2.2090543634875268E-4</v>
+        <v>-4.6659838500573642E-4</v>
       </c>
       <c r="G23">
-        <v>1.4899534601413875E-4</v>
+        <v>5.7599084600067161E-4</v>
       </c>
       <c r="H23">
-        <v>1.3861162955907996E-4</v>
+        <v>6.9347205352700454E-4</v>
       </c>
       <c r="I23">
-        <v>1.596535067560154E-5</v>
+        <v>-7.7850032275234428E-5</v>
       </c>
       <c r="J23">
-        <v>-1.51395986420455E-5</v>
+        <v>-2.9735276442375153E-4</v>
       </c>
       <c r="K23">
-        <v>-3.8045096765947257E-4</v>
+        <v>1.6603513771593775E-4</v>
       </c>
       <c r="L23">
-        <v>-3.7671397780852066E-4</v>
+        <v>7.2134580263658044E-5</v>
       </c>
       <c r="M23">
-        <v>-4.6427709508903119E-4</v>
+        <v>-3.8423601706332605E-4</v>
       </c>
       <c r="N23">
-        <v>-3.9430563060456614E-4</v>
+        <v>-7.0866272852798673E-5</v>
       </c>
       <c r="O23">
-        <v>7.6876093061210106E-5</v>
+        <v>-6.0251583119956499E-5</v>
       </c>
       <c r="P23">
-        <v>-9.6934724572757524E-5</v>
+        <v>2.2828525415892866E-4</v>
       </c>
       <c r="Q23">
-        <v>-2.661655520219098E-4</v>
+        <v>8.0731490063672487E-5</v>
       </c>
       <c r="R23">
-        <v>1.7546977267600099E-4</v>
+        <v>-1.1991082457825809E-4</v>
       </c>
       <c r="S23">
-        <v>-1.0403971901812124E-4</v>
+        <v>-4.6164450322705355E-4</v>
       </c>
       <c r="T23">
-        <v>-2.4145573694213059E-4</v>
+        <v>-1.2656278945907731E-4</v>
       </c>
       <c r="U23">
-        <v>-1.1906319902616792E-4</v>
+        <v>-6.3245886603848778E-3</v>
       </c>
       <c r="V23">
-        <v>6.4511188072241326E-5</v>
+        <v>1.9969843380792177E-5</v>
       </c>
       <c r="W23">
-        <v>4.5726485996641208E-5</v>
+        <v>1.1632564856991036E-4</v>
       </c>
       <c r="X23">
-        <v>2.3963036145122109E-3</v>
+        <v>3.9041223112306163E-3</v>
       </c>
       <c r="Y23">
-        <v>1.1394132423619282E-3</v>
+        <v>2.1033204377843336E-3</v>
       </c>
       <c r="Z23">
-        <v>1.14180093045091E-3</v>
+        <v>1.7861941311982702E-3</v>
       </c>
       <c r="AA23">
-        <v>1.128617649464017E-3</v>
+        <v>1.8520561989303131E-3</v>
       </c>
       <c r="AB23">
-        <v>-1.2986655483020808E-5</v>
+        <v>-1.5171793384304166E-4</v>
       </c>
       <c r="AC23">
-        <v>-4.7846737407848965E-6</v>
+        <v>1.9407337709496857E-4</v>
       </c>
       <c r="AD23">
-        <v>4.7319190284916661E-5</v>
+        <v>-4.4012523390427651E-4</v>
       </c>
       <c r="AE23">
-        <v>-4.4250594001484303E-4</v>
+        <v>9.6168033885531377E-3</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="4">
-        <v>-8.8056629631783623E-2</v>
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24">
+        <v>-2.6999425750324418E-2</v>
       </c>
       <c r="C24">
-        <v>-3.4369943042798063E-5</v>
+        <v>9.3965165858727467E-5</v>
       </c>
       <c r="D24">
-        <v>4.5168458805109964E-7</v>
+        <v>-1.4457021524091158E-6</v>
       </c>
       <c r="E24">
-        <v>3.1057699376862123E-4</v>
+        <v>8.8462643243483719E-4</v>
       </c>
       <c r="F24">
-        <v>2.9942339633353343E-4</v>
+        <v>1.1539576645116312E-3</v>
       </c>
       <c r="G24">
-        <v>3.6094664196645993E-4</v>
+        <v>2.0178087705291104E-3</v>
       </c>
       <c r="H24">
-        <v>2.8059981020544682E-4</v>
+        <v>2.275508788050011E-3</v>
       </c>
       <c r="I24">
-        <v>1.0238385191772319E-4</v>
+        <v>-2.9617804134391724E-4</v>
       </c>
       <c r="J24">
-        <v>-7.9660085159065244E-5</v>
+        <v>3.1027127734345765E-5</v>
       </c>
       <c r="K24">
-        <v>-2.4582271198870403E-4</v>
+        <v>-4.778326837388408E-4</v>
       </c>
       <c r="L24">
-        <v>-3.4137581956191192E-4</v>
+        <v>-4.3427722434931371E-4</v>
       </c>
       <c r="M24">
-        <v>-1.9277684255405948E-4</v>
+        <v>-6.121932368545191E-4</v>
       </c>
       <c r="N24">
-        <v>-1.7100302444384395E-4</v>
+        <v>-6.9105148763527746E-4</v>
       </c>
       <c r="O24">
-        <v>1.0344903868390441E-4</v>
+        <v>2.975705552297446E-4</v>
       </c>
       <c r="P24">
-        <v>4.9287291610111998E-4</v>
+        <v>5.1378747704251739E-5</v>
       </c>
       <c r="Q24">
-        <v>-1.5986730426279362E-4</v>
+        <v>-6.399401024035755E-5</v>
       </c>
       <c r="R24">
-        <v>-2.2846398251503505E-4</v>
+        <v>4.3593541650084958E-4</v>
       </c>
       <c r="S24">
-        <v>-5.4826601102152367E-5</v>
+        <v>-2.4991452807371318E-4</v>
       </c>
       <c r="T24">
-        <v>8.0057584316888057E-5</v>
+        <v>6.1825727696772359E-5</v>
       </c>
       <c r="U24">
-        <v>4.5266018432429337E-4</v>
+        <v>-9.7551093127856703E-3</v>
       </c>
       <c r="V24">
-        <v>-2.1972528175086799E-4</v>
+        <v>8.1693866547207297E-4</v>
       </c>
       <c r="W24">
-        <v>1.2236270062001225E-4</v>
+        <v>2.3687198443829265E-4</v>
       </c>
       <c r="X24">
-        <v>1.1394132423619282E-3</v>
+        <v>2.1033204377843336E-3</v>
       </c>
       <c r="Y24">
-        <v>3.3146367685923141E-3</v>
+        <v>5.2768462651535553E-3</v>
       </c>
       <c r="Z24">
-        <v>1.126972949342196E-3</v>
+        <v>1.7453396151478637E-3</v>
       </c>
       <c r="AA24">
-        <v>1.1399084708895184E-3</v>
+        <v>1.8162323490049325E-3</v>
       </c>
       <c r="AB24">
-        <v>-1.1819314082355626E-5</v>
+        <v>-2.1742628443621075E-4</v>
       </c>
       <c r="AC24">
-        <v>-1.0156273015465917E-4</v>
+        <v>-1.5960144898752266E-4</v>
       </c>
       <c r="AD24">
-        <v>4.5358370753200562E-5</v>
+        <v>-5.6658596963453291E-4</v>
       </c>
       <c r="AE24">
-        <v>-1.1450566768274675E-3</v>
+        <v>1.2483790353955623E-2</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="4">
-        <v>1.306812135078203E-2</v>
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25">
+        <v>6.611732298753259E-2</v>
       </c>
       <c r="C25">
-        <v>5.7247109565838894E-6</v>
+        <v>-1.6917361960915034E-4</v>
       </c>
       <c r="D25">
-        <v>1.5333999195543346E-8</v>
+        <v>2.4065892310144482E-6</v>
       </c>
       <c r="E25">
-        <v>1.7767527515970575E-4</v>
+        <v>-3.6064803144921593E-5</v>
       </c>
       <c r="F25">
-        <v>1.9853308174726752E-4</v>
+        <v>-2.7223485210811898E-4</v>
       </c>
       <c r="G25">
-        <v>2.2530322637951653E-4</v>
+        <v>3.111905074119673E-4</v>
       </c>
       <c r="H25">
-        <v>2.605508110060199E-4</v>
+        <v>3.1228006393693979E-4</v>
       </c>
       <c r="I25">
-        <v>3.4609419491087924E-5</v>
+        <v>-2.7750551696720379E-4</v>
       </c>
       <c r="J25">
-        <v>5.1172868672602211E-5</v>
+        <v>-6.2188839705147776E-5</v>
       </c>
       <c r="K25">
-        <v>-1.284220570935005E-4</v>
+        <v>-3.8246733922961407E-4</v>
       </c>
       <c r="L25">
-        <v>-1.2230621992551528E-4</v>
+        <v>-3.3983709615911795E-4</v>
       </c>
       <c r="M25">
-        <v>-1.3906646043800389E-4</v>
+        <v>-5.6821633514136938E-4</v>
       </c>
       <c r="N25">
-        <v>-1.4266392760561245E-4</v>
+        <v>-3.3076199473364154E-4</v>
       </c>
       <c r="O25">
-        <v>8.3212268812885487E-5</v>
+        <v>2.5410061215240445E-4</v>
       </c>
       <c r="P25">
-        <v>2.1397395422366526E-4</v>
+        <v>3.4452728579310258E-4</v>
       </c>
       <c r="Q25">
-        <v>-8.3156147322452931E-5</v>
+        <v>-2.9044001037349838E-4</v>
       </c>
       <c r="R25">
-        <v>-8.2324881837983325E-5</v>
+        <v>4.08985385420748E-5</v>
       </c>
       <c r="S25">
-        <v>-2.3388965619314977E-5</v>
+        <v>-3.1266888160362202E-4</v>
       </c>
       <c r="T25">
-        <v>-2.6731577784837058E-4</v>
+        <v>6.9160869954369361E-5</v>
       </c>
       <c r="U25">
-        <v>3.8195269640143442E-4</v>
+        <v>-5.8251029763756179E-3</v>
       </c>
       <c r="V25">
-        <v>9.1546500222922404E-5</v>
+        <v>3.631621331590465E-4</v>
       </c>
       <c r="W25">
-        <v>9.0385805348541825E-5</v>
+        <v>3.4509632723331188E-4</v>
       </c>
       <c r="X25">
-        <v>1.14180093045091E-3</v>
+        <v>1.7861941311982702E-3</v>
       </c>
       <c r="Y25">
-        <v>1.126972949342196E-3</v>
+        <v>1.7453396151478637E-3</v>
       </c>
       <c r="Z25">
-        <v>2.4034957567781387E-3</v>
+        <v>2.7388737757088116E-3</v>
       </c>
       <c r="AA25">
-        <v>1.136619478606092E-3</v>
+        <v>1.6972782942771014E-3</v>
       </c>
       <c r="AB25">
-        <v>-2.4725432462594121E-5</v>
+        <v>-1.7270325029185616E-4</v>
       </c>
       <c r="AC25">
-        <v>2.7851526926298562E-5</v>
+        <v>1.5641171722602024E-4</v>
       </c>
       <c r="AD25">
-        <v>9.8701359849394127E-5</v>
+        <v>-2.6754133944927722E-4</v>
       </c>
       <c r="AE25">
-        <v>-1.6252374383883749E-3</v>
+        <v>1.2542017481454802E-2</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="4">
-        <v>-4.3127899685774435E-2</v>
+      <c r="B26">
+        <v>-8.6944866979451113E-2</v>
       </c>
       <c r="C26">
-        <v>-1.5838513064547559E-5</v>
+        <v>-3.875855575427925E-5</v>
       </c>
       <c r="D26">
-        <v>2.6570736051742815E-7</v>
+        <v>3.0475044868048156E-7</v>
       </c>
       <c r="E26">
-        <v>2.8429778853909923E-4</v>
+        <v>1.555712424833489E-4</v>
       </c>
       <c r="F26">
-        <v>2.7598110523056212E-4</v>
+        <v>-1.6058912491110668E-4</v>
       </c>
       <c r="G26">
-        <v>3.9546046006957644E-4</v>
+        <v>5.2490679053886951E-4</v>
       </c>
       <c r="H26">
-        <v>4.0835041409025886E-4</v>
+        <v>7.0290194679995498E-4</v>
       </c>
       <c r="I26">
-        <v>3.9438556723504873E-5</v>
+        <v>-2.165427260908937E-4</v>
       </c>
       <c r="J26">
-        <v>-1.7265724705360424E-5</v>
+        <v>-1.6239261766208763E-4</v>
       </c>
       <c r="K26">
-        <v>4.6902342506572204E-4</v>
+        <v>2.5723409530692409E-5</v>
       </c>
       <c r="L26">
-        <v>-1.0161682224577289E-4</v>
+        <v>-1.5114739733154692E-4</v>
       </c>
       <c r="M26">
-        <v>-4.9608189989342431E-5</v>
+        <v>-3.9098676380741604E-4</v>
       </c>
       <c r="N26">
-        <v>3.8489258457458618E-5</v>
+        <v>-1.8219403422939373E-4</v>
       </c>
       <c r="O26">
-        <v>4.962905437433277E-5</v>
+        <v>2.6284742542824436E-4</v>
       </c>
       <c r="P26">
-        <v>-4.8228911015247774E-6</v>
+        <v>1.6895230994670891E-4</v>
       </c>
       <c r="Q26">
-        <v>-5.6907486115411382E-5</v>
+        <v>-2.877600456760495E-4</v>
       </c>
       <c r="R26">
-        <v>1.7121583925899119E-4</v>
+        <v>2.5207197076730983E-5</v>
       </c>
       <c r="S26">
-        <v>4.2485836602178115E-5</v>
+        <v>-3.3986133414734814E-4</v>
       </c>
       <c r="T26">
-        <v>7.9096730570043443E-6</v>
+        <v>4.7610974969589451E-5</v>
       </c>
       <c r="U26">
-        <v>5.0330488759703189E-4</v>
+        <v>-5.0273970842322768E-3</v>
       </c>
       <c r="V26">
-        <v>6.6245223789805196E-5</v>
+        <v>4.5075525691440875E-4</v>
       </c>
       <c r="W26">
-        <v>6.3410483441622473E-5</v>
+        <v>3.1547674107313545E-4</v>
       </c>
       <c r="X26">
-        <v>1.128617649464017E-3</v>
+        <v>1.8520561989303131E-3</v>
       </c>
       <c r="Y26">
-        <v>1.1399084708895184E-3</v>
+        <v>1.8162323490049325E-3</v>
       </c>
       <c r="Z26">
-        <v>1.136619478606092E-3</v>
+        <v>1.6972782942771014E-3</v>
       </c>
       <c r="AA26">
-        <v>1.6759501026546804E-3</v>
+        <v>2.7756221090144495E-3</v>
       </c>
       <c r="AB26">
-        <v>-1.3352418916546307E-5</v>
+        <v>-1.5561456830912235E-4</v>
       </c>
       <c r="AC26">
-        <v>2.4982273494333625E-5</v>
+        <v>2.6432586247279223E-4</v>
       </c>
       <c r="AD26">
-        <v>5.3013328795380545E-5</v>
+        <v>-2.9390360070430903E-4</v>
       </c>
       <c r="AE26">
-        <v>-1.8101207599157086E-3</v>
+        <v>8.87242350477754E-3</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="4">
-        <v>1.8471480415839833E-2</v>
+      <c r="B27">
+        <v>-1.2445048803401693E-2</v>
       </c>
       <c r="C27">
-        <v>5.9137605493958998E-6</v>
+        <v>2.7676159033733147E-5</v>
       </c>
       <c r="D27">
-        <v>-1.1857098752095007E-7</v>
+        <v>-2.0298817239389688E-7</v>
       </c>
       <c r="E27">
-        <v>-1.5808479232049642E-5</v>
+        <v>-4.1240557598391076E-5</v>
       </c>
       <c r="F27">
-        <v>-1.4929545295904917E-5</v>
+        <v>7.8199851678291627E-5</v>
       </c>
       <c r="G27">
-        <v>-2.6689480399168821E-6</v>
+        <v>-1.9824853210931477E-4</v>
       </c>
       <c r="H27">
-        <v>6.4342486495588409E-6</v>
+        <v>-2.275053647680643E-4</v>
       </c>
       <c r="I27">
-        <v>-2.7214548413133252E-6</v>
+        <v>7.9762339600379759E-5</v>
       </c>
       <c r="J27">
-        <v>-2.7829571149668148E-6</v>
+        <v>-2.1941907255594692E-5</v>
       </c>
       <c r="K27">
-        <v>-2.8285873803390448E-5</v>
+        <v>-1.2153932766847259E-4</v>
       </c>
       <c r="L27">
-        <v>-1.3468760293948025E-5</v>
+        <v>-6.3188053292702329E-5</v>
       </c>
       <c r="M27">
-        <v>-3.8728019827620447E-5</v>
+        <v>-3.1311804414090039E-5</v>
       </c>
       <c r="N27">
-        <v>-3.7190050698999972E-5</v>
+        <v>-7.879956687860401E-5</v>
       </c>
       <c r="O27">
-        <v>4.1569522667938513E-5</v>
+        <v>-2.2960068732225786E-4</v>
       </c>
       <c r="P27">
-        <v>-3.8323392250187401E-5</v>
+        <v>-1.8890471060084807E-4</v>
       </c>
       <c r="Q27">
-        <v>-3.8230551777755741E-5</v>
+        <v>1.6316875023124995E-4</v>
       </c>
       <c r="R27">
-        <v>3.086857548289209E-5</v>
+        <v>7.5724639217917417E-5</v>
       </c>
       <c r="S27">
-        <v>1.5451025931629641E-5</v>
+        <v>1.9454093844275947E-4</v>
       </c>
       <c r="T27">
-        <v>2.7116128091147975E-5</v>
+        <v>7.3684689751557161E-5</v>
       </c>
       <c r="U27">
-        <v>-3.9745613158252062E-4</v>
+        <v>6.3095874666153851E-2</v>
       </c>
       <c r="V27">
-        <v>2.3522284162458171E-5</v>
+        <v>-4.7756520244131122E-5</v>
       </c>
       <c r="W27">
-        <v>5.4576414940648319E-6</v>
+        <v>-2.0618813307545799E-4</v>
       </c>
       <c r="X27">
-        <v>-1.2986655483020808E-5</v>
+        <v>-1.5171793384304166E-4</v>
       </c>
       <c r="Y27">
-        <v>-1.1819314082355626E-5</v>
+        <v>-2.1742628443621075E-4</v>
       </c>
       <c r="Z27">
-        <v>-2.4725432462594121E-5</v>
+        <v>-1.7270325029185616E-4</v>
       </c>
       <c r="AA27">
-        <v>-1.3352418916546307E-5</v>
+        <v>-1.5561456830912235E-4</v>
       </c>
       <c r="AB27">
-        <v>2.6983569595569837E-5</v>
+        <v>1.2013423749410966E-3</v>
       </c>
       <c r="AC27">
-        <v>-1.0462852695158201E-4</v>
+        <v>1.3158745148023898E-3</v>
       </c>
       <c r="AD27">
-        <v>-1.555754373125941E-4</v>
+        <v>-4.1345549131951553E-4</v>
       </c>
       <c r="AE27">
-        <v>1.0539250620569688E-4</v>
+        <v>-0.10441329849340564</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="4">
-        <v>3.7713558541715229E-2</v>
+      <c r="B28">
+        <v>1.4552076719212425E-2</v>
       </c>
       <c r="C28">
-        <v>5.159375546955015E-5</v>
+        <v>-2.8837001124054889E-4</v>
       </c>
       <c r="D28">
-        <v>-8.1506749543800876E-7</v>
+        <v>3.7089664899785427E-6</v>
       </c>
       <c r="E28">
-        <v>2.3912491505732447E-4</v>
+        <v>-3.3106782533749848E-4</v>
       </c>
       <c r="F28">
-        <v>-3.279483099759891E-5</v>
+        <v>-3.8058554416651037E-4</v>
       </c>
       <c r="G28">
-        <v>1.3158211822331036E-5</v>
+        <v>-1.1234744616190403E-4</v>
       </c>
       <c r="H28">
-        <v>5.1524792219336413E-5</v>
+        <v>-1.7836881509195371E-4</v>
       </c>
       <c r="I28">
-        <v>-2.5578364481533339E-5</v>
+        <v>-4.8693203654902339E-5</v>
       </c>
       <c r="J28">
-        <v>-3.9288890784926135E-5</v>
+        <v>-2.9354741869922976E-4</v>
       </c>
       <c r="K28">
-        <v>1.2965498805307535E-3</v>
+        <v>6.4573110388512628E-4</v>
       </c>
       <c r="L28">
-        <v>-6.8579148196939999E-5</v>
+        <v>1.084405486169622E-3</v>
       </c>
       <c r="M28">
-        <v>-5.9849585982117703E-5</v>
+        <v>7.1781241283169067E-4</v>
       </c>
       <c r="N28">
-        <v>-1.1601445814387462E-4</v>
+        <v>9.289849170115716E-4</v>
       </c>
       <c r="O28">
-        <v>-5.2681368138991151E-4</v>
+        <v>-2.0857481001030124E-5</v>
       </c>
       <c r="P28">
-        <v>1.7784775603164904E-4</v>
+        <v>5.5571748364532448E-4</v>
       </c>
       <c r="Q28">
-        <v>4.545165394622421E-4</v>
+        <v>3.222092623969895E-4</v>
       </c>
       <c r="R28">
-        <v>-3.1174316931970438E-4</v>
+        <v>-4.4206742426121902E-4</v>
       </c>
       <c r="S28">
-        <v>1.1634006715949784E-4</v>
+        <v>-1.3531950853782064E-4</v>
       </c>
       <c r="T28">
-        <v>4.5098671527915232E-5</v>
+        <v>-1.333637379017402E-4</v>
       </c>
       <c r="U28">
-        <v>-6.5513384018372339E-4</v>
+        <v>8.2458579527455056E-2</v>
       </c>
       <c r="V28">
-        <v>-3.6485347385505074E-7</v>
+        <v>-2.0169701332905989E-4</v>
       </c>
       <c r="W28">
-        <v>-8.1539065810655041E-5</v>
+        <v>3.6880647758329762E-5</v>
       </c>
       <c r="X28">
-        <v>-4.7846737407848965E-6</v>
+        <v>1.9407337709496857E-4</v>
       </c>
       <c r="Y28">
-        <v>-1.0156273015465917E-4</v>
+        <v>-1.5960144898752266E-4</v>
       </c>
       <c r="Z28">
-        <v>2.7851526926298562E-5</v>
+        <v>1.5641171722602024E-4</v>
       </c>
       <c r="AA28">
-        <v>2.4982273494333625E-5</v>
+        <v>2.6432586247279223E-4</v>
       </c>
       <c r="AB28">
-        <v>-1.0462852695158201E-4</v>
+        <v>1.3158745148023898E-3</v>
       </c>
       <c r="AC28">
-        <v>3.2376679397965007E-3</v>
+        <v>1.0209771673958271E-2</v>
       </c>
       <c r="AD28">
-        <v>8.3715384164173752E-4</v>
+        <v>1.3874063229439059E-3</v>
       </c>
       <c r="AE28">
-        <v>1.5120088370187438E-3</v>
+        <v>-0.12726289467461438</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="4">
-        <v>1.0680613465932139E-2</v>
+      <c r="B29">
+        <v>4.3120410636546876E-2</v>
       </c>
       <c r="C29">
-        <v>2.5710270849494711E-5</v>
+        <v>-8.8906726277164852E-5</v>
       </c>
       <c r="D29">
-        <v>-4.0582316391967095E-7</v>
+        <v>1.0264545465087224E-6</v>
       </c>
       <c r="E29">
-        <v>3.1818351229789257E-4</v>
+        <v>1.9770032406867682E-4</v>
       </c>
       <c r="F29">
-        <v>2.3388041275380824E-4</v>
+        <v>3.3909788902428654E-4</v>
       </c>
       <c r="G29">
-        <v>1.7514425447485776E-4</v>
+        <v>-3.9797461241870326E-4</v>
       </c>
       <c r="H29">
-        <v>1.6785572366683236E-4</v>
+        <v>-3.5256610842830015E-4</v>
       </c>
       <c r="I29">
-        <v>-5.9407444466610905E-5</v>
+        <v>-2.8823954779161811E-5</v>
       </c>
       <c r="J29">
-        <v>-3.1125863325718868E-5</v>
+        <v>-2.8384302803011391E-4</v>
       </c>
       <c r="K29">
-        <v>1.7246407844620504E-4</v>
+        <v>-7.1332150796014036E-5</v>
       </c>
       <c r="L29">
-        <v>-2.1924498427777772E-5</v>
+        <v>8.4224755973066195E-5</v>
       </c>
       <c r="M29">
-        <v>1.2623628609969434E-4</v>
+        <v>1.2550409944924509E-4</v>
       </c>
       <c r="N29">
-        <v>1.4057615879197946E-4</v>
+        <v>-1.0482830196222558E-5</v>
       </c>
       <c r="O29">
-        <v>-1.1693663405852828E-4</v>
+        <v>-3.2755124765183712E-4</v>
       </c>
       <c r="P29">
-        <v>1.2564404886540901E-4</v>
+        <v>-3.36103046794762E-4</v>
       </c>
       <c r="Q29">
-        <v>-8.3217073198970336E-6</v>
+        <v>1.978664787983278E-4</v>
       </c>
       <c r="R29">
-        <v>-2.4049389922529464E-4</v>
+        <v>7.7905155236683771E-5</v>
       </c>
       <c r="S29">
-        <v>1.2973870902276401E-6</v>
+        <v>4.2491279157220584E-5</v>
       </c>
       <c r="T29">
-        <v>3.9161793982513213E-6</v>
+        <v>-3.0856963767368921E-4</v>
       </c>
       <c r="U29">
-        <v>3.5986587515630906E-3</v>
+        <v>-8.782333296422945E-3</v>
       </c>
       <c r="V29">
-        <v>4.2352086338522978E-5</v>
+        <v>-8.3207123552580891E-5</v>
       </c>
       <c r="W29">
-        <v>5.568759610072283E-6</v>
+        <v>-3.5070026313477196E-4</v>
       </c>
       <c r="X29">
-        <v>4.7319190284916661E-5</v>
+        <v>-4.4012523390427651E-4</v>
       </c>
       <c r="Y29">
-        <v>4.5358370753200562E-5</v>
+        <v>-5.6658596963453291E-4</v>
       </c>
       <c r="Z29">
-        <v>9.8701359849394127E-5</v>
+        <v>-2.6754133944927722E-4</v>
       </c>
       <c r="AA29">
-        <v>5.3013328795380545E-5</v>
+        <v>-2.9390360070430903E-4</v>
       </c>
       <c r="AB29">
-        <v>-1.555754373125941E-4</v>
+        <v>-4.1345549131951553E-4</v>
       </c>
       <c r="AC29">
-        <v>8.3715384164173752E-4</v>
+        <v>1.3874063229439059E-3</v>
       </c>
       <c r="AD29">
-        <v>3.3083323387292302E-3</v>
+        <v>1.1826716374992389E-2</v>
       </c>
       <c r="AE29">
-        <v>-3.3889965547701691E-3</v>
+        <v>2.0273257185484346E-2</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="4">
-        <v>-2.9088969591501219</v>
+      <c r="B30">
+        <v>-4.3252847747838725</v>
       </c>
       <c r="C30">
-        <v>-1.3815079267640334E-2</v>
+        <v>-2.4829431322037993E-2</v>
       </c>
       <c r="D30">
-        <v>1.9533488433813129E-4</v>
+        <v>3.2634569391603403E-4</v>
       </c>
       <c r="E30">
-        <v>-1.2059508707464417E-2</v>
+        <v>-1.2387257461297358E-2</v>
       </c>
       <c r="F30">
-        <v>-8.55532189017464E-3</v>
+        <v>-2.2905120743896279E-2</v>
       </c>
       <c r="G30">
-        <v>-7.707975565897307E-3</v>
+        <v>9.8791132255200004E-4</v>
       </c>
       <c r="H30">
-        <v>-7.6562263933973307E-3</v>
+        <v>-7.1839709934884421E-4</v>
       </c>
       <c r="I30">
-        <v>4.6719183804137653E-3</v>
+        <v>-9.458810079688261E-4</v>
       </c>
       <c r="J30">
-        <v>-2.4581550854899849E-3</v>
+        <v>4.0779576794641205E-3</v>
       </c>
       <c r="K30">
-        <v>-8.2742245904287581E-2</v>
+        <v>-6.9344512243916911E-2</v>
       </c>
       <c r="L30">
-        <v>-8.2753910604096759E-2</v>
+        <v>-7.592401252361336E-2</v>
       </c>
       <c r="M30">
-        <v>-8.4244609024092143E-2</v>
+        <v>-7.4408123300112816E-2</v>
       </c>
       <c r="N30">
-        <v>-8.3793811011936059E-2</v>
+        <v>-6.980181834357313E-2</v>
       </c>
       <c r="O30">
-        <v>-6.2254617512547822E-4</v>
+        <v>2.5008630614879075E-2</v>
       </c>
       <c r="P30">
-        <v>8.6616340823723252E-4</v>
+        <v>1.6504489093138681E-2</v>
       </c>
       <c r="Q30">
-        <v>-8.4558287762910578E-4</v>
+        <v>-2.1883668073604076E-2</v>
       </c>
       <c r="R30">
-        <v>3.7602632527530353E-3</v>
+        <v>-1.0053438042088594E-2</v>
       </c>
       <c r="S30">
-        <v>-4.2793830195181314E-3</v>
+        <v>-1.6196901215115495E-2</v>
       </c>
       <c r="T30">
-        <v>-9.7520024108732409E-3</v>
+        <v>-8.7064736070815163E-3</v>
       </c>
       <c r="U30">
-        <v>-8.2991507920076202E-2</v>
+        <v>-5.6162355854335502</v>
       </c>
       <c r="V30">
-        <v>-2.0888084053528877E-2</v>
+        <v>-1.1559934617145107E-2</v>
       </c>
       <c r="W30">
-        <v>-2.9693769645715174E-3</v>
+        <v>1.2265932677672115E-2</v>
       </c>
       <c r="X30">
-        <v>-4.4250594001484303E-4</v>
+        <v>9.6168033885531377E-3</v>
       </c>
       <c r="Y30">
-        <v>-1.1450566768274675E-3</v>
+        <v>1.2483790353955623E-2</v>
       </c>
       <c r="Z30">
-        <v>-1.6252374383883749E-3</v>
+        <v>1.2542017481454802E-2</v>
       </c>
       <c r="AA30">
-        <v>-1.8101207599157086E-3</v>
+        <v>8.87242350477754E-3</v>
       </c>
       <c r="AB30">
-        <v>1.0539250620569688E-4</v>
+        <v>-0.10441329849340564</v>
       </c>
       <c r="AC30">
-        <v>1.5120088370187438E-3</v>
+        <v>-0.12726289467461438</v>
       </c>
       <c r="AD30">
-        <v>-3.3889965547701691E-3</v>
+        <v>2.0273257185484346E-2</v>
       </c>
       <c r="AE30">
-        <v>0.44023385203122389</v>
+        <v>9.7461169630096833</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D1F369-41F0-4695-94AC-40570846D454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2EC755-5B17-44E1-A8B9-80EDAC7563AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -151,11 +151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -193,10 +189,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,10 +538,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -567,7 +562,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" t="s">
@@ -581,7 +576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -683,10 +678,6 @@
       <c r="F5">
         <v>10.430772870143954</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -698,7 +689,7 @@
   <dimension ref="A1:AE30"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="1" max="1" width="29.06640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.45">

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBEAD3C-F0E5-4CEA-A30F-D564A9CF72A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A273F17F-B8B2-4420-ACC6-854015F39794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -8,15 +8,15 @@
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId2"/>
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
-    <sheet name="F1a" sheetId="3" r:id="rId5"/>
-    <sheet name="F1b" sheetId="4" r:id="rId6"/>
+    <sheet name="UK_F1a" sheetId="3" r:id="rId5"/>
+    <sheet name="UK_F1b" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="93">
   <si>
     <t>Description:</t>
   </si>
@@ -72,6 +72,9 @@
     <t>c5</t>
   </si>
   <si>
+    <t>c6</t>
+  </si>
+  <si>
     <t>r1</t>
   </si>
   <si>
@@ -93,7 +96,7 @@
     <t>Constant</t>
   </si>
   <si>
-    <t>COFFICIENT</t>
+    <t>COEFFICIENT</t>
   </si>
   <si>
     <t>F1a - Fertility in initial education spell</t>
@@ -109,9 +112,6 @@
   </si>
   <si>
     <t>Log likelihood</t>
-  </si>
-  <si>
-    <t>c6</t>
   </si>
   <si>
     <t>c7</t>
@@ -301,7 +301,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="97">
+  <fonts count="99">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -341,6 +341,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -705,7 +713,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="91">
+  <borders count="93">
     <border>
       <left/>
       <right/>
@@ -1343,11 +1351,25 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -1413,15 +1435,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1705,7 +1727,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="2" fontId="95" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="96" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1791,69 +1821,69 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
-        <v>26</v>
+      <c r="A3" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>0.46195897419457777</v>
+        <v>0.43998529245408224</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>19.972281645276095</v>
+        <v>23.75823176610708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>-17.810121935809246</v>
+        <v>-18.730961339184425</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="92" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
-        <v>0.27624474315426417</v>
+        <v>0.27609637012682686</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>6149.1689456270406</v>
+        <v>6133.2849385530972</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>41136</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>-14206.817041756953</v>
+        <v>-14209.729502060067</v>
       </c>
     </row>
   </sheetData>
@@ -1862,145 +1892,186 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
         <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="8">
-        <v>-0.66919125876892016</v>
+        <v>-0.61897535628987521</v>
       </c>
       <c r="C2">
-        <v>0.024546837105981573</v>
+        <v>0.018100350483756876</v>
       </c>
       <c r="D2">
-        <v>-0.024489876986718007</v>
+        <v>-0.013556190437132964</v>
       </c>
       <c r="E2">
-        <v>-0.00019393759818385828</v>
+        <v>0.00076140969633739161</v>
       </c>
       <c r="F2">
-        <v>-0.080936622577300041</v>
+        <v>-0.053089699172211208</v>
       </c>
       <c r="G2">
-        <v>-0.45209281000770418</v>
+        <v>-0.055592986304685815</v>
+      </c>
+      <c r="H2">
+        <v>-0.35285307068836597</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="10">
-        <v>0.27930033959742384</v>
+        <v>0.16760982099724808</v>
       </c>
       <c r="C3">
-        <v>-0.024489876986718007</v>
+        <v>-0.013556190437132964</v>
       </c>
       <c r="D3">
-        <v>0.3688691049178825</v>
+        <v>0.32800263372959543</v>
       </c>
       <c r="E3">
-        <v>-0.00030987902268207659</v>
+        <v>-0.0023337062895838296</v>
       </c>
       <c r="F3">
-        <v>0.087995864986091354</v>
+        <v>0.033134374343353555</v>
       </c>
       <c r="G3">
-        <v>0.14902881355297209</v>
+        <v>0.24587819699228119</v>
+      </c>
+      <c r="H3">
+        <v>0.0046220612863422661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="12">
-        <v>0.046476116335624651</v>
+        <v>0.050713503815487233</v>
       </c>
       <c r="C4">
-        <v>-0.00019393759818385828</v>
+        <v>0.00076140969633739161</v>
       </c>
       <c r="D4">
-        <v>-0.00030987902268207659</v>
+        <v>-0.0023337062895838296</v>
       </c>
       <c r="E4">
-        <v>0.0075374420419155085</v>
+        <v>0.0072881401380226838</v>
       </c>
       <c r="F4">
-        <v>0.021848427294217578</v>
+        <v>0.016884111535426599</v>
       </c>
       <c r="G4">
-        <v>-0.094768717915042322</v>
+        <v>0.0088005733941555545</v>
+      </c>
+      <c r="H4">
+        <v>-0.10814923360882489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="14">
-        <v>2.9195735851688491</v>
+        <v>2.7285630583085254</v>
       </c>
       <c r="C5">
-        <v>-0.080936622577300041</v>
+        <v>-0.053089699172211208</v>
       </c>
       <c r="D5">
-        <v>0.087995864986091354</v>
+        <v>0.033134374343353555</v>
       </c>
       <c r="E5">
-        <v>0.021848427294217578</v>
+        <v>0.016884111535426599</v>
       </c>
       <c r="F5">
-        <v>0.67030347334797558</v>
+        <v>0.53327567120109465</v>
       </c>
       <c r="G5">
-        <v>1.1614025188353079</v>
+        <v>0.24640321150460492</v>
+      </c>
+      <c r="H5">
+        <v>0.74974437798476989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="16">
-        <v>12.04247113943809</v>
+        <v>1.9786774546027115</v>
       </c>
       <c r="C6">
-        <v>-0.45209281000770418</v>
+        <v>-0.055592986304685815</v>
       </c>
       <c r="D6">
-        <v>0.14902881355297209</v>
+        <v>0.24587819699228119</v>
       </c>
       <c r="E6">
-        <v>-0.094768717915042322</v>
+        <v>0.0088005733941555545</v>
       </c>
       <c r="F6">
-        <v>1.1614025188353079</v>
+        <v>0.24640321150460492</v>
       </c>
       <c r="G6">
-        <v>9.9256242248754702</v>
+        <v>2.7048866035828816</v>
+      </c>
+      <c r="H6">
+        <v>0.72408127917340115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="18">
+        <v>11.100165933857863</v>
+      </c>
+      <c r="C7">
+        <v>-0.35285307068836597</v>
+      </c>
+      <c r="D7">
+        <v>0.0046220612863422661</v>
+      </c>
+      <c r="E7">
+        <v>-0.10814923360882489</v>
+      </c>
+      <c r="F7">
+        <v>0.74974437798476989</v>
+      </c>
+      <c r="G7">
+        <v>0.72408127917340115</v>
+      </c>
+      <c r="H7">
+        <v>8.3680433604425613</v>
       </c>
     </row>
   </sheetData>
@@ -2013,14 +2084,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>25</v>
+      <c r="A1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>61</v>
@@ -2104,7 +2175,7 @@
         <v>87</v>
       </c>
       <c r="AE1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF1" t="s">
         <v>88</v>
@@ -2116,3968 +2187,3968 @@
         <v>90</v>
       </c>
       <c r="AI1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ1" t="s">
         <v>91</v>
       </c>
       <c r="AK1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="21">
-        <v>0.08270358134733212</v>
+      <c r="A2" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="23">
+        <v>0.08281094739970464</v>
       </c>
       <c r="C2">
-        <v>0.00039296614929917027</v>
+        <v>0.00039251875800426158</v>
       </c>
       <c r="D2">
-        <v>-5.7815984591325914e-006</v>
+        <v>-5.7743545402470278e-006</v>
       </c>
       <c r="E2">
-        <v>-2.2861903998971597e-005</v>
+        <v>-1.9249407553208349e-005</v>
       </c>
       <c r="F2">
-        <v>-4.6899265690170697e-005</v>
+        <v>-4.4018824410242598e-005</v>
       </c>
       <c r="G2">
-        <v>-8.0684101657686638e-005</v>
+        <v>-7.7464774037587459e-005</v>
       </c>
       <c r="H2">
-        <v>-8.1601339374850102e-005</v>
+        <v>-7.8322271745894152e-005</v>
       </c>
       <c r="I2">
-        <v>-9.7977744698626076e-005</v>
+        <v>-9.7961890573745967e-005</v>
       </c>
       <c r="J2">
-        <v>1.7634323004770433e-005</v>
+        <v>1.7944040761638737e-005</v>
       </c>
       <c r="K2">
-        <v>-6.1477876174604032e-007</v>
+        <v>-6.0528235783486892e-007</v>
       </c>
       <c r="L2">
-        <v>2.3103148535298955e-006</v>
+        <v>2.3017795579131125e-006</v>
       </c>
       <c r="M2">
-        <v>3.5787688402047838e-005</v>
+        <v>3.7268962574832799e-005</v>
       </c>
       <c r="N2">
-        <v>3.3955489275193504e-005</v>
+        <v>3.2705467015818872e-005</v>
       </c>
       <c r="O2">
-        <v>4.8613528198598443e-005</v>
+        <v>4.8539798399902537e-005</v>
       </c>
       <c r="P2">
-        <v>7.2687335164220261e-006</v>
+        <v>8.5230097611964893e-006</v>
       </c>
       <c r="Q2">
-        <v>-6.4926426633755919e-006</v>
+        <v>-6.2496492293874007e-006</v>
       </c>
       <c r="R2">
-        <v>1.4655084664476521e-005</v>
+        <v>1.3527777325092688e-005</v>
       </c>
       <c r="S2">
-        <v>5.5722437820825783e-005</v>
+        <v>5.6752725777583406e-005</v>
       </c>
       <c r="T2">
-        <v>8.0062575125312927e-005</v>
+        <v>8.1692528790807978e-005</v>
       </c>
       <c r="U2">
-        <v>6.7211544627742825e-005</v>
+        <v>6.8299365467097955e-005</v>
       </c>
       <c r="V2">
-        <v>8.8093820774956706e-005</v>
+        <v>8.9761743751595735e-005</v>
       </c>
       <c r="W2">
-        <v>8.3160063232037319e-005</v>
+        <v>8.4763511664361774e-005</v>
       </c>
       <c r="X2">
-        <v>9.7180196047770995e-005</v>
+        <v>9.8246970137814884e-005</v>
       </c>
       <c r="Y2">
-        <v>4.468553904350735e-005</v>
+        <v>4.6224320986391204e-005</v>
       </c>
       <c r="Z2">
-        <v>6.9563487958185059e-005</v>
+        <v>7.0778500516263058e-005</v>
       </c>
       <c r="AA2">
-        <v>8.3151655040130702e-005</v>
+        <v>8.5079948503975072e-005</v>
       </c>
       <c r="AB2">
-        <v>7.5127198063917183e-005</v>
+        <v>7.690201728155141e-005</v>
       </c>
       <c r="AC2">
-        <v>5.9494713312798365e-005</v>
+        <v>6.1508778142236459e-005</v>
       </c>
       <c r="AD2">
-        <v>8.8601440144571615e-005</v>
+        <v>9.0115108023285616e-005</v>
       </c>
       <c r="AE2">
-        <v>-8.7936311477617617e-006</v>
+        <v>-8.6059682527599417e-006</v>
       </c>
       <c r="AF2">
-        <v>1.0415766356827662e-005</v>
+        <v>1.1932872535977776e-005</v>
       </c>
       <c r="AG2">
-        <v>-1.1608866337686893e-005</v>
+        <v>-1.0292717707289828e-005</v>
       </c>
       <c r="AH2">
-        <v>-1.3072114289094071e-006</v>
+        <v>-5.1060688818251043e-007</v>
       </c>
       <c r="AI2">
-        <v>2.0928358473491261e-005</v>
+        <v>2.2355625651086439e-005</v>
       </c>
       <c r="AJ2">
-        <v>-2.776007621904707e-005</v>
+        <v>1.7698070115036192e-006</v>
       </c>
       <c r="AK2">
-        <v>-0.0059532741018664872</v>
+        <v>-0.0059696826737514631</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="23">
-        <v>-0.0025652176063727722</v>
+      <c r="B3" s="25">
+        <v>-0.0025673553979851621</v>
       </c>
       <c r="C3">
-        <v>-5.7815984591325914e-006</v>
+        <v>-5.7743545402470278e-006</v>
       </c>
       <c r="D3">
-        <v>8.6049469856210654e-008</v>
+        <v>8.5935870824106202e-008</v>
       </c>
       <c r="E3">
-        <v>3.5412793717388627e-007</v>
+        <v>2.4905505756256773e-007</v>
       </c>
       <c r="F3">
-        <v>6.6098296375113975e-007</v>
+        <v>5.8318337790373072e-007</v>
       </c>
       <c r="G3">
-        <v>1.0767753013679864e-006</v>
+        <v>9.9065983853403045e-007</v>
       </c>
       <c r="H3">
-        <v>9.8785395942277348e-007</v>
+        <v>8.993538638841971e-007</v>
       </c>
       <c r="I3">
-        <v>1.3271457881243191e-006</v>
+        <v>1.3260998799835094e-006</v>
       </c>
       <c r="J3">
-        <v>-3.7997312535893062e-008</v>
+        <v>-4.1475133734813627e-008</v>
       </c>
       <c r="K3">
-        <v>1.0131773760310046e-008</v>
+        <v>1.0041543878951043e-008</v>
       </c>
       <c r="L3">
-        <v>-3.4375617984813553e-008</v>
+        <v>-3.4249436794666086e-008</v>
       </c>
       <c r="M3">
-        <v>-3.8431320371640226e-007</v>
+        <v>-4.125536659672151e-007</v>
       </c>
       <c r="N3">
-        <v>-7.2037741193928609e-007</v>
+        <v>-7.173430179556704e-007</v>
       </c>
       <c r="O3">
-        <v>-6.0573422989463551e-007</v>
+        <v>-6.0454002822415862e-007</v>
       </c>
       <c r="P3">
-        <v>-1.2723923721316363e-007</v>
+        <v>-1.4692906511738871e-007</v>
       </c>
       <c r="Q3">
-        <v>1.0972523685424929e-007</v>
+        <v>1.0749740934547218e-007</v>
       </c>
       <c r="R3">
-        <v>-3.9025168476109379e-008</v>
+        <v>-3.0753097616218367e-008</v>
       </c>
       <c r="S3">
-        <v>-7.2949111956338029e-007</v>
+        <v>-7.6089031189485166e-007</v>
       </c>
       <c r="T3">
-        <v>-1.0559119767036436e-006</v>
+        <v>-1.0734897929720984e-006</v>
       </c>
       <c r="U3">
-        <v>-9.2515918021538417e-007</v>
+        <v>-9.3419025183669299e-007</v>
       </c>
       <c r="V3">
-        <v>-1.147264770040793e-006</v>
+        <v>-1.1651960047662571e-006</v>
       </c>
       <c r="W3">
-        <v>-1.1108265277957712e-006</v>
+        <v>-1.1263347502938863e-006</v>
       </c>
       <c r="X3">
-        <v>-1.3256339155796814e-006</v>
+        <v>-1.333431050370496e-006</v>
       </c>
       <c r="Y3">
-        <v>-6.0130938063793291e-007</v>
+        <v>-6.1524018670199585e-007</v>
       </c>
       <c r="Z3">
-        <v>-9.3566579960460737e-007</v>
+        <v>-9.4511520472124279e-007</v>
       </c>
       <c r="AA3">
-        <v>-1.1533652417715067e-006</v>
+        <v>-1.175032400804453e-006</v>
       </c>
       <c r="AB3">
-        <v>-9.8048892332197493e-007</v>
+        <v>-9.9942618394518535e-007</v>
       </c>
       <c r="AC3">
-        <v>-8.1480332167291081e-007</v>
+        <v>-8.3712284226797291e-007</v>
       </c>
       <c r="AD3">
-        <v>-1.1791774634964906e-006</v>
+        <v>-1.1950696742004009e-006</v>
       </c>
       <c r="AE3">
-        <v>1.3515299766929627e-007</v>
+        <v>1.3319062473676252e-007</v>
       </c>
       <c r="AF3">
-        <v>-1.0900105749146043e-007</v>
+        <v>-1.2617618647790231e-007</v>
       </c>
       <c r="AG3">
-        <v>1.8204632660434428e-007</v>
+        <v>1.665660822106713e-007</v>
       </c>
       <c r="AH3">
-        <v>5.1528308438287076e-008</v>
+        <v>4.4660776335722131e-008</v>
       </c>
       <c r="AI3">
-        <v>-3.1038289278835962e-007</v>
+        <v>-3.292970296199109e-007</v>
       </c>
       <c r="AJ3">
-        <v>4.2726349388245221e-007</v>
+        <v>-3.4196016768595555e-008</v>
       </c>
       <c r="AK3">
-        <v>8.5410491098072619e-005</v>
+        <v>8.5576793513498584e-005</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="25">
-        <v>-0.16381212245596233</v>
+      <c r="B4" s="27">
+        <v>-0.14679004410537683</v>
       </c>
       <c r="C4">
-        <v>-2.2861903998971597e-005</v>
+        <v>-1.9249407553208349e-005</v>
       </c>
       <c r="D4">
-        <v>3.5412793717388627e-007</v>
+        <v>2.4905505756256773e-007</v>
       </c>
       <c r="E4">
-        <v>0.002086165003764991</v>
+        <v>0.0021240315233070476</v>
       </c>
       <c r="F4">
-        <v>0.0013469286166701696</v>
+        <v>0.0013722903749406831</v>
       </c>
       <c r="G4">
-        <v>0.001400171528841839</v>
+        <v>0.0014421896402135672</v>
       </c>
       <c r="H4">
-        <v>0.0013982668398983536</v>
+        <v>0.0014449596754801659</v>
       </c>
       <c r="I4">
-        <v>-0.00020298658255787769</v>
+        <v>-0.00018652631681786991</v>
       </c>
       <c r="J4">
-        <v>7.2366409364507669e-005</v>
+        <v>4.5669968192882183e-005</v>
       </c>
       <c r="K4">
-        <v>-4.8529456116984254e-006</v>
+        <v>-4.6927011232514103e-006</v>
       </c>
       <c r="L4">
-        <v>9.4840618263835121e-007</v>
+        <v>1.1307385634511584e-006</v>
       </c>
       <c r="M4">
-        <v>2.3770729249623874e-005</v>
+        <v>6.953609615436906e-006</v>
       </c>
       <c r="N4">
-        <v>6.8494433081059145e-005</v>
+        <v>0.00025578295642256725</v>
       </c>
       <c r="O4">
-        <v>1.5558722507779673e-006</v>
+        <v>1.3490297642046699e-005</v>
       </c>
       <c r="P4">
-        <v>-9.423424275956918e-006</v>
+        <v>-4.1809253737391116e-005</v>
       </c>
       <c r="Q4">
-        <v>-1.6604064024600775e-005</v>
+        <v>-3.656873159204431e-005</v>
       </c>
       <c r="R4">
-        <v>0.00046095510819785766</v>
+        <v>0.00046322447706607705</v>
       </c>
       <c r="S4">
-        <v>0.00054381735885955268</v>
+        <v>0.00057941235831922375</v>
       </c>
       <c r="T4">
-        <v>0.00022473212364694764</v>
+        <v>0.00011945152502073578</v>
       </c>
       <c r="U4">
-        <v>0.00026605652885259721</v>
+        <v>0.00017007925205957472</v>
       </c>
       <c r="V4">
-        <v>0.00017056668583288704</v>
+        <v>7.544660562002823e-005</v>
       </c>
       <c r="W4">
-        <v>0.00020910286575433974</v>
+        <v>0.00010696817366443291</v>
       </c>
       <c r="X4">
-        <v>0.00021022546714742431</v>
+        <v>0.00010913547239267321</v>
       </c>
       <c r="Y4">
-        <v>0.00023349825005749016</v>
+        <v>0.00012130480040200606</v>
       </c>
       <c r="Z4">
-        <v>0.00019801308776431096</v>
+        <v>0.00010048376945638306</v>
       </c>
       <c r="AA4">
-        <v>0.0001553196846156383</v>
+        <v>5.083080308811535e-005</v>
       </c>
       <c r="AB4">
-        <v>0.00019077679535243881</v>
+        <v>9.36243513600591e-005</v>
       </c>
       <c r="AC4">
-        <v>0.00015726540748523221</v>
+        <v>6.3891959659697684e-005</v>
       </c>
       <c r="AD4">
-        <v>0.00025955544174505922</v>
+        <v>0.00015961664857010502</v>
       </c>
       <c r="AE4">
-        <v>-2.1049117401659752e-005</v>
+        <v>-3.3668288548761541e-005</v>
       </c>
       <c r="AF4">
-        <v>-8.2288049185899357e-006</v>
+        <v>-8.9320255582502962e-005</v>
       </c>
       <c r="AG4">
-        <v>8.3525313269354275e-005</v>
+        <v>2.0969238543456833e-005</v>
       </c>
       <c r="AH4">
-        <v>-8.2205090693667843e-005</v>
+        <v>-0.00011657213436648146</v>
       </c>
       <c r="AI4">
-        <v>0.00042795152856352561</v>
+        <v>0.0003683536085575162</v>
       </c>
       <c r="AJ4">
-        <v>-3.802722896442879e-005</v>
+        <v>2.8989460195837183e-005</v>
       </c>
       <c r="AK4">
-        <v>0.00051500258042400451</v>
+        <v>0.0019311110132411117</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="27">
-        <v>-0.28092517320258287</v>
+      <c r="B5" s="29">
+        <v>-0.27021446453951498</v>
       </c>
       <c r="C5">
-        <v>-4.6899265690170697e-005</v>
+        <v>-4.4018824410242598e-005</v>
       </c>
       <c r="D5">
-        <v>6.6098296375113975e-007</v>
+        <v>5.8318337790373072e-007</v>
       </c>
       <c r="E5">
-        <v>0.0013469286166701696</v>
+        <v>0.0013722903749406831</v>
       </c>
       <c r="F5">
-        <v>0.0019306716665387972</v>
+        <v>0.0019465932328967723</v>
       </c>
       <c r="G5">
-        <v>0.0016205882057170556</v>
+        <v>0.0016461899268286648</v>
       </c>
       <c r="H5">
-        <v>0.0016851203156259696</v>
+        <v>0.0017137269977449943</v>
       </c>
       <c r="I5">
-        <v>-6.8768316802999391e-006</v>
+        <v>3.8835938279154327e-006</v>
       </c>
       <c r="J5">
-        <v>1.1964597267425875e-005</v>
+        <v>-6.3131028003278667e-006</v>
       </c>
       <c r="K5">
-        <v>-3.3966050981376283e-006</v>
+        <v>-3.3042890398355531e-006</v>
       </c>
       <c r="L5">
-        <v>-1.1698952590491121e-006</v>
+        <v>-1.0192638483275899e-006</v>
       </c>
       <c r="M5">
-        <v>0.00040230951681130079</v>
+        <v>0.00038826278014778215</v>
       </c>
       <c r="N5">
-        <v>0.00021126049049380121</v>
+        <v>0.00033717115324915635</v>
       </c>
       <c r="O5">
-        <v>3.6040188717592823e-005</v>
+        <v>4.3834052538375533e-005</v>
       </c>
       <c r="P5">
-        <v>0.00021265689937089268</v>
+        <v>0.00018998722455728593</v>
       </c>
       <c r="Q5">
-        <v>5.9948279479928569e-007</v>
+        <v>-1.2725430983794471e-005</v>
       </c>
       <c r="R5">
-        <v>0.00056509629938558638</v>
+        <v>0.00057082216703754386</v>
       </c>
       <c r="S5">
-        <v>0.00057311835166657039</v>
+        <v>0.00059530357960510896</v>
       </c>
       <c r="T5">
-        <v>7.5640480026260143e-005</v>
+        <v>6.8955386269318282e-006</v>
       </c>
       <c r="U5">
-        <v>7.3191988146539702e-005</v>
+        <v>1.0608874571042923e-005</v>
       </c>
       <c r="V5">
-        <v>6.7123894598100121e-005</v>
+        <v>4.5102694878716839e-006</v>
       </c>
       <c r="W5">
-        <v>7.2710339832432621e-005</v>
+        <v>5.4263048517650325e-006</v>
       </c>
       <c r="X5">
-        <v>2.6059119002294227e-005</v>
+        <v>-3.9758755768698256e-005</v>
       </c>
       <c r="Y5">
-        <v>7.5382692332199739e-005</v>
+        <v>3.7262708609822007e-007</v>
       </c>
       <c r="Z5">
-        <v>6.2343287861789767e-005</v>
+        <v>-1.7451942720680957e-006</v>
       </c>
       <c r="AA5">
-        <v>8.726822481260315e-006</v>
+        <v>-5.9313579612372495e-005</v>
       </c>
       <c r="AB5">
-        <v>8.7072659595821859e-005</v>
+        <v>2.2880950558407348e-005</v>
       </c>
       <c r="AC5">
-        <v>3.4058113681272517e-006</v>
+        <v>-5.8212974969961079e-005</v>
       </c>
       <c r="AD5">
-        <v>0.0001412362380144199</v>
+        <v>7.5901272387147957e-005</v>
       </c>
       <c r="AE5">
-        <v>1.9933207634746663e-006</v>
+        <v>-6.3925347536226518e-006</v>
       </c>
       <c r="AF5">
-        <v>-3.10140743373528e-005</v>
+        <v>-8.5807706341141366e-005</v>
       </c>
       <c r="AG5">
-        <v>7.9462211396181788e-005</v>
+        <v>3.6967851904388816e-005</v>
       </c>
       <c r="AH5">
-        <v>-9.5413829871623707e-005</v>
+        <v>-0.00011781732840372721</v>
       </c>
       <c r="AI5">
-        <v>0.00017196777528168957</v>
+        <v>0.00013332305542719709</v>
       </c>
       <c r="AJ5">
-        <v>4.6791163064435889e-006</v>
+        <v>4.3981889531712217e-005</v>
       </c>
       <c r="AK5">
-        <v>-0.00080003500904269405</v>
+        <v>0.00013905247835352646</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="29">
-        <v>-0.27979278163176063</v>
+      <c r="B6" s="31">
+        <v>-0.26571948745426133</v>
       </c>
       <c r="C6">
-        <v>-8.0684101657686638e-005</v>
+        <v>-7.7464774037587459e-005</v>
       </c>
       <c r="D6">
-        <v>1.0767753013679864e-006</v>
+        <v>9.9065983853403045e-007</v>
       </c>
       <c r="E6">
-        <v>0.001400171528841839</v>
+        <v>0.0014421896402135672</v>
       </c>
       <c r="F6">
-        <v>0.0016205882057170556</v>
+        <v>0.0016461899268286648</v>
       </c>
       <c r="G6">
-        <v>0.0022064312957500755</v>
+        <v>0.0022444085051715056</v>
       </c>
       <c r="H6">
-        <v>0.0019449718280014439</v>
+        <v>0.0019876247713438147</v>
       </c>
       <c r="I6">
-        <v>9.5587296666471775e-005</v>
+        <v>0.00010733841032951836</v>
       </c>
       <c r="J6">
-        <v>-1.826421449426349e-005</v>
+        <v>-3.8491983323564441e-005</v>
       </c>
       <c r="K6">
-        <v>-3.3861283000352449e-006</v>
+        <v>-3.2742649194733674e-006</v>
       </c>
       <c r="L6">
-        <v>-3.9109786046329117e-006</v>
+        <v>-3.7504305854677579e-006</v>
       </c>
       <c r="M6">
-        <v>0.0005733522754804624</v>
+        <v>0.0005602376865665123</v>
       </c>
       <c r="N6">
-        <v>0.00036303008012657386</v>
+        <v>0.00050562848115392263</v>
       </c>
       <c r="O6">
-        <v>8.7573046080076939e-005</v>
+        <v>9.6804629358338777e-005</v>
       </c>
       <c r="P6">
-        <v>0.00033723801180635354</v>
+        <v>0.00031330852430783916</v>
       </c>
       <c r="Q6">
-        <v>-3.8835263359264521e-007</v>
+        <v>-1.5668370879952021e-005</v>
       </c>
       <c r="R6">
-        <v>0.00063049010432582688</v>
+        <v>0.00063767045176412916</v>
       </c>
       <c r="S6">
-        <v>0.00064613469041668989</v>
+        <v>0.00067594827914355289</v>
       </c>
       <c r="T6">
-        <v>3.3011351274323376e-005</v>
+        <v>-4.5628887761550827e-005</v>
       </c>
       <c r="U6">
-        <v>1.0179715412015028e-005</v>
+        <v>-6.1131056372638946e-005</v>
       </c>
       <c r="V6">
-        <v>-8.5099331084860638e-007</v>
+        <v>-7.225082991370931e-005</v>
       </c>
       <c r="W6">
-        <v>1.2876538209106178e-005</v>
+        <v>-6.345736608453069e-005</v>
       </c>
       <c r="X6">
-        <v>-4.2393353162490678e-005</v>
+        <v>-0.00011695038917788669</v>
       </c>
       <c r="Y6">
-        <v>3.8045006017513425e-006</v>
+        <v>-7.9874364425721982e-005</v>
       </c>
       <c r="Z6">
-        <v>-2.6004507926291891e-005</v>
+        <v>-9.8630881957276629e-005</v>
       </c>
       <c r="AA6">
-        <v>-6.8751168441415038e-005</v>
+        <v>-0.0001489587950747681</v>
       </c>
       <c r="AB6">
-        <v>5.0406104686529321e-005</v>
+        <v>-2.2063796574065399e-005</v>
       </c>
       <c r="AC6">
-        <v>-4.463457563528314e-005</v>
+        <v>-0.00011489788731529067</v>
       </c>
       <c r="AD6">
-        <v>4.8316482536272512e-005</v>
+        <v>-2.5382537681997892e-005</v>
       </c>
       <c r="AE6">
-        <v>5.6892891628669155e-006</v>
+        <v>-4.1996179066353822e-006</v>
       </c>
       <c r="AF6">
-        <v>-5.6977609011841703e-005</v>
+        <v>-0.0001180732408547224</v>
       </c>
       <c r="AG6">
-        <v>5.9574767501752943e-005</v>
+        <v>1.2921275226239023e-005</v>
       </c>
       <c r="AH6">
-        <v>-8.6108678746544263e-005</v>
+        <v>-0.00011326944653736171</v>
       </c>
       <c r="AI6">
-        <v>0.00014032909672350769</v>
+        <v>9.5934080215322333e-005</v>
       </c>
       <c r="AJ6">
-        <v>2.2838565004710621e-005</v>
+        <v>1.8933445046519877e-005</v>
       </c>
       <c r="AK6">
-        <v>-0.00034513828480381642</v>
+        <v>0.00072572053918747951</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="31">
-        <v>-0.016221431889055421</v>
+      <c r="B7" s="33">
+        <v>-0.0028005264654678125</v>
       </c>
       <c r="C7">
-        <v>-8.1601339374850102e-005</v>
+        <v>-7.8322271745894152e-005</v>
       </c>
       <c r="D7">
-        <v>9.8785395942277348e-007</v>
+        <v>8.993538638841971e-007</v>
       </c>
       <c r="E7">
-        <v>0.0013982668398983536</v>
+        <v>0.0014449596754801659</v>
       </c>
       <c r="F7">
-        <v>0.0016851203156259696</v>
+        <v>0.0017137269977449943</v>
       </c>
       <c r="G7">
-        <v>0.0019449718280014439</v>
+        <v>0.0019876247713438147</v>
       </c>
       <c r="H7">
-        <v>0.0024913544953443913</v>
+        <v>0.0025375933926777786</v>
       </c>
       <c r="I7">
-        <v>0.00020330896603991389</v>
+        <v>0.00021535080216754593</v>
       </c>
       <c r="J7">
-        <v>-3.1164726985394574e-005</v>
+        <v>-5.1937897891036954e-005</v>
       </c>
       <c r="K7">
-        <v>-4.3414944237985738e-006</v>
+        <v>-4.2378629034739695e-006</v>
       </c>
       <c r="L7">
-        <v>-5.7539014807693265e-006</v>
+        <v>-5.5809352002647503e-006</v>
       </c>
       <c r="M7">
-        <v>0.00065202575744213352</v>
+        <v>0.00063923764018103434</v>
       </c>
       <c r="N7">
-        <v>0.00046477131799076355</v>
+        <v>0.00061047675760683186</v>
       </c>
       <c r="O7">
-        <v>0.00021006538754911766</v>
+        <v>0.00021898988538057024</v>
       </c>
       <c r="P7">
-        <v>0.00053109038481380106</v>
+        <v>0.00050630574587798402</v>
       </c>
       <c r="Q7">
-        <v>4.1950283462710325e-006</v>
+        <v>-1.141340214802329e-005</v>
       </c>
       <c r="R7">
-        <v>0.0006872323477244628</v>
+        <v>0.00069673123821269568</v>
       </c>
       <c r="S7">
-        <v>0.00063128178397712132</v>
+        <v>0.00066276836736550541</v>
       </c>
       <c r="T7">
-        <v>-4.2523947487380911e-006</v>
+        <v>-8.410052874567261e-005</v>
       </c>
       <c r="U7">
-        <v>-2.3947689661180886e-005</v>
+        <v>-9.6530780233772392e-005</v>
       </c>
       <c r="V7">
-        <v>-1.1182342404165448e-005</v>
+        <v>-8.3851696296482082e-005</v>
       </c>
       <c r="W7">
-        <v>-2.7414503134572544e-005</v>
+        <v>-0.00010530634866522082</v>
       </c>
       <c r="X7">
-        <v>-8.5940207956492582e-005</v>
+        <v>-0.000161747974319206</v>
       </c>
       <c r="Y7">
-        <v>-5.5632126752674991e-005</v>
+        <v>-0.00014137870170461634</v>
       </c>
       <c r="Z7">
-        <v>-0.00010558150289496568</v>
+        <v>-0.00018017917408070703</v>
       </c>
       <c r="AA7">
-        <v>-9.6055829832813306e-005</v>
+        <v>-0.00017637661680098291</v>
       </c>
       <c r="AB7">
-        <v>2.1104776571087254e-005</v>
+        <v>-5.2609002730068678e-005</v>
       </c>
       <c r="AC7">
-        <v>-7.9862349460414804e-005</v>
+        <v>-0.00015159909821161807</v>
       </c>
       <c r="AD7">
-        <v>2.9226439141461077e-005</v>
+        <v>-4.5832422621657713e-005</v>
       </c>
       <c r="AE7">
-        <v>1.3539029622157029e-005</v>
+        <v>3.5231072201819653e-006</v>
       </c>
       <c r="AF7">
-        <v>-6.8633473278342262e-005</v>
+        <v>-0.00013163578989670453</v>
       </c>
       <c r="AG7">
-        <v>4.2901421676498218e-005</v>
+        <v>-4.8658050007584642e-006</v>
       </c>
       <c r="AH7">
-        <v>-8.3580561347521183e-005</v>
+        <v>-0.00011149197532905376</v>
       </c>
       <c r="AI7">
-        <v>0.00014614193302442337</v>
+        <v>0.00010091153124267525</v>
       </c>
       <c r="AJ7">
-        <v>-3.8636630179228069e-005</v>
+        <v>-8.8048062115562878e-006</v>
       </c>
       <c r="AK7">
-        <v>-0.00078475508484609742</v>
+        <v>0.00030599024200207367</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="33">
-        <v>-0.27287384049630181</v>
+      <c r="B8" s="35">
+        <v>-0.27270117579093245</v>
       </c>
       <c r="C8">
-        <v>-9.7977744698626076e-005</v>
+        <v>-9.7961890573745967e-005</v>
       </c>
       <c r="D8">
-        <v>1.3271457881243191e-006</v>
+        <v>1.3260998799835094e-006</v>
       </c>
       <c r="E8">
-        <v>-0.00020298658255787769</v>
+        <v>-0.00018652631681786991</v>
       </c>
       <c r="F8">
-        <v>-6.8768316802999391e-006</v>
+        <v>3.8835938279154327e-006</v>
       </c>
       <c r="G8">
-        <v>9.5587296666471775e-005</v>
+        <v>0.00010733841032951836</v>
       </c>
       <c r="H8">
-        <v>0.00020330896603991389</v>
+        <v>0.00021535080216754593</v>
       </c>
       <c r="I8">
-        <v>0.0005113215895666645</v>
+        <v>0.00051244622867071545</v>
       </c>
       <c r="J8">
-        <v>-0.00017395066570124329</v>
+        <v>-0.00017498381886698298</v>
       </c>
       <c r="K8">
-        <v>1.9336233507716637e-006</v>
+        <v>1.9212037103012477e-006</v>
       </c>
       <c r="L8">
-        <v>-6.7567104120786141e-006</v>
+        <v>-6.7745884692110034e-006</v>
       </c>
       <c r="M8">
-        <v>0.00032992125211533539</v>
+        <v>0.0003335309106222463</v>
       </c>
       <c r="N8">
-        <v>3.7467154448009109e-005</v>
+        <v>3.9177173305379915e-005</v>
       </c>
       <c r="O8">
-        <v>-3.3412959538240521e-005</v>
+        <v>-3.4378054515080304e-005</v>
       </c>
       <c r="P8">
-        <v>0.00026433740198819904</v>
+        <v>0.00026430547277401606</v>
       </c>
       <c r="Q8">
-        <v>1.2409871762184802e-005</v>
+        <v>1.1976274416046237e-005</v>
       </c>
       <c r="R8">
-        <v>-0.00012256455988506607</v>
+        <v>-0.00011853384731187457</v>
       </c>
       <c r="S8">
-        <v>-0.00016989532341497721</v>
+        <v>-0.00016510919755817878</v>
       </c>
       <c r="T8">
-        <v>-0.00034886906451357983</v>
+        <v>-0.00035445852664717101</v>
       </c>
       <c r="U8">
-        <v>-0.00034581787752933256</v>
+        <v>-0.00035096751195879533</v>
       </c>
       <c r="V8">
-        <v>-0.00033006099923707315</v>
+        <v>-0.00033594478497776207</v>
       </c>
       <c r="W8">
-        <v>-0.00031512954045674689</v>
+        <v>-0.00031980795269530055</v>
       </c>
       <c r="X8">
-        <v>-0.00036565363523757231</v>
+        <v>-0.00036908763478022479</v>
       </c>
       <c r="Y8">
-        <v>-0.0003274511068535208</v>
+        <v>-0.00033293757268326176</v>
       </c>
       <c r="Z8">
-        <v>-0.00034025506829093939</v>
+        <v>-0.0003457769713406267</v>
       </c>
       <c r="AA8">
-        <v>-0.0003462651165415479</v>
+        <v>-0.00035112402544145219</v>
       </c>
       <c r="AB8">
-        <v>-0.00033457737959395172</v>
+        <v>-0.0003391623807762462</v>
       </c>
       <c r="AC8">
-        <v>-0.00030384858605206583</v>
+        <v>-0.00030947367260431436</v>
       </c>
       <c r="AD8">
-        <v>-0.00041765200584125019</v>
+        <v>-0.00042210482007258571</v>
       </c>
       <c r="AE8">
-        <v>2.4236909532276144e-005</v>
+        <v>2.3933089838775846e-005</v>
       </c>
       <c r="AF8">
-        <v>-7.6492831118559146e-005</v>
+        <v>-7.8694609020375664e-005</v>
       </c>
       <c r="AG8">
-        <v>-5.8882987507424584e-005</v>
+        <v>-5.9975126837147624e-005</v>
       </c>
       <c r="AH8">
-        <v>-0.00012359325907742644</v>
+        <v>-0.00012757116019743503</v>
       </c>
       <c r="AI8">
-        <v>-0.00036184801789370286</v>
+        <v>-0.00036665813457522158</v>
       </c>
       <c r="AJ8">
-        <v>-0.0001107964451360084</v>
+        <v>-0.00011027519986757481</v>
       </c>
       <c r="AK8">
-        <v>0.00040416315983542585</v>
+        <v>0.00043000420121531123</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="35">
-        <v>0.8337542292128286</v>
+      <c r="B9" s="37">
+        <v>0.83338372098727198</v>
       </c>
       <c r="C9">
-        <v>1.7634323004770433e-005</v>
+        <v>1.7944040761638737e-005</v>
       </c>
       <c r="D9">
-        <v>-3.7997312535893062e-008</v>
+        <v>-4.1475133734813627e-008</v>
       </c>
       <c r="E9">
-        <v>7.2366409364507669e-005</v>
+        <v>4.5669968192882183e-005</v>
       </c>
       <c r="F9">
-        <v>1.1964597267425875e-005</v>
+        <v>-6.3131028003278667e-006</v>
       </c>
       <c r="G9">
-        <v>-1.826421449426349e-005</v>
+        <v>-3.8491983323564441e-005</v>
       </c>
       <c r="H9">
-        <v>-3.1164726985394574e-005</v>
+        <v>-5.1937897891036954e-005</v>
       </c>
       <c r="I9">
-        <v>-0.00017395066570124329</v>
+        <v>-0.00017498381886698298</v>
       </c>
       <c r="J9">
-        <v>0.0004207396170291243</v>
+        <v>0.00042160883399303405</v>
       </c>
       <c r="K9">
-        <v>-2.6311704537068229e-006</v>
+        <v>-2.6054794919389213e-006</v>
       </c>
       <c r="L9">
-        <v>2.40042199454168e-006</v>
+        <v>2.423403083917428e-006</v>
       </c>
       <c r="M9">
-        <v>3.6897894625978044e-006</v>
+        <v>-1.0346384826333179e-006</v>
       </c>
       <c r="N9">
-        <v>7.2399585951644474e-005</v>
+        <v>6.6989999705573307e-005</v>
       </c>
       <c r="O9">
-        <v>6.809028636065785e-005</v>
+        <v>6.8603871704368553e-005</v>
       </c>
       <c r="P9">
-        <v>1.3788108214240721e-005</v>
+        <v>1.2781224581157448e-005</v>
       </c>
       <c r="Q9">
-        <v>4.6606269583277692e-007</v>
+        <v>1.0130186048124118e-006</v>
       </c>
       <c r="R9">
-        <v>8.966015180355572e-005</v>
+        <v>8.6283242342479269e-005</v>
       </c>
       <c r="S9">
-        <v>-9.0608635548040381e-006</v>
+        <v>-1.6877199645333205e-005</v>
       </c>
       <c r="T9">
-        <v>0.00012210878915096731</v>
+        <v>0.00012636257607917488</v>
       </c>
       <c r="U9">
-        <v>0.00010337108761337906</v>
+        <v>0.00010768014410220803</v>
       </c>
       <c r="V9">
-        <v>0.00010976003957238181</v>
+        <v>0.0001141595346448564</v>
       </c>
       <c r="W9">
-        <v>8.4284010648295838e-005</v>
+        <v>8.8832977086453528e-005</v>
       </c>
       <c r="X9">
-        <v>0.00013688868687990755</v>
+        <v>0.00014132443658040067</v>
       </c>
       <c r="Y9">
-        <v>6.7517669979448884e-005</v>
+        <v>7.34562718876279e-005</v>
       </c>
       <c r="Z9">
-        <v>9.5596651203738514e-005</v>
+        <v>0.0001006287217598277</v>
       </c>
       <c r="AA9">
-        <v>9.8460915108460393e-005</v>
+        <v>0.00010240644686438792</v>
       </c>
       <c r="AB9">
-        <v>9.4815624407321034e-005</v>
+        <v>9.9031521257687914e-005</v>
       </c>
       <c r="AC9">
-        <v>8.5050096254028057e-005</v>
+        <v>8.9532277120727213e-005</v>
       </c>
       <c r="AD9">
-        <v>9.2377939170261024e-005</v>
+        <v>9.647547247255701e-005</v>
       </c>
       <c r="AE9">
-        <v>-5.1627813522477165e-007</v>
+        <v>-2.1929568694516296e-007</v>
       </c>
       <c r="AF9">
-        <v>3.4567819673059356e-005</v>
+        <v>3.6937808897486051e-005</v>
       </c>
       <c r="AG9">
-        <v>4.7321963432213704e-005</v>
+        <v>4.9609475304825865e-005</v>
       </c>
       <c r="AH9">
-        <v>3.4552707065231591e-005</v>
+        <v>3.7432361840605984e-005</v>
       </c>
       <c r="AI9">
-        <v>3.8999718047942459e-005</v>
+        <v>4.1762874916501319e-005</v>
       </c>
       <c r="AJ9">
-        <v>3.9499267879607571e-005</v>
+        <v>2.9474328514025698e-005</v>
       </c>
       <c r="AK9">
-        <v>-0.00061220067366104299</v>
+        <v>-0.00064099932613252849</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="37">
-        <v>0.0040895818511828457</v>
+      <c r="B10" s="39">
+        <v>0.0040430178446519277</v>
       </c>
       <c r="C10">
-        <v>-6.1477876174604032e-007</v>
+        <v>-6.0528235783486892e-007</v>
       </c>
       <c r="D10">
-        <v>1.0131773760310046e-008</v>
+        <v>1.0041543878951043e-008</v>
       </c>
       <c r="E10">
-        <v>-4.8529456116984254e-006</v>
+        <v>-4.6927011232514103e-006</v>
       </c>
       <c r="F10">
-        <v>-3.3966050981376283e-006</v>
+        <v>-3.3042890398355531e-006</v>
       </c>
       <c r="G10">
-        <v>-3.3861283000352449e-006</v>
+        <v>-3.2742649194733674e-006</v>
       </c>
       <c r="H10">
-        <v>-4.3414944237985738e-006</v>
+        <v>-4.2378629034739695e-006</v>
       </c>
       <c r="I10">
-        <v>1.9336233507716637e-006</v>
+        <v>1.9212037103012477e-006</v>
       </c>
       <c r="J10">
-        <v>-2.6311704537068229e-006</v>
+        <v>-2.6054794919389213e-006</v>
       </c>
       <c r="K10">
-        <v>1.6171001340172877e-006</v>
+        <v>1.6144649093093297e-006</v>
       </c>
       <c r="L10">
-        <v>-5.6928633564361786e-009</v>
+        <v>-6.6835508330880496e-009</v>
       </c>
       <c r="M10">
-        <v>2.415543729332151e-006</v>
+        <v>2.4433524780329978e-006</v>
       </c>
       <c r="N10">
-        <v>-1.3681471135779024e-006</v>
+        <v>-1.4672073013597275e-006</v>
       </c>
       <c r="O10">
-        <v>1.9320463746520567e-006</v>
+        <v>1.9052953258845742e-006</v>
       </c>
       <c r="P10">
-        <v>6.6548998456741508e-006</v>
+        <v>6.6912490257331407e-006</v>
       </c>
       <c r="Q10">
-        <v>-3.2312745308790326e-007</v>
+        <v>-3.0922544510233197e-007</v>
       </c>
       <c r="R10">
-        <v>-2.7418665665219714e-006</v>
+        <v>-2.6993127687237984e-006</v>
       </c>
       <c r="S10">
-        <v>2.2913698010834542e-006</v>
+        <v>2.3339166555069418e-006</v>
       </c>
       <c r="T10">
-        <v>-4.8894495609464801e-006</v>
+        <v>-4.8779963606115706e-006</v>
       </c>
       <c r="U10">
-        <v>-3.3985621469507645e-006</v>
+        <v>-3.3782032581874965e-006</v>
       </c>
       <c r="V10">
-        <v>-4.0339515603811363e-006</v>
+        <v>-4.0445494827200777e-006</v>
       </c>
       <c r="W10">
-        <v>-2.0779184669438174e-006</v>
+        <v>-2.0744881052704565e-006</v>
       </c>
       <c r="X10">
-        <v>-2.7641814002562012e-006</v>
+        <v>-2.7435284129956891e-006</v>
       </c>
       <c r="Y10">
-        <v>-2.6817784995845098e-006</v>
+        <v>-2.615094236669386e-006</v>
       </c>
       <c r="Z10">
-        <v>-3.2802372632566922e-006</v>
+        <v>-3.2491296527743587e-006</v>
       </c>
       <c r="AA10">
-        <v>-3.0516608885218209e-006</v>
+        <v>-3.0510552389879394e-006</v>
       </c>
       <c r="AB10">
-        <v>-3.4162913855761588e-006</v>
+        <v>-3.4209398925226888e-006</v>
       </c>
       <c r="AC10">
-        <v>-3.9796431744897791e-006</v>
+        <v>-3.9805346685886856e-006</v>
       </c>
       <c r="AD10">
-        <v>-2.9113537803038123e-006</v>
+        <v>-2.8732484664435439e-006</v>
       </c>
       <c r="AE10">
-        <v>-5.9568507529288476e-008</v>
+        <v>-5.5257296223323854e-008</v>
       </c>
       <c r="AF10">
-        <v>-3.105591053373309e-006</v>
+        <v>-3.036670617204897e-006</v>
       </c>
       <c r="AG10">
-        <v>-2.3814861666024369e-006</v>
+        <v>-2.2954151598843427e-006</v>
       </c>
       <c r="AH10">
-        <v>5.4892087358272623e-007</v>
+        <v>4.8023561125939344e-007</v>
       </c>
       <c r="AI10">
-        <v>-1.1845251386205844e-006</v>
+        <v>-1.195963566161964e-006</v>
       </c>
       <c r="AJ10">
-        <v>3.1725691106889943e-006</v>
+        <v>4.2129751948823116e-007</v>
       </c>
       <c r="AK10">
-        <v>-5.4423371723098812e-005</v>
+        <v>-5.5431659340447547e-005</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="39">
-        <v>0.0029221045381970989</v>
+      <c r="B11" s="41">
+        <v>0.0029181976262784141</v>
       </c>
       <c r="C11">
-        <v>2.3103148535298955e-006</v>
+        <v>2.3017795579131125e-006</v>
       </c>
       <c r="D11">
-        <v>-3.4375617984813553e-008</v>
+        <v>-3.4249436794666086e-008</v>
       </c>
       <c r="E11">
-        <v>9.4840618263835121e-007</v>
+        <v>1.1307385634511584e-006</v>
       </c>
       <c r="F11">
-        <v>-1.1698952590491121e-006</v>
+        <v>-1.0192638483275899e-006</v>
       </c>
       <c r="G11">
-        <v>-3.9109786046329117e-006</v>
+        <v>-3.7504305854677579e-006</v>
       </c>
       <c r="H11">
-        <v>-5.7539014807693265e-006</v>
+        <v>-5.5809352002647503e-006</v>
       </c>
       <c r="I11">
-        <v>-6.7567104120786141e-006</v>
+        <v>-6.7745884692110034e-006</v>
       </c>
       <c r="J11">
-        <v>2.40042199454168e-006</v>
+        <v>2.423403083917428e-006</v>
       </c>
       <c r="K11">
-        <v>-5.6928633564361786e-009</v>
+        <v>-6.6835508330880496e-009</v>
       </c>
       <c r="L11">
-        <v>1.2766048570814432e-006</v>
+        <v>1.276991410903544e-006</v>
       </c>
       <c r="M11">
-        <v>-3.3543725367236396e-006</v>
+        <v>-3.3529158295964427e-006</v>
       </c>
       <c r="N11">
-        <v>1.9233800930896031e-006</v>
+        <v>1.9911282928348772e-006</v>
       </c>
       <c r="O11">
-        <v>5.6539501899598967e-007</v>
+        <v>5.8066365395834279e-007</v>
       </c>
       <c r="P11">
-        <v>-3.8584869621987541e-006</v>
+        <v>-3.7963805445022197e-006</v>
       </c>
       <c r="Q11">
-        <v>1.3127511355686376e-007</v>
+        <v>1.346347613464506e-007</v>
       </c>
       <c r="R11">
-        <v>4.7240317276291757e-006</v>
+        <v>4.6369736142335177e-006</v>
       </c>
       <c r="S11">
-        <v>3.9066837276805056e-006</v>
+        <v>3.9511647485647202e-006</v>
       </c>
       <c r="T11">
-        <v>7.9847993969881191e-006</v>
+        <v>8.1451502484988511e-006</v>
       </c>
       <c r="U11">
-        <v>7.4145370131942418e-006</v>
+        <v>7.5393250517113572e-006</v>
       </c>
       <c r="V11">
-        <v>6.1332471078729283e-006</v>
+        <v>6.275202489434752e-006</v>
       </c>
       <c r="W11">
-        <v>6.2286883854026853e-006</v>
+        <v>6.3264225918670411e-006</v>
       </c>
       <c r="X11">
-        <v>8.8191725090410704e-006</v>
+        <v>8.8697364200211338e-006</v>
       </c>
       <c r="Y11">
-        <v>6.6473650654206314e-006</v>
+        <v>6.7685759695355885e-006</v>
       </c>
       <c r="Z11">
-        <v>6.3238819022400376e-006</v>
+        <v>6.4442190639198137e-006</v>
       </c>
       <c r="AA11">
-        <v>7.1970304885206834e-006</v>
+        <v>7.3285137890432505e-006</v>
       </c>
       <c r="AB11">
-        <v>7.798173757501018e-006</v>
+        <v>7.9240283364151581e-006</v>
       </c>
       <c r="AC11">
-        <v>6.7684982369673155e-006</v>
+        <v>6.8968412344205426e-006</v>
       </c>
       <c r="AD11">
-        <v>6.4647805950724513e-006</v>
+        <v>6.6016585098159036e-006</v>
       </c>
       <c r="AE11">
-        <v>3.0020751553538957e-007</v>
+        <v>3.0201020838292793e-007</v>
       </c>
       <c r="AF11">
-        <v>2.0246132198194115e-006</v>
+        <v>2.0437701341261483e-006</v>
       </c>
       <c r="AG11">
-        <v>1.1312429316739048e-006</v>
+        <v>1.1797076162841173e-006</v>
       </c>
       <c r="AH11">
-        <v>1.0721830529276193e-007</v>
+        <v>1.8608837218078009e-007</v>
       </c>
       <c r="AI11">
-        <v>3.9807921967334434e-006</v>
+        <v>4.1357559168766605e-006</v>
       </c>
       <c r="AJ11">
-        <v>3.5699569583603486e-006</v>
+        <v>3.6332846920207959e-006</v>
       </c>
       <c r="AK11">
-        <v>-0.00010473328919973167</v>
+        <v>-0.00010510728737623637</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="41">
-        <v>-0.38144175848625916</v>
+      <c r="B12" s="43">
+        <v>-0.37948989366661579</v>
       </c>
       <c r="C12">
-        <v>3.5787688402047838e-005</v>
+        <v>3.7268962574832799e-005</v>
       </c>
       <c r="D12">
-        <v>-3.8431320371640226e-007</v>
+        <v>-4.125536659672151e-007</v>
       </c>
       <c r="E12">
-        <v>2.3770729249623874e-005</v>
+        <v>6.953609615436906e-006</v>
       </c>
       <c r="F12">
-        <v>0.00040230951681130079</v>
+        <v>0.00038826278014778215</v>
       </c>
       <c r="G12">
-        <v>0.0005733522754804624</v>
+        <v>0.0005602376865665123</v>
       </c>
       <c r="H12">
-        <v>0.00065202575744213352</v>
+        <v>0.00063923764018103434</v>
       </c>
       <c r="I12">
-        <v>0.00032992125211533539</v>
+        <v>0.0003335309106222463</v>
       </c>
       <c r="J12">
-        <v>3.6897894625978044e-006</v>
+        <v>-1.0346384826333179e-006</v>
       </c>
       <c r="K12">
-        <v>2.415543729332151e-006</v>
+        <v>2.4433524780329978e-006</v>
       </c>
       <c r="L12">
-        <v>-3.3543725367236396e-006</v>
+        <v>-3.3529158295964427e-006</v>
       </c>
       <c r="M12">
-        <v>0.0014738463394417542</v>
+        <v>0.0014692229638577691</v>
       </c>
       <c r="N12">
-        <v>0.00027319109210897116</v>
+        <v>0.00029286070032428645</v>
       </c>
       <c r="O12">
-        <v>-3.4722981832267165e-005</v>
+        <v>-3.467839694321e-005</v>
       </c>
       <c r="P12">
-        <v>0.00028064143360078059</v>
+        <v>0.00027322684070873906</v>
       </c>
       <c r="Q12">
-        <v>1.8466760276206163e-005</v>
+        <v>1.5948981751741253e-005</v>
       </c>
       <c r="R12">
-        <v>-7.7549797474466182e-005</v>
+        <v>-7.3893402649859071e-005</v>
       </c>
       <c r="S12">
-        <v>-2.8513003009755019e-005</v>
+        <v>-2.8845608013484326e-005</v>
       </c>
       <c r="T12">
-        <v>-0.00024943183504258807</v>
+        <v>-0.00027207371007631227</v>
       </c>
       <c r="U12">
-        <v>-0.00027856043649657864</v>
+        <v>-0.00029773236168577051</v>
       </c>
       <c r="V12">
-        <v>-0.00022288841029625452</v>
+        <v>-0.00024410970595211095</v>
       </c>
       <c r="W12">
-        <v>-0.00023129156660971423</v>
+        <v>-0.00024968575859188585</v>
       </c>
       <c r="X12">
-        <v>-0.00023687969064150791</v>
+        <v>-0.00025180542154413566</v>
       </c>
       <c r="Y12">
-        <v>-0.00024988674099549364</v>
+        <v>-0.00026796225909428754</v>
       </c>
       <c r="Z12">
-        <v>-0.00021537773021940306</v>
+        <v>-0.00023341135252863583</v>
       </c>
       <c r="AA12">
-        <v>-0.00023547726226635294</v>
+        <v>-0.00025691210063771082</v>
       </c>
       <c r="AB12">
-        <v>-0.00022274336524397576</v>
+        <v>-0.00024225467254541727</v>
       </c>
       <c r="AC12">
-        <v>-0.00029175740158209301</v>
+        <v>-0.00031079628628912252</v>
       </c>
       <c r="AD12">
-        <v>-0.0004092463792547585</v>
+        <v>-0.00042839423097991523</v>
       </c>
       <c r="AE12">
-        <v>3.0897632912271853e-005</v>
+        <v>2.9139114341954626e-005</v>
       </c>
       <c r="AF12">
-        <v>-9.006165070576041e-005</v>
+        <v>-0.00010053950615983419</v>
       </c>
       <c r="AG12">
-        <v>-5.3167199253600396e-005</v>
+        <v>-6.0164509628323458e-005</v>
       </c>
       <c r="AH12">
-        <v>2.1238325387253629e-005</v>
+        <v>1.0961934459128436e-005</v>
       </c>
       <c r="AI12">
-        <v>-0.00050407762248914543</v>
+        <v>-0.00052148213907492842</v>
       </c>
       <c r="AJ12">
-        <v>-8.3804812786530828e-005</v>
+        <v>-0.00019222810108840318</v>
       </c>
       <c r="AK12">
-        <v>-0.0032177996112804498</v>
+        <v>-0.0030255448889107178</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="43">
-        <v>-0.17215241919004129</v>
+      <c r="B13" s="45">
+        <v>-0.1691362407826314</v>
       </c>
       <c r="C13">
-        <v>3.3955489275193504e-005</v>
+        <v>3.2705467015818872e-005</v>
       </c>
       <c r="D13">
-        <v>-7.2037741193928609e-007</v>
+        <v>-7.173430179556704e-007</v>
       </c>
       <c r="E13">
-        <v>6.8494433081059145e-005</v>
+        <v>0.00025578295642256725</v>
       </c>
       <c r="F13">
-        <v>0.00021126049049380121</v>
+        <v>0.00033717115324915635</v>
       </c>
       <c r="G13">
-        <v>0.00036303008012657386</v>
+        <v>0.00050562848115392263</v>
       </c>
       <c r="H13">
-        <v>0.00046477131799076355</v>
+        <v>0.00061047675760683186</v>
       </c>
       <c r="I13">
-        <v>3.7467154448009109e-005</v>
+        <v>3.9177173305379915e-005</v>
       </c>
       <c r="J13">
-        <v>7.2399585951644474e-005</v>
+        <v>6.6989999705573307e-005</v>
       </c>
       <c r="K13">
-        <v>-1.3681471135779024e-006</v>
+        <v>-1.4672073013597275e-006</v>
       </c>
       <c r="L13">
-        <v>1.9233800930896031e-006</v>
+        <v>1.9911282928348772e-006</v>
       </c>
       <c r="M13">
-        <v>0.00027319109210897116</v>
+        <v>0.00029286070032428645</v>
       </c>
       <c r="N13">
-        <v>0.0028665419444037863</v>
+        <v>0.0029367374852758486</v>
       </c>
       <c r="O13">
-        <v>4.1353517210583507e-005</v>
+        <v>4.2072870891492168e-005</v>
       </c>
       <c r="P13">
-        <v>5.0641855768751251e-005</v>
+        <v>5.2330442310922543e-005</v>
       </c>
       <c r="Q13">
-        <v>-1.9680950585803954e-005</v>
+        <v>-2.6580452178931586e-005</v>
       </c>
       <c r="R13">
-        <v>-7.7404494346420942e-006</v>
+        <v>2.1913000123870564e-005</v>
       </c>
       <c r="S13">
-        <v>6.499730130769158e-005</v>
+        <v>0.00012874320692052692</v>
       </c>
       <c r="T13">
-        <v>-6.1582861609832005e-005</v>
+        <v>-8.9933965591131081e-005</v>
       </c>
       <c r="U13">
-        <v>-3.4177153694107607e-006</v>
+        <v>-3.3997300250209047e-005</v>
       </c>
       <c r="V13">
-        <v>-0.00012795742615997465</v>
+        <v>-0.00015614942761717448</v>
       </c>
       <c r="W13">
-        <v>-0.00015077079201811531</v>
+        <v>-0.00018197016578438627</v>
       </c>
       <c r="X13">
-        <v>-0.00011601315563224308</v>
+        <v>-0.00014931570708665389</v>
       </c>
       <c r="Y13">
-        <v>-8.6741860427858833e-005</v>
+        <v>-0.0001143684449599633</v>
       </c>
       <c r="Z13">
-        <v>-4.7752968016310528e-005</v>
+        <v>-7.9759205273199473e-005</v>
       </c>
       <c r="AA13">
-        <v>-0.00012771653873828873</v>
+        <v>-0.00015803880204480134</v>
       </c>
       <c r="AB13">
-        <v>-8.4168821347981081e-005</v>
+        <v>-0.00011049491640044646</v>
       </c>
       <c r="AC13">
-        <v>-0.00010930991183936544</v>
+        <v>-0.00013892149108850598</v>
       </c>
       <c r="AD13">
-        <v>-0.00014471462423606973</v>
+        <v>-0.00017116103272999273</v>
       </c>
       <c r="AE13">
-        <v>-2.6576869677112712e-006</v>
+        <v>-7.2473282395949488e-006</v>
       </c>
       <c r="AF13">
-        <v>-0.00013844704084466425</v>
+        <v>-0.00016142937078099856</v>
       </c>
       <c r="AG13">
-        <v>0.00010570428873273954</v>
+        <v>8.9853164289118966e-005</v>
       </c>
       <c r="AH13">
-        <v>-5.6467107573215567e-005</v>
+        <v>-7.7079395805772677e-005</v>
       </c>
       <c r="AI13">
-        <v>-0.00030803117578330833</v>
+        <v>-0.00031703455527711758</v>
       </c>
       <c r="AJ13">
-        <v>4.9091538534460103e-005</v>
+        <v>1.1544028890433282e-005</v>
       </c>
       <c r="AK13">
-        <v>0.00042665862936524775</v>
+        <v>0.00083250770490137091</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="45">
-        <v>-0.2493435778430452</v>
+      <c r="B14" s="47">
+        <v>-0.24999028132496715</v>
       </c>
       <c r="C14">
-        <v>4.8613528198598443e-005</v>
+        <v>4.8539798399902537e-005</v>
       </c>
       <c r="D14">
-        <v>-6.0573422989463551e-007</v>
+        <v>-6.0454002822415862e-007</v>
       </c>
       <c r="E14">
-        <v>1.5558722507779673e-006</v>
+        <v>1.3490297642046699e-005</v>
       </c>
       <c r="F14">
-        <v>3.6040188717592823e-005</v>
+        <v>4.3834052538375533e-005</v>
       </c>
       <c r="G14">
-        <v>8.7573046080076939e-005</v>
+        <v>9.6804629358338777e-005</v>
       </c>
       <c r="H14">
-        <v>0.00021006538754911766</v>
+        <v>0.00021898988538057024</v>
       </c>
       <c r="I14">
-        <v>-3.3412959538240521e-005</v>
+        <v>-3.4378054515080304e-005</v>
       </c>
       <c r="J14">
-        <v>6.809028636065785e-005</v>
+        <v>6.8603871704368553e-005</v>
       </c>
       <c r="K14">
-        <v>1.9320463746520567e-006</v>
+        <v>1.9052953258845742e-006</v>
       </c>
       <c r="L14">
-        <v>5.6539501899598967e-007</v>
+        <v>5.8066365395834279e-007</v>
       </c>
       <c r="M14">
-        <v>-3.4722981832267165e-005</v>
+        <v>-3.467839694321e-005</v>
       </c>
       <c r="N14">
-        <v>4.1353517210583507e-005</v>
+        <v>4.2072870891492168e-005</v>
       </c>
       <c r="O14">
-        <v>0.00055813289923259055</v>
+        <v>0.00055791941284283753</v>
       </c>
       <c r="P14">
-        <v>0.00038609157009160833</v>
+        <v>0.00038666920707895324</v>
       </c>
       <c r="Q14">
-        <v>-1.9936929399051826e-006</v>
+        <v>-1.8034011087907499e-006</v>
       </c>
       <c r="R14">
-        <v>0.00012606853104952235</v>
+        <v>0.00013289803721221673</v>
       </c>
       <c r="S14">
-        <v>-2.4477025419783807e-006</v>
+        <v>1.414108414716478e-006</v>
       </c>
       <c r="T14">
-        <v>4.6625071834985451e-006</v>
+        <v>6.5762911607169551e-006</v>
       </c>
       <c r="U14">
-        <v>1.0538942626716957e-005</v>
+        <v>1.2226630780537884e-005</v>
       </c>
       <c r="V14">
-        <v>9.4679997146918712e-006</v>
+        <v>1.1062700263523651e-005</v>
       </c>
       <c r="W14">
-        <v>-2.0132156069647836e-005</v>
+        <v>-1.8349519125051509e-005</v>
       </c>
       <c r="X14">
-        <v>8.1593432679923604e-008</v>
+        <v>1.1394025822183658e-006</v>
       </c>
       <c r="Y14">
-        <v>-4.0061957683810816e-006</v>
+        <v>-2.6889000845986902e-006</v>
       </c>
       <c r="Z14">
-        <v>2.011760633091348e-005</v>
+        <v>2.1800411542577348e-005</v>
       </c>
       <c r="AA14">
-        <v>-1.1078369404826042e-005</v>
+        <v>-9.8465801934141325e-006</v>
       </c>
       <c r="AB14">
-        <v>1.8522650367347199e-005</v>
+        <v>1.9353835555100752e-005</v>
       </c>
       <c r="AC14">
-        <v>-2.0222369049440608e-005</v>
+        <v>-1.8623300811848468e-005</v>
       </c>
       <c r="AD14">
-        <v>3.1952607038628804e-005</v>
+        <v>3.3904713489462789e-005</v>
       </c>
       <c r="AE14">
-        <v>5.2439245002776466e-006</v>
+        <v>5.3331275515853399e-006</v>
       </c>
       <c r="AF14">
-        <v>1.5100594620332534e-005</v>
+        <v>1.6086792409349754e-005</v>
       </c>
       <c r="AG14">
-        <v>6.8016300809686195e-006</v>
+        <v>7.530740278684602e-006</v>
       </c>
       <c r="AH14">
-        <v>4.3785789263365345e-005</v>
+        <v>4.3909352878767943e-005</v>
       </c>
       <c r="AI14">
-        <v>7.1177631839887878e-005</v>
+        <v>7.339127515338024e-005</v>
       </c>
       <c r="AJ14">
-        <v>6.9783177758067725e-005</v>
+        <v>4.4647162045910959e-005</v>
       </c>
       <c r="AK14">
-        <v>-0.0014316875681647553</v>
+        <v>-0.0014523214380896695</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="47">
-        <v>-0.13677388431894955</v>
+      <c r="B15" s="49">
+        <v>-0.13624178345261223</v>
       </c>
       <c r="C15">
-        <v>7.2687335164220261e-006</v>
+        <v>8.5230097611964893e-006</v>
       </c>
       <c r="D15">
-        <v>-1.2723923721316363e-007</v>
+        <v>-1.4692906511738871e-007</v>
       </c>
       <c r="E15">
-        <v>-9.423424275956918e-006</v>
+        <v>-4.1809253737391116e-005</v>
       </c>
       <c r="F15">
-        <v>0.00021265689937089268</v>
+        <v>0.00018998722455728593</v>
       </c>
       <c r="G15">
-        <v>0.00033723801180635354</v>
+        <v>0.00031330852430783916</v>
       </c>
       <c r="H15">
-        <v>0.00053109038481380106</v>
+        <v>0.00050630574587798402</v>
       </c>
       <c r="I15">
-        <v>0.00026433740198819904</v>
+        <v>0.00026430547277401606</v>
       </c>
       <c r="J15">
-        <v>1.3788108214240721e-005</v>
+        <v>1.2781224581157448e-005</v>
       </c>
       <c r="K15">
-        <v>6.6548998456741508e-006</v>
+        <v>6.6912490257331407e-006</v>
       </c>
       <c r="L15">
-        <v>-3.8584869621987541e-006</v>
+        <v>-3.7963805445022197e-006</v>
       </c>
       <c r="M15">
-        <v>0.00028064143360078059</v>
+        <v>0.00027322684070873906</v>
       </c>
       <c r="N15">
-        <v>5.0641855768751251e-005</v>
+        <v>5.2330442310922543e-005</v>
       </c>
       <c r="O15">
-        <v>0.00038609157009160833</v>
+        <v>0.00038666920707895324</v>
       </c>
       <c r="P15">
-        <v>0.0023274068415561292</v>
+        <v>0.0023217055249010188</v>
       </c>
       <c r="Q15">
-        <v>2.5249171004290184e-005</v>
+        <v>2.4767771551023837e-005</v>
       </c>
       <c r="R15">
-        <v>9.4030862405048612e-005</v>
+        <v>9.6782160815259312e-005</v>
       </c>
       <c r="S15">
-        <v>-0.00027628876787954713</v>
+        <v>-0.00028318743059656455</v>
       </c>
       <c r="T15">
-        <v>-0.00023528336462845306</v>
+        <v>-0.00023806332770871363</v>
       </c>
       <c r="U15">
-        <v>-0.0002513039795189471</v>
+        <v>-0.00025325648643516156</v>
       </c>
       <c r="V15">
-        <v>-0.00035207076810308993</v>
+        <v>-0.00035476441546417568</v>
       </c>
       <c r="W15">
-        <v>-0.0003258928350179679</v>
+        <v>-0.00032777967444936056</v>
       </c>
       <c r="X15">
-        <v>-0.00038569423761304557</v>
+        <v>-0.00038568742938495707</v>
       </c>
       <c r="Y15">
-        <v>-0.00030188496605155839</v>
+        <v>-0.00030426174888951042</v>
       </c>
       <c r="Z15">
-        <v>-0.00027384879968825326</v>
+        <v>-0.0002750224464255031</v>
       </c>
       <c r="AA15">
-        <v>-0.00032895214599066051</v>
+        <v>-0.00033177603410530863</v>
       </c>
       <c r="AB15">
-        <v>-0.0003208331897700473</v>
+        <v>-0.00032190813808523604</v>
       </c>
       <c r="AC15">
-        <v>-0.00038461350823125939</v>
+        <v>-0.00038655607023384427</v>
       </c>
       <c r="AD15">
-        <v>-0.00039255682369269268</v>
+        <v>-0.00039417420335518486</v>
       </c>
       <c r="AE15">
-        <v>5.2313071562975962e-005</v>
+        <v>5.190346369726126e-005</v>
       </c>
       <c r="AF15">
-        <v>2.179347820880626e-005</v>
+        <v>1.8648849759198325e-005</v>
       </c>
       <c r="AG15">
-        <v>-2.2267316008851352e-005</v>
+        <v>-2.4897689481454314e-005</v>
       </c>
       <c r="AH15">
-        <v>-0.000210968658204217</v>
+        <v>-0.00021096320896999755</v>
       </c>
       <c r="AI15">
-        <v>-0.00024803788018202795</v>
+        <v>-0.00025215023373669583</v>
       </c>
       <c r="AJ15">
-        <v>3.1011674530071181e-006</v>
+        <v>-1.7674048167903335e-005</v>
       </c>
       <c r="AK15">
-        <v>-0.0033303275827054053</v>
+        <v>-0.0032912247700982631</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="49">
-        <v>-0.0019802521204033757</v>
+      <c r="B16" s="51">
+        <v>-0.002192419891949922</v>
       </c>
       <c r="C16">
-        <v>-6.4926426633755919e-006</v>
+        <v>-6.2496492293874007e-006</v>
       </c>
       <c r="D16">
-        <v>1.0972523685424929e-007</v>
+        <v>1.0749740934547218e-007</v>
       </c>
       <c r="E16">
-        <v>-1.6604064024600775e-005</v>
+        <v>-3.656873159204431e-005</v>
       </c>
       <c r="F16">
-        <v>5.9948279479928569e-007</v>
+        <v>-1.2725430983794471e-005</v>
       </c>
       <c r="G16">
-        <v>-3.8835263359264521e-007</v>
+        <v>-1.5668370879952021e-005</v>
       </c>
       <c r="H16">
-        <v>4.1950283462710325e-006</v>
+        <v>-1.141340214802329e-005</v>
       </c>
       <c r="I16">
-        <v>1.2409871762184802e-005</v>
+        <v>1.1976274416046237e-005</v>
       </c>
       <c r="J16">
-        <v>4.6606269583277692e-007</v>
+        <v>1.0130186048124118e-006</v>
       </c>
       <c r="K16">
-        <v>-3.2312745308790326e-007</v>
+        <v>-3.0922544510233197e-007</v>
       </c>
       <c r="L16">
-        <v>1.3127511355686376e-007</v>
+        <v>1.346347613464506e-007</v>
       </c>
       <c r="M16">
-        <v>1.8466760276206163e-005</v>
+        <v>1.5948981751741253e-005</v>
       </c>
       <c r="N16">
-        <v>-1.9680950585803954e-005</v>
+        <v>-2.6580452178931586e-005</v>
       </c>
       <c r="O16">
-        <v>-1.9936929399051826e-006</v>
+        <v>-1.8034011087907499e-006</v>
       </c>
       <c r="P16">
-        <v>2.5249171004290184e-005</v>
+        <v>2.4767771551023837e-005</v>
       </c>
       <c r="Q16">
-        <v>0.00011941079533138834</v>
+        <v>0.00011990470629765518</v>
       </c>
       <c r="R16">
-        <v>1.1041042346893832e-005</v>
+        <v>7.116188656240089e-006</v>
       </c>
       <c r="S16">
-        <v>-6.5821205710092168e-006</v>
+        <v>-1.3039867036994455e-005</v>
       </c>
       <c r="T16">
-        <v>1.2931532370644844e-005</v>
+        <v>1.6480958668310675e-005</v>
       </c>
       <c r="U16">
-        <v>1.1740086604088151e-006</v>
+        <v>4.7462791833603746e-006</v>
       </c>
       <c r="V16">
-        <v>1.7211789109187331e-006</v>
+        <v>5.1225611474615962e-006</v>
       </c>
       <c r="W16">
-        <v>-2.056656409630056e-006</v>
+        <v>1.5783654405939276e-006</v>
       </c>
       <c r="X16">
-        <v>-6.0452187855613779e-006</v>
+        <v>-2.1788788495272562e-006</v>
       </c>
       <c r="Y16">
-        <v>1.4089473001546032e-006</v>
+        <v>5.025474612626625e-006</v>
       </c>
       <c r="Z16">
-        <v>-2.2847879971310547e-007</v>
+        <v>3.6534494777459847e-006</v>
       </c>
       <c r="AA16">
-        <v>-2.6902112666956149e-006</v>
+        <v>8.0263072854344641e-007</v>
       </c>
       <c r="AB16">
-        <v>1.7362209117147143e-006</v>
+        <v>5.2327635196598027e-006</v>
       </c>
       <c r="AC16">
-        <v>1.8620619075008712e-006</v>
+        <v>5.5899015461904206e-006</v>
       </c>
       <c r="AD16">
-        <v>-3.4586438810331466e-007</v>
+        <v>3.0045240861399647e-006</v>
       </c>
       <c r="AE16">
-        <v>0.00012724292069795349</v>
+        <v>0.00012753315841933796</v>
       </c>
       <c r="AF16">
-        <v>0.00023355225468625314</v>
+        <v>0.00023547464769164508</v>
       </c>
       <c r="AG16">
-        <v>2.5107236301245188e-005</v>
+        <v>2.6701879739563167e-005</v>
       </c>
       <c r="AH16">
-        <v>5.2703318298864127e-006</v>
+        <v>7.7975424394019152e-006</v>
       </c>
       <c r="AI16">
-        <v>-9.1861678339156053e-006</v>
+        <v>-7.231045517470773e-006</v>
       </c>
       <c r="AJ16">
-        <v>-8.8117516300464591e-006</v>
+        <v>5.3524613870844888e-006</v>
       </c>
       <c r="AK16">
-        <v>-0.0090726425427688391</v>
+        <v>-0.0091007820498416516</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="51">
-        <v>-0.37792829887041013</v>
+      <c r="B17" s="53">
+        <v>-0.37572480802444191</v>
       </c>
       <c r="C17">
-        <v>1.4655084664476521e-005</v>
+        <v>1.3527777325092688e-005</v>
       </c>
       <c r="D17">
-        <v>-3.9025168476109379e-008</v>
+        <v>-3.0753097616218367e-008</v>
       </c>
       <c r="E17">
-        <v>0.00046095510819785766</v>
+        <v>0.00046322447706607705</v>
       </c>
       <c r="F17">
-        <v>0.00056509629938558638</v>
+        <v>0.00057082216703754386</v>
       </c>
       <c r="G17">
-        <v>0.00063049010432582688</v>
+        <v>0.00063767045176412916</v>
       </c>
       <c r="H17">
-        <v>0.0006872323477244628</v>
+        <v>0.00069673123821269568</v>
       </c>
       <c r="I17">
-        <v>-0.00012256455988506607</v>
+        <v>-0.00011853384731187457</v>
       </c>
       <c r="J17">
-        <v>8.966015180355572e-005</v>
+        <v>8.6283242342479269e-005</v>
       </c>
       <c r="K17">
-        <v>-2.7418665665219714e-006</v>
+        <v>-2.6993127687237984e-006</v>
       </c>
       <c r="L17">
-        <v>4.7240317276291757e-006</v>
+        <v>4.6369736142335177e-006</v>
       </c>
       <c r="M17">
-        <v>-7.7549797474466182e-005</v>
+        <v>-7.3893402649859071e-005</v>
       </c>
       <c r="N17">
-        <v>-7.7404494346420942e-006</v>
+        <v>2.1913000123870564e-005</v>
       </c>
       <c r="O17">
-        <v>0.00012606853104952235</v>
+        <v>0.00013289803721221673</v>
       </c>
       <c r="P17">
-        <v>9.4030862405048612e-005</v>
+        <v>9.6782160815259312e-005</v>
       </c>
       <c r="Q17">
-        <v>1.1041042346893832e-005</v>
+        <v>7.116188656240089e-006</v>
       </c>
       <c r="R17">
-        <v>0.0075317470754304545</v>
+        <v>0.0075020374725520388</v>
       </c>
       <c r="S17">
-        <v>0.00044814002329483565</v>
+        <v>0.00044631956939288813</v>
       </c>
       <c r="T17">
-        <v>0.0003390795824499619</v>
+        <v>0.00033502410925518797</v>
       </c>
       <c r="U17">
-        <v>0.00022373769818528032</v>
+        <v>0.00021370584830195756</v>
       </c>
       <c r="V17">
-        <v>0.0002465700663892424</v>
+        <v>0.00024068242343523987</v>
       </c>
       <c r="W17">
-        <v>0.00026301132026333111</v>
+        <v>0.00024883013370535865</v>
       </c>
       <c r="X17">
-        <v>0.00029624467218108898</v>
+        <v>0.00027533714184495121</v>
       </c>
       <c r="Y17">
-        <v>0.00020852532260224005</v>
+        <v>0.00019208837323629342</v>
       </c>
       <c r="Z17">
-        <v>0.00025884295373048934</v>
+        <v>0.00025002795594475857</v>
       </c>
       <c r="AA17">
-        <v>0.00026236426882671453</v>
+        <v>0.00025366245243350471</v>
       </c>
       <c r="AB17">
-        <v>0.00025596922491792325</v>
+        <v>0.0002452191165863613</v>
       </c>
       <c r="AC17">
-        <v>0.00028220544355979761</v>
+        <v>0.00027555185488553581</v>
       </c>
       <c r="AD17">
-        <v>0.00025550154111116802</v>
+        <v>0.00024517768781199146</v>
       </c>
       <c r="AE17">
-        <v>1.7905767390734263e-005</v>
+        <v>1.5735089247312839e-005</v>
       </c>
       <c r="AF17">
-        <v>9.2526805916892061e-005</v>
+        <v>7.7427562601342347e-005</v>
       </c>
       <c r="AG17">
-        <v>0.00011795612906978416</v>
+        <v>0.00010729426752567226</v>
       </c>
       <c r="AH17">
-        <v>4.48854828419081e-005</v>
+        <v>5.0173604958135814e-005</v>
       </c>
       <c r="AI17">
-        <v>3.5313268729460917e-005</v>
+        <v>4.1618340139553019e-005</v>
       </c>
       <c r="AJ17">
-        <v>-0.00014448539611163999</v>
+        <v>0.00024145228825121203</v>
       </c>
       <c r="AK17">
-        <v>-0.0023792009712138634</v>
+        <v>-0.0020904829597113124</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="53">
-        <v>-0.10356415830876586</v>
+      <c r="B18" s="55">
+        <v>-0.097765143852455341</v>
       </c>
       <c r="C18">
-        <v>5.5722437820825783e-005</v>
+        <v>5.6752725777583406e-005</v>
       </c>
       <c r="D18">
-        <v>-7.2949111956338029e-007</v>
+        <v>-7.6089031189485166e-007</v>
       </c>
       <c r="E18">
-        <v>0.00054381735885955268</v>
+        <v>0.00057941235831922375</v>
       </c>
       <c r="F18">
-        <v>0.00057311835166657039</v>
+        <v>0.00059530357960510896</v>
       </c>
       <c r="G18">
-        <v>0.00064613469041668989</v>
+        <v>0.00067594827914355289</v>
       </c>
       <c r="H18">
-        <v>0.00063128178397712132</v>
+        <v>0.00066276836736550541</v>
       </c>
       <c r="I18">
-        <v>-0.00016989532341497721</v>
+        <v>-0.00016510919755817878</v>
       </c>
       <c r="J18">
-        <v>-9.0608635548040381e-006</v>
+        <v>-1.6877199645333205e-005</v>
       </c>
       <c r="K18">
-        <v>2.2913698010834542e-006</v>
+        <v>2.3339166555069418e-006</v>
       </c>
       <c r="L18">
-        <v>3.9066837276805056e-006</v>
+        <v>3.9511647485647202e-006</v>
       </c>
       <c r="M18">
-        <v>-2.8513003009755019e-005</v>
+        <v>-2.8845608013484326e-005</v>
       </c>
       <c r="N18">
-        <v>6.499730130769158e-005</v>
+        <v>0.00012874320692052692</v>
       </c>
       <c r="O18">
-        <v>-2.4477025419783807e-006</v>
+        <v>1.414108414716478e-006</v>
       </c>
       <c r="P18">
-        <v>-0.00027628876787954713</v>
+        <v>-0.00028318743059656455</v>
       </c>
       <c r="Q18">
-        <v>-6.5821205710092168e-006</v>
+        <v>-1.3039867036994455e-005</v>
       </c>
       <c r="R18">
-        <v>0.00044814002329483565</v>
+        <v>0.00044631956939288813</v>
       </c>
       <c r="S18">
-        <v>0.00096250423652090614</v>
+        <v>0.00097886548626550007</v>
       </c>
       <c r="T18">
-        <v>0.00017681271031769945</v>
+        <v>0.00014560050670002803</v>
       </c>
       <c r="U18">
-        <v>0.00019811277924897412</v>
+        <v>0.00016874231452924319</v>
       </c>
       <c r="V18">
-        <v>0.00022596449120826606</v>
+        <v>0.00019774978499841208</v>
       </c>
       <c r="W18">
-        <v>0.00019424801800722717</v>
+        <v>0.00016276072493337588</v>
       </c>
       <c r="X18">
-        <v>0.00021331194480388735</v>
+        <v>0.00018147811160281607</v>
       </c>
       <c r="Y18">
-        <v>0.00018736221051180607</v>
+        <v>0.00015461126592363351</v>
       </c>
       <c r="Z18">
-        <v>0.00017767561061285311</v>
+        <v>0.00014773443675889983</v>
       </c>
       <c r="AA18">
-        <v>0.00017521319074935762</v>
+        <v>0.00014363020562771999</v>
       </c>
       <c r="AB18">
-        <v>0.00022693976104274727</v>
+        <v>0.00019845131311408467</v>
       </c>
       <c r="AC18">
-        <v>0.00021728121247022484</v>
+        <v>0.00018903118988510968</v>
       </c>
       <c r="AD18">
-        <v>0.00026939854804106252</v>
+        <v>0.00023961861492052187</v>
       </c>
       <c r="AE18">
-        <v>-3.2347818765635918e-006</v>
+        <v>-7.385530554710135e-006</v>
       </c>
       <c r="AF18">
-        <v>6.1990294553049819e-006</v>
+        <v>-1.8613255317940488e-005</v>
       </c>
       <c r="AG18">
-        <v>1.401010500264236e-005</v>
+        <v>-3.8895454012202832e-006</v>
       </c>
       <c r="AH18">
-        <v>-8.0884866300023612e-005</v>
+        <v>-9.2502985330669652e-005</v>
       </c>
       <c r="AI18">
-        <v>0.00021311546416552443</v>
+        <v>0.00019578152751385087</v>
       </c>
       <c r="AJ18">
-        <v>-2.4223925193916896e-005</v>
+        <v>4.010783411214627e-006</v>
       </c>
       <c r="AK18">
-        <v>-0.0015550197384527733</v>
+        <v>-0.0011120122780923164</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="55">
-        <v>-0.20931045268720286</v>
+      <c r="B19" s="57">
+        <v>-0.21087733602924458</v>
       </c>
       <c r="C19">
-        <v>8.0062575125312927e-005</v>
+        <v>8.1692528790807978e-005</v>
       </c>
       <c r="D19">
-        <v>-1.0559119767036436e-006</v>
+        <v>-1.0734897929720984e-006</v>
       </c>
       <c r="E19">
-        <v>0.00022473212364694764</v>
+        <v>0.00011945152502073578</v>
       </c>
       <c r="F19">
-        <v>7.5640480026260143e-005</v>
+        <v>6.8955386269318282e-006</v>
       </c>
       <c r="G19">
-        <v>3.3011351274323376e-005</v>
+        <v>-4.5628887761550827e-005</v>
       </c>
       <c r="H19">
-        <v>-4.2523947487380911e-006</v>
+        <v>-8.410052874567261e-005</v>
       </c>
       <c r="I19">
-        <v>-0.00034886906451357983</v>
+        <v>-0.00035445852664717101</v>
       </c>
       <c r="J19">
-        <v>0.00012210878915096731</v>
+        <v>0.00012636257607917488</v>
       </c>
       <c r="K19">
-        <v>-4.8894495609464801e-006</v>
+        <v>-4.8779963606115706e-006</v>
       </c>
       <c r="L19">
-        <v>7.9847993969881191e-006</v>
+        <v>8.1451502484988511e-006</v>
       </c>
       <c r="M19">
-        <v>-0.00024943183504258807</v>
+        <v>-0.00027207371007631227</v>
       </c>
       <c r="N19">
-        <v>-6.1582861609832005e-005</v>
+        <v>-8.9933965591131081e-005</v>
       </c>
       <c r="O19">
-        <v>4.6625071834985451e-006</v>
+        <v>6.5762911607169551e-006</v>
       </c>
       <c r="P19">
-        <v>-0.00023528336462845306</v>
+        <v>-0.00023806332770871363</v>
       </c>
       <c r="Q19">
-        <v>1.2931532370644844e-005</v>
+        <v>1.6480958668310675e-005</v>
       </c>
       <c r="R19">
-        <v>0.0003390795824499619</v>
+        <v>0.00033502410925518797</v>
       </c>
       <c r="S19">
-        <v>0.00017681271031769945</v>
+        <v>0.00014560050670002803</v>
       </c>
       <c r="T19">
-        <v>0.0046623159188769175</v>
+        <v>0.0046919048700983096</v>
       </c>
       <c r="U19">
-        <v>0.0017719859318118102</v>
+        <v>0.0018013316381147266</v>
       </c>
       <c r="V19">
-        <v>0.0017657190223144396</v>
+        <v>0.0017963994774829887</v>
       </c>
       <c r="W19">
-        <v>0.0017419878939218978</v>
+        <v>0.0017694857422944433</v>
       </c>
       <c r="X19">
-        <v>0.0017524119735403123</v>
+        <v>0.0017773890321311396</v>
       </c>
       <c r="Y19">
-        <v>0.0017515836671254796</v>
+        <v>0.0017785283162053017</v>
       </c>
       <c r="Z19">
-        <v>0.0017410287014490767</v>
+        <v>0.0017711915946306029</v>
       </c>
       <c r="AA19">
-        <v>0.0017973288553323418</v>
+        <v>0.001825318604724676</v>
       </c>
       <c r="AB19">
-        <v>0.0018182021752946153</v>
+        <v>0.0018459644943651418</v>
       </c>
       <c r="AC19">
-        <v>0.0018284013225483239</v>
+        <v>0.0018586594396242126</v>
       </c>
       <c r="AD19">
-        <v>0.0018656020279724348</v>
+        <v>0.0018947888768764789</v>
       </c>
       <c r="AE19">
-        <v>-3.2826338768359353e-006</v>
+        <v>-1.0960308333664499e-006</v>
       </c>
       <c r="AF19">
-        <v>0.00019006017239770614</v>
+        <v>0.00020397282885572734</v>
       </c>
       <c r="AG19">
-        <v>0.00020784914027257887</v>
+        <v>0.00021699179593734905</v>
       </c>
       <c r="AH19">
-        <v>0.00066173804903469421</v>
+        <v>0.00068240387508939433</v>
       </c>
       <c r="AI19">
-        <v>0.001254136361659529</v>
+        <v>0.0012741523854077528</v>
       </c>
       <c r="AJ19">
-        <v>0.00052837369403701433</v>
+        <v>0.0004684374999862972</v>
       </c>
       <c r="AK19">
-        <v>-0.003698278484101395</v>
+        <v>-0.0039328911689454037</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="57">
-        <v>-0.087551084342831334</v>
+      <c r="B20" s="59">
+        <v>-0.089604829760407734</v>
       </c>
       <c r="C20">
-        <v>6.7211544627742825e-005</v>
+        <v>6.8299365467097955e-005</v>
       </c>
       <c r="D20">
-        <v>-9.2515918021538417e-007</v>
+        <v>-9.3419025183669299e-007</v>
       </c>
       <c r="E20">
-        <v>0.00026605652885259721</v>
+        <v>0.00017007925205957472</v>
       </c>
       <c r="F20">
-        <v>7.3191988146539702e-005</v>
+        <v>1.0608874571042923e-005</v>
       </c>
       <c r="G20">
-        <v>1.0179715412015028e-005</v>
+        <v>-6.1131056372638946e-005</v>
       </c>
       <c r="H20">
-        <v>-2.3947689661180886e-005</v>
+        <v>-9.6530780233772392e-005</v>
       </c>
       <c r="I20">
-        <v>-0.00034581787752933256</v>
+        <v>-0.00035096751195879533</v>
       </c>
       <c r="J20">
-        <v>0.00010337108761337906</v>
+        <v>0.00010768014410220803</v>
       </c>
       <c r="K20">
-        <v>-3.3985621469507645e-006</v>
+        <v>-3.3782032581874965e-006</v>
       </c>
       <c r="L20">
-        <v>7.4145370131942418e-006</v>
+        <v>7.5393250517113572e-006</v>
       </c>
       <c r="M20">
-        <v>-0.00027856043649657864</v>
+        <v>-0.00029773236168577051</v>
       </c>
       <c r="N20">
-        <v>-3.4177153694107607e-006</v>
+        <v>-3.3997300250209047e-005</v>
       </c>
       <c r="O20">
-        <v>1.0538942626716957e-005</v>
+        <v>1.2226630780537884e-005</v>
       </c>
       <c r="P20">
-        <v>-0.0002513039795189471</v>
+        <v>-0.00025325648643516156</v>
       </c>
       <c r="Q20">
-        <v>1.1740086604088151e-006</v>
+        <v>4.7462791833603746e-006</v>
       </c>
       <c r="R20">
-        <v>0.00022373769818528032</v>
+        <v>0.00021370584830195756</v>
       </c>
       <c r="S20">
-        <v>0.00019811277924897412</v>
+        <v>0.00016874231452924319</v>
       </c>
       <c r="T20">
-        <v>0.0017719859318118102</v>
+        <v>0.0018013316381147266</v>
       </c>
       <c r="U20">
-        <v>0.0026706471907932475</v>
+        <v>0.002696432179516115</v>
       </c>
       <c r="V20">
-        <v>0.0017205378602608485</v>
+        <v>0.0017490411239262928</v>
       </c>
       <c r="W20">
-        <v>0.0016976062513798908</v>
+        <v>0.0017233623135166827</v>
       </c>
       <c r="X20">
-        <v>0.0017175777797911289</v>
+        <v>0.0017407382030243611</v>
       </c>
       <c r="Y20">
-        <v>0.0017119975028951928</v>
+        <v>0.0017377624874040491</v>
       </c>
       <c r="Z20">
-        <v>0.0017033546035443881</v>
+        <v>0.0017314749515714182</v>
       </c>
       <c r="AA20">
-        <v>0.0017527115820639666</v>
+        <v>0.0017787955278552499</v>
       </c>
       <c r="AB20">
-        <v>0.0017667358999756302</v>
+        <v>0.0017923592528980279</v>
       </c>
       <c r="AC20">
-        <v>0.0017851279162151667</v>
+        <v>0.0018130326271467031</v>
       </c>
       <c r="AD20">
-        <v>0.0018157688865110524</v>
+        <v>0.0018425391519079257</v>
       </c>
       <c r="AE20">
-        <v>-1.6354938016738217e-005</v>
+        <v>-1.4127198062799433e-005</v>
       </c>
       <c r="AF20">
-        <v>0.00020982504902484656</v>
+        <v>0.00022345746361017744</v>
       </c>
       <c r="AG20">
-        <v>0.00020642165503529156</v>
+        <v>0.00021481725688436579</v>
       </c>
       <c r="AH20">
-        <v>0.0005702379533463382</v>
+        <v>0.00058923012781002542</v>
       </c>
       <c r="AI20">
-        <v>0.0012051887540159656</v>
+        <v>0.0012247040817999955</v>
       </c>
       <c r="AJ20">
-        <v>0.00045585126002685656</v>
+        <v>0.00040970288915056775</v>
       </c>
       <c r="AK20">
-        <v>-0.0025112449349569718</v>
+        <v>-0.0027436139170862036</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="59">
-        <v>-0.16295628383652294</v>
+      <c r="B21" s="61">
+        <v>-0.16511997506200932</v>
       </c>
       <c r="C21">
-        <v>8.8093820774956706e-005</v>
+        <v>8.9761743751595735e-005</v>
       </c>
       <c r="D21">
-        <v>-1.147264770040793e-006</v>
+        <v>-1.1651960047662571e-006</v>
       </c>
       <c r="E21">
-        <v>0.00017056668583288704</v>
+        <v>7.544660562002823e-005</v>
       </c>
       <c r="F21">
-        <v>6.7123894598100121e-005</v>
+        <v>4.5102694878716839e-006</v>
       </c>
       <c r="G21">
-        <v>-8.5099331084860638e-007</v>
+        <v>-7.225082991370931e-005</v>
       </c>
       <c r="H21">
-        <v>-1.1182342404165448e-005</v>
+        <v>-8.3851696296482082e-005</v>
       </c>
       <c r="I21">
-        <v>-0.00033006099923707315</v>
+        <v>-0.00033594478497776207</v>
       </c>
       <c r="J21">
-        <v>0.00010976003957238181</v>
+        <v>0.0001141595346448564</v>
       </c>
       <c r="K21">
-        <v>-4.0339515603811363e-006</v>
+        <v>-4.0445494827200777e-006</v>
       </c>
       <c r="L21">
-        <v>6.1332471078729283e-006</v>
+        <v>6.275202489434752e-006</v>
       </c>
       <c r="M21">
-        <v>-0.00022288841029625452</v>
+        <v>-0.00024410970595211095</v>
       </c>
       <c r="N21">
-        <v>-0.00012795742615997465</v>
+        <v>-0.00015614942761717448</v>
       </c>
       <c r="O21">
-        <v>9.4679997146918712e-006</v>
+        <v>1.1062700263523651e-005</v>
       </c>
       <c r="P21">
-        <v>-0.00035207076810308993</v>
+        <v>-0.00035476441546417568</v>
       </c>
       <c r="Q21">
-        <v>1.7211789109187331e-006</v>
+        <v>5.1225611474615962e-006</v>
       </c>
       <c r="R21">
-        <v>0.0002465700663892424</v>
+        <v>0.00024068242343523987</v>
       </c>
       <c r="S21">
-        <v>0.00022596449120826606</v>
+        <v>0.00019774978499841208</v>
       </c>
       <c r="T21">
-        <v>0.0017657190223144396</v>
+        <v>0.0017963994774829887</v>
       </c>
       <c r="U21">
-        <v>0.0017205378602608485</v>
+        <v>0.0017490411239262928</v>
       </c>
       <c r="V21">
-        <v>0.0027729538312840319</v>
+        <v>0.0028033005065214562</v>
       </c>
       <c r="W21">
-        <v>0.0016901206916063107</v>
+        <v>0.0017168881372343298</v>
       </c>
       <c r="X21">
-        <v>0.0017067102217015249</v>
+        <v>0.0017310941677899218</v>
       </c>
       <c r="Y21">
-        <v>0.001697131024539393</v>
+        <v>0.0017237077155179072</v>
       </c>
       <c r="Z21">
-        <v>0.0016836474059422123</v>
+        <v>0.001712834234918262</v>
       </c>
       <c r="AA21">
-        <v>0.0017377858934833779</v>
+        <v>0.0017645450644884944</v>
       </c>
       <c r="AB21">
-        <v>0.0017617509399086304</v>
+        <v>0.001788586624807557</v>
       </c>
       <c r="AC21">
-        <v>0.0017647969133427275</v>
+        <v>0.0017938235754523088</v>
       </c>
       <c r="AD21">
-        <v>0.0018114675734443419</v>
+        <v>0.0018400084076074031</v>
       </c>
       <c r="AE21">
-        <v>-1.8333037804321142e-005</v>
+        <v>-1.6294034805064033e-005</v>
       </c>
       <c r="AF21">
-        <v>0.00019071467694401612</v>
+        <v>0.00020498185534884809</v>
       </c>
       <c r="AG21">
-        <v>0.00011419379174596103</v>
+        <v>0.00012388822449912497</v>
       </c>
       <c r="AH21">
-        <v>0.00055880182167906067</v>
+        <v>0.00057759266805115653</v>
       </c>
       <c r="AI21">
-        <v>0.0011732323392096462</v>
+        <v>0.0011933024376243428</v>
       </c>
       <c r="AJ21">
-        <v>0.00050702155762189383</v>
+        <v>0.00043355571259124894</v>
       </c>
       <c r="AK21">
-        <v>-0.0028602589662405052</v>
+        <v>-0.0030879490007732179</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="61">
-        <v>-0.13404369347618297</v>
+      <c r="B22" s="63">
+        <v>-0.13573771652484676</v>
       </c>
       <c r="C22">
-        <v>8.3160063232037319e-005</v>
+        <v>8.4763511664361774e-005</v>
       </c>
       <c r="D22">
-        <v>-1.1108265277957712e-006</v>
+        <v>-1.1263347502938863e-006</v>
       </c>
       <c r="E22">
-        <v>0.00020910286575433974</v>
+        <v>0.00010696817366443291</v>
       </c>
       <c r="F22">
-        <v>7.2710339832432621e-005</v>
+        <v>5.4263048517650325e-006</v>
       </c>
       <c r="G22">
-        <v>1.2876538209106178e-005</v>
+        <v>-6.345736608453069e-005</v>
       </c>
       <c r="H22">
-        <v>-2.7414503134572544e-005</v>
+        <v>-0.00010530634866522082</v>
       </c>
       <c r="I22">
-        <v>-0.00031512954045674689</v>
+        <v>-0.00031980795269530055</v>
       </c>
       <c r="J22">
-        <v>8.4284010648295838e-005</v>
+        <v>8.8832977086453528e-005</v>
       </c>
       <c r="K22">
-        <v>-2.0779184669438174e-006</v>
+        <v>-2.0744881052704565e-006</v>
       </c>
       <c r="L22">
-        <v>6.2286883854026853e-006</v>
+        <v>6.3264225918670411e-006</v>
       </c>
       <c r="M22">
-        <v>-0.00023129156660971423</v>
+        <v>-0.00024968575859188585</v>
       </c>
       <c r="N22">
-        <v>-0.00015077079201811531</v>
+        <v>-0.00018197016578438627</v>
       </c>
       <c r="O22">
-        <v>-2.0132156069647836e-005</v>
+        <v>-1.8349519125051509e-005</v>
       </c>
       <c r="P22">
-        <v>-0.0003258928350179679</v>
+        <v>-0.00032777967444936056</v>
       </c>
       <c r="Q22">
-        <v>-2.056656409630056e-006</v>
+        <v>1.5783654405939276e-006</v>
       </c>
       <c r="R22">
-        <v>0.00026301132026333111</v>
+        <v>0.00024883013370535865</v>
       </c>
       <c r="S22">
-        <v>0.00019424801800722717</v>
+        <v>0.00016276072493337588</v>
       </c>
       <c r="T22">
-        <v>0.0017419878939218978</v>
+        <v>0.0017694857422944433</v>
       </c>
       <c r="U22">
-        <v>0.0016976062513798908</v>
+        <v>0.0017233623135166827</v>
       </c>
       <c r="V22">
-        <v>0.0016901206916063107</v>
+        <v>0.0017168881372343298</v>
       </c>
       <c r="W22">
-        <v>0.0028785246459036209</v>
+        <v>0.0029013004125995339</v>
       </c>
       <c r="X22">
-        <v>0.0016817206209739138</v>
+        <v>0.0017041508510500373</v>
       </c>
       <c r="Y22">
-        <v>0.0016769398385451403</v>
+        <v>0.0017025824819819054</v>
       </c>
       <c r="Z22">
-        <v>0.0016613840620532969</v>
+        <v>0.0016883914778964171</v>
       </c>
       <c r="AA22">
-        <v>0.0017180232293109575</v>
+        <v>0.0017426280234585077</v>
       </c>
       <c r="AB22">
-        <v>0.0017338889482713389</v>
+        <v>0.0017587296122314254</v>
       </c>
       <c r="AC22">
-        <v>0.0017495084953840436</v>
+        <v>0.0017759134165779014</v>
       </c>
       <c r="AD22">
-        <v>0.0017836510721545547</v>
+        <v>0.0018088627614722221</v>
       </c>
       <c r="AE22">
-        <v>-2.1236903339443244e-005</v>
+        <v>-1.8984237556438313e-005</v>
       </c>
       <c r="AF22">
-        <v>0.00013946821938723363</v>
+        <v>0.00015373950261869611</v>
       </c>
       <c r="AG22">
-        <v>0.00014311366674692205</v>
+        <v>0.00015249248178149033</v>
       </c>
       <c r="AH22">
-        <v>0.0005754881675140021</v>
+        <v>0.00059319154313192623</v>
       </c>
       <c r="AI22">
-        <v>0.0011569371853972436</v>
+        <v>0.0011735846669350398</v>
       </c>
       <c r="AJ22">
-        <v>0.00042710839588817325</v>
+        <v>0.00035443174048342165</v>
       </c>
       <c r="AK22">
-        <v>-0.0025426709236660277</v>
+        <v>-0.0027805617835765053</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="63">
-        <v>-0.039065820003776772</v>
+      <c r="B23" s="65">
+        <v>-0.040989446197059</v>
       </c>
       <c r="C23">
-        <v>9.7180196047770995e-005</v>
+        <v>9.8246970137814884e-005</v>
       </c>
       <c r="D23">
-        <v>-1.3256339155796814e-006</v>
+        <v>-1.333431050370496e-006</v>
       </c>
       <c r="E23">
-        <v>0.00021022546714742431</v>
+        <v>0.00010913547239267321</v>
       </c>
       <c r="F23">
-        <v>2.6059119002294227e-005</v>
+        <v>-3.9758755768698256e-005</v>
       </c>
       <c r="G23">
-        <v>-4.2393353162490678e-005</v>
+        <v>-0.00011695038917788669</v>
       </c>
       <c r="H23">
-        <v>-8.5940207956492582e-005</v>
+        <v>-0.000161747974319206</v>
       </c>
       <c r="I23">
-        <v>-0.00036565363523757231</v>
+        <v>-0.00036908763478022479</v>
       </c>
       <c r="J23">
-        <v>0.00013688868687990755</v>
+        <v>0.00014132443658040067</v>
       </c>
       <c r="K23">
-        <v>-2.7641814002562012e-006</v>
+        <v>-2.7435284129956891e-006</v>
       </c>
       <c r="L23">
-        <v>8.8191725090410704e-006</v>
+        <v>8.8697364200211338e-006</v>
       </c>
       <c r="M23">
-        <v>-0.00023687969064150791</v>
+        <v>-0.00025180542154413566</v>
       </c>
       <c r="N23">
-        <v>-0.00011601315563224308</v>
+        <v>-0.00014931570708665389</v>
       </c>
       <c r="O23">
-        <v>8.1593432679923604e-008</v>
+        <v>1.1394025822183658e-006</v>
       </c>
       <c r="P23">
-        <v>-0.00038569423761304557</v>
+        <v>-0.00038568742938495707</v>
       </c>
       <c r="Q23">
-        <v>-6.0452187855613779e-006</v>
+        <v>-2.1788788495272562e-006</v>
       </c>
       <c r="R23">
-        <v>0.00029624467218108898</v>
+        <v>0.00027533714184495121</v>
       </c>
       <c r="S23">
-        <v>0.00021331194480388735</v>
+        <v>0.00018147811160281607</v>
       </c>
       <c r="T23">
-        <v>0.0017524119735403123</v>
+        <v>0.0017773890321311396</v>
       </c>
       <c r="U23">
-        <v>0.0017175777797911289</v>
+        <v>0.0017407382030243611</v>
       </c>
       <c r="V23">
-        <v>0.0017067102217015249</v>
+        <v>0.0017310941677899218</v>
       </c>
       <c r="W23">
-        <v>0.0016817206209739138</v>
+        <v>0.0017041508510500373</v>
       </c>
       <c r="X23">
-        <v>0.0029106295561356389</v>
+        <v>0.0029288885427105767</v>
       </c>
       <c r="Y23">
-        <v>0.0016965315263708335</v>
+        <v>0.0017200565964470781</v>
       </c>
       <c r="Z23">
-        <v>0.0016845639056004775</v>
+        <v>0.0017091719431715983</v>
       </c>
       <c r="AA23">
-        <v>0.0017367536854748359</v>
+        <v>0.0017594955984568529</v>
       </c>
       <c r="AB23">
-        <v>0.0017481610953909597</v>
+        <v>0.0017697439998288825</v>
       </c>
       <c r="AC23">
-        <v>0.0017505753209665674</v>
+        <v>0.0017748232177148141</v>
       </c>
       <c r="AD23">
-        <v>0.001795683044338814</v>
+        <v>0.0018181112401568825</v>
       </c>
       <c r="AE23">
-        <v>-2.2825684574158671e-005</v>
+        <v>-2.0331518319677782e-005</v>
       </c>
       <c r="AF23">
-        <v>0.00011509510320039923</v>
+        <v>0.00013015635478741533</v>
       </c>
       <c r="AG23">
-        <v>0.00010835356309170077</v>
+        <v>0.00011714479725572128</v>
       </c>
       <c r="AH23">
-        <v>0.00050078194256549403</v>
+        <v>0.0005179623690327982</v>
       </c>
       <c r="AI23">
-        <v>0.0011059599220129355</v>
+        <v>0.001120612617944554</v>
       </c>
       <c r="AJ23">
-        <v>0.00037818252868797612</v>
+        <v>0.00032906519880849009</v>
       </c>
       <c r="AK23">
-        <v>-0.0025148309386554594</v>
+        <v>-0.0027608366271446435</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="64" t="s">
+      <c r="A24" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="65">
-        <v>-0.020628752027173642</v>
+      <c r="B24" s="67">
+        <v>-0.02218945068990039</v>
       </c>
       <c r="C24">
-        <v>4.468553904350735e-005</v>
+        <v>4.6224320986391204e-005</v>
       </c>
       <c r="D24">
-        <v>-6.0130938063793291e-007</v>
+        <v>-6.1524018670199585e-007</v>
       </c>
       <c r="E24">
-        <v>0.00023349825005749016</v>
+        <v>0.00012130480040200606</v>
       </c>
       <c r="F24">
-        <v>7.5382692332199739e-005</v>
+        <v>3.7262708609822007e-007</v>
       </c>
       <c r="G24">
-        <v>3.8045006017513425e-006</v>
+        <v>-7.9874364425721982e-005</v>
       </c>
       <c r="H24">
-        <v>-5.5632126752674991e-005</v>
+        <v>-0.00014137870170461634</v>
       </c>
       <c r="I24">
-        <v>-0.0003274511068535208</v>
+        <v>-0.00033293757268326176</v>
       </c>
       <c r="J24">
-        <v>6.7517669979448884e-005</v>
+        <v>7.34562718876279e-005</v>
       </c>
       <c r="K24">
-        <v>-2.6817784995845098e-006</v>
+        <v>-2.615094236669386e-006</v>
       </c>
       <c r="L24">
-        <v>6.6473650654206314e-006</v>
+        <v>6.7685759695355885e-006</v>
       </c>
       <c r="M24">
-        <v>-0.00024988674099549364</v>
+        <v>-0.00026796225909428754</v>
       </c>
       <c r="N24">
-        <v>-8.6741860427858833e-005</v>
+        <v>-0.0001143684449599633</v>
       </c>
       <c r="O24">
-        <v>-4.0061957683810816e-006</v>
+        <v>-2.6889000845986902e-006</v>
       </c>
       <c r="P24">
-        <v>-0.00030188496605155839</v>
+        <v>-0.00030426174888951042</v>
       </c>
       <c r="Q24">
-        <v>1.4089473001546032e-006</v>
+        <v>5.025474612626625e-006</v>
       </c>
       <c r="R24">
-        <v>0.00020852532260224005</v>
+        <v>0.00019208837323629342</v>
       </c>
       <c r="S24">
-        <v>0.00018736221051180607</v>
+        <v>0.00015461126592363351</v>
       </c>
       <c r="T24">
-        <v>0.0017515836671254796</v>
+        <v>0.0017785283162053017</v>
       </c>
       <c r="U24">
-        <v>0.0017119975028951928</v>
+        <v>0.0017377624874040491</v>
       </c>
       <c r="V24">
-        <v>0.001697131024539393</v>
+        <v>0.0017237077155179072</v>
       </c>
       <c r="W24">
-        <v>0.0016769398385451403</v>
+        <v>0.0017025824819819054</v>
       </c>
       <c r="X24">
-        <v>0.0016965315263708335</v>
+        <v>0.0017200565964470781</v>
       </c>
       <c r="Y24">
-        <v>0.0028079253482348777</v>
+        <v>0.0028365851007568469</v>
       </c>
       <c r="Z24">
-        <v>0.0016875118829241483</v>
+        <v>0.0017150336662333119</v>
       </c>
       <c r="AA24">
-        <v>0.0017358133219839266</v>
+        <v>0.0017603846737420743</v>
       </c>
       <c r="AB24">
-        <v>0.0017432149723503861</v>
+        <v>0.0017687795470923565</v>
       </c>
       <c r="AC24">
-        <v>0.0017597623808027862</v>
+        <v>0.0017860517291149788</v>
       </c>
       <c r="AD24">
-        <v>0.0017929563539525173</v>
+        <v>0.0018178637983320726</v>
       </c>
       <c r="AE24">
-        <v>-1.4332158611014779e-005</v>
+        <v>-1.2186120553676022e-005</v>
       </c>
       <c r="AF24">
-        <v>0.0001636161773222318</v>
+        <v>0.00017878522665230751</v>
       </c>
       <c r="AG24">
-        <v>0.00013943919448072202</v>
+        <v>0.0001508843975076467</v>
       </c>
       <c r="AH24">
-        <v>0.00058880885739011465</v>
+        <v>0.00060575778185541359</v>
       </c>
       <c r="AI24">
-        <v>0.0011752204856926448</v>
+        <v>0.001188414475218227</v>
       </c>
       <c r="AJ24">
-        <v>0.00041372865763569138</v>
+        <v>0.00030105874531361507</v>
       </c>
       <c r="AK24">
-        <v>-0.0021346664917624926</v>
+        <v>-0.0023653299709732027</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="67">
-        <v>-0.0081156819625127236</v>
+      <c r="B25" s="69">
+        <v>-0.0099528484435711766</v>
       </c>
       <c r="C25">
-        <v>6.9563487958185059e-005</v>
+        <v>7.0778500516263058e-005</v>
       </c>
       <c r="D25">
-        <v>-9.3566579960460737e-007</v>
+        <v>-9.4511520472124279e-007</v>
       </c>
       <c r="E25">
-        <v>0.00019801308776431096</v>
+        <v>0.00010048376945638306</v>
       </c>
       <c r="F25">
-        <v>6.2343287861789767e-005</v>
+        <v>-1.7451942720680957e-006</v>
       </c>
       <c r="G25">
-        <v>-2.6004507926291891e-005</v>
+        <v>-9.8630881957276629e-005</v>
       </c>
       <c r="H25">
-        <v>-0.00010558150289496568</v>
+        <v>-0.00018017917408070703</v>
       </c>
       <c r="I25">
-        <v>-0.00034025506829093939</v>
+        <v>-0.0003457769713406267</v>
       </c>
       <c r="J25">
-        <v>9.5596651203738514e-005</v>
+        <v>0.0001006287217598277</v>
       </c>
       <c r="K25">
-        <v>-3.2802372632566922e-006</v>
+        <v>-3.2491296527743587e-006</v>
       </c>
       <c r="L25">
-        <v>6.3238819022400376e-006</v>
+        <v>6.4442190639198137e-006</v>
       </c>
       <c r="M25">
-        <v>-0.00021537773021940306</v>
+        <v>-0.00023341135252863583</v>
       </c>
       <c r="N25">
-        <v>-4.7752968016310528e-005</v>
+        <v>-7.9759205273199473e-005</v>
       </c>
       <c r="O25">
-        <v>2.011760633091348e-005</v>
+        <v>2.1800411542577348e-005</v>
       </c>
       <c r="P25">
-        <v>-0.00027384879968825326</v>
+        <v>-0.0002750224464255031</v>
       </c>
       <c r="Q25">
-        <v>-2.2847879971310547e-007</v>
+        <v>3.6534494777459847e-006</v>
       </c>
       <c r="R25">
-        <v>0.00025884295373048934</v>
+        <v>0.00025002795594475857</v>
       </c>
       <c r="S25">
-        <v>0.00017767561061285311</v>
+        <v>0.00014773443675889983</v>
       </c>
       <c r="T25">
-        <v>0.0017410287014490767</v>
+        <v>0.0017711915946306029</v>
       </c>
       <c r="U25">
-        <v>0.0017033546035443881</v>
+        <v>0.0017314749515714182</v>
       </c>
       <c r="V25">
-        <v>0.0016836474059422123</v>
+        <v>0.001712834234918262</v>
       </c>
       <c r="W25">
-        <v>0.0016613840620532969</v>
+        <v>0.0016883914778964171</v>
       </c>
       <c r="X25">
-        <v>0.0016845639056004775</v>
+        <v>0.0017091719431715983</v>
       </c>
       <c r="Y25">
-        <v>0.0016875118829241483</v>
+        <v>0.0017150336662333119</v>
       </c>
       <c r="Z25">
-        <v>0.0024792137011509555</v>
+        <v>0.002508611718903272</v>
       </c>
       <c r="AA25">
-        <v>0.0017222189227101802</v>
+        <v>0.0017494276297107759</v>
       </c>
       <c r="AB25">
-        <v>0.0017286444781656554</v>
+        <v>0.0017557923974102258</v>
       </c>
       <c r="AC25">
-        <v>0.0017482632930485155</v>
+        <v>0.001776915709060529</v>
       </c>
       <c r="AD25">
-        <v>0.0017703464610364351</v>
+        <v>0.0017979494975211999</v>
       </c>
       <c r="AE25">
-        <v>-1.6369865323704454e-005</v>
+        <v>-1.393975370434445e-005</v>
       </c>
       <c r="AF25">
-        <v>0.00016857542627377219</v>
+        <v>0.00018408776664082823</v>
       </c>
       <c r="AG25">
-        <v>0.00014908645924614428</v>
+        <v>0.00015932669593242399</v>
       </c>
       <c r="AH25">
-        <v>0.00057888970067817994</v>
+        <v>0.00059784581339784588</v>
       </c>
       <c r="AI25">
-        <v>0.001155047544201706</v>
+        <v>0.0011736891301534259</v>
       </c>
       <c r="AJ25">
-        <v>0.00041319000819954761</v>
+        <v>0.00036398192802770501</v>
       </c>
       <c r="AK25">
-        <v>-0.0023766259336560997</v>
+        <v>-0.0026339830670702234</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="69">
-        <v>-0.021322883859433855</v>
+      <c r="B26" s="71">
+        <v>-0.023421776289086278</v>
       </c>
       <c r="C26">
-        <v>8.3151655040130702e-005</v>
+        <v>8.5079948503975072e-005</v>
       </c>
       <c r="D26">
-        <v>-1.1533652417715067e-006</v>
+        <v>-1.175032400804453e-006</v>
       </c>
       <c r="E26">
-        <v>0.0001553196846156383</v>
+        <v>5.083080308811535e-005</v>
       </c>
       <c r="F26">
-        <v>8.726822481260315e-006</v>
+        <v>-5.9313579612372495e-005</v>
       </c>
       <c r="G26">
-        <v>-6.8751168441415038e-005</v>
+        <v>-0.0001489587950747681</v>
       </c>
       <c r="H26">
-        <v>-9.6055829832813306e-005</v>
+        <v>-0.00017637661680098291</v>
       </c>
       <c r="I26">
-        <v>-0.0003462651165415479</v>
+        <v>-0.00035112402544145219</v>
       </c>
       <c r="J26">
-        <v>9.8460915108460393e-005</v>
+        <v>0.00010240644686438792</v>
       </c>
       <c r="K26">
-        <v>-3.0516608885218209e-006</v>
+        <v>-3.0510552389879394e-006</v>
       </c>
       <c r="L26">
-        <v>7.1970304885206834e-006</v>
+        <v>7.3285137890432505e-006</v>
       </c>
       <c r="M26">
-        <v>-0.00023547726226635294</v>
+        <v>-0.00025691210063771082</v>
       </c>
       <c r="N26">
-        <v>-0.00012771653873828873</v>
+        <v>-0.00015803880204480134</v>
       </c>
       <c r="O26">
-        <v>-1.1078369404826042e-005</v>
+        <v>-9.8465801934141325e-006</v>
       </c>
       <c r="P26">
-        <v>-0.00032895214599066051</v>
+        <v>-0.00033177603410530863</v>
       </c>
       <c r="Q26">
-        <v>-2.6902112666956149e-006</v>
+        <v>8.0263072854344641e-007</v>
       </c>
       <c r="R26">
-        <v>0.00026236426882671453</v>
+        <v>0.00025366245243350471</v>
       </c>
       <c r="S26">
-        <v>0.00017521319074935762</v>
+        <v>0.00014363020562771999</v>
       </c>
       <c r="T26">
-        <v>0.0017973288553323418</v>
+        <v>0.001825318604724676</v>
       </c>
       <c r="U26">
-        <v>0.0017527115820639666</v>
+        <v>0.0017787955278552499</v>
       </c>
       <c r="V26">
-        <v>0.0017377858934833779</v>
+        <v>0.0017645450644884944</v>
       </c>
       <c r="W26">
-        <v>0.0017180232293109575</v>
+        <v>0.0017426280234585077</v>
       </c>
       <c r="X26">
-        <v>0.0017367536854748359</v>
+        <v>0.0017594955984568529</v>
       </c>
       <c r="Y26">
-        <v>0.0017358133219839266</v>
+        <v>0.0017603846737420743</v>
       </c>
       <c r="Z26">
-        <v>0.0017222189227101802</v>
+        <v>0.0017494276297107759</v>
       </c>
       <c r="AA26">
-        <v>0.002939374841426614</v>
+        <v>0.0029640162544519407</v>
       </c>
       <c r="AB26">
-        <v>0.0017895714975137687</v>
+        <v>0.0018135923048097349</v>
       </c>
       <c r="AC26">
-        <v>0.0018060731905352187</v>
+        <v>0.0018327967868983952</v>
       </c>
       <c r="AD26">
-        <v>0.0018354046093860194</v>
+        <v>0.001861273649882087</v>
       </c>
       <c r="AE26">
-        <v>-2.3632674842858807e-005</v>
+        <v>-2.147552029614305e-005</v>
       </c>
       <c r="AF26">
-        <v>0.00020449906577185844</v>
+        <v>0.0002179629368665151</v>
       </c>
       <c r="AG26">
-        <v>0.00016570860923997702</v>
+        <v>0.00017384561303023047</v>
       </c>
       <c r="AH26">
-        <v>0.0006638319130754548</v>
+        <v>0.00068184615738556937</v>
       </c>
       <c r="AI26">
-        <v>0.0012157070478011694</v>
+        <v>0.001232818345633716</v>
       </c>
       <c r="AJ26">
-        <v>0.00050420640819359946</v>
+        <v>0.0004116904226387617</v>
       </c>
       <c r="AK26">
-        <v>-0.0023718124574974896</v>
+        <v>-0.0026018760636531274</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="71">
-        <v>-0.11575838509135195</v>
+      <c r="B27" s="73">
+        <v>-0.11770996570107203</v>
       </c>
       <c r="C27">
-        <v>7.5127198063917183e-005</v>
+        <v>7.690201728155141e-005</v>
       </c>
       <c r="D27">
-        <v>-9.8048892332197493e-007</v>
+        <v>-9.9942618394518535e-007</v>
       </c>
       <c r="E27">
-        <v>0.00019077679535243881</v>
+        <v>9.36243513600591e-005</v>
       </c>
       <c r="F27">
-        <v>8.7072659595821859e-005</v>
+        <v>2.2880950558407348e-005</v>
       </c>
       <c r="G27">
-        <v>5.0406104686529321e-005</v>
+        <v>-2.2063796574065399e-005</v>
       </c>
       <c r="H27">
-        <v>2.1104776571087254e-005</v>
+        <v>-5.2609002730068678e-005</v>
       </c>
       <c r="I27">
-        <v>-0.00033457737959395172</v>
+        <v>-0.0003391623807762462</v>
       </c>
       <c r="J27">
-        <v>9.4815624407321034e-005</v>
+        <v>9.9031521257687914e-005</v>
       </c>
       <c r="K27">
-        <v>-3.4162913855761588e-006</v>
+        <v>-3.4209398925226888e-006</v>
       </c>
       <c r="L27">
-        <v>7.798173757501018e-006</v>
+        <v>7.9240283364151581e-006</v>
       </c>
       <c r="M27">
-        <v>-0.00022274336524397576</v>
+        <v>-0.00024225467254541727</v>
       </c>
       <c r="N27">
-        <v>-8.4168821347981081e-005</v>
+        <v>-0.00011049491640044646</v>
       </c>
       <c r="O27">
-        <v>1.8522650367347199e-005</v>
+        <v>1.9353835555100752e-005</v>
       </c>
       <c r="P27">
-        <v>-0.0003208331897700473</v>
+        <v>-0.00032190813808523604</v>
       </c>
       <c r="Q27">
-        <v>1.7362209117147143e-006</v>
+        <v>5.2327635196598027e-006</v>
       </c>
       <c r="R27">
-        <v>0.00025596922491792325</v>
+        <v>0.0002452191165863613</v>
       </c>
       <c r="S27">
-        <v>0.00022693976104274727</v>
+        <v>0.00019845131311408467</v>
       </c>
       <c r="T27">
-        <v>0.0018182021752946153</v>
+        <v>0.0018459644943651418</v>
       </c>
       <c r="U27">
-        <v>0.0017667358999756302</v>
+        <v>0.0017923592528980279</v>
       </c>
       <c r="V27">
-        <v>0.0017617509399086304</v>
+        <v>0.001788586624807557</v>
       </c>
       <c r="W27">
-        <v>0.0017338889482713389</v>
+        <v>0.0017587296122314254</v>
       </c>
       <c r="X27">
-        <v>0.0017481610953909597</v>
+        <v>0.0017697439998288825</v>
       </c>
       <c r="Y27">
-        <v>0.0017432149723503861</v>
+        <v>0.0017687795470923565</v>
       </c>
       <c r="Z27">
-        <v>0.0017286444781656554</v>
+        <v>0.0017557923974102258</v>
       </c>
       <c r="AA27">
-        <v>0.0017895714975137687</v>
+        <v>0.0018135923048097349</v>
       </c>
       <c r="AB27">
-        <v>0.0029959799089742559</v>
+        <v>0.0030213429374821715</v>
       </c>
       <c r="AC27">
-        <v>0.0018248436111020303</v>
+        <v>0.0018513153652592947</v>
       </c>
       <c r="AD27">
-        <v>0.0018616808306891335</v>
+        <v>0.0018873062607325678</v>
       </c>
       <c r="AE27">
-        <v>-1.6719365049067255e-005</v>
+        <v>-1.4746037960283324e-005</v>
       </c>
       <c r="AF27">
-        <v>0.00015648551275737561</v>
+        <v>0.00017066242418998788</v>
       </c>
       <c r="AG27">
-        <v>0.00012258240983598103</v>
+        <v>0.0001317668132816891</v>
       </c>
       <c r="AH27">
-        <v>0.00067252007117182008</v>
+        <v>0.00068925773482373027</v>
       </c>
       <c r="AI27">
-        <v>0.0012613202452815551</v>
+        <v>0.0012776992518579002</v>
       </c>
       <c r="AJ27">
-        <v>0.00059626622817652707</v>
+        <v>0.00044300503276680078</v>
       </c>
       <c r="AK27">
-        <v>-0.0028292036188642304</v>
+        <v>-0.0030608948677150662</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="73">
-        <v>-0.1385827743078705</v>
+      <c r="B28" s="75">
+        <v>-0.14036987376707938</v>
       </c>
       <c r="C28">
-        <v>5.9494713312798365e-005</v>
+        <v>6.1508778142236459e-005</v>
       </c>
       <c r="D28">
-        <v>-8.1480332167291081e-007</v>
+        <v>-8.3712284226797291e-007</v>
       </c>
       <c r="E28">
-        <v>0.00015726540748523221</v>
+        <v>6.3891959659697684e-005</v>
       </c>
       <c r="F28">
-        <v>3.4058113681272517e-006</v>
+        <v>-5.8212974969961079e-005</v>
       </c>
       <c r="G28">
-        <v>-4.463457563528314e-005</v>
+        <v>-0.00011489788731529067</v>
       </c>
       <c r="H28">
-        <v>-7.9862349460414804e-005</v>
+        <v>-0.00015159909821161807</v>
       </c>
       <c r="I28">
-        <v>-0.00030384858605206583</v>
+        <v>-0.00030947367260431436</v>
       </c>
       <c r="J28">
-        <v>8.5050096254028057e-005</v>
+        <v>8.9532277120727213e-005</v>
       </c>
       <c r="K28">
-        <v>-3.9796431744897791e-006</v>
+        <v>-3.9805346685886856e-006</v>
       </c>
       <c r="L28">
-        <v>6.7684982369673155e-006</v>
+        <v>6.8968412344205426e-006</v>
       </c>
       <c r="M28">
-        <v>-0.00029175740158209301</v>
+        <v>-0.00031079628628912252</v>
       </c>
       <c r="N28">
-        <v>-0.00010930991183936544</v>
+        <v>-0.00013892149108850598</v>
       </c>
       <c r="O28">
-        <v>-2.0222369049440608e-005</v>
+        <v>-1.8623300811848468e-005</v>
       </c>
       <c r="P28">
-        <v>-0.00038461350823125939</v>
+        <v>-0.00038655607023384427</v>
       </c>
       <c r="Q28">
-        <v>1.8620619075008712e-006</v>
+        <v>5.5899015461904206e-006</v>
       </c>
       <c r="R28">
-        <v>0.00028220544355979761</v>
+        <v>0.00027555185488553581</v>
       </c>
       <c r="S28">
-        <v>0.00021728121247022484</v>
+        <v>0.00018903118988510968</v>
       </c>
       <c r="T28">
-        <v>0.0018284013225483239</v>
+        <v>0.0018586594396242126</v>
       </c>
       <c r="U28">
-        <v>0.0017851279162151667</v>
+        <v>0.0018130326271467031</v>
       </c>
       <c r="V28">
-        <v>0.0017647969133427275</v>
+        <v>0.0017938235754523088</v>
       </c>
       <c r="W28">
-        <v>0.0017495084953840436</v>
+        <v>0.0017759134165779014</v>
       </c>
       <c r="X28">
-        <v>0.0017505753209665674</v>
+        <v>0.0017748232177148141</v>
       </c>
       <c r="Y28">
-        <v>0.0017597623808027862</v>
+        <v>0.0017860517291149788</v>
       </c>
       <c r="Z28">
-        <v>0.0017482632930485155</v>
+        <v>0.001776915709060529</v>
       </c>
       <c r="AA28">
-        <v>0.0018060731905352187</v>
+        <v>0.0018327967868983952</v>
       </c>
       <c r="AB28">
-        <v>0.0018248436111020303</v>
+        <v>0.0018513153652592947</v>
       </c>
       <c r="AC28">
-        <v>0.0031415733471905401</v>
+        <v>0.0031708444353529242</v>
       </c>
       <c r="AD28">
-        <v>0.001876337143648718</v>
+        <v>0.0019041759576593142</v>
       </c>
       <c r="AE28">
-        <v>-1.1388685162989719e-005</v>
+        <v>-9.0549254323836774e-006</v>
       </c>
       <c r="AF28">
-        <v>0.00012050485922488166</v>
+        <v>0.00013501815023228913</v>
       </c>
       <c r="AG28">
-        <v>0.00010108886428791937</v>
+        <v>0.00011042957156223037</v>
       </c>
       <c r="AH28">
-        <v>0.0008122753542342525</v>
+        <v>0.00083120132417694272</v>
       </c>
       <c r="AI28">
-        <v>0.0012576248199146979</v>
+        <v>0.0012765172153347548</v>
       </c>
       <c r="AJ28">
-        <v>0.00047836579722712646</v>
+        <v>0.00041284074789465125</v>
       </c>
       <c r="AK28">
-        <v>-0.0024577381531434425</v>
+        <v>-0.0027172454933257462</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="75">
-        <v>0.0035747574795981347</v>
+      <c r="B29" s="77">
+        <v>0.0026798021834234706</v>
       </c>
       <c r="C29">
-        <v>8.8601440144571615e-005</v>
+        <v>9.0115108023285616e-005</v>
       </c>
       <c r="D29">
-        <v>-1.1791774634964906e-006</v>
+        <v>-1.1950696742004009e-006</v>
       </c>
       <c r="E29">
-        <v>0.00025955544174505922</v>
+        <v>0.00015961664857010502</v>
       </c>
       <c r="F29">
-        <v>0.0001412362380144199</v>
+        <v>7.5901272387147957e-005</v>
       </c>
       <c r="G29">
-        <v>4.8316482536272512e-005</v>
+        <v>-2.5382537681997892e-005</v>
       </c>
       <c r="H29">
-        <v>2.9226439141461077e-005</v>
+        <v>-4.5832422621657713e-005</v>
       </c>
       <c r="I29">
-        <v>-0.00041765200584125019</v>
+        <v>-0.00042210482007258571</v>
       </c>
       <c r="J29">
-        <v>9.2377939170261024e-005</v>
+        <v>9.647547247255701e-005</v>
       </c>
       <c r="K29">
-        <v>-2.9113537803038123e-006</v>
+        <v>-2.8732484664435439e-006</v>
       </c>
       <c r="L29">
-        <v>6.4647805950724513e-006</v>
+        <v>6.6016585098159036e-006</v>
       </c>
       <c r="M29">
-        <v>-0.0004092463792547585</v>
+        <v>-0.00042839423097991523</v>
       </c>
       <c r="N29">
-        <v>-0.00014471462423606973</v>
+        <v>-0.00017116103272999273</v>
       </c>
       <c r="O29">
-        <v>3.1952607038628804e-005</v>
+        <v>3.3904713489462789e-005</v>
       </c>
       <c r="P29">
-        <v>-0.00039255682369269268</v>
+        <v>-0.00039417420335518486</v>
       </c>
       <c r="Q29">
-        <v>-3.4586438810331466e-007</v>
+        <v>3.0045240861399647e-006</v>
       </c>
       <c r="R29">
-        <v>0.00025550154111116802</v>
+        <v>0.00024517768781199146</v>
       </c>
       <c r="S29">
-        <v>0.00026939854804106252</v>
+        <v>0.00023961861492052187</v>
       </c>
       <c r="T29">
-        <v>0.0018656020279724348</v>
+        <v>0.0018947888768764789</v>
       </c>
       <c r="U29">
-        <v>0.0018157688865110524</v>
+        <v>0.0018425391519079257</v>
       </c>
       <c r="V29">
-        <v>0.0018114675734443419</v>
+        <v>0.0018400084076074031</v>
       </c>
       <c r="W29">
-        <v>0.0017836510721545547</v>
+        <v>0.0018088627614722221</v>
       </c>
       <c r="X29">
-        <v>0.001795683044338814</v>
+        <v>0.0018181112401568825</v>
       </c>
       <c r="Y29">
-        <v>0.0017929563539525173</v>
+        <v>0.0018178637983320726</v>
       </c>
       <c r="Z29">
-        <v>0.0017703464610364351</v>
+        <v>0.0017979494975211999</v>
       </c>
       <c r="AA29">
-        <v>0.0018354046093860194</v>
+        <v>0.001861273649882087</v>
       </c>
       <c r="AB29">
-        <v>0.0018616808306891335</v>
+        <v>0.0018873062607325678</v>
       </c>
       <c r="AC29">
-        <v>0.001876337143648718</v>
+        <v>0.0019041759576593142</v>
       </c>
       <c r="AD29">
-        <v>0.0035807714942849133</v>
+        <v>0.003605997663451899</v>
       </c>
       <c r="AE29">
-        <v>-1.7358114828188379e-005</v>
+        <v>-1.5262850964382466e-005</v>
       </c>
       <c r="AF29">
-        <v>0.00015302074118402301</v>
+        <v>0.00016608850361621644</v>
       </c>
       <c r="AG29">
-        <v>9.2208456892700698e-005</v>
+        <v>0.00010025665674882444</v>
       </c>
       <c r="AH29">
-        <v>0.00070680782461463368</v>
+        <v>0.00072620041035508745</v>
       </c>
       <c r="AI29">
-        <v>0.0013743992593264569</v>
+        <v>0.0013921760322840057</v>
       </c>
       <c r="AJ29">
-        <v>0.00047378159542661421</v>
+        <v>0.00042795409911045436</v>
       </c>
       <c r="AK29">
-        <v>-0.0027995484671990735</v>
+        <v>-0.0030230765190943994</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="77">
-        <v>-0.0071893904830816315</v>
+      <c r="A30" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="79">
+        <v>-0.0074371495959508135</v>
       </c>
       <c r="C30">
-        <v>-8.7936311477617617e-006</v>
+        <v>-8.6059682527599417e-006</v>
       </c>
       <c r="D30">
-        <v>1.3515299766929627e-007</v>
+        <v>1.3319062473676252e-007</v>
       </c>
       <c r="E30">
-        <v>-2.1049117401659752e-005</v>
+        <v>-3.3668288548761541e-005</v>
       </c>
       <c r="F30">
-        <v>1.9933207634746663e-006</v>
+        <v>-6.3925347536226518e-006</v>
       </c>
       <c r="G30">
-        <v>5.6892891628669155e-006</v>
+        <v>-4.1996179066353822e-006</v>
       </c>
       <c r="H30">
-        <v>1.3539029622157029e-005</v>
+        <v>3.5231072201819653e-006</v>
       </c>
       <c r="I30">
-        <v>2.4236909532276144e-005</v>
+        <v>2.3933089838775846e-005</v>
       </c>
       <c r="J30">
-        <v>-5.1627813522477165e-007</v>
+        <v>-2.1929568694516296e-007</v>
       </c>
       <c r="K30">
-        <v>-5.9568507529288476e-008</v>
+        <v>-5.5257296223323854e-008</v>
       </c>
       <c r="L30">
-        <v>3.0020751553538957e-007</v>
+        <v>3.0201020838292793e-007</v>
       </c>
       <c r="M30">
-        <v>3.0897632912271853e-005</v>
+        <v>2.9139114341954626e-005</v>
       </c>
       <c r="N30">
-        <v>-2.6576869677112712e-006</v>
+        <v>-7.2473282395949488e-006</v>
       </c>
       <c r="O30">
-        <v>5.2439245002776466e-006</v>
+        <v>5.3331275515853399e-006</v>
       </c>
       <c r="P30">
-        <v>5.2313071562975962e-005</v>
+        <v>5.190346369726126e-005</v>
       </c>
       <c r="Q30">
-        <v>0.00012724292069795349</v>
+        <v>0.00012753315841933796</v>
       </c>
       <c r="R30">
-        <v>1.7905767390734263e-005</v>
+        <v>1.5735089247312839e-005</v>
       </c>
       <c r="S30">
-        <v>-3.2347818765635918e-006</v>
+        <v>-7.385530554710135e-006</v>
       </c>
       <c r="T30">
-        <v>-3.2826338768359353e-006</v>
+        <v>-1.0960308333664499e-006</v>
       </c>
       <c r="U30">
-        <v>-1.6354938016738217e-005</v>
+        <v>-1.4127198062799433e-005</v>
       </c>
       <c r="V30">
-        <v>-1.8333037804321142e-005</v>
+        <v>-1.6294034805064033e-005</v>
       </c>
       <c r="W30">
-        <v>-2.1236903339443244e-005</v>
+        <v>-1.8984237556438313e-005</v>
       </c>
       <c r="X30">
-        <v>-2.2825684574158671e-005</v>
+        <v>-2.0331518319677782e-005</v>
       </c>
       <c r="Y30">
-        <v>-1.4332158611014779e-005</v>
+        <v>-1.2186120553676022e-005</v>
       </c>
       <c r="Z30">
-        <v>-1.6369865323704454e-005</v>
+        <v>-1.393975370434445e-005</v>
       </c>
       <c r="AA30">
-        <v>-2.3632674842858807e-005</v>
+        <v>-2.147552029614305e-005</v>
       </c>
       <c r="AB30">
-        <v>-1.6719365049067255e-005</v>
+        <v>-1.4746037960283324e-005</v>
       </c>
       <c r="AC30">
-        <v>-1.1388685162989719e-005</v>
+        <v>-9.0549254323836774e-006</v>
       </c>
       <c r="AD30">
-        <v>-1.7358114828188379e-005</v>
+        <v>-1.5262850964382466e-005</v>
       </c>
       <c r="AE30">
-        <v>0.00014942563030085601</v>
+        <v>0.0001495834125167649</v>
       </c>
       <c r="AF30">
-        <v>0.00017651878055012838</v>
+        <v>0.00017762736093405356</v>
       </c>
       <c r="AG30">
-        <v>-5.813507833730882e-005</v>
+        <v>-5.7177203223370476e-005</v>
       </c>
       <c r="AH30">
-        <v>1.0903348815162126e-006</v>
+        <v>2.6756477507364554e-006</v>
       </c>
       <c r="AI30">
-        <v>-1.780721771465002e-005</v>
+        <v>-1.6533147270391194e-005</v>
       </c>
       <c r="AJ30">
-        <v>-8.3665600742678821e-006</v>
+        <v>2.8221470370149229e-006</v>
       </c>
       <c r="AK30">
-        <v>-0.0098662735081831709</v>
+        <v>-0.0098823018671289863</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="79">
-        <v>-0.010332889579837655</v>
+      <c r="B31" s="81">
+        <v>-0.011060819422268038</v>
       </c>
       <c r="C31">
-        <v>1.0415766356827662e-005</v>
+        <v>1.1932872535977776e-005</v>
       </c>
       <c r="D31">
-        <v>-1.0900105749146043e-007</v>
+        <v>-1.2617618647790231e-007</v>
       </c>
       <c r="E31">
-        <v>-8.2288049185899357e-006</v>
+        <v>-8.9320255582502962e-005</v>
       </c>
       <c r="F31">
-        <v>-3.10140743373528e-005</v>
+        <v>-8.5807706341141366e-005</v>
       </c>
       <c r="G31">
-        <v>-5.6977609011841703e-005</v>
+        <v>-0.0001180732408547224</v>
       </c>
       <c r="H31">
-        <v>-6.8633473278342262e-005</v>
+        <v>-0.00013163578989670453</v>
       </c>
       <c r="I31">
-        <v>-7.6492831118559146e-005</v>
+        <v>-7.8694609020375664e-005</v>
       </c>
       <c r="J31">
-        <v>3.4567819673059356e-005</v>
+        <v>3.6937808897486051e-005</v>
       </c>
       <c r="K31">
-        <v>-3.105591053373309e-006</v>
+        <v>-3.036670617204897e-006</v>
       </c>
       <c r="L31">
-        <v>2.0246132198194115e-006</v>
+        <v>2.0437701341261483e-006</v>
       </c>
       <c r="M31">
-        <v>-9.006165070576041e-005</v>
+        <v>-0.00010053950615983419</v>
       </c>
       <c r="N31">
-        <v>-0.00013844704084466425</v>
+        <v>-0.00016142937078099856</v>
       </c>
       <c r="O31">
-        <v>1.5100594620332534e-005</v>
+        <v>1.6086792409349754e-005</v>
       </c>
       <c r="P31">
-        <v>2.179347820880626e-005</v>
+        <v>1.8648849759198325e-005</v>
       </c>
       <c r="Q31">
-        <v>0.00023355225468625314</v>
+        <v>0.00023547464769164508</v>
       </c>
       <c r="R31">
-        <v>9.2526805916892061e-005</v>
+        <v>7.7427562601342347e-005</v>
       </c>
       <c r="S31">
-        <v>6.1990294553049819e-006</v>
+        <v>-1.8613255317940488e-005</v>
       </c>
       <c r="T31">
-        <v>0.00019006017239770614</v>
+        <v>0.00020397282885572734</v>
       </c>
       <c r="U31">
-        <v>0.00020982504902484656</v>
+        <v>0.00022345746361017744</v>
       </c>
       <c r="V31">
-        <v>0.00019071467694401612</v>
+        <v>0.00020498185534884809</v>
       </c>
       <c r="W31">
-        <v>0.00013946821938723363</v>
+        <v>0.00015373950261869611</v>
       </c>
       <c r="X31">
-        <v>0.00011509510320039923</v>
+        <v>0.00013015635478741533</v>
       </c>
       <c r="Y31">
-        <v>0.0001636161773222318</v>
+        <v>0.00017878522665230751</v>
       </c>
       <c r="Z31">
-        <v>0.00016857542627377219</v>
+        <v>0.00018408776664082823</v>
       </c>
       <c r="AA31">
-        <v>0.00020449906577185844</v>
+        <v>0.0002179629368665151</v>
       </c>
       <c r="AB31">
-        <v>0.00015648551275737561</v>
+        <v>0.00017066242418998788</v>
       </c>
       <c r="AC31">
-        <v>0.00012050485922488166</v>
+        <v>0.00013501815023228913</v>
       </c>
       <c r="AD31">
-        <v>0.00015302074118402301</v>
+        <v>0.00016608850361621644</v>
       </c>
       <c r="AE31">
-        <v>0.00017651878055012838</v>
+        <v>0.00017762736093405356</v>
       </c>
       <c r="AF31">
-        <v>0.0031561780590445348</v>
+        <v>0.0031636935262289762</v>
       </c>
       <c r="AG31">
-        <v>0.00061691486345166377</v>
+        <v>0.00062302184560825147</v>
       </c>
       <c r="AH31">
-        <v>3.6409659450713922e-005</v>
+        <v>4.6187971762447905e-005</v>
       </c>
       <c r="AI31">
-        <v>6.7794652487348367e-005</v>
+        <v>7.5138566747302502e-005</v>
       </c>
       <c r="AJ31">
-        <v>5.7286086459462128e-005</v>
+        <v>5.4504728898620639e-005</v>
       </c>
       <c r="AK31">
-        <v>-0.017107405003000998</v>
+        <v>-0.017224385826161238</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="81">
-        <v>-0.022203218663756297</v>
+      <c r="B32" s="83">
+        <v>-0.022326080543990587</v>
       </c>
       <c r="C32">
-        <v>-1.1608866337686893e-005</v>
+        <v>-1.0292717707289828e-005</v>
       </c>
       <c r="D32">
-        <v>1.8204632660434428e-007</v>
+        <v>1.665660822106713e-007</v>
       </c>
       <c r="E32">
-        <v>8.3525313269354275e-005</v>
+        <v>2.0969238543456833e-005</v>
       </c>
       <c r="F32">
-        <v>7.9462211396181788e-005</v>
+        <v>3.6967851904388816e-005</v>
       </c>
       <c r="G32">
-        <v>5.9574767501752943e-005</v>
+        <v>1.2921275226239023e-005</v>
       </c>
       <c r="H32">
-        <v>4.2901421676498218e-005</v>
+        <v>-4.8658050007584642e-006</v>
       </c>
       <c r="I32">
-        <v>-5.8882987507424584e-005</v>
+        <v>-5.9975126837147624e-005</v>
       </c>
       <c r="J32">
-        <v>4.7321963432213704e-005</v>
+        <v>4.9609475304825865e-005</v>
       </c>
       <c r="K32">
-        <v>-2.3814861666024369e-006</v>
+        <v>-2.2954151598843427e-006</v>
       </c>
       <c r="L32">
-        <v>1.1312429316739048e-006</v>
+        <v>1.1797076162841173e-006</v>
       </c>
       <c r="M32">
-        <v>-5.3167199253600396e-005</v>
+        <v>-6.0164509628323458e-005</v>
       </c>
       <c r="N32">
-        <v>0.00010570428873273954</v>
+        <v>8.9853164289118966e-005</v>
       </c>
       <c r="O32">
-        <v>6.8016300809686195e-006</v>
+        <v>7.530740278684602e-006</v>
       </c>
       <c r="P32">
-        <v>-2.2267316008851352e-005</v>
+        <v>-2.4897689481454314e-005</v>
       </c>
       <c r="Q32">
-        <v>2.5107236301245188e-005</v>
+        <v>2.6701879739563167e-005</v>
       </c>
       <c r="R32">
-        <v>0.00011795612906978416</v>
+        <v>0.00010729426752567226</v>
       </c>
       <c r="S32">
-        <v>1.401010500264236e-005</v>
+        <v>-3.8895454012202832e-006</v>
       </c>
       <c r="T32">
-        <v>0.00020784914027257887</v>
+        <v>0.00021699179593734905</v>
       </c>
       <c r="U32">
-        <v>0.00020642165503529156</v>
+        <v>0.00021481725688436579</v>
       </c>
       <c r="V32">
-        <v>0.00011419379174596103</v>
+        <v>0.00012388822449912497</v>
       </c>
       <c r="W32">
-        <v>0.00014311366674692205</v>
+        <v>0.00015249248178149033</v>
       </c>
       <c r="X32">
-        <v>0.00010835356309170077</v>
+        <v>0.00011714479725572128</v>
       </c>
       <c r="Y32">
-        <v>0.00013943919448072202</v>
+        <v>0.0001508843975076467</v>
       </c>
       <c r="Z32">
-        <v>0.00014908645924614428</v>
+        <v>0.00015932669593242399</v>
       </c>
       <c r="AA32">
-        <v>0.00016570860923997702</v>
+        <v>0.00017384561303023047</v>
       </c>
       <c r="AB32">
-        <v>0.00012258240983598103</v>
+        <v>0.0001317668132816891</v>
       </c>
       <c r="AC32">
-        <v>0.00010108886428791937</v>
+        <v>0.00011042957156223037</v>
       </c>
       <c r="AD32">
-        <v>9.2208456892700698e-005</v>
+        <v>0.00010025665674882444</v>
       </c>
       <c r="AE32">
-        <v>-5.813507833730882e-005</v>
+        <v>-5.7177203223370476e-005</v>
       </c>
       <c r="AF32">
-        <v>0.00061691486345166377</v>
+        <v>0.00062302184560825147</v>
       </c>
       <c r="AG32">
-        <v>0.0032149813196771207</v>
+        <v>0.0032210722104436067</v>
       </c>
       <c r="AH32">
-        <v>1.7956581388945574e-005</v>
+        <v>2.4399696714580378e-005</v>
       </c>
       <c r="AI32">
-        <v>6.344087217244836e-005</v>
+        <v>6.6734027717226343e-005</v>
       </c>
       <c r="AJ32">
-        <v>0.00013177394380043989</v>
+        <v>6.8277069601347577e-005</v>
       </c>
       <c r="AK32">
-        <v>-0.00066013890972675194</v>
+        <v>-0.00076429216010857047</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="82" t="s">
+      <c r="A33" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="83">
-        <v>0.0020702119206080908</v>
+      <c r="B33" s="85">
+        <v>-0.000437042433672804</v>
       </c>
       <c r="C33">
-        <v>-1.3072114289094071e-006</v>
+        <v>-5.1060688818251043e-007</v>
       </c>
       <c r="D33">
-        <v>5.1528308438287076e-008</v>
+        <v>4.4660776335722131e-008</v>
       </c>
       <c r="E33">
-        <v>-8.2205090693667843e-005</v>
+        <v>-0.00011657213436648146</v>
       </c>
       <c r="F33">
-        <v>-9.5413829871623707e-005</v>
+        <v>-0.00011781732840372721</v>
       </c>
       <c r="G33">
-        <v>-8.6108678746544263e-005</v>
+        <v>-0.00011326944653736171</v>
       </c>
       <c r="H33">
-        <v>-8.3580561347521183e-005</v>
+        <v>-0.00011149197532905376</v>
       </c>
       <c r="I33">
-        <v>-0.00012359325907742644</v>
+        <v>-0.00012757116019743503</v>
       </c>
       <c r="J33">
-        <v>3.4552707065231591e-005</v>
+        <v>3.7432361840605984e-005</v>
       </c>
       <c r="K33">
-        <v>5.4892087358272623e-007</v>
+        <v>4.8023561125939344e-007</v>
       </c>
       <c r="L33">
-        <v>1.0721830529276193e-007</v>
+        <v>1.8608837218078009e-007</v>
       </c>
       <c r="M33">
-        <v>2.1238325387253629e-005</v>
+        <v>1.0961934459128436e-005</v>
       </c>
       <c r="N33">
-        <v>-5.6467107573215567e-005</v>
+        <v>-7.7079395805772677e-005</v>
       </c>
       <c r="O33">
-        <v>4.3785789263365345e-005</v>
+        <v>4.3909352878767943e-005</v>
       </c>
       <c r="P33">
-        <v>-0.000210968658204217</v>
+        <v>-0.00021096320896999755</v>
       </c>
       <c r="Q33">
-        <v>5.2703318298864127e-006</v>
+        <v>7.7975424394019152e-006</v>
       </c>
       <c r="R33">
-        <v>4.48854828419081e-005</v>
+        <v>5.0173604958135814e-005</v>
       </c>
       <c r="S33">
-        <v>-8.0884866300023612e-005</v>
+        <v>-9.2502985330669652e-005</v>
       </c>
       <c r="T33">
-        <v>0.00066173804903469421</v>
+        <v>0.00068240387508939433</v>
       </c>
       <c r="U33">
-        <v>0.0005702379533463382</v>
+        <v>0.00058923012781002542</v>
       </c>
       <c r="V33">
-        <v>0.00055880182167906067</v>
+        <v>0.00057759266805115653</v>
       </c>
       <c r="W33">
-        <v>0.0005754881675140021</v>
+        <v>0.00059319154313192623</v>
       </c>
       <c r="X33">
-        <v>0.00050078194256549403</v>
+        <v>0.0005179623690327982</v>
       </c>
       <c r="Y33">
-        <v>0.00058880885739011465</v>
+        <v>0.00060575778185541359</v>
       </c>
       <c r="Z33">
-        <v>0.00057888970067817994</v>
+        <v>0.00059784581339784588</v>
       </c>
       <c r="AA33">
-        <v>0.0006638319130754548</v>
+        <v>0.00068184615738556937</v>
       </c>
       <c r="AB33">
-        <v>0.00067252007117182008</v>
+        <v>0.00068925773482373027</v>
       </c>
       <c r="AC33">
-        <v>0.0008122753542342525</v>
+        <v>0.00083120132417694272</v>
       </c>
       <c r="AD33">
-        <v>0.00070680782461463368</v>
+        <v>0.00072620041035508745</v>
       </c>
       <c r="AE33">
-        <v>1.0903348815162126e-006</v>
+        <v>2.6756477507364554e-006</v>
       </c>
       <c r="AF33">
-        <v>3.6409659450713922e-005</v>
+        <v>4.6187971762447905e-005</v>
       </c>
       <c r="AG33">
-        <v>1.7956581388945574e-005</v>
+        <v>2.4399696714580378e-005</v>
       </c>
       <c r="AH33">
-        <v>0.0014695387458915194</v>
+        <v>0.0014803211152053593</v>
       </c>
       <c r="AI33">
-        <v>0.00051505275124917463</v>
+        <v>0.00052927879604812813</v>
       </c>
       <c r="AJ33">
-        <v>0.00030204188959580323</v>
+        <v>0.00025660053032867876</v>
       </c>
       <c r="AK33">
-        <v>-0.00082270069599248315</v>
+        <v>-0.0010051011402436064</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="85">
-        <v>0.15664738447875323</v>
+      <c r="A34" s="86" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="87">
+        <v>0.15578696323780414</v>
       </c>
       <c r="C34">
-        <v>2.0928358473491261e-005</v>
+        <v>2.2355625651086439e-005</v>
       </c>
       <c r="D34">
-        <v>-3.1038289278835962e-007</v>
+        <v>-3.292970296199109e-007</v>
       </c>
       <c r="E34">
-        <v>0.00042795152856352561</v>
+        <v>0.0003683536085575162</v>
       </c>
       <c r="F34">
-        <v>0.00017196777528168957</v>
+        <v>0.00013332305542719709</v>
       </c>
       <c r="G34">
-        <v>0.00014032909672350769</v>
+        <v>9.5934080215322333e-005</v>
       </c>
       <c r="H34">
-        <v>0.00014614193302442337</v>
+        <v>0.00010091153124267525</v>
       </c>
       <c r="I34">
-        <v>-0.00036184801789370286</v>
+        <v>-0.00036665813457522158</v>
       </c>
       <c r="J34">
-        <v>3.8999718047942459e-005</v>
+        <v>4.1762874916501319e-005</v>
       </c>
       <c r="K34">
-        <v>-1.1845251386205844e-006</v>
+        <v>-1.195963566161964e-006</v>
       </c>
       <c r="L34">
-        <v>3.9807921967334434e-006</v>
+        <v>4.1357559168766605e-006</v>
       </c>
       <c r="M34">
-        <v>-0.00050407762248914543</v>
+        <v>-0.00052148213907492842</v>
       </c>
       <c r="N34">
-        <v>-0.00030803117578330833</v>
+        <v>-0.00031703455527711758</v>
       </c>
       <c r="O34">
-        <v>7.1177631839887878e-005</v>
+        <v>7.339127515338024e-005</v>
       </c>
       <c r="P34">
-        <v>-0.00024803788018202795</v>
+        <v>-0.00025215023373669583</v>
       </c>
       <c r="Q34">
-        <v>-9.1861678339156053e-006</v>
+        <v>-7.231045517470773e-006</v>
       </c>
       <c r="R34">
-        <v>3.5313268729460917e-005</v>
+        <v>4.1618340139553019e-005</v>
       </c>
       <c r="S34">
-        <v>0.00021311546416552443</v>
+        <v>0.00019578152751385087</v>
       </c>
       <c r="T34">
-        <v>0.001254136361659529</v>
+        <v>0.0012741523854077528</v>
       </c>
       <c r="U34">
-        <v>0.0012051887540159656</v>
+        <v>0.0012247040817999955</v>
       </c>
       <c r="V34">
-        <v>0.0011732323392096462</v>
+        <v>0.0011933024376243428</v>
       </c>
       <c r="W34">
-        <v>0.0011569371853972436</v>
+        <v>0.0011735846669350398</v>
       </c>
       <c r="X34">
-        <v>0.0011059599220129355</v>
+        <v>0.001120612617944554</v>
       </c>
       <c r="Y34">
-        <v>0.0011752204856926448</v>
+        <v>0.001188414475218227</v>
       </c>
       <c r="Z34">
-        <v>0.001155047544201706</v>
+        <v>0.0011736891301534259</v>
       </c>
       <c r="AA34">
-        <v>0.0012157070478011694</v>
+        <v>0.001232818345633716</v>
       </c>
       <c r="AB34">
-        <v>0.0012613202452815551</v>
+        <v>0.0012776992518579002</v>
       </c>
       <c r="AC34">
-        <v>0.0012576248199146979</v>
+        <v>0.0012765172153347548</v>
       </c>
       <c r="AD34">
-        <v>0.0013743992593264569</v>
+        <v>0.0013921760322840057</v>
       </c>
       <c r="AE34">
-        <v>-1.780721771465002e-005</v>
+        <v>-1.6533147270391194e-005</v>
       </c>
       <c r="AF34">
-        <v>6.7794652487348367e-005</v>
+        <v>7.5138566747302502e-005</v>
       </c>
       <c r="AG34">
-        <v>6.344087217244836e-005</v>
+        <v>6.6734027717226343e-005</v>
       </c>
       <c r="AH34">
-        <v>0.00051505275124917463</v>
+        <v>0.00052927879604812813</v>
       </c>
       <c r="AI34">
-        <v>0.0041939764062224136</v>
+        <v>0.0042006240462271046</v>
       </c>
       <c r="AJ34">
-        <v>0.00043334408633881512</v>
+        <v>0.00040191408566267483</v>
       </c>
       <c r="AK34">
-        <v>-0.00052054140046942868</v>
+        <v>-0.00066007736433383872</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="87">
-        <v>0.087902518596039231</v>
+      <c r="B35" s="89">
+        <v>0.018577391818487422</v>
       </c>
       <c r="C35">
-        <v>-2.776007621904707e-005</v>
+        <v>1.7698070115036192e-006</v>
       </c>
       <c r="D35">
-        <v>4.2726349388245221e-007</v>
+        <v>-3.4196016768595555e-008</v>
       </c>
       <c r="E35">
-        <v>-3.802722896442879e-005</v>
+        <v>2.8989460195837183e-005</v>
       </c>
       <c r="F35">
-        <v>4.6791163064435889e-006</v>
+        <v>4.3981889531712217e-005</v>
       </c>
       <c r="G35">
-        <v>2.2838565004710621e-005</v>
+        <v>1.8933445046519877e-005</v>
       </c>
       <c r="H35">
-        <v>-3.8636630179228069e-005</v>
+        <v>-8.8048062115562878e-006</v>
       </c>
       <c r="I35">
-        <v>-0.0001107964451360084</v>
+        <v>-0.00011027519986757481</v>
       </c>
       <c r="J35">
-        <v>3.9499267879607571e-005</v>
+        <v>2.9474328514025698e-005</v>
       </c>
       <c r="K35">
-        <v>3.1725691106889943e-006</v>
+        <v>4.2129751948823116e-007</v>
       </c>
       <c r="L35">
-        <v>3.5699569583603486e-006</v>
+        <v>3.6332846920207959e-006</v>
       </c>
       <c r="M35">
-        <v>-8.3804812786530828e-005</v>
+        <v>-0.00019222810108840318</v>
       </c>
       <c r="N35">
-        <v>4.9091538534460103e-005</v>
+        <v>1.1544028890433282e-005</v>
       </c>
       <c r="O35">
-        <v>6.9783177758067725e-005</v>
+        <v>4.4647162045910959e-005</v>
       </c>
       <c r="P35">
-        <v>3.1011674530071181e-006</v>
+        <v>-1.7674048167903335e-005</v>
       </c>
       <c r="Q35">
-        <v>-8.8117516300464591e-006</v>
+        <v>5.3524613870844888e-006</v>
       </c>
       <c r="R35">
-        <v>-0.00014448539611163999</v>
+        <v>0.00024145228825121203</v>
       </c>
       <c r="S35">
-        <v>-2.4223925193916896e-005</v>
+        <v>4.010783411214627e-006</v>
       </c>
       <c r="T35">
-        <v>0.00052837369403701433</v>
+        <v>0.0004684374999862972</v>
       </c>
       <c r="U35">
-        <v>0.00045585126002685656</v>
+        <v>0.00040970288915056775</v>
       </c>
       <c r="V35">
-        <v>0.00050702155762189383</v>
+        <v>0.00043355571259124894</v>
       </c>
       <c r="W35">
-        <v>0.00042710839588817325</v>
+        <v>0.00035443174048342165</v>
       </c>
       <c r="X35">
-        <v>0.00037818252868797612</v>
+        <v>0.00032906519880849009</v>
       </c>
       <c r="Y35">
-        <v>0.00041372865763569138</v>
+        <v>0.00030105874531361507</v>
       </c>
       <c r="Z35">
-        <v>0.00041319000819954761</v>
+        <v>0.00036398192802770501</v>
       </c>
       <c r="AA35">
-        <v>0.00050420640819359946</v>
+        <v>0.0004116904226387617</v>
       </c>
       <c r="AB35">
-        <v>0.00059626622817652707</v>
+        <v>0.00044300503276680078</v>
       </c>
       <c r="AC35">
-        <v>0.00047836579722712646</v>
+        <v>0.00041284074789465125</v>
       </c>
       <c r="AD35">
-        <v>0.00047378159542661421</v>
+        <v>0.00042795409911045436</v>
       </c>
       <c r="AE35">
-        <v>-8.3665600742678821e-006</v>
+        <v>2.8221470370149229e-006</v>
       </c>
       <c r="AF35">
-        <v>5.7286086459462128e-005</v>
+        <v>5.4504728898620639e-005</v>
       </c>
       <c r="AG35">
-        <v>0.00013177394380043989</v>
+        <v>6.8277069601347577e-005</v>
       </c>
       <c r="AH35">
-        <v>0.00030204188959580323</v>
+        <v>0.00025660053032867876</v>
       </c>
       <c r="AI35">
-        <v>0.00043334408633881512</v>
+        <v>0.00040191408566267483</v>
       </c>
       <c r="AJ35">
-        <v>0.0071500597174716475</v>
+        <v>0.0039257992213861054</v>
       </c>
       <c r="AK35">
-        <v>0.00034210865999567436</v>
+        <v>-0.00092768406182612746</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="88" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="89">
-        <v>-0.14944539968490445</v>
+      <c r="A36" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="91">
+        <v>-0.14246379461262171</v>
       </c>
       <c r="C36">
-        <v>-0.0059532741018664872</v>
+        <v>-0.0059696826737514631</v>
       </c>
       <c r="D36">
-        <v>8.5410491098072619e-005</v>
+        <v>8.5576793513498584e-005</v>
       </c>
       <c r="E36">
-        <v>0.00051500258042400451</v>
+        <v>0.0019311110132411117</v>
       </c>
       <c r="F36">
-        <v>-0.00080003500904269405</v>
+        <v>0.00013905247835352646</v>
       </c>
       <c r="G36">
-        <v>-0.00034513828480381642</v>
+        <v>0.00072572053918747951</v>
       </c>
       <c r="H36">
-        <v>-0.00078475508484609742</v>
+        <v>0.00030599024200207367</v>
       </c>
       <c r="I36">
-        <v>0.00040416315983542585</v>
+        <v>0.00043000420121531123</v>
       </c>
       <c r="J36">
-        <v>-0.00061220067366104299</v>
+        <v>-0.00064099932613252849</v>
       </c>
       <c r="K36">
-        <v>-5.4423371723098812e-005</v>
+        <v>-5.5431659340447547e-005</v>
       </c>
       <c r="L36">
-        <v>-0.00010473328919973167</v>
+        <v>-0.00010510728737623637</v>
       </c>
       <c r="M36">
-        <v>-0.0032177996112804498</v>
+        <v>-0.0030255448889107178</v>
       </c>
       <c r="N36">
-        <v>0.00042665862936524775</v>
+        <v>0.00083250770490137091</v>
       </c>
       <c r="O36">
-        <v>-0.0014316875681647553</v>
+        <v>-0.0014523214380896695</v>
       </c>
       <c r="P36">
-        <v>-0.0033303275827054053</v>
+        <v>-0.0032912247700982631</v>
       </c>
       <c r="Q36">
-        <v>-0.0090726425427688391</v>
+        <v>-0.0091007820498416516</v>
       </c>
       <c r="R36">
-        <v>-0.0023792009712138634</v>
+        <v>-0.0020904829597113124</v>
       </c>
       <c r="S36">
-        <v>-0.0015550197384527733</v>
+        <v>-0.0011120122780923164</v>
       </c>
       <c r="T36">
-        <v>-0.003698278484101395</v>
+        <v>-0.0039328911689454037</v>
       </c>
       <c r="U36">
-        <v>-0.0025112449349569718</v>
+        <v>-0.0027436139170862036</v>
       </c>
       <c r="V36">
-        <v>-0.0028602589662405052</v>
+        <v>-0.0030879490007732179</v>
       </c>
       <c r="W36">
-        <v>-0.0025426709236660277</v>
+        <v>-0.0027805617835765053</v>
       </c>
       <c r="X36">
-        <v>-0.0025148309386554594</v>
+        <v>-0.0027608366271446435</v>
       </c>
       <c r="Y36">
-        <v>-0.0021346664917624926</v>
+        <v>-0.0023653299709732027</v>
       </c>
       <c r="Z36">
-        <v>-0.0023766259336560997</v>
+        <v>-0.0026339830670702234</v>
       </c>
       <c r="AA36">
-        <v>-0.0023718124574974896</v>
+        <v>-0.0026018760636531274</v>
       </c>
       <c r="AB36">
-        <v>-0.0028292036188642304</v>
+        <v>-0.0030608948677150662</v>
       </c>
       <c r="AC36">
-        <v>-0.0024577381531434425</v>
+        <v>-0.0027172454933257462</v>
       </c>
       <c r="AD36">
-        <v>-0.0027995484671990735</v>
+        <v>-0.0030230765190943994</v>
       </c>
       <c r="AE36">
-        <v>-0.0098662735081831709</v>
+        <v>-0.0098823018671289863</v>
       </c>
       <c r="AF36">
-        <v>-0.017107405003000998</v>
+        <v>-0.017224385826161238</v>
       </c>
       <c r="AG36">
-        <v>-0.00066013890972675194</v>
+        <v>-0.00076429216010857047</v>
       </c>
       <c r="AH36">
-        <v>-0.00082270069599248315</v>
+        <v>-0.0010051011402436064</v>
       </c>
       <c r="AI36">
-        <v>-0.00052054140046942868</v>
+        <v>-0.00066007736433383872</v>
       </c>
       <c r="AJ36">
-        <v>0.00034210865999567436</v>
+        <v>-0.00092768406182612746</v>
       </c>
       <c r="AK36">
-        <v>0.81163402861127909</v>
+        <v>0.81312588808031827</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -8,8 +8,8 @@
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId2"/>
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
-    <sheet name="F1a" sheetId="3" r:id="rId5"/>
-    <sheet name="F1b" sheetId="4" r:id="rId6"/>
+    <sheet name="UK_F1a" sheetId="3" r:id="rId5"/>
+    <sheet name="UK_F1b" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/initial_populations/regression_estimates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9BF724-3C72-B745-8EB6-6A5910E3BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B638B6-53EC-5B4D-969D-882AA0921B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_F1" sheetId="3" r:id="rId3"/>
+    <sheet name="F1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
   <si>
     <t>Description:</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
   </si>
   <si>
-    <t>Last edit: 19 Jan 2026 DP</t>
+    <t>Last edit: 4 Feb 2026 DP</t>
   </si>
   <si>
     <t>Process:</t>
@@ -87,9 +87,6 @@
     <t>Dcpst_Single_L1</t>
   </si>
   <si>
-    <t>Ded_Dag</t>
-  </si>
-  <si>
     <t>Ded_Dcpst_Single</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>U1- Partnership formation</t>
@@ -703,35 +697,35 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5">
+        <v>0.16592863975101757</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="B5">
-        <v>0.16611412116958635</v>
-      </c>
-      <c r="E5" t="s">
-        <v>55</v>
-      </c>
       <c r="F5">
-        <v>2065.770042273748</v>
+        <v>2045.0751416788082</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>83131</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6">
-        <v>-8408262.9031905904</v>
+        <v>-8410133.1549487449</v>
       </c>
     </row>
   </sheetData>
@@ -741,10 +735,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AL37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -859,4414 +853,4181 @@
       <c r="AL1" t="s">
         <v>49</v>
       </c>
-      <c r="AM1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>3.3891877277074154</v>
+        <v>-0.53796323096326759</v>
       </c>
       <c r="C2">
-        <v>5.7428659700862328</v>
+        <v>0.2037131803207434</v>
       </c>
       <c r="D2">
-        <v>2.8430375526637477E-3</v>
+        <v>-8.8706111496228727E-5</v>
       </c>
       <c r="E2">
-        <v>-4.1025819672764404E-5</v>
+        <v>1.587818517172757E-6</v>
       </c>
       <c r="F2">
-        <v>1.8195761936229949E-4</v>
+        <v>1.2197673310279661E-5</v>
       </c>
       <c r="G2">
-        <v>1.0654877124420217E-4</v>
+        <v>1.6717971708708962E-5</v>
       </c>
       <c r="H2">
-        <v>1.7371588069019922E-3</v>
+        <v>-1.0821798374013544E-4</v>
       </c>
       <c r="I2">
-        <v>-1.4974048846856242E-3</v>
+        <v>1.6839283846075302E-3</v>
       </c>
       <c r="J2">
-        <v>-0.24590499236674482</v>
+        <v>-0.20313124239577762</v>
       </c>
       <c r="K2">
-        <v>-1.009680367844866</v>
+        <v>-5.3472086254740918E-5</v>
       </c>
       <c r="L2">
-        <v>-3.2934950844818699E-3</v>
+        <v>1.1058824094478505E-3</v>
       </c>
       <c r="M2">
-        <v>-3.2220216797649859E-3</v>
+        <v>1.6587215951037585E-3</v>
       </c>
       <c r="N2">
-        <v>-3.9969364442649195E-3</v>
+        <v>2.1441034239617096E-3</v>
       </c>
       <c r="O2">
-        <v>-4.7979532253217983E-3</v>
+        <v>3.6131410017203576E-4</v>
       </c>
       <c r="P2">
-        <v>-1.0308436604906934E-3</v>
+        <v>4.9868144323422412E-5</v>
       </c>
       <c r="Q2">
-        <v>-2.8379606597901804E-4</v>
+        <v>5.21829155557328E-4</v>
       </c>
       <c r="R2">
-        <v>-1.0313133809074851E-3</v>
+        <v>3.198405765240627E-4</v>
       </c>
       <c r="S2">
-        <v>1.5801831734942387E-4</v>
+        <v>-9.7798575979757556E-5</v>
       </c>
       <c r="T2">
-        <v>4.2656410393490315E-6</v>
+        <v>8.7018067734567208E-4</v>
       </c>
       <c r="U2">
-        <v>2.6953536944015945E-4</v>
+        <v>-9.3771685483352678E-4</v>
       </c>
       <c r="V2">
-        <v>1.902844531420186E-3</v>
+        <v>-1.2249971090131685E-6</v>
       </c>
       <c r="W2">
-        <v>-4.2078968384531845E-4</v>
+        <v>2.8817523859004485E-4</v>
       </c>
       <c r="X2">
-        <v>3.1282729485081831E-3</v>
+        <v>2.2170416128040903E-4</v>
       </c>
       <c r="Y2">
-        <v>1.0127885788091227E-3</v>
+        <v>1.102008510883299E-3</v>
       </c>
       <c r="Z2">
-        <v>4.6484011538466055E-3</v>
+        <v>6.0860812483458197E-4</v>
       </c>
       <c r="AA2">
-        <v>7.6515203382841734E-4</v>
+        <v>-1.0433591577804367E-4</v>
       </c>
       <c r="AB2">
-        <v>8.5970609113847005E-4</v>
+        <v>1.7390887743631259E-4</v>
       </c>
       <c r="AC2">
-        <v>1.6633114158268476E-3</v>
+        <v>4.2150156616949704E-4</v>
       </c>
       <c r="AD2">
-        <v>1.4579493041662131E-3</v>
+        <v>-2.7034115967591171E-4</v>
       </c>
       <c r="AE2">
-        <v>2.6805228191602824E-4</v>
+        <v>1.9941830197874651E-4</v>
       </c>
       <c r="AF2">
-        <v>1.6340122481109526E-3</v>
+        <v>-5.5087533906595932E-5</v>
       </c>
       <c r="AG2">
-        <v>-1.8588424642770971E-5</v>
+        <v>-5.4266938444234077E-4</v>
       </c>
       <c r="AH2">
-        <v>1.526900466354647E-3</v>
+        <v>-2.6054599559575302E-4</v>
       </c>
       <c r="AI2">
-        <v>5.2433031058840562E-4</v>
+        <v>-3.4036150800639212E-5</v>
       </c>
       <c r="AJ2">
-        <v>4.5757463701508877E-4</v>
+        <v>-5.795593808838144E-4</v>
       </c>
       <c r="AK2">
-        <v>7.0318078897457781E-5</v>
+        <v>8.6041579915096394E-4</v>
       </c>
       <c r="AL2">
-        <v>-2.354544002412251E-3</v>
-      </c>
-      <c r="AM2">
-        <v>-5.9057954073663155E-2</v>
+        <v>3.5975548240729585E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.32882934912100437</v>
+        <v>0.32669413703652667</v>
       </c>
       <c r="C3">
-        <v>2.8430375526637477E-3</v>
+        <v>-8.8706111496228727E-5</v>
       </c>
       <c r="D3">
-        <v>2.8971188225431291E-4</v>
+        <v>2.8630805500525945E-4</v>
       </c>
       <c r="E3">
-        <v>-4.3473820502278451E-6</v>
+        <v>-4.295645383776935E-6</v>
       </c>
       <c r="F3">
-        <v>3.2655480730078559E-6</v>
+        <v>3.1636684843346258E-6</v>
       </c>
       <c r="G3">
-        <v>1.8024274174160225E-6</v>
+        <v>1.7390142196271117E-6</v>
       </c>
       <c r="H3">
-        <v>2.8051851667651624E-5</v>
+        <v>3.0860383590532994E-5</v>
       </c>
       <c r="I3">
-        <v>8.3403197191311146E-5</v>
+        <v>8.0973234294992938E-5</v>
       </c>
       <c r="J3">
-        <v>-1.1487846491855603E-4</v>
+        <v>3.9133767276214098E-4</v>
       </c>
       <c r="K3">
-        <v>-1.0004115507826743E-4</v>
+        <v>4.4193640925057779E-5</v>
       </c>
       <c r="L3">
-        <v>4.313586585278037E-5</v>
+        <v>2.6178521736590419E-5</v>
       </c>
       <c r="M3">
-        <v>2.5651970561933247E-5</v>
+        <v>1.9094234857100229E-5</v>
       </c>
       <c r="N3">
-        <v>1.8712976673758951E-5</v>
+        <v>-4.9265798130001485E-5</v>
       </c>
       <c r="O3">
-        <v>-4.9942707230527373E-5</v>
+        <v>-4.2917521765438102E-5</v>
       </c>
       <c r="P3">
-        <v>-4.3488754409715634E-5</v>
+        <v>-7.1704212273286503E-5</v>
       </c>
       <c r="Q3">
-        <v>-7.2227827407686648E-5</v>
+        <v>-3.9815448280479046E-5</v>
       </c>
       <c r="R3">
-        <v>-4.0752767855529613E-5</v>
+        <v>-1.5826027182835878E-5</v>
       </c>
       <c r="S3">
-        <v>-1.601388897922904E-5</v>
+        <v>-9.4091939085051831E-6</v>
       </c>
       <c r="T3">
-        <v>-9.5665726314243978E-6</v>
+        <v>4.8811480853869313E-5</v>
       </c>
       <c r="U3">
-        <v>4.9679579812241252E-5</v>
+        <v>9.0282821865002568E-5</v>
       </c>
       <c r="V3">
-        <v>9.2846445292611105E-5</v>
+        <v>9.5109976528795666E-5</v>
       </c>
       <c r="W3">
-        <v>9.6049839352782768E-5</v>
+        <v>1.4294321974072071E-4</v>
       </c>
       <c r="X3">
-        <v>1.4738893742711622E-4</v>
+        <v>1.4957952847651922E-4</v>
       </c>
       <c r="Y3">
-        <v>1.5154543250395377E-4</v>
+        <v>1.522214887798481E-4</v>
       </c>
       <c r="Z3">
-        <v>1.5668875697035867E-4</v>
+        <v>2.3001583499728407E-4</v>
       </c>
       <c r="AA3">
-        <v>2.3127474920511294E-4</v>
+        <v>1.5017107308375248E-4</v>
       </c>
       <c r="AB3">
-        <v>1.5183862144004716E-4</v>
+        <v>1.5722206879967976E-4</v>
       </c>
       <c r="AC3">
-        <v>1.5924702969909491E-4</v>
+        <v>1.8376037510583706E-4</v>
       </c>
       <c r="AD3">
-        <v>1.8599681349886019E-4</v>
+        <v>1.335043261163157E-4</v>
       </c>
       <c r="AE3">
-        <v>1.3442669690943792E-4</v>
+        <v>1.4214788020234939E-4</v>
       </c>
       <c r="AF3">
-        <v>1.4445110178947559E-4</v>
+        <v>-6.627241824443597E-6</v>
       </c>
       <c r="AG3">
-        <v>-6.7745358203226001E-6</v>
+        <v>-2.5662582464044525E-5</v>
       </c>
       <c r="AH3">
-        <v>-2.5255405409989069E-5</v>
+        <v>-6.7884408203983029E-5</v>
       </c>
       <c r="AI3">
-        <v>-6.8094011122727185E-5</v>
+        <v>1.2123410514249498E-6</v>
       </c>
       <c r="AJ3">
-        <v>1.8209891327113179E-6</v>
+        <v>2.7211542649549069E-5</v>
       </c>
       <c r="AK3">
-        <v>2.9273090688445485E-5</v>
+        <v>3.1753927664675968E-4</v>
       </c>
       <c r="AL3">
-        <v>3.1587034497676872E-4</v>
-      </c>
-      <c r="AM3">
-        <v>-4.3301688558954506E-3</v>
+        <v>-4.2778071679641545E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>-5.73267509160177E-3</v>
+        <v>-5.7015161666606889E-3</v>
       </c>
       <c r="C4">
-        <v>-4.1025819672764404E-5</v>
+        <v>1.587818517172757E-6</v>
       </c>
       <c r="D4">
-        <v>-4.3473820502278451E-6</v>
+        <v>-4.295645383776935E-6</v>
       </c>
       <c r="E4">
-        <v>6.638566285998354E-8</v>
+        <v>6.5594883221164801E-8</v>
       </c>
       <c r="F4">
-        <v>-4.9333998575850296E-8</v>
+        <v>-4.7800150736462066E-8</v>
       </c>
       <c r="G4">
-        <v>-3.163660985979627E-8</v>
+        <v>-3.0681067323285331E-8</v>
       </c>
       <c r="H4">
-        <v>-6.1078475626561546E-7</v>
+        <v>-6.4970318663729596E-7</v>
       </c>
       <c r="I4">
-        <v>-7.8741549794212771E-7</v>
+        <v>-7.533267469054294E-7</v>
       </c>
       <c r="J4">
-        <v>1.6657381860583655E-6</v>
+        <v>-5.791640183632728E-6</v>
       </c>
       <c r="K4">
-        <v>1.4459255834453345E-6</v>
+        <v>-5.8679367113113092E-7</v>
       </c>
       <c r="L4">
-        <v>-5.7069261333213611E-7</v>
+        <v>-3.4023275094416237E-7</v>
       </c>
       <c r="M4">
-        <v>-3.3179849833708459E-7</v>
+        <v>-4.0604385613422154E-7</v>
       </c>
       <c r="N4">
-        <v>-3.9982333836255607E-7</v>
+        <v>6.209178716875955E-7</v>
       </c>
       <c r="O4">
-        <v>6.329474301583831E-7</v>
+        <v>4.3816734219150208E-7</v>
       </c>
       <c r="P4">
-        <v>4.463964944142752E-7</v>
+        <v>1.3733802613425309E-6</v>
       </c>
       <c r="Q4">
-        <v>1.3816280457868595E-6</v>
+        <v>4.6098207380215883E-7</v>
       </c>
       <c r="R4">
-        <v>4.7490509954614934E-7</v>
+        <v>2.4303483718978122E-7</v>
       </c>
       <c r="S4">
-        <v>2.4584522258767164E-7</v>
+        <v>1.660502179178264E-7</v>
       </c>
       <c r="T4">
-        <v>1.6843708670330163E-7</v>
+        <v>-7.7459425747652971E-7</v>
       </c>
       <c r="U4">
-        <v>-7.8718745398372455E-7</v>
+        <v>-1.5281358212027645E-6</v>
       </c>
       <c r="V4">
-        <v>-1.5673812507264997E-6</v>
+        <v>-1.4971063571341248E-6</v>
       </c>
       <c r="W4">
-        <v>-1.511570356076153E-6</v>
+        <v>-2.1694465893661048E-6</v>
       </c>
       <c r="X4">
-        <v>-2.2350821803436185E-6</v>
+        <v>-2.3550439380312498E-6</v>
       </c>
       <c r="Y4">
-        <v>-2.384910570128792E-6</v>
+        <v>-2.3108283910585996E-6</v>
       </c>
       <c r="Z4">
-        <v>-2.3770173722359006E-6</v>
+        <v>-3.6840682382367713E-6</v>
       </c>
       <c r="AA4">
-        <v>-3.7045828273597422E-6</v>
+        <v>-2.2770008120483541E-6</v>
       </c>
       <c r="AB4">
-        <v>-2.3021296811079331E-6</v>
+        <v>-2.4242600517062153E-6</v>
       </c>
       <c r="AC4">
-        <v>-2.455036524541244E-6</v>
+        <v>-2.8065650005086082E-6</v>
       </c>
       <c r="AD4">
-        <v>-2.8403958278397198E-6</v>
+        <v>-2.2153366493178161E-6</v>
       </c>
       <c r="AE4">
-        <v>-2.2302504149478929E-6</v>
+        <v>-2.2092940597415485E-6</v>
       </c>
       <c r="AF4">
-        <v>-2.2438022117473127E-6</v>
+        <v>1.125576341391809E-7</v>
       </c>
       <c r="AG4">
-        <v>1.1477048420761987E-7</v>
+        <v>3.9423953209857961E-7</v>
       </c>
       <c r="AH4">
-        <v>3.8815368504298053E-7</v>
+        <v>1.0450571790468241E-6</v>
       </c>
       <c r="AI4">
-        <v>1.0480362153388137E-6</v>
+        <v>-9.1765557274399722E-8</v>
       </c>
       <c r="AJ4">
-        <v>-1.0156151694862159E-7</v>
+        <v>-6.6017190506680813E-7</v>
       </c>
       <c r="AK4">
-        <v>-6.9092731330447436E-7</v>
+        <v>-5.1064220481602564E-6</v>
       </c>
       <c r="AL4">
-        <v>-5.0858354861719958E-6</v>
-      </c>
-      <c r="AM4">
-        <v>6.2514667328430475E-5</v>
+        <v>6.1724566152687862E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5">
-        <v>7.1700700480162912E-4</v>
+        <v>6.9214561864257317E-4</v>
       </c>
       <c r="C5">
-        <v>1.8195761936229949E-4</v>
+        <v>1.2197673310279661E-5</v>
       </c>
       <c r="D5">
-        <v>3.2655480730078559E-6</v>
+        <v>3.1636684843346258E-6</v>
       </c>
       <c r="E5">
-        <v>-4.9333998575850296E-8</v>
+        <v>-4.7800150736462066E-8</v>
       </c>
       <c r="F5">
-        <v>2.1850622546413282E-6</v>
+        <v>2.1800161625785831E-6</v>
       </c>
       <c r="G5">
-        <v>2.305030214136837E-7</v>
+        <v>2.2893200447315344E-7</v>
       </c>
       <c r="H5">
-        <v>1.9086755228647479E-5</v>
+        <v>1.8860386736401691E-5</v>
       </c>
       <c r="I5">
-        <v>-2.709264597897519E-5</v>
+        <v>-2.6830807515202152E-5</v>
       </c>
       <c r="J5">
-        <v>-7.6878014922692627E-6</v>
+        <v>-1.4400337112006453E-5</v>
       </c>
       <c r="K5">
-        <v>-3.2087901730103773E-5</v>
+        <v>-2.2755861833452517E-6</v>
       </c>
       <c r="L5">
-        <v>-2.370361699935671E-6</v>
+        <v>-7.7980045907026575E-6</v>
       </c>
       <c r="M5">
-        <v>-7.9006944671719527E-6</v>
+        <v>-8.3777002382156356E-6</v>
       </c>
       <c r="N5">
-        <v>-8.5144845496151197E-6</v>
+        <v>-1.6749605364795359E-5</v>
       </c>
       <c r="O5">
-        <v>-1.6933588477824296E-5</v>
+        <v>-1.8904132894317648E-6</v>
       </c>
       <c r="P5">
-        <v>-1.9178952823783877E-6</v>
+        <v>-2.5649215771245024E-6</v>
       </c>
       <c r="Q5">
-        <v>-2.5763689310145097E-6</v>
+        <v>-9.294914511612545E-7</v>
       </c>
       <c r="R5">
-        <v>-9.5108498448200478E-7</v>
+        <v>-2.189508657971858E-7</v>
       </c>
       <c r="S5">
-        <v>-2.2125336040080848E-7</v>
+        <v>2.0532801182330886E-7</v>
       </c>
       <c r="T5">
-        <v>2.1337060960061491E-7</v>
+        <v>8.7580721727992496E-6</v>
       </c>
       <c r="U5">
-        <v>8.7531560742377867E-6</v>
+        <v>-8.7372087316935154E-7</v>
       </c>
       <c r="V5">
-        <v>-7.7375097741167755E-7</v>
+        <v>4.181324953945367E-6</v>
       </c>
       <c r="W5">
-        <v>4.1770817867399214E-6</v>
+        <v>2.477874233379201E-6</v>
       </c>
       <c r="X5">
-        <v>2.5002417636121492E-6</v>
+        <v>3.7111969354215519E-6</v>
       </c>
       <c r="Y5">
-        <v>3.7321480385991278E-6</v>
+        <v>3.5188522756026945E-6</v>
       </c>
       <c r="Z5">
-        <v>3.5364610955665252E-6</v>
+        <v>8.1608263439468179E-6</v>
       </c>
       <c r="AA5">
-        <v>8.1712250969380375E-6</v>
+        <v>-2.5072124823440873E-6</v>
       </c>
       <c r="AB5">
-        <v>-2.5047098233279031E-6</v>
+        <v>3.1383821790104906E-6</v>
       </c>
       <c r="AC5">
-        <v>3.1565156439593024E-6</v>
+        <v>-1.5082257809676658E-7</v>
       </c>
       <c r="AD5">
-        <v>-1.4512099916266097E-7</v>
+        <v>8.4135725862100867E-6</v>
       </c>
       <c r="AE5">
-        <v>8.4250935180472301E-6</v>
+        <v>4.5557602338793885E-6</v>
       </c>
       <c r="AF5">
-        <v>4.5636351790956169E-6</v>
+        <v>2.6307540363029871E-7</v>
       </c>
       <c r="AG5">
-        <v>2.6919958101006399E-7</v>
+        <v>-1.4250298976970779E-7</v>
       </c>
       <c r="AH5">
-        <v>-5.9411153854297023E-8</v>
+        <v>2.7026241282417936E-7</v>
       </c>
       <c r="AI5">
-        <v>2.9236041198898679E-7</v>
+        <v>1.8583050614183141E-6</v>
       </c>
       <c r="AJ5">
-        <v>1.8722911652971187E-6</v>
+        <v>-1.5538661958960803E-6</v>
       </c>
       <c r="AK5">
-        <v>-1.5507415205681441E-6</v>
+        <v>2.044904156808748E-5</v>
       </c>
       <c r="AL5">
-        <v>2.043146148007557E-5</v>
-      </c>
-      <c r="AM5">
-        <v>-1.8728411507836488E-4</v>
+        <v>-1.8487586117047882E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6">
-        <v>6.9858686026353124E-3</v>
+        <v>6.9699577170463578E-3</v>
       </c>
       <c r="C6">
-        <v>1.0654877124420217E-4</v>
+        <v>1.6717971708708962E-5</v>
       </c>
       <c r="D6">
-        <v>1.8024274174160225E-6</v>
+        <v>1.7390142196271117E-6</v>
       </c>
       <c r="E6">
-        <v>-3.163660985979627E-8</v>
+        <v>-3.0681067323285331E-8</v>
       </c>
       <c r="F6">
-        <v>2.305030214136837E-7</v>
+        <v>2.2893200447315344E-7</v>
       </c>
       <c r="G6">
-        <v>1.5213246279844175E-6</v>
+        <v>1.5198810074948115E-6</v>
       </c>
       <c r="H6">
-        <v>1.2740150995503596E-5</v>
+        <v>1.263190212790235E-5</v>
       </c>
       <c r="I6">
-        <v>-1.0489393279001088E-5</v>
+        <v>-1.0372308528914312E-5</v>
       </c>
       <c r="J6">
-        <v>-4.0637755015045232E-6</v>
+        <v>-2.0368050846801811E-5</v>
       </c>
       <c r="K6">
-        <v>-2.9921112581116135E-5</v>
+        <v>-3.9679400939363426E-6</v>
       </c>
       <c r="L6">
-        <v>-4.0212965815500896E-6</v>
+        <v>-1.9133767547301233E-6</v>
       </c>
       <c r="M6">
-        <v>-1.9710932441711321E-6</v>
+        <v>3.2259477344254134E-7</v>
       </c>
       <c r="N6">
-        <v>2.5350236337953893E-7</v>
+        <v>-6.4859836447984063E-6</v>
       </c>
       <c r="O6">
-        <v>-6.5925254357502459E-6</v>
+        <v>-2.5792579274637747E-6</v>
       </c>
       <c r="P6">
-        <v>-2.593464632782862E-6</v>
+        <v>-1.8247166667789016E-6</v>
       </c>
       <c r="Q6">
-        <v>-1.8358681525502474E-6</v>
+        <v>1.354243317468754E-6</v>
       </c>
       <c r="R6">
-        <v>1.3338280719361575E-6</v>
+        <v>1.9169267527975398E-6</v>
       </c>
       <c r="S6">
-        <v>1.9155909160501117E-6</v>
+        <v>-6.5391601548419619E-7</v>
       </c>
       <c r="T6">
-        <v>-6.4546132997340329E-7</v>
+        <v>5.2282006539827995E-6</v>
       </c>
       <c r="U6">
-        <v>5.217889629269265E-6</v>
+        <v>8.9701525568045006E-7</v>
       </c>
       <c r="V6">
-        <v>1.013517422249263E-6</v>
+        <v>1.4325232378887304E-6</v>
       </c>
       <c r="W6">
-        <v>1.4319133921986429E-6</v>
+        <v>4.0825252324169498E-6</v>
       </c>
       <c r="X6">
-        <v>4.1110386517951639E-6</v>
+        <v>-3.9216534051962537E-7</v>
       </c>
       <c r="Y6">
-        <v>-3.7193613904528546E-7</v>
+        <v>1.8264595018545865E-6</v>
       </c>
       <c r="Z6">
-        <v>1.8351626077604833E-6</v>
+        <v>9.7814839245484843E-6</v>
       </c>
       <c r="AA6">
-        <v>9.7908763369184703E-6</v>
+        <v>-9.8207946639996487E-7</v>
       </c>
       <c r="AB6">
-        <v>-9.6728675311149723E-7</v>
+        <v>2.8110374706222935E-6</v>
       </c>
       <c r="AC6">
-        <v>2.8429218507974838E-6</v>
+        <v>8.9143827766621967E-7</v>
       </c>
       <c r="AD6">
-        <v>8.936371113085172E-7</v>
+        <v>2.5059132272244864E-6</v>
       </c>
       <c r="AE6">
-        <v>2.5085102510469983E-6</v>
+        <v>2.4899657047775339E-7</v>
       </c>
       <c r="AF6">
-        <v>2.5768710126616379E-7</v>
+        <v>1.19647761857E-7</v>
       </c>
       <c r="AG6">
-        <v>1.2728581543088008E-7</v>
+        <v>-2.7611536818197686E-6</v>
       </c>
       <c r="AH6">
-        <v>-2.7242544039286854E-6</v>
+        <v>-8.996655002017292E-7</v>
       </c>
       <c r="AI6">
-        <v>-8.9336395582200948E-7</v>
+        <v>2.3963270115475561E-7</v>
       </c>
       <c r="AJ6">
-        <v>2.6254807640354507E-7</v>
+        <v>8.678896353062189E-7</v>
       </c>
       <c r="AK6">
-        <v>9.5399052212621704E-7</v>
+        <v>4.0959581037196572E-5</v>
       </c>
       <c r="AL6">
-        <v>4.0983080922545707E-5</v>
-      </c>
-      <c r="AM6">
-        <v>-6.9981964169605395E-5</v>
+        <v>-6.8259709134607031E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-0.72332276646380522</v>
+        <v>-0.72500260255812055</v>
       </c>
       <c r="C7">
-        <v>1.7371588069019922E-3</v>
+        <v>-1.0821798374013544E-4</v>
       </c>
       <c r="D7">
-        <v>2.8051851667651624E-5</v>
+        <v>3.0860383590532994E-5</v>
       </c>
       <c r="E7">
-        <v>-6.1078475626561546E-7</v>
+        <v>-6.4970318663729596E-7</v>
       </c>
       <c r="F7">
-        <v>1.9086755228647479E-5</v>
+        <v>1.8860386736401691E-5</v>
       </c>
       <c r="G7">
-        <v>1.2740150995503596E-5</v>
+        <v>1.263190212790235E-5</v>
       </c>
       <c r="H7">
-        <v>7.1824614244813574E-3</v>
+        <v>7.1803861705628039E-3</v>
       </c>
       <c r="I7">
-        <v>-6.5430926911042783E-3</v>
+        <v>-6.5434480290226735E-3</v>
       </c>
       <c r="J7">
-        <v>-1.873336330043961E-5</v>
+        <v>-3.5963656972863562E-4</v>
       </c>
       <c r="K7">
-        <v>-1.8347383377681178E-3</v>
+        <v>-9.9424917717905523E-5</v>
       </c>
       <c r="L7">
-        <v>-1.019859183580371E-4</v>
+        <v>-5.0687743142570468E-5</v>
       </c>
       <c r="M7">
-        <v>-4.7204094381652746E-5</v>
+        <v>-4.7837519547153464E-5</v>
       </c>
       <c r="N7">
-        <v>-4.2323974636531889E-5</v>
+        <v>-3.8937589848764547E-4</v>
       </c>
       <c r="O7">
-        <v>-3.8116579723124981E-4</v>
+        <v>1.1626008913003185E-4</v>
       </c>
       <c r="P7">
-        <v>1.1807056301598346E-4</v>
+        <v>-1.3889471390744621E-4</v>
       </c>
       <c r="Q7">
-        <v>-1.3919996866717859E-4</v>
+        <v>1.6172270616711241E-4</v>
       </c>
       <c r="R7">
-        <v>1.6334330157498573E-4</v>
+        <v>5.6625980918611986E-4</v>
       </c>
       <c r="S7">
-        <v>5.6675040727305641E-4</v>
+        <v>4.8251024376459147E-5</v>
       </c>
       <c r="T7">
-        <v>4.7770583733820942E-5</v>
+        <v>5.6545934320001089E-5</v>
       </c>
       <c r="U7">
-        <v>6.0254852596545118E-5</v>
+        <v>-1.010516146360531E-4</v>
       </c>
       <c r="V7">
-        <v>-1.061442103106992E-4</v>
+        <v>5.7443240310345921E-5</v>
       </c>
       <c r="W7">
-        <v>5.6004368058395029E-5</v>
+        <v>5.1214806810342197E-5</v>
       </c>
       <c r="X7">
-        <v>5.1786596857600319E-5</v>
+        <v>1.3098028467256766E-5</v>
       </c>
       <c r="Y7">
-        <v>1.4192249953443484E-5</v>
+        <v>-8.8017565309023925E-5</v>
       </c>
       <c r="Z7">
-        <v>-8.0610294619450746E-5</v>
+        <v>5.1332756511115497E-4</v>
       </c>
       <c r="AA7">
-        <v>5.1362445921747293E-4</v>
+        <v>-4.3541339373581928E-4</v>
       </c>
       <c r="AB7">
-        <v>-4.3773600020082393E-4</v>
+        <v>2.4053366854456625E-5</v>
       </c>
       <c r="AC7">
-        <v>2.4277393921594384E-5</v>
+        <v>7.8760472681513923E-5</v>
       </c>
       <c r="AD7">
-        <v>7.8435055300698567E-5</v>
+        <v>-7.8337378463319844E-4</v>
       </c>
       <c r="AE7">
-        <v>-7.8578512940038364E-4</v>
+        <v>-1.501064405323906E-4</v>
       </c>
       <c r="AF7">
-        <v>-1.5033826445145132E-4</v>
+        <v>2.9605991981905542E-5</v>
       </c>
       <c r="AG7">
-        <v>2.9231398664304106E-5</v>
+        <v>2.0153011783269695E-5</v>
       </c>
       <c r="AH7">
-        <v>1.9837451700222019E-5</v>
+        <v>2.1486612238934903E-4</v>
       </c>
       <c r="AI7">
-        <v>2.1497233697535754E-4</v>
+        <v>-7.833305216560953E-5</v>
       </c>
       <c r="AJ7">
-        <v>-7.80196043041001E-5</v>
+        <v>-2.4769017433527534E-4</v>
       </c>
       <c r="AK7">
-        <v>-2.5805556921137826E-4</v>
+        <v>2.5927400724313761E-4</v>
       </c>
       <c r="AL7">
-        <v>2.5515114068565541E-4</v>
-      </c>
-      <c r="AM7">
-        <v>-5.3507102676044376E-3</v>
+        <v>-5.4078637720599461E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8">
-        <v>6.9521307546236491E-2</v>
+        <v>7.1764267541261972E-2</v>
       </c>
       <c r="C8">
-        <v>-1.4974048846856242E-3</v>
+        <v>1.6839283846075302E-3</v>
       </c>
       <c r="D8">
-        <v>8.3403197191311146E-5</v>
+        <v>8.0973234294992938E-5</v>
       </c>
       <c r="E8">
-        <v>-7.8741549794212771E-7</v>
+        <v>-7.533267469054294E-7</v>
       </c>
       <c r="F8">
-        <v>-2.709264597897519E-5</v>
+        <v>-2.6830807515202152E-5</v>
       </c>
       <c r="G8">
-        <v>-1.0489393279001088E-5</v>
+        <v>-1.0372308528914312E-5</v>
       </c>
       <c r="H8">
-        <v>-6.5430926911042783E-3</v>
+        <v>-6.5434480290226735E-3</v>
       </c>
       <c r="I8">
-        <v>7.5660617499910049E-3</v>
+        <v>7.5695988332411292E-3</v>
       </c>
       <c r="J8">
-        <v>7.1669728309747317E-5</v>
+        <v>-1.3125358233150013E-3</v>
       </c>
       <c r="K8">
-        <v>3.8227818928237645E-4</v>
+        <v>2.1141437109945015E-4</v>
       </c>
       <c r="L8">
-        <v>2.1509980016162281E-4</v>
+        <v>5.9028851660346629E-4</v>
       </c>
       <c r="M8">
-        <v>5.8663846317897402E-4</v>
+        <v>9.9208714953986791E-4</v>
       </c>
       <c r="N8">
-        <v>9.8590772447257639E-4</v>
+        <v>1.2380031878942049E-3</v>
       </c>
       <c r="O8">
-        <v>1.227981314700863E-3</v>
+        <v>1.11327147044202E-4</v>
       </c>
       <c r="P8">
-        <v>1.0979830754175165E-4</v>
+        <v>2.2125225044606782E-4</v>
       </c>
       <c r="Q8">
-        <v>2.215081986578742E-4</v>
+        <v>1.2442722215055011E-4</v>
       </c>
       <c r="R8">
-        <v>1.2330618585362188E-4</v>
+        <v>-3.8489537725640478E-4</v>
       </c>
       <c r="S8">
-        <v>-3.8460353558475739E-4</v>
+        <v>-6.8841955017501753E-5</v>
       </c>
       <c r="T8">
-        <v>-6.8365461980768121E-5</v>
+        <v>-1.2503828804736401E-6</v>
       </c>
       <c r="U8">
-        <v>-6.0995866492246113E-6</v>
+        <v>1.9359189002721156E-4</v>
       </c>
       <c r="V8">
-        <v>1.9800044682579117E-4</v>
+        <v>7.3366007915953431E-5</v>
       </c>
       <c r="W8">
-        <v>7.502088132318454E-5</v>
+        <v>1.501352840029798E-4</v>
       </c>
       <c r="X8">
-        <v>1.4835485397564189E-4</v>
+        <v>6.0242611992599132E-5</v>
       </c>
       <c r="Y8">
-        <v>5.8315982110936169E-5</v>
+        <v>1.5150240584839176E-4</v>
       </c>
       <c r="Z8">
-        <v>1.4220932154272194E-4</v>
+        <v>2.4698874046062908E-4</v>
       </c>
       <c r="AA8">
-        <v>2.4707759380090087E-4</v>
+        <v>5.5491304822533711E-4</v>
       </c>
       <c r="AB8">
-        <v>5.5716790745972879E-4</v>
+        <v>1.7346262185645629E-4</v>
       </c>
       <c r="AC8">
-        <v>1.7283705511705666E-4</v>
+        <v>2.8296198670110405E-4</v>
       </c>
       <c r="AD8">
-        <v>2.8290724321893706E-4</v>
+        <v>7.8150471258504406E-4</v>
       </c>
       <c r="AE8">
-        <v>7.8358815076011933E-4</v>
+        <v>1.1492746149992933E-4</v>
       </c>
       <c r="AF8">
-        <v>1.1459159258371369E-4</v>
+        <v>-2.9825152655369634E-5</v>
       </c>
       <c r="AG8">
-        <v>-2.9331958346535044E-5</v>
+        <v>-4.0185609186017043E-4</v>
       </c>
       <c r="AH8">
-        <v>-4.0281585531746827E-4</v>
+        <v>-4.9891429821407457E-4</v>
       </c>
       <c r="AI8">
-        <v>-4.9941086088878652E-4</v>
+        <v>1.0073765944365229E-4</v>
       </c>
       <c r="AJ8">
-        <v>1.0086184702941606E-4</v>
+        <v>-3.0862442241197537E-4</v>
       </c>
       <c r="AK8">
-        <v>-2.9827769167684666E-4</v>
+        <v>1.8286058719499884E-3</v>
       </c>
       <c r="AL8">
-        <v>1.835597119942951E-3</v>
-      </c>
-      <c r="AM8">
-        <v>3.234878968855515E-3</v>
+        <v>3.283027603503073E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-0.18707619666863737</v>
+        <v>-0.36384704648872401</v>
       </c>
       <c r="C9">
-        <v>-0.24590499236674482</v>
+        <v>-0.20313124239577762</v>
       </c>
       <c r="D9">
-        <v>-1.1487846491855603E-4</v>
+        <v>3.9133767276214098E-4</v>
       </c>
       <c r="E9">
-        <v>1.6657381860583655E-6</v>
+        <v>-5.791640183632728E-6</v>
       </c>
       <c r="F9">
-        <v>-7.6878014922692627E-6</v>
+        <v>-1.4400337112006453E-5</v>
       </c>
       <c r="G9">
-        <v>-4.0637755015045232E-6</v>
+        <v>-2.0368050846801811E-5</v>
       </c>
       <c r="H9">
-        <v>-1.873336330043961E-5</v>
+        <v>-3.5963656972863562E-4</v>
       </c>
       <c r="I9">
-        <v>7.1669728309747317E-5</v>
+        <v>-1.3125358233150013E-3</v>
       </c>
       <c r="J9">
-        <v>1.0732887801154285E-2</v>
+        <v>0.22724627243501472</v>
       </c>
       <c r="K9">
-        <v>3.9351624517591062E-2</v>
+        <v>1.7606700100726835E-4</v>
       </c>
       <c r="L9">
-        <v>1.3671323402372702E-4</v>
+        <v>-4.3458593642227899E-4</v>
       </c>
       <c r="M9">
-        <v>1.7747290367504877E-4</v>
+        <v>-9.8868219705209649E-4</v>
       </c>
       <c r="N9">
-        <v>2.2935846344764445E-4</v>
+        <v>-1.4774661071021769E-3</v>
       </c>
       <c r="O9">
-        <v>2.7204751348254824E-4</v>
+        <v>-3.5432687472970704E-4</v>
       </c>
       <c r="P9">
-        <v>5.7695129760089035E-5</v>
+        <v>-1.3148518674039358E-4</v>
       </c>
       <c r="Q9">
-        <v>1.387190622196588E-5</v>
+        <v>-4.1778325218692707E-4</v>
       </c>
       <c r="R9">
-        <v>6.9823251868474752E-5</v>
+        <v>-1.4111734119706069E-4</v>
       </c>
       <c r="S9">
-        <v>8.8346949707315608E-6</v>
+        <v>1.0348692034041617E-4</v>
       </c>
       <c r="T9">
-        <v>-1.6816302904749903E-7</v>
+        <v>-3.398453766931455E-4</v>
       </c>
       <c r="U9">
-        <v>1.8164848259704974E-5</v>
+        <v>8.6567656666861959E-4</v>
       </c>
       <c r="V9">
-        <v>-1.0044735364836661E-4</v>
+        <v>5.648478999134427E-5</v>
       </c>
       <c r="W9">
-        <v>1.4630410075567972E-5</v>
+        <v>4.7669637045386304E-4</v>
       </c>
       <c r="X9">
-        <v>-1.4033655014624444E-4</v>
+        <v>-3.1364590772588083E-5</v>
       </c>
       <c r="Y9">
-        <v>-4.2020204484788403E-5</v>
+        <v>-9.2050964474666428E-4</v>
       </c>
       <c r="Z9">
-        <v>-1.8887447626586258E-4</v>
+        <v>-6.0535343917145689E-4</v>
       </c>
       <c r="AA9">
-        <v>-2.8559050693349741E-6</v>
+        <v>2.1447403892814243E-4</v>
       </c>
       <c r="AB9">
-        <v>-4.5521928063401736E-5</v>
+        <v>2.5266815975404078E-6</v>
       </c>
       <c r="AC9">
-        <v>-6.6977029962653417E-5</v>
+        <v>-1.9530136455112886E-4</v>
       </c>
       <c r="AD9">
-        <v>-5.0171976386988735E-5</v>
+        <v>3.0514642471913937E-4</v>
       </c>
       <c r="AE9">
-        <v>-2.1063401386416602E-5</v>
+        <v>-3.254268815515096E-5</v>
       </c>
       <c r="AF9">
-        <v>-6.9209672132578524E-5</v>
+        <v>5.1716286630852168E-5</v>
       </c>
       <c r="AG9">
-        <v>2.0024308618112616E-6</v>
+        <v>5.4875272849782685E-4</v>
       </c>
       <c r="AH9">
-        <v>-7.563087660231475E-5</v>
+        <v>1.5394124667027605E-4</v>
       </c>
       <c r="AI9">
-        <v>-3.0155964177004972E-5</v>
+        <v>-2.2290733657123269E-4</v>
       </c>
       <c r="AJ9">
-        <v>-2.0628274906582924E-5</v>
+        <v>4.9545420292900475E-4</v>
       </c>
       <c r="AK9">
-        <v>-5.1082890568032117E-7</v>
+        <v>-1.570168867256235E-3</v>
       </c>
       <c r="AL9">
-        <v>1.6845925653075078E-4</v>
-      </c>
-      <c r="AM9">
-        <v>2.2602707842037731E-3</v>
+        <v>-9.7292232438186271E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-0.59871716580734935</v>
+        <v>-0.1488589195983486</v>
       </c>
       <c r="C10">
-        <v>-1.009680367844866</v>
+        <v>-5.3472086254740918E-5</v>
       </c>
       <c r="D10">
-        <v>-1.0004115507826743E-4</v>
+        <v>4.4193640925057779E-5</v>
       </c>
       <c r="E10">
-        <v>1.4459255834453345E-6</v>
+        <v>-5.8679367113113092E-7</v>
       </c>
       <c r="F10">
-        <v>-3.2087901730103773E-5</v>
+        <v>-2.2755861833452517E-6</v>
       </c>
       <c r="G10">
-        <v>-2.9921112581116135E-5</v>
+        <v>-3.9679400939363426E-6</v>
       </c>
       <c r="H10">
-        <v>-1.8347383377681178E-3</v>
+        <v>-9.9424917717905523E-5</v>
       </c>
       <c r="I10">
-        <v>3.8227818928237645E-4</v>
+        <v>2.1141437109945015E-4</v>
       </c>
       <c r="J10">
-        <v>3.9351624517591062E-2</v>
+        <v>1.7606700100726835E-4</v>
       </c>
       <c r="K10">
-        <v>0.27490751798055463</v>
+        <v>2.5005288481747172E-3</v>
       </c>
       <c r="L10">
-        <v>7.3229379097829151E-4</v>
+        <v>1.4669229142684895E-3</v>
       </c>
       <c r="M10">
-        <v>2.1783678593394515E-4</v>
+        <v>1.5168329999325721E-3</v>
       </c>
       <c r="N10">
-        <v>-1.4529345758080821E-4</v>
+        <v>1.4427623262966156E-3</v>
       </c>
       <c r="O10">
-        <v>-2.741674845773268E-4</v>
+        <v>-1.7818777949385402E-4</v>
       </c>
       <c r="P10">
-        <v>-1.9465066421466167E-4</v>
+        <v>2.6317589197805141E-5</v>
       </c>
       <c r="Q10">
-        <v>-5.582413862192725E-5</v>
+        <v>-1.6445067918913482E-4</v>
       </c>
       <c r="R10">
-        <v>-3.1702968291992453E-4</v>
+        <v>1.38127295233935E-5</v>
       </c>
       <c r="S10">
-        <v>-1.574254551060068E-4</v>
+        <v>-5.3827987557869897E-5</v>
       </c>
       <c r="T10">
-        <v>4.4594799171312691E-6</v>
+        <v>4.2033250775927304E-4</v>
       </c>
       <c r="U10">
-        <v>-1.8079210150238377E-4</v>
+        <v>4.0146537206704253E-4</v>
       </c>
       <c r="V10">
-        <v>1.6621326349666396E-5</v>
+        <v>2.8210805328087032E-4</v>
       </c>
       <c r="W10">
-        <v>2.3205044540792878E-4</v>
+        <v>2.3602776669035918E-4</v>
       </c>
       <c r="X10">
-        <v>3.243693030422351E-4</v>
+        <v>2.7922672978385773E-4</v>
       </c>
       <c r="Y10">
-        <v>3.2180960662535991E-5</v>
+        <v>2.388123506821443E-4</v>
       </c>
       <c r="Z10">
-        <v>-7.6101030231040035E-4</v>
+        <v>4.4083295800708073E-4</v>
       </c>
       <c r="AA10">
-        <v>-6.5997514466694697E-4</v>
+        <v>2.5766761989525063E-4</v>
       </c>
       <c r="AB10">
-        <v>2.1542303047263425E-4</v>
+        <v>2.2500867098353307E-4</v>
       </c>
       <c r="AC10">
-        <v>-1.3360423639818017E-4</v>
+        <v>2.5382482555075464E-4</v>
       </c>
       <c r="AD10">
-        <v>-1.8526023193919422E-4</v>
+        <v>9.6613041658874353E-5</v>
       </c>
       <c r="AE10">
-        <v>2.0933802891666495E-4</v>
+        <v>3.4874653431506554E-4</v>
       </c>
       <c r="AF10">
-        <v>-6.3329662227194512E-5</v>
+        <v>-6.0716183931791956E-5</v>
       </c>
       <c r="AG10">
-        <v>-2.3051827846803864E-5</v>
+        <v>-2.4134555619574811E-4</v>
       </c>
       <c r="AH10">
-        <v>-4.8503737657104758E-6</v>
+        <v>5.7240161079760168E-5</v>
       </c>
       <c r="AI10">
-        <v>-2.1657257925707281E-5</v>
+        <v>4.4322067690803009E-5</v>
       </c>
       <c r="AJ10">
-        <v>-2.6677497277693279E-4</v>
+        <v>3.0132075470445469E-4</v>
       </c>
       <c r="AK10">
-        <v>6.0318400735421369E-5</v>
+        <v>4.7289686848824009E-4</v>
       </c>
       <c r="AL10">
-        <v>-1.5805182777097956E-3</v>
-      </c>
-      <c r="AM10">
-        <v>5.7423536906898477E-3</v>
+        <v>2.0584444529755325E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>23</v>
       </c>
       <c r="B11">
-        <v>-0.14999488405577432</v>
+        <v>-0.2424682489428103</v>
       </c>
       <c r="C11">
-        <v>-3.2934950844818699E-3</v>
+        <v>1.1058824094478505E-3</v>
       </c>
       <c r="D11">
-        <v>4.313586585278037E-5</v>
+        <v>2.6178521736590419E-5</v>
       </c>
       <c r="E11">
-        <v>-5.7069261333213611E-7</v>
+        <v>-3.4023275094416237E-7</v>
       </c>
       <c r="F11">
-        <v>-2.370361699935671E-6</v>
+        <v>-7.7980045907026575E-6</v>
       </c>
       <c r="G11">
-        <v>-4.0212965815500896E-6</v>
+        <v>-1.9133767547301233E-6</v>
       </c>
       <c r="H11">
-        <v>-1.019859183580371E-4</v>
+        <v>-5.0687743142570468E-5</v>
       </c>
       <c r="I11">
-        <v>2.1509980016162281E-4</v>
+        <v>5.9028851660346629E-4</v>
       </c>
       <c r="J11">
-        <v>1.3671323402372702E-4</v>
+        <v>-4.3458593642227899E-4</v>
       </c>
       <c r="K11">
-        <v>7.3229379097829151E-4</v>
+        <v>1.4669229142684895E-3</v>
       </c>
       <c r="L11">
-        <v>2.5096927474798801E-3</v>
+        <v>2.4980765415971587E-3</v>
       </c>
       <c r="M11">
-        <v>1.4734183325095128E-3</v>
+        <v>1.973707461614781E-3</v>
       </c>
       <c r="N11">
-        <v>1.5233337178920839E-3</v>
+        <v>1.924806320524461E-3</v>
       </c>
       <c r="O11">
-        <v>1.4490635491509322E-3</v>
+        <v>-6.591599696360238E-5</v>
       </c>
       <c r="P11">
-        <v>-1.7894608861927455E-4</v>
+        <v>1.5996920351486348E-5</v>
       </c>
       <c r="Q11">
-        <v>2.6921766731276019E-5</v>
+        <v>1.2127931014162274E-4</v>
       </c>
       <c r="R11">
-        <v>-1.6441719143780098E-4</v>
+        <v>9.2521461815934429E-5</v>
       </c>
       <c r="S11">
-        <v>1.431197937152819E-5</v>
+        <v>-8.1562631843719573E-5</v>
       </c>
       <c r="T11">
-        <v>-5.3831622007214242E-5</v>
+        <v>6.9320593683116572E-4</v>
       </c>
       <c r="U11">
-        <v>4.23118614805335E-4</v>
+        <v>3.2307774575907543E-4</v>
       </c>
       <c r="V11">
-        <v>4.0002872243687646E-4</v>
+        <v>3.0908821597158876E-4</v>
       </c>
       <c r="W11">
-        <v>2.8432591744216606E-4</v>
+        <v>3.0251477329939277E-4</v>
       </c>
       <c r="X11">
-        <v>2.3751868632867988E-4</v>
+        <v>2.6260483901056946E-4</v>
       </c>
       <c r="Y11">
-        <v>2.807481192233791E-4</v>
+        <v>2.2454866027842471E-4</v>
       </c>
       <c r="Z11">
-        <v>2.3890033862659216E-4</v>
+        <v>5.9929928550424933E-4</v>
       </c>
       <c r="AA11">
-        <v>4.4336279919422262E-4</v>
+        <v>2.648822735723175E-4</v>
       </c>
       <c r="AB11">
-        <v>2.5997363204390261E-4</v>
+        <v>2.6101166839156021E-4</v>
       </c>
       <c r="AC11">
-        <v>2.2619494225128785E-4</v>
+        <v>5.1786952389974012E-4</v>
       </c>
       <c r="AD11">
-        <v>2.5567747635024066E-4</v>
+        <v>1.4349521267512056E-4</v>
       </c>
       <c r="AE11">
-        <v>9.9356655392510298E-5</v>
+        <v>3.4472341442368408E-4</v>
       </c>
       <c r="AF11">
-        <v>3.5039861140833783E-4</v>
+        <v>-7.410532401757946E-5</v>
       </c>
       <c r="AG11">
-        <v>-6.0665860829154245E-5</v>
+        <v>-3.5737186212504517E-4</v>
       </c>
       <c r="AH11">
-        <v>-2.4419226595269504E-4</v>
+        <v>-1.1549385762271377E-4</v>
       </c>
       <c r="AI11">
-        <v>5.6621114249929909E-5</v>
+        <v>2.6283950258548273E-5</v>
       </c>
       <c r="AJ11">
-        <v>4.2756589411396774E-5</v>
+        <v>3.2922117413787354E-4</v>
       </c>
       <c r="AK11">
-        <v>3.0345001212948988E-4</v>
+        <v>8.9898177066784473E-4</v>
       </c>
       <c r="AL11">
-        <v>4.7628528993952715E-4</v>
-      </c>
-      <c r="AM11">
-        <v>2.0745357425366049E-3</v>
+        <v>3.7112497592041958E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-0.24495243316968565</v>
+        <v>-0.27391490041841382</v>
       </c>
       <c r="C12">
-        <v>-3.2220216797649859E-3</v>
+        <v>1.6587215951037585E-3</v>
       </c>
       <c r="D12">
-        <v>2.5651970561933247E-5</v>
+        <v>1.9094234857100229E-5</v>
       </c>
       <c r="E12">
-        <v>-3.3179849833708459E-7</v>
+        <v>-4.0604385613422154E-7</v>
       </c>
       <c r="F12">
-        <v>-7.9006944671719527E-6</v>
+        <v>-8.3777002382156356E-6</v>
       </c>
       <c r="G12">
-        <v>-1.9710932441711321E-6</v>
+        <v>3.2259477344254134E-7</v>
       </c>
       <c r="H12">
-        <v>-4.7204094381652746E-5</v>
+        <v>-4.7837519547153464E-5</v>
       </c>
       <c r="I12">
-        <v>5.8663846317897402E-4</v>
+        <v>9.9208714953986791E-4</v>
       </c>
       <c r="J12">
-        <v>1.7747290367504877E-4</v>
+        <v>-9.8868219705209649E-4</v>
       </c>
       <c r="K12">
-        <v>2.1783678593394515E-4</v>
+        <v>1.5168329999325721E-3</v>
       </c>
       <c r="L12">
-        <v>1.4734183325095128E-3</v>
+        <v>1.973707461614781E-3</v>
       </c>
       <c r="M12">
-        <v>2.5002084979415568E-3</v>
+        <v>2.9864840033040959E-3</v>
       </c>
       <c r="N12">
-        <v>1.9738383915730521E-3</v>
+        <v>2.2852942632721391E-3</v>
       </c>
       <c r="O12">
-        <v>1.9233313119199911E-3</v>
+        <v>2.0504311379019322E-5</v>
       </c>
       <c r="P12">
-        <v>-6.6685753235848317E-5</v>
+        <v>-1.5970003932191535E-5</v>
       </c>
       <c r="Q12">
-        <v>1.6508044545676316E-5</v>
+        <v>3.1075415495287968E-4</v>
       </c>
       <c r="R12">
-        <v>1.2129267957978107E-4</v>
+        <v>8.2437943991989433E-5</v>
       </c>
       <c r="S12">
-        <v>9.3369207670772174E-5</v>
+        <v>-9.5978219377698985E-5</v>
       </c>
       <c r="T12">
-        <v>-8.1499009315189069E-5</v>
+        <v>7.8760388376139415E-4</v>
       </c>
       <c r="U12">
-        <v>6.9349433310676007E-4</v>
+        <v>4.7735108126634065E-4</v>
       </c>
       <c r="V12">
-        <v>3.195578421782284E-4</v>
+        <v>3.9981735918099664E-4</v>
       </c>
       <c r="W12">
-        <v>3.1030636134102356E-4</v>
+        <v>3.9852101608258116E-4</v>
       </c>
       <c r="X12">
-        <v>2.9949997852634518E-4</v>
+        <v>2.75904763468659E-4</v>
       </c>
       <c r="Y12">
-        <v>2.6217183029218305E-4</v>
+        <v>2.1965349500105156E-4</v>
       </c>
       <c r="Z12">
-        <v>2.2087310537970354E-4</v>
+        <v>1.1219324090366836E-3</v>
       </c>
       <c r="AA12">
-        <v>6.0082668208853761E-4</v>
+        <v>2.5831725145798712E-4</v>
       </c>
       <c r="AB12">
-        <v>2.6518396582563426E-4</v>
+        <v>3.3814898750980849E-4</v>
       </c>
       <c r="AC12">
-        <v>2.6082141306422627E-4</v>
+        <v>4.9376538997072332E-4</v>
       </c>
       <c r="AD12">
-        <v>5.1749178505540666E-4</v>
+        <v>3.5244047450889521E-4</v>
       </c>
       <c r="AE12">
-        <v>1.4450918320381667E-4</v>
+        <v>3.6926016319388391E-4</v>
       </c>
       <c r="AF12">
-        <v>3.4440367008863623E-4</v>
+        <v>-7.2712037833034114E-5</v>
       </c>
       <c r="AG12">
-        <v>-7.3967870968633836E-5</v>
+        <v>-4.6759768700246744E-4</v>
       </c>
       <c r="AH12">
-        <v>-3.5984640965902896E-4</v>
+        <v>-2.3413646908388439E-4</v>
       </c>
       <c r="AI12">
-        <v>-1.1581524033788156E-4</v>
+        <v>1.440224675136781E-4</v>
       </c>
       <c r="AJ12">
-        <v>2.5330598805859555E-5</v>
+        <v>6.8764391419227889E-5</v>
       </c>
       <c r="AK12">
-        <v>3.3002934064755511E-4</v>
+        <v>2.7956394479531042E-3</v>
       </c>
       <c r="AL12">
-        <v>9.0363121166423498E-4</v>
-      </c>
-      <c r="AM12">
-        <v>3.7223852592853744E-3</v>
+        <v>4.1479164061915003E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
-        <v>-0.27748219957064574</v>
+        <v>-8.1189434482133407E-2</v>
       </c>
       <c r="C13">
-        <v>-3.9969364442649195E-3</v>
+        <v>2.1441034239617096E-3</v>
       </c>
       <c r="D13">
-        <v>1.8712976673758951E-5</v>
+        <v>-4.9265798130001485E-5</v>
       </c>
       <c r="E13">
-        <v>-3.9982333836255607E-7</v>
+        <v>6.209178716875955E-7</v>
       </c>
       <c r="F13">
-        <v>-8.5144845496151197E-6</v>
+        <v>-1.6749605364795359E-5</v>
       </c>
       <c r="G13">
-        <v>2.5350236337953893E-7</v>
+        <v>-6.4859836447984063E-6</v>
       </c>
       <c r="H13">
-        <v>-4.2323974636531889E-5</v>
+        <v>-3.8937589848764547E-4</v>
       </c>
       <c r="I13">
-        <v>9.8590772447257639E-4</v>
+        <v>1.2380031878942049E-3</v>
       </c>
       <c r="J13">
-        <v>2.2935846344764445E-4</v>
+        <v>-1.4774661071021769E-3</v>
       </c>
       <c r="K13">
-        <v>-1.4529345758080821E-4</v>
+        <v>1.4427623262966156E-3</v>
       </c>
       <c r="L13">
-        <v>1.5233337178920839E-3</v>
+        <v>1.924806320524461E-3</v>
       </c>
       <c r="M13">
-        <v>1.9738383915730521E-3</v>
+        <v>2.2852942632721391E-3</v>
       </c>
       <c r="N13">
-        <v>2.9839443992086523E-3</v>
+        <v>2.8624452867366079E-3</v>
       </c>
       <c r="O13">
-        <v>2.2800042214291909E-3</v>
+        <v>1.3310520693986239E-4</v>
       </c>
       <c r="P13">
-        <v>1.9621946392924336E-5</v>
+        <v>3.3555026337421115E-5</v>
       </c>
       <c r="Q13">
-        <v>-1.5275774144304581E-5</v>
+        <v>3.2869410123851641E-4</v>
       </c>
       <c r="R13">
-        <v>3.1078833765347998E-4</v>
+        <v>-2.1603487907827999E-4</v>
       </c>
       <c r="S13">
-        <v>8.3699301924957704E-5</v>
+        <v>-3.561397520778368E-5</v>
       </c>
       <c r="T13">
-        <v>-9.5783840142214154E-5</v>
+        <v>7.7383497077485931E-4</v>
       </c>
       <c r="U13">
-        <v>7.8626602026559301E-4</v>
+        <v>2.2891252522802051E-4</v>
       </c>
       <c r="V13">
-        <v>4.7339784162513267E-4</v>
+        <v>1.8021347092630937E-4</v>
       </c>
       <c r="W13">
-        <v>4.0092975978991524E-4</v>
+        <v>1.5262262650921849E-4</v>
       </c>
       <c r="X13">
-        <v>3.9312453551718291E-4</v>
+        <v>1.2484016354407485E-4</v>
       </c>
       <c r="Y13">
-        <v>2.7451183181376784E-4</v>
+        <v>2.1083847500673997E-5</v>
       </c>
       <c r="Z13">
-        <v>2.1440102670977417E-4</v>
+        <v>3.400616264403434E-4</v>
       </c>
       <c r="AA13">
-        <v>1.1234897134512185E-3</v>
+        <v>1.2461962975315191E-4</v>
       </c>
       <c r="AB13">
-        <v>2.5846836761566716E-4</v>
+        <v>1.0001937802377913E-4</v>
       </c>
       <c r="AC13">
-        <v>3.3705903448900747E-4</v>
+        <v>2.5647592363216721E-4</v>
       </c>
       <c r="AD13">
-        <v>4.9276383720333607E-4</v>
+        <v>8.7078311087619757E-5</v>
       </c>
       <c r="AE13">
-        <v>3.5321984850250209E-4</v>
+        <v>2.5983639759235492E-4</v>
       </c>
       <c r="AF13">
-        <v>3.6799086553373128E-4</v>
+        <v>-2.1325762600560388E-5</v>
       </c>
       <c r="AG13">
-        <v>-7.2344313572197759E-5</v>
+        <v>-2.8203260721939303E-4</v>
       </c>
       <c r="AH13">
-        <v>-4.7067492382660021E-4</v>
+        <v>-1.8490776819335083E-4</v>
       </c>
       <c r="AI13">
-        <v>-2.3431559265726291E-4</v>
+        <v>1.0030989854685891E-4</v>
       </c>
       <c r="AJ13">
-        <v>1.4318956040585925E-4</v>
+        <v>5.230558055267212E-5</v>
       </c>
       <c r="AK13">
-        <v>7.0542667268484109E-5</v>
+        <v>5.5680978943236075E-4</v>
       </c>
       <c r="AL13">
-        <v>2.803078540061222E-3</v>
-      </c>
-      <c r="AM13">
-        <v>4.1514510662367396E-3</v>
+        <v>1.8729769437062817E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14">
-        <v>-8.5770775549524281E-2</v>
+        <v>-9.6640544594780761E-2</v>
       </c>
       <c r="C14">
-        <v>-4.7979532253217983E-3</v>
+        <v>3.6131410017203576E-4</v>
       </c>
       <c r="D14">
-        <v>-4.9942707230527373E-5</v>
+        <v>-4.2917521765438102E-5</v>
       </c>
       <c r="E14">
-        <v>6.329474301583831E-7</v>
+        <v>4.3816734219150208E-7</v>
       </c>
       <c r="F14">
-        <v>-1.6933588477824296E-5</v>
+        <v>-1.8904132894317648E-6</v>
       </c>
       <c r="G14">
-        <v>-6.5925254357502459E-6</v>
+        <v>-2.5792579274637747E-6</v>
       </c>
       <c r="H14">
-        <v>-3.8116579723124981E-4</v>
+        <v>1.1626008913003185E-4</v>
       </c>
       <c r="I14">
-        <v>1.227981314700863E-3</v>
+        <v>1.11327147044202E-4</v>
       </c>
       <c r="J14">
-        <v>2.7204751348254824E-4</v>
+        <v>-3.5432687472970704E-4</v>
       </c>
       <c r="K14">
-        <v>-2.741674845773268E-4</v>
+        <v>-1.7818777949385402E-4</v>
       </c>
       <c r="L14">
-        <v>1.4490635491509322E-3</v>
+        <v>-6.591599696360238E-5</v>
       </c>
       <c r="M14">
-        <v>1.9233313119199911E-3</v>
+        <v>2.0504311379019322E-5</v>
       </c>
       <c r="N14">
-        <v>2.2800042214291909E-3</v>
+        <v>1.3310520693986239E-4</v>
       </c>
       <c r="O14">
-        <v>2.8535204416401173E-3</v>
+        <v>3.4220652206147571E-4</v>
       </c>
       <c r="P14">
-        <v>1.32052438687436E-4</v>
+        <v>-1.8087138547863267E-4</v>
       </c>
       <c r="Q14">
-        <v>3.4520653522149199E-5</v>
+        <v>1.642963735986582E-4</v>
       </c>
       <c r="R14">
-        <v>3.2858116218432656E-4</v>
+        <v>6.392274469379578E-5</v>
       </c>
       <c r="S14">
-        <v>-2.1422874021677455E-4</v>
+        <v>1.1054582446912281E-5</v>
       </c>
       <c r="T14">
-        <v>-3.5270793645733069E-5</v>
+        <v>-9.7169892346544236E-5</v>
       </c>
       <c r="U14">
-        <v>7.7095294283113845E-4</v>
+        <v>-1.4613705435898757E-4</v>
       </c>
       <c r="V14">
-        <v>2.2537628627035725E-4</v>
+        <v>-1.4593720770276163E-4</v>
       </c>
       <c r="W14">
-        <v>1.8070755620290459E-4</v>
+        <v>-1.534769365573822E-4</v>
       </c>
       <c r="X14">
-        <v>1.453625021515177E-4</v>
+        <v>-1.5348880824856857E-4</v>
       </c>
       <c r="Y14">
-        <v>1.224207816128172E-4</v>
+        <v>-1.7112612614779134E-4</v>
       </c>
       <c r="Z14">
-        <v>1.2487049385115888E-5</v>
+        <v>-9.5996459987674246E-5</v>
       </c>
       <c r="AA14">
-        <v>3.4089208222259134E-4</v>
+        <v>-1.5851426410824044E-4</v>
       </c>
       <c r="AB14">
-        <v>1.2424306516707037E-4</v>
+        <v>-1.5227428990887746E-4</v>
       </c>
       <c r="AC14">
-        <v>9.8170308284608145E-5</v>
+        <v>-9.1240735139923789E-5</v>
       </c>
       <c r="AD14">
-        <v>2.5465003291989964E-4</v>
+        <v>-7.6497461349766695E-5</v>
       </c>
       <c r="AE14">
-        <v>8.7559292715501435E-5</v>
+        <v>-1.9841385124146673E-4</v>
       </c>
       <c r="AF14">
-        <v>2.5787102185891486E-4</v>
+        <v>1.9707518395667558E-5</v>
       </c>
       <c r="AG14">
-        <v>-2.090197685725042E-5</v>
+        <v>-4.3298257807774577E-5</v>
       </c>
       <c r="AH14">
-        <v>-2.8433936264808755E-4</v>
+        <v>-2.7340057892192605E-5</v>
       </c>
       <c r="AI14">
-        <v>-1.8453782472185496E-4</v>
+        <v>-1.0637958707025315E-4</v>
       </c>
       <c r="AJ14">
-        <v>9.9372795992537424E-5</v>
+        <v>-2.0551544867328128E-4</v>
       </c>
       <c r="AK14">
-        <v>5.5427359514094747E-5</v>
+        <v>-6.4614521162866066E-5</v>
       </c>
       <c r="AL14">
-        <v>5.6447247806284614E-4</v>
-      </c>
-      <c r="AM14">
-        <v>1.8784542518234335E-3</v>
+        <v>-7.919040754307289E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
       <c r="B15">
-        <v>-9.7386617137698445E-2</v>
+        <v>0.16005772878411476</v>
       </c>
       <c r="C15">
-        <v>-1.0308436604906934E-3</v>
+        <v>4.9868144323422412E-5</v>
       </c>
       <c r="D15">
-        <v>-4.3488754409715634E-5</v>
+        <v>-7.1704212273286503E-5</v>
       </c>
       <c r="E15">
-        <v>4.463964944142752E-7</v>
+        <v>1.3733802613425309E-6</v>
       </c>
       <c r="F15">
-        <v>-1.9178952823783877E-6</v>
+        <v>-2.5649215771245024E-6</v>
       </c>
       <c r="G15">
-        <v>-2.593464632782862E-6</v>
+        <v>-1.8247166667789016E-6</v>
       </c>
       <c r="H15">
-        <v>1.1807056301598346E-4</v>
+        <v>-1.3889471390744621E-4</v>
       </c>
       <c r="I15">
-        <v>1.0979830754175165E-4</v>
+        <v>2.2125225044606782E-4</v>
       </c>
       <c r="J15">
-        <v>5.7695129760089035E-5</v>
+        <v>-1.3148518674039358E-4</v>
       </c>
       <c r="K15">
-        <v>-1.9465066421466167E-4</v>
+        <v>2.6317589197805141E-5</v>
       </c>
       <c r="L15">
-        <v>-1.7894608861927455E-4</v>
+        <v>1.5996920351486348E-5</v>
       </c>
       <c r="M15">
-        <v>-6.6685753235848317E-5</v>
+        <v>-1.5970003932191535E-5</v>
       </c>
       <c r="N15">
-        <v>1.9621946392924336E-5</v>
+        <v>3.3555026337421115E-5</v>
       </c>
       <c r="O15">
-        <v>1.32052438687436E-4</v>
+        <v>-1.8087138547863267E-4</v>
       </c>
       <c r="P15">
-        <v>3.4272559585605996E-4</v>
+        <v>6.9497369899848538E-4</v>
       </c>
       <c r="Q15">
-        <v>-1.8080768962173288E-4</v>
+        <v>5.5292413107065183E-5</v>
       </c>
       <c r="R15">
-        <v>1.6500386144731105E-4</v>
+        <v>-6.6392722773998554E-5</v>
       </c>
       <c r="S15">
-        <v>6.4269692681587535E-5</v>
+        <v>2.508255560027211E-5</v>
       </c>
       <c r="T15">
-        <v>1.1047269542324134E-5</v>
+        <v>-9.1545456347768905E-5</v>
       </c>
       <c r="U15">
-        <v>-9.787883401485883E-5</v>
+        <v>-2.8902058776873053E-5</v>
       </c>
       <c r="V15">
-        <v>-1.4713758041230967E-4</v>
+        <v>-6.1162579146565715E-5</v>
       </c>
       <c r="W15">
-        <v>-1.46533462482834E-4</v>
+        <v>-5.8219880179834249E-5</v>
       </c>
       <c r="X15">
-        <v>-1.5572552061725263E-4</v>
+        <v>-7.278238942481612E-5</v>
       </c>
       <c r="Y15">
-        <v>-1.5451330389274945E-4</v>
+        <v>-4.0865569470503789E-5</v>
       </c>
       <c r="Z15">
-        <v>-1.729765474145342E-4</v>
+        <v>-1.3966093208154777E-4</v>
       </c>
       <c r="AA15">
-        <v>-9.6446162468214911E-5</v>
+        <v>-4.032931878466916E-5</v>
       </c>
       <c r="AB15">
-        <v>-1.5940032805199261E-4</v>
+        <v>-2.9799196378727452E-5</v>
       </c>
       <c r="AC15">
-        <v>-1.5322882595677952E-4</v>
+        <v>-1.2357253197622882E-4</v>
       </c>
       <c r="AD15">
-        <v>-9.220187852812493E-5</v>
+        <v>-1.195201122290816E-4</v>
       </c>
       <c r="AE15">
-        <v>-7.7018579124131178E-5</v>
+        <v>-7.4539733048804423E-5</v>
       </c>
       <c r="AF15">
-        <v>-1.9948303755894741E-4</v>
+        <v>2.6398815104724331E-5</v>
       </c>
       <c r="AG15">
-        <v>1.9752171383797402E-5</v>
+        <v>6.857118340413009E-5</v>
       </c>
       <c r="AH15">
-        <v>-4.3702183334916973E-5</v>
+        <v>7.1712720550812275E-5</v>
       </c>
       <c r="AI15">
-        <v>-2.7364535477065999E-5</v>
+        <v>7.4223138723151494E-5</v>
       </c>
       <c r="AJ15">
-        <v>-1.0618963301686811E-4</v>
+        <v>9.2620957553202248E-6</v>
       </c>
       <c r="AK15">
-        <v>-2.0655310234175947E-4</v>
+        <v>-1.726816996656833E-4</v>
       </c>
       <c r="AL15">
-        <v>-6.2933058102638412E-5</v>
-      </c>
-      <c r="AM15">
-        <v>-6.6314735607186752E-5</v>
+        <v>-8.0789588079949767E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16">
-        <v>0.16008745335527236</v>
+        <v>-6.333355669376246E-3</v>
       </c>
       <c r="C16">
-        <v>-2.8379606597901804E-4</v>
+        <v>5.21829155557328E-4</v>
       </c>
       <c r="D16">
-        <v>-7.2227827407686648E-5</v>
+        <v>-3.9815448280479046E-5</v>
       </c>
       <c r="E16">
-        <v>1.3816280457868595E-6</v>
+        <v>4.6098207380215883E-7</v>
       </c>
       <c r="F16">
-        <v>-2.5763689310145097E-6</v>
+        <v>-9.294914511612545E-7</v>
       </c>
       <c r="G16">
-        <v>-1.8358681525502474E-6</v>
+        <v>1.354243317468754E-6</v>
       </c>
       <c r="H16">
-        <v>-1.3919996866717859E-4</v>
+        <v>1.6172270616711241E-4</v>
       </c>
       <c r="I16">
-        <v>2.215081986578742E-4</v>
+        <v>1.2442722215055011E-4</v>
       </c>
       <c r="J16">
-        <v>1.387190622196588E-5</v>
+        <v>-4.1778325218692707E-4</v>
       </c>
       <c r="K16">
-        <v>-5.582413862192725E-5</v>
+        <v>-1.6445067918913482E-4</v>
       </c>
       <c r="L16">
-        <v>2.6921766731276019E-5</v>
+        <v>1.2127931014162274E-4</v>
       </c>
       <c r="M16">
-        <v>1.6508044545676316E-5</v>
+        <v>3.1075415495287968E-4</v>
       </c>
       <c r="N16">
-        <v>-1.5275774144304581E-5</v>
+        <v>3.2869410123851641E-4</v>
       </c>
       <c r="O16">
-        <v>3.4520653522149199E-5</v>
+        <v>1.642963735986582E-4</v>
       </c>
       <c r="P16">
-        <v>-1.8080768962173288E-4</v>
+        <v>5.5292413107065183E-5</v>
       </c>
       <c r="Q16">
-        <v>6.9498059035343388E-4</v>
+        <v>2.6446646791373246E-3</v>
       </c>
       <c r="R16">
-        <v>5.5462697284404816E-5</v>
+        <v>2.4184711740874647E-4</v>
       </c>
       <c r="S16">
-        <v>-6.6489408119846044E-5</v>
+        <v>4.2485396126744807E-5</v>
       </c>
       <c r="T16">
-        <v>2.5166286468326615E-5</v>
+        <v>-1.9514606478398939E-4</v>
       </c>
       <c r="U16">
-        <v>-9.1413042880032208E-5</v>
+        <v>-3.7237435516096015E-5</v>
       </c>
       <c r="V16">
-        <v>-2.9105187571238537E-5</v>
+        <v>-1.5678340433674287E-4</v>
       </c>
       <c r="W16">
-        <v>-6.117768884596783E-5</v>
+        <v>-5.0812769015288055E-5</v>
       </c>
       <c r="X16">
-        <v>-5.7833762470660096E-5</v>
+        <v>-1.5137691416454419E-4</v>
       </c>
       <c r="Y16">
-        <v>-7.2886696618612302E-5</v>
+        <v>-1.6311854147984481E-4</v>
       </c>
       <c r="Z16">
-        <v>-4.110478433166604E-5</v>
+        <v>-4.5029204461077658E-6</v>
       </c>
       <c r="AA16">
-        <v>-1.3997903167193724E-4</v>
+        <v>-1.5371937325589797E-4</v>
       </c>
       <c r="AB16">
-        <v>-4.0410406948740833E-5</v>
+        <v>-1.1468064486220317E-4</v>
       </c>
       <c r="AC16">
-        <v>-2.9898629570002986E-5</v>
+        <v>-1.0604325568780706E-4</v>
       </c>
       <c r="AD16">
-        <v>-1.2382371359395569E-4</v>
+        <v>-1.5319049780141862E-4</v>
       </c>
       <c r="AE16">
-        <v>-1.1969413871786477E-4</v>
+        <v>-2.4819717713608718E-4</v>
       </c>
       <c r="AF16">
-        <v>-7.4635623787186163E-5</v>
+        <v>6.2276125026192983E-5</v>
       </c>
       <c r="AG16">
-        <v>2.6459863303056441E-5</v>
+        <v>3.1277564311195556E-5</v>
       </c>
       <c r="AH16">
-        <v>6.873867114884042E-5</v>
+        <v>-3.1742618556409241E-5</v>
       </c>
       <c r="AI16">
-        <v>7.1693323015535902E-5</v>
+        <v>-1.5937145141711495E-4</v>
       </c>
       <c r="AJ16">
-        <v>7.3857458468417969E-5</v>
+        <v>-1.8819564898173524E-4</v>
       </c>
       <c r="AK16">
-        <v>9.0098479719378334E-6</v>
+        <v>3.6945243513388697E-4</v>
       </c>
       <c r="AL16">
-        <v>-1.7331703606577318E-4</v>
-      </c>
-      <c r="AM16">
-        <v>-8.0527993687790653E-4</v>
+        <v>-3.2889535914228749E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="B17">
-        <v>-6.8826511114318681E-3</v>
+        <v>-4.5373534790713398E-2</v>
       </c>
       <c r="C17">
-        <v>-1.0313133809074851E-3</v>
+        <v>3.198405765240627E-4</v>
       </c>
       <c r="D17">
-        <v>-4.0752767855529613E-5</v>
+        <v>-1.5826027182835878E-5</v>
       </c>
       <c r="E17">
-        <v>4.7490509954614934E-7</v>
+        <v>2.4303483718978122E-7</v>
       </c>
       <c r="F17">
-        <v>-9.5108498448200478E-7</v>
+        <v>-2.189508657971858E-7</v>
       </c>
       <c r="G17">
-        <v>1.3338280719361575E-6</v>
+        <v>1.9169267527975398E-6</v>
       </c>
       <c r="H17">
-        <v>1.6334330157498573E-4</v>
+        <v>5.6625980918611986E-4</v>
       </c>
       <c r="I17">
-        <v>1.2330618585362188E-4</v>
+        <v>-3.8489537725640478E-4</v>
       </c>
       <c r="J17">
-        <v>6.9823251868474752E-5</v>
+        <v>-1.4111734119706069E-4</v>
       </c>
       <c r="K17">
-        <v>-3.1702968291992453E-4</v>
+        <v>1.38127295233935E-5</v>
       </c>
       <c r="L17">
-        <v>-1.6441719143780098E-4</v>
+        <v>9.2521461815934429E-5</v>
       </c>
       <c r="M17">
-        <v>1.2129267957978107E-4</v>
+        <v>8.2437943991989433E-5</v>
       </c>
       <c r="N17">
-        <v>3.1078833765347998E-4</v>
+        <v>-2.1603487907827999E-4</v>
       </c>
       <c r="O17">
-        <v>3.2858116218432656E-4</v>
+        <v>6.392274469379578E-5</v>
       </c>
       <c r="P17">
-        <v>1.6500386144731105E-4</v>
+        <v>-6.6392722773998554E-5</v>
       </c>
       <c r="Q17">
-        <v>5.5462697284404816E-5</v>
+        <v>2.4184711740874647E-4</v>
       </c>
       <c r="R17">
-        <v>2.6464642239895269E-3</v>
+        <v>8.0161284809879599E-4</v>
       </c>
       <c r="S17">
-        <v>2.4231744721639483E-4</v>
+        <v>-2.5894476776015498E-5</v>
       </c>
       <c r="T17">
-        <v>4.2541049751767645E-5</v>
+        <v>3.6416801490513889E-5</v>
       </c>
       <c r="U17">
-        <v>-1.9574497481106043E-4</v>
+        <v>1.0763621724097197E-4</v>
       </c>
       <c r="V17">
-        <v>-3.8583533472948372E-5</v>
+        <v>7.5575006893857752E-5</v>
       </c>
       <c r="W17">
-        <v>-1.5736251017265648E-4</v>
+        <v>1.2070144954812461E-4</v>
       </c>
       <c r="X17">
-        <v>-5.222322755109215E-5</v>
+        <v>1.1044952554318887E-4</v>
       </c>
       <c r="Y17">
-        <v>-1.5236968830351547E-4</v>
+        <v>1.2389858534860997E-4</v>
       </c>
       <c r="Z17">
-        <v>-1.6475223817242351E-4</v>
+        <v>4.7511272818472972E-4</v>
       </c>
       <c r="AA17">
-        <v>-5.3689993275541454E-6</v>
+        <v>1.8962679754172817E-5</v>
       </c>
       <c r="AB17">
-        <v>-1.5466067366424297E-4</v>
+        <v>1.7945779214186377E-4</v>
       </c>
       <c r="AC17">
-        <v>-1.1564785913779693E-4</v>
+        <v>2.9116251141705766E-4</v>
       </c>
       <c r="AD17">
-        <v>-1.0703690292183555E-4</v>
+        <v>-1.4906258453559575E-5</v>
       </c>
       <c r="AE17">
-        <v>-1.5415729884673434E-4</v>
+        <v>5.1735375042640626E-5</v>
       </c>
       <c r="AF17">
-        <v>-2.4922417955293484E-4</v>
+        <v>-2.4937886476859653E-5</v>
       </c>
       <c r="AG17">
-        <v>6.2377255584980605E-5</v>
+        <v>-1.3401442170895693E-4</v>
       </c>
       <c r="AH17">
-        <v>3.0846777140921557E-5</v>
+        <v>-1.0463586593841934E-4</v>
       </c>
       <c r="AI17">
-        <v>-3.1595952468371411E-5</v>
+        <v>-9.4955411713562793E-5</v>
       </c>
       <c r="AJ17">
-        <v>-1.5968204351363033E-4</v>
+        <v>6.1720142017724429E-5</v>
       </c>
       <c r="AK17">
-        <v>-1.8976451300693398E-4</v>
+        <v>1.0707419821768243E-3</v>
       </c>
       <c r="AL17">
-        <v>3.7055892597160842E-4</v>
-      </c>
-      <c r="AM17">
-        <v>-3.2763077183586742E-3</v>
+        <v>1.5884291220587734E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18">
-        <v>-4.5540269726481244E-2</v>
+        <v>4.3516100953845741E-3</v>
       </c>
       <c r="C18">
-        <v>1.5801831734942387E-4</v>
+        <v>-9.7798575979757556E-5</v>
       </c>
       <c r="D18">
-        <v>-1.601388897922904E-5</v>
+        <v>-9.4091939085051831E-6</v>
       </c>
       <c r="E18">
-        <v>2.4584522258767164E-7</v>
+        <v>1.660502179178264E-7</v>
       </c>
       <c r="F18">
-        <v>-2.2125336040080848E-7</v>
+        <v>2.0532801182330886E-7</v>
       </c>
       <c r="G18">
-        <v>1.9155909160501117E-6</v>
+        <v>-6.5391601548419619E-7</v>
       </c>
       <c r="H18">
-        <v>5.6675040727305641E-4</v>
+        <v>4.8251024376459147E-5</v>
       </c>
       <c r="I18">
-        <v>-3.8460353558475739E-4</v>
+        <v>-6.8841955017501753E-5</v>
       </c>
       <c r="J18">
-        <v>8.8346949707315608E-6</v>
+        <v>1.0348692034041617E-4</v>
       </c>
       <c r="K18">
-        <v>-1.574254551060068E-4</v>
+        <v>-5.3827987557869897E-5</v>
       </c>
       <c r="L18">
-        <v>1.431197937152819E-5</v>
+        <v>-8.1562631843719573E-5</v>
       </c>
       <c r="M18">
-        <v>9.3369207670772174E-5</v>
+        <v>-9.5978219377698985E-5</v>
       </c>
       <c r="N18">
-        <v>8.3699301924957704E-5</v>
+        <v>-3.561397520778368E-5</v>
       </c>
       <c r="O18">
-        <v>-2.1422874021677455E-4</v>
+        <v>1.1054582446912281E-5</v>
       </c>
       <c r="P18">
-        <v>6.4269692681587535E-5</v>
+        <v>2.508255560027211E-5</v>
       </c>
       <c r="Q18">
-        <v>-6.6489408119846044E-5</v>
+        <v>4.2485396126744807E-5</v>
       </c>
       <c r="R18">
-        <v>2.4231744721639483E-4</v>
+        <v>-2.5894476776015498E-5</v>
       </c>
       <c r="S18">
-        <v>8.017194251897159E-4</v>
+        <v>1.306669067404273E-4</v>
       </c>
       <c r="T18">
-        <v>-2.5921675100792663E-5</v>
+        <v>-2.4955748218541602E-5</v>
       </c>
       <c r="U18">
-        <v>3.7039167759277385E-5</v>
+        <v>-5.369479008496752E-5</v>
       </c>
       <c r="V18">
-        <v>1.0699876378717201E-4</v>
+        <v>-6.2330235486660751E-5</v>
       </c>
       <c r="W18">
-        <v>7.5559327029237023E-5</v>
+        <v>-6.0859718618287185E-5</v>
       </c>
       <c r="X18">
-        <v>1.2037808522880712E-4</v>
+        <v>-4.3631710935890158E-5</v>
       </c>
       <c r="Y18">
-        <v>1.1052571643032266E-4</v>
+        <v>-3.8511068326931106E-5</v>
       </c>
       <c r="Z18">
-        <v>1.2394643665575257E-4</v>
+        <v>-1.6431611009947236E-4</v>
       </c>
       <c r="AA18">
-        <v>4.7521946424553658E-4</v>
+        <v>-6.4341016670543079E-5</v>
       </c>
       <c r="AB18">
-        <v>1.876053680029683E-5</v>
+        <v>-6.7874054031758987E-5</v>
       </c>
       <c r="AC18">
-        <v>1.7942428263615577E-4</v>
+        <v>-9.5757965635501815E-5</v>
       </c>
       <c r="AD18">
-        <v>2.9121474408204417E-4</v>
+        <v>-8.7939373720460814E-5</v>
       </c>
       <c r="AE18">
-        <v>-1.502417581982781E-5</v>
+        <v>-4.5208238212029669E-5</v>
       </c>
       <c r="AF18">
-        <v>5.1607586754535972E-5</v>
+        <v>1.4291660648760806E-4</v>
       </c>
       <c r="AG18">
-        <v>-2.4943211079179053E-5</v>
+        <v>2.3549165937703648E-4</v>
       </c>
       <c r="AH18">
-        <v>-1.3443637459761707E-4</v>
+        <v>-4.9303328716974321E-7</v>
       </c>
       <c r="AI18">
-        <v>-1.049910511935942E-4</v>
+        <v>-2.44031792207694E-7</v>
       </c>
       <c r="AJ18">
-        <v>-9.5190001677382884E-5</v>
+        <v>-3.8020929355750063E-5</v>
       </c>
       <c r="AK18">
-        <v>5.9809645098635503E-5</v>
+        <v>-3.6295903438855748E-4</v>
       </c>
       <c r="AL18">
-        <v>1.0713418764131751E-3</v>
-      </c>
-      <c r="AM18">
-        <v>1.5916175450307393E-3</v>
+        <v>-9.7853815072540817E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>31</v>
       </c>
       <c r="B19">
-        <v>4.5204160718515084E-3</v>
+        <v>0.10500009155419515</v>
       </c>
       <c r="C19">
-        <v>4.2656410393490315E-6</v>
+        <v>8.7018067734567208E-4</v>
       </c>
       <c r="D19">
-        <v>-9.5665726314243978E-6</v>
+        <v>4.8811480853869313E-5</v>
       </c>
       <c r="E19">
-        <v>1.6843708670330163E-7</v>
+        <v>-7.7459425747652971E-7</v>
       </c>
       <c r="F19">
-        <v>2.1337060960061491E-7</v>
+        <v>8.7580721727992496E-6</v>
       </c>
       <c r="G19">
-        <v>-6.4546132997340329E-7</v>
+        <v>5.2282006539827995E-6</v>
       </c>
       <c r="H19">
-        <v>4.7770583733820942E-5</v>
+        <v>5.6545934320001089E-5</v>
       </c>
       <c r="I19">
-        <v>-6.8365461980768121E-5</v>
+        <v>-1.2503828804736401E-6</v>
       </c>
       <c r="J19">
-        <v>-1.6816302904749903E-7</v>
+        <v>-3.398453766931455E-4</v>
       </c>
       <c r="K19">
-        <v>4.4594799171312691E-6</v>
+        <v>4.2033250775927304E-4</v>
       </c>
       <c r="L19">
-        <v>-5.3831622007214242E-5</v>
+        <v>6.9320593683116572E-4</v>
       </c>
       <c r="M19">
-        <v>-8.1499009315189069E-5</v>
+        <v>7.8760388376139415E-4</v>
       </c>
       <c r="N19">
-        <v>-9.5783840142214154E-5</v>
+        <v>7.7383497077485931E-4</v>
       </c>
       <c r="O19">
-        <v>-3.5270793645733069E-5</v>
+        <v>-9.7169892346544236E-5</v>
       </c>
       <c r="P19">
-        <v>1.1047269542324134E-5</v>
+        <v>-9.1545456347768905E-5</v>
       </c>
       <c r="Q19">
-        <v>2.5166286468326615E-5</v>
+        <v>-1.9514606478398939E-4</v>
       </c>
       <c r="R19">
-        <v>4.2541049751767645E-5</v>
+        <v>3.6416801490513889E-5</v>
       </c>
       <c r="S19">
-        <v>-2.5921675100792663E-5</v>
+        <v>-2.4955748218541602E-5</v>
       </c>
       <c r="T19">
-        <v>1.3062833595923616E-4</v>
+        <v>1.1718914429542406E-3</v>
       </c>
       <c r="U19">
-        <v>-2.4812503364620309E-5</v>
+        <v>1.6816196024752749E-4</v>
       </c>
       <c r="V19">
-        <v>-5.3966196560097562E-5</v>
+        <v>2.2341737050153126E-4</v>
       </c>
       <c r="W19">
-        <v>-6.2296738726032481E-5</v>
+        <v>2.0506522737004279E-4</v>
       </c>
       <c r="X19">
-        <v>-6.0735581475498523E-5</v>
+        <v>2.2259619707391619E-4</v>
       </c>
       <c r="Y19">
-        <v>-4.3489910721889249E-5</v>
+        <v>1.8618809015172669E-4</v>
       </c>
       <c r="Z19">
-        <v>-3.8122597823805459E-5</v>
+        <v>2.9713506728380073E-4</v>
       </c>
       <c r="AA19">
-        <v>-1.6455209498085661E-4</v>
+        <v>1.1763993073281795E-4</v>
       </c>
       <c r="AB19">
-        <v>-6.44125421729281E-5</v>
+        <v>2.0036106367037369E-4</v>
       </c>
       <c r="AC19">
-        <v>-6.789967205686042E-5</v>
+        <v>1.5355421674384344E-4</v>
       </c>
       <c r="AD19">
-        <v>-9.5798756977432797E-5</v>
+        <v>2.3314160962631628E-4</v>
       </c>
       <c r="AE19">
-        <v>-8.807244877128838E-5</v>
+        <v>2.552069544261243E-4</v>
       </c>
       <c r="AF19">
-        <v>-4.5148932407947789E-5</v>
+        <v>-2.3013033238314802E-5</v>
       </c>
       <c r="AG19">
-        <v>1.4286261606888222E-4</v>
+        <v>-5.1638884831770471E-5</v>
       </c>
       <c r="AH19">
-        <v>2.3562612410413242E-4</v>
+        <v>-9.0171096759436077E-5</v>
       </c>
       <c r="AI19">
-        <v>-2.8317153302412357E-7</v>
+        <v>-6.0997626068332185E-5</v>
       </c>
       <c r="AJ19">
-        <v>-3.3869928338023381E-7</v>
+        <v>5.9211623298469356E-5</v>
       </c>
       <c r="AK19">
-        <v>-3.7605603984413281E-5</v>
+        <v>2.6882419343617157E-4</v>
       </c>
       <c r="AL19">
-        <v>-3.6303497510194183E-4</v>
-      </c>
-      <c r="AM19">
-        <v>-9.7808717481448343E-3</v>
+        <v>-5.9191310484509214E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>32</v>
       </c>
       <c r="B20">
-        <v>0.10399482938207391</v>
+        <v>-2.6414882107528709E-2</v>
       </c>
       <c r="C20">
-        <v>2.6953536944015945E-4</v>
+        <v>-9.3771685483352678E-4</v>
       </c>
       <c r="D20">
-        <v>4.9679579812241252E-5</v>
+        <v>9.0282821865002568E-5</v>
       </c>
       <c r="E20">
-        <v>-7.8718745398372455E-7</v>
+        <v>-1.5281358212027645E-6</v>
       </c>
       <c r="F20">
-        <v>8.7531560742377867E-6</v>
+        <v>-8.7372087316935154E-7</v>
       </c>
       <c r="G20">
-        <v>5.217889629269265E-6</v>
+        <v>8.9701525568045006E-7</v>
       </c>
       <c r="H20">
-        <v>6.0254852596545118E-5</v>
+        <v>-1.010516146360531E-4</v>
       </c>
       <c r="I20">
-        <v>-6.0995866492246113E-6</v>
+        <v>1.9359189002721156E-4</v>
       </c>
       <c r="J20">
-        <v>1.8164848259704974E-5</v>
+        <v>8.6567656666861959E-4</v>
       </c>
       <c r="K20">
-        <v>-1.8079210150238377E-4</v>
+        <v>4.0146537206704253E-4</v>
       </c>
       <c r="L20">
-        <v>4.23118614805335E-4</v>
+        <v>3.2307774575907543E-4</v>
       </c>
       <c r="M20">
-        <v>6.9349433310676007E-4</v>
+        <v>4.7735108126634065E-4</v>
       </c>
       <c r="N20">
-        <v>7.8626602026559301E-4</v>
+        <v>2.2891252522802051E-4</v>
       </c>
       <c r="O20">
-        <v>7.7095294283113845E-4</v>
+        <v>-1.4613705435898757E-4</v>
       </c>
       <c r="P20">
-        <v>-9.787883401485883E-5</v>
+        <v>-2.8902058776873053E-5</v>
       </c>
       <c r="Q20">
-        <v>-9.1413042880032208E-5</v>
+        <v>-3.7237435516096015E-5</v>
       </c>
       <c r="R20">
-        <v>-1.9574497481106043E-4</v>
+        <v>1.0763621724097197E-4</v>
       </c>
       <c r="S20">
-        <v>3.7039167759277385E-5</v>
+        <v>-5.369479008496752E-5</v>
       </c>
       <c r="T20">
-        <v>-2.4812503364620309E-5</v>
+        <v>1.6816196024752749E-4</v>
       </c>
       <c r="U20">
-        <v>1.172068050008315E-3</v>
+        <v>5.6224706508192232E-3</v>
       </c>
       <c r="V20">
-        <v>1.6793641247611179E-4</v>
+        <v>1.8348630122893644E-3</v>
       </c>
       <c r="W20">
-        <v>2.2372637562473324E-4</v>
+        <v>1.882222461360833E-3</v>
       </c>
       <c r="X20">
-        <v>2.0355423556118297E-4</v>
+        <v>1.800459284979964E-3</v>
       </c>
       <c r="Y20">
-        <v>2.2253288523920177E-4</v>
+        <v>1.7995724512835361E-3</v>
       </c>
       <c r="Z20">
-        <v>1.8445918258976085E-4</v>
+        <v>2.1666517481043878E-3</v>
       </c>
       <c r="AA20">
-        <v>2.9783195449737776E-4</v>
+        <v>1.8670109773249004E-3</v>
       </c>
       <c r="AB20">
-        <v>1.1783185069508162E-4</v>
+        <v>1.9346371975489636E-3</v>
       </c>
       <c r="AC20">
-        <v>2.0023478032212482E-4</v>
+        <v>1.9209148825839266E-3</v>
       </c>
       <c r="AD20">
-        <v>1.5330965533843198E-4</v>
+        <v>1.8921780405685503E-3</v>
       </c>
       <c r="AE20">
-        <v>2.3337092414353052E-4</v>
+        <v>1.9071583568653137E-3</v>
       </c>
       <c r="AF20">
-        <v>2.5510915916254154E-4</v>
+        <v>-5.6499350464947355E-5</v>
       </c>
       <c r="AG20">
-        <v>-2.2867368889623969E-5</v>
+        <v>2.6469155160787532E-5</v>
       </c>
       <c r="AH20">
-        <v>-5.1720934482023988E-5</v>
+        <v>1.8053653134589276E-4</v>
       </c>
       <c r="AI20">
-        <v>-8.9906477423526876E-5</v>
+        <v>5.6122115525973778E-4</v>
       </c>
       <c r="AJ20">
-        <v>-6.1479921442143424E-5</v>
+        <v>1.1836873575856084E-3</v>
       </c>
       <c r="AK20">
-        <v>6.0939893587249748E-5</v>
+        <v>1.8265705311134891E-3</v>
       </c>
       <c r="AL20">
-        <v>2.7051384568456491E-4</v>
-      </c>
-      <c r="AM20">
-        <v>-6.1422780239228474E-4</v>
+        <v>6.0438473745494468E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
       <c r="B21">
-        <v>-2.4978253874392342E-2</v>
+        <v>4.290597633466741E-2</v>
       </c>
       <c r="C21">
-        <v>1.902844531420186E-3</v>
+        <v>-1.2249971090131685E-6</v>
       </c>
       <c r="D21">
-        <v>9.2846445292611105E-5</v>
+        <v>9.5109976528795666E-5</v>
       </c>
       <c r="E21">
-        <v>-1.5673812507264997E-6</v>
+        <v>-1.4971063571341248E-6</v>
       </c>
       <c r="F21">
-        <v>-7.7375097741167755E-7</v>
+        <v>4.181324953945367E-6</v>
       </c>
       <c r="G21">
-        <v>1.013517422249263E-6</v>
+        <v>1.4325232378887304E-6</v>
       </c>
       <c r="H21">
-        <v>-1.061442103106992E-4</v>
+        <v>5.7443240310345921E-5</v>
       </c>
       <c r="I21">
-        <v>1.9800044682579117E-4</v>
+        <v>7.3366007915953431E-5</v>
       </c>
       <c r="J21">
-        <v>-1.0044735364836661E-4</v>
+        <v>5.648478999134427E-5</v>
       </c>
       <c r="K21">
-        <v>1.6621326349666396E-5</v>
+        <v>2.8210805328087032E-4</v>
       </c>
       <c r="L21">
-        <v>4.0002872243687646E-4</v>
+        <v>3.0908821597158876E-4</v>
       </c>
       <c r="M21">
-        <v>3.195578421782284E-4</v>
+        <v>3.9981735918099664E-4</v>
       </c>
       <c r="N21">
-        <v>4.7339784162513267E-4</v>
+        <v>1.8021347092630937E-4</v>
       </c>
       <c r="O21">
-        <v>2.2537628627035725E-4</v>
+        <v>-1.4593720770276163E-4</v>
       </c>
       <c r="P21">
-        <v>-1.4713758041230967E-4</v>
+        <v>-6.1162579146565715E-5</v>
       </c>
       <c r="Q21">
-        <v>-2.9105187571238537E-5</v>
+        <v>-1.5678340433674287E-4</v>
       </c>
       <c r="R21">
-        <v>-3.8583533472948372E-5</v>
+        <v>7.5575006893857752E-5</v>
       </c>
       <c r="S21">
-        <v>1.0699876378717201E-4</v>
+        <v>-6.2330235486660751E-5</v>
       </c>
       <c r="T21">
-        <v>-5.3966196560097562E-5</v>
+        <v>2.2341737050153126E-4</v>
       </c>
       <c r="U21">
-        <v>1.6793641247611179E-4</v>
+        <v>1.8348630122893644E-3</v>
       </c>
       <c r="V21">
-        <v>5.6288848609699843E-3</v>
+        <v>2.8612085673158294E-3</v>
       </c>
       <c r="W21">
-        <v>1.8382140872032072E-3</v>
+        <v>1.8354479885912508E-3</v>
       </c>
       <c r="X21">
-        <v>1.8869540482633375E-3</v>
+        <v>1.776217392515024E-3</v>
       </c>
       <c r="Y21">
-        <v>1.8046517476372425E-3</v>
+        <v>1.7708420949610066E-3</v>
       </c>
       <c r="Z21">
-        <v>1.8046496599184441E-3</v>
+        <v>2.0309898032322879E-3</v>
       </c>
       <c r="AA21">
-        <v>2.1703461420003434E-3</v>
+        <v>1.8113882579045601E-3</v>
       </c>
       <c r="AB21">
-        <v>1.8714191540346852E-3</v>
+        <v>1.8815832756291565E-3</v>
       </c>
       <c r="AC21">
-        <v>1.9389077337941055E-3</v>
+        <v>1.8667607528573295E-3</v>
       </c>
       <c r="AD21">
-        <v>1.9252022066267465E-3</v>
+        <v>1.8289124802721287E-3</v>
       </c>
       <c r="AE21">
-        <v>1.8962113864322235E-3</v>
+        <v>1.8610075630263855E-3</v>
       </c>
       <c r="AF21">
-        <v>1.9115358375099828E-3</v>
+        <v>-7.0412316212073401E-5</v>
       </c>
       <c r="AG21">
-        <v>-5.6545501402569348E-5</v>
+        <v>-1.1503186087038618E-4</v>
       </c>
       <c r="AH21">
-        <v>2.7696654529116359E-5</v>
+        <v>6.8074780378203788E-6</v>
       </c>
       <c r="AI21">
-        <v>1.7907900226452587E-4</v>
+        <v>4.6836300676074427E-4</v>
       </c>
       <c r="AJ21">
-        <v>5.6598799508010035E-4</v>
+        <v>1.0445037578769743E-3</v>
       </c>
       <c r="AK21">
-        <v>1.192465050895538E-3</v>
+        <v>1.3197456253007927E-3</v>
       </c>
       <c r="AL21">
-        <v>1.8284712075635947E-3</v>
-      </c>
-      <c r="AM21">
-        <v>5.694244609876992E-4</v>
+        <v>1.0058639878370102E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="B22">
-        <v>4.2732603908318206E-2</v>
+        <v>-3.1668889714538476E-2</v>
       </c>
       <c r="C22">
-        <v>-4.2078968384531845E-4</v>
+        <v>2.8817523859004485E-4</v>
       </c>
       <c r="D22">
-        <v>9.6049839352782768E-5</v>
+        <v>1.4294321974072071E-4</v>
       </c>
       <c r="E22">
-        <v>-1.511570356076153E-6</v>
+        <v>-2.1694465893661048E-6</v>
       </c>
       <c r="F22">
-        <v>4.1770817867399214E-6</v>
+        <v>2.477874233379201E-6</v>
       </c>
       <c r="G22">
-        <v>1.4319133921986429E-6</v>
+        <v>4.0825252324169498E-6</v>
       </c>
       <c r="H22">
-        <v>5.6004368058395029E-5</v>
+        <v>5.1214806810342197E-5</v>
       </c>
       <c r="I22">
-        <v>7.502088132318454E-5</v>
+        <v>1.501352840029798E-4</v>
       </c>
       <c r="J22">
-        <v>1.4630410075567972E-5</v>
+        <v>4.7669637045386304E-4</v>
       </c>
       <c r="K22">
-        <v>2.3205044540792878E-4</v>
+        <v>2.3602776669035918E-4</v>
       </c>
       <c r="L22">
-        <v>2.8432591744216606E-4</v>
+        <v>3.0251477329939277E-4</v>
       </c>
       <c r="M22">
-        <v>3.1030636134102356E-4</v>
+        <v>3.9852101608258116E-4</v>
       </c>
       <c r="N22">
-        <v>4.0092975978991524E-4</v>
+        <v>1.5262262650921849E-4</v>
       </c>
       <c r="O22">
-        <v>1.8070755620290459E-4</v>
+        <v>-1.534769365573822E-4</v>
       </c>
       <c r="P22">
-        <v>-1.46533462482834E-4</v>
+        <v>-5.8219880179834249E-5</v>
       </c>
       <c r="Q22">
-        <v>-6.117768884596783E-5</v>
+        <v>-5.0812769015288055E-5</v>
       </c>
       <c r="R22">
-        <v>-1.5736251017265648E-4</v>
+        <v>1.2070144954812461E-4</v>
       </c>
       <c r="S22">
-        <v>7.5559327029237023E-5</v>
+        <v>-6.0859718618287185E-5</v>
       </c>
       <c r="T22">
-        <v>-6.2296738726032481E-5</v>
+        <v>2.0506522737004279E-4</v>
       </c>
       <c r="U22">
-        <v>2.2372637562473324E-4</v>
+        <v>1.882222461360833E-3</v>
       </c>
       <c r="V22">
-        <v>1.8382140872032072E-3</v>
+        <v>1.8354479885912508E-3</v>
       </c>
       <c r="W22">
-        <v>2.8639670666372654E-3</v>
+        <v>3.2758118808703328E-3</v>
       </c>
       <c r="X22">
-        <v>1.8375474511509186E-3</v>
+        <v>1.8098791877475151E-3</v>
       </c>
       <c r="Y22">
-        <v>1.7783624958683359E-3</v>
+        <v>1.8041615919183259E-3</v>
       </c>
       <c r="Z22">
-        <v>1.7723813127954941E-3</v>
+        <v>2.1632966595566865E-3</v>
       </c>
       <c r="AA22">
-        <v>2.0331319873624805E-3</v>
+        <v>1.8520485904735449E-3</v>
       </c>
       <c r="AB22">
-        <v>1.8138084848835594E-3</v>
+        <v>1.9341792812432701E-3</v>
       </c>
       <c r="AC22">
-        <v>1.8838588098463408E-3</v>
+        <v>1.9322586562673014E-3</v>
       </c>
       <c r="AD22">
-        <v>1.8691447824575607E-3</v>
+        <v>1.8684394054824106E-3</v>
       </c>
       <c r="AE22">
-        <v>1.831359291587169E-3</v>
+        <v>1.8831430315509753E-3</v>
       </c>
       <c r="AF22">
-        <v>1.8631592445847028E-3</v>
+        <v>-6.4337940354237475E-5</v>
       </c>
       <c r="AG22">
-        <v>-7.0418644602849711E-5</v>
+        <v>-1.1550104900275498E-4</v>
       </c>
       <c r="AH22">
-        <v>-1.1471156441654853E-4</v>
+        <v>-1.3069947915023491E-4</v>
       </c>
       <c r="AI22">
-        <v>7.0811717903053787E-6</v>
+        <v>5.4374429515761371E-4</v>
       </c>
       <c r="AJ22">
-        <v>4.7015161629061102E-4</v>
+        <v>1.0631946224133367E-3</v>
       </c>
       <c r="AK22">
-        <v>1.0459547480446284E-3</v>
+        <v>1.7510267005242911E-3</v>
       </c>
       <c r="AL22">
-        <v>1.3219690394723712E-3</v>
-      </c>
-      <c r="AM22">
-        <v>9.86714475718041E-4</v>
+        <v>-9.5468859506385798E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23">
-        <v>-3.2182375588479237E-2</v>
+        <v>7.0711548906415192E-2</v>
       </c>
       <c r="C23">
-        <v>3.1282729485081831E-3</v>
+        <v>2.2170416128040903E-4</v>
       </c>
       <c r="D23">
-        <v>1.4738893742711622E-4</v>
+        <v>1.4957952847651922E-4</v>
       </c>
       <c r="E23">
-        <v>-2.2350821803436185E-6</v>
+        <v>-2.3550439380312498E-6</v>
       </c>
       <c r="F23">
-        <v>2.5002417636121492E-6</v>
+        <v>3.7111969354215519E-6</v>
       </c>
       <c r="G23">
-        <v>4.1110386517951639E-6</v>
+        <v>-3.9216534051962537E-7</v>
       </c>
       <c r="H23">
-        <v>5.1786596857600319E-5</v>
+        <v>1.3098028467256766E-5</v>
       </c>
       <c r="I23">
-        <v>1.4835485397564189E-4</v>
+        <v>6.0242611992599132E-5</v>
       </c>
       <c r="J23">
-        <v>-1.4033655014624444E-4</v>
+        <v>-3.1364590772588083E-5</v>
       </c>
       <c r="K23">
-        <v>3.243693030422351E-4</v>
+        <v>2.7922672978385773E-4</v>
       </c>
       <c r="L23">
-        <v>2.3751868632867988E-4</v>
+        <v>2.6260483901056946E-4</v>
       </c>
       <c r="M23">
-        <v>2.9949997852634518E-4</v>
+        <v>2.75904763468659E-4</v>
       </c>
       <c r="N23">
-        <v>3.9312453551718291E-4</v>
+        <v>1.2484016354407485E-4</v>
       </c>
       <c r="O23">
-        <v>1.453625021515177E-4</v>
+        <v>-1.5348880824856857E-4</v>
       </c>
       <c r="P23">
-        <v>-1.5572552061725263E-4</v>
+        <v>-7.278238942481612E-5</v>
       </c>
       <c r="Q23">
-        <v>-5.7833762470660096E-5</v>
+        <v>-1.5137691416454419E-4</v>
       </c>
       <c r="R23">
-        <v>-5.222322755109215E-5</v>
+        <v>1.1044952554318887E-4</v>
       </c>
       <c r="S23">
-        <v>1.2037808522880712E-4</v>
+        <v>-4.3631710935890158E-5</v>
       </c>
       <c r="T23">
-        <v>-6.0735581475498523E-5</v>
+        <v>2.2259619707391619E-4</v>
       </c>
       <c r="U23">
-        <v>2.0355423556118297E-4</v>
+        <v>1.800459284979964E-3</v>
       </c>
       <c r="V23">
-        <v>1.8869540482633375E-3</v>
+        <v>1.776217392515024E-3</v>
       </c>
       <c r="W23">
-        <v>1.8375474511509186E-3</v>
+        <v>1.8098791877475151E-3</v>
       </c>
       <c r="X23">
-        <v>3.276453272017494E-3</v>
+        <v>3.3033366221129311E-3</v>
       </c>
       <c r="Y23">
-        <v>1.8115640191715707E-3</v>
+        <v>1.7584267745646693E-3</v>
       </c>
       <c r="Z23">
-        <v>1.8048514837773852E-3</v>
+        <v>1.9567478024411552E-3</v>
       </c>
       <c r="AA23">
-        <v>2.1656771779103592E-3</v>
+        <v>1.8030008205559456E-3</v>
       </c>
       <c r="AB23">
-        <v>1.8547322432379959E-3</v>
+        <v>1.8573647739284708E-3</v>
       </c>
       <c r="AC23">
-        <v>1.9363596856763388E-3</v>
+        <v>1.8532024385665112E-3</v>
       </c>
       <c r="AD23">
-        <v>1.9346883420801573E-3</v>
+        <v>1.7983825340473002E-3</v>
       </c>
       <c r="AE23">
-        <v>1.8707892840616946E-3</v>
+        <v>1.8569513397162542E-3</v>
       </c>
       <c r="AF23">
-        <v>1.8853605580632167E-3</v>
+        <v>-5.2430183193363119E-5</v>
       </c>
       <c r="AG23">
-        <v>-6.4183289550642528E-5</v>
+        <v>-1.9549359270589297E-5</v>
       </c>
       <c r="AH23">
-        <v>-1.1456906563213652E-4</v>
+        <v>1.8168399997780496E-5</v>
       </c>
       <c r="AI23">
-        <v>-1.3049895254920043E-4</v>
+        <v>4.5968359914726941E-4</v>
       </c>
       <c r="AJ23">
-        <v>5.4650575482159214E-4</v>
+        <v>1.0785559956834681E-3</v>
       </c>
       <c r="AK23">
-        <v>1.0683784807115457E-3</v>
+        <v>9.837932987819104E-4</v>
       </c>
       <c r="AL23">
-        <v>1.7545619587290514E-3</v>
-      </c>
-      <c r="AM23">
-        <v>-1.7552611036087025E-4</v>
+        <v>-1.026965352970967E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24">
-        <v>7.0427692708390721E-2</v>
+        <v>3.1999259160062458E-2</v>
       </c>
       <c r="C24">
-        <v>1.0127885788091227E-3</v>
+        <v>1.102008510883299E-3</v>
       </c>
       <c r="D24">
-        <v>1.5154543250395377E-4</v>
+        <v>1.522214887798481E-4</v>
       </c>
       <c r="E24">
-        <v>-2.384910570128792E-6</v>
+        <v>-2.3108283910585996E-6</v>
       </c>
       <c r="F24">
-        <v>3.7321480385991278E-6</v>
+        <v>3.5188522756026945E-6</v>
       </c>
       <c r="G24">
-        <v>-3.7193613904528546E-7</v>
+        <v>1.8264595018545865E-6</v>
       </c>
       <c r="H24">
-        <v>1.4192249953443484E-5</v>
+        <v>-8.8017565309023925E-5</v>
       </c>
       <c r="I24">
-        <v>5.8315982110936169E-5</v>
+        <v>1.5150240584839176E-4</v>
       </c>
       <c r="J24">
-        <v>-4.2020204484788403E-5</v>
+        <v>-9.2050964474666428E-4</v>
       </c>
       <c r="K24">
-        <v>3.2180960662535991E-5</v>
+        <v>2.388123506821443E-4</v>
       </c>
       <c r="L24">
-        <v>2.807481192233791E-4</v>
+        <v>2.2454866027842471E-4</v>
       </c>
       <c r="M24">
-        <v>2.6217183029218305E-4</v>
+        <v>2.1965349500105156E-4</v>
       </c>
       <c r="N24">
-        <v>2.7451183181376784E-4</v>
+        <v>2.1083847500673997E-5</v>
       </c>
       <c r="O24">
-        <v>1.224207816128172E-4</v>
+        <v>-1.7112612614779134E-4</v>
       </c>
       <c r="P24">
-        <v>-1.5451330389274945E-4</v>
+        <v>-4.0865569470503789E-5</v>
       </c>
       <c r="Q24">
-        <v>-7.2886696618612302E-5</v>
+        <v>-1.6311854147984481E-4</v>
       </c>
       <c r="R24">
-        <v>-1.5236968830351547E-4</v>
+        <v>1.2389858534860997E-4</v>
       </c>
       <c r="S24">
-        <v>1.1052571643032266E-4</v>
+        <v>-3.8511068326931106E-5</v>
       </c>
       <c r="T24">
-        <v>-4.3489910721889249E-5</v>
+        <v>1.8618809015172669E-4</v>
       </c>
       <c r="U24">
-        <v>2.2253288523920177E-4</v>
+        <v>1.7995724512835361E-3</v>
       </c>
       <c r="V24">
-        <v>1.8046517476372425E-3</v>
+        <v>1.7708420949610066E-3</v>
       </c>
       <c r="W24">
-        <v>1.7783624958683359E-3</v>
+        <v>1.8041615919183259E-3</v>
       </c>
       <c r="X24">
-        <v>1.8115640191715707E-3</v>
+        <v>1.7584267745646693E-3</v>
       </c>
       <c r="Y24">
-        <v>3.3048568252568833E-3</v>
+        <v>3.2382409320086277E-3</v>
       </c>
       <c r="Z24">
-        <v>1.7595746483663084E-3</v>
+        <v>1.9558405663298861E-3</v>
       </c>
       <c r="AA24">
-        <v>1.9588488570942207E-3</v>
+        <v>1.7887210481933806E-3</v>
       </c>
       <c r="AB24">
-        <v>1.8053382438442285E-3</v>
+        <v>1.8462995632666404E-3</v>
       </c>
       <c r="AC24">
-        <v>1.8595123161974062E-3</v>
+        <v>1.8357093467472993E-3</v>
       </c>
       <c r="AD24">
-        <v>1.8553795633777792E-3</v>
+        <v>1.7878342997027963E-3</v>
       </c>
       <c r="AE24">
-        <v>1.8006777375628061E-3</v>
+        <v>1.8329763815158643E-3</v>
       </c>
       <c r="AF24">
-        <v>1.8590195649157183E-3</v>
+        <v>-5.0786148394265244E-5</v>
       </c>
       <c r="AG24">
-        <v>-5.2263685145797923E-5</v>
+        <v>4.0742151102146553E-5</v>
       </c>
       <c r="AH24">
-        <v>-1.9034038251386563E-5</v>
+        <v>-7.5674714735055396E-5</v>
       </c>
       <c r="AI24">
-        <v>1.8168006827741002E-5</v>
+        <v>3.6206250781035688E-4</v>
       </c>
       <c r="AJ24">
-        <v>4.6125226273772317E-4</v>
+        <v>1.025034530679973E-3</v>
       </c>
       <c r="AK24">
-        <v>1.0814777353295977E-3</v>
+        <v>1.2080313465170607E-3</v>
       </c>
       <c r="AL24">
-        <v>9.8541773840157961E-4</v>
-      </c>
-      <c r="AM24">
-        <v>-1.0711311331634641E-3</v>
+        <v>-1.4869029737390638E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
       <c r="B25">
-        <v>3.1384347863801065E-2</v>
+        <v>0.1297071041261269</v>
       </c>
       <c r="C25">
-        <v>4.6484011538466055E-3</v>
+        <v>6.0860812483458197E-4</v>
       </c>
       <c r="D25">
-        <v>1.5668875697035867E-4</v>
+        <v>2.3001583499728407E-4</v>
       </c>
       <c r="E25">
-        <v>-2.3770173722359006E-6</v>
+        <v>-3.6840682382367713E-6</v>
       </c>
       <c r="F25">
-        <v>3.5364610955665252E-6</v>
+        <v>8.1608263439468179E-6</v>
       </c>
       <c r="G25">
-        <v>1.8351626077604833E-6</v>
+        <v>9.7814839245484843E-6</v>
       </c>
       <c r="H25">
-        <v>-8.0610294619450746E-5</v>
+        <v>5.1332756511115497E-4</v>
       </c>
       <c r="I25">
-        <v>1.4220932154272194E-4</v>
+        <v>2.4698874046062908E-4</v>
       </c>
       <c r="J25">
-        <v>-1.8887447626586258E-4</v>
+        <v>-6.0535343917145689E-4</v>
       </c>
       <c r="K25">
-        <v>-7.6101030231040035E-4</v>
+        <v>4.4083295800708073E-4</v>
       </c>
       <c r="L25">
-        <v>2.3890033862659216E-4</v>
+        <v>5.9929928550424933E-4</v>
       </c>
       <c r="M25">
-        <v>2.2087310537970354E-4</v>
+        <v>1.1219324090366836E-3</v>
       </c>
       <c r="N25">
-        <v>2.1440102670977417E-4</v>
+        <v>3.400616264403434E-4</v>
       </c>
       <c r="O25">
-        <v>1.2487049385115888E-5</v>
+        <v>-9.5996459987674246E-5</v>
       </c>
       <c r="P25">
-        <v>-1.729765474145342E-4</v>
+        <v>-1.3966093208154777E-4</v>
       </c>
       <c r="Q25">
-        <v>-4.110478433166604E-5</v>
+        <v>-4.5029204461077658E-6</v>
       </c>
       <c r="R25">
-        <v>-1.6475223817242351E-4</v>
+        <v>4.7511272818472972E-4</v>
       </c>
       <c r="S25">
-        <v>1.2394643665575257E-4</v>
+        <v>-1.6431611009947236E-4</v>
       </c>
       <c r="T25">
-        <v>-3.8122597823805459E-5</v>
+        <v>2.9713506728380073E-4</v>
       </c>
       <c r="U25">
-        <v>1.8445918258976085E-4</v>
+        <v>2.1666517481043878E-3</v>
       </c>
       <c r="V25">
-        <v>1.8046496599184441E-3</v>
+        <v>2.0309898032322879E-3</v>
       </c>
       <c r="W25">
-        <v>1.7723813127954941E-3</v>
+        <v>2.1632966595566865E-3</v>
       </c>
       <c r="X25">
-        <v>1.8048514837773852E-3</v>
+        <v>1.9567478024411552E-3</v>
       </c>
       <c r="Y25">
-        <v>1.7595746483663084E-3</v>
+        <v>1.9558405663298861E-3</v>
       </c>
       <c r="Z25">
-        <v>3.2383339720640923E-3</v>
+        <v>4.6321186847695555E-3</v>
       </c>
       <c r="AA25">
-        <v>1.9578392833900574E-3</v>
+        <v>2.0110122264670764E-3</v>
       </c>
       <c r="AB25">
-        <v>1.7909779590045991E-3</v>
+        <v>2.2050386899664888E-3</v>
       </c>
       <c r="AC25">
-        <v>1.8481329394425977E-3</v>
+        <v>2.1362311863101302E-3</v>
       </c>
       <c r="AD25">
-        <v>1.8373947820576827E-3</v>
+        <v>1.9954592492396517E-3</v>
       </c>
       <c r="AE25">
-        <v>1.7900606471617109E-3</v>
+        <v>2.0155004804722275E-3</v>
       </c>
       <c r="AF25">
-        <v>1.8343529681997246E-3</v>
+        <v>-1.2817537535796022E-4</v>
       </c>
       <c r="AG25">
-        <v>-5.0537062479261674E-5</v>
+        <v>-6.7574854544676392E-4</v>
       </c>
       <c r="AH25">
-        <v>4.2870351143301096E-5</v>
+        <v>-5.8225179389595038E-4</v>
       </c>
       <c r="AI25">
-        <v>-7.4774059216048026E-5</v>
+        <v>4.7282201911867579E-4</v>
       </c>
       <c r="AJ25">
-        <v>3.6331976278472175E-4</v>
+        <v>7.731054847294178E-4</v>
       </c>
       <c r="AK25">
-        <v>1.0298147281452231E-3</v>
+        <v>5.020944841527499E-3</v>
       </c>
       <c r="AL25">
-        <v>1.2107695286829399E-3</v>
-      </c>
-      <c r="AM25">
-        <v>-1.581823136913917E-3</v>
+        <v>4.4075115370711855E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
       <c r="B26">
-        <v>0.1297355728563544</v>
+        <v>3.7723388271779339E-2</v>
       </c>
       <c r="C26">
-        <v>7.6515203382841734E-4</v>
+        <v>-1.0433591577804367E-4</v>
       </c>
       <c r="D26">
-        <v>2.3127474920511294E-4</v>
+        <v>1.5017107308375248E-4</v>
       </c>
       <c r="E26">
-        <v>-3.7045828273597422E-6</v>
+        <v>-2.2770008120483541E-6</v>
       </c>
       <c r="F26">
-        <v>8.1712250969380375E-6</v>
+        <v>-2.5072124823440873E-6</v>
       </c>
       <c r="G26">
-        <v>9.7908763369184703E-6</v>
+        <v>-9.8207946639996487E-7</v>
       </c>
       <c r="H26">
-        <v>5.1362445921747293E-4</v>
+        <v>-4.3541339373581928E-4</v>
       </c>
       <c r="I26">
-        <v>2.4707759380090087E-4</v>
+        <v>5.5491304822533711E-4</v>
       </c>
       <c r="J26">
-        <v>-2.8559050693349741E-6</v>
+        <v>2.1447403892814243E-4</v>
       </c>
       <c r="K26">
-        <v>-6.5997514466694697E-4</v>
+        <v>2.5766761989525063E-4</v>
       </c>
       <c r="L26">
-        <v>4.4336279919422262E-4</v>
+        <v>2.648822735723175E-4</v>
       </c>
       <c r="M26">
-        <v>6.0082668208853761E-4</v>
+        <v>2.5831725145798712E-4</v>
       </c>
       <c r="N26">
-        <v>1.1234897134512185E-3</v>
+        <v>1.2461962975315191E-4</v>
       </c>
       <c r="O26">
-        <v>3.4089208222259134E-4</v>
+        <v>-1.5851426410824044E-4</v>
       </c>
       <c r="P26">
-        <v>-9.6446162468214911E-5</v>
+        <v>-4.032931878466916E-5</v>
       </c>
       <c r="Q26">
-        <v>-1.3997903167193724E-4</v>
+        <v>-1.5371937325589797E-4</v>
       </c>
       <c r="R26">
-        <v>-5.3689993275541454E-6</v>
+        <v>1.8962679754172817E-5</v>
       </c>
       <c r="S26">
-        <v>4.7521946424553658E-4</v>
+        <v>-6.4341016670543079E-5</v>
       </c>
       <c r="T26">
-        <v>-1.6455209498085661E-4</v>
+        <v>1.1763993073281795E-4</v>
       </c>
       <c r="U26">
-        <v>2.9783195449737776E-4</v>
+        <v>1.8670109773249004E-3</v>
       </c>
       <c r="V26">
-        <v>2.1703461420003434E-3</v>
+        <v>1.8113882579045601E-3</v>
       </c>
       <c r="W26">
-        <v>2.0331319873624805E-3</v>
+        <v>1.8520485904735449E-3</v>
       </c>
       <c r="X26">
-        <v>2.1656771779103592E-3</v>
+        <v>1.8030008205559456E-3</v>
       </c>
       <c r="Y26">
-        <v>1.9588488570942207E-3</v>
+        <v>1.7887210481933806E-3</v>
       </c>
       <c r="Z26">
-        <v>1.9578392833900574E-3</v>
+        <v>2.0110122264670764E-3</v>
       </c>
       <c r="AA26">
-        <v>4.6355185930657735E-3</v>
+        <v>2.8966639682518006E-3</v>
       </c>
       <c r="AB26">
-        <v>2.013542077360216E-3</v>
+        <v>1.8938117967053844E-3</v>
       </c>
       <c r="AC26">
-        <v>2.2073041928373869E-3</v>
+        <v>1.8763353271686873E-3</v>
       </c>
       <c r="AD26">
-        <v>2.138660646256332E-3</v>
+        <v>1.8376063185178747E-3</v>
       </c>
       <c r="AE26">
-        <v>1.9973862959721364E-3</v>
+        <v>1.8777138585094276E-3</v>
       </c>
       <c r="AF26">
-        <v>2.0176319441087276E-3</v>
+        <v>-6.3636035500774953E-5</v>
       </c>
       <c r="AG26">
-        <v>-1.2833422910895302E-4</v>
+        <v>-2.2812092868332323E-4</v>
       </c>
       <c r="AH26">
-        <v>-6.7689183050250389E-4</v>
+        <v>-1.2489949214035433E-4</v>
       </c>
       <c r="AI26">
-        <v>-5.8362009018309057E-4</v>
+        <v>4.2061135733532478E-4</v>
       </c>
       <c r="AJ26">
-        <v>4.7458974699143841E-4</v>
+        <v>1.3813809201118979E-3</v>
       </c>
       <c r="AK26">
-        <v>7.7340329807507719E-4</v>
+        <v>1.1035429547748919E-3</v>
       </c>
       <c r="AL26">
-        <v>5.0221945784018193E-3</v>
-      </c>
-      <c r="AM26">
-        <v>4.4012924686034635E-3</v>
+        <v>6.5950443506066804E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>39</v>
       </c>
       <c r="B27">
-        <v>3.7981810724308493E-2</v>
+        <v>6.4956515305753484E-2</v>
       </c>
       <c r="C27">
-        <v>8.5970609113847005E-4</v>
+        <v>1.7390887743631259E-4</v>
       </c>
       <c r="D27">
-        <v>1.5183862144004716E-4</v>
+        <v>1.5722206879967976E-4</v>
       </c>
       <c r="E27">
-        <v>-2.3021296811079331E-6</v>
+        <v>-2.4242600517062153E-6</v>
       </c>
       <c r="F27">
-        <v>-2.5047098233279031E-6</v>
+        <v>3.1383821790104906E-6</v>
       </c>
       <c r="G27">
-        <v>-9.6728675311149723E-7</v>
+        <v>2.8110374706222935E-6</v>
       </c>
       <c r="H27">
-        <v>-4.3773600020082393E-4</v>
+        <v>2.4053366854456625E-5</v>
       </c>
       <c r="I27">
-        <v>5.5716790745972879E-4</v>
+        <v>1.7346262185645629E-4</v>
       </c>
       <c r="J27">
-        <v>-4.5521928063401736E-5</v>
+        <v>2.5266815975404078E-6</v>
       </c>
       <c r="K27">
-        <v>2.1542303047263425E-4</v>
+        <v>2.2500867098353307E-4</v>
       </c>
       <c r="L27">
-        <v>2.5997363204390261E-4</v>
+        <v>2.6101166839156021E-4</v>
       </c>
       <c r="M27">
-        <v>2.6518396582563426E-4</v>
+        <v>3.3814898750980849E-4</v>
       </c>
       <c r="N27">
-        <v>2.5846836761566716E-4</v>
+        <v>1.0001937802377913E-4</v>
       </c>
       <c r="O27">
-        <v>1.2424306516707037E-4</v>
+        <v>-1.5227428990887746E-4</v>
       </c>
       <c r="P27">
-        <v>-1.5940032805199261E-4</v>
+        <v>-2.9799196378727452E-5</v>
       </c>
       <c r="Q27">
-        <v>-4.0410406948740833E-5</v>
+        <v>-1.1468064486220317E-4</v>
       </c>
       <c r="R27">
-        <v>-1.5466067366424297E-4</v>
+        <v>1.7945779214186377E-4</v>
       </c>
       <c r="S27">
-        <v>1.876053680029683E-5</v>
+        <v>-6.7874054031758987E-5</v>
       </c>
       <c r="T27">
-        <v>-6.44125421729281E-5</v>
+        <v>2.0036106367037369E-4</v>
       </c>
       <c r="U27">
-        <v>1.1783185069508162E-4</v>
+        <v>1.9346371975489636E-3</v>
       </c>
       <c r="V27">
-        <v>1.8714191540346852E-3</v>
+        <v>1.8815832756291565E-3</v>
       </c>
       <c r="W27">
-        <v>1.8138084848835594E-3</v>
+        <v>1.9341792812432701E-3</v>
       </c>
       <c r="X27">
-        <v>1.8547322432379959E-3</v>
+        <v>1.8573647739284708E-3</v>
       </c>
       <c r="Y27">
-        <v>1.8053382438442285E-3</v>
+        <v>1.8462995632666404E-3</v>
       </c>
       <c r="Z27">
-        <v>1.7909779590045991E-3</v>
+        <v>2.2050386899664888E-3</v>
       </c>
       <c r="AA27">
-        <v>2.013542077360216E-3</v>
+        <v>1.8938117967053844E-3</v>
       </c>
       <c r="AB27">
-        <v>2.8995662485676479E-3</v>
+        <v>3.3318764632824858E-3</v>
       </c>
       <c r="AC27">
-        <v>1.8964571787716943E-3</v>
+        <v>1.9688336433732858E-3</v>
       </c>
       <c r="AD27">
-        <v>1.8790573926520363E-3</v>
+        <v>1.9275678688464232E-3</v>
       </c>
       <c r="AE27">
-        <v>1.8401733366525392E-3</v>
+        <v>1.9420807917101784E-3</v>
       </c>
       <c r="AF27">
-        <v>1.8802873543835987E-3</v>
+        <v>-7.5059973846014532E-5</v>
       </c>
       <c r="AG27">
-        <v>-6.370043657908517E-5</v>
+        <v>-1.3739843543340434E-4</v>
       </c>
       <c r="AH27">
-        <v>-2.2809238433694427E-4</v>
+        <v>-6.7056601599595677E-5</v>
       </c>
       <c r="AI27">
-        <v>-1.2542946034105416E-4</v>
+        <v>6.0038568062309948E-4</v>
       </c>
       <c r="AJ27">
-        <v>4.22535956951722E-4</v>
+        <v>1.147101839345168E-3</v>
       </c>
       <c r="AK27">
-        <v>1.3840934479318586E-3</v>
+        <v>1.7756404352799533E-3</v>
       </c>
       <c r="AL27">
-        <v>1.105995988530035E-3</v>
-      </c>
-      <c r="AM27">
-        <v>6.3516295862781763E-4</v>
+        <v>2.9091441605154453E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
       <c r="B28">
-        <v>6.5049377975146719E-2</v>
+        <v>7.4729049316063681E-2</v>
       </c>
       <c r="C28">
-        <v>1.6633114158268476E-3</v>
+        <v>4.2150156616949704E-4</v>
       </c>
       <c r="D28">
-        <v>1.5924702969909491E-4</v>
+        <v>1.8376037510583706E-4</v>
       </c>
       <c r="E28">
-        <v>-2.455036524541244E-6</v>
+        <v>-2.8065650005086082E-6</v>
       </c>
       <c r="F28">
-        <v>3.1565156439593024E-6</v>
+        <v>-1.5082257809676658E-7</v>
       </c>
       <c r="G28">
-        <v>2.8429218507974838E-6</v>
+        <v>8.9143827766621967E-7</v>
       </c>
       <c r="H28">
-        <v>2.4277393921594384E-5</v>
+        <v>7.8760472681513923E-5</v>
       </c>
       <c r="I28">
-        <v>1.7283705511705666E-4</v>
+        <v>2.8296198670110405E-4</v>
       </c>
       <c r="J28">
-        <v>-6.6977029962653417E-5</v>
+        <v>-1.9530136455112886E-4</v>
       </c>
       <c r="K28">
-        <v>-1.3360423639818017E-4</v>
+        <v>2.5382482555075464E-4</v>
       </c>
       <c r="L28">
-        <v>2.2619494225128785E-4</v>
+        <v>5.1786952389974012E-4</v>
       </c>
       <c r="M28">
-        <v>2.6082141306422627E-4</v>
+        <v>4.9376538997072332E-4</v>
       </c>
       <c r="N28">
-        <v>3.3705903448900747E-4</v>
+        <v>2.5647592363216721E-4</v>
       </c>
       <c r="O28">
-        <v>9.8170308284608145E-5</v>
+        <v>-9.1240735139923789E-5</v>
       </c>
       <c r="P28">
-        <v>-1.5322882595677952E-4</v>
+        <v>-1.2357253197622882E-4</v>
       </c>
       <c r="Q28">
-        <v>-2.9898629570002986E-5</v>
+        <v>-1.0604325568780706E-4</v>
       </c>
       <c r="R28">
-        <v>-1.1564785913779693E-4</v>
+        <v>2.9116251141705766E-4</v>
       </c>
       <c r="S28">
-        <v>1.7942428263615577E-4</v>
+        <v>-9.5757965635501815E-5</v>
       </c>
       <c r="T28">
-        <v>-6.789967205686042E-5</v>
+        <v>1.5355421674384344E-4</v>
       </c>
       <c r="U28">
-        <v>2.0023478032212482E-4</v>
+        <v>1.9209148825839266E-3</v>
       </c>
       <c r="V28">
-        <v>1.9389077337941055E-3</v>
+        <v>1.8667607528573295E-3</v>
       </c>
       <c r="W28">
-        <v>1.8838588098463408E-3</v>
+        <v>1.9322586562673014E-3</v>
       </c>
       <c r="X28">
-        <v>1.9363596856763388E-3</v>
+        <v>1.8532024385665112E-3</v>
       </c>
       <c r="Y28">
-        <v>1.8595123161974062E-3</v>
+        <v>1.8357093467472993E-3</v>
       </c>
       <c r="Z28">
-        <v>1.8481329394425977E-3</v>
+        <v>2.1362311863101302E-3</v>
       </c>
       <c r="AA28">
-        <v>2.2073041928373869E-3</v>
+        <v>1.8763353271686873E-3</v>
       </c>
       <c r="AB28">
-        <v>1.8964571787716943E-3</v>
+        <v>1.9688336433732858E-3</v>
       </c>
       <c r="AC28">
-        <v>3.3347291152713309E-3</v>
+        <v>4.0962981621967248E-3</v>
       </c>
       <c r="AD28">
-        <v>1.9714239441752644E-3</v>
+        <v>1.8991714272233189E-3</v>
       </c>
       <c r="AE28">
-        <v>1.9299755060135848E-3</v>
+        <v>1.9338329731531669E-3</v>
       </c>
       <c r="AF28">
-        <v>1.9444866366701164E-3</v>
+        <v>-9.8990169686980815E-5</v>
       </c>
       <c r="AG28">
-        <v>-7.509834003771518E-5</v>
+        <v>-2.2677823573466417E-4</v>
       </c>
       <c r="AH28">
-        <v>-1.3720930906776125E-4</v>
+        <v>-2.1625297835409956E-4</v>
       </c>
       <c r="AI28">
-        <v>-6.7644282914914537E-5</v>
+        <v>5.5479371773590536E-4</v>
       </c>
       <c r="AJ28">
-        <v>6.0229692131918413E-4</v>
+        <v>1.1120213918337631E-3</v>
       </c>
       <c r="AK28">
-        <v>1.1502191678555357E-3</v>
+        <v>1.5524630189226868E-3</v>
       </c>
       <c r="AL28">
-        <v>1.7772742010037893E-3</v>
-      </c>
-      <c r="AM28">
-        <v>2.5779861418317269E-4</v>
+        <v>1.9276042925722818E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>41</v>
       </c>
       <c r="B29">
-        <v>7.4778110564061542E-2</v>
+        <v>-2.9344845719019704E-3</v>
       </c>
       <c r="C29">
-        <v>1.4579493041662131E-3</v>
+        <v>-2.7034115967591171E-4</v>
       </c>
       <c r="D29">
-        <v>1.8599681349886019E-4</v>
+        <v>1.335043261163157E-4</v>
       </c>
       <c r="E29">
-        <v>-2.8403958278397198E-6</v>
+        <v>-2.2153366493178161E-6</v>
       </c>
       <c r="F29">
-        <v>-1.4512099916266097E-7</v>
+        <v>8.4135725862100867E-6</v>
       </c>
       <c r="G29">
-        <v>8.936371113085172E-7</v>
+        <v>2.5059132272244864E-6</v>
       </c>
       <c r="H29">
-        <v>7.8435055300698567E-5</v>
+        <v>-7.8337378463319844E-4</v>
       </c>
       <c r="I29">
-        <v>2.8290724321893706E-4</v>
+        <v>7.8150471258504406E-4</v>
       </c>
       <c r="J29">
-        <v>-5.0171976386988735E-5</v>
+        <v>3.0514642471913937E-4</v>
       </c>
       <c r="K29">
-        <v>-1.8526023193919422E-4</v>
+        <v>9.6613041658874353E-5</v>
       </c>
       <c r="L29">
-        <v>2.5567747635024066E-4</v>
+        <v>1.4349521267512056E-4</v>
       </c>
       <c r="M29">
-        <v>5.1749178505540666E-4</v>
+        <v>3.5244047450889521E-4</v>
       </c>
       <c r="N29">
-        <v>4.9276383720333607E-4</v>
+        <v>8.7078311087619757E-5</v>
       </c>
       <c r="O29">
-        <v>2.5465003291989964E-4</v>
+        <v>-7.6497461349766695E-5</v>
       </c>
       <c r="P29">
-        <v>-9.220187852812493E-5</v>
+        <v>-1.195201122290816E-4</v>
       </c>
       <c r="Q29">
-        <v>-1.2382371359395569E-4</v>
+        <v>-1.5319049780141862E-4</v>
       </c>
       <c r="R29">
-        <v>-1.0703690292183555E-4</v>
+        <v>-1.4906258453559575E-5</v>
       </c>
       <c r="S29">
-        <v>2.9121474408204417E-4</v>
+        <v>-8.7939373720460814E-5</v>
       </c>
       <c r="T29">
-        <v>-9.5798756977432797E-5</v>
+        <v>2.3314160962631628E-4</v>
       </c>
       <c r="U29">
-        <v>1.5330965533843198E-4</v>
+        <v>1.8921780405685503E-3</v>
       </c>
       <c r="V29">
-        <v>1.9252022066267465E-3</v>
+        <v>1.8289124802721287E-3</v>
       </c>
       <c r="W29">
-        <v>1.8691447824575607E-3</v>
+        <v>1.8684394054824106E-3</v>
       </c>
       <c r="X29">
-        <v>1.9346883420801573E-3</v>
+        <v>1.7983825340473002E-3</v>
       </c>
       <c r="Y29">
-        <v>1.8553795633777792E-3</v>
+        <v>1.7878342997027963E-3</v>
       </c>
       <c r="Z29">
-        <v>1.8373947820576827E-3</v>
+        <v>1.9954592492396517E-3</v>
       </c>
       <c r="AA29">
-        <v>2.138660646256332E-3</v>
+        <v>1.8376063185178747E-3</v>
       </c>
       <c r="AB29">
-        <v>1.8790573926520363E-3</v>
+        <v>1.9275678688464232E-3</v>
       </c>
       <c r="AC29">
-        <v>1.9714239441752644E-3</v>
+        <v>1.8991714272233189E-3</v>
       </c>
       <c r="AD29">
-        <v>4.1004313897513777E-3</v>
+        <v>3.8876628130453065E-3</v>
       </c>
       <c r="AE29">
-        <v>1.9016913448074184E-3</v>
+        <v>1.9001062537711702E-3</v>
       </c>
       <c r="AF29">
-        <v>1.9362401380943559E-3</v>
+        <v>-8.3385608564000464E-5</v>
       </c>
       <c r="AG29">
-        <v>-9.9015657120663289E-5</v>
+        <v>-2.4135696849906661E-4</v>
       </c>
       <c r="AH29">
-        <v>-2.2726788221839205E-4</v>
+        <v>-9.2774506379233578E-5</v>
       </c>
       <c r="AI29">
-        <v>-2.1703768196958855E-4</v>
+        <v>5.581750610414609E-4</v>
       </c>
       <c r="AJ29">
-        <v>5.5659818762407594E-4</v>
+        <v>1.1780165856323539E-3</v>
       </c>
       <c r="AK29">
-        <v>1.1146383934852425E-3</v>
+        <v>1.9360507151429717E-3</v>
       </c>
       <c r="AL29">
-        <v>1.5549650244190277E-3</v>
-      </c>
-      <c r="AM29">
-        <v>1.8936372799631136E-3</v>
+        <v>2.0325970766077138E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
       <c r="B30">
-        <v>-2.8470971582238566E-3</v>
+        <v>0.17308111488175659</v>
       </c>
       <c r="C30">
-        <v>2.6805228191602824E-4</v>
+        <v>1.9941830197874651E-4</v>
       </c>
       <c r="D30">
-        <v>1.3442669690943792E-4</v>
+        <v>1.4214788020234939E-4</v>
       </c>
       <c r="E30">
-        <v>-2.2302504149478929E-6</v>
+        <v>-2.2092940597415485E-6</v>
       </c>
       <c r="F30">
-        <v>8.4250935180472301E-6</v>
+        <v>4.5557602338793885E-6</v>
       </c>
       <c r="G30">
-        <v>2.5085102510469983E-6</v>
+        <v>2.4899657047775339E-7</v>
       </c>
       <c r="H30">
-        <v>-7.8578512940038364E-4</v>
+        <v>-1.501064405323906E-4</v>
       </c>
       <c r="I30">
-        <v>7.8358815076011933E-4</v>
+        <v>1.1492746149992933E-4</v>
       </c>
       <c r="J30">
-        <v>-2.1063401386416602E-5</v>
+        <v>-3.254268815515096E-5</v>
       </c>
       <c r="K30">
-        <v>2.0933802891666495E-4</v>
+        <v>3.4874653431506554E-4</v>
       </c>
       <c r="L30">
-        <v>9.9356655392510298E-5</v>
+        <v>3.4472341442368408E-4</v>
       </c>
       <c r="M30">
-        <v>1.4450918320381667E-4</v>
+        <v>3.6926016319388391E-4</v>
       </c>
       <c r="N30">
-        <v>3.5321984850250209E-4</v>
+        <v>2.5983639759235492E-4</v>
       </c>
       <c r="O30">
-        <v>8.7559292715501435E-5</v>
+        <v>-1.9841385124146673E-4</v>
       </c>
       <c r="P30">
-        <v>-7.7018579124131178E-5</v>
+        <v>-7.4539733048804423E-5</v>
       </c>
       <c r="Q30">
-        <v>-1.1969413871786477E-4</v>
+        <v>-2.4819717713608718E-4</v>
       </c>
       <c r="R30">
-        <v>-1.5415729884673434E-4</v>
+        <v>5.1735375042640626E-5</v>
       </c>
       <c r="S30">
-        <v>-1.502417581982781E-5</v>
+        <v>-4.5208238212029669E-5</v>
       </c>
       <c r="T30">
-        <v>-8.807244877128838E-5</v>
+        <v>2.552069544261243E-4</v>
       </c>
       <c r="U30">
-        <v>2.3337092414353052E-4</v>
+        <v>1.9071583568653137E-3</v>
       </c>
       <c r="V30">
-        <v>1.8962113864322235E-3</v>
+        <v>1.8610075630263855E-3</v>
       </c>
       <c r="W30">
-        <v>1.831359291587169E-3</v>
+        <v>1.8831430315509753E-3</v>
       </c>
       <c r="X30">
-        <v>1.8707892840616946E-3</v>
+        <v>1.8569513397162542E-3</v>
       </c>
       <c r="Y30">
-        <v>1.8006777375628061E-3</v>
+        <v>1.8329763815158643E-3</v>
       </c>
       <c r="Z30">
-        <v>1.7900606471617109E-3</v>
+        <v>2.0155004804722275E-3</v>
       </c>
       <c r="AA30">
-        <v>1.9973862959721364E-3</v>
+        <v>1.8777138585094276E-3</v>
       </c>
       <c r="AB30">
-        <v>1.8401733366525392E-3</v>
+        <v>1.9420807917101784E-3</v>
       </c>
       <c r="AC30">
-        <v>1.9299755060135848E-3</v>
+        <v>1.9338329731531669E-3</v>
       </c>
       <c r="AD30">
-        <v>1.9016913448074184E-3</v>
+        <v>1.9001062537711702E-3</v>
       </c>
       <c r="AE30">
-        <v>3.8914000420741763E-3</v>
+        <v>3.9661022466254796E-3</v>
       </c>
       <c r="AF30">
-        <v>1.9026459141454296E-3</v>
+        <v>-5.7484644859376273E-5</v>
       </c>
       <c r="AG30">
-        <v>-8.3525068682301516E-5</v>
+        <v>-8.2533625303852619E-5</v>
       </c>
       <c r="AH30">
-        <v>-2.4161847021225463E-4</v>
+        <v>-1.3452226406100197E-4</v>
       </c>
       <c r="AI30">
-        <v>-9.2660787261825009E-5</v>
+        <v>6.1822856350853754E-4</v>
       </c>
       <c r="AJ30">
-        <v>5.6022914072101034E-4</v>
+        <v>1.3024363879380653E-3</v>
       </c>
       <c r="AK30">
-        <v>1.1808789245431319E-3</v>
+        <v>1.0562808567668666E-3</v>
       </c>
       <c r="AL30">
-        <v>1.9379309420799306E-3</v>
-      </c>
-      <c r="AM30">
-        <v>2.0254315966184901E-3</v>
+        <v>-9.183181803220624E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>43</v>
       </c>
       <c r="B31">
-        <v>0.17304218035963012</v>
+        <v>-1.661491736175633E-2</v>
       </c>
       <c r="C31">
-        <v>1.6340122481109526E-3</v>
+        <v>-5.5087533906595932E-5</v>
       </c>
       <c r="D31">
-        <v>1.4445110178947559E-4</v>
+        <v>-6.627241824443597E-6</v>
       </c>
       <c r="E31">
-        <v>-2.2438022117473127E-6</v>
+        <v>1.125576341391809E-7</v>
       </c>
       <c r="F31">
-        <v>4.5636351790956169E-6</v>
+        <v>2.6307540363029871E-7</v>
       </c>
       <c r="G31">
-        <v>2.5768710126616379E-7</v>
+        <v>1.19647761857E-7</v>
       </c>
       <c r="H31">
-        <v>-1.5033826445145132E-4</v>
+        <v>2.9605991981905542E-5</v>
       </c>
       <c r="I31">
-        <v>1.1459159258371369E-4</v>
+        <v>-2.9825152655369634E-5</v>
       </c>
       <c r="J31">
-        <v>-6.9209672132578524E-5</v>
+        <v>5.1716286630852168E-5</v>
       </c>
       <c r="K31">
-        <v>-6.3329662227194512E-5</v>
+        <v>-6.0716183931791956E-5</v>
       </c>
       <c r="L31">
-        <v>3.5039861140833783E-4</v>
+        <v>-7.410532401757946E-5</v>
       </c>
       <c r="M31">
-        <v>3.4440367008863623E-4</v>
+        <v>-7.2712037833034114E-5</v>
       </c>
       <c r="N31">
-        <v>3.6799086553373128E-4</v>
+        <v>-2.1325762600560388E-5</v>
       </c>
       <c r="O31">
-        <v>2.5787102185891486E-4</v>
+        <v>1.9707518395667558E-5</v>
       </c>
       <c r="P31">
-        <v>-1.9948303755894741E-4</v>
+        <v>2.6398815104724331E-5</v>
       </c>
       <c r="Q31">
-        <v>-7.4635623787186163E-5</v>
+        <v>6.2276125026192983E-5</v>
       </c>
       <c r="R31">
-        <v>-2.4922417955293484E-4</v>
+        <v>-2.4937886476859653E-5</v>
       </c>
       <c r="S31">
-        <v>5.1607586754535972E-5</v>
+        <v>1.4291660648760806E-4</v>
       </c>
       <c r="T31">
-        <v>-4.5148932407947789E-5</v>
+        <v>-2.3013033238314802E-5</v>
       </c>
       <c r="U31">
-        <v>2.5510915916254154E-4</v>
+        <v>-5.6499350464947355E-5</v>
       </c>
       <c r="V31">
-        <v>1.9115358375099828E-3</v>
+        <v>-7.0412316212073401E-5</v>
       </c>
       <c r="W31">
-        <v>1.8631592445847028E-3</v>
+        <v>-6.4337940354237475E-5</v>
       </c>
       <c r="X31">
-        <v>1.8853605580632167E-3</v>
+        <v>-5.2430183193363119E-5</v>
       </c>
       <c r="Y31">
-        <v>1.8590195649157183E-3</v>
+        <v>-5.0786148394265244E-5</v>
       </c>
       <c r="Z31">
-        <v>1.8343529681997246E-3</v>
+        <v>-1.2817537535796022E-4</v>
       </c>
       <c r="AA31">
-        <v>2.0176319441087276E-3</v>
+        <v>-6.3636035500774953E-5</v>
       </c>
       <c r="AB31">
-        <v>1.8802873543835987E-3</v>
+        <v>-7.5059973846014532E-5</v>
       </c>
       <c r="AC31">
-        <v>1.9444866366701164E-3</v>
+        <v>-9.8990169686980815E-5</v>
       </c>
       <c r="AD31">
-        <v>1.9362401380943559E-3</v>
+        <v>-8.3385608564000464E-5</v>
       </c>
       <c r="AE31">
-        <v>1.9026459141454296E-3</v>
+        <v>-5.7484644859376273E-5</v>
       </c>
       <c r="AF31">
-        <v>3.9695985546325703E-3</v>
+        <v>1.706290007437449E-4</v>
       </c>
       <c r="AG31">
-        <v>-5.746525507453107E-5</v>
+        <v>1.8393115895323255E-4</v>
       </c>
       <c r="AH31">
-        <v>-8.2187692580145582E-5</v>
+        <v>-8.7675036956259833E-5</v>
       </c>
       <c r="AI31">
-        <v>-1.351563260659838E-4</v>
+        <v>-7.0229314752890196E-6</v>
       </c>
       <c r="AJ31">
-        <v>6.1952538332214529E-4</v>
+        <v>-3.7372737483836078E-5</v>
       </c>
       <c r="AK31">
-        <v>1.3054466515233659E-3</v>
+        <v>-2.3005476229107785E-4</v>
       </c>
       <c r="AL31">
-        <v>1.057284445971484E-3</v>
-      </c>
-      <c r="AM31">
-        <v>-9.6029836819870682E-4</v>
+        <v>-1.1043417331431445E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>44</v>
       </c>
       <c r="B32">
-        <v>-1.6465558549638975E-2</v>
+        <v>2.7997815753547491E-2</v>
       </c>
       <c r="C32">
-        <v>-1.8588424642770971E-5</v>
+        <v>-5.4266938444234077E-4</v>
       </c>
       <c r="D32">
-        <v>-6.7745358203226001E-6</v>
+        <v>-2.5662582464044525E-5</v>
       </c>
       <c r="E32">
-        <v>1.1477048420761987E-7</v>
+        <v>3.9423953209857961E-7</v>
       </c>
       <c r="F32">
-        <v>2.6919958101006399E-7</v>
+        <v>-1.4250298976970779E-7</v>
       </c>
       <c r="G32">
-        <v>1.2728581543088008E-7</v>
+        <v>-2.7611536818197686E-6</v>
       </c>
       <c r="H32">
-        <v>2.9231398664304106E-5</v>
+        <v>2.0153011783269695E-5</v>
       </c>
       <c r="I32">
-        <v>-2.9331958346535044E-5</v>
+        <v>-4.0185609186017043E-4</v>
       </c>
       <c r="J32">
-        <v>2.0024308618112616E-6</v>
+        <v>5.4875272849782685E-4</v>
       </c>
       <c r="K32">
-        <v>-2.3051827846803864E-5</v>
+        <v>-2.4134555619574811E-4</v>
       </c>
       <c r="L32">
-        <v>-6.0665860829154245E-5</v>
+        <v>-3.5737186212504517E-4</v>
       </c>
       <c r="M32">
-        <v>-7.3967870968633836E-5</v>
+        <v>-4.6759768700246744E-4</v>
       </c>
       <c r="N32">
-        <v>-7.2344313572197759E-5</v>
+        <v>-2.8203260721939303E-4</v>
       </c>
       <c r="O32">
-        <v>-2.090197685725042E-5</v>
+        <v>-4.3298257807774577E-5</v>
       </c>
       <c r="P32">
-        <v>1.9752171383797402E-5</v>
+        <v>6.857118340413009E-5</v>
       </c>
       <c r="Q32">
-        <v>2.6459863303056441E-5</v>
+        <v>3.1277564311195556E-5</v>
       </c>
       <c r="R32">
-        <v>6.2377255584980605E-5</v>
+        <v>-1.3401442170895693E-4</v>
       </c>
       <c r="S32">
-        <v>-2.4943211079179053E-5</v>
+        <v>2.3549165937703648E-4</v>
       </c>
       <c r="T32">
-        <v>1.4286261606888222E-4</v>
+        <v>-5.1638884831770471E-5</v>
       </c>
       <c r="U32">
-        <v>-2.2867368889623969E-5</v>
+        <v>2.6469155160787532E-5</v>
       </c>
       <c r="V32">
-        <v>-5.6545501402569348E-5</v>
+        <v>-1.1503186087038618E-4</v>
       </c>
       <c r="W32">
-        <v>-7.0418644602849711E-5</v>
+        <v>-1.1550104900275498E-4</v>
       </c>
       <c r="X32">
-        <v>-6.4183289550642528E-5</v>
+        <v>-1.9549359270589297E-5</v>
       </c>
       <c r="Y32">
-        <v>-5.2263685145797923E-5</v>
+        <v>4.0742151102146553E-5</v>
       </c>
       <c r="Z32">
-        <v>-5.0537062479261674E-5</v>
+        <v>-6.7574854544676392E-4</v>
       </c>
       <c r="AA32">
-        <v>-1.2833422910895302E-4</v>
+        <v>-2.2812092868332323E-4</v>
       </c>
       <c r="AB32">
-        <v>-6.370043657908517E-5</v>
+        <v>-1.3739843543340434E-4</v>
       </c>
       <c r="AC32">
-        <v>-7.509834003771518E-5</v>
+        <v>-2.2677823573466417E-4</v>
       </c>
       <c r="AD32">
-        <v>-9.9015657120663289E-5</v>
+        <v>-2.4135696849906661E-4</v>
       </c>
       <c r="AE32">
-        <v>-8.3525068682301516E-5</v>
+        <v>-8.2533625303852619E-5</v>
       </c>
       <c r="AF32">
-        <v>-5.746525507453107E-5</v>
+        <v>1.8393115895323255E-4</v>
       </c>
       <c r="AG32">
-        <v>1.7056540300976707E-4</v>
+        <v>3.3085676591248139E-3</v>
       </c>
       <c r="AH32">
-        <v>1.8395648608631777E-4</v>
+        <v>6.0678636613808838E-4</v>
       </c>
       <c r="AI32">
-        <v>-8.7543757926643144E-5</v>
+        <v>8.0403957863479231E-5</v>
       </c>
       <c r="AJ32">
-        <v>-7.0964462087919761E-6</v>
+        <v>-5.1273313666291842E-6</v>
       </c>
       <c r="AK32">
-        <v>-3.7130254941546842E-5</v>
+        <v>-1.574358579453719E-3</v>
       </c>
       <c r="AL32">
-        <v>-2.2985506541271794E-4</v>
-      </c>
-      <c r="AM32">
-        <v>-1.1037986354171643E-2</v>
+        <v>-1.5940132141244581E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>45</v>
       </c>
       <c r="B33">
-        <v>2.8947903115328348E-2</v>
+        <v>3.6348188807681418E-2</v>
       </c>
       <c r="C33">
-        <v>1.526900466354647E-3</v>
+        <v>-2.6054599559575302E-4</v>
       </c>
       <c r="D33">
-        <v>-2.5255405409989069E-5</v>
+        <v>-6.7884408203983029E-5</v>
       </c>
       <c r="E33">
-        <v>3.8815368504298053E-7</v>
+        <v>1.0450571790468241E-6</v>
       </c>
       <c r="F33">
-        <v>-5.9411153854297023E-8</v>
+        <v>2.7026241282417936E-7</v>
       </c>
       <c r="G33">
-        <v>-2.7242544039286854E-6</v>
+        <v>-8.996655002017292E-7</v>
       </c>
       <c r="H33">
-        <v>1.9837451700222019E-5</v>
+        <v>2.1486612238934903E-4</v>
       </c>
       <c r="I33">
-        <v>-4.0281585531746827E-4</v>
+        <v>-4.9891429821407457E-4</v>
       </c>
       <c r="J33">
-        <v>-7.563087660231475E-5</v>
+        <v>1.5394124667027605E-4</v>
       </c>
       <c r="K33">
-        <v>-4.8503737657104758E-6</v>
+        <v>5.7240161079760168E-5</v>
       </c>
       <c r="L33">
-        <v>-2.4419226595269504E-4</v>
+        <v>-1.1549385762271377E-4</v>
       </c>
       <c r="M33">
-        <v>-3.5984640965902896E-4</v>
+        <v>-2.3413646908388439E-4</v>
       </c>
       <c r="N33">
-        <v>-4.7067492382660021E-4</v>
+        <v>-1.8490776819335083E-4</v>
       </c>
       <c r="O33">
-        <v>-2.8433936264808755E-4</v>
+        <v>-2.7340057892192605E-5</v>
       </c>
       <c r="P33">
-        <v>-4.3702183334916973E-5</v>
+        <v>7.1712720550812275E-5</v>
       </c>
       <c r="Q33">
-        <v>6.873867114884042E-5</v>
+        <v>-3.1742618556409241E-5</v>
       </c>
       <c r="R33">
-        <v>3.0846777140921557E-5</v>
+        <v>-1.0463586593841934E-4</v>
       </c>
       <c r="S33">
-        <v>-1.3443637459761707E-4</v>
+        <v>-4.9303328716974321E-7</v>
       </c>
       <c r="T33">
-        <v>2.3562612410413242E-4</v>
+        <v>-9.0171096759436077E-5</v>
       </c>
       <c r="U33">
-        <v>-5.1720934482023988E-5</v>
+        <v>1.8053653134589276E-4</v>
       </c>
       <c r="V33">
-        <v>2.7696654529116359E-5</v>
+        <v>6.8074780378203788E-6</v>
       </c>
       <c r="W33">
-        <v>-1.1471156441654853E-4</v>
+        <v>-1.3069947915023491E-4</v>
       </c>
       <c r="X33">
-        <v>-1.1456906563213652E-4</v>
+        <v>1.8168399997780496E-5</v>
       </c>
       <c r="Y33">
-        <v>-1.9034038251386563E-5</v>
+        <v>-7.5674714735055396E-5</v>
       </c>
       <c r="Z33">
-        <v>4.2870351143301096E-5</v>
+        <v>-5.8225179389595038E-4</v>
       </c>
       <c r="AA33">
-        <v>-6.7689183050250389E-4</v>
+        <v>-1.2489949214035433E-4</v>
       </c>
       <c r="AB33">
-        <v>-2.2809238433694427E-4</v>
+        <v>-6.7056601599595677E-5</v>
       </c>
       <c r="AC33">
-        <v>-1.3720930906776125E-4</v>
+        <v>-2.1625297835409956E-4</v>
       </c>
       <c r="AD33">
-        <v>-2.2726788221839205E-4</v>
+        <v>-9.2774506379233578E-5</v>
       </c>
       <c r="AE33">
-        <v>-2.4161847021225463E-4</v>
+        <v>-1.3452226406100197E-4</v>
       </c>
       <c r="AF33">
-        <v>-8.2187692580145582E-5</v>
+        <v>-8.7675036956259833E-5</v>
       </c>
       <c r="AG33">
-        <v>1.8395648608631777E-4</v>
+        <v>6.0678636613808838E-4</v>
       </c>
       <c r="AH33">
-        <v>3.3131507706859221E-3</v>
+        <v>3.5170891698118548E-3</v>
       </c>
       <c r="AI33">
-        <v>6.08286595842303E-4</v>
+        <v>7.5789528929307622E-5</v>
       </c>
       <c r="AJ33">
-        <v>8.0613608049803429E-5</v>
+        <v>1.7749237591551531E-5</v>
       </c>
       <c r="AK33">
-        <v>-2.8630827317776761E-6</v>
+        <v>-1.503586257544362E-3</v>
       </c>
       <c r="AL33">
-        <v>-1.5778180893442142E-3</v>
-      </c>
-      <c r="AM33">
-        <v>-1.5959109492830394E-2</v>
+        <v>2.7276929820847437E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>46</v>
       </c>
       <c r="B34">
-        <v>3.6726002805026678E-2</v>
+        <v>-6.2769054824928963E-2</v>
       </c>
       <c r="C34">
-        <v>5.2433031058840562E-4</v>
+        <v>-3.4036150800639212E-5</v>
       </c>
       <c r="D34">
-        <v>-6.8094011122727185E-5</v>
+        <v>1.2123410514249498E-6</v>
       </c>
       <c r="E34">
-        <v>1.0480362153388137E-6</v>
+        <v>-9.1765557274399722E-8</v>
       </c>
       <c r="F34">
-        <v>2.9236041198898679E-7</v>
+        <v>1.8583050614183141E-6</v>
       </c>
       <c r="G34">
-        <v>-8.9336395582200948E-7</v>
+        <v>2.3963270115475561E-7</v>
       </c>
       <c r="H34">
-        <v>2.1497233697535754E-4</v>
+        <v>-7.833305216560953E-5</v>
       </c>
       <c r="I34">
-        <v>-4.9941086088878652E-4</v>
+        <v>1.0073765944365229E-4</v>
       </c>
       <c r="J34">
-        <v>-3.0155964177004972E-5</v>
+        <v>-2.2290733657123269E-4</v>
       </c>
       <c r="K34">
-        <v>-2.1657257925707281E-5</v>
+        <v>4.4322067690803009E-5</v>
       </c>
       <c r="L34">
-        <v>5.6621114249929909E-5</v>
+        <v>2.6283950258548273E-5</v>
       </c>
       <c r="M34">
-        <v>-1.1581524033788156E-4</v>
+        <v>1.440224675136781E-4</v>
       </c>
       <c r="N34">
-        <v>-2.3431559265726291E-4</v>
+        <v>1.0030989854685891E-4</v>
       </c>
       <c r="O34">
-        <v>-1.8453782472185496E-4</v>
+        <v>-1.0637958707025315E-4</v>
       </c>
       <c r="P34">
-        <v>-2.7364535477065999E-5</v>
+        <v>7.4223138723151494E-5</v>
       </c>
       <c r="Q34">
-        <v>7.1693323015535902E-5</v>
+        <v>-1.5937145141711495E-4</v>
       </c>
       <c r="R34">
-        <v>-3.1595952468371411E-5</v>
+        <v>-9.4955411713562793E-5</v>
       </c>
       <c r="S34">
-        <v>-1.049910511935942E-4</v>
+        <v>-2.44031792207694E-7</v>
       </c>
       <c r="T34">
-        <v>-2.8317153302412357E-7</v>
+        <v>-6.0997626068332185E-5</v>
       </c>
       <c r="U34">
-        <v>-8.9906477423526876E-5</v>
+        <v>5.6122115525973778E-4</v>
       </c>
       <c r="V34">
-        <v>1.7907900226452587E-4</v>
+        <v>4.6836300676074427E-4</v>
       </c>
       <c r="W34">
-        <v>7.0811717903053787E-6</v>
+        <v>5.4374429515761371E-4</v>
       </c>
       <c r="X34">
-        <v>-1.3049895254920043E-4</v>
+        <v>4.5968359914726941E-4</v>
       </c>
       <c r="Y34">
-        <v>1.8168006827741002E-5</v>
+        <v>3.6206250781035688E-4</v>
       </c>
       <c r="Z34">
-        <v>-7.4774059216048026E-5</v>
+        <v>4.7282201911867579E-4</v>
       </c>
       <c r="AA34">
-        <v>-5.8362009018309057E-4</v>
+        <v>4.2061135733532478E-4</v>
       </c>
       <c r="AB34">
-        <v>-1.2542946034105416E-4</v>
+        <v>6.0038568062309948E-4</v>
       </c>
       <c r="AC34">
-        <v>-6.7644282914914537E-5</v>
+        <v>5.5479371773590536E-4</v>
       </c>
       <c r="AD34">
-        <v>-2.1703768196958855E-4</v>
+        <v>5.581750610414609E-4</v>
       </c>
       <c r="AE34">
-        <v>-9.2660787261825009E-5</v>
+        <v>6.1822856350853754E-4</v>
       </c>
       <c r="AF34">
-        <v>-1.351563260659838E-4</v>
+        <v>-7.0229314752890196E-6</v>
       </c>
       <c r="AG34">
-        <v>-8.7543757926643144E-5</v>
+        <v>8.0403957863479231E-5</v>
       </c>
       <c r="AH34">
-        <v>6.08286595842303E-4</v>
+        <v>7.5789528929307622E-5</v>
       </c>
       <c r="AI34">
-        <v>3.5205552977626438E-3</v>
+        <v>1.927697959723855E-3</v>
       </c>
       <c r="AJ34">
-        <v>7.5492845433700832E-5</v>
+        <v>4.5722541574981686E-4</v>
       </c>
       <c r="AK34">
-        <v>1.8452375148559751E-5</v>
+        <v>5.1665692488913739E-4</v>
       </c>
       <c r="AL34">
-        <v>-1.5071525787433253E-3</v>
-      </c>
-      <c r="AM34">
-        <v>2.7153084404094516E-3</v>
+        <v>-5.1058777859496699E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
       <c r="B35">
-        <v>-6.2440957890380969E-2</v>
+        <v>0.24528404350112165</v>
       </c>
       <c r="C35">
-        <v>4.5757463701508877E-4</v>
+        <v>-5.795593808838144E-4</v>
       </c>
       <c r="D35">
-        <v>1.8209891327113179E-6</v>
+        <v>2.7211542649549069E-5</v>
       </c>
       <c r="E35">
-        <v>-1.0156151694862159E-7</v>
+        <v>-6.6017190506680813E-7</v>
       </c>
       <c r="F35">
-        <v>1.8722911652971187E-6</v>
+        <v>-1.5538661958960803E-6</v>
       </c>
       <c r="G35">
-        <v>2.6254807640354507E-7</v>
+        <v>8.678896353062189E-7</v>
       </c>
       <c r="H35">
-        <v>-7.80196043041001E-5</v>
+        <v>-2.4769017433527534E-4</v>
       </c>
       <c r="I35">
-        <v>1.0086184702941606E-4</v>
+        <v>-3.0862442241197537E-4</v>
       </c>
       <c r="J35">
-        <v>-2.0628274906582924E-5</v>
+        <v>4.9545420292900475E-4</v>
       </c>
       <c r="K35">
-        <v>-2.6677497277693279E-4</v>
+        <v>3.0132075470445469E-4</v>
       </c>
       <c r="L35">
-        <v>4.2756589411396774E-5</v>
+        <v>3.2922117413787354E-4</v>
       </c>
       <c r="M35">
-        <v>2.5330598805859555E-5</v>
+        <v>6.8764391419227889E-5</v>
       </c>
       <c r="N35">
-        <v>1.4318956040585925E-4</v>
+        <v>5.230558055267212E-5</v>
       </c>
       <c r="O35">
-        <v>9.9372795992537424E-5</v>
+        <v>-2.0551544867328128E-4</v>
       </c>
       <c r="P35">
-        <v>-1.0618963301686811E-4</v>
+        <v>9.2620957553202248E-6</v>
       </c>
       <c r="Q35">
-        <v>7.3857458468417969E-5</v>
+        <v>-1.8819564898173524E-4</v>
       </c>
       <c r="R35">
-        <v>-1.5968204351363033E-4</v>
+        <v>6.1720142017724429E-5</v>
       </c>
       <c r="S35">
-        <v>-9.5190001677382884E-5</v>
+        <v>-3.8020929355750063E-5</v>
       </c>
       <c r="T35">
-        <v>-3.3869928338023381E-7</v>
+        <v>5.9211623298469356E-5</v>
       </c>
       <c r="U35">
-        <v>-6.1479921442143424E-5</v>
+        <v>1.1836873575856084E-3</v>
       </c>
       <c r="V35">
-        <v>5.6598799508010035E-4</v>
+        <v>1.0445037578769743E-3</v>
       </c>
       <c r="W35">
-        <v>4.7015161629061102E-4</v>
+        <v>1.0631946224133367E-3</v>
       </c>
       <c r="X35">
-        <v>5.4650575482159214E-4</v>
+        <v>1.0785559956834681E-3</v>
       </c>
       <c r="Y35">
-        <v>4.6125226273772317E-4</v>
+        <v>1.025034530679973E-3</v>
       </c>
       <c r="Z35">
-        <v>3.6331976278472175E-4</v>
+        <v>7.731054847294178E-4</v>
       </c>
       <c r="AA35">
-        <v>4.7458974699143841E-4</v>
+        <v>1.3813809201118979E-3</v>
       </c>
       <c r="AB35">
-        <v>4.22535956951722E-4</v>
+        <v>1.147101839345168E-3</v>
       </c>
       <c r="AC35">
-        <v>6.0229692131918413E-4</v>
+        <v>1.1120213918337631E-3</v>
       </c>
       <c r="AD35">
-        <v>5.5659818762407594E-4</v>
+        <v>1.1780165856323539E-3</v>
       </c>
       <c r="AE35">
-        <v>5.6022914072101034E-4</v>
+        <v>1.3024363879380653E-3</v>
       </c>
       <c r="AF35">
-        <v>6.1952538332214529E-4</v>
+        <v>-3.7372737483836078E-5</v>
       </c>
       <c r="AG35">
-        <v>-7.0964462087919761E-6</v>
+        <v>-5.1273313666291842E-6</v>
       </c>
       <c r="AH35">
-        <v>8.0613608049803429E-5</v>
+        <v>1.7749237591551531E-5</v>
       </c>
       <c r="AI35">
-        <v>7.5492845433700832E-5</v>
+        <v>4.5722541574981686E-4</v>
       </c>
       <c r="AJ35">
-        <v>1.9296155021254655E-3</v>
+        <v>5.9681355398103738E-3</v>
       </c>
       <c r="AK35">
-        <v>4.5819629693480098E-4</v>
+        <v>1.3066270865045356E-4</v>
       </c>
       <c r="AL35">
-        <v>5.1794772317520325E-4</v>
-      </c>
-      <c r="AM35">
-        <v>-5.1589638176948761E-4</v>
+        <v>1.6938115856483093E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36">
-        <v>0.2479056773208482</v>
+        <v>2.7061644908211429E-2</v>
       </c>
       <c r="C36">
-        <v>7.0318078897457781E-5</v>
+        <v>8.6041579915096394E-4</v>
       </c>
       <c r="D36">
-        <v>2.9273090688445485E-5</v>
+        <v>3.1753927664675968E-4</v>
       </c>
       <c r="E36">
-        <v>-6.9092731330447436E-7</v>
+        <v>-5.1064220481602564E-6</v>
       </c>
       <c r="F36">
-        <v>-1.5507415205681441E-6</v>
+        <v>2.044904156808748E-5</v>
       </c>
       <c r="G36">
-        <v>9.5399052212621704E-7</v>
+        <v>4.0959581037196572E-5</v>
       </c>
       <c r="H36">
-        <v>-2.5805556921137826E-4</v>
+        <v>2.5927400724313761E-4</v>
       </c>
       <c r="I36">
-        <v>-2.9827769167684666E-4</v>
+        <v>1.8286058719499884E-3</v>
       </c>
       <c r="J36">
-        <v>-5.1082890568032117E-7</v>
+        <v>-1.570168867256235E-3</v>
       </c>
       <c r="K36">
-        <v>6.0318400735421369E-5</v>
+        <v>4.7289686848824009E-4</v>
       </c>
       <c r="L36">
-        <v>3.0345001212948988E-4</v>
+        <v>8.9898177066784473E-4</v>
       </c>
       <c r="M36">
-        <v>3.3002934064755511E-4</v>
+        <v>2.7956394479531042E-3</v>
       </c>
       <c r="N36">
-        <v>7.0542667268484109E-5</v>
+        <v>5.5680978943236075E-4</v>
       </c>
       <c r="O36">
-        <v>5.5427359514094747E-5</v>
+        <v>-6.4614521162866066E-5</v>
       </c>
       <c r="P36">
-        <v>-2.0655310234175947E-4</v>
+        <v>-1.726816996656833E-4</v>
       </c>
       <c r="Q36">
-        <v>9.0098479719378334E-6</v>
+        <v>3.6945243513388697E-4</v>
       </c>
       <c r="R36">
-        <v>-1.8976451300693398E-4</v>
+        <v>1.0707419821768243E-3</v>
       </c>
       <c r="S36">
-        <v>5.9809645098635503E-5</v>
+        <v>-3.6295903438855748E-4</v>
       </c>
       <c r="T36">
-        <v>-3.7605603984413281E-5</v>
+        <v>2.6882419343617157E-4</v>
       </c>
       <c r="U36">
-        <v>6.0939893587249748E-5</v>
+        <v>1.8265705311134891E-3</v>
       </c>
       <c r="V36">
-        <v>1.192465050895538E-3</v>
+        <v>1.3197456253007927E-3</v>
       </c>
       <c r="W36">
-        <v>1.0459547480446284E-3</v>
+        <v>1.7510267005242911E-3</v>
       </c>
       <c r="X36">
-        <v>1.0683784807115457E-3</v>
+        <v>9.837932987819104E-4</v>
       </c>
       <c r="Y36">
-        <v>1.0814777353295977E-3</v>
+        <v>1.2080313465170607E-3</v>
       </c>
       <c r="Z36">
-        <v>1.0298147281452231E-3</v>
+        <v>5.020944841527499E-3</v>
       </c>
       <c r="AA36">
-        <v>7.7340329807507719E-4</v>
+        <v>1.1035429547748919E-3</v>
       </c>
       <c r="AB36">
-        <v>1.3840934479318586E-3</v>
+        <v>1.7756404352799533E-3</v>
       </c>
       <c r="AC36">
-        <v>1.1502191678555357E-3</v>
+        <v>1.5524630189226868E-3</v>
       </c>
       <c r="AD36">
-        <v>1.1146383934852425E-3</v>
+        <v>1.9360507151429717E-3</v>
       </c>
       <c r="AE36">
-        <v>1.1808789245431319E-3</v>
+        <v>1.0562808567668666E-3</v>
       </c>
       <c r="AF36">
-        <v>1.3054466515233659E-3</v>
+        <v>-2.3005476229107785E-4</v>
       </c>
       <c r="AG36">
-        <v>-3.7130254941546842E-5</v>
+        <v>-1.574358579453719E-3</v>
       </c>
       <c r="AH36">
-        <v>-2.8630827317776761E-6</v>
+        <v>-1.503586257544362E-3</v>
       </c>
       <c r="AI36">
-        <v>1.8452375148559751E-5</v>
+        <v>5.1665692488913739E-4</v>
       </c>
       <c r="AJ36">
-        <v>4.5819629693480098E-4</v>
+        <v>1.3066270865045356E-4</v>
       </c>
       <c r="AK36">
-        <v>5.962925005750506E-3</v>
+        <v>1.8938998798951095E-2</v>
       </c>
       <c r="AL36">
-        <v>1.2672194960711841E-4</v>
-      </c>
-      <c r="AM36">
-        <v>1.6235110457462534E-3</v>
+        <v>1.3617414840649295E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>49</v>
       </c>
       <c r="B37">
-        <v>2.7149846667201782E-2</v>
+        <v>-5.9525394446174751</v>
       </c>
       <c r="C37">
-        <v>-2.354544002412251E-3</v>
+        <v>3.5975548240729585E-3</v>
       </c>
       <c r="D37">
-        <v>3.1587034497676872E-4</v>
+        <v>-4.2778071679641545E-3</v>
       </c>
       <c r="E37">
-        <v>-5.0858354861719958E-6</v>
+        <v>6.1724566152687862E-5</v>
       </c>
       <c r="F37">
-        <v>2.043146148007557E-5</v>
+        <v>-1.8487586117047882E-4</v>
       </c>
       <c r="G37">
-        <v>4.0983080922545707E-5</v>
+        <v>-6.8259709134607031E-5</v>
       </c>
       <c r="H37">
-        <v>2.5515114068565541E-4</v>
+        <v>-5.4078637720599461E-3</v>
       </c>
       <c r="I37">
-        <v>1.835597119942951E-3</v>
+        <v>3.283027603503073E-3</v>
       </c>
       <c r="J37">
-        <v>1.6845925653075078E-4</v>
+        <v>-9.7292232438186271E-3</v>
       </c>
       <c r="K37">
-        <v>-1.5805182777097956E-3</v>
+        <v>2.0584444529755325E-3</v>
       </c>
       <c r="L37">
-        <v>4.7628528993952715E-4</v>
+        <v>3.7112497592041958E-3</v>
       </c>
       <c r="M37">
-        <v>9.0363121166423498E-4</v>
+        <v>4.1479164061915003E-3</v>
       </c>
       <c r="N37">
-        <v>2.803078540061222E-3</v>
+        <v>1.8729769437062817E-3</v>
       </c>
       <c r="O37">
-        <v>5.6447247806284614E-4</v>
+        <v>-7.919040754307289E-5</v>
       </c>
       <c r="P37">
-        <v>-6.2933058102638412E-5</v>
+        <v>-8.0789588079949767E-4</v>
       </c>
       <c r="Q37">
-        <v>-1.7331703606577318E-4</v>
+        <v>-3.2889535914228749E-3</v>
       </c>
       <c r="R37">
-        <v>3.7055892597160842E-4</v>
+        <v>1.5884291220587734E-3</v>
       </c>
       <c r="S37">
-        <v>1.0713418764131751E-3</v>
+        <v>-9.7853815072540817E-3</v>
       </c>
       <c r="T37">
-        <v>-3.6303497510194183E-4</v>
+        <v>-5.9191310484509214E-4</v>
       </c>
       <c r="U37">
-        <v>2.7051384568456491E-4</v>
+        <v>6.0438473745494468E-4</v>
       </c>
       <c r="V37">
-        <v>1.8284712075635947E-3</v>
+        <v>1.0058639878370102E-3</v>
       </c>
       <c r="W37">
-        <v>1.3219690394723712E-3</v>
+        <v>-9.5468859506385798E-5</v>
       </c>
       <c r="X37">
-        <v>1.7545619587290514E-3</v>
+        <v>-1.026965352970967E-3</v>
       </c>
       <c r="Y37">
-        <v>9.8541773840157961E-4</v>
+        <v>-1.4869029737390638E-3</v>
       </c>
       <c r="Z37">
-        <v>1.2107695286829399E-3</v>
+        <v>4.4075115370711855E-3</v>
       </c>
       <c r="AA37">
-        <v>5.0221945784018193E-3</v>
+        <v>6.5950443506066804E-4</v>
       </c>
       <c r="AB37">
-        <v>1.105995988530035E-3</v>
+        <v>2.9091441605154453E-4</v>
       </c>
       <c r="AC37">
-        <v>1.7772742010037893E-3</v>
+        <v>1.9276042925722818E-3</v>
       </c>
       <c r="AD37">
-        <v>1.5549650244190277E-3</v>
+        <v>2.0325970766077138E-3</v>
       </c>
       <c r="AE37">
-        <v>1.9379309420799306E-3</v>
+        <v>-9.183181803220624E-4</v>
       </c>
       <c r="AF37">
-        <v>1.057284445971484E-3</v>
+        <v>-1.1043417331431445E-2</v>
       </c>
       <c r="AG37">
-        <v>-2.2985506541271794E-4</v>
+        <v>-1.5940132141244581E-2</v>
       </c>
       <c r="AH37">
-        <v>-1.5778180893442142E-3</v>
+        <v>2.7276929820847437E-3</v>
       </c>
       <c r="AI37">
-        <v>-1.5071525787433253E-3</v>
+        <v>-5.1058777859496699E-4</v>
       </c>
       <c r="AJ37">
-        <v>5.1794772317520325E-4</v>
+        <v>1.6938115856483093E-3</v>
       </c>
       <c r="AK37">
-        <v>1.2672194960711841E-4</v>
+        <v>1.3617414840649295E-2</v>
       </c>
       <c r="AL37">
-        <v>1.8941519841451843E-2</v>
-      </c>
-      <c r="AM37">
-        <v>1.3639745375194709E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38">
-        <v>-5.9980596762651155</v>
-      </c>
-      <c r="C38">
-        <v>-5.9057954073663155E-2</v>
-      </c>
-      <c r="D38">
-        <v>-4.3301688558954506E-3</v>
-      </c>
-      <c r="E38">
-        <v>6.2514667328430475E-5</v>
-      </c>
-      <c r="F38">
-        <v>-1.8728411507836488E-4</v>
-      </c>
-      <c r="G38">
-        <v>-6.9981964169605395E-5</v>
-      </c>
-      <c r="H38">
-        <v>-5.3507102676044376E-3</v>
-      </c>
-      <c r="I38">
-        <v>3.234878968855515E-3</v>
-      </c>
-      <c r="J38">
-        <v>2.2602707842037731E-3</v>
-      </c>
-      <c r="K38">
-        <v>5.7423536906898477E-3</v>
-      </c>
-      <c r="L38">
-        <v>2.0745357425366049E-3</v>
-      </c>
-      <c r="M38">
-        <v>3.7223852592853744E-3</v>
-      </c>
-      <c r="N38">
-        <v>4.1514510662367396E-3</v>
-      </c>
-      <c r="O38">
-        <v>1.8784542518234335E-3</v>
-      </c>
-      <c r="P38">
-        <v>-6.6314735607186752E-5</v>
-      </c>
-      <c r="Q38">
-        <v>-8.0527993687790653E-4</v>
-      </c>
-      <c r="R38">
-        <v>-3.2763077183586742E-3</v>
-      </c>
-      <c r="S38">
-        <v>1.5916175450307393E-3</v>
-      </c>
-      <c r="T38">
-        <v>-9.7808717481448343E-3</v>
-      </c>
-      <c r="U38">
-        <v>-6.1422780239228474E-4</v>
-      </c>
-      <c r="V38">
-        <v>5.694244609876992E-4</v>
-      </c>
-      <c r="W38">
-        <v>9.86714475718041E-4</v>
-      </c>
-      <c r="X38">
-        <v>-1.7552611036087025E-4</v>
-      </c>
-      <c r="Y38">
-        <v>-1.0711311331634641E-3</v>
-      </c>
-      <c r="Z38">
-        <v>-1.581823136913917E-3</v>
-      </c>
-      <c r="AA38">
-        <v>4.4012924686034635E-3</v>
-      </c>
-      <c r="AB38">
-        <v>6.3516295862781763E-4</v>
-      </c>
-      <c r="AC38">
-        <v>2.5779861418317269E-4</v>
-      </c>
-      <c r="AD38">
-        <v>1.8936372799631136E-3</v>
-      </c>
-      <c r="AE38">
-        <v>2.0254315966184901E-3</v>
-      </c>
-      <c r="AF38">
-        <v>-9.6029836819870682E-4</v>
-      </c>
-      <c r="AG38">
-        <v>-1.1037986354171643E-2</v>
-      </c>
-      <c r="AH38">
-        <v>-1.5959109492830394E-2</v>
-      </c>
-      <c r="AI38">
-        <v>2.7153084404094516E-3</v>
-      </c>
-      <c r="AJ38">
-        <v>-5.1589638176948761E-4</v>
-      </c>
-      <c r="AK38">
-        <v>1.6235110457462534E-3</v>
-      </c>
-      <c r="AL38">
-        <v>1.3639745375194709E-2</v>
-      </c>
-      <c r="AM38">
-        <v>0.84070618111677264</v>
+        <v>0.8399781691603474</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B638B6-53EC-5B4D-969D-882AA0921B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE37BF26-5340-FA42-8D2D-FD4767140567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="19540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,10 @@
     <t>Model parameters governing projection of fertility</t>
   </si>
   <si>
-    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
-  </si>
-  <si>
-    <t>Last edit: 4 Feb 2026 DP</t>
+    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>Last edit: 18 Feb 2026 AK</t>
   </si>
   <si>
     <t>Process:</t>
@@ -75,10 +75,10 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Dhe_pcs</t>
-  </si>
-  <si>
-    <t>Dhe_mcs</t>
+    <t>Dhe_pcs_L1</t>
+  </si>
+  <si>
+    <t>Dhe_mcs_L1</t>
   </si>
   <si>
     <t>Dcpst_Single</t>
@@ -705,13 +705,13 @@
         <v>51</v>
       </c>
       <c r="B5">
-        <v>0.16592863975101757</v>
+        <v>0.17255651593708887</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
       </c>
       <c r="F5">
-        <v>2045.0751416788082</v>
+        <v>2062.2278289036431</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -719,13 +719,13 @@
         <v>52</v>
       </c>
       <c r="B6">
-        <v>83131</v>
+        <v>83141</v>
       </c>
       <c r="E6" t="s">
         <v>54</v>
       </c>
       <c r="F6">
-        <v>-8410133.1549487449</v>
+        <v>-8343957.9440288832</v>
       </c>
     </row>
   </sheetData>
@@ -859,115 +859,115 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>-0.53796323096326759</v>
+        <v>-0.5417673295966734</v>
       </c>
       <c r="C2">
-        <v>0.2037131803207434</v>
+        <v>0.20689372339458942</v>
       </c>
       <c r="D2">
-        <v>-8.8706111496228727E-5</v>
+        <v>-8.7650252885285835E-5</v>
       </c>
       <c r="E2">
-        <v>1.587818517172757E-6</v>
+        <v>1.6203588280907841E-6</v>
       </c>
       <c r="F2">
-        <v>1.2197673310279661E-5</v>
+        <v>1.6674977643326595E-5</v>
       </c>
       <c r="G2">
-        <v>1.6717971708708962E-5</v>
+        <v>8.8375607195397254E-6</v>
       </c>
       <c r="H2">
-        <v>-1.0821798374013544E-4</v>
+        <v>-2.3820253505149754E-4</v>
       </c>
       <c r="I2">
-        <v>1.6839283846075302E-3</v>
+        <v>1.851964931233227E-3</v>
       </c>
       <c r="J2">
-        <v>-0.20313124239577762</v>
+        <v>-0.2063167767679219</v>
       </c>
       <c r="K2">
-        <v>-5.3472086254740918E-5</v>
+        <v>-4.0661639389152459E-5</v>
       </c>
       <c r="L2">
-        <v>1.1058824094478505E-3</v>
+        <v>1.1665878744977572E-3</v>
       </c>
       <c r="M2">
-        <v>1.6587215951037585E-3</v>
+        <v>1.7483264867809503E-3</v>
       </c>
       <c r="N2">
-        <v>2.1441034239617096E-3</v>
+        <v>2.2221954755328585E-3</v>
       </c>
       <c r="O2">
-        <v>3.6131410017203576E-4</v>
+        <v>3.4732995096946795E-4</v>
       </c>
       <c r="P2">
-        <v>4.9868144323422412E-5</v>
+        <v>2.6988363133168886E-5</v>
       </c>
       <c r="Q2">
-        <v>5.21829155557328E-4</v>
+        <v>4.845077199879175E-4</v>
       </c>
       <c r="R2">
-        <v>3.198405765240627E-4</v>
+        <v>3.1795346361254695E-4</v>
       </c>
       <c r="S2">
-        <v>-9.7798575979757556E-5</v>
+        <v>-1.2611545203569901E-4</v>
       </c>
       <c r="T2">
-        <v>8.7018067734567208E-4</v>
+        <v>9.2020723213705104E-4</v>
       </c>
       <c r="U2">
-        <v>-9.3771685483352678E-4</v>
+        <v>-8.3185897810384346E-4</v>
       </c>
       <c r="V2">
-        <v>-1.2249971090131685E-6</v>
+        <v>1.0994851444448214E-4</v>
       </c>
       <c r="W2">
-        <v>2.8817523859004485E-4</v>
+        <v>3.4149617901906395E-4</v>
       </c>
       <c r="X2">
-        <v>2.2170416128040903E-4</v>
+        <v>2.757096644079506E-4</v>
       </c>
       <c r="Y2">
-        <v>1.102008510883299E-3</v>
+        <v>1.1808498675604704E-3</v>
       </c>
       <c r="Z2">
-        <v>6.0860812483458197E-4</v>
+        <v>7.4247671277029737E-4</v>
       </c>
       <c r="AA2">
-        <v>-1.0433591577804367E-4</v>
+        <v>-4.9765183271509631E-5</v>
       </c>
       <c r="AB2">
-        <v>1.7390887743631259E-4</v>
+        <v>2.4825774097442439E-4</v>
       </c>
       <c r="AC2">
-        <v>4.2150156616949704E-4</v>
+        <v>5.2745291080845348E-4</v>
       </c>
       <c r="AD2">
-        <v>-2.7034115967591171E-4</v>
+        <v>-1.7026087981654719E-4</v>
       </c>
       <c r="AE2">
-        <v>1.9941830197874651E-4</v>
+        <v>2.9161731110436805E-4</v>
       </c>
       <c r="AF2">
-        <v>-5.5087533906595932E-5</v>
+        <v>-8.0918402398451217E-5</v>
       </c>
       <c r="AG2">
-        <v>-5.4266938444234077E-4</v>
+        <v>-6.2360362102182199E-4</v>
       </c>
       <c r="AH2">
-        <v>-2.6054599559575302E-4</v>
+        <v>-3.1948740925249412E-4</v>
       </c>
       <c r="AI2">
-        <v>-3.4036150800639212E-5</v>
+        <v>-8.8495808434180777E-6</v>
       </c>
       <c r="AJ2">
-        <v>-5.795593808838144E-4</v>
+        <v>-5.6208873549715025E-4</v>
       </c>
       <c r="AK2">
-        <v>8.6041579915096394E-4</v>
+        <v>1.1514552942687786E-3</v>
       </c>
       <c r="AL2">
-        <v>3.5975548240729585E-3</v>
+        <v>5.6228231092129016E-3</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.2">
@@ -975,115 +975,115 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.32669413703652667</v>
+        <v>0.32556055985606963</v>
       </c>
       <c r="C3">
-        <v>-8.8706111496228727E-5</v>
+        <v>-8.7650252885285835E-5</v>
       </c>
       <c r="D3">
-        <v>2.8630805500525945E-4</v>
+        <v>2.9192058089791179E-4</v>
       </c>
       <c r="E3">
-        <v>-4.295645383776935E-6</v>
+        <v>-4.3877945903019645E-6</v>
       </c>
       <c r="F3">
-        <v>3.1636684843346258E-6</v>
+        <v>7.2319880423254487E-7</v>
       </c>
       <c r="G3">
-        <v>1.7390142196271117E-6</v>
+        <v>1.6283815324822284E-6</v>
       </c>
       <c r="H3">
-        <v>3.0860383590532994E-5</v>
+        <v>3.1600137412635641E-5</v>
       </c>
       <c r="I3">
-        <v>8.0973234294992938E-5</v>
+        <v>8.8503457402390462E-5</v>
       </c>
       <c r="J3">
-        <v>3.9133767276214098E-4</v>
+        <v>4.3105392503053593E-4</v>
       </c>
       <c r="K3">
-        <v>4.4193640925057779E-5</v>
+        <v>5.4701746606775688E-5</v>
       </c>
       <c r="L3">
-        <v>2.6178521736590419E-5</v>
+        <v>3.8365383452976134E-5</v>
       </c>
       <c r="M3">
-        <v>1.9094234857100229E-5</v>
+        <v>3.4162348906487377E-5</v>
       </c>
       <c r="N3">
-        <v>-4.9265798130001485E-5</v>
+        <v>-2.9703153544453692E-5</v>
       </c>
       <c r="O3">
-        <v>-4.2917521765438102E-5</v>
+        <v>-3.8532428382768145E-5</v>
       </c>
       <c r="P3">
-        <v>-7.1704212273286503E-5</v>
+        <v>-7.0140612572357845E-5</v>
       </c>
       <c r="Q3">
-        <v>-3.9815448280479046E-5</v>
+        <v>-3.372248923272478E-5</v>
       </c>
       <c r="R3">
-        <v>-1.5826027182835878E-5</v>
+        <v>-1.0961679661497309E-5</v>
       </c>
       <c r="S3">
-        <v>-9.4091939085051831E-6</v>
+        <v>-8.5091991468634652E-6</v>
       </c>
       <c r="T3">
-        <v>4.8811480853869313E-5</v>
+        <v>4.8252627919070511E-5</v>
       </c>
       <c r="U3">
-        <v>9.0282821865002568E-5</v>
+        <v>9.4858443313781252E-5</v>
       </c>
       <c r="V3">
-        <v>9.5109976528795666E-5</v>
+        <v>9.0989921146466591E-5</v>
       </c>
       <c r="W3">
-        <v>1.4294321974072071E-4</v>
+        <v>1.4487261463278959E-4</v>
       </c>
       <c r="X3">
-        <v>1.4957952847651922E-4</v>
+        <v>1.4618794467486144E-4</v>
       </c>
       <c r="Y3">
-        <v>1.522214887798481E-4</v>
+        <v>1.5407145857511883E-4</v>
       </c>
       <c r="Z3">
-        <v>2.3001583499728407E-4</v>
+        <v>2.259556551210181E-4</v>
       </c>
       <c r="AA3">
-        <v>1.5017107308375248E-4</v>
+        <v>1.4802843819413443E-4</v>
       </c>
       <c r="AB3">
-        <v>1.5722206879967976E-4</v>
+        <v>1.5896817758003585E-4</v>
       </c>
       <c r="AC3">
-        <v>1.8376037510583706E-4</v>
+        <v>1.893873104706718E-4</v>
       </c>
       <c r="AD3">
-        <v>1.335043261163157E-4</v>
+        <v>1.32615399178658E-4</v>
       </c>
       <c r="AE3">
-        <v>1.4214788020234939E-4</v>
+        <v>1.4098724052648021E-4</v>
       </c>
       <c r="AF3">
-        <v>-6.627241824443597E-6</v>
+        <v>-6.5480369921827196E-6</v>
       </c>
       <c r="AG3">
-        <v>-2.5662582464044525E-5</v>
+        <v>-2.2814881233977624E-5</v>
       </c>
       <c r="AH3">
-        <v>-6.7884408203983029E-5</v>
+        <v>-5.8848370436622149E-5</v>
       </c>
       <c r="AI3">
-        <v>1.2123410514249498E-6</v>
+        <v>-8.8832500070960829E-7</v>
       </c>
       <c r="AJ3">
-        <v>2.7211542649549069E-5</v>
+        <v>2.6587371594577599E-5</v>
       </c>
       <c r="AK3">
-        <v>3.1753927664675968E-4</v>
+        <v>3.0357656159759813E-4</v>
       </c>
       <c r="AL3">
-        <v>-4.2778071679641545E-3</v>
+        <v>-4.3029436348681095E-3</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.2">
@@ -1091,115 +1091,115 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>-5.7015161666606889E-3</v>
+        <v>-5.7308908425384268E-3</v>
       </c>
       <c r="C4">
-        <v>1.587818517172757E-6</v>
+        <v>1.6203588280907841E-6</v>
       </c>
       <c r="D4">
-        <v>-4.295645383776935E-6</v>
+        <v>-4.3877945903019645E-6</v>
       </c>
       <c r="E4">
-        <v>6.5594883221164801E-8</v>
+        <v>6.71242032532564E-8</v>
       </c>
       <c r="F4">
-        <v>-4.7800150736462066E-8</v>
+        <v>-4.2955754244341753E-9</v>
       </c>
       <c r="G4">
-        <v>-3.0681067323285331E-8</v>
+        <v>-2.5116913132917602E-8</v>
       </c>
       <c r="H4">
-        <v>-6.4970318663729596E-7</v>
+        <v>-5.8641607554991325E-7</v>
       </c>
       <c r="I4">
-        <v>-7.533267469054294E-7</v>
+        <v>-9.2575490783543675E-7</v>
       </c>
       <c r="J4">
-        <v>-5.791640183632728E-6</v>
+        <v>-6.4599525700069504E-6</v>
       </c>
       <c r="K4">
-        <v>-5.8679367113113092E-7</v>
+        <v>-7.4963859530949051E-7</v>
       </c>
       <c r="L4">
-        <v>-3.4023275094416237E-7</v>
+        <v>-5.1213070607315817E-7</v>
       </c>
       <c r="M4">
-        <v>-4.0604385613422154E-7</v>
+        <v>-6.453980828737918E-7</v>
       </c>
       <c r="N4">
-        <v>6.209178716875955E-7</v>
+        <v>2.8632678055209805E-7</v>
       </c>
       <c r="O4">
-        <v>4.3816734219150208E-7</v>
+        <v>3.6857133250170009E-7</v>
       </c>
       <c r="P4">
-        <v>1.3733802613425309E-6</v>
+        <v>1.3409092103494789E-6</v>
       </c>
       <c r="Q4">
-        <v>4.6098207380215883E-7</v>
+        <v>3.7574335880633599E-7</v>
       </c>
       <c r="R4">
-        <v>2.4303483718978122E-7</v>
+        <v>1.8243497411146717E-7</v>
       </c>
       <c r="S4">
-        <v>1.660502179178264E-7</v>
+        <v>1.4662442463619891E-7</v>
       </c>
       <c r="T4">
-        <v>-7.7459425747652971E-7</v>
+        <v>-7.5423300659791378E-7</v>
       </c>
       <c r="U4">
-        <v>-1.5281358212027645E-6</v>
+        <v>-1.5941604962152209E-6</v>
       </c>
       <c r="V4">
-        <v>-1.4971063571341248E-6</v>
+        <v>-1.4215308313672527E-6</v>
       </c>
       <c r="W4">
-        <v>-2.1694465893661048E-6</v>
+        <v>-2.1880704982306739E-6</v>
       </c>
       <c r="X4">
-        <v>-2.3550439380312498E-6</v>
+        <v>-2.2935474202485726E-6</v>
       </c>
       <c r="Y4">
-        <v>-2.3108283910585996E-6</v>
+        <v>-2.3205239619852815E-6</v>
       </c>
       <c r="Z4">
-        <v>-3.6840682382367713E-6</v>
+        <v>-3.6011796830267802E-6</v>
       </c>
       <c r="AA4">
-        <v>-2.2770008120483541E-6</v>
+        <v>-2.2484883685931817E-6</v>
       </c>
       <c r="AB4">
-        <v>-2.4242600517062153E-6</v>
+        <v>-2.444515472902585E-6</v>
       </c>
       <c r="AC4">
-        <v>-2.8065650005086082E-6</v>
+        <v>-2.8541760923217105E-6</v>
       </c>
       <c r="AD4">
-        <v>-2.2153366493178161E-6</v>
+        <v>-2.2235583409769943E-6</v>
       </c>
       <c r="AE4">
-        <v>-2.2092940597415485E-6</v>
+        <v>-2.1947200263740539E-6</v>
       </c>
       <c r="AF4">
-        <v>1.125576341391809E-7</v>
+        <v>1.0621507698816218E-7</v>
       </c>
       <c r="AG4">
-        <v>3.9423953209857961E-7</v>
+        <v>3.4269065024779852E-7</v>
       </c>
       <c r="AH4">
-        <v>1.0450571790468241E-6</v>
+        <v>9.2052224732956764E-7</v>
       </c>
       <c r="AI4">
-        <v>-9.1765557274399722E-8</v>
+        <v>-6.0458511754425616E-8</v>
       </c>
       <c r="AJ4">
-        <v>-6.6017190506680813E-7</v>
+        <v>-6.3658086131453118E-7</v>
       </c>
       <c r="AK4">
-        <v>-5.1064220481602564E-6</v>
+        <v>-4.8469249737167347E-6</v>
       </c>
       <c r="AL4">
-        <v>6.1724566152687862E-5</v>
+        <v>6.2095563514372068E-5</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.2">
@@ -1207,115 +1207,115 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>6.9214561864257317E-4</v>
+        <v>-1.333954564159049E-2</v>
       </c>
       <c r="C5">
-        <v>1.2197673310279661E-5</v>
+        <v>1.6674977643326595E-5</v>
       </c>
       <c r="D5">
-        <v>3.1636684843346258E-6</v>
+        <v>7.2319880423254487E-7</v>
       </c>
       <c r="E5">
-        <v>-4.7800150736462066E-8</v>
+        <v>-4.2955754244341753E-9</v>
       </c>
       <c r="F5">
-        <v>2.1800161625785831E-6</v>
+        <v>1.6230041540255241E-6</v>
       </c>
       <c r="G5">
-        <v>2.2893200447315344E-7</v>
+        <v>1.3597428050289186E-7</v>
       </c>
       <c r="H5">
-        <v>1.8860386736401691E-5</v>
+        <v>2.0695527601508195E-5</v>
       </c>
       <c r="I5">
-        <v>-2.6830807515202152E-5</v>
+        <v>-1.873683299306136E-5</v>
       </c>
       <c r="J5">
-        <v>-1.4400337112006453E-5</v>
+        <v>-2.0687433745343028E-5</v>
       </c>
       <c r="K5">
-        <v>-2.2755861833452517E-6</v>
+        <v>-2.1501196011452816E-6</v>
       </c>
       <c r="L5">
-        <v>-7.7980045907026575E-6</v>
+        <v>-7.0104895062125848E-7</v>
       </c>
       <c r="M5">
-        <v>-8.3777002382156356E-6</v>
+        <v>-2.8625642739088967E-6</v>
       </c>
       <c r="N5">
-        <v>-1.6749605364795359E-5</v>
+        <v>-1.114490688866099E-5</v>
       </c>
       <c r="O5">
-        <v>-1.8904132894317648E-6</v>
+        <v>-3.121457821565219E-6</v>
       </c>
       <c r="P5">
-        <v>-2.5649215771245024E-6</v>
+        <v>-5.9405426792837709E-7</v>
       </c>
       <c r="Q5">
-        <v>-9.294914511612545E-7</v>
+        <v>6.4400334893784247E-7</v>
       </c>
       <c r="R5">
-        <v>-2.189508657971858E-7</v>
+        <v>1.8169749025254589E-6</v>
       </c>
       <c r="S5">
-        <v>2.0532801182330886E-7</v>
+        <v>-6.680357150721785E-7</v>
       </c>
       <c r="T5">
-        <v>8.7580721727992496E-6</v>
+        <v>8.7905071189336316E-6</v>
       </c>
       <c r="U5">
-        <v>-8.7372087316935154E-7</v>
+        <v>1.3450910449102438E-6</v>
       </c>
       <c r="V5">
-        <v>4.181324953945367E-6</v>
+        <v>4.025986691406764E-6</v>
       </c>
       <c r="W5">
-        <v>2.477874233379201E-6</v>
+        <v>3.0335189609310603E-6</v>
       </c>
       <c r="X5">
-        <v>3.7111969354215519E-6</v>
+        <v>1.787296442355267E-6</v>
       </c>
       <c r="Y5">
-        <v>3.5188522756026945E-6</v>
+        <v>2.5905925079753452E-6</v>
       </c>
       <c r="Z5">
-        <v>8.1608263439468179E-6</v>
+        <v>9.3593891896448023E-6</v>
       </c>
       <c r="AA5">
-        <v>-2.5072124823440873E-6</v>
+        <v>-3.2226068100530355E-7</v>
       </c>
       <c r="AB5">
-        <v>3.1383821790104906E-6</v>
+        <v>2.933929736608103E-6</v>
       </c>
       <c r="AC5">
-        <v>-1.5082257809676658E-7</v>
+        <v>3.8554528048439566E-6</v>
       </c>
       <c r="AD5">
-        <v>8.4135725862100867E-6</v>
+        <v>-2.415809021071694E-6</v>
       </c>
       <c r="AE5">
-        <v>4.5557602338793885E-6</v>
+        <v>7.7629029585715725E-7</v>
       </c>
       <c r="AF5">
-        <v>2.6307540363029871E-7</v>
+        <v>-4.9024836013137848E-7</v>
       </c>
       <c r="AG5">
-        <v>-1.4250298976970779E-7</v>
+        <v>-3.2825900366200404E-6</v>
       </c>
       <c r="AH5">
-        <v>2.7026241282417936E-7</v>
+        <v>1.1418962405719454E-6</v>
       </c>
       <c r="AI5">
-        <v>1.8583050614183141E-6</v>
+        <v>1.1742854685407121E-6</v>
       </c>
       <c r="AJ5">
-        <v>-1.5538661958960803E-6</v>
+        <v>1.2982559169137864E-6</v>
       </c>
       <c r="AK5">
-        <v>2.044904156808748E-5</v>
+        <v>1.7491739014877301E-5</v>
       </c>
       <c r="AL5">
-        <v>-1.8487586117047882E-4</v>
+        <v>-5.9799285709484311E-5</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.2">
@@ -1323,115 +1323,115 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>6.9699577170463578E-3</v>
+        <v>7.3136753138918235E-3</v>
       </c>
       <c r="C6">
-        <v>1.6717971708708962E-5</v>
+        <v>8.8375607195397254E-6</v>
       </c>
       <c r="D6">
-        <v>1.7390142196271117E-6</v>
+        <v>1.6283815324822284E-6</v>
       </c>
       <c r="E6">
-        <v>-3.0681067323285331E-8</v>
+        <v>-2.5116913132917602E-8</v>
       </c>
       <c r="F6">
-        <v>2.2893200447315344E-7</v>
+        <v>1.3597428050289186E-7</v>
       </c>
       <c r="G6">
-        <v>1.5198810074948115E-6</v>
+        <v>1.6080713753388241E-6</v>
       </c>
       <c r="H6">
-        <v>1.263190212790235E-5</v>
+        <v>1.1895710114589063E-5</v>
       </c>
       <c r="I6">
-        <v>-1.0372308528914312E-5</v>
+        <v>-2.0677585851648737E-5</v>
       </c>
       <c r="J6">
-        <v>-2.0368050846801811E-5</v>
+        <v>-5.693329186873047E-6</v>
       </c>
       <c r="K6">
-        <v>-3.9679400939363426E-6</v>
+        <v>-1.6173396355447972E-6</v>
       </c>
       <c r="L6">
-        <v>-1.9133767547301233E-6</v>
+        <v>-7.0428418031717917E-6</v>
       </c>
       <c r="M6">
-        <v>3.2259477344254134E-7</v>
+        <v>-1.3044032947946965E-5</v>
       </c>
       <c r="N6">
-        <v>-6.4859836447984063E-6</v>
+        <v>-1.0377087129056522E-5</v>
       </c>
       <c r="O6">
-        <v>-2.5792579274637747E-6</v>
+        <v>-2.1596407065900496E-6</v>
       </c>
       <c r="P6">
-        <v>-1.8247166667789016E-6</v>
+        <v>-2.4151293474165215E-7</v>
       </c>
       <c r="Q6">
-        <v>1.354243317468754E-6</v>
+        <v>1.3857960920250325E-6</v>
       </c>
       <c r="R6">
-        <v>1.9169267527975398E-6</v>
+        <v>-2.6065300542258092E-6</v>
       </c>
       <c r="S6">
-        <v>-6.5391601548419619E-7</v>
+        <v>1.3960139662901061E-6</v>
       </c>
       <c r="T6">
-        <v>5.2282006539827995E-6</v>
+        <v>5.60627969163034E-6</v>
       </c>
       <c r="U6">
-        <v>8.9701525568045006E-7</v>
+        <v>-5.1534373013510123E-6</v>
       </c>
       <c r="V6">
-        <v>1.4325232378887304E-6</v>
+        <v>-5.3881480956986952E-6</v>
       </c>
       <c r="W6">
-        <v>4.0825252324169498E-6</v>
+        <v>-3.978296045687748E-6</v>
       </c>
       <c r="X6">
-        <v>-3.9216534051962537E-7</v>
+        <v>-3.3621390639611549E-6</v>
       </c>
       <c r="Y6">
-        <v>1.8264595018545865E-6</v>
+        <v>-3.0170639728523384E-6</v>
       </c>
       <c r="Z6">
-        <v>9.7814839245484843E-6</v>
+        <v>-1.5015801289762255E-5</v>
       </c>
       <c r="AA6">
-        <v>-9.8207946639996487E-7</v>
+        <v>-4.6052025874814753E-6</v>
       </c>
       <c r="AB6">
-        <v>2.8110374706222935E-6</v>
+        <v>-4.3000086553069987E-6</v>
       </c>
       <c r="AC6">
-        <v>8.9143827766621967E-7</v>
+        <v>-8.5616003693075622E-6</v>
       </c>
       <c r="AD6">
-        <v>2.5059132272244864E-6</v>
+        <v>-5.7311705649340298E-6</v>
       </c>
       <c r="AE6">
-        <v>2.4899657047775339E-7</v>
+        <v>-4.4975271888920363E-6</v>
       </c>
       <c r="AF6">
-        <v>1.19647761857E-7</v>
+        <v>1.6017039390630714E-6</v>
       </c>
       <c r="AG6">
-        <v>-2.7611536818197686E-6</v>
+        <v>6.9666733803318287E-6</v>
       </c>
       <c r="AH6">
-        <v>-8.996655002017292E-7</v>
+        <v>7.9335378816885133E-6</v>
       </c>
       <c r="AI6">
-        <v>2.3963270115475561E-7</v>
+        <v>-1.3426483138006019E-6</v>
       </c>
       <c r="AJ6">
-        <v>8.678896353062189E-7</v>
+        <v>7.8090787094033233E-7</v>
       </c>
       <c r="AK6">
-        <v>4.0959581037196572E-5</v>
+        <v>-3.2066877272311491E-5</v>
       </c>
       <c r="AL6">
-        <v>-6.8259709134607031E-5</v>
+        <v>-1.9925253474693512E-4</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.2">
@@ -1439,115 +1439,115 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-0.72500260255812055</v>
+        <v>-0.73039069228578146</v>
       </c>
       <c r="C7">
-        <v>-1.0821798374013544E-4</v>
+        <v>-2.3820253505149754E-4</v>
       </c>
       <c r="D7">
-        <v>3.0860383590532994E-5</v>
+        <v>3.1600137412635641E-5</v>
       </c>
       <c r="E7">
-        <v>-6.4970318663729596E-7</v>
+        <v>-5.8641607554991325E-7</v>
       </c>
       <c r="F7">
-        <v>1.8860386736401691E-5</v>
+        <v>2.0695527601508195E-5</v>
       </c>
       <c r="G7">
-        <v>1.263190212790235E-5</v>
+        <v>1.1895710114589063E-5</v>
       </c>
       <c r="H7">
-        <v>7.1803861705628039E-3</v>
+        <v>6.8938922859935791E-3</v>
       </c>
       <c r="I7">
-        <v>-6.5434480290226735E-3</v>
+        <v>-6.2016823629979494E-3</v>
       </c>
       <c r="J7">
-        <v>-3.5963656972863562E-4</v>
+        <v>-2.2311573797110704E-4</v>
       </c>
       <c r="K7">
-        <v>-9.9424917717905523E-5</v>
+        <v>-5.0903607121856055E-5</v>
       </c>
       <c r="L7">
-        <v>-5.0687743142570468E-5</v>
+        <v>-3.6374307427904139E-6</v>
       </c>
       <c r="M7">
-        <v>-4.7837519547153464E-5</v>
+        <v>1.5908970527672819E-5</v>
       </c>
       <c r="N7">
-        <v>-3.8937589848764547E-4</v>
+        <v>-3.3940033655148363E-4</v>
       </c>
       <c r="O7">
-        <v>1.1626008913003185E-4</v>
+        <v>1.0468923318698208E-4</v>
       </c>
       <c r="P7">
-        <v>-1.3889471390744621E-4</v>
+        <v>-1.4991488865634376E-4</v>
       </c>
       <c r="Q7">
-        <v>1.6172270616711241E-4</v>
+        <v>1.3113093278026549E-4</v>
       </c>
       <c r="R7">
-        <v>5.6625980918611986E-4</v>
+        <v>5.3285487967453854E-4</v>
       </c>
       <c r="S7">
-        <v>4.8251024376459147E-5</v>
+        <v>3.803704287464983E-5</v>
       </c>
       <c r="T7">
-        <v>5.6545934320001089E-5</v>
+        <v>8.2778847100849304E-5</v>
       </c>
       <c r="U7">
-        <v>-1.010516146360531E-4</v>
+        <v>-7.8108468133902091E-5</v>
       </c>
       <c r="V7">
-        <v>5.7443240310345921E-5</v>
+        <v>8.2830541979518019E-5</v>
       </c>
       <c r="W7">
-        <v>5.1214806810342197E-5</v>
+        <v>7.7820315155593934E-5</v>
       </c>
       <c r="X7">
-        <v>1.3098028467256766E-5</v>
+        <v>2.4047013417550134E-5</v>
       </c>
       <c r="Y7">
-        <v>-8.8017565309023925E-5</v>
+        <v>-8.3808408624042583E-5</v>
       </c>
       <c r="Z7">
-        <v>5.1332756511115497E-4</v>
+        <v>5.7397957415506156E-4</v>
       </c>
       <c r="AA7">
-        <v>-4.3541339373581928E-4</v>
+        <v>-3.6570262537853973E-4</v>
       </c>
       <c r="AB7">
-        <v>2.4053366854456625E-5</v>
+        <v>2.7440817027310954E-5</v>
       </c>
       <c r="AC7">
-        <v>7.8760472681513923E-5</v>
+        <v>1.0469873139276317E-4</v>
       </c>
       <c r="AD7">
-        <v>-7.8337378463319844E-4</v>
+        <v>-7.4956962011894378E-4</v>
       </c>
       <c r="AE7">
-        <v>-1.501064405323906E-4</v>
+        <v>-1.1734055070874182E-4</v>
       </c>
       <c r="AF7">
-        <v>2.9605991981905542E-5</v>
+        <v>2.4685362986764417E-5</v>
       </c>
       <c r="AG7">
-        <v>2.0153011783269695E-5</v>
+        <v>-2.8612371171717375E-5</v>
       </c>
       <c r="AH7">
-        <v>2.1486612238934903E-4</v>
+        <v>1.5107928011534832E-4</v>
       </c>
       <c r="AI7">
-        <v>-7.833305216560953E-5</v>
+        <v>-7.6571780707228705E-5</v>
       </c>
       <c r="AJ7">
-        <v>-2.4769017433527534E-4</v>
+        <v>-3.2188432900283603E-4</v>
       </c>
       <c r="AK7">
-        <v>2.5927400724313761E-4</v>
+        <v>4.3476785753204848E-4</v>
       </c>
       <c r="AL7">
-        <v>-5.4078637720599461E-3</v>
+        <v>-4.9234706080819087E-3</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.2">
@@ -1555,115 +1555,115 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>7.1764267541261972E-2</v>
+        <v>9.3323256806860447E-2</v>
       </c>
       <c r="C8">
-        <v>1.6839283846075302E-3</v>
+        <v>1.851964931233227E-3</v>
       </c>
       <c r="D8">
-        <v>8.0973234294992938E-5</v>
+        <v>8.8503457402390462E-5</v>
       </c>
       <c r="E8">
-        <v>-7.533267469054294E-7</v>
+        <v>-9.2575490783543675E-7</v>
       </c>
       <c r="F8">
-        <v>-2.6830807515202152E-5</v>
+        <v>-1.873683299306136E-5</v>
       </c>
       <c r="G8">
-        <v>-1.0372308528914312E-5</v>
+        <v>-2.0677585851648737E-5</v>
       </c>
       <c r="H8">
-        <v>-6.5434480290226735E-3</v>
+        <v>-6.2016823629979494E-3</v>
       </c>
       <c r="I8">
-        <v>7.5695988332411292E-3</v>
+        <v>7.1516338585948646E-3</v>
       </c>
       <c r="J8">
-        <v>-1.3125358233150013E-3</v>
+        <v>-1.4927277031094657E-3</v>
       </c>
       <c r="K8">
-        <v>2.1141437109945015E-4</v>
+        <v>1.8110236637086538E-4</v>
       </c>
       <c r="L8">
-        <v>5.9028851660346629E-4</v>
+        <v>5.6028322491987511E-4</v>
       </c>
       <c r="M8">
-        <v>9.9208714953986791E-4</v>
+        <v>9.50101971731237E-4</v>
       </c>
       <c r="N8">
-        <v>1.2380031878942049E-3</v>
+        <v>1.158100242385475E-3</v>
       </c>
       <c r="O8">
-        <v>1.11327147044202E-4</v>
+        <v>1.102141873955699E-4</v>
       </c>
       <c r="P8">
-        <v>2.2125225044606782E-4</v>
+        <v>2.1148586977616214E-4</v>
       </c>
       <c r="Q8">
-        <v>1.2442722215055011E-4</v>
+        <v>1.1996236000682767E-4</v>
       </c>
       <c r="R8">
-        <v>-3.8489537725640478E-4</v>
+        <v>-3.2832298733198899E-4</v>
       </c>
       <c r="S8">
-        <v>-6.8841955017501753E-5</v>
+        <v>-6.5569495540851268E-5</v>
       </c>
       <c r="T8">
-        <v>-1.2503828804736401E-6</v>
+        <v>-1.1210077178624761E-5</v>
       </c>
       <c r="U8">
-        <v>1.9359189002721156E-4</v>
+        <v>1.6723232310480058E-4</v>
       </c>
       <c r="V8">
-        <v>7.3366007915953431E-5</v>
+        <v>7.8761043703936087E-5</v>
       </c>
       <c r="W8">
-        <v>1.501352840029798E-4</v>
+        <v>1.5617021102617528E-4</v>
       </c>
       <c r="X8">
-        <v>6.0242611992599132E-5</v>
+        <v>8.493791552452478E-5</v>
       </c>
       <c r="Y8">
-        <v>1.5150240584839176E-4</v>
+        <v>1.6872118467352391E-4</v>
       </c>
       <c r="Z8">
-        <v>2.4698874046062908E-4</v>
+        <v>2.7017764597488288E-4</v>
       </c>
       <c r="AA8">
-        <v>5.5491304822533711E-4</v>
+        <v>4.9201389291589771E-4</v>
       </c>
       <c r="AB8">
-        <v>1.7346262185645629E-4</v>
+        <v>1.9517263947546284E-4</v>
       </c>
       <c r="AC8">
-        <v>2.8296198670110405E-4</v>
+        <v>2.8919674123564082E-4</v>
       </c>
       <c r="AD8">
-        <v>7.8150471258504406E-4</v>
+        <v>7.8384503772815169E-4</v>
       </c>
       <c r="AE8">
-        <v>1.1492746149992933E-4</v>
+        <v>1.3665156364574445E-4</v>
       </c>
       <c r="AF8">
-        <v>-2.9825152655369634E-5</v>
+        <v>-3.429748908508357E-5</v>
       </c>
       <c r="AG8">
-        <v>-4.0185609186017043E-4</v>
+        <v>-3.7788258330483321E-4</v>
       </c>
       <c r="AH8">
-        <v>-4.9891429821407457E-4</v>
+        <v>-4.7657066418037536E-4</v>
       </c>
       <c r="AI8">
-        <v>1.0073765944365229E-4</v>
+        <v>1.2947653891524349E-4</v>
       </c>
       <c r="AJ8">
-        <v>-3.0862442241197537E-4</v>
+        <v>-2.3466057833660542E-4</v>
       </c>
       <c r="AK8">
-        <v>1.8286058719499884E-3</v>
+        <v>1.8302801377575017E-3</v>
       </c>
       <c r="AL8">
-        <v>3.283027603503073E-3</v>
+        <v>3.1865844272790933E-3</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.2">
@@ -1671,115 +1671,115 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-0.36384704648872401</v>
+        <v>-0.34254847148407402</v>
       </c>
       <c r="C9">
-        <v>-0.20313124239577762</v>
+        <v>-0.2063167767679219</v>
       </c>
       <c r="D9">
-        <v>3.9133767276214098E-4</v>
+        <v>4.3105392503053593E-4</v>
       </c>
       <c r="E9">
-        <v>-5.791640183632728E-6</v>
+        <v>-6.4599525700069504E-6</v>
       </c>
       <c r="F9">
-        <v>-1.4400337112006453E-5</v>
+        <v>-2.0687433745343028E-5</v>
       </c>
       <c r="G9">
-        <v>-2.0368050846801811E-5</v>
+        <v>-5.693329186873047E-6</v>
       </c>
       <c r="H9">
-        <v>-3.5963656972863562E-4</v>
+        <v>-2.2311573797110704E-4</v>
       </c>
       <c r="I9">
-        <v>-1.3125358233150013E-3</v>
+        <v>-1.4927277031094657E-3</v>
       </c>
       <c r="J9">
-        <v>0.22724627243501472</v>
+        <v>0.23038767930603743</v>
       </c>
       <c r="K9">
-        <v>1.7606700100726835E-4</v>
+        <v>1.7048220796075849E-4</v>
       </c>
       <c r="L9">
-        <v>-4.3458593642227899E-4</v>
+        <v>-5.059156210665721E-4</v>
       </c>
       <c r="M9">
-        <v>-9.8868219705209649E-4</v>
+        <v>-1.1002311338627166E-3</v>
       </c>
       <c r="N9">
-        <v>-1.4774661071021769E-3</v>
+        <v>-1.5864235048432193E-3</v>
       </c>
       <c r="O9">
-        <v>-3.5432687472970704E-4</v>
+        <v>-3.4274843074847024E-4</v>
       </c>
       <c r="P9">
-        <v>-1.3148518674039358E-4</v>
+        <v>-1.1915632042609158E-4</v>
       </c>
       <c r="Q9">
-        <v>-4.1778325218692707E-4</v>
+        <v>-3.7316481097308702E-4</v>
       </c>
       <c r="R9">
-        <v>-1.4111734119706069E-4</v>
+        <v>-1.3841277220785558E-4</v>
       </c>
       <c r="S9">
-        <v>1.0348692034041617E-4</v>
+        <v>1.3004048201979937E-4</v>
       </c>
       <c r="T9">
-        <v>-3.398453766931455E-4</v>
+        <v>-3.8491506647991239E-4</v>
       </c>
       <c r="U9">
-        <v>8.6567656666861959E-4</v>
+        <v>7.8261807956351084E-4</v>
       </c>
       <c r="V9">
-        <v>5.648478999134427E-5</v>
+        <v>-4.606866627905544E-5</v>
       </c>
       <c r="W9">
-        <v>4.7669637045386304E-4</v>
+        <v>4.2440083018852135E-4</v>
       </c>
       <c r="X9">
-        <v>-3.1364590772588083E-5</v>
+        <v>-4.8702403317142564E-5</v>
       </c>
       <c r="Y9">
-        <v>-9.2050964474666428E-4</v>
+        <v>-9.697572426541211E-4</v>
       </c>
       <c r="Z9">
-        <v>-6.0535343917145689E-4</v>
+        <v>-7.0117169484747134E-4</v>
       </c>
       <c r="AA9">
-        <v>2.1447403892814243E-4</v>
+        <v>1.7062760662318806E-4</v>
       </c>
       <c r="AB9">
-        <v>2.5266815975404078E-6</v>
+        <v>-4.2985306358092861E-5</v>
       </c>
       <c r="AC9">
-        <v>-1.9530136455112886E-4</v>
+        <v>-2.6858003947689379E-4</v>
       </c>
       <c r="AD9">
-        <v>3.0514642471913937E-4</v>
+        <v>2.6394694738619904E-4</v>
       </c>
       <c r="AE9">
-        <v>-3.254268815515096E-5</v>
+        <v>-1.073128013379111E-4</v>
       </c>
       <c r="AF9">
-        <v>5.1716286630852168E-5</v>
+        <v>7.9209862058215427E-5</v>
       </c>
       <c r="AG9">
-        <v>5.4875272849782685E-4</v>
+        <v>6.2253562752687206E-4</v>
       </c>
       <c r="AH9">
-        <v>1.5394124667027605E-4</v>
+        <v>1.9903133381305756E-4</v>
       </c>
       <c r="AI9">
-        <v>-2.2290733657123269E-4</v>
+        <v>-2.5799401418363972E-4</v>
       </c>
       <c r="AJ9">
-        <v>4.9545420292900475E-4</v>
+        <v>4.8224390791841681E-4</v>
       </c>
       <c r="AK9">
-        <v>-1.570168867256235E-3</v>
+        <v>-1.7438565342721519E-3</v>
       </c>
       <c r="AL9">
-        <v>-9.7292232438186271E-3</v>
+        <v>-1.2535627420580798E-2</v>
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.2">
@@ -1787,115 +1787,115 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-0.1488589195983486</v>
+        <v>-0.15754527941184487</v>
       </c>
       <c r="C10">
-        <v>-5.3472086254740918E-5</v>
+        <v>-4.0661639389152459E-5</v>
       </c>
       <c r="D10">
-        <v>4.4193640925057779E-5</v>
+        <v>5.4701746606775688E-5</v>
       </c>
       <c r="E10">
-        <v>-5.8679367113113092E-7</v>
+        <v>-7.4963859530949051E-7</v>
       </c>
       <c r="F10">
-        <v>-2.2755861833452517E-6</v>
+        <v>-2.1501196011452816E-6</v>
       </c>
       <c r="G10">
-        <v>-3.9679400939363426E-6</v>
+        <v>-1.6173396355447972E-6</v>
       </c>
       <c r="H10">
-        <v>-9.9424917717905523E-5</v>
+        <v>-5.0903607121856055E-5</v>
       </c>
       <c r="I10">
-        <v>2.1141437109945015E-4</v>
+        <v>1.8110236637086538E-4</v>
       </c>
       <c r="J10">
-        <v>1.7606700100726835E-4</v>
+        <v>1.7048220796075849E-4</v>
       </c>
       <c r="K10">
-        <v>2.5005288481747172E-3</v>
+        <v>2.5156438334846777E-3</v>
       </c>
       <c r="L10">
-        <v>1.4669229142684895E-3</v>
+        <v>1.4717374351948878E-3</v>
       </c>
       <c r="M10">
-        <v>1.5168329999325721E-3</v>
+        <v>1.5296249880488132E-3</v>
       </c>
       <c r="N10">
-        <v>1.4427623262966156E-3</v>
+        <v>1.4588993995679601E-3</v>
       </c>
       <c r="O10">
-        <v>-1.7818777949385402E-4</v>
+        <v>-1.6763124048379022E-4</v>
       </c>
       <c r="P10">
-        <v>2.6317589197805141E-5</v>
+        <v>2.7304610888868938E-5</v>
       </c>
       <c r="Q10">
-        <v>-1.6445067918913482E-4</v>
+        <v>-1.3337174712682435E-4</v>
       </c>
       <c r="R10">
-        <v>1.38127295233935E-5</v>
+        <v>2.613776721260494E-6</v>
       </c>
       <c r="S10">
-        <v>-5.3827987557869897E-5</v>
+        <v>-5.0072335337061495E-5</v>
       </c>
       <c r="T10">
-        <v>4.2033250775927304E-4</v>
+        <v>4.3115134031259544E-4</v>
       </c>
       <c r="U10">
-        <v>4.0146537206704253E-4</v>
+        <v>3.9769228000006963E-4</v>
       </c>
       <c r="V10">
-        <v>2.8210805328087032E-4</v>
+        <v>2.9149035000510816E-4</v>
       </c>
       <c r="W10">
-        <v>2.3602776669035918E-4</v>
+        <v>2.5618405511322324E-4</v>
       </c>
       <c r="X10">
-        <v>2.7922672978385773E-4</v>
+        <v>2.6405773381428434E-4</v>
       </c>
       <c r="Y10">
-        <v>2.388123506821443E-4</v>
+        <v>2.3334799207485679E-4</v>
       </c>
       <c r="Z10">
-        <v>4.4083295800708073E-4</v>
+        <v>4.5710208142066928E-4</v>
       </c>
       <c r="AA10">
-        <v>2.5766761989525063E-4</v>
+        <v>2.6603606550988233E-4</v>
       </c>
       <c r="AB10">
-        <v>2.2500867098353307E-4</v>
+        <v>2.2383866395621094E-4</v>
       </c>
       <c r="AC10">
-        <v>2.5382482555075464E-4</v>
+        <v>2.6738044630313876E-4</v>
       </c>
       <c r="AD10">
-        <v>9.6613041658874353E-5</v>
+        <v>1.2251050196845269E-4</v>
       </c>
       <c r="AE10">
-        <v>3.4874653431506554E-4</v>
+        <v>3.5041205824387937E-4</v>
       </c>
       <c r="AF10">
-        <v>-6.0716183931791956E-5</v>
+        <v>-5.3198390313247991E-5</v>
       </c>
       <c r="AG10">
-        <v>-2.4134555619574811E-4</v>
+        <v>-2.2956566892288533E-4</v>
       </c>
       <c r="AH10">
-        <v>5.7240161079760168E-5</v>
+        <v>4.8524388377189443E-6</v>
       </c>
       <c r="AI10">
-        <v>4.4322067690803009E-5</v>
+        <v>6.2505597259229838E-5</v>
       </c>
       <c r="AJ10">
-        <v>3.0132075470445469E-4</v>
+        <v>3.0223645115781271E-4</v>
       </c>
       <c r="AK10">
-        <v>4.7289686848824009E-4</v>
+        <v>4.5920266683632718E-4</v>
       </c>
       <c r="AL10">
-        <v>2.0584444529755325E-3</v>
+        <v>1.4031707666022179E-3</v>
       </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.2">
@@ -1903,115 +1903,115 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>-0.2424682489428103</v>
+        <v>-0.2297547895689363</v>
       </c>
       <c r="C11">
-        <v>1.1058824094478505E-3</v>
+        <v>1.1665878744977572E-3</v>
       </c>
       <c r="D11">
-        <v>2.6178521736590419E-5</v>
+        <v>3.8365383452976134E-5</v>
       </c>
       <c r="E11">
-        <v>-3.4023275094416237E-7</v>
+        <v>-5.1213070607315817E-7</v>
       </c>
       <c r="F11">
-        <v>-7.7980045907026575E-6</v>
+        <v>-7.0104895062125848E-7</v>
       </c>
       <c r="G11">
-        <v>-1.9133767547301233E-6</v>
+        <v>-7.0428418031717917E-6</v>
       </c>
       <c r="H11">
-        <v>-5.0687743142570468E-5</v>
+        <v>-3.6374307427904139E-6</v>
       </c>
       <c r="I11">
-        <v>5.9028851660346629E-4</v>
+        <v>5.6028322491987511E-4</v>
       </c>
       <c r="J11">
-        <v>-4.3458593642227899E-4</v>
+        <v>-5.059156210665721E-4</v>
       </c>
       <c r="K11">
-        <v>1.4669229142684895E-3</v>
+        <v>1.4717374351948878E-3</v>
       </c>
       <c r="L11">
-        <v>2.4980765415971587E-3</v>
+        <v>2.5307018564911096E-3</v>
       </c>
       <c r="M11">
-        <v>1.973707461614781E-3</v>
+        <v>2.0204117647961493E-3</v>
       </c>
       <c r="N11">
-        <v>1.924806320524461E-3</v>
+        <v>1.9457990520984057E-3</v>
       </c>
       <c r="O11">
-        <v>-6.591599696360238E-5</v>
+        <v>-5.2558274154734932E-5</v>
       </c>
       <c r="P11">
-        <v>1.5996920351486348E-5</v>
+        <v>-3.7169213685412866E-6</v>
       </c>
       <c r="Q11">
-        <v>1.2127931014162274E-4</v>
+        <v>1.4881035912969271E-4</v>
       </c>
       <c r="R11">
-        <v>9.2521461815934429E-5</v>
+        <v>9.8345382135163798E-5</v>
       </c>
       <c r="S11">
-        <v>-8.1562631843719573E-5</v>
+        <v>-8.4351643269366572E-5</v>
       </c>
       <c r="T11">
-        <v>6.9320593683116572E-4</v>
+        <v>7.2118885906164625E-4</v>
       </c>
       <c r="U11">
-        <v>3.2307774575907543E-4</v>
+        <v>3.2376182698039063E-4</v>
       </c>
       <c r="V11">
-        <v>3.0908821597158876E-4</v>
+        <v>3.2780818822117542E-4</v>
       </c>
       <c r="W11">
-        <v>3.0251477329939277E-4</v>
+        <v>3.3070796374947342E-4</v>
       </c>
       <c r="X11">
-        <v>2.6260483901056946E-4</v>
+        <v>2.9032905878042186E-4</v>
       </c>
       <c r="Y11">
-        <v>2.2454866027842471E-4</v>
+        <v>2.4227837182292855E-4</v>
       </c>
       <c r="Z11">
-        <v>5.9929928550424933E-4</v>
+        <v>6.7535015399344421E-4</v>
       </c>
       <c r="AA11">
-        <v>2.648822735723175E-4</v>
+        <v>2.8649995437703504E-4</v>
       </c>
       <c r="AB11">
-        <v>2.6101166839156021E-4</v>
+        <v>2.8231829718151664E-4</v>
       </c>
       <c r="AC11">
-        <v>5.1786952389974012E-4</v>
+        <v>5.6550515479090004E-4</v>
       </c>
       <c r="AD11">
-        <v>1.4349521267512056E-4</v>
+        <v>1.9578221947756739E-4</v>
       </c>
       <c r="AE11">
-        <v>3.4472341442368408E-4</v>
+        <v>3.7615268189726894E-4</v>
       </c>
       <c r="AF11">
-        <v>-7.410532401757946E-5</v>
+        <v>-7.532249675688184E-5</v>
       </c>
       <c r="AG11">
-        <v>-3.5737186212504517E-4</v>
+        <v>-3.788466122760974E-4</v>
       </c>
       <c r="AH11">
-        <v>-1.1549385762271377E-4</v>
+        <v>-1.7468080567819037E-4</v>
       </c>
       <c r="AI11">
-        <v>2.6283950258548273E-5</v>
+        <v>3.8954035308220981E-5</v>
       </c>
       <c r="AJ11">
-        <v>3.2922117413787354E-4</v>
+        <v>3.2940417034890528E-4</v>
       </c>
       <c r="AK11">
-        <v>8.9898177066784473E-4</v>
+        <v>1.0603517332801963E-3</v>
       </c>
       <c r="AL11">
-        <v>3.7112497592041958E-3</v>
+        <v>3.4777977475982241E-3</v>
       </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.2">
@@ -2019,115 +2019,115 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-0.27391490041841382</v>
+        <v>-0.24332480721351663</v>
       </c>
       <c r="C12">
-        <v>1.6587215951037585E-3</v>
+        <v>1.7483264867809503E-3</v>
       </c>
       <c r="D12">
-        <v>1.9094234857100229E-5</v>
+        <v>3.4162348906487377E-5</v>
       </c>
       <c r="E12">
-        <v>-4.0604385613422154E-7</v>
+        <v>-6.453980828737918E-7</v>
       </c>
       <c r="F12">
-        <v>-8.3777002382156356E-6</v>
+        <v>-2.8625642739088967E-6</v>
       </c>
       <c r="G12">
-        <v>3.2259477344254134E-7</v>
+        <v>-1.3044032947946965E-5</v>
       </c>
       <c r="H12">
-        <v>-4.7837519547153464E-5</v>
+        <v>1.5908970527672819E-5</v>
       </c>
       <c r="I12">
-        <v>9.9208714953986791E-4</v>
+        <v>9.50101971731237E-4</v>
       </c>
       <c r="J12">
-        <v>-9.8868219705209649E-4</v>
+        <v>-1.1002311338627166E-3</v>
       </c>
       <c r="K12">
-        <v>1.5168329999325721E-3</v>
+        <v>1.5296249880488132E-3</v>
       </c>
       <c r="L12">
-        <v>1.973707461614781E-3</v>
+        <v>2.0204117647961493E-3</v>
       </c>
       <c r="M12">
-        <v>2.9864840033040959E-3</v>
+        <v>3.0999879144835763E-3</v>
       </c>
       <c r="N12">
-        <v>2.2852942632721391E-3</v>
+        <v>2.3410452925407806E-3</v>
       </c>
       <c r="O12">
-        <v>2.0504311379019322E-5</v>
+        <v>3.2377149041498861E-5</v>
       </c>
       <c r="P12">
-        <v>-1.5970003932191535E-5</v>
+        <v>-3.9041051923910803E-5</v>
       </c>
       <c r="Q12">
-        <v>3.1075415495287968E-4</v>
+        <v>3.3152648945091031E-4</v>
       </c>
       <c r="R12">
-        <v>8.2437943991989433E-5</v>
+        <v>1.0427452557665578E-4</v>
       </c>
       <c r="S12">
-        <v>-9.5978219377698985E-5</v>
+        <v>-1.039146394817229E-4</v>
       </c>
       <c r="T12">
-        <v>7.8760388376139415E-4</v>
+        <v>7.980596790374498E-4</v>
       </c>
       <c r="U12">
-        <v>4.7735108126634065E-4</v>
+        <v>5.0596014004889583E-4</v>
       </c>
       <c r="V12">
-        <v>3.9981735918099664E-4</v>
+        <v>4.4216391870953355E-4</v>
       </c>
       <c r="W12">
-        <v>3.9852101608258116E-4</v>
+        <v>4.5706671843364418E-4</v>
       </c>
       <c r="X12">
-        <v>2.75904763468659E-4</v>
+        <v>3.2403182938415593E-4</v>
       </c>
       <c r="Y12">
-        <v>2.1965349500105156E-4</v>
+        <v>2.429153031594863E-4</v>
       </c>
       <c r="Z12">
-        <v>1.1219324090366836E-3</v>
+        <v>1.2783127283579694E-3</v>
       </c>
       <c r="AA12">
-        <v>2.5831725145798712E-4</v>
+        <v>2.9476491666278245E-4</v>
       </c>
       <c r="AB12">
-        <v>3.3814898750980849E-4</v>
+        <v>3.8416753022632935E-4</v>
       </c>
       <c r="AC12">
-        <v>4.9376538997072332E-4</v>
+        <v>5.2715607285883385E-4</v>
       </c>
       <c r="AD12">
-        <v>3.5244047450889521E-4</v>
+        <v>4.448831451388941E-4</v>
       </c>
       <c r="AE12">
-        <v>3.6926016319388391E-4</v>
+        <v>4.3462663560270103E-4</v>
       </c>
       <c r="AF12">
-        <v>-7.2712037833034114E-5</v>
+        <v>-8.0055629491404361E-5</v>
       </c>
       <c r="AG12">
-        <v>-4.6759768700246744E-4</v>
+        <v>-5.1745765218050863E-4</v>
       </c>
       <c r="AH12">
-        <v>-2.3413646908388439E-4</v>
+        <v>-3.1808389993299773E-4</v>
       </c>
       <c r="AI12">
-        <v>1.440224675136781E-4</v>
+        <v>1.7991050047050865E-4</v>
       </c>
       <c r="AJ12">
-        <v>6.8764391419227889E-5</v>
+        <v>7.0594813430274522E-5</v>
       </c>
       <c r="AK12">
-        <v>2.7956394479531042E-3</v>
+        <v>3.1568656109815544E-3</v>
       </c>
       <c r="AL12">
-        <v>4.1479164061915003E-3</v>
+        <v>4.7059739549920373E-3</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.2">
@@ -2135,115 +2135,115 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>-8.1189434482133407E-2</v>
+        <v>-3.525340792420352E-2</v>
       </c>
       <c r="C13">
-        <v>2.1441034239617096E-3</v>
+        <v>2.2221954755328585E-3</v>
       </c>
       <c r="D13">
-        <v>-4.9265798130001485E-5</v>
+        <v>-2.9703153544453692E-5</v>
       </c>
       <c r="E13">
-        <v>6.209178716875955E-7</v>
+        <v>2.8632678055209805E-7</v>
       </c>
       <c r="F13">
-        <v>-1.6749605364795359E-5</v>
+        <v>-1.114490688866099E-5</v>
       </c>
       <c r="G13">
-        <v>-6.4859836447984063E-6</v>
+        <v>-1.0377087129056522E-5</v>
       </c>
       <c r="H13">
-        <v>-3.8937589848764547E-4</v>
+        <v>-3.3940033655148363E-4</v>
       </c>
       <c r="I13">
-        <v>1.2380031878942049E-3</v>
+        <v>1.158100242385475E-3</v>
       </c>
       <c r="J13">
-        <v>-1.4774661071021769E-3</v>
+        <v>-1.5864235048432193E-3</v>
       </c>
       <c r="K13">
-        <v>1.4427623262966156E-3</v>
+        <v>1.4588993995679601E-3</v>
       </c>
       <c r="L13">
-        <v>1.924806320524461E-3</v>
+        <v>1.9457990520984057E-3</v>
       </c>
       <c r="M13">
-        <v>2.2852942632721391E-3</v>
+        <v>2.3410452925407806E-3</v>
       </c>
       <c r="N13">
-        <v>2.8624452867366079E-3</v>
+        <v>2.886442283029532E-3</v>
       </c>
       <c r="O13">
-        <v>1.3310520693986239E-4</v>
+        <v>1.3539028157254739E-4</v>
       </c>
       <c r="P13">
-        <v>3.3555026337421115E-5</v>
+        <v>4.8327684571907137E-6</v>
       </c>
       <c r="Q13">
-        <v>3.2869410123851641E-4</v>
+        <v>3.4002604892777329E-4</v>
       </c>
       <c r="R13">
-        <v>-2.1603487907827999E-4</v>
+        <v>-2.2675587168549286E-4</v>
       </c>
       <c r="S13">
-        <v>-3.561397520778368E-5</v>
+        <v>-4.1577346955971764E-5</v>
       </c>
       <c r="T13">
-        <v>7.7383497077485931E-4</v>
+        <v>8.0337449069115311E-4</v>
       </c>
       <c r="U13">
-        <v>2.2891252522802051E-4</v>
+        <v>2.2638868117231826E-4</v>
       </c>
       <c r="V13">
-        <v>1.8021347092630937E-4</v>
+        <v>2.0518260968167105E-4</v>
       </c>
       <c r="W13">
-        <v>1.5262262650921849E-4</v>
+        <v>1.8216755710596545E-4</v>
       </c>
       <c r="X13">
-        <v>1.2484016354407485E-4</v>
+        <v>1.6180093589072796E-4</v>
       </c>
       <c r="Y13">
-        <v>2.1083847500673997E-5</v>
+        <v>3.8972067752932299E-5</v>
       </c>
       <c r="Z13">
-        <v>3.400616264403434E-4</v>
+        <v>4.366983539967049E-4</v>
       </c>
       <c r="AA13">
-        <v>1.2461962975315191E-4</v>
+        <v>1.3209274138706849E-4</v>
       </c>
       <c r="AB13">
-        <v>1.0001937802377913E-4</v>
+        <v>1.2037379874075784E-4</v>
       </c>
       <c r="AC13">
-        <v>2.5647592363216721E-4</v>
+        <v>2.7534866816342489E-4</v>
       </c>
       <c r="AD13">
-        <v>8.7078311087619757E-5</v>
+        <v>1.7012385417653178E-4</v>
       </c>
       <c r="AE13">
-        <v>2.5983639759235492E-4</v>
+        <v>2.9528335472843274E-4</v>
       </c>
       <c r="AF13">
-        <v>-2.1325762600560388E-5</v>
+        <v>-2.5768063188203037E-5</v>
       </c>
       <c r="AG13">
-        <v>-2.8203260721939303E-4</v>
+        <v>-3.0244798523954355E-4</v>
       </c>
       <c r="AH13">
-        <v>-1.8490776819335083E-4</v>
+        <v>-2.5158671525581545E-4</v>
       </c>
       <c r="AI13">
-        <v>1.0030989854685891E-4</v>
+        <v>1.0726655595173811E-4</v>
       </c>
       <c r="AJ13">
-        <v>5.230558055267212E-5</v>
+        <v>3.0815174623492758E-5</v>
       </c>
       <c r="AK13">
-        <v>5.5680978943236075E-4</v>
+        <v>7.9930420359565837E-4</v>
       </c>
       <c r="AL13">
-        <v>1.8729769437062817E-3</v>
+        <v>1.8556641604542436E-3</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.2">
@@ -2251,115 +2251,115 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>-9.6640544594780761E-2</v>
+        <v>-8.8596224399571988E-2</v>
       </c>
       <c r="C14">
-        <v>3.6131410017203576E-4</v>
+        <v>3.4732995096946795E-4</v>
       </c>
       <c r="D14">
-        <v>-4.2917521765438102E-5</v>
+        <v>-3.8532428382768145E-5</v>
       </c>
       <c r="E14">
-        <v>4.3816734219150208E-7</v>
+        <v>3.6857133250170009E-7</v>
       </c>
       <c r="F14">
-        <v>-1.8904132894317648E-6</v>
+        <v>-3.121457821565219E-6</v>
       </c>
       <c r="G14">
-        <v>-2.5792579274637747E-6</v>
+        <v>-2.1596407065900496E-6</v>
       </c>
       <c r="H14">
-        <v>1.1626008913003185E-4</v>
+        <v>1.0468923318698208E-4</v>
       </c>
       <c r="I14">
-        <v>1.11327147044202E-4</v>
+        <v>1.102141873955699E-4</v>
       </c>
       <c r="J14">
-        <v>-3.5432687472970704E-4</v>
+        <v>-3.4274843074847024E-4</v>
       </c>
       <c r="K14">
-        <v>-1.7818777949385402E-4</v>
+        <v>-1.6763124048379022E-4</v>
       </c>
       <c r="L14">
-        <v>-6.591599696360238E-5</v>
+        <v>-5.2558274154734932E-5</v>
       </c>
       <c r="M14">
-        <v>2.0504311379019322E-5</v>
+        <v>3.2377149041498861E-5</v>
       </c>
       <c r="N14">
-        <v>1.3310520693986239E-4</v>
+        <v>1.3539028157254739E-4</v>
       </c>
       <c r="O14">
-        <v>3.4220652206147571E-4</v>
+        <v>3.2916624102146644E-4</v>
       </c>
       <c r="P14">
-        <v>-1.8087138547863267E-4</v>
+        <v>-1.8350485477258805E-4</v>
       </c>
       <c r="Q14">
-        <v>1.642963735986582E-4</v>
+        <v>1.269549398388255E-4</v>
       </c>
       <c r="R14">
-        <v>6.392274469379578E-5</v>
+        <v>6.296566279423023E-5</v>
       </c>
       <c r="S14">
-        <v>1.1054582446912281E-5</v>
+        <v>7.8363561147576615E-6</v>
       </c>
       <c r="T14">
-        <v>-9.7169892346544236E-5</v>
+        <v>-9.4010888610620107E-5</v>
       </c>
       <c r="U14">
-        <v>-1.4613705435898757E-4</v>
+        <v>-1.4410691911377927E-4</v>
       </c>
       <c r="V14">
-        <v>-1.4593720770276163E-4</v>
+        <v>-1.330242215334467E-4</v>
       </c>
       <c r="W14">
-        <v>-1.534769365573822E-4</v>
+        <v>-1.4899708390225181E-4</v>
       </c>
       <c r="X14">
-        <v>-1.5348880824856857E-4</v>
+        <v>-1.4138090008725194E-4</v>
       </c>
       <c r="Y14">
-        <v>-1.7112612614779134E-4</v>
+        <v>-1.6015725900731063E-4</v>
       </c>
       <c r="Z14">
-        <v>-9.5996459987674246E-5</v>
+        <v>-7.3363439001952854E-5</v>
       </c>
       <c r="AA14">
-        <v>-1.5851426410824044E-4</v>
+        <v>-1.5368392756940065E-4</v>
       </c>
       <c r="AB14">
-        <v>-1.5227428990887746E-4</v>
+        <v>-1.4124830392842655E-4</v>
       </c>
       <c r="AC14">
-        <v>-9.1240735139923789E-5</v>
+        <v>-7.4790375693594216E-5</v>
       </c>
       <c r="AD14">
-        <v>-7.6497461349766695E-5</v>
+        <v>-6.1249570158942041E-5</v>
       </c>
       <c r="AE14">
-        <v>-1.9841385124146673E-4</v>
+        <v>-1.8085411692275293E-4</v>
       </c>
       <c r="AF14">
-        <v>1.9707518395667558E-5</v>
+        <v>1.5986069526128001E-5</v>
       </c>
       <c r="AG14">
-        <v>-4.3298257807774577E-5</v>
+        <v>-4.9800421270333088E-5</v>
       </c>
       <c r="AH14">
-        <v>-2.7340057892192605E-5</v>
+        <v>-2.4422012228731121E-5</v>
       </c>
       <c r="AI14">
-        <v>-1.0637958707025315E-4</v>
+        <v>-1.1038931377588696E-4</v>
       </c>
       <c r="AJ14">
-        <v>-2.0551544867328128E-4</v>
+        <v>-2.0707938850017554E-4</v>
       </c>
       <c r="AK14">
-        <v>-6.4614521162866066E-5</v>
+        <v>-2.2125848087024228E-5</v>
       </c>
       <c r="AL14">
-        <v>-7.919040754307289E-5</v>
+        <v>1.4954101625526666E-4</v>
       </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.2">
@@ -2367,115 +2367,115 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>0.16005772878411476</v>
+        <v>0.1696358589558957</v>
       </c>
       <c r="C15">
-        <v>4.9868144323422412E-5</v>
+        <v>2.6988363133168886E-5</v>
       </c>
       <c r="D15">
-        <v>-7.1704212273286503E-5</v>
+        <v>-7.0140612572357845E-5</v>
       </c>
       <c r="E15">
-        <v>1.3733802613425309E-6</v>
+        <v>1.3409092103494789E-6</v>
       </c>
       <c r="F15">
-        <v>-2.5649215771245024E-6</v>
+        <v>-5.9405426792837709E-7</v>
       </c>
       <c r="G15">
-        <v>-1.8247166667789016E-6</v>
+        <v>-2.4151293474165215E-7</v>
       </c>
       <c r="H15">
-        <v>-1.3889471390744621E-4</v>
+        <v>-1.4991488865634376E-4</v>
       </c>
       <c r="I15">
-        <v>2.2125225044606782E-4</v>
+        <v>2.1148586977616214E-4</v>
       </c>
       <c r="J15">
-        <v>-1.3148518674039358E-4</v>
+        <v>-1.1915632042609158E-4</v>
       </c>
       <c r="K15">
-        <v>2.6317589197805141E-5</v>
+        <v>2.7304610888868938E-5</v>
       </c>
       <c r="L15">
-        <v>1.5996920351486348E-5</v>
+        <v>-3.7169213685412866E-6</v>
       </c>
       <c r="M15">
-        <v>-1.5970003932191535E-5</v>
+        <v>-3.9041051923910803E-5</v>
       </c>
       <c r="N15">
-        <v>3.3555026337421115E-5</v>
+        <v>4.8327684571907137E-6</v>
       </c>
       <c r="O15">
-        <v>-1.8087138547863267E-4</v>
+        <v>-1.8350485477258805E-4</v>
       </c>
       <c r="P15">
-        <v>6.9497369899848538E-4</v>
+        <v>6.894877258131442E-4</v>
       </c>
       <c r="Q15">
-        <v>5.5292413107065183E-5</v>
+        <v>3.9484830519038426E-5</v>
       </c>
       <c r="R15">
-        <v>-6.6392722773998554E-5</v>
+        <v>-7.1777747038358284E-5</v>
       </c>
       <c r="S15">
-        <v>2.508255560027211E-5</v>
+        <v>2.4121341071563352E-5</v>
       </c>
       <c r="T15">
-        <v>-9.1545456347768905E-5</v>
+        <v>-8.3269974051972942E-5</v>
       </c>
       <c r="U15">
-        <v>-2.8902058776873053E-5</v>
+        <v>-2.7048957475572215E-5</v>
       </c>
       <c r="V15">
-        <v>-6.1162579146565715E-5</v>
+        <v>-5.3248494911361664E-5</v>
       </c>
       <c r="W15">
-        <v>-5.8219880179834249E-5</v>
+        <v>-4.5455751880689739E-5</v>
       </c>
       <c r="X15">
-        <v>-7.278238942481612E-5</v>
+        <v>-5.7631025949004722E-5</v>
       </c>
       <c r="Y15">
-        <v>-4.0865569470503789E-5</v>
+        <v>-3.5527551726629803E-5</v>
       </c>
       <c r="Z15">
-        <v>-1.3966093208154777E-4</v>
+        <v>-1.3263381910058527E-4</v>
       </c>
       <c r="AA15">
-        <v>-4.032931878466916E-5</v>
+        <v>-3.2969459477362844E-5</v>
       </c>
       <c r="AB15">
-        <v>-2.9799196378727452E-5</v>
+        <v>-2.2895654394294344E-5</v>
       </c>
       <c r="AC15">
-        <v>-1.2357253197622882E-4</v>
+        <v>-1.2545451693361795E-4</v>
       </c>
       <c r="AD15">
-        <v>-1.195201122290816E-4</v>
+        <v>-1.0364208742550753E-4</v>
       </c>
       <c r="AE15">
-        <v>-7.4539733048804423E-5</v>
+        <v>-6.514157267702343E-5</v>
       </c>
       <c r="AF15">
-        <v>2.6398815104724331E-5</v>
+        <v>2.6395041758708247E-5</v>
       </c>
       <c r="AG15">
-        <v>6.857118340413009E-5</v>
+        <v>6.9733309581051568E-5</v>
       </c>
       <c r="AH15">
-        <v>7.1712720550812275E-5</v>
+        <v>6.9763613772951899E-5</v>
       </c>
       <c r="AI15">
-        <v>7.4223138723151494E-5</v>
+        <v>7.2662368048550041E-5</v>
       </c>
       <c r="AJ15">
-        <v>9.2620957553202248E-6</v>
+        <v>2.2607564456644093E-5</v>
       </c>
       <c r="AK15">
-        <v>-1.726816996656833E-4</v>
+        <v>-1.4927980298021389E-4</v>
       </c>
       <c r="AL15">
-        <v>-8.0789588079949767E-4</v>
+        <v>-9.2389600404516471E-4</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.2">
@@ -2483,115 +2483,115 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>-6.333355669376246E-3</v>
+        <v>-7.6960972568159407E-3</v>
       </c>
       <c r="C16">
-        <v>5.21829155557328E-4</v>
+        <v>4.845077199879175E-4</v>
       </c>
       <c r="D16">
-        <v>-3.9815448280479046E-5</v>
+        <v>-3.372248923272478E-5</v>
       </c>
       <c r="E16">
-        <v>4.6098207380215883E-7</v>
+        <v>3.7574335880633599E-7</v>
       </c>
       <c r="F16">
-        <v>-9.294914511612545E-7</v>
+        <v>6.4400334893784247E-7</v>
       </c>
       <c r="G16">
-        <v>1.354243317468754E-6</v>
+        <v>1.3857960920250325E-6</v>
       </c>
       <c r="H16">
-        <v>1.6172270616711241E-4</v>
+        <v>1.3113093278026549E-4</v>
       </c>
       <c r="I16">
-        <v>1.2442722215055011E-4</v>
+        <v>1.1996236000682767E-4</v>
       </c>
       <c r="J16">
-        <v>-4.1778325218692707E-4</v>
+        <v>-3.7316481097308702E-4</v>
       </c>
       <c r="K16">
-        <v>-1.6445067918913482E-4</v>
+        <v>-1.3337174712682435E-4</v>
       </c>
       <c r="L16">
-        <v>1.2127931014162274E-4</v>
+        <v>1.4881035912969271E-4</v>
       </c>
       <c r="M16">
-        <v>3.1075415495287968E-4</v>
+        <v>3.3152648945091031E-4</v>
       </c>
       <c r="N16">
-        <v>3.2869410123851641E-4</v>
+        <v>3.4002604892777329E-4</v>
       </c>
       <c r="O16">
-        <v>1.642963735986582E-4</v>
+        <v>1.269549398388255E-4</v>
       </c>
       <c r="P16">
-        <v>5.5292413107065183E-5</v>
+        <v>3.9484830519038426E-5</v>
       </c>
       <c r="Q16">
-        <v>2.6446646791373246E-3</v>
+        <v>2.6598765162618564E-3</v>
       </c>
       <c r="R16">
-        <v>2.4184711740874647E-4</v>
+        <v>2.3297478241770582E-4</v>
       </c>
       <c r="S16">
-        <v>4.2485396126744807E-5</v>
+        <v>3.4904808729044097E-5</v>
       </c>
       <c r="T16">
-        <v>-1.9514606478398939E-4</v>
+        <v>-1.6837384825445312E-4</v>
       </c>
       <c r="U16">
-        <v>-3.7237435516096015E-5</v>
+        <v>1.0373421379304432E-5</v>
       </c>
       <c r="V16">
-        <v>-1.5678340433674287E-4</v>
+        <v>-1.117354671923111E-4</v>
       </c>
       <c r="W16">
-        <v>-5.0812769015288055E-5</v>
+        <v>9.4287239992525975E-6</v>
       </c>
       <c r="X16">
-        <v>-1.5137691416454419E-4</v>
+        <v>-1.0251950836340615E-4</v>
       </c>
       <c r="Y16">
-        <v>-1.6311854147984481E-4</v>
+        <v>-1.1483252342324861E-4</v>
       </c>
       <c r="Z16">
-        <v>-4.5029204461077658E-6</v>
+        <v>7.3650882546151043E-5</v>
       </c>
       <c r="AA16">
-        <v>-1.5371937325589797E-4</v>
+        <v>-9.1174832405318805E-5</v>
       </c>
       <c r="AB16">
-        <v>-1.1468064486220317E-4</v>
+        <v>-5.9829093505551391E-5</v>
       </c>
       <c r="AC16">
-        <v>-1.0604325568780706E-4</v>
+        <v>-6.3944817539409051E-5</v>
       </c>
       <c r="AD16">
-        <v>-1.5319049780141862E-4</v>
+        <v>-9.6870081066907309E-5</v>
       </c>
       <c r="AE16">
-        <v>-2.4819717713608718E-4</v>
+        <v>-2.0547518966914247E-4</v>
       </c>
       <c r="AF16">
-        <v>6.2276125026192983E-5</v>
+        <v>5.5217241106854903E-5</v>
       </c>
       <c r="AG16">
-        <v>3.1277564311195556E-5</v>
+        <v>1.5095427334314274E-5</v>
       </c>
       <c r="AH16">
-        <v>-3.1742618556409241E-5</v>
+        <v>-4.7615599785720097E-5</v>
       </c>
       <c r="AI16">
-        <v>-1.5937145141711495E-4</v>
+        <v>-1.4975506209247366E-4</v>
       </c>
       <c r="AJ16">
-        <v>-1.8819564898173524E-4</v>
+        <v>-1.4551202399548608E-4</v>
       </c>
       <c r="AK16">
-        <v>3.6945243513388697E-4</v>
+        <v>4.3247647696569719E-4</v>
       </c>
       <c r="AL16">
-        <v>-3.2889535914228749E-3</v>
+        <v>-2.9369984849974707E-3</v>
       </c>
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.2">
@@ -2599,115 +2599,115 @@
         <v>29</v>
       </c>
       <c r="B17">
-        <v>-4.5373534790713398E-2</v>
+        <v>-2.3922035373982246E-2</v>
       </c>
       <c r="C17">
-        <v>3.198405765240627E-4</v>
+        <v>3.1795346361254695E-4</v>
       </c>
       <c r="D17">
-        <v>-1.5826027182835878E-5</v>
+        <v>-1.0961679661497309E-5</v>
       </c>
       <c r="E17">
-        <v>2.4303483718978122E-7</v>
+        <v>1.8243497411146717E-7</v>
       </c>
       <c r="F17">
-        <v>-2.189508657971858E-7</v>
+        <v>1.8169749025254589E-6</v>
       </c>
       <c r="G17">
-        <v>1.9169267527975398E-6</v>
+        <v>-2.6065300542258092E-6</v>
       </c>
       <c r="H17">
-        <v>5.6625980918611986E-4</v>
+        <v>5.3285487967453854E-4</v>
       </c>
       <c r="I17">
-        <v>-3.8489537725640478E-4</v>
+        <v>-3.2832298733198899E-4</v>
       </c>
       <c r="J17">
-        <v>-1.4111734119706069E-4</v>
+        <v>-1.3841277220785558E-4</v>
       </c>
       <c r="K17">
-        <v>1.38127295233935E-5</v>
+        <v>2.613776721260494E-6</v>
       </c>
       <c r="L17">
-        <v>9.2521461815934429E-5</v>
+        <v>9.8345382135163798E-5</v>
       </c>
       <c r="M17">
-        <v>8.2437943991989433E-5</v>
+        <v>1.0427452557665578E-4</v>
       </c>
       <c r="N17">
-        <v>-2.1603487907827999E-4</v>
+        <v>-2.2675587168549286E-4</v>
       </c>
       <c r="O17">
-        <v>6.392274469379578E-5</v>
+        <v>6.296566279423023E-5</v>
       </c>
       <c r="P17">
-        <v>-6.6392722773998554E-5</v>
+        <v>-7.1777747038358284E-5</v>
       </c>
       <c r="Q17">
-        <v>2.4184711740874647E-4</v>
+        <v>2.3297478241770582E-4</v>
       </c>
       <c r="R17">
-        <v>8.0161284809879599E-4</v>
+        <v>8.2722662820415745E-4</v>
       </c>
       <c r="S17">
-        <v>-2.5894476776015498E-5</v>
+        <v>-3.0690882509336407E-5</v>
       </c>
       <c r="T17">
-        <v>3.6416801490513889E-5</v>
+        <v>2.9047555104608677E-5</v>
       </c>
       <c r="U17">
-        <v>1.0763621724097197E-4</v>
+        <v>1.271425686217113E-4</v>
       </c>
       <c r="V17">
-        <v>7.5575006893857752E-5</v>
+        <v>8.8395592307760574E-5</v>
       </c>
       <c r="W17">
-        <v>1.2070144954812461E-4</v>
+        <v>1.4815178542516817E-4</v>
       </c>
       <c r="X17">
-        <v>1.1044952554318887E-4</v>
+        <v>1.2793428384854792E-4</v>
       </c>
       <c r="Y17">
-        <v>1.2389858534860997E-4</v>
+        <v>1.3822003228968703E-4</v>
       </c>
       <c r="Z17">
-        <v>4.7511272818472972E-4</v>
+        <v>5.4142873525537009E-4</v>
       </c>
       <c r="AA17">
-        <v>1.8962679754172817E-5</v>
+        <v>4.1169310045427237E-5</v>
       </c>
       <c r="AB17">
-        <v>1.7945779214186377E-4</v>
+        <v>2.0325523126090919E-4</v>
       </c>
       <c r="AC17">
-        <v>2.9116251141705766E-4</v>
+        <v>3.1865545823334021E-4</v>
       </c>
       <c r="AD17">
-        <v>-1.4906258453559575E-5</v>
+        <v>2.8577178219182855E-5</v>
       </c>
       <c r="AE17">
-        <v>5.1735375042640626E-5</v>
+        <v>8.0774329570172838E-5</v>
       </c>
       <c r="AF17">
-        <v>-2.4937886476859653E-5</v>
+        <v>-2.9181602343716386E-5</v>
       </c>
       <c r="AG17">
-        <v>-1.3401442170895693E-4</v>
+        <v>-1.6425031801793328E-4</v>
       </c>
       <c r="AH17">
-        <v>-1.0463586593841934E-4</v>
+        <v>-1.464280794781427E-4</v>
       </c>
       <c r="AI17">
-        <v>-9.4955411713562793E-5</v>
+        <v>-8.3144337218020383E-5</v>
       </c>
       <c r="AJ17">
-        <v>6.1720142017724429E-5</v>
+        <v>6.6909091201014168E-5</v>
       </c>
       <c r="AK17">
-        <v>1.0707419821768243E-3</v>
+        <v>1.2622166399992238E-3</v>
       </c>
       <c r="AL17">
-        <v>1.5884291220587734E-3</v>
+        <v>1.9159844410129145E-3</v>
       </c>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.2">
@@ -2715,115 +2715,115 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>4.3516100953845741E-3</v>
+        <v>3.8945568469491709E-3</v>
       </c>
       <c r="C18">
-        <v>-9.7798575979757556E-5</v>
+        <v>-1.2611545203569901E-4</v>
       </c>
       <c r="D18">
-        <v>-9.4091939085051831E-6</v>
+        <v>-8.5091991468634652E-6</v>
       </c>
       <c r="E18">
-        <v>1.660502179178264E-7</v>
+        <v>1.4662442463619891E-7</v>
       </c>
       <c r="F18">
-        <v>2.0532801182330886E-7</v>
+        <v>-6.680357150721785E-7</v>
       </c>
       <c r="G18">
-        <v>-6.5391601548419619E-7</v>
+        <v>1.3960139662901061E-6</v>
       </c>
       <c r="H18">
-        <v>4.8251024376459147E-5</v>
+        <v>3.803704287464983E-5</v>
       </c>
       <c r="I18">
-        <v>-6.8841955017501753E-5</v>
+        <v>-6.5569495540851268E-5</v>
       </c>
       <c r="J18">
-        <v>1.0348692034041617E-4</v>
+        <v>1.3004048201979937E-4</v>
       </c>
       <c r="K18">
-        <v>-5.3827987557869897E-5</v>
+        <v>-5.0072335337061495E-5</v>
       </c>
       <c r="L18">
-        <v>-8.1562631843719573E-5</v>
+        <v>-8.4351643269366572E-5</v>
       </c>
       <c r="M18">
-        <v>-9.5978219377698985E-5</v>
+        <v>-1.039146394817229E-4</v>
       </c>
       <c r="N18">
-        <v>-3.561397520778368E-5</v>
+        <v>-4.1577346955971764E-5</v>
       </c>
       <c r="O18">
-        <v>1.1054582446912281E-5</v>
+        <v>7.8363561147576615E-6</v>
       </c>
       <c r="P18">
-        <v>2.508255560027211E-5</v>
+        <v>2.4121341071563352E-5</v>
       </c>
       <c r="Q18">
-        <v>4.2485396126744807E-5</v>
+        <v>3.4904808729044097E-5</v>
       </c>
       <c r="R18">
-        <v>-2.5894476776015498E-5</v>
+        <v>-3.0690882509336407E-5</v>
       </c>
       <c r="S18">
-        <v>1.306669067404273E-4</v>
+        <v>1.3105812821983739E-4</v>
       </c>
       <c r="T18">
-        <v>-2.4955748218541602E-5</v>
+        <v>-2.2629943882376694E-5</v>
       </c>
       <c r="U18">
-        <v>-5.369479008496752E-5</v>
+        <v>-6.171784764328078E-5</v>
       </c>
       <c r="V18">
-        <v>-6.2330235486660751E-5</v>
+        <v>-6.7974464738856499E-5</v>
       </c>
       <c r="W18">
-        <v>-6.0859718618287185E-5</v>
+        <v>-6.5472062491542552E-5</v>
       </c>
       <c r="X18">
-        <v>-4.3631710935890158E-5</v>
+        <v>-4.4706284725290913E-5</v>
       </c>
       <c r="Y18">
-        <v>-3.8511068326931106E-5</v>
+        <v>-3.9417604131501693E-5</v>
       </c>
       <c r="Z18">
-        <v>-1.6431611009947236E-4</v>
+        <v>-1.7316322947060273E-4</v>
       </c>
       <c r="AA18">
-        <v>-6.4341016670543079E-5</v>
+        <v>-6.7060874585868108E-5</v>
       </c>
       <c r="AB18">
-        <v>-6.7874054031758987E-5</v>
+        <v>-6.8202614579487841E-5</v>
       </c>
       <c r="AC18">
-        <v>-9.5757965635501815E-5</v>
+        <v>-1.010634633340046E-4</v>
       </c>
       <c r="AD18">
-        <v>-8.7939373720460814E-5</v>
+        <v>-8.8252890970888682E-5</v>
       </c>
       <c r="AE18">
-        <v>-4.5208238212029669E-5</v>
+        <v>-5.0869929795726784E-5</v>
       </c>
       <c r="AF18">
-        <v>1.4291660648760806E-4</v>
+        <v>1.4369995520663976E-4</v>
       </c>
       <c r="AG18">
-        <v>2.3549165937703648E-4</v>
+        <v>2.4045305354425568E-4</v>
       </c>
       <c r="AH18">
-        <v>-4.9303328716974321E-7</v>
+        <v>5.1184794542013037E-6</v>
       </c>
       <c r="AI18">
-        <v>-2.44031792207694E-7</v>
+        <v>-1.0318830751175363E-5</v>
       </c>
       <c r="AJ18">
-        <v>-3.8020929355750063E-5</v>
+        <v>-4.1495320219959823E-5</v>
       </c>
       <c r="AK18">
-        <v>-3.6295903438855748E-4</v>
+        <v>-3.6945511760223121E-4</v>
       </c>
       <c r="AL18">
-        <v>-9.7853815072540817E-3</v>
+        <v>-9.865326003005076E-3</v>
       </c>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.2">
@@ -2831,115 +2831,115 @@
         <v>31</v>
       </c>
       <c r="B19">
-        <v>0.10500009155419515</v>
+        <v>6.2173770767347501E-2</v>
       </c>
       <c r="C19">
-        <v>8.7018067734567208E-4</v>
+        <v>9.2020723213705104E-4</v>
       </c>
       <c r="D19">
-        <v>4.8811480853869313E-5</v>
+        <v>4.8252627919070511E-5</v>
       </c>
       <c r="E19">
-        <v>-7.7459425747652971E-7</v>
+        <v>-7.5423300659791378E-7</v>
       </c>
       <c r="F19">
-        <v>8.7580721727992496E-6</v>
+        <v>8.7905071189336316E-6</v>
       </c>
       <c r="G19">
-        <v>5.2282006539827995E-6</v>
+        <v>5.60627969163034E-6</v>
       </c>
       <c r="H19">
-        <v>5.6545934320001089E-5</v>
+        <v>8.2778847100849304E-5</v>
       </c>
       <c r="I19">
-        <v>-1.2503828804736401E-6</v>
+        <v>-1.1210077178624761E-5</v>
       </c>
       <c r="J19">
-        <v>-3.398453766931455E-4</v>
+        <v>-3.8491506647991239E-4</v>
       </c>
       <c r="K19">
-        <v>4.2033250775927304E-4</v>
+        <v>4.3115134031259544E-4</v>
       </c>
       <c r="L19">
-        <v>6.9320593683116572E-4</v>
+        <v>7.2118885906164625E-4</v>
       </c>
       <c r="M19">
-        <v>7.8760388376139415E-4</v>
+        <v>7.980596790374498E-4</v>
       </c>
       <c r="N19">
-        <v>7.7383497077485931E-4</v>
+        <v>8.0337449069115311E-4</v>
       </c>
       <c r="O19">
-        <v>-9.7169892346544236E-5</v>
+        <v>-9.4010888610620107E-5</v>
       </c>
       <c r="P19">
-        <v>-9.1545456347768905E-5</v>
+        <v>-8.3269974051972942E-5</v>
       </c>
       <c r="Q19">
-        <v>-1.9514606478398939E-4</v>
+        <v>-1.6837384825445312E-4</v>
       </c>
       <c r="R19">
-        <v>3.6416801490513889E-5</v>
+        <v>2.9047555104608677E-5</v>
       </c>
       <c r="S19">
-        <v>-2.4955748218541602E-5</v>
+        <v>-2.2629943882376694E-5</v>
       </c>
       <c r="T19">
-        <v>1.1718914429542406E-3</v>
+        <v>1.2117303912154622E-3</v>
       </c>
       <c r="U19">
-        <v>1.6816196024752749E-4</v>
+        <v>1.7667256537239249E-4</v>
       </c>
       <c r="V19">
-        <v>2.2341737050153126E-4</v>
+        <v>2.1298464911942769E-4</v>
       </c>
       <c r="W19">
-        <v>2.0506522737004279E-4</v>
+        <v>1.9772647039112233E-4</v>
       </c>
       <c r="X19">
-        <v>2.2259619707391619E-4</v>
+        <v>2.233250105026045E-4</v>
       </c>
       <c r="Y19">
-        <v>1.8618809015172669E-4</v>
+        <v>1.7193831475931362E-4</v>
       </c>
       <c r="Z19">
-        <v>2.9713506728380073E-4</v>
+        <v>2.5970262285962857E-4</v>
       </c>
       <c r="AA19">
-        <v>1.1763993073281795E-4</v>
+        <v>1.1922635542131398E-4</v>
       </c>
       <c r="AB19">
-        <v>2.0036106367037369E-4</v>
+        <v>1.8972155858813225E-4</v>
       </c>
       <c r="AC19">
-        <v>1.5355421674384344E-4</v>
+        <v>1.4552762293012069E-4</v>
       </c>
       <c r="AD19">
-        <v>2.3314160962631628E-4</v>
+        <v>1.9141987622453994E-4</v>
       </c>
       <c r="AE19">
-        <v>2.552069544261243E-4</v>
+        <v>2.3519481990508543E-4</v>
       </c>
       <c r="AF19">
-        <v>-2.3013033238314802E-5</v>
+        <v>-2.0020278928987788E-5</v>
       </c>
       <c r="AG19">
-        <v>-5.1638884831770471E-5</v>
+        <v>-4.3876688809288021E-5</v>
       </c>
       <c r="AH19">
-        <v>-9.0171096759436077E-5</v>
+        <v>-7.8474926040751495E-5</v>
       </c>
       <c r="AI19">
-        <v>-6.0997626068332185E-5</v>
+        <v>-4.9310419049289518E-5</v>
       </c>
       <c r="AJ19">
-        <v>5.9211623298469356E-5</v>
+        <v>7.0617155048474742E-5</v>
       </c>
       <c r="AK19">
-        <v>2.6882419343617157E-4</v>
+        <v>1.2677358794206325E-4</v>
       </c>
       <c r="AL19">
-        <v>-5.9191310484509214E-4</v>
+        <v>-8.1785769193418525E-4</v>
       </c>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.2">
@@ -2947,115 +2947,115 @@
         <v>32</v>
       </c>
       <c r="B20">
-        <v>-2.6414882107528709E-2</v>
+        <v>-2.4811669829727923E-2</v>
       </c>
       <c r="C20">
-        <v>-9.3771685483352678E-4</v>
+        <v>-8.3185897810384346E-4</v>
       </c>
       <c r="D20">
-        <v>9.0282821865002568E-5</v>
+        <v>9.4858443313781252E-5</v>
       </c>
       <c r="E20">
-        <v>-1.5281358212027645E-6</v>
+        <v>-1.5941604962152209E-6</v>
       </c>
       <c r="F20">
-        <v>-8.7372087316935154E-7</v>
+        <v>1.3450910449102438E-6</v>
       </c>
       <c r="G20">
-        <v>8.9701525568045006E-7</v>
+        <v>-5.1534373013510123E-6</v>
       </c>
       <c r="H20">
-        <v>-1.010516146360531E-4</v>
+        <v>-7.8108468133902091E-5</v>
       </c>
       <c r="I20">
-        <v>1.9359189002721156E-4</v>
+        <v>1.6723232310480058E-4</v>
       </c>
       <c r="J20">
-        <v>8.6567656666861959E-4</v>
+        <v>7.8261807956351084E-4</v>
       </c>
       <c r="K20">
-        <v>4.0146537206704253E-4</v>
+        <v>3.9769228000006963E-4</v>
       </c>
       <c r="L20">
-        <v>3.2307774575907543E-4</v>
+        <v>3.2376182698039063E-4</v>
       </c>
       <c r="M20">
-        <v>4.7735108126634065E-4</v>
+        <v>5.0596014004889583E-4</v>
       </c>
       <c r="N20">
-        <v>2.2891252522802051E-4</v>
+        <v>2.2638868117231826E-4</v>
       </c>
       <c r="O20">
-        <v>-1.4613705435898757E-4</v>
+        <v>-1.4410691911377927E-4</v>
       </c>
       <c r="P20">
-        <v>-2.8902058776873053E-5</v>
+        <v>-2.7048957475572215E-5</v>
       </c>
       <c r="Q20">
-        <v>-3.7237435516096015E-5</v>
+        <v>1.0373421379304432E-5</v>
       </c>
       <c r="R20">
-        <v>1.0763621724097197E-4</v>
+        <v>1.271425686217113E-4</v>
       </c>
       <c r="S20">
-        <v>-5.369479008496752E-5</v>
+        <v>-6.171784764328078E-5</v>
       </c>
       <c r="T20">
-        <v>1.6816196024752749E-4</v>
+        <v>1.7667256537239249E-4</v>
       </c>
       <c r="U20">
-        <v>5.6224706508192232E-3</v>
+        <v>5.6740232289179656E-3</v>
       </c>
       <c r="V20">
-        <v>1.8348630122893644E-3</v>
+        <v>1.8574535407028699E-3</v>
       </c>
       <c r="W20">
-        <v>1.882222461360833E-3</v>
+        <v>1.9210975534026768E-3</v>
       </c>
       <c r="X20">
-        <v>1.800459284979964E-3</v>
+        <v>1.8273397178050575E-3</v>
       </c>
       <c r="Y20">
-        <v>1.7995724512835361E-3</v>
+        <v>1.8218355247612106E-3</v>
       </c>
       <c r="Z20">
-        <v>2.1666517481043878E-3</v>
+        <v>2.2275628201659341E-3</v>
       </c>
       <c r="AA20">
-        <v>1.8670109773249004E-3</v>
+        <v>1.8998891386364958E-3</v>
       </c>
       <c r="AB20">
-        <v>1.9346371975489636E-3</v>
+        <v>1.9630295266209875E-3</v>
       </c>
       <c r="AC20">
-        <v>1.9209148825839266E-3</v>
+        <v>1.9464228286575627E-3</v>
       </c>
       <c r="AD20">
-        <v>1.8921780405685503E-3</v>
+        <v>1.9233599925610326E-3</v>
       </c>
       <c r="AE20">
-        <v>1.9071583568653137E-3</v>
+        <v>1.9376800643951713E-3</v>
       </c>
       <c r="AF20">
-        <v>-5.6499350464947355E-5</v>
+        <v>-6.5243425858294441E-5</v>
       </c>
       <c r="AG20">
-        <v>2.6469155160787532E-5</v>
+        <v>-1.739988023915335E-5</v>
       </c>
       <c r="AH20">
-        <v>1.8053653134589276E-4</v>
+        <v>1.9536586607487346E-4</v>
       </c>
       <c r="AI20">
-        <v>5.6122115525973778E-4</v>
+        <v>5.8301872379350954E-4</v>
       </c>
       <c r="AJ20">
-        <v>1.1836873575856084E-3</v>
+        <v>1.2285457859871624E-3</v>
       </c>
       <c r="AK20">
-        <v>1.8265705311134891E-3</v>
+        <v>1.9465304900853578E-3</v>
       </c>
       <c r="AL20">
-        <v>6.0438473745494468E-4</v>
+        <v>1.2570580759453292E-3</v>
       </c>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.2">
@@ -3063,115 +3063,115 @@
         <v>33</v>
       </c>
       <c r="B21">
-        <v>4.290597633466741E-2</v>
+        <v>3.8294562312711063E-2</v>
       </c>
       <c r="C21">
-        <v>-1.2249971090131685E-6</v>
+        <v>1.0994851444448214E-4</v>
       </c>
       <c r="D21">
-        <v>9.5109976528795666E-5</v>
+        <v>9.0989921146466591E-5</v>
       </c>
       <c r="E21">
-        <v>-1.4971063571341248E-6</v>
+        <v>-1.4215308313672527E-6</v>
       </c>
       <c r="F21">
-        <v>4.181324953945367E-6</v>
+        <v>4.025986691406764E-6</v>
       </c>
       <c r="G21">
-        <v>1.4325232378887304E-6</v>
+        <v>-5.3881480956986952E-6</v>
       </c>
       <c r="H21">
-        <v>5.7443240310345921E-5</v>
+        <v>8.2830541979518019E-5</v>
       </c>
       <c r="I21">
-        <v>7.3366007915953431E-5</v>
+        <v>7.8761043703936087E-5</v>
       </c>
       <c r="J21">
-        <v>5.648478999134427E-5</v>
+        <v>-4.606866627905544E-5</v>
       </c>
       <c r="K21">
-        <v>2.8210805328087032E-4</v>
+        <v>2.9149035000510816E-4</v>
       </c>
       <c r="L21">
-        <v>3.0908821597158876E-4</v>
+        <v>3.2780818822117542E-4</v>
       </c>
       <c r="M21">
-        <v>3.9981735918099664E-4</v>
+        <v>4.4216391870953355E-4</v>
       </c>
       <c r="N21">
-        <v>1.8021347092630937E-4</v>
+        <v>2.0518260968167105E-4</v>
       </c>
       <c r="O21">
-        <v>-1.4593720770276163E-4</v>
+        <v>-1.330242215334467E-4</v>
       </c>
       <c r="P21">
-        <v>-6.1162579146565715E-5</v>
+        <v>-5.3248494911361664E-5</v>
       </c>
       <c r="Q21">
-        <v>-1.5678340433674287E-4</v>
+        <v>-1.117354671923111E-4</v>
       </c>
       <c r="R21">
-        <v>7.5575006893857752E-5</v>
+        <v>8.8395592307760574E-5</v>
       </c>
       <c r="S21">
-        <v>-6.2330235486660751E-5</v>
+        <v>-6.7974464738856499E-5</v>
       </c>
       <c r="T21">
-        <v>2.2341737050153126E-4</v>
+        <v>2.1298464911942769E-4</v>
       </c>
       <c r="U21">
-        <v>1.8348630122893644E-3</v>
+        <v>1.8574535407028699E-3</v>
       </c>
       <c r="V21">
-        <v>2.8612085673158294E-3</v>
+        <v>2.8920092573815788E-3</v>
       </c>
       <c r="W21">
-        <v>1.8354479885912508E-3</v>
+        <v>1.8637322063900959E-3</v>
       </c>
       <c r="X21">
-        <v>1.776217392515024E-3</v>
+        <v>1.7932585873553352E-3</v>
       </c>
       <c r="Y21">
-        <v>1.7708420949610066E-3</v>
+        <v>1.782955011217812E-3</v>
       </c>
       <c r="Z21">
-        <v>2.0309898032322879E-3</v>
+        <v>2.0644669881111416E-3</v>
       </c>
       <c r="AA21">
-        <v>1.8113882579045601E-3</v>
+        <v>1.8361811837960412E-3</v>
       </c>
       <c r="AB21">
-        <v>1.8815832756291565E-3</v>
+        <v>1.8992719755830723E-3</v>
       </c>
       <c r="AC21">
-        <v>1.8667607528573295E-3</v>
+        <v>1.8811358344825223E-3</v>
       </c>
       <c r="AD21">
-        <v>1.8289124802721287E-3</v>
+        <v>1.8440763326476764E-3</v>
       </c>
       <c r="AE21">
-        <v>1.8610075630263855E-3</v>
+        <v>1.8782525007587443E-3</v>
       </c>
       <c r="AF21">
-        <v>-7.0412316212073401E-5</v>
+        <v>-7.7848699895063703E-5</v>
       </c>
       <c r="AG21">
-        <v>-1.1503186087038618E-4</v>
+        <v>-1.4088841276468076E-4</v>
       </c>
       <c r="AH21">
-        <v>6.8074780378203788E-6</v>
+        <v>9.2847571774129197E-6</v>
       </c>
       <c r="AI21">
-        <v>4.6836300676074427E-4</v>
+        <v>4.7392527083531223E-4</v>
       </c>
       <c r="AJ21">
-        <v>1.0445037578769743E-3</v>
+        <v>1.0787743869131619E-3</v>
       </c>
       <c r="AK21">
-        <v>1.3197456253007927E-3</v>
+        <v>1.3632526422522979E-3</v>
       </c>
       <c r="AL21">
-        <v>1.0058639878370102E-3</v>
+        <v>1.7711631564490352E-3</v>
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.2">
@@ -3179,115 +3179,115 @@
         <v>34</v>
       </c>
       <c r="B22">
-        <v>-3.1668889714538476E-2</v>
+        <v>-3.45107458494864E-2</v>
       </c>
       <c r="C22">
-        <v>2.8817523859004485E-4</v>
+        <v>3.4149617901906395E-4</v>
       </c>
       <c r="D22">
-        <v>1.4294321974072071E-4</v>
+        <v>1.4487261463278959E-4</v>
       </c>
       <c r="E22">
-        <v>-2.1694465893661048E-6</v>
+        <v>-2.1880704982306739E-6</v>
       </c>
       <c r="F22">
-        <v>2.477874233379201E-6</v>
+        <v>3.0335189609310603E-6</v>
       </c>
       <c r="G22">
-        <v>4.0825252324169498E-6</v>
+        <v>-3.978296045687748E-6</v>
       </c>
       <c r="H22">
-        <v>5.1214806810342197E-5</v>
+        <v>7.7820315155593934E-5</v>
       </c>
       <c r="I22">
-        <v>1.501352840029798E-4</v>
+        <v>1.5617021102617528E-4</v>
       </c>
       <c r="J22">
-        <v>4.7669637045386304E-4</v>
+        <v>4.2440083018852135E-4</v>
       </c>
       <c r="K22">
-        <v>2.3602776669035918E-4</v>
+        <v>2.5618405511322324E-4</v>
       </c>
       <c r="L22">
-        <v>3.0251477329939277E-4</v>
+        <v>3.3070796374947342E-4</v>
       </c>
       <c r="M22">
-        <v>3.9852101608258116E-4</v>
+        <v>4.5706671843364418E-4</v>
       </c>
       <c r="N22">
-        <v>1.5262262650921849E-4</v>
+        <v>1.8216755710596545E-4</v>
       </c>
       <c r="O22">
-        <v>-1.534769365573822E-4</v>
+        <v>-1.4899708390225181E-4</v>
       </c>
       <c r="P22">
-        <v>-5.8219880179834249E-5</v>
+        <v>-4.5455751880689739E-5</v>
       </c>
       <c r="Q22">
-        <v>-5.0812769015288055E-5</v>
+        <v>9.4287239992525975E-6</v>
       </c>
       <c r="R22">
-        <v>1.2070144954812461E-4</v>
+        <v>1.4815178542516817E-4</v>
       </c>
       <c r="S22">
-        <v>-6.0859718618287185E-5</v>
+        <v>-6.5472062491542552E-5</v>
       </c>
       <c r="T22">
-        <v>2.0506522737004279E-4</v>
+        <v>1.9772647039112233E-4</v>
       </c>
       <c r="U22">
-        <v>1.882222461360833E-3</v>
+        <v>1.9210975534026768E-3</v>
       </c>
       <c r="V22">
-        <v>1.8354479885912508E-3</v>
+        <v>1.8637322063900959E-3</v>
       </c>
       <c r="W22">
-        <v>3.2758118808703328E-3</v>
+        <v>3.3576488540754132E-3</v>
       </c>
       <c r="X22">
-        <v>1.8098791877475151E-3</v>
+        <v>1.8412059755808844E-3</v>
       </c>
       <c r="Y22">
-        <v>1.8041615919183259E-3</v>
+        <v>1.8283368597180748E-3</v>
       </c>
       <c r="Z22">
-        <v>2.1632966595566865E-3</v>
+        <v>2.2383163748330055E-3</v>
       </c>
       <c r="AA22">
-        <v>1.8520485904735449E-3</v>
+        <v>1.8868885036266024E-3</v>
       </c>
       <c r="AB22">
-        <v>1.9341792812432701E-3</v>
+        <v>1.9707676792196102E-3</v>
       </c>
       <c r="AC22">
-        <v>1.9322586562673014E-3</v>
+        <v>1.965770522141053E-3</v>
       </c>
       <c r="AD22">
-        <v>1.8684394054824106E-3</v>
+        <v>1.9024252576710921E-3</v>
       </c>
       <c r="AE22">
-        <v>1.8831430315509753E-3</v>
+        <v>1.9202388501367673E-3</v>
       </c>
       <c r="AF22">
-        <v>-6.4337940354237475E-5</v>
+        <v>-7.020635470974851E-5</v>
       </c>
       <c r="AG22">
-        <v>-1.1550104900275498E-4</v>
+        <v>-1.3642910401312242E-4</v>
       </c>
       <c r="AH22">
-        <v>-1.3069947915023491E-4</v>
+        <v>-1.503532742914133E-4</v>
       </c>
       <c r="AI22">
-        <v>5.4374429515761371E-4</v>
+        <v>5.984255336311437E-4</v>
       </c>
       <c r="AJ22">
-        <v>1.0631946224133367E-3</v>
+        <v>1.1088562784142143E-3</v>
       </c>
       <c r="AK22">
-        <v>1.7510267005242911E-3</v>
+        <v>1.8957295801901343E-3</v>
       </c>
       <c r="AL22">
-        <v>-9.5468859506385798E-5</v>
+        <v>4.7721010105692893E-4</v>
       </c>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.2">
@@ -3295,115 +3295,115 @@
         <v>35</v>
       </c>
       <c r="B23">
-        <v>7.0711548906415192E-2</v>
+        <v>6.5426379414525199E-2</v>
       </c>
       <c r="C23">
-        <v>2.2170416128040903E-4</v>
+        <v>2.757096644079506E-4</v>
       </c>
       <c r="D23">
-        <v>1.4957952847651922E-4</v>
+        <v>1.4618794467486144E-4</v>
       </c>
       <c r="E23">
-        <v>-2.3550439380312498E-6</v>
+        <v>-2.2935474202485726E-6</v>
       </c>
       <c r="F23">
-        <v>3.7111969354215519E-6</v>
+        <v>1.787296442355267E-6</v>
       </c>
       <c r="G23">
-        <v>-3.9216534051962537E-7</v>
+        <v>-3.3621390639611549E-6</v>
       </c>
       <c r="H23">
-        <v>1.3098028467256766E-5</v>
+        <v>2.4047013417550134E-5</v>
       </c>
       <c r="I23">
-        <v>6.0242611992599132E-5</v>
+        <v>8.493791552452478E-5</v>
       </c>
       <c r="J23">
-        <v>-3.1364590772588083E-5</v>
+        <v>-4.8702403317142564E-5</v>
       </c>
       <c r="K23">
-        <v>2.7922672978385773E-4</v>
+        <v>2.6405773381428434E-4</v>
       </c>
       <c r="L23">
-        <v>2.6260483901056946E-4</v>
+        <v>2.9032905878042186E-4</v>
       </c>
       <c r="M23">
-        <v>2.75904763468659E-4</v>
+        <v>3.2403182938415593E-4</v>
       </c>
       <c r="N23">
-        <v>1.2484016354407485E-4</v>
+        <v>1.6180093589072796E-4</v>
       </c>
       <c r="O23">
-        <v>-1.5348880824856857E-4</v>
+        <v>-1.4138090008725194E-4</v>
       </c>
       <c r="P23">
-        <v>-7.278238942481612E-5</v>
+        <v>-5.7631025949004722E-5</v>
       </c>
       <c r="Q23">
-        <v>-1.5137691416454419E-4</v>
+        <v>-1.0251950836340615E-4</v>
       </c>
       <c r="R23">
-        <v>1.1044952554318887E-4</v>
+        <v>1.2793428384854792E-4</v>
       </c>
       <c r="S23">
-        <v>-4.3631710935890158E-5</v>
+        <v>-4.4706284725290913E-5</v>
       </c>
       <c r="T23">
-        <v>2.2259619707391619E-4</v>
+        <v>2.233250105026045E-4</v>
       </c>
       <c r="U23">
-        <v>1.800459284979964E-3</v>
+        <v>1.8273397178050575E-3</v>
       </c>
       <c r="V23">
-        <v>1.776217392515024E-3</v>
+        <v>1.7932585873553352E-3</v>
       </c>
       <c r="W23">
-        <v>1.8098791877475151E-3</v>
+        <v>1.8412059755808844E-3</v>
       </c>
       <c r="X23">
-        <v>3.3033366221129311E-3</v>
+        <v>3.3362171581227703E-3</v>
       </c>
       <c r="Y23">
-        <v>1.7584267745646693E-3</v>
+        <v>1.7762694242612596E-3</v>
       </c>
       <c r="Z23">
-        <v>1.9567478024411552E-3</v>
+        <v>1.9881072086810839E-3</v>
       </c>
       <c r="AA23">
-        <v>1.8030008205559456E-3</v>
+        <v>1.8276990663665615E-3</v>
       </c>
       <c r="AB23">
-        <v>1.8573647739284708E-3</v>
+        <v>1.8774178622319483E-3</v>
       </c>
       <c r="AC23">
-        <v>1.8532024385665112E-3</v>
+        <v>1.8769145228621185E-3</v>
       </c>
       <c r="AD23">
-        <v>1.7983825340473002E-3</v>
+        <v>1.8174325194119526E-3</v>
       </c>
       <c r="AE23">
-        <v>1.8569513397162542E-3</v>
+        <v>1.8722320475111842E-3</v>
       </c>
       <c r="AF23">
-        <v>-5.2430183193363119E-5</v>
+        <v>-5.5200881995006354E-5</v>
       </c>
       <c r="AG23">
-        <v>-1.9549359270589297E-5</v>
+        <v>2.6955957791965262E-6</v>
       </c>
       <c r="AH23">
-        <v>1.8168399997780496E-5</v>
+        <v>4.4072758604101771E-5</v>
       </c>
       <c r="AI23">
-        <v>4.5968359914726941E-4</v>
+        <v>4.7267867859671775E-4</v>
       </c>
       <c r="AJ23">
-        <v>1.0785559956834681E-3</v>
+        <v>1.1040403878310912E-3</v>
       </c>
       <c r="AK23">
-        <v>9.837932987819104E-4</v>
+        <v>1.0375629922608097E-3</v>
       </c>
       <c r="AL23">
-        <v>-1.026965352970967E-3</v>
+        <v>-7.226130790821822E-4</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.2">
@@ -3411,115 +3411,115 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <v>3.1999259160062458E-2</v>
+        <v>3.018930546027087E-2</v>
       </c>
       <c r="C24">
-        <v>1.102008510883299E-3</v>
+        <v>1.1808498675604704E-3</v>
       </c>
       <c r="D24">
-        <v>1.522214887798481E-4</v>
+        <v>1.5407145857511883E-4</v>
       </c>
       <c r="E24">
-        <v>-2.3108283910585996E-6</v>
+        <v>-2.3205239619852815E-6</v>
       </c>
       <c r="F24">
-        <v>3.5188522756026945E-6</v>
+        <v>2.5905925079753452E-6</v>
       </c>
       <c r="G24">
-        <v>1.8264595018545865E-6</v>
+        <v>-3.0170639728523384E-6</v>
       </c>
       <c r="H24">
-        <v>-8.8017565309023925E-5</v>
+        <v>-8.3808408624042583E-5</v>
       </c>
       <c r="I24">
-        <v>1.5150240584839176E-4</v>
+        <v>1.6872118467352391E-4</v>
       </c>
       <c r="J24">
-        <v>-9.2050964474666428E-4</v>
+        <v>-9.697572426541211E-4</v>
       </c>
       <c r="K24">
-        <v>2.388123506821443E-4</v>
+        <v>2.3334799207485679E-4</v>
       </c>
       <c r="L24">
-        <v>2.2454866027842471E-4</v>
+        <v>2.4227837182292855E-4</v>
       </c>
       <c r="M24">
-        <v>2.1965349500105156E-4</v>
+        <v>2.429153031594863E-4</v>
       </c>
       <c r="N24">
-        <v>2.1083847500673997E-5</v>
+        <v>3.8972067752932299E-5</v>
       </c>
       <c r="O24">
-        <v>-1.7112612614779134E-4</v>
+        <v>-1.6015725900731063E-4</v>
       </c>
       <c r="P24">
-        <v>-4.0865569470503789E-5</v>
+        <v>-3.5527551726629803E-5</v>
       </c>
       <c r="Q24">
-        <v>-1.6311854147984481E-4</v>
+        <v>-1.1483252342324861E-4</v>
       </c>
       <c r="R24">
-        <v>1.2389858534860997E-4</v>
+        <v>1.3822003228968703E-4</v>
       </c>
       <c r="S24">
-        <v>-3.8511068326931106E-5</v>
+        <v>-3.9417604131501693E-5</v>
       </c>
       <c r="T24">
-        <v>1.8618809015172669E-4</v>
+        <v>1.7193831475931362E-4</v>
       </c>
       <c r="U24">
-        <v>1.7995724512835361E-3</v>
+        <v>1.8218355247612106E-3</v>
       </c>
       <c r="V24">
-        <v>1.7708420949610066E-3</v>
+        <v>1.782955011217812E-3</v>
       </c>
       <c r="W24">
-        <v>1.8041615919183259E-3</v>
+        <v>1.8283368597180748E-3</v>
       </c>
       <c r="X24">
-        <v>1.7584267745646693E-3</v>
+        <v>1.7762694242612596E-3</v>
       </c>
       <c r="Y24">
-        <v>3.2382409320086277E-3</v>
+        <v>3.2543184264771231E-3</v>
       </c>
       <c r="Z24">
-        <v>1.9558405663298861E-3</v>
+        <v>1.9806291009456596E-3</v>
       </c>
       <c r="AA24">
-        <v>1.7887210481933806E-3</v>
+        <v>1.8122559693235856E-3</v>
       </c>
       <c r="AB24">
-        <v>1.8462995632666404E-3</v>
+        <v>1.8619094128234255E-3</v>
       </c>
       <c r="AC24">
-        <v>1.8357093467472993E-3</v>
+        <v>1.850184178547674E-3</v>
       </c>
       <c r="AD24">
-        <v>1.7878342997027963E-3</v>
+        <v>1.8025160185180581E-3</v>
       </c>
       <c r="AE24">
-        <v>1.8329763815158643E-3</v>
+        <v>1.8484412143911853E-3</v>
       </c>
       <c r="AF24">
-        <v>-5.0786148394265244E-5</v>
+        <v>-5.3642192370963064E-5</v>
       </c>
       <c r="AG24">
-        <v>4.0742151102146553E-5</v>
+        <v>4.2592642428493799E-5</v>
       </c>
       <c r="AH24">
-        <v>-7.5674714735055396E-5</v>
+        <v>-8.401888011996849E-5</v>
       </c>
       <c r="AI24">
-        <v>3.6206250781035688E-4</v>
+        <v>3.7477679368164011E-4</v>
       </c>
       <c r="AJ24">
-        <v>1.025034530679973E-3</v>
+        <v>1.0646149767165279E-3</v>
       </c>
       <c r="AK24">
-        <v>1.2080313465170607E-3</v>
+        <v>1.1939845923663209E-3</v>
       </c>
       <c r="AL24">
-        <v>-1.4869029737390638E-3</v>
+        <v>-1.2135758395987839E-3</v>
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.2">
@@ -3527,115 +3527,115 @@
         <v>37</v>
       </c>
       <c r="B25">
-        <v>0.1297071041261269</v>
+        <v>0.13592302876403042</v>
       </c>
       <c r="C25">
-        <v>6.0860812483458197E-4</v>
+        <v>7.4247671277029737E-4</v>
       </c>
       <c r="D25">
-        <v>2.3001583499728407E-4</v>
+        <v>2.259556551210181E-4</v>
       </c>
       <c r="E25">
-        <v>-3.6840682382367713E-6</v>
+        <v>-3.6011796830267802E-6</v>
       </c>
       <c r="F25">
-        <v>8.1608263439468179E-6</v>
+        <v>9.3593891896448023E-6</v>
       </c>
       <c r="G25">
-        <v>9.7814839245484843E-6</v>
+        <v>-1.5015801289762255E-5</v>
       </c>
       <c r="H25">
-        <v>5.1332756511115497E-4</v>
+        <v>5.7397957415506156E-4</v>
       </c>
       <c r="I25">
-        <v>2.4698874046062908E-4</v>
+        <v>2.7017764597488288E-4</v>
       </c>
       <c r="J25">
-        <v>-6.0535343917145689E-4</v>
+        <v>-7.0117169484747134E-4</v>
       </c>
       <c r="K25">
-        <v>4.4083295800708073E-4</v>
+        <v>4.5710208142066928E-4</v>
       </c>
       <c r="L25">
-        <v>5.9929928550424933E-4</v>
+        <v>6.7535015399344421E-4</v>
       </c>
       <c r="M25">
-        <v>1.1219324090366836E-3</v>
+        <v>1.2783127283579694E-3</v>
       </c>
       <c r="N25">
-        <v>3.400616264403434E-4</v>
+        <v>4.366983539967049E-4</v>
       </c>
       <c r="O25">
-        <v>-9.5996459987674246E-5</v>
+        <v>-7.3363439001952854E-5</v>
       </c>
       <c r="P25">
-        <v>-1.3966093208154777E-4</v>
+        <v>-1.3263381910058527E-4</v>
       </c>
       <c r="Q25">
-        <v>-4.5029204461077658E-6</v>
+        <v>7.3650882546151043E-5</v>
       </c>
       <c r="R25">
-        <v>4.7511272818472972E-4</v>
+        <v>5.4142873525537009E-4</v>
       </c>
       <c r="S25">
-        <v>-1.6431611009947236E-4</v>
+        <v>-1.7316322947060273E-4</v>
       </c>
       <c r="T25">
-        <v>2.9713506728380073E-4</v>
+        <v>2.5970262285962857E-4</v>
       </c>
       <c r="U25">
-        <v>2.1666517481043878E-3</v>
+        <v>2.2275628201659341E-3</v>
       </c>
       <c r="V25">
-        <v>2.0309898032322879E-3</v>
+        <v>2.0644669881111416E-3</v>
       </c>
       <c r="W25">
-        <v>2.1632966595566865E-3</v>
+        <v>2.2383163748330055E-3</v>
       </c>
       <c r="X25">
-        <v>1.9567478024411552E-3</v>
+        <v>1.9881072086810839E-3</v>
       </c>
       <c r="Y25">
-        <v>1.9558405663298861E-3</v>
+        <v>1.9806291009456596E-3</v>
       </c>
       <c r="Z25">
-        <v>4.6321186847695555E-3</v>
+        <v>4.8135226276238181E-3</v>
       </c>
       <c r="AA25">
-        <v>2.0110122264670764E-3</v>
+        <v>2.0564349075441529E-3</v>
       </c>
       <c r="AB25">
-        <v>2.2050386899664888E-3</v>
+        <v>2.2542763621640448E-3</v>
       </c>
       <c r="AC25">
-        <v>2.1362311863101302E-3</v>
+        <v>2.1638738051560397E-3</v>
       </c>
       <c r="AD25">
-        <v>1.9954592492396517E-3</v>
+        <v>2.0481966209711698E-3</v>
       </c>
       <c r="AE25">
-        <v>2.0155004804722275E-3</v>
+        <v>2.0831186283410993E-3</v>
       </c>
       <c r="AF25">
-        <v>-1.2817537535796022E-4</v>
+        <v>-1.4093580619647489E-4</v>
       </c>
       <c r="AG25">
-        <v>-6.7574854544676392E-4</v>
+        <v>-7.4248406366680996E-4</v>
       </c>
       <c r="AH25">
-        <v>-5.8225179389595038E-4</v>
+        <v>-6.6130374815320759E-4</v>
       </c>
       <c r="AI25">
-        <v>4.7282201911867579E-4</v>
+        <v>5.334691063070547E-4</v>
       </c>
       <c r="AJ25">
-        <v>7.731054847294178E-4</v>
+        <v>8.1997913473877686E-4</v>
       </c>
       <c r="AK25">
-        <v>5.020944841527499E-3</v>
+        <v>5.4141513711097704E-3</v>
       </c>
       <c r="AL25">
-        <v>4.4075115370711855E-3</v>
+        <v>6.0709668385634432E-3</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.2">
@@ -3643,115 +3643,115 @@
         <v>38</v>
       </c>
       <c r="B26">
-        <v>3.7723388271779339E-2</v>
+        <v>3.0955094135511951E-2</v>
       </c>
       <c r="C26">
-        <v>-1.0433591577804367E-4</v>
+        <v>-4.9765183271509631E-5</v>
       </c>
       <c r="D26">
-        <v>1.5017107308375248E-4</v>
+        <v>1.4802843819413443E-4</v>
       </c>
       <c r="E26">
-        <v>-2.2770008120483541E-6</v>
+        <v>-2.2484883685931817E-6</v>
       </c>
       <c r="F26">
-        <v>-2.5072124823440873E-6</v>
+        <v>-3.2226068100530355E-7</v>
       </c>
       <c r="G26">
-        <v>-9.8207946639996487E-7</v>
+        <v>-4.6052025874814753E-6</v>
       </c>
       <c r="H26">
-        <v>-4.3541339373581928E-4</v>
+        <v>-3.6570262537853973E-4</v>
       </c>
       <c r="I26">
-        <v>5.5491304822533711E-4</v>
+        <v>4.9201389291589771E-4</v>
       </c>
       <c r="J26">
-        <v>2.1447403892814243E-4</v>
+        <v>1.7062760662318806E-4</v>
       </c>
       <c r="K26">
-        <v>2.5766761989525063E-4</v>
+        <v>2.6603606550988233E-4</v>
       </c>
       <c r="L26">
-        <v>2.648822735723175E-4</v>
+        <v>2.8649995437703504E-4</v>
       </c>
       <c r="M26">
-        <v>2.5831725145798712E-4</v>
+        <v>2.9476491666278245E-4</v>
       </c>
       <c r="N26">
-        <v>1.2461962975315191E-4</v>
+        <v>1.3209274138706849E-4</v>
       </c>
       <c r="O26">
-        <v>-1.5851426410824044E-4</v>
+        <v>-1.5368392756940065E-4</v>
       </c>
       <c r="P26">
-        <v>-4.032931878466916E-5</v>
+        <v>-3.2969459477362844E-5</v>
       </c>
       <c r="Q26">
-        <v>-1.5371937325589797E-4</v>
+        <v>-9.1174832405318805E-5</v>
       </c>
       <c r="R26">
-        <v>1.8962679754172817E-5</v>
+        <v>4.1169310045427237E-5</v>
       </c>
       <c r="S26">
-        <v>-6.4341016670543079E-5</v>
+        <v>-6.7060874585868108E-5</v>
       </c>
       <c r="T26">
-        <v>1.1763993073281795E-4</v>
+        <v>1.1922635542131398E-4</v>
       </c>
       <c r="U26">
-        <v>1.8670109773249004E-3</v>
+        <v>1.8998891386364958E-3</v>
       </c>
       <c r="V26">
-        <v>1.8113882579045601E-3</v>
+        <v>1.8361811837960412E-3</v>
       </c>
       <c r="W26">
-        <v>1.8520485904735449E-3</v>
+        <v>1.8868885036266024E-3</v>
       </c>
       <c r="X26">
-        <v>1.8030008205559456E-3</v>
+        <v>1.8276990663665615E-3</v>
       </c>
       <c r="Y26">
-        <v>1.7887210481933806E-3</v>
+        <v>1.8122559693235856E-3</v>
       </c>
       <c r="Z26">
-        <v>2.0110122264670764E-3</v>
+        <v>2.0564349075441529E-3</v>
       </c>
       <c r="AA26">
-        <v>2.8966639682518006E-3</v>
+        <v>2.9316603558258957E-3</v>
       </c>
       <c r="AB26">
-        <v>1.8938117967053844E-3</v>
+        <v>1.9215979904241541E-3</v>
       </c>
       <c r="AC26">
-        <v>1.8763353271686873E-3</v>
+        <v>1.9032699298811395E-3</v>
       </c>
       <c r="AD26">
-        <v>1.8376063185178747E-3</v>
+        <v>1.856816853619405E-3</v>
       </c>
       <c r="AE26">
-        <v>1.8777138585094276E-3</v>
+        <v>1.9024711633172046E-3</v>
       </c>
       <c r="AF26">
-        <v>-6.3636035500774953E-5</v>
+        <v>-6.7493599942603096E-5</v>
       </c>
       <c r="AG26">
-        <v>-2.2812092868332323E-4</v>
+        <v>-2.3430696383188137E-4</v>
       </c>
       <c r="AH26">
-        <v>-1.2489949214035433E-4</v>
+        <v>-1.2716359259362122E-4</v>
       </c>
       <c r="AI26">
-        <v>4.2061135733532478E-4</v>
+        <v>4.4374869259857012E-4</v>
       </c>
       <c r="AJ26">
-        <v>1.3813809201118979E-3</v>
+        <v>1.4488374129706801E-3</v>
       </c>
       <c r="AK26">
-        <v>1.1035429547748919E-3</v>
+        <v>1.1867053760042101E-3</v>
       </c>
       <c r="AL26">
-        <v>6.5950443506066804E-4</v>
+        <v>9.0587102558815739E-4</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.2">
@@ -3759,115 +3759,115 @@
         <v>39</v>
       </c>
       <c r="B27">
-        <v>6.4956515305753484E-2</v>
+        <v>6.3516342594651554E-2</v>
       </c>
       <c r="C27">
-        <v>1.7390887743631259E-4</v>
+        <v>2.4825774097442439E-4</v>
       </c>
       <c r="D27">
-        <v>1.5722206879967976E-4</v>
+        <v>1.5896817758003585E-4</v>
       </c>
       <c r="E27">
-        <v>-2.4242600517062153E-6</v>
+        <v>-2.444515472902585E-6</v>
       </c>
       <c r="F27">
-        <v>3.1383821790104906E-6</v>
+        <v>2.933929736608103E-6</v>
       </c>
       <c r="G27">
-        <v>2.8110374706222935E-6</v>
+        <v>-4.3000086553069987E-6</v>
       </c>
       <c r="H27">
-        <v>2.4053366854456625E-5</v>
+        <v>2.7440817027310954E-5</v>
       </c>
       <c r="I27">
-        <v>1.7346262185645629E-4</v>
+        <v>1.9517263947546284E-4</v>
       </c>
       <c r="J27">
-        <v>2.5266815975404078E-6</v>
+        <v>-4.2985306358092861E-5</v>
       </c>
       <c r="K27">
-        <v>2.2500867098353307E-4</v>
+        <v>2.2383866395621094E-4</v>
       </c>
       <c r="L27">
-        <v>2.6101166839156021E-4</v>
+        <v>2.8231829718151664E-4</v>
       </c>
       <c r="M27">
-        <v>3.3814898750980849E-4</v>
+        <v>3.8416753022632935E-4</v>
       </c>
       <c r="N27">
-        <v>1.0001937802377913E-4</v>
+        <v>1.2037379874075784E-4</v>
       </c>
       <c r="O27">
-        <v>-1.5227428990887746E-4</v>
+        <v>-1.4124830392842655E-4</v>
       </c>
       <c r="P27">
-        <v>-2.9799196378727452E-5</v>
+        <v>-2.2895654394294344E-5</v>
       </c>
       <c r="Q27">
-        <v>-1.1468064486220317E-4</v>
+        <v>-5.9829093505551391E-5</v>
       </c>
       <c r="R27">
-        <v>1.7945779214186377E-4</v>
+        <v>2.0325523126090919E-4</v>
       </c>
       <c r="S27">
-        <v>-6.7874054031758987E-5</v>
+        <v>-6.8202614579487841E-5</v>
       </c>
       <c r="T27">
-        <v>2.0036106367037369E-4</v>
+        <v>1.8972155858813225E-4</v>
       </c>
       <c r="U27">
-        <v>1.9346371975489636E-3</v>
+        <v>1.9630295266209875E-3</v>
       </c>
       <c r="V27">
-        <v>1.8815832756291565E-3</v>
+        <v>1.8992719755830723E-3</v>
       </c>
       <c r="W27">
-        <v>1.9341792812432701E-3</v>
+        <v>1.9707676792196102E-3</v>
       </c>
       <c r="X27">
-        <v>1.8573647739284708E-3</v>
+        <v>1.8774178622319483E-3</v>
       </c>
       <c r="Y27">
-        <v>1.8462995632666404E-3</v>
+        <v>1.8619094128234255E-3</v>
       </c>
       <c r="Z27">
-        <v>2.2050386899664888E-3</v>
+        <v>2.2542763621640448E-3</v>
       </c>
       <c r="AA27">
-        <v>1.8938117967053844E-3</v>
+        <v>1.9215979904241541E-3</v>
       </c>
       <c r="AB27">
-        <v>3.3318764632824858E-3</v>
+        <v>3.3667304503532947E-3</v>
       </c>
       <c r="AC27">
-        <v>1.9688336433732858E-3</v>
+        <v>1.9885443892528913E-3</v>
       </c>
       <c r="AD27">
-        <v>1.9275678688464232E-3</v>
+        <v>1.9480045299527665E-3</v>
       </c>
       <c r="AE27">
-        <v>1.9420807917101784E-3</v>
+        <v>1.9653605530497759E-3</v>
       </c>
       <c r="AF27">
-        <v>-7.5059973846014532E-5</v>
+        <v>-7.7202226925622238E-5</v>
       </c>
       <c r="AG27">
-        <v>-1.3739843543340434E-4</v>
+        <v>-1.5488015027715718E-4</v>
       </c>
       <c r="AH27">
-        <v>-6.7056601599595677E-5</v>
+        <v>-5.8781373411021388E-5</v>
       </c>
       <c r="AI27">
-        <v>6.0038568062309948E-4</v>
+        <v>6.1783562397735206E-4</v>
       </c>
       <c r="AJ27">
-        <v>1.147101839345168E-3</v>
+        <v>1.1859839618537532E-3</v>
       </c>
       <c r="AK27">
-        <v>1.7756404352799533E-3</v>
+        <v>1.862279970772633E-3</v>
       </c>
       <c r="AL27">
-        <v>2.9091441605154453E-4</v>
+        <v>5.7668590562836609E-4</v>
       </c>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.2">
@@ -3875,115 +3875,115 @@
         <v>40</v>
       </c>
       <c r="B28">
-        <v>7.4729049316063681E-2</v>
+        <v>7.5263932554714141E-2</v>
       </c>
       <c r="C28">
-        <v>4.2150156616949704E-4</v>
+        <v>5.2745291080845348E-4</v>
       </c>
       <c r="D28">
-        <v>1.8376037510583706E-4</v>
+        <v>1.893873104706718E-4</v>
       </c>
       <c r="E28">
-        <v>-2.8065650005086082E-6</v>
+        <v>-2.8541760923217105E-6</v>
       </c>
       <c r="F28">
-        <v>-1.5082257809676658E-7</v>
+        <v>3.8554528048439566E-6</v>
       </c>
       <c r="G28">
-        <v>8.9143827766621967E-7</v>
+        <v>-8.5616003693075622E-6</v>
       </c>
       <c r="H28">
-        <v>7.8760472681513923E-5</v>
+        <v>1.0469873139276317E-4</v>
       </c>
       <c r="I28">
-        <v>2.8296198670110405E-4</v>
+        <v>2.8919674123564082E-4</v>
       </c>
       <c r="J28">
-        <v>-1.9530136455112886E-4</v>
+        <v>-2.6858003947689379E-4</v>
       </c>
       <c r="K28">
-        <v>2.5382482555075464E-4</v>
+        <v>2.6738044630313876E-4</v>
       </c>
       <c r="L28">
-        <v>5.1786952389974012E-4</v>
+        <v>5.6550515479090004E-4</v>
       </c>
       <c r="M28">
-        <v>4.9376538997072332E-4</v>
+        <v>5.2715607285883385E-4</v>
       </c>
       <c r="N28">
-        <v>2.5647592363216721E-4</v>
+        <v>2.7534866816342489E-4</v>
       </c>
       <c r="O28">
-        <v>-9.1240735139923789E-5</v>
+        <v>-7.4790375693594216E-5</v>
       </c>
       <c r="P28">
-        <v>-1.2357253197622882E-4</v>
+        <v>-1.2545451693361795E-4</v>
       </c>
       <c r="Q28">
-        <v>-1.0604325568780706E-4</v>
+        <v>-6.3944817539409051E-5</v>
       </c>
       <c r="R28">
-        <v>2.9116251141705766E-4</v>
+        <v>3.1865545823334021E-4</v>
       </c>
       <c r="S28">
-        <v>-9.5757965635501815E-5</v>
+        <v>-1.010634633340046E-4</v>
       </c>
       <c r="T28">
-        <v>1.5355421674384344E-4</v>
+        <v>1.4552762293012069E-4</v>
       </c>
       <c r="U28">
-        <v>1.9209148825839266E-3</v>
+        <v>1.9464228286575627E-3</v>
       </c>
       <c r="V28">
-        <v>1.8667607528573295E-3</v>
+        <v>1.8811358344825223E-3</v>
       </c>
       <c r="W28">
-        <v>1.9322586562673014E-3</v>
+        <v>1.965770522141053E-3</v>
       </c>
       <c r="X28">
-        <v>1.8532024385665112E-3</v>
+        <v>1.8769145228621185E-3</v>
       </c>
       <c r="Y28">
-        <v>1.8357093467472993E-3</v>
+        <v>1.850184178547674E-3</v>
       </c>
       <c r="Z28">
-        <v>2.1362311863101302E-3</v>
+        <v>2.1638738051560397E-3</v>
       </c>
       <c r="AA28">
-        <v>1.8763353271686873E-3</v>
+        <v>1.9032699298811395E-3</v>
       </c>
       <c r="AB28">
-        <v>1.9688336433732858E-3</v>
+        <v>1.9885443892528913E-3</v>
       </c>
       <c r="AC28">
-        <v>4.0962981621967248E-3</v>
+        <v>4.1675337375369518E-3</v>
       </c>
       <c r="AD28">
-        <v>1.8991714272233189E-3</v>
+        <v>1.9169977512163792E-3</v>
       </c>
       <c r="AE28">
-        <v>1.9338329731531669E-3</v>
+        <v>1.9591852787436935E-3</v>
       </c>
       <c r="AF28">
-        <v>-9.8990169686980815E-5</v>
+        <v>-1.0695497798035567E-4</v>
       </c>
       <c r="AG28">
-        <v>-2.2677823573466417E-4</v>
+        <v>-2.4700683277729127E-4</v>
       </c>
       <c r="AH28">
-        <v>-2.1625297835409956E-4</v>
+        <v>-2.338641137896052E-4</v>
       </c>
       <c r="AI28">
-        <v>5.5479371773590536E-4</v>
+        <v>5.7884200575148131E-4</v>
       </c>
       <c r="AJ28">
-        <v>1.1120213918337631E-3</v>
+        <v>1.1448334830974536E-3</v>
       </c>
       <c r="AK28">
-        <v>1.5524630189226868E-3</v>
+        <v>1.5714534724323055E-3</v>
       </c>
       <c r="AL28">
-        <v>1.9276042925722818E-3</v>
+        <v>2.39158432356305E-3</v>
       </c>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.2">
@@ -3991,115 +3991,115 @@
         <v>41</v>
       </c>
       <c r="B29">
-        <v>-2.9344845719019704E-3</v>
+        <v>-6.6728772307127942E-3</v>
       </c>
       <c r="C29">
-        <v>-2.7034115967591171E-4</v>
+        <v>-1.7026087981654719E-4</v>
       </c>
       <c r="D29">
-        <v>1.335043261163157E-4</v>
+        <v>1.32615399178658E-4</v>
       </c>
       <c r="E29">
-        <v>-2.2153366493178161E-6</v>
+        <v>-2.2235583409769943E-6</v>
       </c>
       <c r="F29">
-        <v>8.4135725862100867E-6</v>
+        <v>-2.415809021071694E-6</v>
       </c>
       <c r="G29">
-        <v>2.5059132272244864E-6</v>
+        <v>-5.7311705649340298E-6</v>
       </c>
       <c r="H29">
-        <v>-7.8337378463319844E-4</v>
+        <v>-7.4956962011894378E-4</v>
       </c>
       <c r="I29">
-        <v>7.8150471258504406E-4</v>
+        <v>7.8384503772815169E-4</v>
       </c>
       <c r="J29">
-        <v>3.0514642471913937E-4</v>
+        <v>2.6394694738619904E-4</v>
       </c>
       <c r="K29">
-        <v>9.6613041658874353E-5</v>
+        <v>1.2251050196845269E-4</v>
       </c>
       <c r="L29">
-        <v>1.4349521267512056E-4</v>
+        <v>1.9578221947756739E-4</v>
       </c>
       <c r="M29">
-        <v>3.5244047450889521E-4</v>
+        <v>4.448831451388941E-4</v>
       </c>
       <c r="N29">
-        <v>8.7078311087619757E-5</v>
+        <v>1.7012385417653178E-4</v>
       </c>
       <c r="O29">
-        <v>-7.6497461349766695E-5</v>
+        <v>-6.1249570158942041E-5</v>
       </c>
       <c r="P29">
-        <v>-1.195201122290816E-4</v>
+        <v>-1.0364208742550753E-4</v>
       </c>
       <c r="Q29">
-        <v>-1.5319049780141862E-4</v>
+        <v>-9.6870081066907309E-5</v>
       </c>
       <c r="R29">
-        <v>-1.4906258453559575E-5</v>
+        <v>2.8577178219182855E-5</v>
       </c>
       <c r="S29">
-        <v>-8.7939373720460814E-5</v>
+        <v>-8.8252890970888682E-5</v>
       </c>
       <c r="T29">
-        <v>2.3314160962631628E-4</v>
+        <v>1.9141987622453994E-4</v>
       </c>
       <c r="U29">
-        <v>1.8921780405685503E-3</v>
+        <v>1.9233599925610326E-3</v>
       </c>
       <c r="V29">
-        <v>1.8289124802721287E-3</v>
+        <v>1.8440763326476764E-3</v>
       </c>
       <c r="W29">
-        <v>1.8684394054824106E-3</v>
+        <v>1.9024252576710921E-3</v>
       </c>
       <c r="X29">
-        <v>1.7983825340473002E-3</v>
+        <v>1.8174325194119526E-3</v>
       </c>
       <c r="Y29">
-        <v>1.7878342997027963E-3</v>
+        <v>1.8025160185180581E-3</v>
       </c>
       <c r="Z29">
-        <v>1.9954592492396517E-3</v>
+        <v>2.0481966209711698E-3</v>
       </c>
       <c r="AA29">
-        <v>1.8376063185178747E-3</v>
+        <v>1.856816853619405E-3</v>
       </c>
       <c r="AB29">
-        <v>1.9275678688464232E-3</v>
+        <v>1.9480045299527665E-3</v>
       </c>
       <c r="AC29">
-        <v>1.8991714272233189E-3</v>
+        <v>1.9169977512163792E-3</v>
       </c>
       <c r="AD29">
-        <v>3.8876628130453065E-3</v>
+        <v>3.9019964433098827E-3</v>
       </c>
       <c r="AE29">
-        <v>1.9001062537711702E-3</v>
+        <v>1.9211273540793716E-3</v>
       </c>
       <c r="AF29">
-        <v>-8.3385608564000464E-5</v>
+        <v>-8.7829298093057659E-5</v>
       </c>
       <c r="AG29">
-        <v>-2.4135696849906661E-4</v>
+        <v>-2.4594542165654542E-4</v>
       </c>
       <c r="AH29">
-        <v>-9.2774506379233578E-5</v>
+        <v>-9.1699161903381317E-5</v>
       </c>
       <c r="AI29">
-        <v>5.581750610414609E-4</v>
+        <v>5.5911280825299715E-4</v>
       </c>
       <c r="AJ29">
-        <v>1.1780165856323539E-3</v>
+        <v>1.2034185227086307E-3</v>
       </c>
       <c r="AK29">
-        <v>1.9360507151429717E-3</v>
+        <v>2.0062384480775556E-3</v>
       </c>
       <c r="AL29">
-        <v>2.0325970766077138E-3</v>
+        <v>2.9904667246059887E-3</v>
       </c>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.2">
@@ -4107,115 +4107,115 @@
         <v>42</v>
       </c>
       <c r="B30">
-        <v>0.17308111488175659</v>
+        <v>0.16642521238694868</v>
       </c>
       <c r="C30">
-        <v>1.9941830197874651E-4</v>
+        <v>2.9161731110436805E-4</v>
       </c>
       <c r="D30">
-        <v>1.4214788020234939E-4</v>
+        <v>1.4098724052648021E-4</v>
       </c>
       <c r="E30">
-        <v>-2.2092940597415485E-6</v>
+        <v>-2.1947200263740539E-6</v>
       </c>
       <c r="F30">
-        <v>4.5557602338793885E-6</v>
+        <v>7.7629029585715725E-7</v>
       </c>
       <c r="G30">
-        <v>2.4899657047775339E-7</v>
+        <v>-4.4975271888920363E-6</v>
       </c>
       <c r="H30">
-        <v>-1.501064405323906E-4</v>
+        <v>-1.1734055070874182E-4</v>
       </c>
       <c r="I30">
-        <v>1.1492746149992933E-4</v>
+        <v>1.3665156364574445E-4</v>
       </c>
       <c r="J30">
-        <v>-3.254268815515096E-5</v>
+        <v>-1.073128013379111E-4</v>
       </c>
       <c r="K30">
-        <v>3.4874653431506554E-4</v>
+        <v>3.5041205824387937E-4</v>
       </c>
       <c r="L30">
-        <v>3.4472341442368408E-4</v>
+        <v>3.7615268189726894E-4</v>
       </c>
       <c r="M30">
-        <v>3.6926016319388391E-4</v>
+        <v>4.3462663560270103E-4</v>
       </c>
       <c r="N30">
-        <v>2.5983639759235492E-4</v>
+        <v>2.9528335472843274E-4</v>
       </c>
       <c r="O30">
-        <v>-1.9841385124146673E-4</v>
+        <v>-1.8085411692275293E-4</v>
       </c>
       <c r="P30">
-        <v>-7.4539733048804423E-5</v>
+        <v>-6.514157267702343E-5</v>
       </c>
       <c r="Q30">
-        <v>-2.4819717713608718E-4</v>
+        <v>-2.0547518966914247E-4</v>
       </c>
       <c r="R30">
-        <v>5.1735375042640626E-5</v>
+        <v>8.0774329570172838E-5</v>
       </c>
       <c r="S30">
-        <v>-4.5208238212029669E-5</v>
+        <v>-5.0869929795726784E-5</v>
       </c>
       <c r="T30">
-        <v>2.552069544261243E-4</v>
+        <v>2.3519481990508543E-4</v>
       </c>
       <c r="U30">
-        <v>1.9071583568653137E-3</v>
+        <v>1.9376800643951713E-3</v>
       </c>
       <c r="V30">
-        <v>1.8610075630263855E-3</v>
+        <v>1.8782525007587443E-3</v>
       </c>
       <c r="W30">
-        <v>1.8831430315509753E-3</v>
+        <v>1.9202388501367673E-3</v>
       </c>
       <c r="X30">
-        <v>1.8569513397162542E-3</v>
+        <v>1.8722320475111842E-3</v>
       </c>
       <c r="Y30">
-        <v>1.8329763815158643E-3</v>
+        <v>1.8484412143911853E-3</v>
       </c>
       <c r="Z30">
-        <v>2.0155004804722275E-3</v>
+        <v>2.0831186283410993E-3</v>
       </c>
       <c r="AA30">
-        <v>1.8777138585094276E-3</v>
+        <v>1.9024711633172046E-3</v>
       </c>
       <c r="AB30">
-        <v>1.9420807917101784E-3</v>
+        <v>1.9653605530497759E-3</v>
       </c>
       <c r="AC30">
-        <v>1.9338329731531669E-3</v>
+        <v>1.9591852787436935E-3</v>
       </c>
       <c r="AD30">
-        <v>1.9001062537711702E-3</v>
+        <v>1.9211273540793716E-3</v>
       </c>
       <c r="AE30">
-        <v>3.9661022466254796E-3</v>
+        <v>3.9556954389940949E-3</v>
       </c>
       <c r="AF30">
-        <v>-5.7484644859376273E-5</v>
+        <v>-6.4178530993556844E-5</v>
       </c>
       <c r="AG30">
-        <v>-8.2533625303852619E-5</v>
+        <v>-9.9465801042176571E-5</v>
       </c>
       <c r="AH30">
-        <v>-1.3452226406100197E-4</v>
+        <v>-1.460807525187798E-4</v>
       </c>
       <c r="AI30">
-        <v>6.1822856350853754E-4</v>
+        <v>6.172206033571748E-4</v>
       </c>
       <c r="AJ30">
-        <v>1.3024363879380653E-3</v>
+        <v>1.3315524693766337E-3</v>
       </c>
       <c r="AK30">
-        <v>1.0562808567668666E-3</v>
+        <v>1.2190915682234716E-3</v>
       </c>
       <c r="AL30">
-        <v>-9.183181803220624E-4</v>
+        <v>-1.3411422266633921E-4</v>
       </c>
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.2">
@@ -4223,115 +4223,115 @@
         <v>43</v>
       </c>
       <c r="B31">
-        <v>-1.661491736175633E-2</v>
+        <v>-1.8454351048976848E-2</v>
       </c>
       <c r="C31">
-        <v>-5.5087533906595932E-5</v>
+        <v>-8.0918402398451217E-5</v>
       </c>
       <c r="D31">
-        <v>-6.627241824443597E-6</v>
+        <v>-6.5480369921827196E-6</v>
       </c>
       <c r="E31">
-        <v>1.125576341391809E-7</v>
+        <v>1.0621507698816218E-7</v>
       </c>
       <c r="F31">
-        <v>2.6307540363029871E-7</v>
+        <v>-4.9024836013137848E-7</v>
       </c>
       <c r="G31">
-        <v>1.19647761857E-7</v>
+        <v>1.6017039390630714E-6</v>
       </c>
       <c r="H31">
-        <v>2.9605991981905542E-5</v>
+        <v>2.4685362986764417E-5</v>
       </c>
       <c r="I31">
-        <v>-2.9825152655369634E-5</v>
+        <v>-3.429748908508357E-5</v>
       </c>
       <c r="J31">
-        <v>5.1716286630852168E-5</v>
+        <v>7.9209862058215427E-5</v>
       </c>
       <c r="K31">
-        <v>-6.0716183931791956E-5</v>
+        <v>-5.3198390313247991E-5</v>
       </c>
       <c r="L31">
-        <v>-7.410532401757946E-5</v>
+        <v>-7.532249675688184E-5</v>
       </c>
       <c r="M31">
-        <v>-7.2712037833034114E-5</v>
+        <v>-8.0055629491404361E-5</v>
       </c>
       <c r="N31">
-        <v>-2.1325762600560388E-5</v>
+        <v>-2.5768063188203037E-5</v>
       </c>
       <c r="O31">
-        <v>1.9707518395667558E-5</v>
+        <v>1.5986069526128001E-5</v>
       </c>
       <c r="P31">
-        <v>2.6398815104724331E-5</v>
+        <v>2.6395041758708247E-5</v>
       </c>
       <c r="Q31">
-        <v>6.2276125026192983E-5</v>
+        <v>5.5217241106854903E-5</v>
       </c>
       <c r="R31">
-        <v>-2.4937886476859653E-5</v>
+        <v>-2.9181602343716386E-5</v>
       </c>
       <c r="S31">
-        <v>1.4291660648760806E-4</v>
+        <v>1.4369995520663976E-4</v>
       </c>
       <c r="T31">
-        <v>-2.3013033238314802E-5</v>
+        <v>-2.0020278928987788E-5</v>
       </c>
       <c r="U31">
-        <v>-5.6499350464947355E-5</v>
+        <v>-6.5243425858294441E-5</v>
       </c>
       <c r="V31">
-        <v>-7.0412316212073401E-5</v>
+        <v>-7.7848699895063703E-5</v>
       </c>
       <c r="W31">
-        <v>-6.4337940354237475E-5</v>
+        <v>-7.020635470974851E-5</v>
       </c>
       <c r="X31">
-        <v>-5.2430183193363119E-5</v>
+        <v>-5.5200881995006354E-5</v>
       </c>
       <c r="Y31">
-        <v>-5.0786148394265244E-5</v>
+        <v>-5.3642192370963064E-5</v>
       </c>
       <c r="Z31">
-        <v>-1.2817537535796022E-4</v>
+        <v>-1.4093580619647489E-4</v>
       </c>
       <c r="AA31">
-        <v>-6.3636035500774953E-5</v>
+        <v>-6.7493599942603096E-5</v>
       </c>
       <c r="AB31">
-        <v>-7.5059973846014532E-5</v>
+        <v>-7.7202226925622238E-5</v>
       </c>
       <c r="AC31">
-        <v>-9.8990169686980815E-5</v>
+        <v>-1.0695497798035567E-4</v>
       </c>
       <c r="AD31">
-        <v>-8.3385608564000464E-5</v>
+        <v>-8.7829298093057659E-5</v>
       </c>
       <c r="AE31">
-        <v>-5.7484644859376273E-5</v>
+        <v>-6.4178530993556844E-5</v>
       </c>
       <c r="AF31">
-        <v>1.706290007437449E-4</v>
+        <v>1.7164990506143314E-4</v>
       </c>
       <c r="AG31">
-        <v>1.8393115895323255E-4</v>
+        <v>1.8903295102049369E-4</v>
       </c>
       <c r="AH31">
-        <v>-8.7675036956259833E-5</v>
+        <v>-8.1450751014827856E-5</v>
       </c>
       <c r="AI31">
-        <v>-7.0229314752890196E-6</v>
+        <v>-1.5487862703133549E-5</v>
       </c>
       <c r="AJ31">
-        <v>-3.7372737483836078E-5</v>
+        <v>-3.8719637487067901E-5</v>
       </c>
       <c r="AK31">
-        <v>-2.3005476229107785E-4</v>
+        <v>-2.5157874182950984E-4</v>
       </c>
       <c r="AL31">
-        <v>-1.1043417331431445E-2</v>
+        <v>-1.1116829257833943E-2</v>
       </c>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.2">
@@ -4339,115 +4339,115 @@
         <v>44</v>
       </c>
       <c r="B32">
-        <v>2.7997815753547491E-2</v>
+        <v>1.7753517746582188E-2</v>
       </c>
       <c r="C32">
-        <v>-5.4266938444234077E-4</v>
+        <v>-6.2360362102182199E-4</v>
       </c>
       <c r="D32">
-        <v>-2.5662582464044525E-5</v>
+        <v>-2.2814881233977624E-5</v>
       </c>
       <c r="E32">
-        <v>3.9423953209857961E-7</v>
+        <v>3.4269065024779852E-7</v>
       </c>
       <c r="F32">
-        <v>-1.4250298976970779E-7</v>
+        <v>-3.2825900366200404E-6</v>
       </c>
       <c r="G32">
-        <v>-2.7611536818197686E-6</v>
+        <v>6.9666733803318287E-6</v>
       </c>
       <c r="H32">
-        <v>2.0153011783269695E-5</v>
+        <v>-2.8612371171717375E-5</v>
       </c>
       <c r="I32">
-        <v>-4.0185609186017043E-4</v>
+        <v>-3.7788258330483321E-4</v>
       </c>
       <c r="J32">
-        <v>5.4875272849782685E-4</v>
+        <v>6.2253562752687206E-4</v>
       </c>
       <c r="K32">
-        <v>-2.4134555619574811E-4</v>
+        <v>-2.2956566892288533E-4</v>
       </c>
       <c r="L32">
-        <v>-3.5737186212504517E-4</v>
+        <v>-3.788466122760974E-4</v>
       </c>
       <c r="M32">
-        <v>-4.6759768700246744E-4</v>
+        <v>-5.1745765218050863E-4</v>
       </c>
       <c r="N32">
-        <v>-2.8203260721939303E-4</v>
+        <v>-3.0244798523954355E-4</v>
       </c>
       <c r="O32">
-        <v>-4.3298257807774577E-5</v>
+        <v>-4.9800421270333088E-5</v>
       </c>
       <c r="P32">
-        <v>6.857118340413009E-5</v>
+        <v>6.9733309581051568E-5</v>
       </c>
       <c r="Q32">
-        <v>3.1277564311195556E-5</v>
+        <v>1.5095427334314274E-5</v>
       </c>
       <c r="R32">
-        <v>-1.3401442170895693E-4</v>
+        <v>-1.6425031801793328E-4</v>
       </c>
       <c r="S32">
-        <v>2.3549165937703648E-4</v>
+        <v>2.4045305354425568E-4</v>
       </c>
       <c r="T32">
-        <v>-5.1638884831770471E-5</v>
+        <v>-4.3876688809288021E-5</v>
       </c>
       <c r="U32">
-        <v>2.6469155160787532E-5</v>
+        <v>-1.739988023915335E-5</v>
       </c>
       <c r="V32">
-        <v>-1.1503186087038618E-4</v>
+        <v>-1.4088841276468076E-4</v>
       </c>
       <c r="W32">
-        <v>-1.1550104900275498E-4</v>
+        <v>-1.3642910401312242E-4</v>
       </c>
       <c r="X32">
-        <v>-1.9549359270589297E-5</v>
+        <v>2.6955957791965262E-6</v>
       </c>
       <c r="Y32">
-        <v>4.0742151102146553E-5</v>
+        <v>4.2592642428493799E-5</v>
       </c>
       <c r="Z32">
-        <v>-6.7574854544676392E-4</v>
+        <v>-7.4248406366680996E-4</v>
       </c>
       <c r="AA32">
-        <v>-2.2812092868332323E-4</v>
+        <v>-2.3430696383188137E-4</v>
       </c>
       <c r="AB32">
-        <v>-1.3739843543340434E-4</v>
+        <v>-1.5488015027715718E-4</v>
       </c>
       <c r="AC32">
-        <v>-2.2677823573466417E-4</v>
+        <v>-2.4700683277729127E-4</v>
       </c>
       <c r="AD32">
-        <v>-2.4135696849906661E-4</v>
+        <v>-2.4594542165654542E-4</v>
       </c>
       <c r="AE32">
-        <v>-8.2533625303852619E-5</v>
+        <v>-9.9465801042176571E-5</v>
       </c>
       <c r="AF32">
-        <v>1.8393115895323255E-4</v>
+        <v>1.8903295102049369E-4</v>
       </c>
       <c r="AG32">
-        <v>3.3085676591248139E-3</v>
+        <v>3.3542489097109843E-3</v>
       </c>
       <c r="AH32">
-        <v>6.0678636613808838E-4</v>
+        <v>6.531406634690453E-4</v>
       </c>
       <c r="AI32">
-        <v>8.0403957863479231E-5</v>
+        <v>5.4902893653102809E-5</v>
       </c>
       <c r="AJ32">
-        <v>-5.1273313666291842E-6</v>
+        <v>-2.2795764967437418E-5</v>
       </c>
       <c r="AK32">
-        <v>-1.574358579453719E-3</v>
+        <v>-1.7518715608664734E-3</v>
       </c>
       <c r="AL32">
-        <v>-1.5940132141244581E-2</v>
+        <v>-1.6586420923301981E-2</v>
       </c>
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.2">
@@ -4455,115 +4455,115 @@
         <v>45</v>
       </c>
       <c r="B33">
-        <v>3.6348188807681418E-2</v>
+        <v>5.3994522380213315E-2</v>
       </c>
       <c r="C33">
-        <v>-2.6054599559575302E-4</v>
+        <v>-3.1948740925249412E-4</v>
       </c>
       <c r="D33">
-        <v>-6.7884408203983029E-5</v>
+        <v>-5.8848370436622149E-5</v>
       </c>
       <c r="E33">
-        <v>1.0450571790468241E-6</v>
+        <v>9.2052224732956764E-7</v>
       </c>
       <c r="F33">
-        <v>2.7026241282417936E-7</v>
+        <v>1.1418962405719454E-6</v>
       </c>
       <c r="G33">
-        <v>-8.996655002017292E-7</v>
+        <v>7.9335378816885133E-6</v>
       </c>
       <c r="H33">
-        <v>2.1486612238934903E-4</v>
+        <v>1.5107928011534832E-4</v>
       </c>
       <c r="I33">
-        <v>-4.9891429821407457E-4</v>
+        <v>-4.7657066418037536E-4</v>
       </c>
       <c r="J33">
-        <v>1.5394124667027605E-4</v>
+        <v>1.9903133381305756E-4</v>
       </c>
       <c r="K33">
-        <v>5.7240161079760168E-5</v>
+        <v>4.8524388377189443E-6</v>
       </c>
       <c r="L33">
-        <v>-1.1549385762271377E-4</v>
+        <v>-1.7468080567819037E-4</v>
       </c>
       <c r="M33">
-        <v>-2.3413646908388439E-4</v>
+        <v>-3.1808389993299773E-4</v>
       </c>
       <c r="N33">
-        <v>-1.8490776819335083E-4</v>
+        <v>-2.5158671525581545E-4</v>
       </c>
       <c r="O33">
-        <v>-2.7340057892192605E-5</v>
+        <v>-2.4422012228731121E-5</v>
       </c>
       <c r="P33">
-        <v>7.1712720550812275E-5</v>
+        <v>6.9763613772951899E-5</v>
       </c>
       <c r="Q33">
-        <v>-3.1742618556409241E-5</v>
+        <v>-4.7615599785720097E-5</v>
       </c>
       <c r="R33">
-        <v>-1.0463586593841934E-4</v>
+        <v>-1.464280794781427E-4</v>
       </c>
       <c r="S33">
-        <v>-4.9303328716974321E-7</v>
+        <v>5.1184794542013037E-6</v>
       </c>
       <c r="T33">
-        <v>-9.0171096759436077E-5</v>
+        <v>-7.8474926040751495E-5</v>
       </c>
       <c r="U33">
-        <v>1.8053653134589276E-4</v>
+        <v>1.9536586607487346E-4</v>
       </c>
       <c r="V33">
-        <v>6.8074780378203788E-6</v>
+        <v>9.2847571774129197E-6</v>
       </c>
       <c r="W33">
-        <v>-1.3069947915023491E-4</v>
+        <v>-1.503532742914133E-4</v>
       </c>
       <c r="X33">
-        <v>1.8168399997780496E-5</v>
+        <v>4.4072758604101771E-5</v>
       </c>
       <c r="Y33">
-        <v>-7.5674714735055396E-5</v>
+        <v>-8.401888011996849E-5</v>
       </c>
       <c r="Z33">
-        <v>-5.8225179389595038E-4</v>
+        <v>-6.6130374815320759E-4</v>
       </c>
       <c r="AA33">
-        <v>-1.2489949214035433E-4</v>
+        <v>-1.2716359259362122E-4</v>
       </c>
       <c r="AB33">
-        <v>-6.7056601599595677E-5</v>
+        <v>-5.8781373411021388E-5</v>
       </c>
       <c r="AC33">
-        <v>-2.1625297835409956E-4</v>
+        <v>-2.338641137896052E-4</v>
       </c>
       <c r="AD33">
-        <v>-9.2774506379233578E-5</v>
+        <v>-9.1699161903381317E-5</v>
       </c>
       <c r="AE33">
-        <v>-1.3452226406100197E-4</v>
+        <v>-1.460807525187798E-4</v>
       </c>
       <c r="AF33">
-        <v>-8.7675036956259833E-5</v>
+        <v>-8.1450751014827856E-5</v>
       </c>
       <c r="AG33">
-        <v>6.0678636613808838E-4</v>
+        <v>6.531406634690453E-4</v>
       </c>
       <c r="AH33">
-        <v>3.5170891698118548E-3</v>
+        <v>3.618660619111095E-3</v>
       </c>
       <c r="AI33">
-        <v>7.5789528929307622E-5</v>
+        <v>5.2839149478547866E-5</v>
       </c>
       <c r="AJ33">
-        <v>1.7749237591551531E-5</v>
+        <v>-4.3824082767767933E-6</v>
       </c>
       <c r="AK33">
-        <v>-1.503586257544362E-3</v>
+        <v>-1.6928144441604107E-3</v>
       </c>
       <c r="AL33">
-        <v>2.7276929820847437E-3</v>
+        <v>1.7681202666619059E-3</v>
       </c>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.2">
@@ -4571,115 +4571,115 @@
         <v>46</v>
       </c>
       <c r="B34">
-        <v>-6.2769054824928963E-2</v>
+        <v>-8.4209077119675332E-2</v>
       </c>
       <c r="C34">
-        <v>-3.4036150800639212E-5</v>
+        <v>-8.8495808434180777E-6</v>
       </c>
       <c r="D34">
-        <v>1.2123410514249498E-6</v>
+        <v>-8.8832500070960829E-7</v>
       </c>
       <c r="E34">
-        <v>-9.1765557274399722E-8</v>
+        <v>-6.0458511754425616E-8</v>
       </c>
       <c r="F34">
-        <v>1.8583050614183141E-6</v>
+        <v>1.1742854685407121E-6</v>
       </c>
       <c r="G34">
-        <v>2.3963270115475561E-7</v>
+        <v>-1.3426483138006019E-6</v>
       </c>
       <c r="H34">
-        <v>-7.833305216560953E-5</v>
+        <v>-7.6571780707228705E-5</v>
       </c>
       <c r="I34">
-        <v>1.0073765944365229E-4</v>
+        <v>1.2947653891524349E-4</v>
       </c>
       <c r="J34">
-        <v>-2.2290733657123269E-4</v>
+        <v>-2.5799401418363972E-4</v>
       </c>
       <c r="K34">
-        <v>4.4322067690803009E-5</v>
+        <v>6.2505597259229838E-5</v>
       </c>
       <c r="L34">
-        <v>2.6283950258548273E-5</v>
+        <v>3.8954035308220981E-5</v>
       </c>
       <c r="M34">
-        <v>1.440224675136781E-4</v>
+        <v>1.7991050047050865E-4</v>
       </c>
       <c r="N34">
-        <v>1.0030989854685891E-4</v>
+        <v>1.0726655595173811E-4</v>
       </c>
       <c r="O34">
-        <v>-1.0637958707025315E-4</v>
+        <v>-1.1038931377588696E-4</v>
       </c>
       <c r="P34">
-        <v>7.4223138723151494E-5</v>
+        <v>7.2662368048550041E-5</v>
       </c>
       <c r="Q34">
-        <v>-1.5937145141711495E-4</v>
+        <v>-1.4975506209247366E-4</v>
       </c>
       <c r="R34">
-        <v>-9.4955411713562793E-5</v>
+        <v>-8.3144337218020383E-5</v>
       </c>
       <c r="S34">
-        <v>-2.44031792207694E-7</v>
+        <v>-1.0318830751175363E-5</v>
       </c>
       <c r="T34">
-        <v>-6.0997626068332185E-5</v>
+        <v>-4.9310419049289518E-5</v>
       </c>
       <c r="U34">
-        <v>5.6122115525973778E-4</v>
+        <v>5.8301872379350954E-4</v>
       </c>
       <c r="V34">
-        <v>4.6836300676074427E-4</v>
+        <v>4.7392527083531223E-4</v>
       </c>
       <c r="W34">
-        <v>5.4374429515761371E-4</v>
+        <v>5.984255336311437E-4</v>
       </c>
       <c r="X34">
-        <v>4.5968359914726941E-4</v>
+        <v>4.7267867859671775E-4</v>
       </c>
       <c r="Y34">
-        <v>3.6206250781035688E-4</v>
+        <v>3.7477679368164011E-4</v>
       </c>
       <c r="Z34">
-        <v>4.7282201911867579E-4</v>
+        <v>5.334691063070547E-4</v>
       </c>
       <c r="AA34">
-        <v>4.2061135733532478E-4</v>
+        <v>4.4374869259857012E-4</v>
       </c>
       <c r="AB34">
-        <v>6.0038568062309948E-4</v>
+        <v>6.1783562397735206E-4</v>
       </c>
       <c r="AC34">
-        <v>5.5479371773590536E-4</v>
+        <v>5.7884200575148131E-4</v>
       </c>
       <c r="AD34">
-        <v>5.581750610414609E-4</v>
+        <v>5.5911280825299715E-4</v>
       </c>
       <c r="AE34">
-        <v>6.1822856350853754E-4</v>
+        <v>6.172206033571748E-4</v>
       </c>
       <c r="AF34">
-        <v>-7.0229314752890196E-6</v>
+        <v>-1.5487862703133549E-5</v>
       </c>
       <c r="AG34">
-        <v>8.0403957863479231E-5</v>
+        <v>5.4902893653102809E-5</v>
       </c>
       <c r="AH34">
-        <v>7.5789528929307622E-5</v>
+        <v>5.2839149478547866E-5</v>
       </c>
       <c r="AI34">
-        <v>1.927697959723855E-3</v>
+        <v>1.9634488661614087E-3</v>
       </c>
       <c r="AJ34">
-        <v>4.5722541574981686E-4</v>
+        <v>4.6873844441431878E-4</v>
       </c>
       <c r="AK34">
-        <v>5.1665692488913739E-4</v>
+        <v>6.9453470652139273E-4</v>
       </c>
       <c r="AL34">
-        <v>-5.1058777859496699E-4</v>
+        <v>3.1896255378081363E-4</v>
       </c>
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.2">
@@ -4687,115 +4687,115 @@
         <v>47</v>
       </c>
       <c r="B35">
-        <v>0.24528404350112165</v>
+        <v>0.23579542775177731</v>
       </c>
       <c r="C35">
-        <v>-5.795593808838144E-4</v>
+        <v>-5.6208873549715025E-4</v>
       </c>
       <c r="D35">
-        <v>2.7211542649549069E-5</v>
+        <v>2.6587371594577599E-5</v>
       </c>
       <c r="E35">
-        <v>-6.6017190506680813E-7</v>
+        <v>-6.3658086131453118E-7</v>
       </c>
       <c r="F35">
-        <v>-1.5538661958960803E-6</v>
+        <v>1.2982559169137864E-6</v>
       </c>
       <c r="G35">
-        <v>8.678896353062189E-7</v>
+        <v>7.8090787094033233E-7</v>
       </c>
       <c r="H35">
-        <v>-2.4769017433527534E-4</v>
+        <v>-3.2188432900283603E-4</v>
       </c>
       <c r="I35">
-        <v>-3.0862442241197537E-4</v>
+        <v>-2.3466057833660542E-4</v>
       </c>
       <c r="J35">
-        <v>4.9545420292900475E-4</v>
+        <v>4.8224390791841681E-4</v>
       </c>
       <c r="K35">
-        <v>3.0132075470445469E-4</v>
+        <v>3.0223645115781271E-4</v>
       </c>
       <c r="L35">
-        <v>3.2922117413787354E-4</v>
+        <v>3.2940417034890528E-4</v>
       </c>
       <c r="M35">
-        <v>6.8764391419227889E-5</v>
+        <v>7.0594813430274522E-5</v>
       </c>
       <c r="N35">
-        <v>5.230558055267212E-5</v>
+        <v>3.0815174623492758E-5</v>
       </c>
       <c r="O35">
-        <v>-2.0551544867328128E-4</v>
+        <v>-2.0707938850017554E-4</v>
       </c>
       <c r="P35">
-        <v>9.2620957553202248E-6</v>
+        <v>2.2607564456644093E-5</v>
       </c>
       <c r="Q35">
-        <v>-1.8819564898173524E-4</v>
+        <v>-1.4551202399548608E-4</v>
       </c>
       <c r="R35">
-        <v>6.1720142017724429E-5</v>
+        <v>6.6909091201014168E-5</v>
       </c>
       <c r="S35">
-        <v>-3.8020929355750063E-5</v>
+        <v>-4.1495320219959823E-5</v>
       </c>
       <c r="T35">
-        <v>5.9211623298469356E-5</v>
+        <v>7.0617155048474742E-5</v>
       </c>
       <c r="U35">
-        <v>1.1836873575856084E-3</v>
+        <v>1.2285457859871624E-3</v>
       </c>
       <c r="V35">
-        <v>1.0445037578769743E-3</v>
+        <v>1.0787743869131619E-3</v>
       </c>
       <c r="W35">
-        <v>1.0631946224133367E-3</v>
+        <v>1.1088562784142143E-3</v>
       </c>
       <c r="X35">
-        <v>1.0785559956834681E-3</v>
+        <v>1.1040403878310912E-3</v>
       </c>
       <c r="Y35">
-        <v>1.025034530679973E-3</v>
+        <v>1.0646149767165279E-3</v>
       </c>
       <c r="Z35">
-        <v>7.731054847294178E-4</v>
+        <v>8.1997913473877686E-4</v>
       </c>
       <c r="AA35">
-        <v>1.3813809201118979E-3</v>
+        <v>1.4488374129706801E-3</v>
       </c>
       <c r="AB35">
-        <v>1.147101839345168E-3</v>
+        <v>1.1859839618537532E-3</v>
       </c>
       <c r="AC35">
-        <v>1.1120213918337631E-3</v>
+        <v>1.1448334830974536E-3</v>
       </c>
       <c r="AD35">
-        <v>1.1780165856323539E-3</v>
+        <v>1.2034185227086307E-3</v>
       </c>
       <c r="AE35">
-        <v>1.3024363879380653E-3</v>
+        <v>1.3315524693766337E-3</v>
       </c>
       <c r="AF35">
-        <v>-3.7372737483836078E-5</v>
+        <v>-3.8719637487067901E-5</v>
       </c>
       <c r="AG35">
-        <v>-5.1273313666291842E-6</v>
+        <v>-2.2795764967437418E-5</v>
       </c>
       <c r="AH35">
-        <v>1.7749237591551531E-5</v>
+        <v>-4.3824082767767933E-6</v>
       </c>
       <c r="AI35">
-        <v>4.5722541574981686E-4</v>
+        <v>4.6873844441431878E-4</v>
       </c>
       <c r="AJ35">
-        <v>5.9681355398103738E-3</v>
+        <v>6.0908503018393479E-3</v>
       </c>
       <c r="AK35">
-        <v>1.3066270865045356E-4</v>
+        <v>1.9106678059232444E-4</v>
       </c>
       <c r="AL35">
-        <v>1.6938115856483093E-3</v>
+        <v>1.7263186101067751E-3</v>
       </c>
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.2">
@@ -4803,115 +4803,115 @@
         <v>48</v>
       </c>
       <c r="B36">
-        <v>2.7061644908211429E-2</v>
+        <v>3.24048591595077E-2</v>
       </c>
       <c r="C36">
-        <v>8.6041579915096394E-4</v>
+        <v>1.1514552942687786E-3</v>
       </c>
       <c r="D36">
-        <v>3.1753927664675968E-4</v>
+        <v>3.0357656159759813E-4</v>
       </c>
       <c r="E36">
-        <v>-5.1064220481602564E-6</v>
+        <v>-4.8469249737167347E-6</v>
       </c>
       <c r="F36">
-        <v>2.044904156808748E-5</v>
+        <v>1.7491739014877301E-5</v>
       </c>
       <c r="G36">
-        <v>4.0959581037196572E-5</v>
+        <v>-3.2066877272311491E-5</v>
       </c>
       <c r="H36">
-        <v>2.5927400724313761E-4</v>
+        <v>4.3476785753204848E-4</v>
       </c>
       <c r="I36">
-        <v>1.8286058719499884E-3</v>
+        <v>1.8302801377575017E-3</v>
       </c>
       <c r="J36">
-        <v>-1.570168867256235E-3</v>
+        <v>-1.7438565342721519E-3</v>
       </c>
       <c r="K36">
-        <v>4.7289686848824009E-4</v>
+        <v>4.5920266683632718E-4</v>
       </c>
       <c r="L36">
-        <v>8.9898177066784473E-4</v>
+        <v>1.0603517332801963E-3</v>
       </c>
       <c r="M36">
-        <v>2.7956394479531042E-3</v>
+        <v>3.1568656109815544E-3</v>
       </c>
       <c r="N36">
-        <v>5.5680978943236075E-4</v>
+        <v>7.9930420359565837E-4</v>
       </c>
       <c r="O36">
-        <v>-6.4614521162866066E-5</v>
+        <v>-2.2125848087024228E-5</v>
       </c>
       <c r="P36">
-        <v>-1.726816996656833E-4</v>
+        <v>-1.4927980298021389E-4</v>
       </c>
       <c r="Q36">
-        <v>3.6945243513388697E-4</v>
+        <v>4.3247647696569719E-4</v>
       </c>
       <c r="R36">
-        <v>1.0707419821768243E-3</v>
+        <v>1.2622166399992238E-3</v>
       </c>
       <c r="S36">
-        <v>-3.6295903438855748E-4</v>
+        <v>-3.6945511760223121E-4</v>
       </c>
       <c r="T36">
-        <v>2.6882419343617157E-4</v>
+        <v>1.2677358794206325E-4</v>
       </c>
       <c r="U36">
-        <v>1.8265705311134891E-3</v>
+        <v>1.9465304900853578E-3</v>
       </c>
       <c r="V36">
-        <v>1.3197456253007927E-3</v>
+        <v>1.3632526422522979E-3</v>
       </c>
       <c r="W36">
-        <v>1.7510267005242911E-3</v>
+        <v>1.8957295801901343E-3</v>
       </c>
       <c r="X36">
-        <v>9.837932987819104E-4</v>
+        <v>1.0375629922608097E-3</v>
       </c>
       <c r="Y36">
-        <v>1.2080313465170607E-3</v>
+        <v>1.1939845923663209E-3</v>
       </c>
       <c r="Z36">
-        <v>5.020944841527499E-3</v>
+        <v>5.4141513711097704E-3</v>
       </c>
       <c r="AA36">
-        <v>1.1035429547748919E-3</v>
+        <v>1.1867053760042101E-3</v>
       </c>
       <c r="AB36">
-        <v>1.7756404352799533E-3</v>
+        <v>1.862279970772633E-3</v>
       </c>
       <c r="AC36">
-        <v>1.5524630189226868E-3</v>
+        <v>1.5714534724323055E-3</v>
       </c>
       <c r="AD36">
-        <v>1.9360507151429717E-3</v>
+        <v>2.0062384480775556E-3</v>
       </c>
       <c r="AE36">
-        <v>1.0562808567668666E-3</v>
+        <v>1.2190915682234716E-3</v>
       </c>
       <c r="AF36">
-        <v>-2.3005476229107785E-4</v>
+        <v>-2.5157874182950984E-4</v>
       </c>
       <c r="AG36">
-        <v>-1.574358579453719E-3</v>
+        <v>-1.7518715608664734E-3</v>
       </c>
       <c r="AH36">
-        <v>-1.503586257544362E-3</v>
+        <v>-1.6928144441604107E-3</v>
       </c>
       <c r="AI36">
-        <v>5.1665692488913739E-4</v>
+        <v>6.9453470652139273E-4</v>
       </c>
       <c r="AJ36">
-        <v>1.3066270865045356E-4</v>
+        <v>1.9106678059232444E-4</v>
       </c>
       <c r="AK36">
-        <v>1.8938998798951095E-2</v>
+        <v>1.9787985782367585E-2</v>
       </c>
       <c r="AL36">
-        <v>1.3617414840649295E-2</v>
+        <v>1.7658860256053871E-2</v>
       </c>
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.2">
@@ -4919,115 +4919,115 @@
         <v>49</v>
       </c>
       <c r="B37">
-        <v>-5.9525394446174751</v>
+        <v>-5.1432421204314558</v>
       </c>
       <c r="C37">
-        <v>3.5975548240729585E-3</v>
+        <v>5.6228231092129016E-3</v>
       </c>
       <c r="D37">
-        <v>-4.2778071679641545E-3</v>
+        <v>-4.3029436348681095E-3</v>
       </c>
       <c r="E37">
-        <v>6.1724566152687862E-5</v>
+        <v>6.2095563514372068E-5</v>
       </c>
       <c r="F37">
-        <v>-1.8487586117047882E-4</v>
+        <v>-5.9799285709484311E-5</v>
       </c>
       <c r="G37">
-        <v>-6.8259709134607031E-5</v>
+        <v>-1.9925253474693512E-4</v>
       </c>
       <c r="H37">
-        <v>-5.4078637720599461E-3</v>
+        <v>-4.9234706080819087E-3</v>
       </c>
       <c r="I37">
-        <v>3.283027603503073E-3</v>
+        <v>3.1865844272790933E-3</v>
       </c>
       <c r="J37">
-        <v>-9.7292232438186271E-3</v>
+        <v>-1.2535627420580798E-2</v>
       </c>
       <c r="K37">
-        <v>2.0584444529755325E-3</v>
+        <v>1.4031707666022179E-3</v>
       </c>
       <c r="L37">
-        <v>3.7112497592041958E-3</v>
+        <v>3.4777977475982241E-3</v>
       </c>
       <c r="M37">
-        <v>4.1479164061915003E-3</v>
+        <v>4.7059739549920373E-3</v>
       </c>
       <c r="N37">
-        <v>1.8729769437062817E-3</v>
+        <v>1.8556641604542436E-3</v>
       </c>
       <c r="O37">
-        <v>-7.919040754307289E-5</v>
+        <v>1.4954101625526666E-4</v>
       </c>
       <c r="P37">
-        <v>-8.0789588079949767E-4</v>
+        <v>-9.2389600404516471E-4</v>
       </c>
       <c r="Q37">
-        <v>-3.2889535914228749E-3</v>
+        <v>-2.9369984849974707E-3</v>
       </c>
       <c r="R37">
-        <v>1.5884291220587734E-3</v>
+        <v>1.9159844410129145E-3</v>
       </c>
       <c r="S37">
-        <v>-9.7853815072540817E-3</v>
+        <v>-9.865326003005076E-3</v>
       </c>
       <c r="T37">
-        <v>-5.9191310484509214E-4</v>
+        <v>-8.1785769193418525E-4</v>
       </c>
       <c r="U37">
-        <v>6.0438473745494468E-4</v>
+        <v>1.2570580759453292E-3</v>
       </c>
       <c r="V37">
-        <v>1.0058639878370102E-3</v>
+        <v>1.7711631564490352E-3</v>
       </c>
       <c r="W37">
-        <v>-9.5468859506385798E-5</v>
+        <v>4.7721010105692893E-4</v>
       </c>
       <c r="X37">
-        <v>-1.026965352970967E-3</v>
+        <v>-7.226130790821822E-4</v>
       </c>
       <c r="Y37">
-        <v>-1.4869029737390638E-3</v>
+        <v>-1.2135758395987839E-3</v>
       </c>
       <c r="Z37">
-        <v>4.4075115370711855E-3</v>
+        <v>6.0709668385634432E-3</v>
       </c>
       <c r="AA37">
-        <v>6.5950443506066804E-4</v>
+        <v>9.0587102558815739E-4</v>
       </c>
       <c r="AB37">
-        <v>2.9091441605154453E-4</v>
+        <v>5.7668590562836609E-4</v>
       </c>
       <c r="AC37">
-        <v>1.9276042925722818E-3</v>
+        <v>2.39158432356305E-3</v>
       </c>
       <c r="AD37">
-        <v>2.0325970766077138E-3</v>
+        <v>2.9904667246059887E-3</v>
       </c>
       <c r="AE37">
-        <v>-9.183181803220624E-4</v>
+        <v>-1.3411422266633921E-4</v>
       </c>
       <c r="AF37">
-        <v>-1.1043417331431445E-2</v>
+        <v>-1.1116829257833943E-2</v>
       </c>
       <c r="AG37">
-        <v>-1.5940132141244581E-2</v>
+        <v>-1.6586420923301981E-2</v>
       </c>
       <c r="AH37">
-        <v>2.7276929820847437E-3</v>
+        <v>1.7681202666619059E-3</v>
       </c>
       <c r="AI37">
-        <v>-5.1058777859496699E-4</v>
+        <v>3.1896255378081363E-4</v>
       </c>
       <c r="AJ37">
-        <v>1.6938115856483093E-3</v>
+        <v>1.7263186101067751E-3</v>
       </c>
       <c r="AK37">
-        <v>1.3617414840649295E-2</v>
+        <v>1.7658860256053871E-2</v>
       </c>
       <c r="AL37">
-        <v>0.8399781691603474</v>
+        <v>0.84480597127174828</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE37BF26-5340-FA42-8D2D-FD4767140567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9421BE-BBF0-6247-9ED8-FAAEE376D50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="19540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="19440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
   <si>
     <t>Description:</t>
   </si>
@@ -153,7 +153,37 @@
     <t>UKN</t>
   </si>
   <si>
-    <t>Year_transformed</t>
+    <t>Ethn_Asian</t>
+  </si>
+  <si>
+    <t>Ethn_Black</t>
+  </si>
+  <si>
+    <t>Ethn_Other</t>
+  </si>
+  <si>
+    <t>Y2012</t>
+  </si>
+  <si>
+    <t>Y2013</t>
+  </si>
+  <si>
+    <t>Y2014</t>
+  </si>
+  <si>
+    <t>Y2015</t>
+  </si>
+  <si>
+    <t>Y2016</t>
+  </si>
+  <si>
+    <t>Y2017</t>
+  </si>
+  <si>
+    <t>Y2018</t>
+  </si>
+  <si>
+    <t>Y2019</t>
   </si>
   <si>
     <t>Y2020</t>
@@ -162,13 +192,10 @@
     <t>Y2021</t>
   </si>
   <si>
-    <t>Ethn_Asian</t>
+    <t>Y2022</t>
   </si>
   <si>
-    <t>Ethn_Black</t>
-  </si>
-  <si>
-    <t>Ethn_Other</t>
+    <t>Y2023</t>
   </si>
   <si>
     <t>Constant</t>
@@ -697,35 +724,35 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5">
-        <v>0.17255651593708887</v>
+        <v>0.17360684929356052</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F5">
-        <v>2062.2278289036431</v>
+        <v>2076.9765821442825</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B6">
-        <v>83141</v>
+        <v>83159</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F6">
-        <v>-8343957.9440288832</v>
+        <v>-8334865.8124281764</v>
       </c>
     </row>
   </sheetData>
@@ -735,10 +762,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AL37"/>
+  <dimension ref="A1:AU46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -853,4181 +883,6467 @@
       <c r="AL1" t="s">
         <v>49</v>
       </c>
+      <c r="AM1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>-0.5417673295966734</v>
+        <v>-0.5025226826316096</v>
       </c>
       <c r="C2">
-        <v>0.20689372339458942</v>
+        <v>0.21600614862715664</v>
       </c>
       <c r="D2">
-        <v>-8.7650252885285835E-5</v>
+        <v>-1.7295687855294311E-4</v>
       </c>
       <c r="E2">
-        <v>1.6203588280907841E-6</v>
+        <v>2.8455140033424632E-6</v>
       </c>
       <c r="F2">
-        <v>1.6674977643326595E-5</v>
+        <v>1.7729175521014558E-5</v>
       </c>
       <c r="G2">
-        <v>8.8375607195397254E-6</v>
+        <v>1.1247909733640507E-5</v>
       </c>
       <c r="H2">
-        <v>-2.3820253505149754E-4</v>
+        <v>-2.6687010361741499E-4</v>
       </c>
       <c r="I2">
-        <v>1.851964931233227E-3</v>
+        <v>1.8198744750356783E-3</v>
       </c>
       <c r="J2">
-        <v>-0.2063167767679219</v>
+        <v>-0.21533003086564118</v>
       </c>
       <c r="K2">
-        <v>-4.0661639389152459E-5</v>
+        <v>2.5932113223107491E-4</v>
       </c>
       <c r="L2">
-        <v>1.1665878744977572E-3</v>
+        <v>1.3274681199570964E-3</v>
       </c>
       <c r="M2">
-        <v>1.7483264867809503E-3</v>
+        <v>1.9818300077712354E-3</v>
       </c>
       <c r="N2">
-        <v>2.2221954755328585E-3</v>
+        <v>2.6516101817952572E-3</v>
       </c>
       <c r="O2">
-        <v>3.4732995096946795E-4</v>
+        <v>3.7587318996434491E-4</v>
       </c>
       <c r="P2">
-        <v>2.6988363133168886E-5</v>
+        <v>2.6385184483131E-6</v>
       </c>
       <c r="Q2">
-        <v>4.845077199879175E-4</v>
+        <v>4.5479630617692663E-4</v>
       </c>
       <c r="R2">
-        <v>3.1795346361254695E-4</v>
+        <v>1.7637045151684379E-4</v>
       </c>
       <c r="S2">
-        <v>-1.2611545203569901E-4</v>
+        <v>-1.251789244486449E-4</v>
       </c>
       <c r="T2">
-        <v>9.2020723213705104E-4</v>
+        <v>1.041836276508457E-3</v>
       </c>
       <c r="U2">
-        <v>-8.3185897810384346E-4</v>
+        <v>-9.7054546060580736E-4</v>
       </c>
       <c r="V2">
-        <v>1.0994851444448214E-4</v>
+        <v>5.4564998490394968E-5</v>
       </c>
       <c r="W2">
-        <v>3.4149617901906395E-4</v>
+        <v>1.8750886129412046E-4</v>
       </c>
       <c r="X2">
-        <v>2.757096644079506E-4</v>
+        <v>1.7417468226116123E-4</v>
       </c>
       <c r="Y2">
-        <v>1.1808498675604704E-3</v>
+        <v>1.1704798638986812E-3</v>
       </c>
       <c r="Z2">
-        <v>7.4247671277029737E-4</v>
+        <v>3.0977700081253126E-4</v>
       </c>
       <c r="AA2">
-        <v>-4.9765183271509631E-5</v>
+        <v>-2.3168052236172273E-4</v>
       </c>
       <c r="AB2">
-        <v>2.4825774097442439E-4</v>
+        <v>1.1083057383660315E-4</v>
       </c>
       <c r="AC2">
-        <v>5.2745291080845348E-4</v>
+        <v>4.2859504367466473E-4</v>
       </c>
       <c r="AD2">
-        <v>-1.7026087981654719E-4</v>
+        <v>-3.0515108315302524E-4</v>
       </c>
       <c r="AE2">
-        <v>2.9161731110436805E-4</v>
+        <v>2.7577093877088291E-4</v>
       </c>
       <c r="AF2">
-        <v>-8.0918402398451217E-5</v>
+        <v>-1.7086948375300958E-4</v>
       </c>
       <c r="AG2">
-        <v>-6.2360362102182199E-4</v>
+        <v>-7.271117272031548E-4</v>
       </c>
       <c r="AH2">
-        <v>-3.1948740925249412E-4</v>
+        <v>9.4978284495575438E-5</v>
       </c>
       <c r="AI2">
-        <v>-8.8495808434180777E-6</v>
+        <v>7.2453697443566542E-5</v>
       </c>
       <c r="AJ2">
-        <v>-5.6208873549715025E-4</v>
+        <v>-1.457459738600491E-4</v>
       </c>
       <c r="AK2">
-        <v>1.1514552942687786E-3</v>
+        <v>-3.2296856206759286E-4</v>
       </c>
       <c r="AL2">
-        <v>5.6228231092129016E-3</v>
+        <v>-1.6617413575765929E-4</v>
+      </c>
+      <c r="AM2">
+        <v>-2.5202347770346498E-4</v>
+      </c>
+      <c r="AN2">
+        <v>-5.7337834726975227E-4</v>
+      </c>
+      <c r="AO2">
+        <v>-1.0634216363907389E-3</v>
+      </c>
+      <c r="AP2">
+        <v>-1.0299670305708684E-3</v>
+      </c>
+      <c r="AQ2">
+        <v>-1.3219112194654131E-3</v>
+      </c>
+      <c r="AR2">
+        <v>-1.1045134201077556E-3</v>
+      </c>
+      <c r="AS2">
+        <v>-1.2556812294808421E-3</v>
+      </c>
+      <c r="AT2">
+        <v>-1.6006890430100701E-3</v>
+      </c>
+      <c r="AU2">
+        <v>5.8481990798482097E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.32556055985606963</v>
+        <v>0.32442398974552544</v>
       </c>
       <c r="C3">
-        <v>-8.7650252885285835E-5</v>
+        <v>-1.7295687855294311E-4</v>
       </c>
       <c r="D3">
-        <v>2.9192058089791179E-4</v>
+        <v>2.8988865495948994E-4</v>
       </c>
       <c r="E3">
-        <v>-4.3877945903019645E-6</v>
+        <v>-4.3551396322375061E-6</v>
       </c>
       <c r="F3">
-        <v>7.2319880423254487E-7</v>
+        <v>1.0562105689703698E-6</v>
       </c>
       <c r="G3">
-        <v>1.6283815324822284E-6</v>
+        <v>1.9366087279998134E-6</v>
       </c>
       <c r="H3">
-        <v>3.1600137412635641E-5</v>
+        <v>3.9201782151309424E-5</v>
       </c>
       <c r="I3">
-        <v>8.8503457402390462E-5</v>
+        <v>6.3425231892760836E-5</v>
       </c>
       <c r="J3">
-        <v>4.3105392503053593E-4</v>
+        <v>5.0279616425283726E-4</v>
       </c>
       <c r="K3">
-        <v>5.4701746606775688E-5</v>
+        <v>-1.7659681447410058E-5</v>
       </c>
       <c r="L3">
-        <v>3.8365383452976134E-5</v>
+        <v>-3.8953652292593628E-5</v>
       </c>
       <c r="M3">
-        <v>3.4162348906487377E-5</v>
+        <v>-5.0925009776365757E-5</v>
       </c>
       <c r="N3">
-        <v>-2.9703153544453692E-5</v>
+        <v>-1.076216084498012E-4</v>
       </c>
       <c r="O3">
-        <v>-3.8532428382768145E-5</v>
+        <v>-3.6106785516018059E-5</v>
       </c>
       <c r="P3">
-        <v>-7.0140612572357845E-5</v>
+        <v>-7.2966823620947545E-5</v>
       </c>
       <c r="Q3">
-        <v>-3.372248923272478E-5</v>
+        <v>-3.8268627266736864E-5</v>
       </c>
       <c r="R3">
-        <v>-1.0961679661497309E-5</v>
+        <v>-6.7421397264230427E-6</v>
       </c>
       <c r="S3">
-        <v>-8.5091991468634652E-6</v>
+        <v>-9.4708286405458583E-6</v>
       </c>
       <c r="T3">
-        <v>4.8252627919070511E-5</v>
+        <v>2.7492391960233991E-5</v>
       </c>
       <c r="U3">
-        <v>9.4858443313781252E-5</v>
+        <v>9.8927952892223525E-5</v>
       </c>
       <c r="V3">
-        <v>9.0989921146466591E-5</v>
+        <v>9.5079942167840791E-5</v>
       </c>
       <c r="W3">
-        <v>1.4487261463278959E-4</v>
+        <v>1.4691638870072143E-4</v>
       </c>
       <c r="X3">
-        <v>1.4618794467486144E-4</v>
+        <v>1.5074793642326679E-4</v>
       </c>
       <c r="Y3">
-        <v>1.5407145857511883E-4</v>
+        <v>1.5990936557895802E-4</v>
       </c>
       <c r="Z3">
-        <v>2.259556551210181E-4</v>
+        <v>2.3333750365392859E-4</v>
       </c>
       <c r="AA3">
-        <v>1.4802843819413443E-4</v>
+        <v>1.4710683324064471E-4</v>
       </c>
       <c r="AB3">
-        <v>1.5896817758003585E-4</v>
+        <v>1.6248664741998144E-4</v>
       </c>
       <c r="AC3">
-        <v>1.893873104706718E-4</v>
+        <v>1.8920973522796572E-4</v>
       </c>
       <c r="AD3">
-        <v>1.32615399178658E-4</v>
+        <v>1.3590899109925384E-4</v>
       </c>
       <c r="AE3">
-        <v>1.4098724052648021E-4</v>
+        <v>1.4480737597476288E-4</v>
       </c>
       <c r="AF3">
-        <v>-6.5480369921827196E-6</v>
+        <v>4.2496548621341439E-6</v>
       </c>
       <c r="AG3">
-        <v>-2.2814881233977624E-5</v>
+        <v>1.0928340390111172E-5</v>
       </c>
       <c r="AH3">
-        <v>-5.8848370436622149E-5</v>
+        <v>3.0283722296007079E-4</v>
       </c>
       <c r="AI3">
-        <v>-8.8832500070960829E-7</v>
+        <v>1.0205070861490613E-5</v>
       </c>
       <c r="AJ3">
-        <v>2.6587371594577599E-5</v>
+        <v>-2.4316417688229845E-5</v>
       </c>
       <c r="AK3">
-        <v>3.0357656159759813E-4</v>
+        <v>-4.684455885529959E-5</v>
       </c>
       <c r="AL3">
-        <v>-4.3029436348681095E-3</v>
+        <v>-7.6431697608922954E-6</v>
+      </c>
+      <c r="AM3">
+        <v>-2.3035205662714532E-6</v>
+      </c>
+      <c r="AN3">
+        <v>-1.1193694265442498E-4</v>
+      </c>
+      <c r="AO3">
+        <v>-7.5239833745349184E-5</v>
+      </c>
+      <c r="AP3">
+        <v>-1.1378451772216247E-6</v>
+      </c>
+      <c r="AQ3">
+        <v>-9.5802651759463106E-5</v>
+      </c>
+      <c r="AR3">
+        <v>-1.3270880661851378E-4</v>
+      </c>
+      <c r="AS3">
+        <v>-9.3061310053134394E-5</v>
+      </c>
+      <c r="AT3">
+        <v>-1.5684145108530237E-4</v>
+      </c>
+      <c r="AU3">
+        <v>-4.2396841960852111E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>-5.7308908425384268E-3</v>
+        <v>-5.7210122969991875E-3</v>
       </c>
       <c r="C4">
-        <v>1.6203588280907841E-6</v>
+        <v>2.8455140033424632E-6</v>
       </c>
       <c r="D4">
-        <v>-4.3877945903019645E-6</v>
+        <v>-4.3551396322375061E-6</v>
       </c>
       <c r="E4">
-        <v>6.71242032532564E-8</v>
+        <v>6.6612602194096939E-8</v>
       </c>
       <c r="F4">
-        <v>-4.2955754244341753E-9</v>
+        <v>-9.1439765667942255E-9</v>
       </c>
       <c r="G4">
-        <v>-2.5116913132917602E-8</v>
+        <v>-2.9582275532528633E-8</v>
       </c>
       <c r="H4">
-        <v>-5.8641607554991325E-7</v>
+        <v>-7.3290986458287852E-7</v>
       </c>
       <c r="I4">
-        <v>-9.2575490783543675E-7</v>
+        <v>-5.2466805671863841E-7</v>
       </c>
       <c r="J4">
-        <v>-6.4599525700069504E-6</v>
+        <v>-7.4988810255346874E-6</v>
       </c>
       <c r="K4">
-        <v>-7.4963859530949051E-7</v>
+        <v>3.0535942018473136E-7</v>
       </c>
       <c r="L4">
-        <v>-5.1213070607315817E-7</v>
+        <v>6.1822583715588782E-7</v>
       </c>
       <c r="M4">
-        <v>-6.453980828737918E-7</v>
+        <v>5.6860490414754292E-7</v>
       </c>
       <c r="N4">
-        <v>2.8632678055209805E-7</v>
+        <v>1.3985962078601941E-6</v>
       </c>
       <c r="O4">
-        <v>3.6857133250170009E-7</v>
+        <v>3.1977635568931349E-7</v>
       </c>
       <c r="P4">
-        <v>1.3409092103494789E-6</v>
+        <v>1.3875519820610691E-6</v>
       </c>
       <c r="Q4">
-        <v>3.7574335880633599E-7</v>
+        <v>4.5857766933257175E-7</v>
       </c>
       <c r="R4">
-        <v>1.8243497411146717E-7</v>
+        <v>1.2457386088757203E-7</v>
       </c>
       <c r="S4">
-        <v>1.4662442463619891E-7</v>
+        <v>1.5777525640655847E-7</v>
       </c>
       <c r="T4">
-        <v>-7.5423300659791378E-7</v>
+        <v>-4.6778657208482653E-7</v>
       </c>
       <c r="U4">
-        <v>-1.5941604962152209E-6</v>
+        <v>-1.6239886133263865E-6</v>
       </c>
       <c r="V4">
-        <v>-1.4215308313672527E-6</v>
+        <v>-1.4719476802219044E-6</v>
       </c>
       <c r="W4">
-        <v>-2.1880704982306739E-6</v>
+        <v>-2.196207892305563E-6</v>
       </c>
       <c r="X4">
-        <v>-2.2935474202485726E-6</v>
+        <v>-2.3493849533306612E-6</v>
       </c>
       <c r="Y4">
-        <v>-2.3205239619852815E-6</v>
+        <v>-2.3959578918805207E-6</v>
       </c>
       <c r="Z4">
-        <v>-3.6011796830267802E-6</v>
+        <v>-3.6629162700659441E-6</v>
       </c>
       <c r="AA4">
-        <v>-2.2484883685931817E-6</v>
+        <v>-2.2085897662705473E-6</v>
       </c>
       <c r="AB4">
-        <v>-2.444515472902585E-6</v>
+        <v>-2.4888690582538551E-6</v>
       </c>
       <c r="AC4">
-        <v>-2.8541760923217105E-6</v>
+        <v>-2.8396197687050266E-6</v>
       </c>
       <c r="AD4">
-        <v>-2.2235583409769943E-6</v>
+        <v>-2.2782035001266128E-6</v>
       </c>
       <c r="AE4">
-        <v>-2.1947200263740539E-6</v>
+        <v>-2.248727378350405E-6</v>
       </c>
       <c r="AF4">
-        <v>1.0621507698816218E-7</v>
+        <v>-7.8341773549262298E-8</v>
       </c>
       <c r="AG4">
-        <v>3.4269065024779852E-7</v>
+        <v>-4.1506155484026742E-7</v>
       </c>
       <c r="AH4">
-        <v>9.2052224732956764E-7</v>
+        <v>-4.7160196370800889E-6</v>
       </c>
       <c r="AI4">
-        <v>-6.0458511754425616E-8</v>
+        <v>-1.5810842167565041E-7</v>
       </c>
       <c r="AJ4">
-        <v>-6.3658086131453118E-7</v>
+        <v>3.9266878423489316E-7</v>
       </c>
       <c r="AK4">
-        <v>-4.8469249737167347E-6</v>
+        <v>7.5710540428586476E-7</v>
       </c>
       <c r="AL4">
-        <v>6.2095563514372068E-5</v>
+        <v>1.3172027740181858E-7</v>
+      </c>
+      <c r="AM4">
+        <v>8.0026250570442185E-8</v>
+      </c>
+      <c r="AN4">
+        <v>1.7235100429788163E-6</v>
+      </c>
+      <c r="AO4">
+        <v>1.2332699593461846E-6</v>
+      </c>
+      <c r="AP4">
+        <v>6.4979115164791063E-8</v>
+      </c>
+      <c r="AQ4">
+        <v>1.4884127873182531E-6</v>
+      </c>
+      <c r="AR4">
+        <v>2.0900562173179122E-6</v>
+      </c>
+      <c r="AS4">
+        <v>1.4802965949607964E-6</v>
+      </c>
+      <c r="AT4">
+        <v>2.5360102618727631E-6</v>
+      </c>
+      <c r="AU4">
+        <v>6.1407488751264155E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5">
-        <v>-1.333954564159049E-2</v>
+        <v>-1.367540346975092E-2</v>
       </c>
       <c r="C5">
-        <v>1.6674977643326595E-5</v>
+        <v>1.7729175521014558E-5</v>
       </c>
       <c r="D5">
-        <v>7.2319880423254487E-7</v>
+        <v>1.0562105689703698E-6</v>
       </c>
       <c r="E5">
-        <v>-4.2955754244341753E-9</v>
+        <v>-9.1439765667942255E-9</v>
       </c>
       <c r="F5">
-        <v>1.6230041540255241E-6</v>
+        <v>1.6476827569431858E-6</v>
       </c>
       <c r="G5">
-        <v>1.3597428050289186E-7</v>
+        <v>1.4256888290571296E-7</v>
       </c>
       <c r="H5">
-        <v>2.0695527601508195E-5</v>
+        <v>2.2196580049995878E-5</v>
       </c>
       <c r="I5">
-        <v>-1.873683299306136E-5</v>
+        <v>-2.0025227269764727E-5</v>
       </c>
       <c r="J5">
-        <v>-2.0687433745343028E-5</v>
+        <v>-2.1307714775938956E-5</v>
       </c>
       <c r="K5">
-        <v>-2.1501196011452816E-6</v>
+        <v>-2.3630516238477981E-7</v>
       </c>
       <c r="L5">
-        <v>-7.0104895062125848E-7</v>
+        <v>-1.5298785193490056E-6</v>
       </c>
       <c r="M5">
-        <v>-2.8625642739088967E-6</v>
+        <v>-2.0530767283394639E-6</v>
       </c>
       <c r="N5">
-        <v>-1.114490688866099E-5</v>
+        <v>-1.2109706463232639E-5</v>
       </c>
       <c r="O5">
-        <v>-3.121457821565219E-6</v>
+        <v>-3.415366293250443E-6</v>
       </c>
       <c r="P5">
-        <v>-5.9405426792837709E-7</v>
+        <v>-6.1513517194133042E-7</v>
       </c>
       <c r="Q5">
-        <v>6.4400334893784247E-7</v>
+        <v>9.6890339596409447E-7</v>
       </c>
       <c r="R5">
-        <v>1.8169749025254589E-6</v>
+        <v>2.8583726526747659E-6</v>
       </c>
       <c r="S5">
-        <v>-6.680357150721785E-7</v>
+        <v>-7.8505238787798489E-7</v>
       </c>
       <c r="T5">
-        <v>8.7905071189336316E-6</v>
+        <v>8.6040096158168785E-6</v>
       </c>
       <c r="U5">
-        <v>1.3450910449102438E-6</v>
+        <v>3.1468399815566228E-6</v>
       </c>
       <c r="V5">
-        <v>4.025986691406764E-6</v>
+        <v>5.783616677808439E-6</v>
       </c>
       <c r="W5">
-        <v>3.0335189609310603E-6</v>
+        <v>4.7676942403857943E-6</v>
       </c>
       <c r="X5">
-        <v>1.787296442355267E-6</v>
+        <v>3.3524620796651282E-6</v>
       </c>
       <c r="Y5">
-        <v>2.5905925079753452E-6</v>
+        <v>4.152174774520362E-6</v>
       </c>
       <c r="Z5">
-        <v>9.3593891896448023E-6</v>
+        <v>1.2775487888316958E-5</v>
       </c>
       <c r="AA5">
-        <v>-3.2226068100530355E-7</v>
+        <v>6.6418248115305166E-7</v>
       </c>
       <c r="AB5">
-        <v>2.933929736608103E-6</v>
+        <v>4.4523577941857526E-6</v>
       </c>
       <c r="AC5">
-        <v>3.8554528048439566E-6</v>
+        <v>5.4354416787044539E-6</v>
       </c>
       <c r="AD5">
-        <v>-2.415809021071694E-6</v>
+        <v>-1.0036698328465053E-6</v>
       </c>
       <c r="AE5">
-        <v>7.7629029585715725E-7</v>
+        <v>2.4609921991839383E-6</v>
       </c>
       <c r="AF5">
-        <v>-4.9024836013137848E-7</v>
+        <v>1.4414291941447038E-6</v>
       </c>
       <c r="AG5">
-        <v>-3.2825900366200404E-6</v>
+        <v>2.2981709855281051E-6</v>
       </c>
       <c r="AH5">
-        <v>1.1418962405719454E-6</v>
+        <v>2.4098944779464906E-5</v>
       </c>
       <c r="AI5">
-        <v>1.1742854685407121E-6</v>
+        <v>-3.1514990734461074E-7</v>
       </c>
       <c r="AJ5">
-        <v>1.2982559169137864E-6</v>
+        <v>-2.4126666220041149E-6</v>
       </c>
       <c r="AK5">
-        <v>1.7491739014877301E-5</v>
+        <v>-2.7087695738902654E-6</v>
       </c>
       <c r="AL5">
-        <v>-5.9799285709484311E-5</v>
+        <v>-3.2572241879932559E-6</v>
+      </c>
+      <c r="AM5">
+        <v>-2.6149635826030237E-6</v>
+      </c>
+      <c r="AN5">
+        <v>-5.5205581438847831E-6</v>
+      </c>
+      <c r="AO5">
+        <v>-5.9756925769621121E-6</v>
+      </c>
+      <c r="AP5">
+        <v>-3.959923018285441E-6</v>
+      </c>
+      <c r="AQ5">
+        <v>-9.9675464334619498E-6</v>
+      </c>
+      <c r="AR5">
+        <v>-5.7780912244787474E-6</v>
+      </c>
+      <c r="AS5">
+        <v>-9.4379282955830057E-6</v>
+      </c>
+      <c r="AT5">
+        <v>-1.0320583005252008E-5</v>
+      </c>
+      <c r="AU5">
+        <v>-6.5876529304665938E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6">
-        <v>7.3136753138918235E-3</v>
+        <v>7.1113807796567268E-3</v>
       </c>
       <c r="C6">
-        <v>8.8375607195397254E-6</v>
+        <v>1.1247909733640507E-5</v>
       </c>
       <c r="D6">
-        <v>1.6283815324822284E-6</v>
+        <v>1.9366087279998134E-6</v>
       </c>
       <c r="E6">
-        <v>-2.5116913132917602E-8</v>
+        <v>-2.9582275532528633E-8</v>
       </c>
       <c r="F6">
-        <v>1.3597428050289186E-7</v>
+        <v>1.4256888290571296E-7</v>
       </c>
       <c r="G6">
-        <v>1.6080713753388241E-6</v>
+        <v>1.6319129339670666E-6</v>
       </c>
       <c r="H6">
-        <v>1.1895710114589063E-5</v>
+        <v>1.3011855912570905E-5</v>
       </c>
       <c r="I6">
-        <v>-2.0677585851648737E-5</v>
+        <v>-2.3571729887147702E-5</v>
       </c>
       <c r="J6">
-        <v>-5.693329186873047E-6</v>
+        <v>-8.8914182930838117E-6</v>
       </c>
       <c r="K6">
-        <v>-1.6173396355447972E-6</v>
+        <v>-3.1745416843851855E-6</v>
       </c>
       <c r="L6">
-        <v>-7.0428418031717917E-6</v>
+        <v>-8.7034004928669086E-6</v>
       </c>
       <c r="M6">
-        <v>-1.3044032947946965E-5</v>
+        <v>-1.7440560639125662E-5</v>
       </c>
       <c r="N6">
-        <v>-1.0377087129056522E-5</v>
+        <v>-1.3859135255442884E-5</v>
       </c>
       <c r="O6">
-        <v>-2.1596407065900496E-6</v>
+        <v>-2.4647209811798819E-6</v>
       </c>
       <c r="P6">
-        <v>-2.4151293474165215E-7</v>
+        <v>3.2144898546203162E-7</v>
       </c>
       <c r="Q6">
-        <v>1.3857960920250325E-6</v>
+        <v>2.2919377344612559E-6</v>
       </c>
       <c r="R6">
-        <v>-2.6065300542258092E-6</v>
+        <v>-2.9160843794511976E-6</v>
       </c>
       <c r="S6">
-        <v>1.3960139662901061E-6</v>
+        <v>1.8965239525081537E-6</v>
       </c>
       <c r="T6">
-        <v>5.60627969163034E-6</v>
+        <v>4.319260879761743E-6</v>
       </c>
       <c r="U6">
-        <v>-5.1534373013510123E-6</v>
+        <v>-5.2755043143294661E-6</v>
       </c>
       <c r="V6">
-        <v>-5.3881480956986952E-6</v>
+        <v>-5.5073157264664097E-6</v>
       </c>
       <c r="W6">
-        <v>-3.978296045687748E-6</v>
+        <v>-3.9931705189359123E-6</v>
       </c>
       <c r="X6">
-        <v>-3.3621390639611549E-6</v>
+        <v>-3.407896297764828E-6</v>
       </c>
       <c r="Y6">
-        <v>-3.0170639728523384E-6</v>
+        <v>-2.6690302979215298E-6</v>
       </c>
       <c r="Z6">
-        <v>-1.5015801289762255E-5</v>
+        <v>-1.5884645149613988E-5</v>
       </c>
       <c r="AA6">
-        <v>-4.6052025874814753E-6</v>
+        <v>-4.9081711568488192E-6</v>
       </c>
       <c r="AB6">
-        <v>-4.3000086553069987E-6</v>
+        <v>-4.4849332679971133E-6</v>
       </c>
       <c r="AC6">
-        <v>-8.5616003693075622E-6</v>
+        <v>-8.0056641666897195E-6</v>
       </c>
       <c r="AD6">
-        <v>-5.7311705649340298E-6</v>
+        <v>-5.5079077665563853E-6</v>
       </c>
       <c r="AE6">
-        <v>-4.4975271888920363E-6</v>
+        <v>-5.7421973717640336E-6</v>
       </c>
       <c r="AF6">
-        <v>1.6017039390630714E-6</v>
+        <v>-9.1622564767329906E-8</v>
       </c>
       <c r="AG6">
-        <v>6.9666733803318287E-6</v>
+        <v>1.7372370126222754E-6</v>
       </c>
       <c r="AH6">
-        <v>7.9335378816885133E-6</v>
+        <v>-3.4679176341613998E-5</v>
       </c>
       <c r="AI6">
-        <v>-1.3426483138006019E-6</v>
+        <v>-6.7106940989004921E-7</v>
       </c>
       <c r="AJ6">
-        <v>7.8090787094033233E-7</v>
+        <v>5.6499761215360679E-6</v>
       </c>
       <c r="AK6">
-        <v>-3.2066877272311491E-5</v>
+        <v>7.2554557994983922E-6</v>
       </c>
       <c r="AL6">
-        <v>-1.9925253474693512E-4</v>
+        <v>7.0675536509961346E-6</v>
+      </c>
+      <c r="AM6">
+        <v>8.5981574308133855E-6</v>
+      </c>
+      <c r="AN6">
+        <v>1.1149868566805912E-5</v>
+      </c>
+      <c r="AO6">
+        <v>1.830714264824734E-5</v>
+      </c>
+      <c r="AP6">
+        <v>2.3227775808873645E-5</v>
+      </c>
+      <c r="AQ6">
+        <v>2.737095350730911E-5</v>
+      </c>
+      <c r="AR6">
+        <v>3.003960990140152E-5</v>
+      </c>
+      <c r="AS6">
+        <v>3.9193579692237303E-5</v>
+      </c>
+      <c r="AT6">
+        <v>3.0909749266587168E-5</v>
+      </c>
+      <c r="AU6">
+        <v>-2.1693612129859707E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-0.73039069228578146</v>
+        <v>-0.7285031363997263</v>
       </c>
       <c r="C7">
-        <v>-2.3820253505149754E-4</v>
+        <v>-2.6687010361741499E-4</v>
       </c>
       <c r="D7">
-        <v>3.1600137412635641E-5</v>
+        <v>3.9201782151309424E-5</v>
       </c>
       <c r="E7">
-        <v>-5.8641607554991325E-7</v>
+        <v>-7.3290986458287852E-7</v>
       </c>
       <c r="F7">
-        <v>2.0695527601508195E-5</v>
+        <v>2.2196580049995878E-5</v>
       </c>
       <c r="G7">
-        <v>1.1895710114589063E-5</v>
+        <v>1.3011855912570905E-5</v>
       </c>
       <c r="H7">
-        <v>6.8938922859935791E-3</v>
+        <v>6.9251518482942136E-3</v>
       </c>
       <c r="I7">
-        <v>-6.2016823629979494E-3</v>
+        <v>-6.2075872255680734E-3</v>
       </c>
       <c r="J7">
-        <v>-2.2311573797110704E-4</v>
+        <v>-1.7565041986819128E-4</v>
       </c>
       <c r="K7">
-        <v>-5.0903607121856055E-5</v>
+        <v>-5.729009198314601E-6</v>
       </c>
       <c r="L7">
-        <v>-3.6374307427904139E-6</v>
+        <v>9.4808307334306758E-5</v>
       </c>
       <c r="M7">
-        <v>1.5908970527672819E-5</v>
+        <v>1.3280375060573308E-4</v>
       </c>
       <c r="N7">
-        <v>-3.3940033655148363E-4</v>
+        <v>-2.9251960992745683E-4</v>
       </c>
       <c r="O7">
-        <v>1.0468923318698208E-4</v>
+        <v>1.0816218494954063E-4</v>
       </c>
       <c r="P7">
-        <v>-1.4991488865634376E-4</v>
+        <v>-1.593355953760023E-4</v>
       </c>
       <c r="Q7">
-        <v>1.3113093278026549E-4</v>
+        <v>1.3071846020232586E-4</v>
       </c>
       <c r="R7">
-        <v>5.3285487967453854E-4</v>
+        <v>5.4929014112099317E-4</v>
       </c>
       <c r="S7">
-        <v>3.803704287464983E-5</v>
+        <v>-6.3075923319529017E-6</v>
       </c>
       <c r="T7">
-        <v>8.2778847100849304E-5</v>
+        <v>1.113148325347807E-4</v>
       </c>
       <c r="U7">
-        <v>-7.8108468133902091E-5</v>
+        <v>-7.1771963827092005E-5</v>
       </c>
       <c r="V7">
-        <v>8.2830541979518019E-5</v>
+        <v>9.8280272617993908E-5</v>
       </c>
       <c r="W7">
-        <v>7.7820315155593934E-5</v>
+        <v>8.3416178005291336E-5</v>
       </c>
       <c r="X7">
-        <v>2.4047013417550134E-5</v>
+        <v>1.7342415299603461E-5</v>
       </c>
       <c r="Y7">
-        <v>-8.3808408624042583E-5</v>
+        <v>-8.5882310251763315E-5</v>
       </c>
       <c r="Z7">
-        <v>5.7397957415506156E-4</v>
+        <v>6.1041590193664213E-4</v>
       </c>
       <c r="AA7">
-        <v>-3.6570262537853973E-4</v>
+        <v>-4.0838823613900948E-4</v>
       </c>
       <c r="AB7">
-        <v>2.7440817027310954E-5</v>
+        <v>3.2292026343024572E-5</v>
       </c>
       <c r="AC7">
-        <v>1.0469873139276317E-4</v>
+        <v>1.2062988412385768E-4</v>
       </c>
       <c r="AD7">
-        <v>-7.4956962011894378E-4</v>
+        <v>-6.6379358501457593E-4</v>
       </c>
       <c r="AE7">
-        <v>-1.1734055070874182E-4</v>
+        <v>-8.6658756004176236E-5</v>
       </c>
       <c r="AF7">
-        <v>2.4685362986764417E-5</v>
+        <v>-8.2009075671355867E-5</v>
       </c>
       <c r="AG7">
-        <v>-2.8612371171717375E-5</v>
+        <v>-3.2204909809660515E-4</v>
       </c>
       <c r="AH7">
-        <v>1.5107928011534832E-4</v>
+        <v>7.569797815032836E-4</v>
       </c>
       <c r="AI7">
-        <v>-7.6571780707228705E-5</v>
+        <v>3.154097395337681E-5</v>
       </c>
       <c r="AJ7">
-        <v>-3.2188432900283603E-4</v>
+        <v>-3.8967541752909997E-5</v>
       </c>
       <c r="AK7">
-        <v>4.3476785753204848E-4</v>
+        <v>-3.2716154427743179E-5</v>
       </c>
       <c r="AL7">
-        <v>-4.9234706080819087E-3</v>
+        <v>3.3683557643789065E-6</v>
+      </c>
+      <c r="AM7">
+        <v>-8.1954394023224064E-5</v>
+      </c>
+      <c r="AN7">
+        <v>-4.8712541919943399E-5</v>
+      </c>
+      <c r="AO7">
+        <v>-1.4521720311634644E-4</v>
+      </c>
+      <c r="AP7">
+        <v>-1.5670164690677053E-4</v>
+      </c>
+      <c r="AQ7">
+        <v>-2.7368189950660897E-4</v>
+      </c>
+      <c r="AR7">
+        <v>-4.9718385528769744E-5</v>
+      </c>
+      <c r="AS7">
+        <v>-1.7869128148039707E-4</v>
+      </c>
+      <c r="AT7">
+        <v>-6.8387926258074759E-4</v>
+      </c>
+      <c r="AU7">
+        <v>-2.1286625774757581E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8">
-        <v>9.3323256806860447E-2</v>
+        <v>0.11818149124097538</v>
       </c>
       <c r="C8">
-        <v>1.851964931233227E-3</v>
+        <v>1.8198744750356783E-3</v>
       </c>
       <c r="D8">
-        <v>8.8503457402390462E-5</v>
+        <v>6.3425231892760836E-5</v>
       </c>
       <c r="E8">
-        <v>-9.2575490783543675E-7</v>
+        <v>-5.2466805671863841E-7</v>
       </c>
       <c r="F8">
-        <v>-1.873683299306136E-5</v>
+        <v>-2.0025227269764727E-5</v>
       </c>
       <c r="G8">
-        <v>-2.0677585851648737E-5</v>
+        <v>-2.3571729887147702E-5</v>
       </c>
       <c r="H8">
-        <v>-6.2016823629979494E-3</v>
+        <v>-6.2075872255680734E-3</v>
       </c>
       <c r="I8">
-        <v>7.1516338585948646E-3</v>
+        <v>7.1996767138358172E-3</v>
       </c>
       <c r="J8">
-        <v>-1.4927277031094657E-3</v>
+        <v>-1.4536066073621116E-3</v>
       </c>
       <c r="K8">
-        <v>1.8110236637086538E-4</v>
+        <v>1.7699006260169341E-4</v>
       </c>
       <c r="L8">
-        <v>5.6028322491987511E-4</v>
+        <v>5.4993075389722288E-4</v>
       </c>
       <c r="M8">
-        <v>9.50101971731237E-4</v>
+        <v>9.6586949599774077E-4</v>
       </c>
       <c r="N8">
-        <v>1.158100242385475E-3</v>
+        <v>1.1961953923912104E-3</v>
       </c>
       <c r="O8">
-        <v>1.102141873955699E-4</v>
+        <v>1.083563854331074E-4</v>
       </c>
       <c r="P8">
-        <v>2.1148586977616214E-4</v>
+        <v>2.0710622202490359E-4</v>
       </c>
       <c r="Q8">
-        <v>1.1996236000682767E-4</v>
+        <v>1.0225176214711347E-4</v>
       </c>
       <c r="R8">
-        <v>-3.2832298733198899E-4</v>
+        <v>-3.2772630023695441E-4</v>
       </c>
       <c r="S8">
-        <v>-6.5569495540851268E-5</v>
+        <v>-8.8298309109658985E-5</v>
       </c>
       <c r="T8">
-        <v>-1.1210077178624761E-5</v>
+        <v>-2.5476384497442997E-5</v>
       </c>
       <c r="U8">
-        <v>1.6723232310480058E-4</v>
+        <v>1.2038757087642725E-4</v>
       </c>
       <c r="V8">
-        <v>7.8761043703936087E-5</v>
+        <v>4.1476273327815304E-5</v>
       </c>
       <c r="W8">
-        <v>1.5617021102617528E-4</v>
+        <v>1.2093731012935037E-4</v>
       </c>
       <c r="X8">
-        <v>8.493791552452478E-5</v>
+        <v>4.7924168673697809E-5</v>
       </c>
       <c r="Y8">
-        <v>1.6872118467352391E-4</v>
+        <v>1.3850348755038E-4</v>
       </c>
       <c r="Z8">
-        <v>2.7017764597488288E-4</v>
+        <v>2.4830437195354172E-4</v>
       </c>
       <c r="AA8">
-        <v>4.9201389291589771E-4</v>
+        <v>5.1515515074394911E-4</v>
       </c>
       <c r="AB8">
-        <v>1.9517263947546284E-4</v>
+        <v>1.7434438347362606E-4</v>
       </c>
       <c r="AC8">
-        <v>2.8919674123564082E-4</v>
+        <v>2.0695842207000008E-4</v>
       </c>
       <c r="AD8">
-        <v>7.8384503772815169E-4</v>
+        <v>6.3113848644205065E-4</v>
       </c>
       <c r="AE8">
-        <v>1.3665156364574445E-4</v>
+        <v>1.303673320766452E-4</v>
       </c>
       <c r="AF8">
-        <v>-3.429748908508357E-5</v>
+        <v>4.6448424123054751E-5</v>
       </c>
       <c r="AG8">
-        <v>-3.7788258330483321E-4</v>
+        <v>-2.8182949471123231E-4</v>
       </c>
       <c r="AH8">
-        <v>-4.7657066418037536E-4</v>
+        <v>1.6466497326228687E-3</v>
       </c>
       <c r="AI8">
-        <v>1.2947653891524349E-4</v>
+        <v>2.4858284565457296E-5</v>
       </c>
       <c r="AJ8">
-        <v>-2.3466057833660542E-4</v>
+        <v>-2.0741697122163673E-4</v>
       </c>
       <c r="AK8">
-        <v>1.8302801377575017E-3</v>
+        <v>-2.5527420565392748E-4</v>
       </c>
       <c r="AL8">
-        <v>3.1865844272790933E-3</v>
+        <v>-2.7530970207390992E-4</v>
+      </c>
+      <c r="AM8">
+        <v>-2.0057950543037658E-4</v>
+      </c>
+      <c r="AN8">
+        <v>-2.3033472778555037E-4</v>
+      </c>
+      <c r="AO8">
+        <v>-5.5929512684262887E-4</v>
+      </c>
+      <c r="AP8">
+        <v>-7.4390087981907483E-4</v>
+      </c>
+      <c r="AQ8">
+        <v>-9.9499561864485088E-4</v>
+      </c>
+      <c r="AR8">
+        <v>-1.1175724890876591E-3</v>
+      </c>
+      <c r="AS8">
+        <v>-1.3358052350502516E-3</v>
+      </c>
+      <c r="AT8">
+        <v>-8.0915382904970991E-4</v>
+      </c>
+      <c r="AU8">
+        <v>4.9174150541547723E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-0.34254847148407402</v>
+        <v>-0.36920710580020832</v>
       </c>
       <c r="C9">
-        <v>-0.2063167767679219</v>
+        <v>-0.21533003086564118</v>
       </c>
       <c r="D9">
-        <v>4.3105392503053593E-4</v>
+        <v>5.0279616425283726E-4</v>
       </c>
       <c r="E9">
-        <v>-6.4599525700069504E-6</v>
+        <v>-7.4988810255346874E-6</v>
       </c>
       <c r="F9">
-        <v>-2.0687433745343028E-5</v>
+        <v>-2.1307714775938956E-5</v>
       </c>
       <c r="G9">
-        <v>-5.693329186873047E-6</v>
+        <v>-8.8914182930838117E-6</v>
       </c>
       <c r="H9">
-        <v>-2.2311573797110704E-4</v>
+        <v>-1.7565041986819128E-4</v>
       </c>
       <c r="I9">
-        <v>-1.4927277031094657E-3</v>
+        <v>-1.4536066073621116E-3</v>
       </c>
       <c r="J9">
-        <v>0.23038767930603743</v>
+        <v>0.2391804786461271</v>
       </c>
       <c r="K9">
-        <v>1.7048220796075849E-4</v>
+        <v>4.9671554974353649E-5</v>
       </c>
       <c r="L9">
-        <v>-5.059156210665721E-4</v>
+        <v>-6.0567250827570952E-4</v>
       </c>
       <c r="M9">
-        <v>-1.1002311338627166E-3</v>
+        <v>-1.336674551478652E-3</v>
       </c>
       <c r="N9">
-        <v>-1.5864235048432193E-3</v>
+        <v>-1.9892320853265319E-3</v>
       </c>
       <c r="O9">
-        <v>-3.4274843074847024E-4</v>
+        <v>-4.0359289467484634E-4</v>
       </c>
       <c r="P9">
-        <v>-1.1915632042609158E-4</v>
+        <v>-8.5129009090236652E-5</v>
       </c>
       <c r="Q9">
-        <v>-3.7316481097308702E-4</v>
+        <v>-3.357211269023282E-4</v>
       </c>
       <c r="R9">
-        <v>-1.3841277220785558E-4</v>
+        <v>-1.0674752592823361E-6</v>
       </c>
       <c r="S9">
-        <v>1.3004048201979937E-4</v>
+        <v>1.5113738574621413E-4</v>
       </c>
       <c r="T9">
-        <v>-3.8491506647991239E-4</v>
+        <v>-5.6944046867761142E-4</v>
       </c>
       <c r="U9">
-        <v>7.8261807956351084E-4</v>
+        <v>9.0862886650066297E-4</v>
       </c>
       <c r="V9">
-        <v>-4.606866627905544E-5</v>
+        <v>-2.3736145379538436E-5</v>
       </c>
       <c r="W9">
-        <v>4.2440083018852135E-4</v>
+        <v>5.431154799444577E-4</v>
       </c>
       <c r="X9">
-        <v>-4.8702403317142564E-5</v>
+        <v>7.0516791561772035E-6</v>
       </c>
       <c r="Y9">
-        <v>-9.697572426541211E-4</v>
+        <v>-1.0186047159472193E-3</v>
       </c>
       <c r="Z9">
-        <v>-7.0117169484747134E-4</v>
+        <v>-2.6712375145992269E-4</v>
       </c>
       <c r="AA9">
-        <v>1.7062760662318806E-4</v>
+        <v>3.4328163838019861E-4</v>
       </c>
       <c r="AB9">
-        <v>-4.2985306358092861E-5</v>
+        <v>6.5252524664925212E-5</v>
       </c>
       <c r="AC9">
-        <v>-2.6858003947689379E-4</v>
+        <v>-2.0554707821432059E-4</v>
       </c>
       <c r="AD9">
-        <v>2.6394694738619904E-4</v>
+        <v>3.4344748464618254E-4</v>
       </c>
       <c r="AE9">
-        <v>-1.073128013379111E-4</v>
+        <v>-1.2591936478939731E-4</v>
       </c>
       <c r="AF9">
-        <v>7.9209862058215427E-5</v>
+        <v>-7.8786127680551096E-5</v>
       </c>
       <c r="AG9">
-        <v>6.2253562752687206E-4</v>
+        <v>6.5161772132101058E-4</v>
       </c>
       <c r="AH9">
-        <v>1.9903133381305756E-4</v>
+        <v>-5.2058688108051407E-4</v>
       </c>
       <c r="AI9">
-        <v>-2.5799401418363972E-4</v>
+        <v>-1.070020474176034E-4</v>
       </c>
       <c r="AJ9">
-        <v>4.8224390791841681E-4</v>
+        <v>3.9067558483004642E-4</v>
       </c>
       <c r="AK9">
-        <v>-1.7438565342721519E-3</v>
+        <v>4.0817818849773926E-4</v>
       </c>
       <c r="AL9">
-        <v>-1.2535627420580798E-2</v>
+        <v>2.3551907407821232E-4</v>
+      </c>
+      <c r="AM9">
+        <v>3.5043202034392589E-4</v>
+      </c>
+      <c r="AN9">
+        <v>8.8045624623842803E-4</v>
+      </c>
+      <c r="AO9">
+        <v>1.1959733923385418E-3</v>
+      </c>
+      <c r="AP9">
+        <v>1.3649793152613471E-3</v>
+      </c>
+      <c r="AQ9">
+        <v>1.637611452639254E-3</v>
+      </c>
+      <c r="AR9">
+        <v>1.268923942076115E-3</v>
+      </c>
+      <c r="AS9">
+        <v>1.6942946694034622E-3</v>
+      </c>
+      <c r="AT9">
+        <v>2.0757794349520057E-3</v>
+      </c>
+      <c r="AU9">
+        <v>-1.3995203087571351E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-0.15754527941184487</v>
+        <v>-1.755178449506584E-2</v>
       </c>
       <c r="C10">
-        <v>-4.0661639389152459E-5</v>
+        <v>2.5932113223107491E-4</v>
       </c>
       <c r="D10">
-        <v>5.4701746606775688E-5</v>
+        <v>-1.7659681447410058E-5</v>
       </c>
       <c r="E10">
-        <v>-7.4963859530949051E-7</v>
+        <v>3.0535942018473136E-7</v>
       </c>
       <c r="F10">
-        <v>-2.1501196011452816E-6</v>
+        <v>-2.3630516238477981E-7</v>
       </c>
       <c r="G10">
-        <v>-1.6173396355447972E-6</v>
+        <v>-3.1745416843851855E-6</v>
       </c>
       <c r="H10">
-        <v>-5.0903607121856055E-5</v>
+        <v>-5.729009198314601E-6</v>
       </c>
       <c r="I10">
-        <v>1.8110236637086538E-4</v>
+        <v>1.7699006260169341E-4</v>
       </c>
       <c r="J10">
-        <v>1.7048220796075849E-4</v>
+        <v>4.9671554974353649E-5</v>
       </c>
       <c r="K10">
-        <v>2.5156438334846777E-3</v>
+        <v>2.5628348399608573E-3</v>
       </c>
       <c r="L10">
-        <v>1.4717374351948878E-3</v>
+        <v>1.5011128249999392E-3</v>
       </c>
       <c r="M10">
-        <v>1.5296249880488132E-3</v>
+        <v>1.5733530997984087E-3</v>
       </c>
       <c r="N10">
-        <v>1.4588993995679601E-3</v>
+        <v>1.4530432421906558E-3</v>
       </c>
       <c r="O10">
-        <v>-1.6763124048379022E-4</v>
+        <v>-2.2698926808337839E-4</v>
       </c>
       <c r="P10">
-        <v>2.7304610888868938E-5</v>
+        <v>7.4215261132279544E-5</v>
       </c>
       <c r="Q10">
-        <v>-1.3337174712682435E-4</v>
+        <v>1.349773042218054E-5</v>
       </c>
       <c r="R10">
-        <v>2.613776721260494E-6</v>
+        <v>2.9273851682260377E-5</v>
       </c>
       <c r="S10">
-        <v>-5.0072335337061495E-5</v>
+        <v>2.3114156746363254E-6</v>
       </c>
       <c r="T10">
-        <v>4.3115134031259544E-4</v>
+        <v>3.1481064640636632E-4</v>
       </c>
       <c r="U10">
-        <v>3.9769228000006963E-4</v>
+        <v>1.906855425443403E-4</v>
       </c>
       <c r="V10">
-        <v>2.9149035000510816E-4</v>
+        <v>1.3362045721442809E-4</v>
       </c>
       <c r="W10">
-        <v>2.5618405511322324E-4</v>
+        <v>9.8605869791130974E-5</v>
       </c>
       <c r="X10">
-        <v>2.6405773381428434E-4</v>
+        <v>8.4394877642775639E-5</v>
       </c>
       <c r="Y10">
-        <v>2.3334799207485679E-4</v>
+        <v>6.1968292330410801E-5</v>
       </c>
       <c r="Z10">
-        <v>4.5710208142066928E-4</v>
+        <v>3.0310185452071944E-4</v>
       </c>
       <c r="AA10">
-        <v>2.6603606550988233E-4</v>
+        <v>1.2360263150523995E-4</v>
       </c>
       <c r="AB10">
-        <v>2.2383866395621094E-4</v>
+        <v>8.2964096729517029E-5</v>
       </c>
       <c r="AC10">
-        <v>2.6738044630313876E-4</v>
+        <v>6.2293615772855606E-5</v>
       </c>
       <c r="AD10">
-        <v>1.2251050196845269E-4</v>
+        <v>-1.08724140801997E-4</v>
       </c>
       <c r="AE10">
-        <v>3.5041205824387937E-4</v>
+        <v>2.3655596144819002E-4</v>
       </c>
       <c r="AF10">
-        <v>-5.3198390313247991E-5</v>
+        <v>-1.167880846125979E-4</v>
       </c>
       <c r="AG10">
-        <v>-2.2956566892288533E-4</v>
+        <v>1.9036421294253776E-4</v>
       </c>
       <c r="AH10">
-        <v>4.8524388377189443E-6</v>
+        <v>5.9179312826791513E-4</v>
       </c>
       <c r="AI10">
-        <v>6.2505597259229838E-5</v>
+        <v>-7.5675133215368244E-6</v>
       </c>
       <c r="AJ10">
-        <v>3.0223645115781271E-4</v>
+        <v>1.5128740919226357E-5</v>
       </c>
       <c r="AK10">
-        <v>4.5920266683632718E-4</v>
+        <v>4.274724938509736E-5</v>
       </c>
       <c r="AL10">
-        <v>1.4031707666022179E-3</v>
+        <v>1.4992548610135098E-5</v>
+      </c>
+      <c r="AM10">
+        <v>-6.5965844836344948E-6</v>
+      </c>
+      <c r="AN10">
+        <v>-1.6873656978281138E-4</v>
+      </c>
+      <c r="AO10">
+        <v>3.0330668067853712E-5</v>
+      </c>
+      <c r="AP10">
+        <v>8.6971451097401977E-5</v>
+      </c>
+      <c r="AQ10">
+        <v>1.0455229263392051E-5</v>
+      </c>
+      <c r="AR10">
+        <v>3.3375765034787674E-5</v>
+      </c>
+      <c r="AS10">
+        <v>-8.5717559370340323E-5</v>
+      </c>
+      <c r="AT10">
+        <v>1.4968971892091471E-4</v>
+      </c>
+      <c r="AU10">
+        <v>-1.2358924308702203E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>23</v>
       </c>
       <c r="B11">
-        <v>-0.2297547895689363</v>
+        <v>-0.11333916513781403</v>
       </c>
       <c r="C11">
-        <v>1.1665878744977572E-3</v>
+        <v>1.3274681199570964E-3</v>
       </c>
       <c r="D11">
-        <v>3.8365383452976134E-5</v>
+        <v>-3.8953652292593628E-5</v>
       </c>
       <c r="E11">
-        <v>-5.1213070607315817E-7</v>
+        <v>6.1822583715588782E-7</v>
       </c>
       <c r="F11">
-        <v>-7.0104895062125848E-7</v>
+        <v>-1.5298785193490056E-6</v>
       </c>
       <c r="G11">
-        <v>-7.0428418031717917E-6</v>
+        <v>-8.7034004928669086E-6</v>
       </c>
       <c r="H11">
-        <v>-3.6374307427904139E-6</v>
+        <v>9.4808307334306758E-5</v>
       </c>
       <c r="I11">
-        <v>5.6028322491987511E-4</v>
+        <v>5.4993075389722288E-4</v>
       </c>
       <c r="J11">
-        <v>-5.059156210665721E-4</v>
+        <v>-6.0567250827570952E-4</v>
       </c>
       <c r="K11">
-        <v>1.4717374351948878E-3</v>
+        <v>1.5011128249999392E-3</v>
       </c>
       <c r="L11">
-        <v>2.5307018564911096E-3</v>
+        <v>2.5504226071409873E-3</v>
       </c>
       <c r="M11">
-        <v>2.0204117647961493E-3</v>
+        <v>2.0565592209394528E-3</v>
       </c>
       <c r="N11">
-        <v>1.9457990520984057E-3</v>
+        <v>1.9674663404116049E-3</v>
       </c>
       <c r="O11">
-        <v>-5.2558274154734932E-5</v>
+        <v>-7.5944343068019092E-5</v>
       </c>
       <c r="P11">
-        <v>-3.7169213685412866E-6</v>
+        <v>2.1989352823522621E-5</v>
       </c>
       <c r="Q11">
-        <v>1.4881035912969271E-4</v>
+        <v>1.9266492715666828E-4</v>
       </c>
       <c r="R11">
-        <v>9.8345382135163798E-5</v>
+        <v>7.4522811783120368E-5</v>
       </c>
       <c r="S11">
-        <v>-8.4351643269366572E-5</v>
+        <v>-1.7141492204883599E-5</v>
       </c>
       <c r="T11">
-        <v>7.2118885906164625E-4</v>
+        <v>5.5691181286081685E-4</v>
       </c>
       <c r="U11">
-        <v>3.2376182698039063E-4</v>
+        <v>4.9512348306491338E-5</v>
       </c>
       <c r="V11">
-        <v>3.2780818822117542E-4</v>
+        <v>9.1714903042823878E-5</v>
       </c>
       <c r="W11">
-        <v>3.3070796374947342E-4</v>
+        <v>8.2587101317808094E-5</v>
       </c>
       <c r="X11">
-        <v>2.9032905878042186E-4</v>
+        <v>9.5727949804365244E-6</v>
       </c>
       <c r="Y11">
-        <v>2.4227837182292855E-4</v>
+        <v>-1.9839076935754491E-5</v>
       </c>
       <c r="Z11">
-        <v>6.7535015399344421E-4</v>
+        <v>4.0229875352584344E-4</v>
       </c>
       <c r="AA11">
-        <v>2.8649995437703504E-4</v>
+        <v>5.28478673144364E-5</v>
       </c>
       <c r="AB11">
-        <v>2.8231829718151664E-4</v>
+        <v>5.980712799096113E-5</v>
       </c>
       <c r="AC11">
-        <v>5.6550515479090004E-4</v>
+        <v>2.5206395908443173E-4</v>
       </c>
       <c r="AD11">
-        <v>1.9578221947756739E-4</v>
+        <v>-8.6910246014952326E-5</v>
       </c>
       <c r="AE11">
-        <v>3.7615268189726894E-4</v>
+        <v>1.3601764012944782E-4</v>
       </c>
       <c r="AF11">
-        <v>-7.532249675688184E-5</v>
+        <v>-1.2084142332938956E-4</v>
       </c>
       <c r="AG11">
-        <v>-3.788466122760974E-4</v>
+        <v>3.2497000561919527E-5</v>
       </c>
       <c r="AH11">
-        <v>-1.7468080567819037E-4</v>
+        <v>1.1432436952071193E-3</v>
       </c>
       <c r="AI11">
-        <v>3.8954035308220981E-5</v>
+        <v>-3.5379400575322412E-6</v>
       </c>
       <c r="AJ11">
-        <v>3.2940417034890528E-4</v>
+        <v>-3.2472079426416043E-5</v>
       </c>
       <c r="AK11">
-        <v>1.0603517332801963E-3</v>
+        <v>-2.1771908081161663E-5</v>
       </c>
       <c r="AL11">
-        <v>3.4777977475982241E-3</v>
+        <v>-4.8873064273347987E-5</v>
+      </c>
+      <c r="AM11">
+        <v>-1.0301586597259423E-4</v>
+      </c>
+      <c r="AN11">
+        <v>-1.8322251015505614E-4</v>
+      </c>
+      <c r="AO11">
+        <v>-5.5342668254955386E-5</v>
+      </c>
+      <c r="AP11">
+        <v>-2.0275385750355163E-4</v>
+      </c>
+      <c r="AQ11">
+        <v>-1.9541615091354806E-4</v>
+      </c>
+      <c r="AR11">
+        <v>-2.3841059653838649E-4</v>
+      </c>
+      <c r="AS11">
+        <v>-2.6598135631398026E-4</v>
+      </c>
+      <c r="AT11">
+        <v>1.0287586585005235E-4</v>
+      </c>
+      <c r="AU11">
+        <v>-2.9534727688781959E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-0.24332480721351663</v>
+        <v>-0.10334010922035083</v>
       </c>
       <c r="C12">
-        <v>1.7483264867809503E-3</v>
+        <v>1.9818300077712354E-3</v>
       </c>
       <c r="D12">
-        <v>3.4162348906487377E-5</v>
+        <v>-5.0925009776365757E-5</v>
       </c>
       <c r="E12">
-        <v>-6.453980828737918E-7</v>
+        <v>5.6860490414754292E-7</v>
       </c>
       <c r="F12">
-        <v>-2.8625642739088967E-6</v>
+        <v>-2.0530767283394639E-6</v>
       </c>
       <c r="G12">
-        <v>-1.3044032947946965E-5</v>
+        <v>-1.7440560639125662E-5</v>
       </c>
       <c r="H12">
-        <v>1.5908970527672819E-5</v>
+        <v>1.3280375060573308E-4</v>
       </c>
       <c r="I12">
-        <v>9.50101971731237E-4</v>
+        <v>9.6586949599774077E-4</v>
       </c>
       <c r="J12">
-        <v>-1.1002311338627166E-3</v>
+        <v>-1.336674551478652E-3</v>
       </c>
       <c r="K12">
-        <v>1.5296249880488132E-3</v>
+        <v>1.5733530997984087E-3</v>
       </c>
       <c r="L12">
-        <v>2.0204117647961493E-3</v>
+        <v>2.0565592209394528E-3</v>
       </c>
       <c r="M12">
-        <v>3.0999879144835763E-3</v>
+        <v>3.2286497093199952E-3</v>
       </c>
       <c r="N12">
-        <v>2.3410452925407806E-3</v>
+        <v>2.3966737318994943E-3</v>
       </c>
       <c r="O12">
-        <v>3.2377149041498861E-5</v>
+        <v>2.1507196389246712E-5</v>
       </c>
       <c r="P12">
-        <v>-3.9041051923910803E-5</v>
+        <v>-1.0449651742590595E-5</v>
       </c>
       <c r="Q12">
-        <v>3.3152648945091031E-4</v>
+        <v>3.3624995541029119E-4</v>
       </c>
       <c r="R12">
-        <v>1.0427452557665578E-4</v>
+        <v>1.226329666786019E-4</v>
       </c>
       <c r="S12">
-        <v>-1.039146394817229E-4</v>
+        <v>-1.2302446865166663E-4</v>
       </c>
       <c r="T12">
-        <v>7.980596790374498E-4</v>
+        <v>6.545442077442599E-4</v>
       </c>
       <c r="U12">
-        <v>5.0596014004889583E-4</v>
+        <v>2.8771262856621234E-4</v>
       </c>
       <c r="V12">
-        <v>4.4216391870953355E-4</v>
+        <v>2.6177914963687447E-4</v>
       </c>
       <c r="W12">
-        <v>4.5706671843364418E-4</v>
+        <v>2.5826410564054706E-4</v>
       </c>
       <c r="X12">
-        <v>3.2403182938415593E-4</v>
+        <v>9.1146905976084936E-5</v>
       </c>
       <c r="Y12">
-        <v>2.429153031594863E-4</v>
+        <v>2.3929086946701772E-5</v>
       </c>
       <c r="Z12">
-        <v>1.2783127283579694E-3</v>
+        <v>1.1051113998619632E-3</v>
       </c>
       <c r="AA12">
-        <v>2.9476491666278245E-4</v>
+        <v>1.8465144935246502E-4</v>
       </c>
       <c r="AB12">
-        <v>3.8416753022632935E-4</v>
+        <v>2.0804022258710144E-4</v>
       </c>
       <c r="AC12">
-        <v>5.2715607285883385E-4</v>
+        <v>2.5890209672722821E-4</v>
       </c>
       <c r="AD12">
-        <v>4.448831451388941E-4</v>
+        <v>1.8519599141990313E-4</v>
       </c>
       <c r="AE12">
-        <v>4.3462663560270103E-4</v>
+        <v>3.1652083765556539E-4</v>
       </c>
       <c r="AF12">
-        <v>-8.0055629491404361E-5</v>
+        <v>-9.0767274057522017E-5</v>
       </c>
       <c r="AG12">
-        <v>-5.1745765218050863E-4</v>
+        <v>1.0091281177832236E-4</v>
       </c>
       <c r="AH12">
-        <v>-3.1808389993299773E-4</v>
+        <v>3.270260660272483E-3</v>
       </c>
       <c r="AI12">
-        <v>1.7991050047050865E-4</v>
+        <v>8.2097524577768834E-5</v>
       </c>
       <c r="AJ12">
-        <v>7.0594813430274522E-5</v>
+        <v>-2.3163401761432464E-4</v>
       </c>
       <c r="AK12">
-        <v>3.1568656109815544E-3</v>
+        <v>-2.7036220049417943E-4</v>
       </c>
       <c r="AL12">
-        <v>4.7059739549920373E-3</v>
+        <v>-2.9106205201970845E-4</v>
+      </c>
+      <c r="AM12">
+        <v>-3.765099541791604E-4</v>
+      </c>
+      <c r="AN12">
+        <v>-5.084854321967874E-4</v>
+      </c>
+      <c r="AO12">
+        <v>-7.908893289484862E-4</v>
+      </c>
+      <c r="AP12">
+        <v>-1.1167793908291247E-3</v>
+      </c>
+      <c r="AQ12">
+        <v>-1.3730210391528167E-3</v>
+      </c>
+      <c r="AR12">
+        <v>-1.3570425170390781E-3</v>
+      </c>
+      <c r="AS12">
+        <v>-1.7288138069218E-3</v>
+      </c>
+      <c r="AT12">
+        <v>-1.7329435947558214E-3</v>
+      </c>
+      <c r="AU12">
+        <v>6.7403296261062586E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
-        <v>-3.525340792420352E-2</v>
+        <v>0.10143783328301448</v>
       </c>
       <c r="C13">
-        <v>2.2221954755328585E-3</v>
+        <v>2.6516101817952572E-3</v>
       </c>
       <c r="D13">
-        <v>-2.9703153544453692E-5</v>
+        <v>-1.076216084498012E-4</v>
       </c>
       <c r="E13">
-        <v>2.8632678055209805E-7</v>
+        <v>1.3985962078601941E-6</v>
       </c>
       <c r="F13">
-        <v>-1.114490688866099E-5</v>
+        <v>-1.2109706463232639E-5</v>
       </c>
       <c r="G13">
-        <v>-1.0377087129056522E-5</v>
+        <v>-1.3859135255442884E-5</v>
       </c>
       <c r="H13">
-        <v>-3.3940033655148363E-4</v>
+        <v>-2.9251960992745683E-4</v>
       </c>
       <c r="I13">
-        <v>1.158100242385475E-3</v>
+        <v>1.1961953923912104E-3</v>
       </c>
       <c r="J13">
-        <v>-1.5864235048432193E-3</v>
+        <v>-1.9892320853265319E-3</v>
       </c>
       <c r="K13">
-        <v>1.4588993995679601E-3</v>
+        <v>1.4530432421906558E-3</v>
       </c>
       <c r="L13">
-        <v>1.9457990520984057E-3</v>
+        <v>1.9674663404116049E-3</v>
       </c>
       <c r="M13">
-        <v>2.3410452925407806E-3</v>
+        <v>2.3966737318994943E-3</v>
       </c>
       <c r="N13">
-        <v>2.886442283029532E-3</v>
+        <v>2.909062984292392E-3</v>
       </c>
       <c r="O13">
-        <v>1.3539028157254739E-4</v>
+        <v>1.1273946694154431E-4</v>
       </c>
       <c r="P13">
-        <v>4.8327684571907137E-6</v>
+        <v>4.0447224215929441E-5</v>
       </c>
       <c r="Q13">
-        <v>3.4002604892777329E-4</v>
+        <v>3.809472701916583E-4</v>
       </c>
       <c r="R13">
-        <v>-2.2675587168549286E-4</v>
+        <v>-2.4379828001537033E-4</v>
       </c>
       <c r="S13">
-        <v>-4.1577346955971764E-5</v>
+        <v>-2.1300285445725802E-5</v>
       </c>
       <c r="T13">
-        <v>8.0337449069115311E-4</v>
+        <v>6.721914826169754E-4</v>
       </c>
       <c r="U13">
-        <v>2.2638868117231826E-4</v>
+        <v>-8.4491816705058794E-5</v>
       </c>
       <c r="V13">
-        <v>2.0518260968167105E-4</v>
+        <v>-2.4716232105078482E-5</v>
       </c>
       <c r="W13">
-        <v>1.8216755710596545E-4</v>
+        <v>-5.5970575455671024E-5</v>
       </c>
       <c r="X13">
-        <v>1.6180093589072796E-4</v>
+        <v>-1.0149697730347235E-4</v>
       </c>
       <c r="Y13">
-        <v>3.8972067752932299E-5</v>
+        <v>-2.1261428387516233E-4</v>
       </c>
       <c r="Z13">
-        <v>4.366983539967049E-4</v>
+        <v>1.597332734002579E-4</v>
       </c>
       <c r="AA13">
-        <v>1.3209274138706849E-4</v>
+        <v>-4.9206750242215733E-5</v>
       </c>
       <c r="AB13">
-        <v>1.2037379874075784E-4</v>
+        <v>-7.4648949533822725E-5</v>
       </c>
       <c r="AC13">
-        <v>2.7534866816342489E-4</v>
+        <v>-2.2691468805456007E-5</v>
       </c>
       <c r="AD13">
-        <v>1.7012385417653178E-4</v>
+        <v>-1.0850377633825299E-4</v>
       </c>
       <c r="AE13">
-        <v>2.9528335472843274E-4</v>
+        <v>8.8460187235087599E-5</v>
       </c>
       <c r="AF13">
-        <v>-2.5768063188203037E-5</v>
+        <v>-1.0389006373935481E-4</v>
       </c>
       <c r="AG13">
-        <v>-3.0244798523954355E-4</v>
+        <v>-9.0492745923244504E-5</v>
       </c>
       <c r="AH13">
-        <v>-2.5158671525581545E-4</v>
+        <v>7.1250885617729523E-4</v>
       </c>
       <c r="AI13">
-        <v>1.0726655595173811E-4</v>
+        <v>5.764840794305778E-5</v>
       </c>
       <c r="AJ13">
-        <v>3.0815174623492758E-5</v>
+        <v>3.8279175976755931E-5</v>
       </c>
       <c r="AK13">
-        <v>7.9930420359565837E-4</v>
+        <v>5.5778827835007176E-5</v>
       </c>
       <c r="AL13">
-        <v>1.8556641604542436E-3</v>
+        <v>3.7509881698415582E-5</v>
+      </c>
+      <c r="AM13">
+        <v>-3.7031971759828291E-5</v>
+      </c>
+      <c r="AN13">
+        <v>8.0718804269612276E-5</v>
+      </c>
+      <c r="AO13">
+        <v>-4.1974521998459934E-5</v>
+      </c>
+      <c r="AP13">
+        <v>-1.5922690149384306E-4</v>
+      </c>
+      <c r="AQ13">
+        <v>-1.9360777105775903E-4</v>
+      </c>
+      <c r="AR13">
+        <v>-2.6714318308061551E-4</v>
+      </c>
+      <c r="AS13">
+        <v>-2.337530485738773E-4</v>
+      </c>
+      <c r="AT13">
+        <v>-1.0159839309487029E-4</v>
+      </c>
+      <c r="AU13">
+        <v>1.9703965920606229E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14">
-        <v>-8.8596224399571988E-2</v>
+        <v>-8.8841239640745376E-2</v>
       </c>
       <c r="C14">
-        <v>3.4732995096946795E-4</v>
+        <v>3.7587318996434491E-4</v>
       </c>
       <c r="D14">
-        <v>-3.8532428382768145E-5</v>
+        <v>-3.6106785516018059E-5</v>
       </c>
       <c r="E14">
-        <v>3.6857133250170009E-7</v>
+        <v>3.1977635568931349E-7</v>
       </c>
       <c r="F14">
-        <v>-3.121457821565219E-6</v>
+        <v>-3.415366293250443E-6</v>
       </c>
       <c r="G14">
-        <v>-2.1596407065900496E-6</v>
+        <v>-2.4647209811798819E-6</v>
       </c>
       <c r="H14">
-        <v>1.0468923318698208E-4</v>
+        <v>1.0816218494954063E-4</v>
       </c>
       <c r="I14">
-        <v>1.102141873955699E-4</v>
+        <v>1.083563854331074E-4</v>
       </c>
       <c r="J14">
-        <v>-3.4274843074847024E-4</v>
+        <v>-4.0359289467484634E-4</v>
       </c>
       <c r="K14">
-        <v>-1.6763124048379022E-4</v>
+        <v>-2.2698926808337839E-4</v>
       </c>
       <c r="L14">
-        <v>-5.2558274154734932E-5</v>
+        <v>-7.5944343068019092E-5</v>
       </c>
       <c r="M14">
-        <v>3.2377149041498861E-5</v>
+        <v>2.1507196389246712E-5</v>
       </c>
       <c r="N14">
-        <v>1.3539028157254739E-4</v>
+        <v>1.1273946694154431E-4</v>
       </c>
       <c r="O14">
-        <v>3.2916624102146644E-4</v>
+        <v>3.3521565044295485E-4</v>
       </c>
       <c r="P14">
-        <v>-1.8350485477258805E-4</v>
+        <v>-1.9140325460355342E-4</v>
       </c>
       <c r="Q14">
-        <v>1.269549398388255E-4</v>
+        <v>1.1292926880669609E-4</v>
       </c>
       <c r="R14">
-        <v>6.296566279423023E-5</v>
+        <v>6.3420166614041465E-5</v>
       </c>
       <c r="S14">
-        <v>7.8363561147576615E-6</v>
+        <v>-9.7241579033181238E-6</v>
       </c>
       <c r="T14">
-        <v>-9.4010888610620107E-5</v>
+        <v>-9.4471191534895011E-5</v>
       </c>
       <c r="U14">
-        <v>-1.4410691911377927E-4</v>
+        <v>-1.4992329930084956E-4</v>
       </c>
       <c r="V14">
-        <v>-1.330242215334467E-4</v>
+        <v>-1.3598727103044913E-4</v>
       </c>
       <c r="W14">
-        <v>-1.4899708390225181E-4</v>
+        <v>-1.4895009000629068E-4</v>
       </c>
       <c r="X14">
-        <v>-1.4138090008725194E-4</v>
+        <v>-1.4359161631001901E-4</v>
       </c>
       <c r="Y14">
-        <v>-1.6015725900731063E-4</v>
+        <v>-1.6366089785843163E-4</v>
       </c>
       <c r="Z14">
-        <v>-7.3363439001952854E-5</v>
+        <v>-6.935591291789688E-5</v>
       </c>
       <c r="AA14">
-        <v>-1.5368392756940065E-4</v>
+        <v>-1.5072007102519809E-4</v>
       </c>
       <c r="AB14">
-        <v>-1.4124830392842655E-4</v>
+        <v>-1.3635777955985076E-4</v>
       </c>
       <c r="AC14">
-        <v>-7.4790375693594216E-5</v>
+        <v>-8.2491700594445163E-5</v>
       </c>
       <c r="AD14">
-        <v>-6.1249570158942041E-5</v>
+        <v>-4.2461438463185246E-5</v>
       </c>
       <c r="AE14">
-        <v>-1.8085411692275293E-4</v>
+        <v>-1.8141992305822734E-4</v>
       </c>
       <c r="AF14">
-        <v>1.5986069526128001E-5</v>
+        <v>-1.1519956412483156E-4</v>
       </c>
       <c r="AG14">
-        <v>-4.9800421270333088E-5</v>
+        <v>-2.0451028593854577E-4</v>
       </c>
       <c r="AH14">
-        <v>-2.4422012228731121E-5</v>
+        <v>2.5856414634635536E-6</v>
       </c>
       <c r="AI14">
-        <v>-1.1038931377588696E-4</v>
+        <v>-2.0863760186579761E-6</v>
       </c>
       <c r="AJ14">
-        <v>-2.0707938850017554E-4</v>
+        <v>-3.0362236680767871E-5</v>
       </c>
       <c r="AK14">
-        <v>-2.2125848087024228E-5</v>
+        <v>-4.6331775413856673E-5</v>
       </c>
       <c r="AL14">
-        <v>1.4954101625526666E-4</v>
+        <v>-3.6688986266927853E-5</v>
+      </c>
+      <c r="AM14">
+        <v>-4.1997182123142357E-5</v>
+      </c>
+      <c r="AN14">
+        <v>1.1999363142142447E-4</v>
+      </c>
+      <c r="AO14">
+        <v>-9.6630875924855327E-5</v>
+      </c>
+      <c r="AP14">
+        <v>-9.0587706422052953E-5</v>
+      </c>
+      <c r="AQ14">
+        <v>-1.2779584307016727E-4</v>
+      </c>
+      <c r="AR14">
+        <v>-6.759672338848069E-5</v>
+      </c>
+      <c r="AS14">
+        <v>-1.189235217487468E-4</v>
+      </c>
+      <c r="AT14">
+        <v>-4.813663330345986E-5</v>
+      </c>
+      <c r="AU14">
+        <v>1.4987506668879616E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
       <c r="B15">
-        <v>0.1696358589558957</v>
+        <v>0.17150461029276345</v>
       </c>
       <c r="C15">
-        <v>2.6988363133168886E-5</v>
+        <v>2.6385184483131E-6</v>
       </c>
       <c r="D15">
-        <v>-7.0140612572357845E-5</v>
+        <v>-7.2966823620947545E-5</v>
       </c>
       <c r="E15">
-        <v>1.3409092103494789E-6</v>
+        <v>1.3875519820610691E-6</v>
       </c>
       <c r="F15">
-        <v>-5.9405426792837709E-7</v>
+        <v>-6.1513517194133042E-7</v>
       </c>
       <c r="G15">
-        <v>-2.4151293474165215E-7</v>
+        <v>3.2144898546203162E-7</v>
       </c>
       <c r="H15">
-        <v>-1.4991488865634376E-4</v>
+        <v>-1.593355953760023E-4</v>
       </c>
       <c r="I15">
-        <v>2.1148586977616214E-4</v>
+        <v>2.0710622202490359E-4</v>
       </c>
       <c r="J15">
-        <v>-1.1915632042609158E-4</v>
+        <v>-8.5129009090236652E-5</v>
       </c>
       <c r="K15">
-        <v>2.7304610888868938E-5</v>
+        <v>7.4215261132279544E-5</v>
       </c>
       <c r="L15">
-        <v>-3.7169213685412866E-6</v>
+        <v>2.1989352823522621E-5</v>
       </c>
       <c r="M15">
-        <v>-3.9041051923910803E-5</v>
+        <v>-1.0449651742590595E-5</v>
       </c>
       <c r="N15">
-        <v>4.8327684571907137E-6</v>
+        <v>4.0447224215929441E-5</v>
       </c>
       <c r="O15">
-        <v>-1.8350485477258805E-4</v>
+        <v>-1.9140325460355342E-4</v>
       </c>
       <c r="P15">
-        <v>6.894877258131442E-4</v>
+        <v>6.9442955017730214E-4</v>
       </c>
       <c r="Q15">
-        <v>3.9484830519038426E-5</v>
+        <v>4.9446611384954125E-5</v>
       </c>
       <c r="R15">
-        <v>-7.1777747038358284E-5</v>
+        <v>-8.301729594056579E-5</v>
       </c>
       <c r="S15">
-        <v>2.4121341071563352E-5</v>
+        <v>1.8855862025319502E-5</v>
       </c>
       <c r="T15">
-        <v>-8.3269974051972942E-5</v>
+        <v>-7.38526790015407E-5</v>
       </c>
       <c r="U15">
-        <v>-2.7048957475572215E-5</v>
+        <v>-3.8154772608760959E-5</v>
       </c>
       <c r="V15">
-        <v>-5.3248494911361664E-5</v>
+        <v>-6.3044901711247487E-5</v>
       </c>
       <c r="W15">
-        <v>-4.5455751880689739E-5</v>
+        <v>-5.7935457059005518E-5</v>
       </c>
       <c r="X15">
-        <v>-5.7631025949004722E-5</v>
+        <v>-6.5819555982325189E-5</v>
       </c>
       <c r="Y15">
-        <v>-3.5527551726629803E-5</v>
+        <v>-3.7468656616220185E-5</v>
       </c>
       <c r="Z15">
-        <v>-1.3263381910058527E-4</v>
+        <v>-1.782539898621197E-4</v>
       </c>
       <c r="AA15">
-        <v>-3.2969459477362844E-5</v>
+        <v>-3.5217254681591116E-5</v>
       </c>
       <c r="AB15">
-        <v>-2.2895654394294344E-5</v>
+        <v>-3.702918054220624E-5</v>
       </c>
       <c r="AC15">
-        <v>-1.2545451693361795E-4</v>
+        <v>-1.2855757985712156E-4</v>
       </c>
       <c r="AD15">
-        <v>-1.0364208742550753E-4</v>
+        <v>-1.4396753953512328E-4</v>
       </c>
       <c r="AE15">
-        <v>-6.514157267702343E-5</v>
+        <v>-8.196439007572231E-5</v>
       </c>
       <c r="AF15">
-        <v>2.6395041758708247E-5</v>
+        <v>8.4662705554258434E-5</v>
       </c>
       <c r="AG15">
-        <v>6.9733309581051568E-5</v>
+        <v>6.6162244468470947E-5</v>
       </c>
       <c r="AH15">
-        <v>6.9763613772951899E-5</v>
+        <v>-2.7394837652581182E-4</v>
       </c>
       <c r="AI15">
-        <v>7.2662368048550041E-5</v>
+        <v>-6.5547945583112544E-6</v>
       </c>
       <c r="AJ15">
-        <v>2.2607564456644093E-5</v>
+        <v>4.1123231197991042E-5</v>
       </c>
       <c r="AK15">
-        <v>-1.4927980298021389E-4</v>
+        <v>6.2056798502229998E-5</v>
       </c>
       <c r="AL15">
-        <v>-9.2389600404516471E-4</v>
+        <v>5.9141119826975729E-5</v>
+      </c>
+      <c r="AM15">
+        <v>6.4940417909613204E-5</v>
+      </c>
+      <c r="AN15">
+        <v>1.7568057079390937E-4</v>
+      </c>
+      <c r="AO15">
+        <v>2.0055864824601751E-4</v>
+      </c>
+      <c r="AP15">
+        <v>1.5493901145648321E-4</v>
+      </c>
+      <c r="AQ15">
+        <v>2.4730747425309231E-4</v>
+      </c>
+      <c r="AR15">
+        <v>2.7308768218809126E-4</v>
+      </c>
+      <c r="AS15">
+        <v>2.7317076696866446E-4</v>
+      </c>
+      <c r="AT15">
+        <v>2.5749343941864461E-4</v>
+      </c>
+      <c r="AU15">
+        <v>-2.7499677607067691E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16">
-        <v>-7.6960972568159407E-3</v>
+        <v>1.1774153186037868E-2</v>
       </c>
       <c r="C16">
-        <v>4.845077199879175E-4</v>
+        <v>4.5479630617692663E-4</v>
       </c>
       <c r="D16">
-        <v>-3.372248923272478E-5</v>
+        <v>-3.8268627266736864E-5</v>
       </c>
       <c r="E16">
-        <v>3.7574335880633599E-7</v>
+        <v>4.5857766933257175E-7</v>
       </c>
       <c r="F16">
-        <v>6.4400334893784247E-7</v>
+        <v>9.6890339596409447E-7</v>
       </c>
       <c r="G16">
-        <v>1.3857960920250325E-6</v>
+        <v>2.2919377344612559E-6</v>
       </c>
       <c r="H16">
-        <v>1.3113093278026549E-4</v>
+        <v>1.3071846020232586E-4</v>
       </c>
       <c r="I16">
-        <v>1.1996236000682767E-4</v>
+        <v>1.0225176214711347E-4</v>
       </c>
       <c r="J16">
-        <v>-3.7316481097308702E-4</v>
+        <v>-3.357211269023282E-4</v>
       </c>
       <c r="K16">
-        <v>-1.3337174712682435E-4</v>
+        <v>1.349773042218054E-5</v>
       </c>
       <c r="L16">
-        <v>1.4881035912969271E-4</v>
+        <v>1.9266492715666828E-4</v>
       </c>
       <c r="M16">
-        <v>3.3152648945091031E-4</v>
+        <v>3.3624995541029119E-4</v>
       </c>
       <c r="N16">
-        <v>3.4002604892777329E-4</v>
+        <v>3.809472701916583E-4</v>
       </c>
       <c r="O16">
-        <v>1.269549398388255E-4</v>
+        <v>1.1292926880669609E-4</v>
       </c>
       <c r="P16">
-        <v>3.9484830519038426E-5</v>
+        <v>4.9446611384954125E-5</v>
       </c>
       <c r="Q16">
-        <v>2.6598765162618564E-3</v>
+        <v>2.5747739387373641E-3</v>
       </c>
       <c r="R16">
-        <v>2.3297478241770582E-4</v>
+        <v>2.1913167883282943E-4</v>
       </c>
       <c r="S16">
-        <v>3.4904808729044097E-5</v>
+        <v>2.152019817382167E-8</v>
       </c>
       <c r="T16">
-        <v>-1.6837384825445312E-4</v>
+        <v>-1.4440280686153073E-4</v>
       </c>
       <c r="U16">
-        <v>1.0373421379304432E-5</v>
+        <v>-2.6801630633065313E-5</v>
       </c>
       <c r="V16">
-        <v>-1.117354671923111E-4</v>
+        <v>-1.4598041312303338E-4</v>
       </c>
       <c r="W16">
-        <v>9.4287239992525975E-6</v>
+        <v>-2.2401230289397843E-5</v>
       </c>
       <c r="X16">
-        <v>-1.0251950836340615E-4</v>
+        <v>-1.2828538766499696E-4</v>
       </c>
       <c r="Y16">
-        <v>-1.1483252342324861E-4</v>
+        <v>-1.3966910239060644E-4</v>
       </c>
       <c r="Z16">
-        <v>7.3650882546151043E-5</v>
+        <v>-2.4501215264448426E-5</v>
       </c>
       <c r="AA16">
-        <v>-9.1174832405318805E-5</v>
+        <v>-1.3973866636855751E-4</v>
       </c>
       <c r="AB16">
-        <v>-5.9829093505551391E-5</v>
+        <v>-9.0249479485285768E-5</v>
       </c>
       <c r="AC16">
-        <v>-6.3944817539409051E-5</v>
+        <v>-9.4672787049431098E-5</v>
       </c>
       <c r="AD16">
-        <v>-9.6870081066907309E-5</v>
+        <v>-1.4888204729556121E-4</v>
       </c>
       <c r="AE16">
-        <v>-2.0547518966914247E-4</v>
+        <v>-2.4081160121491532E-4</v>
       </c>
       <c r="AF16">
-        <v>5.5217241106854903E-5</v>
+        <v>-1.8472502587747389E-4</v>
       </c>
       <c r="AG16">
-        <v>1.5095427334314274E-5</v>
+        <v>-1.6032356014389243E-4</v>
       </c>
       <c r="AH16">
-        <v>-4.7615599785720097E-5</v>
+        <v>2.3855001279246731E-4</v>
       </c>
       <c r="AI16">
-        <v>-1.4975506209247366E-4</v>
+        <v>2.1424125191493481E-5</v>
       </c>
       <c r="AJ16">
-        <v>-1.4551202399548608E-4</v>
+        <v>4.3310463294058299E-5</v>
       </c>
       <c r="AK16">
-        <v>4.3247647696569719E-4</v>
+        <v>3.0243003215370273E-5</v>
       </c>
       <c r="AL16">
-        <v>-2.9369984849974707E-3</v>
+        <v>9.9187783901062129E-5</v>
+      </c>
+      <c r="AM16">
+        <v>4.5659398814754717E-6</v>
+      </c>
+      <c r="AN16">
+        <v>3.5467282610334778E-4</v>
+      </c>
+      <c r="AO16">
+        <v>9.9335769994272671E-5</v>
+      </c>
+      <c r="AP16">
+        <v>1.4475906175838904E-4</v>
+      </c>
+      <c r="AQ16">
+        <v>1.3099041661238466E-4</v>
+      </c>
+      <c r="AR16">
+        <v>1.3368543363995335E-4</v>
+      </c>
+      <c r="AS16">
+        <v>8.9842787849920853E-5</v>
+      </c>
+      <c r="AT16">
+        <v>6.5267646650780486E-5</v>
+      </c>
+      <c r="AU16">
+        <v>-5.0502537188203654E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="B17">
-        <v>-2.3922035373982246E-2</v>
+        <v>-2.9789862061208577E-2</v>
       </c>
       <c r="C17">
-        <v>3.1795346361254695E-4</v>
+        <v>1.7637045151684379E-4</v>
       </c>
       <c r="D17">
-        <v>-1.0961679661497309E-5</v>
+        <v>-6.7421397264230427E-6</v>
       </c>
       <c r="E17">
-        <v>1.8243497411146717E-7</v>
+        <v>1.2457386088757203E-7</v>
       </c>
       <c r="F17">
-        <v>1.8169749025254589E-6</v>
+        <v>2.8583726526747659E-6</v>
       </c>
       <c r="G17">
-        <v>-2.6065300542258092E-6</v>
+        <v>-2.9160843794511976E-6</v>
       </c>
       <c r="H17">
-        <v>5.3285487967453854E-4</v>
+        <v>5.4929014112099317E-4</v>
       </c>
       <c r="I17">
-        <v>-3.2832298733198899E-4</v>
+        <v>-3.2772630023695441E-4</v>
       </c>
       <c r="J17">
-        <v>-1.3841277220785558E-4</v>
+        <v>-1.0674752592823361E-6</v>
       </c>
       <c r="K17">
-        <v>2.613776721260494E-6</v>
+        <v>2.9273851682260377E-5</v>
       </c>
       <c r="L17">
-        <v>9.8345382135163798E-5</v>
+        <v>7.4522811783120368E-5</v>
       </c>
       <c r="M17">
-        <v>1.0427452557665578E-4</v>
+        <v>1.226329666786019E-4</v>
       </c>
       <c r="N17">
-        <v>-2.2675587168549286E-4</v>
+        <v>-2.4379828001537033E-4</v>
       </c>
       <c r="O17">
-        <v>6.296566279423023E-5</v>
+        <v>6.3420166614041465E-5</v>
       </c>
       <c r="P17">
-        <v>-7.1777747038358284E-5</v>
+        <v>-8.301729594056579E-5</v>
       </c>
       <c r="Q17">
-        <v>2.3297478241770582E-4</v>
+        <v>2.1913167883282943E-4</v>
       </c>
       <c r="R17">
-        <v>8.2722662820415745E-4</v>
+        <v>8.4702279396881627E-4</v>
       </c>
       <c r="S17">
-        <v>-3.0690882509336407E-5</v>
+        <v>-5.5661780513082573E-5</v>
       </c>
       <c r="T17">
-        <v>2.9047555104608677E-5</v>
+        <v>1.7237752156914227E-5</v>
       </c>
       <c r="U17">
-        <v>1.271425686217113E-4</v>
+        <v>1.8299925971461899E-4</v>
       </c>
       <c r="V17">
-        <v>8.8395592307760574E-5</v>
+        <v>1.3328758547934467E-4</v>
       </c>
       <c r="W17">
-        <v>1.4815178542516817E-4</v>
+        <v>1.9163080814031739E-4</v>
       </c>
       <c r="X17">
-        <v>1.2793428384854792E-4</v>
+        <v>1.6969360494653853E-4</v>
       </c>
       <c r="Y17">
-        <v>1.3822003228968703E-4</v>
+        <v>1.7256337651403776E-4</v>
       </c>
       <c r="Z17">
-        <v>5.4142873525537009E-4</v>
+        <v>6.3443915418618974E-4</v>
       </c>
       <c r="AA17">
-        <v>4.1169310045427237E-5</v>
+        <v>7.092254184415976E-5</v>
       </c>
       <c r="AB17">
-        <v>2.0325523126090919E-4</v>
+        <v>2.3911329826071834E-4</v>
       </c>
       <c r="AC17">
-        <v>3.1865545823334021E-4</v>
+        <v>3.6189080419627914E-4</v>
       </c>
       <c r="AD17">
-        <v>2.8577178219182855E-5</v>
+        <v>6.604002278490482E-5</v>
       </c>
       <c r="AE17">
-        <v>8.0774329570172838E-5</v>
+        <v>1.5443206641331335E-4</v>
       </c>
       <c r="AF17">
-        <v>-2.9181602343716386E-5</v>
+        <v>-1.1826501668490294E-4</v>
       </c>
       <c r="AG17">
-        <v>-1.6425031801793328E-4</v>
+        <v>7.3008512166095155E-5</v>
       </c>
       <c r="AH17">
-        <v>-1.464280794781427E-4</v>
+        <v>1.4592670078669959E-3</v>
       </c>
       <c r="AI17">
-        <v>-8.3144337218020383E-5</v>
+        <v>8.8683531728410805E-6</v>
       </c>
       <c r="AJ17">
-        <v>6.6909091201014168E-5</v>
+        <v>-1.7277727892688191E-4</v>
       </c>
       <c r="AK17">
-        <v>1.2622166399992238E-3</v>
+        <v>-2.1105419822174632E-4</v>
       </c>
       <c r="AL17">
-        <v>1.9159844410129145E-3</v>
+        <v>-2.286239893450254E-4</v>
+      </c>
+      <c r="AM17">
+        <v>-2.3864668825181033E-4</v>
+      </c>
+      <c r="AN17">
+        <v>-3.3336512455707886E-4</v>
+      </c>
+      <c r="AO17">
+        <v>-4.5727045328657247E-4</v>
+      </c>
+      <c r="AP17">
+        <v>-5.809496865754588E-4</v>
+      </c>
+      <c r="AQ17">
+        <v>-7.357300457618151E-4</v>
+      </c>
+      <c r="AR17">
+        <v>-7.3961136516413986E-4</v>
+      </c>
+      <c r="AS17">
+        <v>-9.0350903655139119E-4</v>
+      </c>
+      <c r="AT17">
+        <v>-1.007617370786248E-3</v>
+      </c>
+      <c r="AU17">
+        <v>3.0765591358530376E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18">
-        <v>3.8945568469491709E-3</v>
+        <v>2.8543144252540092E-2</v>
       </c>
       <c r="C18">
-        <v>-1.2611545203569901E-4</v>
+        <v>-1.251789244486449E-4</v>
       </c>
       <c r="D18">
-        <v>-8.5091991468634652E-6</v>
+        <v>-9.4708286405458583E-6</v>
       </c>
       <c r="E18">
-        <v>1.4662442463619891E-7</v>
+        <v>1.5777525640655847E-7</v>
       </c>
       <c r="F18">
-        <v>-6.680357150721785E-7</v>
+        <v>-7.8505238787798489E-7</v>
       </c>
       <c r="G18">
-        <v>1.3960139662901061E-6</v>
+        <v>1.8965239525081537E-6</v>
       </c>
       <c r="H18">
-        <v>3.803704287464983E-5</v>
+        <v>-6.3075923319529017E-6</v>
       </c>
       <c r="I18">
-        <v>-6.5569495540851268E-5</v>
+        <v>-8.8298309109658985E-5</v>
       </c>
       <c r="J18">
-        <v>1.3004048201979937E-4</v>
+        <v>1.5113738574621413E-4</v>
       </c>
       <c r="K18">
-        <v>-5.0072335337061495E-5</v>
+        <v>2.3114156746363254E-6</v>
       </c>
       <c r="L18">
-        <v>-8.4351643269366572E-5</v>
+        <v>-1.7141492204883599E-5</v>
       </c>
       <c r="M18">
-        <v>-1.039146394817229E-4</v>
+        <v>-1.2302446865166663E-4</v>
       </c>
       <c r="N18">
-        <v>-4.1577346955971764E-5</v>
+        <v>-2.1300285445725802E-5</v>
       </c>
       <c r="O18">
-        <v>7.8363561147576615E-6</v>
+        <v>-9.7241579033181238E-6</v>
       </c>
       <c r="P18">
-        <v>2.4121341071563352E-5</v>
+        <v>1.8855862025319502E-5</v>
       </c>
       <c r="Q18">
-        <v>3.4904808729044097E-5</v>
+        <v>2.152019817382167E-8</v>
       </c>
       <c r="R18">
-        <v>-3.0690882509336407E-5</v>
+        <v>-5.5661780513082573E-5</v>
       </c>
       <c r="S18">
-        <v>1.3105812821983739E-4</v>
+        <v>6.104641710819416E-5</v>
       </c>
       <c r="T18">
-        <v>-2.2629943882376694E-5</v>
+        <v>-4.1658348281120334E-6</v>
       </c>
       <c r="U18">
-        <v>-6.171784764328078E-5</v>
+        <v>-7.0051419671780032E-5</v>
       </c>
       <c r="V18">
-        <v>-6.7974464738856499E-5</v>
+        <v>-5.7342623507554039E-5</v>
       </c>
       <c r="W18">
-        <v>-6.5472062491542552E-5</v>
+        <v>-6.8123742159222002E-5</v>
       </c>
       <c r="X18">
-        <v>-4.4706284725290913E-5</v>
+        <v>-4.1231331469171744E-5</v>
       </c>
       <c r="Y18">
-        <v>-3.9417604131501693E-5</v>
+        <v>-3.3841226299177751E-5</v>
       </c>
       <c r="Z18">
-        <v>-1.7316322947060273E-4</v>
+        <v>-2.4394949117701684E-4</v>
       </c>
       <c r="AA18">
-        <v>-6.7060874585868108E-5</v>
+        <v>-7.1943486689014067E-5</v>
       </c>
       <c r="AB18">
-        <v>-6.8202614579487841E-5</v>
+        <v>-6.7323716341837159E-5</v>
       </c>
       <c r="AC18">
-        <v>-1.010634633340046E-4</v>
+        <v>-6.2272408511824617E-5</v>
       </c>
       <c r="AD18">
-        <v>-8.8252890970888682E-5</v>
+        <v>-7.6215484571437312E-5</v>
       </c>
       <c r="AE18">
-        <v>-5.0869929795726784E-5</v>
+        <v>-7.5894190473031948E-5</v>
       </c>
       <c r="AF18">
-        <v>1.4369995520663976E-4</v>
+        <v>1.6071097488305503E-5</v>
       </c>
       <c r="AG18">
-        <v>2.4045305354425568E-4</v>
+        <v>-2.8932826486339233E-5</v>
       </c>
       <c r="AH18">
-        <v>5.1184794542013037E-6</v>
+        <v>-6.0707507983759519E-4</v>
       </c>
       <c r="AI18">
-        <v>-1.0318830751175363E-5</v>
+        <v>-1.1187267807247542E-4</v>
       </c>
       <c r="AJ18">
-        <v>-4.1495320219959823E-5</v>
+        <v>6.4905290289194568E-5</v>
       </c>
       <c r="AK18">
-        <v>-3.6945511760223121E-4</v>
+        <v>8.4261867914481575E-5</v>
       </c>
       <c r="AL18">
-        <v>-9.865326003005076E-3</v>
+        <v>8.2409155162653752E-5</v>
+      </c>
+      <c r="AM18">
+        <v>9.9071876008128179E-5</v>
+      </c>
+      <c r="AN18">
+        <v>1.9136655290883959E-4</v>
+      </c>
+      <c r="AO18">
+        <v>3.288774277324341E-4</v>
+      </c>
+      <c r="AP18">
+        <v>4.4260695638047472E-4</v>
+      </c>
+      <c r="AQ18">
+        <v>5.9604308133663934E-4</v>
+      </c>
+      <c r="AR18">
+        <v>5.5705729321204722E-4</v>
+      </c>
+      <c r="AS18">
+        <v>7.0277096198894913E-4</v>
+      </c>
+      <c r="AT18">
+        <v>8.4387520836503097E-4</v>
+      </c>
+      <c r="AU18">
+        <v>-3.5672774236356931E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>31</v>
       </c>
       <c r="B19">
-        <v>6.2173770767347501E-2</v>
+        <v>0.1081940065869198</v>
       </c>
       <c r="C19">
-        <v>9.2020723213705104E-4</v>
+        <v>1.041836276508457E-3</v>
       </c>
       <c r="D19">
-        <v>4.8252627919070511E-5</v>
+        <v>2.7492391960233991E-5</v>
       </c>
       <c r="E19">
-        <v>-7.5423300659791378E-7</v>
+        <v>-4.6778657208482653E-7</v>
       </c>
       <c r="F19">
-        <v>8.7905071189336316E-6</v>
+        <v>8.6040096158168785E-6</v>
       </c>
       <c r="G19">
-        <v>5.60627969163034E-6</v>
+        <v>4.319260879761743E-6</v>
       </c>
       <c r="H19">
-        <v>8.2778847100849304E-5</v>
+        <v>1.113148325347807E-4</v>
       </c>
       <c r="I19">
-        <v>-1.1210077178624761E-5</v>
+        <v>-2.5476384497442997E-5</v>
       </c>
       <c r="J19">
-        <v>-3.8491506647991239E-4</v>
+        <v>-5.6944046867761142E-4</v>
       </c>
       <c r="K19">
-        <v>4.3115134031259544E-4</v>
+        <v>3.1481064640636632E-4</v>
       </c>
       <c r="L19">
-        <v>7.2118885906164625E-4</v>
+        <v>5.5691181286081685E-4</v>
       </c>
       <c r="M19">
-        <v>7.980596790374498E-4</v>
+        <v>6.545442077442599E-4</v>
       </c>
       <c r="N19">
-        <v>8.0337449069115311E-4</v>
+        <v>6.721914826169754E-4</v>
       </c>
       <c r="O19">
-        <v>-9.4010888610620107E-5</v>
+        <v>-9.4471191534895011E-5</v>
       </c>
       <c r="P19">
-        <v>-8.3269974051972942E-5</v>
+        <v>-7.38526790015407E-5</v>
       </c>
       <c r="Q19">
-        <v>-1.6837384825445312E-4</v>
+        <v>-1.4440280686153073E-4</v>
       </c>
       <c r="R19">
-        <v>2.9047555104608677E-5</v>
+        <v>1.7237752156914227E-5</v>
       </c>
       <c r="S19">
-        <v>-2.2629943882376694E-5</v>
+        <v>-4.1658348281120334E-6</v>
       </c>
       <c r="T19">
-        <v>1.2117303912154622E-3</v>
+        <v>1.101428936213343E-3</v>
       </c>
       <c r="U19">
-        <v>1.7667256537239249E-4</v>
+        <v>7.2710283622815311E-5</v>
       </c>
       <c r="V19">
-        <v>2.1298464911942769E-4</v>
+        <v>1.3651218994676075E-4</v>
       </c>
       <c r="W19">
-        <v>1.9772647039112233E-4</v>
+        <v>1.0896029431976196E-4</v>
       </c>
       <c r="X19">
-        <v>2.233250105026045E-4</v>
+        <v>1.282134540032591E-4</v>
       </c>
       <c r="Y19">
-        <v>1.7193831475931362E-4</v>
+        <v>8.0830017261401019E-5</v>
       </c>
       <c r="Z19">
-        <v>2.5970262285962857E-4</v>
+        <v>1.5334066420524253E-4</v>
       </c>
       <c r="AA19">
-        <v>1.1922635542131398E-4</v>
+        <v>5.9874234150736611E-5</v>
       </c>
       <c r="AB19">
-        <v>1.8972155858813225E-4</v>
+        <v>1.1636690049373834E-4</v>
       </c>
       <c r="AC19">
-        <v>1.4552762293012069E-4</v>
+        <v>4.256635529366844E-5</v>
       </c>
       <c r="AD19">
-        <v>1.9141987622453994E-4</v>
+        <v>1.1766376478074977E-4</v>
       </c>
       <c r="AE19">
-        <v>2.3519481990508543E-4</v>
+        <v>1.5517820720287938E-4</v>
       </c>
       <c r="AF19">
-        <v>-2.0020278928987788E-5</v>
+        <v>-1.1700696185898906E-4</v>
       </c>
       <c r="AG19">
-        <v>-4.3876688809288021E-5</v>
+        <v>4.5209143831683861E-5</v>
       </c>
       <c r="AH19">
-        <v>-7.8474926040751495E-5</v>
+        <v>8.1988955980486465E-5</v>
       </c>
       <c r="AI19">
-        <v>-4.9310419049289518E-5</v>
+        <v>7.8812404870216824E-6</v>
       </c>
       <c r="AJ19">
-        <v>7.0617155048474742E-5</v>
+        <v>2.1108190110501169E-5</v>
       </c>
       <c r="AK19">
-        <v>1.2677358794206325E-4</v>
+        <v>1.2126832635617896E-5</v>
       </c>
       <c r="AL19">
-        <v>-8.1785769193418525E-4</v>
+        <v>9.0201323255491642E-6</v>
+      </c>
+      <c r="AM19">
+        <v>3.5618057022892332E-5</v>
+      </c>
+      <c r="AN19">
+        <v>-5.6874107760989528E-5</v>
+      </c>
+      <c r="AO19">
+        <v>3.1244630984451904E-6</v>
+      </c>
+      <c r="AP19">
+        <v>6.0665113662792831E-5</v>
+      </c>
+      <c r="AQ19">
+        <v>1.9941947784998804E-5</v>
+      </c>
+      <c r="AR19">
+        <v>-8.1652238525404923E-5</v>
+      </c>
+      <c r="AS19">
+        <v>-4.5860736276707136E-5</v>
+      </c>
+      <c r="AT19">
+        <v>2.7897285651183948E-6</v>
+      </c>
+      <c r="AU19">
+        <v>-1.5899799474807068E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>32</v>
       </c>
       <c r="B20">
-        <v>-2.4811669829727923E-2</v>
+        <v>-2.4263270540114328E-2</v>
       </c>
       <c r="C20">
-        <v>-8.3185897810384346E-4</v>
+        <v>-9.7054546060580736E-4</v>
       </c>
       <c r="D20">
-        <v>9.4858443313781252E-5</v>
+        <v>9.8927952892223525E-5</v>
       </c>
       <c r="E20">
-        <v>-1.5941604962152209E-6</v>
+        <v>-1.6239886133263865E-6</v>
       </c>
       <c r="F20">
-        <v>1.3450910449102438E-6</v>
+        <v>3.1468399815566228E-6</v>
       </c>
       <c r="G20">
-        <v>-5.1534373013510123E-6</v>
+        <v>-5.2755043143294661E-6</v>
       </c>
       <c r="H20">
-        <v>-7.8108468133902091E-5</v>
+        <v>-7.1771963827092005E-5</v>
       </c>
       <c r="I20">
-        <v>1.6723232310480058E-4</v>
+        <v>1.2038757087642725E-4</v>
       </c>
       <c r="J20">
-        <v>7.8261807956351084E-4</v>
+        <v>9.0862886650066297E-4</v>
       </c>
       <c r="K20">
-        <v>3.9769228000006963E-4</v>
+        <v>1.906855425443403E-4</v>
       </c>
       <c r="L20">
-        <v>3.2376182698039063E-4</v>
+        <v>4.9512348306491338E-5</v>
       </c>
       <c r="M20">
-        <v>5.0596014004889583E-4</v>
+        <v>2.8771262856621234E-4</v>
       </c>
       <c r="N20">
-        <v>2.2638868117231826E-4</v>
+        <v>-8.4491816705058794E-5</v>
       </c>
       <c r="O20">
-        <v>-1.4410691911377927E-4</v>
+        <v>-1.4992329930084956E-4</v>
       </c>
       <c r="P20">
-        <v>-2.7048957475572215E-5</v>
+        <v>-3.8154772608760959E-5</v>
       </c>
       <c r="Q20">
-        <v>1.0373421379304432E-5</v>
+        <v>-2.6801630633065313E-5</v>
       </c>
       <c r="R20">
-        <v>1.271425686217113E-4</v>
+        <v>1.8299925971461899E-4</v>
       </c>
       <c r="S20">
-        <v>-6.171784764328078E-5</v>
+        <v>-7.0051419671780032E-5</v>
       </c>
       <c r="T20">
-        <v>1.7667256537239249E-4</v>
+        <v>7.2710283622815311E-5</v>
       </c>
       <c r="U20">
-        <v>5.6740232289179656E-3</v>
+        <v>5.6672458854762145E-3</v>
       </c>
       <c r="V20">
-        <v>1.8574535407028699E-3</v>
+        <v>1.843457031775194E-3</v>
       </c>
       <c r="W20">
-        <v>1.9210975534026768E-3</v>
+        <v>1.8951162975537883E-3</v>
       </c>
       <c r="X20">
-        <v>1.8273397178050575E-3</v>
+        <v>1.81659700246443E-3</v>
       </c>
       <c r="Y20">
-        <v>1.8218355247612106E-3</v>
+        <v>1.8040548963349631E-3</v>
       </c>
       <c r="Z20">
-        <v>2.2275628201659341E-3</v>
+        <v>2.2845257641886177E-3</v>
       </c>
       <c r="AA20">
-        <v>1.8998891386364958E-3</v>
+        <v>1.8920863153112052E-3</v>
       </c>
       <c r="AB20">
-        <v>1.9630295266209875E-3</v>
+        <v>1.9477809784958805E-3</v>
       </c>
       <c r="AC20">
-        <v>1.9464228286575627E-3</v>
+        <v>1.928583003832811E-3</v>
       </c>
       <c r="AD20">
-        <v>1.9233599925610326E-3</v>
+        <v>1.8850066000003034E-3</v>
       </c>
       <c r="AE20">
-        <v>1.9376800643951713E-3</v>
+        <v>1.9536564121836733E-3</v>
       </c>
       <c r="AF20">
-        <v>-6.5243425858294441E-5</v>
+        <v>5.5222455131041966E-4</v>
       </c>
       <c r="AG20">
-        <v>-1.739988023915335E-5</v>
+        <v>1.2104864789878457E-3</v>
       </c>
       <c r="AH20">
-        <v>1.9536586607487346E-4</v>
+        <v>2.0509825947148883E-3</v>
       </c>
       <c r="AI20">
-        <v>5.8301872379350954E-4</v>
+        <v>1.0120439514530529E-5</v>
       </c>
       <c r="AJ20">
-        <v>1.2285457859871624E-3</v>
+        <v>-1.4618571504023217E-4</v>
       </c>
       <c r="AK20">
-        <v>1.9465304900853578E-3</v>
+        <v>-2.7183823172937716E-4</v>
       </c>
       <c r="AL20">
-        <v>1.2570580759453292E-3</v>
+        <v>-2.3210394694152617E-4</v>
+      </c>
+      <c r="AM20">
+        <v>-8.2276183820985177E-5</v>
+      </c>
+      <c r="AN20">
+        <v>-6.6993753514627019E-4</v>
+      </c>
+      <c r="AO20">
+        <v>-5.5086115599919244E-4</v>
+      </c>
+      <c r="AP20">
+        <v>-7.2703373353399285E-4</v>
+      </c>
+      <c r="AQ20">
+        <v>-7.1527984050689247E-4</v>
+      </c>
+      <c r="AR20">
+        <v>-5.5307589161014562E-4</v>
+      </c>
+      <c r="AS20">
+        <v>-1.1941716633905516E-3</v>
+      </c>
+      <c r="AT20">
+        <v>-1.0629014125968844E-3</v>
+      </c>
+      <c r="AU20">
+        <v>1.153261567551158E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
       <c r="B21">
-        <v>3.8294562312711063E-2</v>
+        <v>3.5390011363223998E-2</v>
       </c>
       <c r="C21">
-        <v>1.0994851444448214E-4</v>
+        <v>5.4564998490394968E-5</v>
       </c>
       <c r="D21">
-        <v>9.0989921146466591E-5</v>
+        <v>9.5079942167840791E-5</v>
       </c>
       <c r="E21">
-        <v>-1.4215308313672527E-6</v>
+        <v>-1.4719476802219044E-6</v>
       </c>
       <c r="F21">
-        <v>4.025986691406764E-6</v>
+        <v>5.783616677808439E-6</v>
       </c>
       <c r="G21">
-        <v>-5.3881480956986952E-6</v>
+        <v>-5.5073157264664097E-6</v>
       </c>
       <c r="H21">
-        <v>8.2830541979518019E-5</v>
+        <v>9.8280272617993908E-5</v>
       </c>
       <c r="I21">
-        <v>7.8761043703936087E-5</v>
+        <v>4.1476273327815304E-5</v>
       </c>
       <c r="J21">
-        <v>-4.606866627905544E-5</v>
+        <v>-2.3736145379538436E-5</v>
       </c>
       <c r="K21">
-        <v>2.9149035000510816E-4</v>
+        <v>1.3362045721442809E-4</v>
       </c>
       <c r="L21">
-        <v>3.2780818822117542E-4</v>
+        <v>9.1714903042823878E-5</v>
       </c>
       <c r="M21">
-        <v>4.4216391870953355E-4</v>
+        <v>2.6177914963687447E-4</v>
       </c>
       <c r="N21">
-        <v>2.0518260968167105E-4</v>
+        <v>-2.4716232105078482E-5</v>
       </c>
       <c r="O21">
-        <v>-1.330242215334467E-4</v>
+        <v>-1.3598727103044913E-4</v>
       </c>
       <c r="P21">
-        <v>-5.3248494911361664E-5</v>
+        <v>-6.3044901711247487E-5</v>
       </c>
       <c r="Q21">
-        <v>-1.117354671923111E-4</v>
+        <v>-1.4598041312303338E-4</v>
       </c>
       <c r="R21">
-        <v>8.8395592307760574E-5</v>
+        <v>1.3328758547934467E-4</v>
       </c>
       <c r="S21">
-        <v>-6.7974464738856499E-5</v>
+        <v>-5.7342623507554039E-5</v>
       </c>
       <c r="T21">
-        <v>2.1298464911942769E-4</v>
+        <v>1.3651218994676075E-4</v>
       </c>
       <c r="U21">
-        <v>1.8574535407028699E-3</v>
+        <v>1.843457031775194E-3</v>
       </c>
       <c r="V21">
-        <v>2.8920092573815788E-3</v>
+        <v>2.8795227447019085E-3</v>
       </c>
       <c r="W21">
-        <v>1.8637322063900959E-3</v>
+        <v>1.8446265558887632E-3</v>
       </c>
       <c r="X21">
-        <v>1.7932585873553352E-3</v>
+        <v>1.7830097382464513E-3</v>
       </c>
       <c r="Y21">
-        <v>1.782955011217812E-3</v>
+        <v>1.7695313690283174E-3</v>
       </c>
       <c r="Z21">
-        <v>2.0644669881111416E-3</v>
+        <v>2.1308345756094966E-3</v>
       </c>
       <c r="AA21">
-        <v>1.8361811837960412E-3</v>
+        <v>1.8307813351931951E-3</v>
       </c>
       <c r="AB21">
-        <v>1.8992719755830723E-3</v>
+        <v>1.8897212411745157E-3</v>
       </c>
       <c r="AC21">
-        <v>1.8811358344825223E-3</v>
+        <v>1.8605600858381554E-3</v>
       </c>
       <c r="AD21">
-        <v>1.8440763326476764E-3</v>
+        <v>1.8140542848835981E-3</v>
       </c>
       <c r="AE21">
-        <v>1.8782525007587443E-3</v>
+        <v>1.8933636443939075E-3</v>
       </c>
       <c r="AF21">
-        <v>-7.7848699895063703E-5</v>
+        <v>4.5822649062025563E-4</v>
       </c>
       <c r="AG21">
-        <v>-1.4088841276468076E-4</v>
+        <v>1.0676035607798836E-3</v>
       </c>
       <c r="AH21">
-        <v>9.2847571774129197E-6</v>
+        <v>1.5176362474077264E-3</v>
       </c>
       <c r="AI21">
-        <v>4.7392527083531223E-4</v>
+        <v>-3.4786042642580089E-5</v>
       </c>
       <c r="AJ21">
-        <v>1.0787743869131619E-3</v>
+        <v>-1.735730348375082E-4</v>
       </c>
       <c r="AK21">
-        <v>1.3632526422522979E-3</v>
+        <v>-2.6366735097988901E-4</v>
       </c>
       <c r="AL21">
-        <v>1.7711631564490352E-3</v>
+        <v>-2.1293977735779466E-4</v>
+      </c>
+      <c r="AM21">
+        <v>-1.9654147609520932E-4</v>
+      </c>
+      <c r="AN21">
+        <v>-6.4827926502178835E-4</v>
+      </c>
+      <c r="AO21">
+        <v>-4.7609468647268321E-4</v>
+      </c>
+      <c r="AP21">
+        <v>-6.2808793997390193E-4</v>
+      </c>
+      <c r="AQ21">
+        <v>-7.6297195198454923E-4</v>
+      </c>
+      <c r="AR21">
+        <v>-6.8631778886263806E-4</v>
+      </c>
+      <c r="AS21">
+        <v>-1.1641833501645736E-3</v>
+      </c>
+      <c r="AT21">
+        <v>-8.4145823694903657E-4</v>
+      </c>
+      <c r="AU21">
+        <v>2.8190986247373512E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="B22">
-        <v>-3.45107458494864E-2</v>
+        <v>-3.2633159734876432E-2</v>
       </c>
       <c r="C22">
-        <v>3.4149617901906395E-4</v>
+        <v>1.8750886129412046E-4</v>
       </c>
       <c r="D22">
-        <v>1.4487261463278959E-4</v>
+        <v>1.4691638870072143E-4</v>
       </c>
       <c r="E22">
-        <v>-2.1880704982306739E-6</v>
+        <v>-2.196207892305563E-6</v>
       </c>
       <c r="F22">
-        <v>3.0335189609310603E-6</v>
+        <v>4.7676942403857943E-6</v>
       </c>
       <c r="G22">
-        <v>-3.978296045687748E-6</v>
+        <v>-3.9931705189359123E-6</v>
       </c>
       <c r="H22">
-        <v>7.7820315155593934E-5</v>
+        <v>8.3416178005291336E-5</v>
       </c>
       <c r="I22">
-        <v>1.5617021102617528E-4</v>
+        <v>1.2093731012935037E-4</v>
       </c>
       <c r="J22">
-        <v>4.2440083018852135E-4</v>
+        <v>5.431154799444577E-4</v>
       </c>
       <c r="K22">
-        <v>2.5618405511322324E-4</v>
+        <v>9.8605869791130974E-5</v>
       </c>
       <c r="L22">
-        <v>3.3070796374947342E-4</v>
+        <v>8.2587101317808094E-5</v>
       </c>
       <c r="M22">
-        <v>4.5706671843364418E-4</v>
+        <v>2.5826410564054706E-4</v>
       </c>
       <c r="N22">
-        <v>1.8216755710596545E-4</v>
+        <v>-5.5970575455671024E-5</v>
       </c>
       <c r="O22">
-        <v>-1.4899708390225181E-4</v>
+        <v>-1.4895009000629068E-4</v>
       </c>
       <c r="P22">
-        <v>-4.5455751880689739E-5</v>
+        <v>-5.7935457059005518E-5</v>
       </c>
       <c r="Q22">
-        <v>9.4287239992525975E-6</v>
+        <v>-2.2401230289397843E-5</v>
       </c>
       <c r="R22">
-        <v>1.4815178542516817E-4</v>
+        <v>1.9163080814031739E-4</v>
       </c>
       <c r="S22">
-        <v>-6.5472062491542552E-5</v>
+        <v>-6.8123742159222002E-5</v>
       </c>
       <c r="T22">
-        <v>1.9772647039112233E-4</v>
+        <v>1.0896029431976196E-4</v>
       </c>
       <c r="U22">
-        <v>1.9210975534026768E-3</v>
+        <v>1.8951162975537883E-3</v>
       </c>
       <c r="V22">
-        <v>1.8637322063900959E-3</v>
+        <v>1.8446265558887632E-3</v>
       </c>
       <c r="W22">
-        <v>3.3576488540754132E-3</v>
+        <v>3.2966184966204746E-3</v>
       </c>
       <c r="X22">
-        <v>1.8412059755808844E-3</v>
+        <v>1.820507973572574E-3</v>
       </c>
       <c r="Y22">
-        <v>1.8283368597180748E-3</v>
+        <v>1.804104188789193E-3</v>
       </c>
       <c r="Z22">
-        <v>2.2383163748330055E-3</v>
+        <v>2.2741214480275968E-3</v>
       </c>
       <c r="AA22">
-        <v>1.8868885036266024E-3</v>
+        <v>1.866837593237227E-3</v>
       </c>
       <c r="AB22">
-        <v>1.9707676792196102E-3</v>
+        <v>1.9475253185488866E-3</v>
       </c>
       <c r="AC22">
-        <v>1.965770522141053E-3</v>
+        <v>1.9408720198035127E-3</v>
       </c>
       <c r="AD22">
-        <v>1.9024252576710921E-3</v>
+        <v>1.8559956197155764E-3</v>
       </c>
       <c r="AE22">
-        <v>1.9202388501367673E-3</v>
+        <v>1.932024964989839E-3</v>
       </c>
       <c r="AF22">
-        <v>-7.020635470974851E-5</v>
+        <v>5.4541746097795879E-4</v>
       </c>
       <c r="AG22">
-        <v>-1.3642910401312242E-4</v>
+        <v>1.0941564630721121E-3</v>
       </c>
       <c r="AH22">
-        <v>-1.503532742914133E-4</v>
+        <v>1.9807769367150589E-3</v>
       </c>
       <c r="AI22">
-        <v>5.984255336311437E-4</v>
+        <v>-2.499196204178031E-5</v>
       </c>
       <c r="AJ22">
-        <v>1.1088562784142143E-3</v>
+        <v>-2.222834236084621E-4</v>
       </c>
       <c r="AK22">
-        <v>1.8957295801901343E-3</v>
+        <v>-3.0196647512403438E-4</v>
       </c>
       <c r="AL22">
-        <v>4.7721010105692893E-4</v>
+        <v>-2.6065005605670287E-4</v>
+      </c>
+      <c r="AM22">
+        <v>-2.1341272329631613E-4</v>
+      </c>
+      <c r="AN22">
+        <v>-7.1922342183553347E-4</v>
+      </c>
+      <c r="AO22">
+        <v>-5.4323793292006825E-4</v>
+      </c>
+      <c r="AP22">
+        <v>-6.4071700354734022E-4</v>
+      </c>
+      <c r="AQ22">
+        <v>-8.4705198227061611E-4</v>
+      </c>
+      <c r="AR22">
+        <v>-9.2020975575314795E-4</v>
+      </c>
+      <c r="AS22">
+        <v>-1.2460338821984555E-3</v>
+      </c>
+      <c r="AT22">
+        <v>-1.1748513424215444E-3</v>
+      </c>
+      <c r="AU22">
+        <v>-5.5808922949478201E-6</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23">
-        <v>6.5426379414525199E-2</v>
+        <v>6.1794622473232579E-2</v>
       </c>
       <c r="C23">
-        <v>2.757096644079506E-4</v>
+        <v>1.7417468226116123E-4</v>
       </c>
       <c r="D23">
-        <v>1.4618794467486144E-4</v>
+        <v>1.5074793642326679E-4</v>
       </c>
       <c r="E23">
-        <v>-2.2935474202485726E-6</v>
+        <v>-2.3493849533306612E-6</v>
       </c>
       <c r="F23">
-        <v>1.787296442355267E-6</v>
+        <v>3.3524620796651282E-6</v>
       </c>
       <c r="G23">
-        <v>-3.3621390639611549E-6</v>
+        <v>-3.407896297764828E-6</v>
       </c>
       <c r="H23">
-        <v>2.4047013417550134E-5</v>
+        <v>1.7342415299603461E-5</v>
       </c>
       <c r="I23">
-        <v>8.493791552452478E-5</v>
+        <v>4.7924168673697809E-5</v>
       </c>
       <c r="J23">
-        <v>-4.8702403317142564E-5</v>
+        <v>7.0516791561772035E-6</v>
       </c>
       <c r="K23">
-        <v>2.6405773381428434E-4</v>
+        <v>8.4394877642775639E-5</v>
       </c>
       <c r="L23">
-        <v>2.9032905878042186E-4</v>
+        <v>9.5727949804365244E-6</v>
       </c>
       <c r="M23">
-        <v>3.2403182938415593E-4</v>
+        <v>9.1146905976084936E-5</v>
       </c>
       <c r="N23">
-        <v>1.6180093589072796E-4</v>
+        <v>-1.0149697730347235E-4</v>
       </c>
       <c r="O23">
-        <v>-1.4138090008725194E-4</v>
+        <v>-1.4359161631001901E-4</v>
       </c>
       <c r="P23">
-        <v>-5.7631025949004722E-5</v>
+        <v>-6.5819555982325189E-5</v>
       </c>
       <c r="Q23">
-        <v>-1.0251950836340615E-4</v>
+        <v>-1.2828538766499696E-4</v>
       </c>
       <c r="R23">
-        <v>1.2793428384854792E-4</v>
+        <v>1.6969360494653853E-4</v>
       </c>
       <c r="S23">
-        <v>-4.4706284725290913E-5</v>
+        <v>-4.1231331469171744E-5</v>
       </c>
       <c r="T23">
-        <v>2.233250105026045E-4</v>
+        <v>1.282134540032591E-4</v>
       </c>
       <c r="U23">
-        <v>1.8273397178050575E-3</v>
+        <v>1.81659700246443E-3</v>
       </c>
       <c r="V23">
-        <v>1.7932585873553352E-3</v>
+        <v>1.7830097382464513E-3</v>
       </c>
       <c r="W23">
-        <v>1.8412059755808844E-3</v>
+        <v>1.820507973572574E-3</v>
       </c>
       <c r="X23">
-        <v>3.3362171581227703E-3</v>
+        <v>3.3054676265112382E-3</v>
       </c>
       <c r="Y23">
-        <v>1.7762694242612596E-3</v>
+        <v>1.7646358826804106E-3</v>
       </c>
       <c r="Z23">
-        <v>1.9881072086810839E-3</v>
+        <v>2.050020095753433E-3</v>
       </c>
       <c r="AA23">
-        <v>1.8276990663665615E-3</v>
+        <v>1.8237929699404718E-3</v>
       </c>
       <c r="AB23">
-        <v>1.8774178622319483E-3</v>
+        <v>1.8678918029877577E-3</v>
       </c>
       <c r="AC23">
-        <v>1.8769145228621185E-3</v>
+        <v>1.866348791835577E-3</v>
       </c>
       <c r="AD23">
-        <v>1.8174325194119526E-3</v>
+        <v>1.7969400457006823E-3</v>
       </c>
       <c r="AE23">
-        <v>1.8722320475111842E-3</v>
+        <v>1.8816706633350282E-3</v>
       </c>
       <c r="AF23">
-        <v>-5.5200881995006354E-5</v>
+        <v>4.7167846278260071E-4</v>
       </c>
       <c r="AG23">
-        <v>2.6955957791965262E-6</v>
+        <v>1.0995669824266912E-3</v>
       </c>
       <c r="AH23">
-        <v>4.4072758604101771E-5</v>
+        <v>1.1670659690562407E-3</v>
       </c>
       <c r="AI23">
-        <v>4.7267867859671775E-4</v>
+        <v>-4.0023519254057157E-5</v>
       </c>
       <c r="AJ23">
-        <v>1.1040403878310912E-3</v>
+        <v>-1.3790465488396509E-4</v>
       </c>
       <c r="AK23">
-        <v>1.0375629922608097E-3</v>
+        <v>-2.0639526779680107E-4</v>
       </c>
       <c r="AL23">
-        <v>-7.226130790821822E-4</v>
+        <v>-2.0428646664533883E-4</v>
+      </c>
+      <c r="AM23">
+        <v>-1.2203502691173645E-4</v>
+      </c>
+      <c r="AN23">
+        <v>-5.5519241835815317E-4</v>
+      </c>
+      <c r="AO23">
+        <v>-3.0260295184230237E-4</v>
+      </c>
+      <c r="AP23">
+        <v>-4.3355922614210464E-4</v>
+      </c>
+      <c r="AQ23">
+        <v>-4.9168352594055557E-4</v>
+      </c>
+      <c r="AR23">
+        <v>-4.9571584320549141E-4</v>
+      </c>
+      <c r="AS23">
+        <v>-9.0969961137177258E-4</v>
+      </c>
+      <c r="AT23">
+        <v>-7.2904947513073148E-4</v>
+      </c>
+      <c r="AU23">
+        <v>-1.4574350763654972E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24">
-        <v>3.018930546027087E-2</v>
+        <v>2.5956919128491584E-2</v>
       </c>
       <c r="C24">
-        <v>1.1808498675604704E-3</v>
+        <v>1.1704798638986812E-3</v>
       </c>
       <c r="D24">
-        <v>1.5407145857511883E-4</v>
+        <v>1.5990936557895802E-4</v>
       </c>
       <c r="E24">
-        <v>-2.3205239619852815E-6</v>
+        <v>-2.3959578918805207E-6</v>
       </c>
       <c r="F24">
-        <v>2.5905925079753452E-6</v>
+        <v>4.152174774520362E-6</v>
       </c>
       <c r="G24">
-        <v>-3.0170639728523384E-6</v>
+        <v>-2.6690302979215298E-6</v>
       </c>
       <c r="H24">
-        <v>-8.3808408624042583E-5</v>
+        <v>-8.5882310251763315E-5</v>
       </c>
       <c r="I24">
-        <v>1.6872118467352391E-4</v>
+        <v>1.3850348755038E-4</v>
       </c>
       <c r="J24">
-        <v>-9.697572426541211E-4</v>
+        <v>-1.0186047159472193E-3</v>
       </c>
       <c r="K24">
-        <v>2.3334799207485679E-4</v>
+        <v>6.1968292330410801E-5</v>
       </c>
       <c r="L24">
-        <v>2.4227837182292855E-4</v>
+        <v>-1.9839076935754491E-5</v>
       </c>
       <c r="M24">
-        <v>2.429153031594863E-4</v>
+        <v>2.3929086946701772E-5</v>
       </c>
       <c r="N24">
-        <v>3.8972067752932299E-5</v>
+        <v>-2.1261428387516233E-4</v>
       </c>
       <c r="O24">
-        <v>-1.6015725900731063E-4</v>
+        <v>-1.6366089785843163E-4</v>
       </c>
       <c r="P24">
-        <v>-3.5527551726629803E-5</v>
+        <v>-3.7468656616220185E-5</v>
       </c>
       <c r="Q24">
-        <v>-1.1483252342324861E-4</v>
+        <v>-1.3966910239060644E-4</v>
       </c>
       <c r="R24">
-        <v>1.3822003228968703E-4</v>
+        <v>1.7256337651403776E-4</v>
       </c>
       <c r="S24">
-        <v>-3.9417604131501693E-5</v>
+        <v>-3.3841226299177751E-5</v>
       </c>
       <c r="T24">
-        <v>1.7193831475931362E-4</v>
+        <v>8.0830017261401019E-5</v>
       </c>
       <c r="U24">
-        <v>1.8218355247612106E-3</v>
+        <v>1.8040548963349631E-3</v>
       </c>
       <c r="V24">
-        <v>1.782955011217812E-3</v>
+        <v>1.7695313690283174E-3</v>
       </c>
       <c r="W24">
-        <v>1.8283368597180748E-3</v>
+        <v>1.804104188789193E-3</v>
       </c>
       <c r="X24">
-        <v>1.7762694242612596E-3</v>
+        <v>1.7646358826804106E-3</v>
       </c>
       <c r="Y24">
-        <v>3.2543184264771231E-3</v>
+        <v>3.2014534023821761E-3</v>
       </c>
       <c r="Z24">
-        <v>1.9806291009456596E-3</v>
+        <v>2.0374065388089665E-3</v>
       </c>
       <c r="AA24">
-        <v>1.8122559693235856E-3</v>
+        <v>1.7991998334723101E-3</v>
       </c>
       <c r="AB24">
-        <v>1.8619094128234255E-3</v>
+        <v>1.8469141380985643E-3</v>
       </c>
       <c r="AC24">
-        <v>1.850184178547674E-3</v>
+        <v>1.8388440800716247E-3</v>
       </c>
       <c r="AD24">
-        <v>1.8025160185180581E-3</v>
+        <v>1.777623871341648E-3</v>
       </c>
       <c r="AE24">
-        <v>1.8484412143911853E-3</v>
+        <v>1.8493788822386058E-3</v>
       </c>
       <c r="AF24">
-        <v>-5.3642192370963064E-5</v>
+        <v>3.7430464332883741E-4</v>
       </c>
       <c r="AG24">
-        <v>4.2592642428493799E-5</v>
+        <v>1.0564705258027435E-3</v>
       </c>
       <c r="AH24">
-        <v>-8.401888011996849E-5</v>
+        <v>1.2990777626314884E-3</v>
       </c>
       <c r="AI24">
-        <v>3.7477679368164011E-4</v>
+        <v>-3.2386604695445434E-5</v>
       </c>
       <c r="AJ24">
-        <v>1.0646149767165279E-3</v>
+        <v>-7.5726175257987728E-5</v>
       </c>
       <c r="AK24">
-        <v>1.1939845923663209E-3</v>
+        <v>-1.8932627099346711E-4</v>
       </c>
       <c r="AL24">
-        <v>-1.2135758395987839E-3</v>
+        <v>-8.9944113438987917E-5</v>
+      </c>
+      <c r="AM24">
+        <v>-1.3073068847459896E-4</v>
+      </c>
+      <c r="AN24">
+        <v>-4.8471743416625759E-4</v>
+      </c>
+      <c r="AO24">
+        <v>-2.9008563550688956E-4</v>
+      </c>
+      <c r="AP24">
+        <v>-4.4846861395478853E-4</v>
+      </c>
+      <c r="AQ24">
+        <v>-3.8567967773249804E-4</v>
+      </c>
+      <c r="AR24">
+        <v>-5.5869472581503632E-4</v>
+      </c>
+      <c r="AS24">
+        <v>-7.48719624499951E-4</v>
+      </c>
+      <c r="AT24">
+        <v>-6.2662803021042417E-4</v>
+      </c>
+      <c r="AU24">
+        <v>-2.1364607358226317E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
       <c r="B25">
-        <v>0.13592302876403042</v>
+        <v>0.13539154630023056</v>
       </c>
       <c r="C25">
-        <v>7.4247671277029737E-4</v>
+        <v>3.0977700081253126E-4</v>
       </c>
       <c r="D25">
-        <v>2.259556551210181E-4</v>
+        <v>2.3333750365392859E-4</v>
       </c>
       <c r="E25">
-        <v>-3.6011796830267802E-6</v>
+        <v>-3.6629162700659441E-6</v>
       </c>
       <c r="F25">
-        <v>9.3593891896448023E-6</v>
+        <v>1.2775487888316958E-5</v>
       </c>
       <c r="G25">
-        <v>-1.5015801289762255E-5</v>
+        <v>-1.5884645149613988E-5</v>
       </c>
       <c r="H25">
-        <v>5.7397957415506156E-4</v>
+        <v>6.1041590193664213E-4</v>
       </c>
       <c r="I25">
-        <v>2.7017764597488288E-4</v>
+        <v>2.4830437195354172E-4</v>
       </c>
       <c r="J25">
-        <v>-7.0117169484747134E-4</v>
+        <v>-2.6712375145992269E-4</v>
       </c>
       <c r="K25">
-        <v>4.5710208142066928E-4</v>
+        <v>3.0310185452071944E-4</v>
       </c>
       <c r="L25">
-        <v>6.7535015399344421E-4</v>
+        <v>4.0229875352584344E-4</v>
       </c>
       <c r="M25">
-        <v>1.2783127283579694E-3</v>
+        <v>1.1051113998619632E-3</v>
       </c>
       <c r="N25">
-        <v>4.366983539967049E-4</v>
+        <v>1.597332734002579E-4</v>
       </c>
       <c r="O25">
-        <v>-7.3363439001952854E-5</v>
+        <v>-6.935591291789688E-5</v>
       </c>
       <c r="P25">
-        <v>-1.3263381910058527E-4</v>
+        <v>-1.782539898621197E-4</v>
       </c>
       <c r="Q25">
-        <v>7.3650882546151043E-5</v>
+        <v>-2.4501215264448426E-5</v>
       </c>
       <c r="R25">
-        <v>5.4142873525537009E-4</v>
+        <v>6.3443915418618974E-4</v>
       </c>
       <c r="S25">
-        <v>-1.7316322947060273E-4</v>
+        <v>-2.4394949117701684E-4</v>
       </c>
       <c r="T25">
-        <v>2.5970262285962857E-4</v>
+        <v>1.5334066420524253E-4</v>
       </c>
       <c r="U25">
-        <v>2.2275628201659341E-3</v>
+        <v>2.2845257641886177E-3</v>
       </c>
       <c r="V25">
-        <v>2.0644669881111416E-3</v>
+        <v>2.1308345756094966E-3</v>
       </c>
       <c r="W25">
-        <v>2.2383163748330055E-3</v>
+        <v>2.2741214480275968E-3</v>
       </c>
       <c r="X25">
-        <v>1.9881072086810839E-3</v>
+        <v>2.050020095753433E-3</v>
       </c>
       <c r="Y25">
-        <v>1.9806291009456596E-3</v>
+        <v>2.0374065388089665E-3</v>
       </c>
       <c r="Z25">
-        <v>4.8135226276238181E-3</v>
+        <v>4.9805142950022111E-3</v>
       </c>
       <c r="AA25">
-        <v>2.0564349075441529E-3</v>
+        <v>2.0899122320725072E-3</v>
       </c>
       <c r="AB25">
-        <v>2.2542763621640448E-3</v>
+        <v>2.3157111939564406E-3</v>
       </c>
       <c r="AC25">
-        <v>2.1638738051560397E-3</v>
+        <v>2.2150016957733802E-3</v>
       </c>
       <c r="AD25">
-        <v>2.0481966209711698E-3</v>
+        <v>2.0618504534151323E-3</v>
       </c>
       <c r="AE25">
-        <v>2.0831186283410993E-3</v>
+        <v>2.2578114457343082E-3</v>
       </c>
       <c r="AF25">
-        <v>-1.4093580619647489E-4</v>
+        <v>3.9961846891592922E-4</v>
       </c>
       <c r="AG25">
-        <v>-7.4248406366680996E-4</v>
+        <v>7.6110835093249664E-4</v>
       </c>
       <c r="AH25">
-        <v>-6.6130374815320759E-4</v>
+        <v>5.7451380598246907E-3</v>
       </c>
       <c r="AI25">
-        <v>5.334691063070547E-4</v>
+        <v>6.145432030138547E-5</v>
       </c>
       <c r="AJ25">
-        <v>8.1997913473877686E-4</v>
+        <v>-6.3132692777074335E-4</v>
       </c>
       <c r="AK25">
-        <v>5.4141513711097704E-3</v>
+        <v>-7.7921659729108194E-4</v>
       </c>
       <c r="AL25">
-        <v>6.0709668385634432E-3</v>
+        <v>-7.55944378909713E-4</v>
+      </c>
+      <c r="AM25">
+        <v>-7.6265337286278542E-4</v>
+      </c>
+      <c r="AN25">
+        <v>-1.5015550189061565E-3</v>
+      </c>
+      <c r="AO25">
+        <v>-1.8002273384082877E-3</v>
+      </c>
+      <c r="AP25">
+        <v>-2.1483748786743887E-3</v>
+      </c>
+      <c r="AQ25">
+        <v>-2.9099270654457084E-3</v>
+      </c>
+      <c r="AR25">
+        <v>-2.9105284915857477E-3</v>
+      </c>
+      <c r="AS25">
+        <v>-3.6017276791085774E-3</v>
+      </c>
+      <c r="AT25">
+        <v>-3.7268648001447038E-3</v>
+      </c>
+      <c r="AU25">
+        <v>8.9958657276790581E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
       <c r="B26">
-        <v>3.0955094135511951E-2</v>
+        <v>2.7490106370601744E-2</v>
       </c>
       <c r="C26">
-        <v>-4.9765183271509631E-5</v>
+        <v>-2.3168052236172273E-4</v>
       </c>
       <c r="D26">
-        <v>1.4802843819413443E-4</v>
+        <v>1.4710683324064471E-4</v>
       </c>
       <c r="E26">
-        <v>-2.2484883685931817E-6</v>
+        <v>-2.2085897662705473E-6</v>
       </c>
       <c r="F26">
-        <v>-3.2226068100530355E-7</v>
+        <v>6.6418248115305166E-7</v>
       </c>
       <c r="G26">
-        <v>-4.6052025874814753E-6</v>
+        <v>-4.9081711568488192E-6</v>
       </c>
       <c r="H26">
-        <v>-3.6570262537853973E-4</v>
+        <v>-4.0838823613900948E-4</v>
       </c>
       <c r="I26">
-        <v>4.9201389291589771E-4</v>
+        <v>5.1515515074394911E-4</v>
       </c>
       <c r="J26">
-        <v>1.7062760662318806E-4</v>
+        <v>3.4328163838019861E-4</v>
       </c>
       <c r="K26">
-        <v>2.6603606550988233E-4</v>
+        <v>1.2360263150523995E-4</v>
       </c>
       <c r="L26">
-        <v>2.8649995437703504E-4</v>
+        <v>5.28478673144364E-5</v>
       </c>
       <c r="M26">
-        <v>2.9476491666278245E-4</v>
+        <v>1.8465144935246502E-4</v>
       </c>
       <c r="N26">
-        <v>1.3209274138706849E-4</v>
+        <v>-4.9206750242215733E-5</v>
       </c>
       <c r="O26">
-        <v>-1.5368392756940065E-4</v>
+        <v>-1.5072007102519809E-4</v>
       </c>
       <c r="P26">
-        <v>-3.2969459477362844E-5</v>
+        <v>-3.5217254681591116E-5</v>
       </c>
       <c r="Q26">
-        <v>-9.1174832405318805E-5</v>
+        <v>-1.3973866636855751E-4</v>
       </c>
       <c r="R26">
-        <v>4.1169310045427237E-5</v>
+        <v>7.092254184415976E-5</v>
       </c>
       <c r="S26">
-        <v>-6.7060874585868108E-5</v>
+        <v>-7.1943486689014067E-5</v>
       </c>
       <c r="T26">
-        <v>1.1922635542131398E-4</v>
+        <v>5.9874234150736611E-5</v>
       </c>
       <c r="U26">
-        <v>1.8998891386364958E-3</v>
+        <v>1.8920863153112052E-3</v>
       </c>
       <c r="V26">
-        <v>1.8361811837960412E-3</v>
+        <v>1.8307813351931951E-3</v>
       </c>
       <c r="W26">
-        <v>1.8868885036266024E-3</v>
+        <v>1.866837593237227E-3</v>
       </c>
       <c r="X26">
-        <v>1.8276990663665615E-3</v>
+        <v>1.8237929699404718E-3</v>
       </c>
       <c r="Y26">
-        <v>1.8122559693235856E-3</v>
+        <v>1.7991998334723101E-3</v>
       </c>
       <c r="Z26">
-        <v>2.0564349075441529E-3</v>
+        <v>2.0899122320725072E-3</v>
       </c>
       <c r="AA26">
-        <v>2.9316603558258957E-3</v>
+        <v>2.9216007110105849E-3</v>
       </c>
       <c r="AB26">
-        <v>1.9215979904241541E-3</v>
+        <v>1.9100150464710897E-3</v>
       </c>
       <c r="AC26">
-        <v>1.9032699298811395E-3</v>
+        <v>1.9005510562313441E-3</v>
       </c>
       <c r="AD26">
-        <v>1.856816853619405E-3</v>
+        <v>1.8327750947213441E-3</v>
       </c>
       <c r="AE26">
-        <v>1.9024711633172046E-3</v>
+        <v>1.9299375546956766E-3</v>
       </c>
       <c r="AF26">
-        <v>-6.7493599942603096E-5</v>
+        <v>4.1993126454157974E-4</v>
       </c>
       <c r="AG26">
-        <v>-2.3430696383188137E-4</v>
+        <v>1.5005502043031051E-3</v>
       </c>
       <c r="AH26">
-        <v>-1.2716359259362122E-4</v>
+        <v>1.227058125451509E-3</v>
       </c>
       <c r="AI26">
-        <v>4.4374869259857012E-4</v>
+        <v>-4.2796603876276568E-6</v>
       </c>
       <c r="AJ26">
-        <v>1.4488374129706801E-3</v>
+        <v>-1.8704219703104372E-4</v>
       </c>
       <c r="AK26">
-        <v>1.1867053760042101E-3</v>
+        <v>-2.6031000019997516E-4</v>
       </c>
       <c r="AL26">
-        <v>9.0587102558815739E-4</v>
+        <v>-2.2916673300355818E-4</v>
+      </c>
+      <c r="AM26">
+        <v>-1.90036299966651E-4</v>
+      </c>
+      <c r="AN26">
+        <v>-6.898535800335451E-4</v>
+      </c>
+      <c r="AO26">
+        <v>-4.9255068508111339E-4</v>
+      </c>
+      <c r="AP26">
+        <v>-7.0352486394762576E-4</v>
+      </c>
+      <c r="AQ26">
+        <v>-9.2847434895327284E-4</v>
+      </c>
+      <c r="AR26">
+        <v>-8.7196504810442815E-4</v>
+      </c>
+      <c r="AS26">
+        <v>-1.1093085344636398E-3</v>
+      </c>
+      <c r="AT26">
+        <v>-1.1802094484395934E-3</v>
+      </c>
+      <c r="AU26">
+        <v>6.0030815431863158E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>39</v>
       </c>
       <c r="B27">
-        <v>6.3516342594651554E-2</v>
+        <v>6.2887667768475555E-2</v>
       </c>
       <c r="C27">
-        <v>2.4825774097442439E-4</v>
+        <v>1.1083057383660315E-4</v>
       </c>
       <c r="D27">
-        <v>1.5896817758003585E-4</v>
+        <v>1.6248664741998144E-4</v>
       </c>
       <c r="E27">
-        <v>-2.444515472902585E-6</v>
+        <v>-2.4888690582538551E-6</v>
       </c>
       <c r="F27">
-        <v>2.933929736608103E-6</v>
+        <v>4.4523577941857526E-6</v>
       </c>
       <c r="G27">
-        <v>-4.3000086553069987E-6</v>
+        <v>-4.4849332679971133E-6</v>
       </c>
       <c r="H27">
-        <v>2.7440817027310954E-5</v>
+        <v>3.2292026343024572E-5</v>
       </c>
       <c r="I27">
-        <v>1.9517263947546284E-4</v>
+        <v>1.7434438347362606E-4</v>
       </c>
       <c r="J27">
-        <v>-4.2985306358092861E-5</v>
+        <v>6.5252524664925212E-5</v>
       </c>
       <c r="K27">
-        <v>2.2383866395621094E-4</v>
+        <v>8.2964096729517029E-5</v>
       </c>
       <c r="L27">
-        <v>2.8231829718151664E-4</v>
+        <v>5.980712799096113E-5</v>
       </c>
       <c r="M27">
-        <v>3.8416753022632935E-4</v>
+        <v>2.0804022258710144E-4</v>
       </c>
       <c r="N27">
-        <v>1.2037379874075784E-4</v>
+        <v>-7.4648949533822725E-5</v>
       </c>
       <c r="O27">
-        <v>-1.4124830392842655E-4</v>
+        <v>-1.3635777955985076E-4</v>
       </c>
       <c r="P27">
-        <v>-2.2895654394294344E-5</v>
+        <v>-3.702918054220624E-5</v>
       </c>
       <c r="Q27">
-        <v>-5.9829093505551391E-5</v>
+        <v>-9.0249479485285768E-5</v>
       </c>
       <c r="R27">
-        <v>2.0325523126090919E-4</v>
+        <v>2.3911329826071834E-4</v>
       </c>
       <c r="S27">
-        <v>-6.8202614579487841E-5</v>
+        <v>-6.7323716341837159E-5</v>
       </c>
       <c r="T27">
-        <v>1.8972155858813225E-4</v>
+        <v>1.1636690049373834E-4</v>
       </c>
       <c r="U27">
-        <v>1.9630295266209875E-3</v>
+        <v>1.9477809784958805E-3</v>
       </c>
       <c r="V27">
-        <v>1.8992719755830723E-3</v>
+        <v>1.8897212411745157E-3</v>
       </c>
       <c r="W27">
-        <v>1.9707676792196102E-3</v>
+        <v>1.9475253185488866E-3</v>
       </c>
       <c r="X27">
-        <v>1.8774178622319483E-3</v>
+        <v>1.8678918029877577E-3</v>
       </c>
       <c r="Y27">
-        <v>1.8619094128234255E-3</v>
+        <v>1.8469141380985643E-3</v>
       </c>
       <c r="Z27">
-        <v>2.2542763621640448E-3</v>
+        <v>2.3157111939564406E-3</v>
       </c>
       <c r="AA27">
-        <v>1.9215979904241541E-3</v>
+        <v>1.9100150464710897E-3</v>
       </c>
       <c r="AB27">
-        <v>3.3667304503532947E-3</v>
+        <v>3.3553177752240321E-3</v>
       </c>
       <c r="AC27">
-        <v>1.9885443892528913E-3</v>
+        <v>1.9775676620438732E-3</v>
       </c>
       <c r="AD27">
-        <v>1.9480045299527665E-3</v>
+        <v>1.9178385732668919E-3</v>
       </c>
       <c r="AE27">
-        <v>1.9653605530497759E-3</v>
+        <v>1.9884181431445939E-3</v>
       </c>
       <c r="AF27">
-        <v>-7.7202226925622238E-5</v>
+        <v>5.8562129410566716E-4</v>
       </c>
       <c r="AG27">
-        <v>-1.5488015027715718E-4</v>
+        <v>1.1722058559822783E-3</v>
       </c>
       <c r="AH27">
-        <v>-5.8781373411021388E-5</v>
+        <v>1.994399682510405E-3</v>
       </c>
       <c r="AI27">
-        <v>6.1783562397735206E-4</v>
+        <v>-3.3695457723128695E-5</v>
       </c>
       <c r="AJ27">
-        <v>1.1859839618537532E-3</v>
+        <v>-2.0591250652386402E-4</v>
       </c>
       <c r="AK27">
-        <v>1.862279970772633E-3</v>
+        <v>-2.741766309370152E-4</v>
       </c>
       <c r="AL27">
-        <v>5.7668590562836609E-4</v>
+        <v>-2.4309541846563685E-4</v>
+      </c>
+      <c r="AM27">
+        <v>-1.9128014305446069E-4</v>
+      </c>
+      <c r="AN27">
+        <v>-7.1768277991378815E-4</v>
+      </c>
+      <c r="AO27">
+        <v>-5.7004555191601802E-4</v>
+      </c>
+      <c r="AP27">
+        <v>-7.1900446572537979E-4</v>
+      </c>
+      <c r="AQ27">
+        <v>-8.7438373012052855E-4</v>
+      </c>
+      <c r="AR27">
+        <v>-8.5941822666952758E-4</v>
+      </c>
+      <c r="AS27">
+        <v>-1.2554051312959761E-3</v>
+      </c>
+      <c r="AT27">
+        <v>-1.1123738430084363E-3</v>
+      </c>
+      <c r="AU27">
+        <v>-2.6724290588908337E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
       <c r="B28">
-        <v>7.5263932554714141E-2</v>
+        <v>7.5876160494193115E-2</v>
       </c>
       <c r="C28">
-        <v>5.2745291080845348E-4</v>
+        <v>4.2859504367466473E-4</v>
       </c>
       <c r="D28">
-        <v>1.893873104706718E-4</v>
+        <v>1.8920973522796572E-4</v>
       </c>
       <c r="E28">
-        <v>-2.8541760923217105E-6</v>
+        <v>-2.8396197687050266E-6</v>
       </c>
       <c r="F28">
-        <v>3.8554528048439566E-6</v>
+        <v>5.4354416787044539E-6</v>
       </c>
       <c r="G28">
-        <v>-8.5616003693075622E-6</v>
+        <v>-8.0056641666897195E-6</v>
       </c>
       <c r="H28">
-        <v>1.0469873139276317E-4</v>
+        <v>1.2062988412385768E-4</v>
       </c>
       <c r="I28">
-        <v>2.8919674123564082E-4</v>
+        <v>2.0695842207000008E-4</v>
       </c>
       <c r="J28">
-        <v>-2.6858003947689379E-4</v>
+        <v>-2.0554707821432059E-4</v>
       </c>
       <c r="K28">
-        <v>2.6738044630313876E-4</v>
+        <v>6.2293615772855606E-5</v>
       </c>
       <c r="L28">
-        <v>5.6550515479090004E-4</v>
+        <v>2.5206395908443173E-4</v>
       </c>
       <c r="M28">
-        <v>5.2715607285883385E-4</v>
+        <v>2.5890209672722821E-4</v>
       </c>
       <c r="N28">
-        <v>2.7534866816342489E-4</v>
+        <v>-2.2691468805456007E-5</v>
       </c>
       <c r="O28">
-        <v>-7.4790375693594216E-5</v>
+        <v>-8.2491700594445163E-5</v>
       </c>
       <c r="P28">
-        <v>-1.2545451693361795E-4</v>
+        <v>-1.2855757985712156E-4</v>
       </c>
       <c r="Q28">
-        <v>-6.3944817539409051E-5</v>
+        <v>-9.4672787049431098E-5</v>
       </c>
       <c r="R28">
-        <v>3.1865545823334021E-4</v>
+        <v>3.6189080419627914E-4</v>
       </c>
       <c r="S28">
-        <v>-1.010634633340046E-4</v>
+        <v>-6.2272408511824617E-5</v>
       </c>
       <c r="T28">
-        <v>1.4552762293012069E-4</v>
+        <v>4.256635529366844E-5</v>
       </c>
       <c r="U28">
-        <v>1.9464228286575627E-3</v>
+        <v>1.928583003832811E-3</v>
       </c>
       <c r="V28">
-        <v>1.8811358344825223E-3</v>
+        <v>1.8605600858381554E-3</v>
       </c>
       <c r="W28">
-        <v>1.965770522141053E-3</v>
+        <v>1.9408720198035127E-3</v>
       </c>
       <c r="X28">
-        <v>1.8769145228621185E-3</v>
+        <v>1.866348791835577E-3</v>
       </c>
       <c r="Y28">
-        <v>1.850184178547674E-3</v>
+        <v>1.8388440800716247E-3</v>
       </c>
       <c r="Z28">
-        <v>2.1638738051560397E-3</v>
+        <v>2.2150016957733802E-3</v>
       </c>
       <c r="AA28">
-        <v>1.9032699298811395E-3</v>
+        <v>1.9005510562313441E-3</v>
       </c>
       <c r="AB28">
-        <v>1.9885443892528913E-3</v>
+        <v>1.9775676620438732E-3</v>
       </c>
       <c r="AC28">
-        <v>4.1675337375369518E-3</v>
+        <v>4.1231586569919019E-3</v>
       </c>
       <c r="AD28">
-        <v>1.9169977512163792E-3</v>
+        <v>1.8759040144978884E-3</v>
       </c>
       <c r="AE28">
-        <v>1.9591852787436935E-3</v>
+        <v>1.9642899285810143E-3</v>
       </c>
       <c r="AF28">
-        <v>-1.0695497798035567E-4</v>
+        <v>5.6020976520217679E-4</v>
       </c>
       <c r="AG28">
-        <v>-2.4700683277729127E-4</v>
+        <v>1.1363961173158229E-3</v>
       </c>
       <c r="AH28">
-        <v>-2.338641137896052E-4</v>
+        <v>1.6473841316092756E-3</v>
       </c>
       <c r="AI28">
-        <v>5.7884200575148131E-4</v>
+        <v>2.0261670741997142E-6</v>
       </c>
       <c r="AJ28">
-        <v>1.1448334830974536E-3</v>
+        <v>-1.831665071103019E-4</v>
       </c>
       <c r="AK28">
-        <v>1.5714534724323055E-3</v>
+        <v>-2.5512360444014453E-4</v>
       </c>
       <c r="AL28">
-        <v>2.39158432356305E-3</v>
+        <v>-2.405842450373814E-4</v>
+      </c>
+      <c r="AM28">
+        <v>-1.8247928078676627E-4</v>
+      </c>
+      <c r="AN28">
+        <v>-6.9786796141080407E-4</v>
+      </c>
+      <c r="AO28">
+        <v>-5.3211042630958586E-4</v>
+      </c>
+      <c r="AP28">
+        <v>-6.9552216556233778E-4</v>
+      </c>
+      <c r="AQ28">
+        <v>-8.1096702567763201E-4</v>
+      </c>
+      <c r="AR28">
+        <v>-9.1866655652736006E-4</v>
+      </c>
+      <c r="AS28">
+        <v>-1.22690153279853E-3</v>
+      </c>
+      <c r="AT28">
+        <v>-5.4983778432068659E-4</v>
+      </c>
+      <c r="AU28">
+        <v>-1.1020223973797101E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>41</v>
       </c>
       <c r="B29">
-        <v>-6.6728772307127942E-3</v>
+        <v>-8.0013095061161003E-3</v>
       </c>
       <c r="C29">
-        <v>-1.7026087981654719E-4</v>
+        <v>-3.0515108315302524E-4</v>
       </c>
       <c r="D29">
-        <v>1.32615399178658E-4</v>
+        <v>1.3590899109925384E-4</v>
       </c>
       <c r="E29">
-        <v>-2.2235583409769943E-6</v>
+        <v>-2.2782035001266128E-6</v>
       </c>
       <c r="F29">
-        <v>-2.415809021071694E-6</v>
+        <v>-1.0036698328465053E-6</v>
       </c>
       <c r="G29">
-        <v>-5.7311705649340298E-6</v>
+        <v>-5.5079077665563853E-6</v>
       </c>
       <c r="H29">
-        <v>-7.4956962011894378E-4</v>
+        <v>-6.6379358501457593E-4</v>
       </c>
       <c r="I29">
-        <v>7.8384503772815169E-4</v>
+        <v>6.3113848644205065E-4</v>
       </c>
       <c r="J29">
-        <v>2.6394694738619904E-4</v>
+        <v>3.4344748464618254E-4</v>
       </c>
       <c r="K29">
-        <v>1.2251050196845269E-4</v>
+        <v>-1.08724140801997E-4</v>
       </c>
       <c r="L29">
-        <v>1.9578221947756739E-4</v>
+        <v>-8.6910246014952326E-5</v>
       </c>
       <c r="M29">
-        <v>4.448831451388941E-4</v>
+        <v>1.8519599141990313E-4</v>
       </c>
       <c r="N29">
-        <v>1.7012385417653178E-4</v>
+        <v>-1.0850377633825299E-4</v>
       </c>
       <c r="O29">
-        <v>-6.1249570158942041E-5</v>
+        <v>-4.2461438463185246E-5</v>
       </c>
       <c r="P29">
-        <v>-1.0364208742550753E-4</v>
+        <v>-1.4396753953512328E-4</v>
       </c>
       <c r="Q29">
-        <v>-9.6870081066907309E-5</v>
+        <v>-1.4888204729556121E-4</v>
       </c>
       <c r="R29">
-        <v>2.8577178219182855E-5</v>
+        <v>6.604002278490482E-5</v>
       </c>
       <c r="S29">
-        <v>-8.8252890970888682E-5</v>
+        <v>-7.6215484571437312E-5</v>
       </c>
       <c r="T29">
-        <v>1.9141987622453994E-4</v>
+        <v>1.1766376478074977E-4</v>
       </c>
       <c r="U29">
-        <v>1.9233599925610326E-3</v>
+        <v>1.8850066000003034E-3</v>
       </c>
       <c r="V29">
-        <v>1.8440763326476764E-3</v>
+        <v>1.8140542848835981E-3</v>
       </c>
       <c r="W29">
-        <v>1.9024252576710921E-3</v>
+        <v>1.8559956197155764E-3</v>
       </c>
       <c r="X29">
-        <v>1.8174325194119526E-3</v>
+        <v>1.7969400457006823E-3</v>
       </c>
       <c r="Y29">
-        <v>1.8025160185180581E-3</v>
+        <v>1.777623871341648E-3</v>
       </c>
       <c r="Z29">
-        <v>2.0481966209711698E-3</v>
+        <v>2.0618504534151323E-3</v>
       </c>
       <c r="AA29">
-        <v>1.856816853619405E-3</v>
+        <v>1.8327750947213441E-3</v>
       </c>
       <c r="AB29">
-        <v>1.9480045299527665E-3</v>
+        <v>1.9178385732668919E-3</v>
       </c>
       <c r="AC29">
-        <v>1.9169977512163792E-3</v>
+        <v>1.8759040144978884E-3</v>
       </c>
       <c r="AD29">
-        <v>3.9019964433098827E-3</v>
+        <v>3.8794770187897264E-3</v>
       </c>
       <c r="AE29">
-        <v>1.9211273540793716E-3</v>
+        <v>1.9259240629881937E-3</v>
       </c>
       <c r="AF29">
-        <v>-8.7829298093057659E-5</v>
+        <v>5.1296141256009734E-4</v>
       </c>
       <c r="AG29">
-        <v>-2.4594542165654542E-4</v>
+        <v>1.1785385835360795E-3</v>
       </c>
       <c r="AH29">
-        <v>-9.1699161903381317E-5</v>
+        <v>1.918700779292494E-3</v>
       </c>
       <c r="AI29">
-        <v>5.5911280825299715E-4</v>
+        <v>-3.7548381374824286E-5</v>
       </c>
       <c r="AJ29">
-        <v>1.2034185227086307E-3</v>
+        <v>-2.5132371931357975E-4</v>
       </c>
       <c r="AK29">
-        <v>2.0062384480775556E-3</v>
+        <v>-3.1509568979258898E-4</v>
       </c>
       <c r="AL29">
-        <v>2.9904667246059887E-3</v>
+        <v>-2.776299492114919E-4</v>
+      </c>
+      <c r="AM29">
+        <v>-2.5042824782719629E-4</v>
+      </c>
+      <c r="AN29">
+        <v>-7.2337417903350345E-4</v>
+      </c>
+      <c r="AO29">
+        <v>-5.9497219909908708E-4</v>
+      </c>
+      <c r="AP29">
+        <v>-7.6630375265618464E-4</v>
+      </c>
+      <c r="AQ29">
+        <v>-9.647635663437024E-4</v>
+      </c>
+      <c r="AR29">
+        <v>-8.8412400452546509E-4</v>
+      </c>
+      <c r="AS29">
+        <v>-1.3907166561169734E-3</v>
+      </c>
+      <c r="AT29">
+        <v>-9.3255600321319031E-4</v>
+      </c>
+      <c r="AU29">
+        <v>1.4417730007639275E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
       <c r="B30">
-        <v>0.16642521238694868</v>
+        <v>0.15749407277528707</v>
       </c>
       <c r="C30">
-        <v>2.9161731110436805E-4</v>
+        <v>2.7577093877088291E-4</v>
       </c>
       <c r="D30">
-        <v>1.4098724052648021E-4</v>
+        <v>1.4480737597476288E-4</v>
       </c>
       <c r="E30">
-        <v>-2.1947200263740539E-6</v>
+        <v>-2.248727378350405E-6</v>
       </c>
       <c r="F30">
-        <v>7.7629029585715725E-7</v>
+        <v>2.4609921991839383E-6</v>
       </c>
       <c r="G30">
-        <v>-4.4975271888920363E-6</v>
+        <v>-5.7421973717640336E-6</v>
       </c>
       <c r="H30">
-        <v>-1.1734055070874182E-4</v>
+        <v>-8.6658756004176236E-5</v>
       </c>
       <c r="I30">
-        <v>1.3665156364574445E-4</v>
+        <v>1.303673320766452E-4</v>
       </c>
       <c r="J30">
-        <v>-1.073128013379111E-4</v>
+        <v>-1.2591936478939731E-4</v>
       </c>
       <c r="K30">
-        <v>3.5041205824387937E-4</v>
+        <v>2.3655596144819002E-4</v>
       </c>
       <c r="L30">
-        <v>3.7615268189726894E-4</v>
+        <v>1.3601764012944782E-4</v>
       </c>
       <c r="M30">
-        <v>4.3462663560270103E-4</v>
+        <v>3.1652083765556539E-4</v>
       </c>
       <c r="N30">
-        <v>2.9528335472843274E-4</v>
+        <v>8.8460187235087599E-5</v>
       </c>
       <c r="O30">
-        <v>-1.8085411692275293E-4</v>
+        <v>-1.8141992305822734E-4</v>
       </c>
       <c r="P30">
-        <v>-6.514157267702343E-5</v>
+        <v>-8.196439007572231E-5</v>
       </c>
       <c r="Q30">
-        <v>-2.0547518966914247E-4</v>
+        <v>-2.4081160121491532E-4</v>
       </c>
       <c r="R30">
-        <v>8.0774329570172838E-5</v>
+        <v>1.5443206641331335E-4</v>
       </c>
       <c r="S30">
-        <v>-5.0869929795726784E-5</v>
+        <v>-7.5894190473031948E-5</v>
       </c>
       <c r="T30">
-        <v>2.3519481990508543E-4</v>
+        <v>1.5517820720287938E-4</v>
       </c>
       <c r="U30">
-        <v>1.9376800643951713E-3</v>
+        <v>1.9536564121836733E-3</v>
       </c>
       <c r="V30">
-        <v>1.8782525007587443E-3</v>
+        <v>1.8933636443939075E-3</v>
       </c>
       <c r="W30">
-        <v>1.9202388501367673E-3</v>
+        <v>1.932024964989839E-3</v>
       </c>
       <c r="X30">
-        <v>1.8722320475111842E-3</v>
+        <v>1.8816706633350282E-3</v>
       </c>
       <c r="Y30">
-        <v>1.8484412143911853E-3</v>
+        <v>1.8493788822386058E-3</v>
       </c>
       <c r="Z30">
-        <v>2.0831186283410993E-3</v>
+        <v>2.2578114457343082E-3</v>
       </c>
       <c r="AA30">
-        <v>1.9024711633172046E-3</v>
+        <v>1.9299375546956766E-3</v>
       </c>
       <c r="AB30">
-        <v>1.9653605530497759E-3</v>
+        <v>1.9884181431445939E-3</v>
       </c>
       <c r="AC30">
-        <v>1.9591852787436935E-3</v>
+        <v>1.9642899285810143E-3</v>
       </c>
       <c r="AD30">
-        <v>1.9211273540793716E-3</v>
+        <v>1.9259240629881937E-3</v>
       </c>
       <c r="AE30">
-        <v>3.9556954389940949E-3</v>
+        <v>4.0126989044665783E-3</v>
       </c>
       <c r="AF30">
-        <v>-6.4178530993556844E-5</v>
+        <v>6.0715579651648868E-4</v>
       </c>
       <c r="AG30">
-        <v>-9.9465801042176571E-5</v>
+        <v>1.3373328007359963E-3</v>
       </c>
       <c r="AH30">
-        <v>-1.460807525187798E-4</v>
+        <v>1.6607220972941531E-3</v>
       </c>
       <c r="AI30">
-        <v>6.172206033571748E-4</v>
+        <v>5.9062991052573176E-5</v>
       </c>
       <c r="AJ30">
-        <v>1.3315524693766337E-3</v>
+        <v>-1.2893405038363805E-4</v>
       </c>
       <c r="AK30">
-        <v>1.2190915682234716E-3</v>
+        <v>-2.0319132742537926E-4</v>
       </c>
       <c r="AL30">
-        <v>-1.3411422266633921E-4</v>
+        <v>-1.5440250820237438E-4</v>
+      </c>
+      <c r="AM30">
+        <v>-1.3027321429269636E-4</v>
+      </c>
+      <c r="AN30">
+        <v>-7.4978807089301123E-4</v>
+      </c>
+      <c r="AO30">
+        <v>-5.6114431154626076E-4</v>
+      </c>
+      <c r="AP30">
+        <v>-7.6722691928970575E-4</v>
+      </c>
+      <c r="AQ30">
+        <v>-9.1736563237758482E-4</v>
+      </c>
+      <c r="AR30">
+        <v>-1.0042041824657737E-3</v>
+      </c>
+      <c r="AS30">
+        <v>-1.2504727475739323E-3</v>
+      </c>
+      <c r="AT30">
+        <v>-1.369059009961671E-3</v>
+      </c>
+      <c r="AU30">
+        <v>7.2285586698124515E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>43</v>
       </c>
       <c r="B31">
-        <v>-1.8454351048976848E-2</v>
+        <v>-7.6484954451536954E-2</v>
       </c>
       <c r="C31">
-        <v>-8.0918402398451217E-5</v>
+        <v>-1.7086948375300958E-4</v>
       </c>
       <c r="D31">
-        <v>-6.5480369921827196E-6</v>
+        <v>4.2496548621341439E-6</v>
       </c>
       <c r="E31">
-        <v>1.0621507698816218E-7</v>
+        <v>-7.8341773549262298E-8</v>
       </c>
       <c r="F31">
-        <v>-4.9024836013137848E-7</v>
+        <v>1.4414291941447038E-6</v>
       </c>
       <c r="G31">
-        <v>1.6017039390630714E-6</v>
+        <v>-9.1622564767329906E-8</v>
       </c>
       <c r="H31">
-        <v>2.4685362986764417E-5</v>
+        <v>-8.2009075671355867E-5</v>
       </c>
       <c r="I31">
-        <v>-3.429748908508357E-5</v>
+        <v>4.6448424123054751E-5</v>
       </c>
       <c r="J31">
-        <v>7.9209862058215427E-5</v>
+        <v>-7.8786127680551096E-5</v>
       </c>
       <c r="K31">
-        <v>-5.3198390313247991E-5</v>
+        <v>-1.167880846125979E-4</v>
       </c>
       <c r="L31">
-        <v>-7.532249675688184E-5</v>
+        <v>-1.2084142332938956E-4</v>
       </c>
       <c r="M31">
-        <v>-8.0055629491404361E-5</v>
+        <v>-9.0767274057522017E-5</v>
       </c>
       <c r="N31">
-        <v>-2.5768063188203037E-5</v>
+        <v>-1.0389006373935481E-4</v>
       </c>
       <c r="O31">
-        <v>1.5986069526128001E-5</v>
+        <v>-1.1519956412483156E-4</v>
       </c>
       <c r="P31">
-        <v>2.6395041758708247E-5</v>
+        <v>8.4662705554258434E-5</v>
       </c>
       <c r="Q31">
-        <v>5.5217241106854903E-5</v>
+        <v>-1.8472502587747389E-4</v>
       </c>
       <c r="R31">
-        <v>-2.9181602343716386E-5</v>
+        <v>-1.1826501668490294E-4</v>
       </c>
       <c r="S31">
-        <v>1.4369995520663976E-4</v>
+        <v>1.6071097488305503E-5</v>
       </c>
       <c r="T31">
-        <v>-2.0020278928987788E-5</v>
+        <v>-1.1700696185898906E-4</v>
       </c>
       <c r="U31">
-        <v>-6.5243425858294441E-5</v>
+        <v>5.5222455131041966E-4</v>
       </c>
       <c r="V31">
-        <v>-7.7848699895063703E-5</v>
+        <v>4.5822649062025563E-4</v>
       </c>
       <c r="W31">
-        <v>-7.020635470974851E-5</v>
+        <v>5.4541746097795879E-4</v>
       </c>
       <c r="X31">
-        <v>-5.5200881995006354E-5</v>
+        <v>4.7167846278260071E-4</v>
       </c>
       <c r="Y31">
-        <v>-5.3642192370963064E-5</v>
+        <v>3.7430464332883741E-4</v>
       </c>
       <c r="Z31">
-        <v>-1.4093580619647489E-4</v>
+        <v>3.9961846891592922E-4</v>
       </c>
       <c r="AA31">
-        <v>-6.7493599942603096E-5</v>
+        <v>4.1993126454157974E-4</v>
       </c>
       <c r="AB31">
-        <v>-7.7202226925622238E-5</v>
+        <v>5.8562129410566716E-4</v>
       </c>
       <c r="AC31">
-        <v>-1.0695497798035567E-4</v>
+        <v>5.6020976520217679E-4</v>
       </c>
       <c r="AD31">
-        <v>-8.7829298093057659E-5</v>
+        <v>5.1296141256009734E-4</v>
       </c>
       <c r="AE31">
-        <v>-6.4178530993556844E-5</v>
+        <v>6.0715579651648868E-4</v>
       </c>
       <c r="AF31">
-        <v>1.7164990506143314E-4</v>
+        <v>1.8233689480501038E-3</v>
       </c>
       <c r="AG31">
-        <v>1.8903295102049369E-4</v>
+        <v>4.5151082976908636E-4</v>
       </c>
       <c r="AH31">
-        <v>-8.1450751014827856E-5</v>
+        <v>2.1850847526951652E-4</v>
       </c>
       <c r="AI31">
-        <v>-1.5487862703133549E-5</v>
+        <v>-6.8086976990667131E-5</v>
       </c>
       <c r="AJ31">
-        <v>-3.8719637487067901E-5</v>
+        <v>9.5797783478499422E-6</v>
       </c>
       <c r="AK31">
-        <v>-2.5157874182950984E-4</v>
+        <v>1.9102233403633885E-6</v>
       </c>
       <c r="AL31">
-        <v>-1.1116829257833943E-2</v>
+        <v>9.8875988801121499E-6</v>
+      </c>
+      <c r="AM31">
+        <v>4.8672460746263229E-5</v>
+      </c>
+      <c r="AN31">
+        <v>-6.7381055752373893E-5</v>
+      </c>
+      <c r="AO31">
+        <v>5.1055016908646946E-5</v>
+      </c>
+      <c r="AP31">
+        <v>1.5645585714936083E-5</v>
+      </c>
+      <c r="AQ31">
+        <v>1.718193633144763E-4</v>
+      </c>
+      <c r="AR31">
+        <v>1.4777191706925657E-4</v>
+      </c>
+      <c r="AS31">
+        <v>-2.4203778359033461E-5</v>
+      </c>
+      <c r="AT31">
+        <v>9.6667694645151663E-5</v>
+      </c>
+      <c r="AU31">
+        <v>-1.435500354919881E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>44</v>
       </c>
       <c r="B32">
-        <v>1.7753517746582188E-2</v>
+        <v>0.24332775117528335</v>
       </c>
       <c r="C32">
-        <v>-6.2360362102182199E-4</v>
+        <v>-7.271117272031548E-4</v>
       </c>
       <c r="D32">
-        <v>-2.2814881233977624E-5</v>
+        <v>1.0928340390111172E-5</v>
       </c>
       <c r="E32">
-        <v>3.4269065024779852E-7</v>
+        <v>-4.1506155484026742E-7</v>
       </c>
       <c r="F32">
-        <v>-3.2825900366200404E-6</v>
+        <v>2.2981709855281051E-6</v>
       </c>
       <c r="G32">
-        <v>6.9666733803318287E-6</v>
+        <v>1.7372370126222754E-6</v>
       </c>
       <c r="H32">
-        <v>-2.8612371171717375E-5</v>
+        <v>-3.2204909809660515E-4</v>
       </c>
       <c r="I32">
-        <v>-3.7788258330483321E-4</v>
+        <v>-2.8182949471123231E-4</v>
       </c>
       <c r="J32">
-        <v>6.2253562752687206E-4</v>
+        <v>6.5161772132101058E-4</v>
       </c>
       <c r="K32">
-        <v>-2.2956566892288533E-4</v>
+        <v>1.9036421294253776E-4</v>
       </c>
       <c r="L32">
-        <v>-3.788466122760974E-4</v>
+        <v>3.2497000561919527E-5</v>
       </c>
       <c r="M32">
-        <v>-5.1745765218050863E-4</v>
+        <v>1.0091281177832236E-4</v>
       </c>
       <c r="N32">
-        <v>-3.0244798523954355E-4</v>
+        <v>-9.0492745923244504E-5</v>
       </c>
       <c r="O32">
-        <v>-4.9800421270333088E-5</v>
+        <v>-2.0451028593854577E-4</v>
       </c>
       <c r="P32">
-        <v>6.9733309581051568E-5</v>
+        <v>6.6162244468470947E-5</v>
       </c>
       <c r="Q32">
-        <v>1.5095427334314274E-5</v>
+        <v>-1.6032356014389243E-4</v>
       </c>
       <c r="R32">
-        <v>-1.6425031801793328E-4</v>
+        <v>7.3008512166095155E-5</v>
       </c>
       <c r="S32">
-        <v>2.4045305354425568E-4</v>
+        <v>-2.8932826486339233E-5</v>
       </c>
       <c r="T32">
-        <v>-4.3876688809288021E-5</v>
+        <v>4.5209143831683861E-5</v>
       </c>
       <c r="U32">
-        <v>-1.739988023915335E-5</v>
+        <v>1.2104864789878457E-3</v>
       </c>
       <c r="V32">
-        <v>-1.4088841276468076E-4</v>
+        <v>1.0676035607798836E-3</v>
       </c>
       <c r="W32">
-        <v>-1.3642910401312242E-4</v>
+        <v>1.0941564630721121E-3</v>
       </c>
       <c r="X32">
-        <v>2.6955957791965262E-6</v>
+        <v>1.0995669824266912E-3</v>
       </c>
       <c r="Y32">
-        <v>4.2592642428493799E-5</v>
+        <v>1.0564705258027435E-3</v>
       </c>
       <c r="Z32">
-        <v>-7.4248406366680996E-4</v>
+        <v>7.6110835093249664E-4</v>
       </c>
       <c r="AA32">
-        <v>-2.3430696383188137E-4</v>
+        <v>1.5005502043031051E-3</v>
       </c>
       <c r="AB32">
-        <v>-1.5488015027715718E-4</v>
+        <v>1.1722058559822783E-3</v>
       </c>
       <c r="AC32">
-        <v>-2.4700683277729127E-4</v>
+        <v>1.1363961173158229E-3</v>
       </c>
       <c r="AD32">
-        <v>-2.4594542165654542E-4</v>
+        <v>1.1785385835360795E-3</v>
       </c>
       <c r="AE32">
-        <v>-9.9465801042176571E-5</v>
+        <v>1.3373328007359963E-3</v>
       </c>
       <c r="AF32">
-        <v>1.8903295102049369E-4</v>
+        <v>4.5151082976908636E-4</v>
       </c>
       <c r="AG32">
-        <v>3.3542489097109843E-3</v>
+        <v>6.3927863182933553E-3</v>
       </c>
       <c r="AH32">
-        <v>6.531406634690453E-4</v>
+        <v>-2.459112951780449E-5</v>
       </c>
       <c r="AI32">
-        <v>5.4902893653102809E-5</v>
+        <v>-1.6586132656877013E-5</v>
       </c>
       <c r="AJ32">
-        <v>-2.2795764967437418E-5</v>
+        <v>-1.0228711237910266E-4</v>
       </c>
       <c r="AK32">
-        <v>-1.7518715608664734E-3</v>
+        <v>-1.3833477004174591E-4</v>
       </c>
       <c r="AL32">
-        <v>-1.6586420923301981E-2</v>
+        <v>-8.3887713790567009E-5</v>
+      </c>
+      <c r="AM32">
+        <v>-7.867160445808861E-5</v>
+      </c>
+      <c r="AN32">
+        <v>-4.0348818599809141E-4</v>
+      </c>
+      <c r="AO32">
+        <v>-1.3972976176566466E-4</v>
+      </c>
+      <c r="AP32">
+        <v>-2.2256886806160656E-4</v>
+      </c>
+      <c r="AQ32">
+        <v>-2.5084333125675786E-4</v>
+      </c>
+      <c r="AR32">
+        <v>-2.810350244567487E-4</v>
+      </c>
+      <c r="AS32">
+        <v>-1.9242796872755803E-4</v>
+      </c>
+      <c r="AT32">
+        <v>-5.1845314167608481E-4</v>
+      </c>
+      <c r="AU32">
+        <v>7.8961086682545131E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>45</v>
       </c>
       <c r="B33">
-        <v>5.3994522380213315E-2</v>
+        <v>4.5809633885961945E-2</v>
       </c>
       <c r="C33">
-        <v>-3.1948740925249412E-4</v>
+        <v>9.4978284495575438E-5</v>
       </c>
       <c r="D33">
-        <v>-5.8848370436622149E-5</v>
+        <v>3.0283722296007079E-4</v>
       </c>
       <c r="E33">
-        <v>9.2052224732956764E-7</v>
+        <v>-4.7160196370800889E-6</v>
       </c>
       <c r="F33">
-        <v>1.1418962405719454E-6</v>
+        <v>2.4098944779464906E-5</v>
       </c>
       <c r="G33">
-        <v>7.9335378816885133E-6</v>
+        <v>-3.4679176341613998E-5</v>
       </c>
       <c r="H33">
-        <v>1.5107928011534832E-4</v>
+        <v>7.569797815032836E-4</v>
       </c>
       <c r="I33">
-        <v>-4.7657066418037536E-4</v>
+        <v>1.6466497326228687E-3</v>
       </c>
       <c r="J33">
-        <v>1.9903133381305756E-4</v>
+        <v>-5.2058688108051407E-4</v>
       </c>
       <c r="K33">
-        <v>4.8524388377189443E-6</v>
+        <v>5.9179312826791513E-4</v>
       </c>
       <c r="L33">
-        <v>-1.7468080567819037E-4</v>
+        <v>1.1432436952071193E-3</v>
       </c>
       <c r="M33">
-        <v>-3.1808389993299773E-4</v>
+        <v>3.270260660272483E-3</v>
       </c>
       <c r="N33">
-        <v>-2.5158671525581545E-4</v>
+        <v>7.1250885617729523E-4</v>
       </c>
       <c r="O33">
-        <v>-2.4422012228731121E-5</v>
+        <v>2.5856414634635536E-6</v>
       </c>
       <c r="P33">
-        <v>6.9763613772951899E-5</v>
+        <v>-2.7394837652581182E-4</v>
       </c>
       <c r="Q33">
-        <v>-4.7615599785720097E-5</v>
+        <v>2.3855001279246731E-4</v>
       </c>
       <c r="R33">
-        <v>-1.464280794781427E-4</v>
+        <v>1.4592670078669959E-3</v>
       </c>
       <c r="S33">
-        <v>5.1184794542013037E-6</v>
+        <v>-6.0707507983759519E-4</v>
       </c>
       <c r="T33">
-        <v>-7.8474926040751495E-5</v>
+        <v>8.1988955980486465E-5</v>
       </c>
       <c r="U33">
-        <v>1.9536586607487346E-4</v>
+        <v>2.0509825947148883E-3</v>
       </c>
       <c r="V33">
-        <v>9.2847571774129197E-6</v>
+        <v>1.5176362474077264E-3</v>
       </c>
       <c r="W33">
-        <v>-1.503532742914133E-4</v>
+        <v>1.9807769367150589E-3</v>
       </c>
       <c r="X33">
-        <v>4.4072758604101771E-5</v>
+        <v>1.1670659690562407E-3</v>
       </c>
       <c r="Y33">
-        <v>-8.401888011996849E-5</v>
+        <v>1.2990777626314884E-3</v>
       </c>
       <c r="Z33">
-        <v>-6.6130374815320759E-4</v>
+        <v>5.7451380598246907E-3</v>
       </c>
       <c r="AA33">
-        <v>-1.2716359259362122E-4</v>
+        <v>1.227058125451509E-3</v>
       </c>
       <c r="AB33">
-        <v>-5.8781373411021388E-5</v>
+        <v>1.994399682510405E-3</v>
       </c>
       <c r="AC33">
-        <v>-2.338641137896052E-4</v>
+        <v>1.6473841316092756E-3</v>
       </c>
       <c r="AD33">
-        <v>-9.1699161903381317E-5</v>
+        <v>1.918700779292494E-3</v>
       </c>
       <c r="AE33">
-        <v>-1.460807525187798E-4</v>
+        <v>1.6607220972941531E-3</v>
       </c>
       <c r="AF33">
-        <v>-8.1450751014827856E-5</v>
+        <v>2.1850847526951652E-4</v>
       </c>
       <c r="AG33">
-        <v>6.531406634690453E-4</v>
+        <v>-2.459112951780449E-5</v>
       </c>
       <c r="AH33">
-        <v>3.618660619111095E-3</v>
+        <v>1.9850039646644443E-2</v>
       </c>
       <c r="AI33">
-        <v>5.2839149478547866E-5</v>
+        <v>2.6164477070161467E-4</v>
       </c>
       <c r="AJ33">
-        <v>-4.3824082767767933E-6</v>
+        <v>-1.5206416807179903E-3</v>
       </c>
       <c r="AK33">
-        <v>-1.6928144441604107E-3</v>
+        <v>-1.7541743062897284E-3</v>
       </c>
       <c r="AL33">
-        <v>1.7681202666619059E-3</v>
+        <v>-1.6919492135371579E-3</v>
+      </c>
+      <c r="AM33">
+        <v>-1.9151617257306291E-3</v>
+      </c>
+      <c r="AN33">
+        <v>-2.93475396261238E-3</v>
+      </c>
+      <c r="AO33">
+        <v>-4.3609421446692571E-3</v>
+      </c>
+      <c r="AP33">
+        <v>-5.4895360432781195E-3</v>
+      </c>
+      <c r="AQ33">
+        <v>-6.8570836505904894E-3</v>
+      </c>
+      <c r="AR33">
+        <v>-6.9261432945378221E-3</v>
+      </c>
+      <c r="AS33">
+        <v>-8.6366179423270958E-3</v>
+      </c>
+      <c r="AT33">
+        <v>-9.2379292303136108E-3</v>
+      </c>
+      <c r="AU33">
+        <v>2.9876246985266947E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>46</v>
       </c>
       <c r="B34">
-        <v>-8.4209077119675332E-2</v>
+        <v>2.2701334192071758E-2</v>
       </c>
       <c r="C34">
-        <v>-8.8495808434180777E-6</v>
+        <v>7.2453697443566542E-5</v>
       </c>
       <c r="D34">
-        <v>-8.8832500070960829E-7</v>
+        <v>1.0205070861490613E-5</v>
       </c>
       <c r="E34">
-        <v>-6.0458511754425616E-8</v>
+        <v>-1.5810842167565041E-7</v>
       </c>
       <c r="F34">
-        <v>1.1742854685407121E-6</v>
+        <v>-3.1514990734461074E-7</v>
       </c>
       <c r="G34">
-        <v>-1.3426483138006019E-6</v>
+        <v>-6.7106940989004921E-7</v>
       </c>
       <c r="H34">
-        <v>-7.6571780707228705E-5</v>
+        <v>3.154097395337681E-5</v>
       </c>
       <c r="I34">
-        <v>1.2947653891524349E-4</v>
+        <v>2.4858284565457296E-5</v>
       </c>
       <c r="J34">
-        <v>-2.5799401418363972E-4</v>
+        <v>-1.070020474176034E-4</v>
       </c>
       <c r="K34">
-        <v>6.2505597259229838E-5</v>
+        <v>-7.5675133215368244E-6</v>
       </c>
       <c r="L34">
-        <v>3.8954035308220981E-5</v>
+        <v>-3.5379400575322412E-6</v>
       </c>
       <c r="M34">
-        <v>1.7991050047050865E-4</v>
+        <v>8.2097524577768834E-5</v>
       </c>
       <c r="N34">
-        <v>1.0726655595173811E-4</v>
+        <v>5.764840794305778E-5</v>
       </c>
       <c r="O34">
-        <v>-1.1038931377588696E-4</v>
+        <v>-2.0863760186579761E-6</v>
       </c>
       <c r="P34">
-        <v>7.2662368048550041E-5</v>
+        <v>-6.5547945583112544E-6</v>
       </c>
       <c r="Q34">
-        <v>-1.4975506209247366E-4</v>
+        <v>2.1424125191493481E-5</v>
       </c>
       <c r="R34">
-        <v>-8.3144337218020383E-5</v>
+        <v>8.8683531728410805E-6</v>
       </c>
       <c r="S34">
-        <v>-1.0318830751175363E-5</v>
+        <v>-1.1187267807247542E-4</v>
       </c>
       <c r="T34">
-        <v>-4.9310419049289518E-5</v>
+        <v>7.8812404870216824E-6</v>
       </c>
       <c r="U34">
-        <v>5.8301872379350954E-4</v>
+        <v>1.0120439514530529E-5</v>
       </c>
       <c r="V34">
-        <v>4.7392527083531223E-4</v>
+        <v>-3.4786042642580089E-5</v>
       </c>
       <c r="W34">
-        <v>5.984255336311437E-4</v>
+        <v>-2.499196204178031E-5</v>
       </c>
       <c r="X34">
-        <v>4.7267867859671775E-4</v>
+        <v>-4.0023519254057157E-5</v>
       </c>
       <c r="Y34">
-        <v>3.7477679368164011E-4</v>
+        <v>-3.2386604695445434E-5</v>
       </c>
       <c r="Z34">
-        <v>5.334691063070547E-4</v>
+        <v>6.145432030138547E-5</v>
       </c>
       <c r="AA34">
-        <v>4.4374869259857012E-4</v>
+        <v>-4.2796603876276568E-6</v>
       </c>
       <c r="AB34">
-        <v>6.1783562397735206E-4</v>
+        <v>-3.3695457723128695E-5</v>
       </c>
       <c r="AC34">
-        <v>5.7884200575148131E-4</v>
+        <v>2.0261670741997142E-6</v>
       </c>
       <c r="AD34">
-        <v>5.5911280825299715E-4</v>
+        <v>-3.7548381374824286E-5</v>
       </c>
       <c r="AE34">
-        <v>6.172206033571748E-4</v>
+        <v>5.9062991052573176E-5</v>
       </c>
       <c r="AF34">
-        <v>-1.5487862703133549E-5</v>
+        <v>-6.8086976990667131E-5</v>
       </c>
       <c r="AG34">
-        <v>5.4902893653102809E-5</v>
+        <v>-1.6586132656877013E-5</v>
       </c>
       <c r="AH34">
-        <v>5.2839149478547866E-5</v>
+        <v>2.6164477070161467E-4</v>
       </c>
       <c r="AI34">
-        <v>1.9634488661614087E-3</v>
+        <v>2.0587138461387084E-3</v>
       </c>
       <c r="AJ34">
-        <v>4.6873844441431878E-4</v>
+        <v>9.9067895910626407E-4</v>
       </c>
       <c r="AK34">
-        <v>6.9453470652139273E-4</v>
+        <v>9.5905456849943848E-4</v>
       </c>
       <c r="AL34">
-        <v>3.1896255378081363E-4</v>
+        <v>9.6969205972959049E-4</v>
+      </c>
+      <c r="AM34">
+        <v>9.3281252992532312E-4</v>
+      </c>
+      <c r="AN34">
+        <v>7.5910887509507419E-4</v>
+      </c>
+      <c r="AO34">
+        <v>5.2681891293791458E-4</v>
+      </c>
+      <c r="AP34">
+        <v>3.1619712601155259E-4</v>
+      </c>
+      <c r="AQ34">
+        <v>4.8374445902270302E-5</v>
+      </c>
+      <c r="AR34">
+        <v>1.29591067450259E-4</v>
+      </c>
+      <c r="AS34">
+        <v>-1.2561814202328644E-4</v>
+      </c>
+      <c r="AT34">
+        <v>-3.6418363684720748E-4</v>
+      </c>
+      <c r="AU34">
+        <v>5.7539466125018368E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
       <c r="B35">
-        <v>0.23579542775177731</v>
+        <v>0.10377880775072996</v>
       </c>
       <c r="C35">
-        <v>-5.6208873549715025E-4</v>
+        <v>-1.457459738600491E-4</v>
       </c>
       <c r="D35">
-        <v>2.6587371594577599E-5</v>
+        <v>-2.4316417688229845E-5</v>
       </c>
       <c r="E35">
-        <v>-6.3658086131453118E-7</v>
+        <v>3.9266878423489316E-7</v>
       </c>
       <c r="F35">
-        <v>1.2982559169137864E-6</v>
+        <v>-2.4126666220041149E-6</v>
       </c>
       <c r="G35">
-        <v>7.8090787094033233E-7</v>
+        <v>5.6499761215360679E-6</v>
       </c>
       <c r="H35">
-        <v>-3.2188432900283603E-4</v>
+        <v>-3.8967541752909997E-5</v>
       </c>
       <c r="I35">
-        <v>-2.3466057833660542E-4</v>
+        <v>-2.0741697122163673E-4</v>
       </c>
       <c r="J35">
-        <v>4.8224390791841681E-4</v>
+        <v>3.9067558483004642E-4</v>
       </c>
       <c r="K35">
-        <v>3.0223645115781271E-4</v>
+        <v>1.5128740919226357E-5</v>
       </c>
       <c r="L35">
-        <v>3.2940417034890528E-4</v>
+        <v>-3.2472079426416043E-5</v>
       </c>
       <c r="M35">
-        <v>7.0594813430274522E-5</v>
+        <v>-2.3163401761432464E-4</v>
       </c>
       <c r="N35">
-        <v>3.0815174623492758E-5</v>
+        <v>3.8279175976755931E-5</v>
       </c>
       <c r="O35">
-        <v>-2.0707938850017554E-4</v>
+        <v>-3.0362236680767871E-5</v>
       </c>
       <c r="P35">
-        <v>2.2607564456644093E-5</v>
+        <v>4.1123231197991042E-5</v>
       </c>
       <c r="Q35">
-        <v>-1.4551202399548608E-4</v>
+        <v>4.3310463294058299E-5</v>
       </c>
       <c r="R35">
-        <v>6.6909091201014168E-5</v>
+        <v>-1.7277727892688191E-4</v>
       </c>
       <c r="S35">
-        <v>-4.1495320219959823E-5</v>
+        <v>6.4905290289194568E-5</v>
       </c>
       <c r="T35">
-        <v>7.0617155048474742E-5</v>
+        <v>2.1108190110501169E-5</v>
       </c>
       <c r="U35">
-        <v>1.2285457859871624E-3</v>
+        <v>-1.4618571504023217E-4</v>
       </c>
       <c r="V35">
-        <v>1.0787743869131619E-3</v>
+        <v>-1.735730348375082E-4</v>
       </c>
       <c r="W35">
-        <v>1.1088562784142143E-3</v>
+        <v>-2.222834236084621E-4</v>
       </c>
       <c r="X35">
-        <v>1.1040403878310912E-3</v>
+        <v>-1.3790465488396509E-4</v>
       </c>
       <c r="Y35">
-        <v>1.0646149767165279E-3</v>
+        <v>-7.5726175257987728E-5</v>
       </c>
       <c r="Z35">
-        <v>8.1997913473877686E-4</v>
+        <v>-6.3132692777074335E-4</v>
       </c>
       <c r="AA35">
-        <v>1.4488374129706801E-3</v>
+        <v>-1.8704219703104372E-4</v>
       </c>
       <c r="AB35">
-        <v>1.1859839618537532E-3</v>
+        <v>-2.0591250652386402E-4</v>
       </c>
       <c r="AC35">
-        <v>1.1448334830974536E-3</v>
+        <v>-1.831665071103019E-4</v>
       </c>
       <c r="AD35">
-        <v>1.2034185227086307E-3</v>
+        <v>-2.5132371931357975E-4</v>
       </c>
       <c r="AE35">
-        <v>1.3315524693766337E-3</v>
+        <v>-1.2893405038363805E-4</v>
       </c>
       <c r="AF35">
-        <v>-3.8719637487067901E-5</v>
+        <v>9.5797783478499422E-6</v>
       </c>
       <c r="AG35">
-        <v>-2.2795764967437418E-5</v>
+        <v>-1.0228711237910266E-4</v>
       </c>
       <c r="AH35">
-        <v>-4.3824082767767933E-6</v>
+        <v>-1.5206416807179903E-3</v>
       </c>
       <c r="AI35">
-        <v>4.6873844441431878E-4</v>
+        <v>9.9067895910626407E-4</v>
       </c>
       <c r="AJ35">
-        <v>6.0908503018393479E-3</v>
+        <v>1.9534912635608484E-3</v>
       </c>
       <c r="AK35">
-        <v>1.9106678059232444E-4</v>
+        <v>1.2086803059714476E-3</v>
       </c>
       <c r="AL35">
-        <v>1.7263186101067751E-3</v>
+        <v>1.2121274075516915E-3</v>
+      </c>
+      <c r="AM35">
+        <v>1.224270917349096E-3</v>
+      </c>
+      <c r="AN35">
+        <v>1.3230174293690214E-3</v>
+      </c>
+      <c r="AO35">
+        <v>1.48763490612567E-3</v>
+      </c>
+      <c r="AP35">
+        <v>1.6117184704342417E-3</v>
+      </c>
+      <c r="AQ35">
+        <v>1.7816885640539321E-3</v>
+      </c>
+      <c r="AR35">
+        <v>1.7506913718790765E-3</v>
+      </c>
+      <c r="AS35">
+        <v>1.9264543201326194E-3</v>
+      </c>
+      <c r="AT35">
+        <v>2.0856640077210331E-3</v>
+      </c>
+      <c r="AU35">
+        <v>-4.5446550720419782E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36">
-        <v>3.24048591595077E-2</v>
+        <v>1.6541026439127773E-2</v>
       </c>
       <c r="C36">
-        <v>1.1514552942687786E-3</v>
+        <v>-3.2296856206759286E-4</v>
       </c>
       <c r="D36">
-        <v>3.0357656159759813E-4</v>
+        <v>-4.684455885529959E-5</v>
       </c>
       <c r="E36">
-        <v>-4.8469249737167347E-6</v>
+        <v>7.5710540428586476E-7</v>
       </c>
       <c r="F36">
-        <v>1.7491739014877301E-5</v>
+        <v>-2.7087695738902654E-6</v>
       </c>
       <c r="G36">
-        <v>-3.2066877272311491E-5</v>
+        <v>7.2554557994983922E-6</v>
       </c>
       <c r="H36">
-        <v>4.3476785753204848E-4</v>
+        <v>-3.2716154427743179E-5</v>
       </c>
       <c r="I36">
-        <v>1.8302801377575017E-3</v>
+        <v>-2.5527420565392748E-4</v>
       </c>
       <c r="J36">
-        <v>-1.7438565342721519E-3</v>
+        <v>4.0817818849773926E-4</v>
       </c>
       <c r="K36">
-        <v>4.5920266683632718E-4</v>
+        <v>4.274724938509736E-5</v>
       </c>
       <c r="L36">
-        <v>1.0603517332801963E-3</v>
+        <v>-2.1771908081161663E-5</v>
       </c>
       <c r="M36">
-        <v>3.1568656109815544E-3</v>
+        <v>-2.7036220049417943E-4</v>
       </c>
       <c r="N36">
-        <v>7.9930420359565837E-4</v>
+        <v>5.5778827835007176E-5</v>
       </c>
       <c r="O36">
-        <v>-2.2125848087024228E-5</v>
+        <v>-4.6331775413856673E-5</v>
       </c>
       <c r="P36">
-        <v>-1.4927980298021389E-4</v>
+        <v>6.2056798502229998E-5</v>
       </c>
       <c r="Q36">
-        <v>4.3247647696569719E-4</v>
+        <v>3.0243003215370273E-5</v>
       </c>
       <c r="R36">
-        <v>1.2622166399992238E-3</v>
+        <v>-2.1105419822174632E-4</v>
       </c>
       <c r="S36">
-        <v>-3.6945511760223121E-4</v>
+        <v>8.4261867914481575E-5</v>
       </c>
       <c r="T36">
-        <v>1.2677358794206325E-4</v>
+        <v>1.2126832635617896E-5</v>
       </c>
       <c r="U36">
-        <v>1.9465304900853578E-3</v>
+        <v>-2.7183823172937716E-4</v>
       </c>
       <c r="V36">
-        <v>1.3632526422522979E-3</v>
+        <v>-2.6366735097988901E-4</v>
       </c>
       <c r="W36">
-        <v>1.8957295801901343E-3</v>
+        <v>-3.0196647512403438E-4</v>
       </c>
       <c r="X36">
-        <v>1.0375629922608097E-3</v>
+        <v>-2.0639526779680107E-4</v>
       </c>
       <c r="Y36">
-        <v>1.1939845923663209E-3</v>
+        <v>-1.8932627099346711E-4</v>
       </c>
       <c r="Z36">
-        <v>5.4141513711097704E-3</v>
+        <v>-7.7921659729108194E-4</v>
       </c>
       <c r="AA36">
-        <v>1.1867053760042101E-3</v>
+        <v>-2.6031000019997516E-4</v>
       </c>
       <c r="AB36">
-        <v>1.862279970772633E-3</v>
+        <v>-2.741766309370152E-4</v>
       </c>
       <c r="AC36">
-        <v>1.5714534724323055E-3</v>
+        <v>-2.5512360444014453E-4</v>
       </c>
       <c r="AD36">
-        <v>2.0062384480775556E-3</v>
+        <v>-3.1509568979258898E-4</v>
       </c>
       <c r="AE36">
-        <v>1.2190915682234716E-3</v>
+        <v>-2.0319132742537926E-4</v>
       </c>
       <c r="AF36">
-        <v>-2.5157874182950984E-4</v>
+        <v>1.9102233403633885E-6</v>
       </c>
       <c r="AG36">
-        <v>-1.7518715608664734E-3</v>
+        <v>-1.3833477004174591E-4</v>
       </c>
       <c r="AH36">
-        <v>-1.6928144441604107E-3</v>
+        <v>-1.7541743062897284E-3</v>
       </c>
       <c r="AI36">
-        <v>6.9453470652139273E-4</v>
+        <v>9.5905456849943848E-4</v>
       </c>
       <c r="AJ36">
-        <v>1.9106678059232444E-4</v>
+        <v>1.2086803059714476E-3</v>
       </c>
       <c r="AK36">
-        <v>1.9787985782367585E-2</v>
+        <v>2.1938505865615322E-3</v>
       </c>
       <c r="AL36">
-        <v>1.7658860256053871E-2</v>
+        <v>1.2463313079657565E-3</v>
+      </c>
+      <c r="AM36">
+        <v>1.2607263913615961E-3</v>
+      </c>
+      <c r="AN36">
+        <v>1.3985584943910106E-3</v>
+      </c>
+      <c r="AO36">
+        <v>1.5984052689294427E-3</v>
+      </c>
+      <c r="AP36">
+        <v>1.7584073734055287E-3</v>
+      </c>
+      <c r="AQ36">
+        <v>1.9815454093362727E-3</v>
+      </c>
+      <c r="AR36">
+        <v>1.934079308536573E-3</v>
+      </c>
+      <c r="AS36">
+        <v>2.1539199616336154E-3</v>
+      </c>
+      <c r="AT36">
+        <v>2.35998389017778E-3</v>
+      </c>
+      <c r="AU36">
+        <v>-5.3675119861106568E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>49</v>
       </c>
       <c r="B37">
-        <v>-5.1432421204314558</v>
+        <v>8.6356912880246578E-2</v>
       </c>
       <c r="C37">
-        <v>5.6228231092129016E-3</v>
+        <v>-1.6617413575765929E-4</v>
       </c>
       <c r="D37">
-        <v>-4.3029436348681095E-3</v>
+        <v>-7.6431697608922954E-6</v>
       </c>
       <c r="E37">
-        <v>6.2095563514372068E-5</v>
+        <v>1.3172027740181858E-7</v>
       </c>
       <c r="F37">
-        <v>-5.9799285709484311E-5</v>
+        <v>-3.2572241879932559E-6</v>
       </c>
       <c r="G37">
-        <v>-1.9925253474693512E-4</v>
+        <v>7.0675536509961346E-6</v>
       </c>
       <c r="H37">
-        <v>-4.9234706080819087E-3</v>
+        <v>3.3683557643789065E-6</v>
       </c>
       <c r="I37">
-        <v>3.1865844272790933E-3</v>
+        <v>-2.7530970207390992E-4</v>
       </c>
       <c r="J37">
-        <v>-1.2535627420580798E-2</v>
+        <v>2.3551907407821232E-4</v>
       </c>
       <c r="K37">
-        <v>1.4031707666022179E-3</v>
+        <v>1.4992548610135098E-5</v>
       </c>
       <c r="L37">
-        <v>3.4777977475982241E-3</v>
+        <v>-4.8873064273347987E-5</v>
       </c>
       <c r="M37">
-        <v>4.7059739549920373E-3</v>
+        <v>-2.9106205201970845E-4</v>
       </c>
       <c r="N37">
-        <v>1.8556641604542436E-3</v>
+        <v>3.7509881698415582E-5</v>
       </c>
       <c r="O37">
-        <v>1.4954101625526666E-4</v>
+        <v>-3.6688986266927853E-5</v>
       </c>
       <c r="P37">
-        <v>-9.2389600404516471E-4</v>
+        <v>5.9141119826975729E-5</v>
       </c>
       <c r="Q37">
-        <v>-2.9369984849974707E-3</v>
+        <v>9.9187783901062129E-5</v>
       </c>
       <c r="R37">
-        <v>1.9159844410129145E-3</v>
+        <v>-2.286239893450254E-4</v>
       </c>
       <c r="S37">
-        <v>-9.865326003005076E-3</v>
+        <v>8.2409155162653752E-5</v>
       </c>
       <c r="T37">
-        <v>-8.1785769193418525E-4</v>
+        <v>9.0201323255491642E-6</v>
       </c>
       <c r="U37">
-        <v>1.2570580759453292E-3</v>
+        <v>-2.3210394694152617E-4</v>
       </c>
       <c r="V37">
-        <v>1.7711631564490352E-3</v>
+        <v>-2.1293977735779466E-4</v>
       </c>
       <c r="W37">
-        <v>4.7721010105692893E-4</v>
+        <v>-2.6065005605670287E-4</v>
       </c>
       <c r="X37">
-        <v>-7.226130790821822E-4</v>
+        <v>-2.0428646664533883E-4</v>
       </c>
       <c r="Y37">
-        <v>-1.2135758395987839E-3</v>
+        <v>-8.9944113438987917E-5</v>
       </c>
       <c r="Z37">
-        <v>6.0709668385634432E-3</v>
+        <v>-7.55944378909713E-4</v>
       </c>
       <c r="AA37">
-        <v>9.0587102558815739E-4</v>
+        <v>-2.2916673300355818E-4</v>
       </c>
       <c r="AB37">
-        <v>5.7668590562836609E-4</v>
+        <v>-2.4309541846563685E-4</v>
       </c>
       <c r="AC37">
-        <v>2.39158432356305E-3</v>
+        <v>-2.405842450373814E-4</v>
       </c>
       <c r="AD37">
-        <v>2.9904667246059887E-3</v>
+        <v>-2.776299492114919E-4</v>
       </c>
       <c r="AE37">
-        <v>-1.3411422266633921E-4</v>
+        <v>-1.5440250820237438E-4</v>
       </c>
       <c r="AF37">
-        <v>-1.1116829257833943E-2</v>
+        <v>9.8875988801121499E-6</v>
       </c>
       <c r="AG37">
-        <v>-1.6586420923301981E-2</v>
+        <v>-8.3887713790567009E-5</v>
       </c>
       <c r="AH37">
-        <v>1.7681202666619059E-3</v>
+        <v>-1.6919492135371579E-3</v>
       </c>
       <c r="AI37">
-        <v>3.1896255378081363E-4</v>
+        <v>9.6969205972959049E-4</v>
       </c>
       <c r="AJ37">
-        <v>1.7263186101067751E-3</v>
+        <v>1.2121274075516915E-3</v>
       </c>
       <c r="AK37">
-        <v>1.7658860256053871E-2</v>
+        <v>1.2463313079657565E-3</v>
       </c>
       <c r="AL37">
-        <v>0.84480597127174828</v>
+        <v>2.3711731110131269E-3</v>
+      </c>
+      <c r="AM37">
+        <v>1.261807188579545E-3</v>
+      </c>
+      <c r="AN37">
+        <v>1.3974891691330626E-3</v>
+      </c>
+      <c r="AO37">
+        <v>1.5965640807935394E-3</v>
+      </c>
+      <c r="AP37">
+        <v>1.7542830861333944E-3</v>
+      </c>
+      <c r="AQ37">
+        <v>1.9760811371085981E-3</v>
+      </c>
+      <c r="AR37">
+        <v>1.9312041297782304E-3</v>
+      </c>
+      <c r="AS37">
+        <v>2.1570518591889926E-3</v>
+      </c>
+      <c r="AT37">
+        <v>2.3393716601407735E-3</v>
+      </c>
+      <c r="AU37">
+        <v>-5.8378677398663315E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38">
+        <v>-0.1106595072101353</v>
+      </c>
+      <c r="C38">
+        <v>-2.5202347770346498E-4</v>
+      </c>
+      <c r="D38">
+        <v>-2.3035205662714532E-6</v>
+      </c>
+      <c r="E38">
+        <v>8.0026250570442185E-8</v>
+      </c>
+      <c r="F38">
+        <v>-2.6149635826030237E-6</v>
+      </c>
+      <c r="G38">
+        <v>8.5981574308133855E-6</v>
+      </c>
+      <c r="H38">
+        <v>-8.1954394023224064E-5</v>
+      </c>
+      <c r="I38">
+        <v>-2.0057950543037658E-4</v>
+      </c>
+      <c r="J38">
+        <v>3.5043202034392589E-4</v>
+      </c>
+      <c r="K38">
+        <v>-6.5965844836344948E-6</v>
+      </c>
+      <c r="L38">
+        <v>-1.0301586597259423E-4</v>
+      </c>
+      <c r="M38">
+        <v>-3.765099541791604E-4</v>
+      </c>
+      <c r="N38">
+        <v>-3.7031971759828291E-5</v>
+      </c>
+      <c r="O38">
+        <v>-4.1997182123142357E-5</v>
+      </c>
+      <c r="P38">
+        <v>6.4940417909613204E-5</v>
+      </c>
+      <c r="Q38">
+        <v>4.5659398814754717E-6</v>
+      </c>
+      <c r="R38">
+        <v>-2.3864668825181033E-4</v>
+      </c>
+      <c r="S38">
+        <v>9.9071876008128179E-5</v>
+      </c>
+      <c r="T38">
+        <v>3.5618057022892332E-5</v>
+      </c>
+      <c r="U38">
+        <v>-8.2276183820985177E-5</v>
+      </c>
+      <c r="V38">
+        <v>-1.9654147609520932E-4</v>
+      </c>
+      <c r="W38">
+        <v>-2.1341272329631613E-4</v>
+      </c>
+      <c r="X38">
+        <v>-1.2203502691173645E-4</v>
+      </c>
+      <c r="Y38">
+        <v>-1.3073068847459896E-4</v>
+      </c>
+      <c r="Z38">
+        <v>-7.6265337286278542E-4</v>
+      </c>
+      <c r="AA38">
+        <v>-1.90036299966651E-4</v>
+      </c>
+      <c r="AB38">
+        <v>-1.9128014305446069E-4</v>
+      </c>
+      <c r="AC38">
+        <v>-1.8247928078676627E-4</v>
+      </c>
+      <c r="AD38">
+        <v>-2.5042824782719629E-4</v>
+      </c>
+      <c r="AE38">
+        <v>-1.3027321429269636E-4</v>
+      </c>
+      <c r="AF38">
+        <v>4.8672460746263229E-5</v>
+      </c>
+      <c r="AG38">
+        <v>-7.867160445808861E-5</v>
+      </c>
+      <c r="AH38">
+        <v>-1.9151617257306291E-3</v>
+      </c>
+      <c r="AI38">
+        <v>9.3281252992532312E-4</v>
+      </c>
+      <c r="AJ38">
+        <v>1.224270917349096E-3</v>
+      </c>
+      <c r="AK38">
+        <v>1.2607263913615961E-3</v>
+      </c>
+      <c r="AL38">
+        <v>1.261807188579545E-3</v>
+      </c>
+      <c r="AM38">
+        <v>2.8153762862375966E-3</v>
+      </c>
+      <c r="AN38">
+        <v>1.4570563368971937E-3</v>
+      </c>
+      <c r="AO38">
+        <v>1.6794655144381472E-3</v>
+      </c>
+      <c r="AP38">
+        <v>1.8655178392094733E-3</v>
+      </c>
+      <c r="AQ38">
+        <v>2.1315698292396507E-3</v>
+      </c>
+      <c r="AR38">
+        <v>2.0778199915408701E-3</v>
+      </c>
+      <c r="AS38">
+        <v>2.3358562882466946E-3</v>
+      </c>
+      <c r="AT38">
+        <v>2.5682383677622257E-3</v>
+      </c>
+      <c r="AU38">
+        <v>-7.0598201350167422E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39">
+        <v>0.1151740156383491</v>
+      </c>
+      <c r="C39">
+        <v>-5.7337834726975227E-4</v>
+      </c>
+      <c r="D39">
+        <v>-1.1193694265442498E-4</v>
+      </c>
+      <c r="E39">
+        <v>1.7235100429788163E-6</v>
+      </c>
+      <c r="F39">
+        <v>-5.5205581438847831E-6</v>
+      </c>
+      <c r="G39">
+        <v>1.1149868566805912E-5</v>
+      </c>
+      <c r="H39">
+        <v>-4.8712541919943399E-5</v>
+      </c>
+      <c r="I39">
+        <v>-2.3033472778555037E-4</v>
+      </c>
+      <c r="J39">
+        <v>8.8045624623842803E-4</v>
+      </c>
+      <c r="K39">
+        <v>-1.6873656978281138E-4</v>
+      </c>
+      <c r="L39">
+        <v>-1.8322251015505614E-4</v>
+      </c>
+      <c r="M39">
+        <v>-5.084854321967874E-4</v>
+      </c>
+      <c r="N39">
+        <v>8.0718804269612276E-5</v>
+      </c>
+      <c r="O39">
+        <v>1.1999363142142447E-4</v>
+      </c>
+      <c r="P39">
+        <v>1.7568057079390937E-4</v>
+      </c>
+      <c r="Q39">
+        <v>3.5467282610334778E-4</v>
+      </c>
+      <c r="R39">
+        <v>-3.3336512455707886E-4</v>
+      </c>
+      <c r="S39">
+        <v>1.9136655290883959E-4</v>
+      </c>
+      <c r="T39">
+        <v>-5.6874107760989528E-5</v>
+      </c>
+      <c r="U39">
+        <v>-6.6993753514627019E-4</v>
+      </c>
+      <c r="V39">
+        <v>-6.4827926502178835E-4</v>
+      </c>
+      <c r="W39">
+        <v>-7.1922342183553347E-4</v>
+      </c>
+      <c r="X39">
+        <v>-5.5519241835815317E-4</v>
+      </c>
+      <c r="Y39">
+        <v>-4.8471743416625759E-4</v>
+      </c>
+      <c r="Z39">
+        <v>-1.5015550189061565E-3</v>
+      </c>
+      <c r="AA39">
+        <v>-6.898535800335451E-4</v>
+      </c>
+      <c r="AB39">
+        <v>-7.1768277991378815E-4</v>
+      </c>
+      <c r="AC39">
+        <v>-6.9786796141080407E-4</v>
+      </c>
+      <c r="AD39">
+        <v>-7.2337417903350345E-4</v>
+      </c>
+      <c r="AE39">
+        <v>-7.4978807089301123E-4</v>
+      </c>
+      <c r="AF39">
+        <v>-6.7381055752373893E-5</v>
+      </c>
+      <c r="AG39">
+        <v>-4.0348818599809141E-4</v>
+      </c>
+      <c r="AH39">
+        <v>-2.93475396261238E-3</v>
+      </c>
+      <c r="AI39">
+        <v>7.5910887509507419E-4</v>
+      </c>
+      <c r="AJ39">
+        <v>1.3230174293690214E-3</v>
+      </c>
+      <c r="AK39">
+        <v>1.3985584943910106E-3</v>
+      </c>
+      <c r="AL39">
+        <v>1.3974891691330626E-3</v>
+      </c>
+      <c r="AM39">
+        <v>1.4570563368971937E-3</v>
+      </c>
+      <c r="AN39">
+        <v>3.669384620960137E-3</v>
+      </c>
+      <c r="AO39">
+        <v>2.2008634291156444E-3</v>
+      </c>
+      <c r="AP39">
+        <v>2.5652120741166138E-3</v>
+      </c>
+      <c r="AQ39">
+        <v>3.0783263221678646E-3</v>
+      </c>
+      <c r="AR39">
+        <v>2.9729328137209372E-3</v>
+      </c>
+      <c r="AS39">
+        <v>3.4680637765033906E-3</v>
+      </c>
+      <c r="AT39">
+        <v>3.9047242254009748E-3</v>
+      </c>
+      <c r="AU39">
+        <v>-1.0728039126267165E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40">
+        <v>0.14393864288031458</v>
+      </c>
+      <c r="C40">
+        <v>-1.0634216363907389E-3</v>
+      </c>
+      <c r="D40">
+        <v>-7.5239833745349184E-5</v>
+      </c>
+      <c r="E40">
+        <v>1.2332699593461846E-6</v>
+      </c>
+      <c r="F40">
+        <v>-5.9756925769621121E-6</v>
+      </c>
+      <c r="G40">
+        <v>1.830714264824734E-5</v>
+      </c>
+      <c r="H40">
+        <v>-1.4521720311634644E-4</v>
+      </c>
+      <c r="I40">
+        <v>-5.5929512684262887E-4</v>
+      </c>
+      <c r="J40">
+        <v>1.1959733923385418E-3</v>
+      </c>
+      <c r="K40">
+        <v>3.0330668067853712E-5</v>
+      </c>
+      <c r="L40">
+        <v>-5.5342668254955386E-5</v>
+      </c>
+      <c r="M40">
+        <v>-7.908893289484862E-4</v>
+      </c>
+      <c r="N40">
+        <v>-4.1974521998459934E-5</v>
+      </c>
+      <c r="O40">
+        <v>-9.6630875924855327E-5</v>
+      </c>
+      <c r="P40">
+        <v>2.0055864824601751E-4</v>
+      </c>
+      <c r="Q40">
+        <v>9.9335769994272671E-5</v>
+      </c>
+      <c r="R40">
+        <v>-4.5727045328657247E-4</v>
+      </c>
+      <c r="S40">
+        <v>3.288774277324341E-4</v>
+      </c>
+      <c r="T40">
+        <v>3.1244630984451904E-6</v>
+      </c>
+      <c r="U40">
+        <v>-5.5086115599919244E-4</v>
+      </c>
+      <c r="V40">
+        <v>-4.7609468647268321E-4</v>
+      </c>
+      <c r="W40">
+        <v>-5.4323793292006825E-4</v>
+      </c>
+      <c r="X40">
+        <v>-3.0260295184230237E-4</v>
+      </c>
+      <c r="Y40">
+        <v>-2.9008563550688956E-4</v>
+      </c>
+      <c r="Z40">
+        <v>-1.8002273384082877E-3</v>
+      </c>
+      <c r="AA40">
+        <v>-4.9255068508111339E-4</v>
+      </c>
+      <c r="AB40">
+        <v>-5.7004555191601802E-4</v>
+      </c>
+      <c r="AC40">
+        <v>-5.3211042630958586E-4</v>
+      </c>
+      <c r="AD40">
+        <v>-5.9497219909908708E-4</v>
+      </c>
+      <c r="AE40">
+        <v>-5.6114431154626076E-4</v>
+      </c>
+      <c r="AF40">
+        <v>5.1055016908646946E-5</v>
+      </c>
+      <c r="AG40">
+        <v>-1.3972976176566466E-4</v>
+      </c>
+      <c r="AH40">
+        <v>-4.3609421446692571E-3</v>
+      </c>
+      <c r="AI40">
+        <v>5.2681891293791458E-4</v>
+      </c>
+      <c r="AJ40">
+        <v>1.48763490612567E-3</v>
+      </c>
+      <c r="AK40">
+        <v>1.5984052689294427E-3</v>
+      </c>
+      <c r="AL40">
+        <v>1.5965640807935394E-3</v>
+      </c>
+      <c r="AM40">
+        <v>1.6794655144381472E-3</v>
+      </c>
+      <c r="AN40">
+        <v>2.2008634291156444E-3</v>
+      </c>
+      <c r="AO40">
+        <v>4.7478607312055662E-3</v>
+      </c>
+      <c r="AP40">
+        <v>3.5758724137886274E-3</v>
+      </c>
+      <c r="AQ40">
+        <v>4.4156026967230571E-3</v>
+      </c>
+      <c r="AR40">
+        <v>4.2250605812730081E-3</v>
+      </c>
+      <c r="AS40">
+        <v>5.042979524720664E-3</v>
+      </c>
+      <c r="AT40">
+        <v>5.7907598339625773E-3</v>
+      </c>
+      <c r="AU40">
+        <v>-1.9982059859967732E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41">
+        <v>0.15430760560428189</v>
+      </c>
+      <c r="C41">
+        <v>-1.0299670305708684E-3</v>
+      </c>
+      <c r="D41">
+        <v>-1.1378451772216247E-6</v>
+      </c>
+      <c r="E41">
+        <v>6.4979115164791063E-8</v>
+      </c>
+      <c r="F41">
+        <v>-3.959923018285441E-6</v>
+      </c>
+      <c r="G41">
+        <v>2.3227775808873645E-5</v>
+      </c>
+      <c r="H41">
+        <v>-1.5670164690677053E-4</v>
+      </c>
+      <c r="I41">
+        <v>-7.4390087981907483E-4</v>
+      </c>
+      <c r="J41">
+        <v>1.3649793152613471E-3</v>
+      </c>
+      <c r="K41">
+        <v>8.6971451097401977E-5</v>
+      </c>
+      <c r="L41">
+        <v>-2.0275385750355163E-4</v>
+      </c>
+      <c r="M41">
+        <v>-1.1167793908291247E-3</v>
+      </c>
+      <c r="N41">
+        <v>-1.5922690149384306E-4</v>
+      </c>
+      <c r="O41">
+        <v>-9.0587706422052953E-5</v>
+      </c>
+      <c r="P41">
+        <v>1.5493901145648321E-4</v>
+      </c>
+      <c r="Q41">
+        <v>1.4475906175838904E-4</v>
+      </c>
+      <c r="R41">
+        <v>-5.809496865754588E-4</v>
+      </c>
+      <c r="S41">
+        <v>4.4260695638047472E-4</v>
+      </c>
+      <c r="T41">
+        <v>6.0665113662792831E-5</v>
+      </c>
+      <c r="U41">
+        <v>-7.2703373353399285E-4</v>
+      </c>
+      <c r="V41">
+        <v>-6.2808793997390193E-4</v>
+      </c>
+      <c r="W41">
+        <v>-6.4071700354734022E-4</v>
+      </c>
+      <c r="X41">
+        <v>-4.3355922614210464E-4</v>
+      </c>
+      <c r="Y41">
+        <v>-4.4846861395478853E-4</v>
+      </c>
+      <c r="Z41">
+        <v>-2.1483748786743887E-3</v>
+      </c>
+      <c r="AA41">
+        <v>-7.0352486394762576E-4</v>
+      </c>
+      <c r="AB41">
+        <v>-7.1900446572537979E-4</v>
+      </c>
+      <c r="AC41">
+        <v>-6.9552216556233778E-4</v>
+      </c>
+      <c r="AD41">
+        <v>-7.6630375265618464E-4</v>
+      </c>
+      <c r="AE41">
+        <v>-7.6722691928970575E-4</v>
+      </c>
+      <c r="AF41">
+        <v>1.5645585714936083E-5</v>
+      </c>
+      <c r="AG41">
+        <v>-2.2256886806160656E-4</v>
+      </c>
+      <c r="AH41">
+        <v>-5.4895360432781195E-3</v>
+      </c>
+      <c r="AI41">
+        <v>3.1619712601155259E-4</v>
+      </c>
+      <c r="AJ41">
+        <v>1.6117184704342417E-3</v>
+      </c>
+      <c r="AK41">
+        <v>1.7584073734055287E-3</v>
+      </c>
+      <c r="AL41">
+        <v>1.7542830861333944E-3</v>
+      </c>
+      <c r="AM41">
+        <v>1.8655178392094733E-3</v>
+      </c>
+      <c r="AN41">
+        <v>2.5652120741166138E-3</v>
+      </c>
+      <c r="AO41">
+        <v>3.5758724137886274E-3</v>
+      </c>
+      <c r="AP41">
+        <v>6.554804566725584E-3</v>
+      </c>
+      <c r="AQ41">
+        <v>5.5479912879596669E-3</v>
+      </c>
+      <c r="AR41">
+        <v>5.2866229741584123E-3</v>
+      </c>
+      <c r="AS41">
+        <v>6.3715388252059994E-3</v>
+      </c>
+      <c r="AT41">
+        <v>7.3694455975968397E-3</v>
+      </c>
+      <c r="AU41">
+        <v>-2.8178766604876067E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42">
+        <v>0.16452873543210664</v>
+      </c>
+      <c r="C42">
+        <v>-1.3219112194654131E-3</v>
+      </c>
+      <c r="D42">
+        <v>-9.5802651759463106E-5</v>
+      </c>
+      <c r="E42">
+        <v>1.4884127873182531E-6</v>
+      </c>
+      <c r="F42">
+        <v>-9.9675464334619498E-6</v>
+      </c>
+      <c r="G42">
+        <v>2.737095350730911E-5</v>
+      </c>
+      <c r="H42">
+        <v>-2.7368189950660897E-4</v>
+      </c>
+      <c r="I42">
+        <v>-9.9499561864485088E-4</v>
+      </c>
+      <c r="J42">
+        <v>1.637611452639254E-3</v>
+      </c>
+      <c r="K42">
+        <v>1.0455229263392051E-5</v>
+      </c>
+      <c r="L42">
+        <v>-1.9541615091354806E-4</v>
+      </c>
+      <c r="M42">
+        <v>-1.3730210391528167E-3</v>
+      </c>
+      <c r="N42">
+        <v>-1.9360777105775903E-4</v>
+      </c>
+      <c r="O42">
+        <v>-1.2779584307016727E-4</v>
+      </c>
+      <c r="P42">
+        <v>2.4730747425309231E-4</v>
+      </c>
+      <c r="Q42">
+        <v>1.3099041661238466E-4</v>
+      </c>
+      <c r="R42">
+        <v>-7.357300457618151E-4</v>
+      </c>
+      <c r="S42">
+        <v>5.9604308133663934E-4</v>
+      </c>
+      <c r="T42">
+        <v>1.9941947784998804E-5</v>
+      </c>
+      <c r="U42">
+        <v>-7.1527984050689247E-4</v>
+      </c>
+      <c r="V42">
+        <v>-7.6297195198454923E-4</v>
+      </c>
+      <c r="W42">
+        <v>-8.4705198227061611E-4</v>
+      </c>
+      <c r="X42">
+        <v>-4.9168352594055557E-4</v>
+      </c>
+      <c r="Y42">
+        <v>-3.8567967773249804E-4</v>
+      </c>
+      <c r="Z42">
+        <v>-2.9099270654457084E-3</v>
+      </c>
+      <c r="AA42">
+        <v>-9.2847434895327284E-4</v>
+      </c>
+      <c r="AB42">
+        <v>-8.7438373012052855E-4</v>
+      </c>
+      <c r="AC42">
+        <v>-8.1096702567763201E-4</v>
+      </c>
+      <c r="AD42">
+        <v>-9.647635663437024E-4</v>
+      </c>
+      <c r="AE42">
+        <v>-9.1736563237758482E-4</v>
+      </c>
+      <c r="AF42">
+        <v>1.718193633144763E-4</v>
+      </c>
+      <c r="AG42">
+        <v>-2.5084333125675786E-4</v>
+      </c>
+      <c r="AH42">
+        <v>-6.8570836505904894E-3</v>
+      </c>
+      <c r="AI42">
+        <v>4.8374445902270302E-5</v>
+      </c>
+      <c r="AJ42">
+        <v>1.7816885640539321E-3</v>
+      </c>
+      <c r="AK42">
+        <v>1.9815454093362727E-3</v>
+      </c>
+      <c r="AL42">
+        <v>1.9760811371085981E-3</v>
+      </c>
+      <c r="AM42">
+        <v>2.1315698292396507E-3</v>
+      </c>
+      <c r="AN42">
+        <v>3.0783263221678646E-3</v>
+      </c>
+      <c r="AO42">
+        <v>4.4156026967230571E-3</v>
+      </c>
+      <c r="AP42">
+        <v>5.5479912879596669E-3</v>
+      </c>
+      <c r="AQ42">
+        <v>9.4266633249900922E-3</v>
+      </c>
+      <c r="AR42">
+        <v>6.7100938680983531E-3</v>
+      </c>
+      <c r="AS42">
+        <v>8.1621071994462634E-3</v>
+      </c>
+      <c r="AT42">
+        <v>9.5056055801783779E-3</v>
+      </c>
+      <c r="AU42">
+        <v>-3.572923770870963E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43">
+        <v>0.16552372673721372</v>
+      </c>
+      <c r="C43">
+        <v>-1.1045134201077556E-3</v>
+      </c>
+      <c r="D43">
+        <v>-1.3270880661851378E-4</v>
+      </c>
+      <c r="E43">
+        <v>2.0900562173179122E-6</v>
+      </c>
+      <c r="F43">
+        <v>-5.7780912244787474E-6</v>
+      </c>
+      <c r="G43">
+        <v>3.003960990140152E-5</v>
+      </c>
+      <c r="H43">
+        <v>-4.9718385528769744E-5</v>
+      </c>
+      <c r="I43">
+        <v>-1.1175724890876591E-3</v>
+      </c>
+      <c r="J43">
+        <v>1.268923942076115E-3</v>
+      </c>
+      <c r="K43">
+        <v>3.3375765034787674E-5</v>
+      </c>
+      <c r="L43">
+        <v>-2.3841059653838649E-4</v>
+      </c>
+      <c r="M43">
+        <v>-1.3570425170390781E-3</v>
+      </c>
+      <c r="N43">
+        <v>-2.6714318308061551E-4</v>
+      </c>
+      <c r="O43">
+        <v>-6.759672338848069E-5</v>
+      </c>
+      <c r="P43">
+        <v>2.7308768218809126E-4</v>
+      </c>
+      <c r="Q43">
+        <v>1.3368543363995335E-4</v>
+      </c>
+      <c r="R43">
+        <v>-7.3961136516413986E-4</v>
+      </c>
+      <c r="S43">
+        <v>5.5705729321204722E-4</v>
+      </c>
+      <c r="T43">
+        <v>-8.1652238525404923E-5</v>
+      </c>
+      <c r="U43">
+        <v>-5.5307589161014562E-4</v>
+      </c>
+      <c r="V43">
+        <v>-6.8631778886263806E-4</v>
+      </c>
+      <c r="W43">
+        <v>-9.2020975575314795E-4</v>
+      </c>
+      <c r="X43">
+        <v>-4.9571584320549141E-4</v>
+      </c>
+      <c r="Y43">
+        <v>-5.5869472581503632E-4</v>
+      </c>
+      <c r="Z43">
+        <v>-2.9105284915857477E-3</v>
+      </c>
+      <c r="AA43">
+        <v>-8.7196504810442815E-4</v>
+      </c>
+      <c r="AB43">
+        <v>-8.5941822666952758E-4</v>
+      </c>
+      <c r="AC43">
+        <v>-9.1866655652736006E-4</v>
+      </c>
+      <c r="AD43">
+        <v>-8.8412400452546509E-4</v>
+      </c>
+      <c r="AE43">
+        <v>-1.0042041824657737E-3</v>
+      </c>
+      <c r="AF43">
+        <v>1.4777191706925657E-4</v>
+      </c>
+      <c r="AG43">
+        <v>-2.810350244567487E-4</v>
+      </c>
+      <c r="AH43">
+        <v>-6.9261432945378221E-3</v>
+      </c>
+      <c r="AI43">
+        <v>1.29591067450259E-4</v>
+      </c>
+      <c r="AJ43">
+        <v>1.7506913718790765E-3</v>
+      </c>
+      <c r="AK43">
+        <v>1.934079308536573E-3</v>
+      </c>
+      <c r="AL43">
+        <v>1.9312041297782304E-3</v>
+      </c>
+      <c r="AM43">
+        <v>2.0778199915408701E-3</v>
+      </c>
+      <c r="AN43">
+        <v>2.9729328137209372E-3</v>
+      </c>
+      <c r="AO43">
+        <v>4.2250605812730081E-3</v>
+      </c>
+      <c r="AP43">
+        <v>5.2866229741584123E-3</v>
+      </c>
+      <c r="AQ43">
+        <v>6.7100938680983531E-3</v>
+      </c>
+      <c r="AR43">
+        <v>9.2563034398242122E-3</v>
+      </c>
+      <c r="AS43">
+        <v>7.7792368016090033E-3</v>
+      </c>
+      <c r="AT43">
+        <v>9.0099148687359295E-3</v>
+      </c>
+      <c r="AU43">
+        <v>-3.3129869508300741E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44">
+        <v>0.20927104840211161</v>
+      </c>
+      <c r="C44">
+        <v>-1.2556812294808421E-3</v>
+      </c>
+      <c r="D44">
+        <v>-9.3061310053134394E-5</v>
+      </c>
+      <c r="E44">
+        <v>1.4802965949607964E-6</v>
+      </c>
+      <c r="F44">
+        <v>-9.4379282955830057E-6</v>
+      </c>
+      <c r="G44">
+        <v>3.9193579692237303E-5</v>
+      </c>
+      <c r="H44">
+        <v>-1.7869128148039707E-4</v>
+      </c>
+      <c r="I44">
+        <v>-1.3358052350502516E-3</v>
+      </c>
+      <c r="J44">
+        <v>1.6942946694034622E-3</v>
+      </c>
+      <c r="K44">
+        <v>-8.5717559370340323E-5</v>
+      </c>
+      <c r="L44">
+        <v>-2.6598135631398026E-4</v>
+      </c>
+      <c r="M44">
+        <v>-1.7288138069218E-3</v>
+      </c>
+      <c r="N44">
+        <v>-2.337530485738773E-4</v>
+      </c>
+      <c r="O44">
+        <v>-1.189235217487468E-4</v>
+      </c>
+      <c r="P44">
+        <v>2.7317076696866446E-4</v>
+      </c>
+      <c r="Q44">
+        <v>8.9842787849920853E-5</v>
+      </c>
+      <c r="R44">
+        <v>-9.0350903655139119E-4</v>
+      </c>
+      <c r="S44">
+        <v>7.0277096198894913E-4</v>
+      </c>
+      <c r="T44">
+        <v>-4.5860736276707136E-5</v>
+      </c>
+      <c r="U44">
+        <v>-1.1941716633905516E-3</v>
+      </c>
+      <c r="V44">
+        <v>-1.1641833501645736E-3</v>
+      </c>
+      <c r="W44">
+        <v>-1.2460338821984555E-3</v>
+      </c>
+      <c r="X44">
+        <v>-9.0969961137177258E-4</v>
+      </c>
+      <c r="Y44">
+        <v>-7.48719624499951E-4</v>
+      </c>
+      <c r="Z44">
+        <v>-3.6017276791085774E-3</v>
+      </c>
+      <c r="AA44">
+        <v>-1.1093085344636398E-3</v>
+      </c>
+      <c r="AB44">
+        <v>-1.2554051312959761E-3</v>
+      </c>
+      <c r="AC44">
+        <v>-1.22690153279853E-3</v>
+      </c>
+      <c r="AD44">
+        <v>-1.3907166561169734E-3</v>
+      </c>
+      <c r="AE44">
+        <v>-1.2504727475739323E-3</v>
+      </c>
+      <c r="AF44">
+        <v>-2.4203778359033461E-5</v>
+      </c>
+      <c r="AG44">
+        <v>-1.9242796872755803E-4</v>
+      </c>
+      <c r="AH44">
+        <v>-8.6366179423270958E-3</v>
+      </c>
+      <c r="AI44">
+        <v>-1.2561814202328644E-4</v>
+      </c>
+      <c r="AJ44">
+        <v>1.9264543201326194E-3</v>
+      </c>
+      <c r="AK44">
+        <v>2.1539199616336154E-3</v>
+      </c>
+      <c r="AL44">
+        <v>2.1570518591889926E-3</v>
+      </c>
+      <c r="AM44">
+        <v>2.3358562882466946E-3</v>
+      </c>
+      <c r="AN44">
+        <v>3.4680637765033906E-3</v>
+      </c>
+      <c r="AO44">
+        <v>5.042979524720664E-3</v>
+      </c>
+      <c r="AP44">
+        <v>6.3715388252059994E-3</v>
+      </c>
+      <c r="AQ44">
+        <v>8.1621071994462634E-3</v>
+      </c>
+      <c r="AR44">
+        <v>7.7792368016090033E-3</v>
+      </c>
+      <c r="AS44">
+        <v>1.3090100003785795E-2</v>
+      </c>
+      <c r="AT44">
+        <v>1.106577041262399E-2</v>
+      </c>
+      <c r="AU44">
+        <v>-4.2464511323986071E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45">
+        <v>0.25370903016544111</v>
+      </c>
+      <c r="C45">
+        <v>-1.6006890430100701E-3</v>
+      </c>
+      <c r="D45">
+        <v>-1.5684145108530237E-4</v>
+      </c>
+      <c r="E45">
+        <v>2.5360102618727631E-6</v>
+      </c>
+      <c r="F45">
+        <v>-1.0320583005252008E-5</v>
+      </c>
+      <c r="G45">
+        <v>3.0909749266587168E-5</v>
+      </c>
+      <c r="H45">
+        <v>-6.8387926258074759E-4</v>
+      </c>
+      <c r="I45">
+        <v>-8.0915382904970991E-4</v>
+      </c>
+      <c r="J45">
+        <v>2.0757794349520057E-3</v>
+      </c>
+      <c r="K45">
+        <v>1.4968971892091471E-4</v>
+      </c>
+      <c r="L45">
+        <v>1.0287586585005235E-4</v>
+      </c>
+      <c r="M45">
+        <v>-1.7329435947558214E-3</v>
+      </c>
+      <c r="N45">
+        <v>-1.0159839309487029E-4</v>
+      </c>
+      <c r="O45">
+        <v>-4.813663330345986E-5</v>
+      </c>
+      <c r="P45">
+        <v>2.5749343941864461E-4</v>
+      </c>
+      <c r="Q45">
+        <v>6.5267646650780486E-5</v>
+      </c>
+      <c r="R45">
+        <v>-1.007617370786248E-3</v>
+      </c>
+      <c r="S45">
+        <v>8.4387520836503097E-4</v>
+      </c>
+      <c r="T45">
+        <v>2.7897285651183948E-6</v>
+      </c>
+      <c r="U45">
+        <v>-1.0629014125968844E-3</v>
+      </c>
+      <c r="V45">
+        <v>-8.4145823694903657E-4</v>
+      </c>
+      <c r="W45">
+        <v>-1.1748513424215444E-3</v>
+      </c>
+      <c r="X45">
+        <v>-7.2904947513073148E-4</v>
+      </c>
+      <c r="Y45">
+        <v>-6.2662803021042417E-4</v>
+      </c>
+      <c r="Z45">
+        <v>-3.7268648001447038E-3</v>
+      </c>
+      <c r="AA45">
+        <v>-1.1802094484395934E-3</v>
+      </c>
+      <c r="AB45">
+        <v>-1.1123738430084363E-3</v>
+      </c>
+      <c r="AC45">
+        <v>-5.4983778432068659E-4</v>
+      </c>
+      <c r="AD45">
+        <v>-9.3255600321319031E-4</v>
+      </c>
+      <c r="AE45">
+        <v>-1.369059009961671E-3</v>
+      </c>
+      <c r="AF45">
+        <v>9.6667694645151663E-5</v>
+      </c>
+      <c r="AG45">
+        <v>-5.1845314167608481E-4</v>
+      </c>
+      <c r="AH45">
+        <v>-9.2379292303136108E-3</v>
+      </c>
+      <c r="AI45">
+        <v>-3.6418363684720748E-4</v>
+      </c>
+      <c r="AJ45">
+        <v>2.0856640077210331E-3</v>
+      </c>
+      <c r="AK45">
+        <v>2.35998389017778E-3</v>
+      </c>
+      <c r="AL45">
+        <v>2.3393716601407735E-3</v>
+      </c>
+      <c r="AM45">
+        <v>2.5682383677622257E-3</v>
+      </c>
+      <c r="AN45">
+        <v>3.9047242254009748E-3</v>
+      </c>
+      <c r="AO45">
+        <v>5.7907598339625773E-3</v>
+      </c>
+      <c r="AP45">
+        <v>7.3694455975968397E-3</v>
+      </c>
+      <c r="AQ45">
+        <v>9.5056055801783779E-3</v>
+      </c>
+      <c r="AR45">
+        <v>9.0099148687359295E-3</v>
+      </c>
+      <c r="AS45">
+        <v>1.106577041262399E-2</v>
+      </c>
+      <c r="AT45">
+        <v>1.7166815796996495E-2</v>
+      </c>
+      <c r="AU45">
+        <v>-5.0267771552855056E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46">
+        <v>-7.0597473593603679</v>
+      </c>
+      <c r="C46">
+        <v>5.8481990798482097E-3</v>
+      </c>
+      <c r="D46">
+        <v>-4.2396841960852111E-3</v>
+      </c>
+      <c r="E46">
+        <v>6.1407488751264155E-5</v>
+      </c>
+      <c r="F46">
+        <v>-6.5876529304665938E-5</v>
+      </c>
+      <c r="G46">
+        <v>-2.1693612129859707E-4</v>
+      </c>
+      <c r="H46">
+        <v>-2.1286625774757581E-3</v>
+      </c>
+      <c r="I46">
+        <v>4.9174150541547723E-3</v>
+      </c>
+      <c r="J46">
+        <v>-1.3995203087571351E-2</v>
+      </c>
+      <c r="K46">
+        <v>-1.2358924308702203E-3</v>
+      </c>
+      <c r="L46">
+        <v>-2.9534727688781959E-5</v>
+      </c>
+      <c r="M46">
+        <v>6.7403296261062586E-3</v>
+      </c>
+      <c r="N46">
+        <v>1.9703965920606229E-3</v>
+      </c>
+      <c r="O46">
+        <v>1.4987506668879616E-3</v>
+      </c>
+      <c r="P46">
+        <v>-2.7499677607067691E-4</v>
+      </c>
+      <c r="Q46">
+        <v>-5.0502537188203654E-5</v>
+      </c>
+      <c r="R46">
+        <v>3.0765591358530376E-3</v>
+      </c>
+      <c r="S46">
+        <v>-3.5672774236356931E-3</v>
+      </c>
+      <c r="T46">
+        <v>-1.5899799474807068E-3</v>
+      </c>
+      <c r="U46">
+        <v>1.153261567551158E-3</v>
+      </c>
+      <c r="V46">
+        <v>2.8190986247373512E-4</v>
+      </c>
+      <c r="W46">
+        <v>-5.5808922949478201E-6</v>
+      </c>
+      <c r="X46">
+        <v>-1.4574350763654972E-3</v>
+      </c>
+      <c r="Y46">
+        <v>-2.1364607358226317E-3</v>
+      </c>
+      <c r="Z46">
+        <v>8.9958657276790581E-3</v>
+      </c>
+      <c r="AA46">
+        <v>6.0030815431863158E-4</v>
+      </c>
+      <c r="AB46">
+        <v>-2.6724290588908337E-4</v>
+      </c>
+      <c r="AC46">
+        <v>-1.1020223973797101E-3</v>
+      </c>
+      <c r="AD46">
+        <v>1.4417730007639275E-3</v>
+      </c>
+      <c r="AE46">
+        <v>7.2285586698124515E-4</v>
+      </c>
+      <c r="AF46">
+        <v>-1.435500354919881E-3</v>
+      </c>
+      <c r="AG46">
+        <v>7.8961086682545131E-4</v>
+      </c>
+      <c r="AH46">
+        <v>2.9876246985266947E-2</v>
+      </c>
+      <c r="AI46">
+        <v>5.7539466125018368E-3</v>
+      </c>
+      <c r="AJ46">
+        <v>-4.5446550720419782E-3</v>
+      </c>
+      <c r="AK46">
+        <v>-5.3675119861106568E-3</v>
+      </c>
+      <c r="AL46">
+        <v>-5.8378677398663315E-3</v>
+      </c>
+      <c r="AM46">
+        <v>-7.0598201350167422E-3</v>
+      </c>
+      <c r="AN46">
+        <v>-1.0728039126267165E-2</v>
+      </c>
+      <c r="AO46">
+        <v>-1.9982059859967732E-2</v>
+      </c>
+      <c r="AP46">
+        <v>-2.8178766604876067E-2</v>
+      </c>
+      <c r="AQ46">
+        <v>-3.572923770870963E-2</v>
+      </c>
+      <c r="AR46">
+        <v>-3.3129869508300741E-2</v>
+      </c>
+      <c r="AS46">
+        <v>-4.2464511323986071E-2</v>
+      </c>
+      <c r="AT46">
+        <v>-5.0267771552855056E-2</v>
+      </c>
+      <c r="AU46">
+        <v>0.30229768744990659</v>
       </c>
     </row>
   </sheetData>
